--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -155,7 +155,7 @@
     <t>拉火车模式-触发局</t>
   </si>
   <si>
-    <t>10010021|10010022|10010023|10010024|10010025|10010011</t>
+    <t>10010021|10010022|10010023|10010024|10010025|10010026</t>
   </si>
   <si>
     <t>需要改出美元、火车和保险箱</t>

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -281,6 +281,12 @@
     <t>概率出大财神</t>
   </si>
   <si>
+    <t>大财神5个-jackpot</t>
+  </si>
+  <si>
+    <t>必出5个大财神</t>
+  </si>
+  <si>
     <t>财神到-变wild</t>
   </si>
   <si>
@@ -291,12 +297,6 @@
   </si>
   <si>
     <t>该处正财神&amp;横财神</t>
-  </si>
-  <si>
-    <t>大财神5个-jackpot</t>
-  </si>
-  <si>
-    <t>必出5个大财神</t>
   </si>
   <si>
     <t>埃及艳后</t>
@@ -489,12 +489,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2364,7 +2364,7 @@
     </row>
     <row r="18" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A18" s="24" t="str">
-        <f t="shared" si="1"/>
+        <f>B18&amp;C18</f>
         <v>1012002</v>
       </c>
       <c r="B18" s="25">
@@ -2389,15 +2389,13 @@
       <c r="I18" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="J18" s="24" t="s">
+      <c r="J18" s="24"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="42">
+        <v>10120021</v>
+      </c>
+      <c r="M18" s="24" t="s">
         <v>52</v>
-      </c>
-      <c r="K18" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="L18" s="42"/>
-      <c r="M18" s="24" t="s">
-        <v>54</v>
       </c>
       <c r="N18" s="25">
         <v>3</v>
@@ -2409,7 +2407,7 @@
     </row>
     <row r="19" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A19" s="24" t="str">
-        <f t="shared" si="1"/>
+        <f>B19&amp;C19</f>
         <v>1012003</v>
       </c>
       <c r="B19" s="25">
@@ -2420,7 +2418,7 @@
       </c>
       <c r="D19" s="25"/>
       <c r="E19" s="25" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F19" s="25">
         <v>1</v>
@@ -2434,11 +2432,13 @@
       <c r="I19" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="J19" s="24"/>
-      <c r="K19" s="24"/>
-      <c r="L19" s="42">
-        <v>10120031</v>
-      </c>
+      <c r="J19" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="K19" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="L19" s="42"/>
       <c r="M19" s="24" t="s">
         <v>56</v>
       </c>

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialMode" sheetId="1" r:id="rId1"/>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="59">
   <si>
     <t>id</t>
   </si>
@@ -269,7 +269,10 @@
     <t>麻将胡了</t>
   </si>
   <si>
-    <t>概率出免费</t>
+    <t>10070011|10070031|10070032|10070033|10070034|10070035|10070036|10070037|10070038</t>
+  </si>
+  <si>
+    <t>概率出免费|概率出黄金图标</t>
   </si>
   <si>
     <t>免费旋转-触发局</t>
@@ -489,12 +492,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2262,11 +2265,11 @@
       </c>
       <c r="J15" s="22"/>
       <c r="K15" s="22"/>
-      <c r="L15" s="41">
-        <v>10070011</v>
+      <c r="L15" s="41" t="s">
+        <v>47</v>
       </c>
       <c r="M15" s="22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N15" s="27">
         <v>4</v>
@@ -2288,7 +2291,7 @@
       </c>
       <c r="D16" s="23"/>
       <c r="E16" s="23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F16" s="23">
         <v>1</v>
@@ -2329,7 +2332,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E17" s="25" t="s">
         <v>22</v>
@@ -2352,7 +2355,7 @@
         <v>10120011</v>
       </c>
       <c r="M17" s="24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N17" s="25">
         <v>3</v>
@@ -2364,7 +2367,7 @@
     </row>
     <row r="18" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A18" s="24" t="str">
-        <f>B18&amp;C18</f>
+        <f t="shared" si="1"/>
         <v>1012002</v>
       </c>
       <c r="B18" s="25">
@@ -2375,7 +2378,7 @@
       </c>
       <c r="D18" s="25"/>
       <c r="E18" s="25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F18" s="25">
         <v>1</v>
@@ -2395,7 +2398,7 @@
         <v>10120021</v>
       </c>
       <c r="M18" s="24" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N18" s="25">
         <v>3</v>
@@ -2407,7 +2410,7 @@
     </row>
     <row r="19" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A19" s="24" t="str">
-        <f>B19&amp;C19</f>
+        <f t="shared" si="1"/>
         <v>1012003</v>
       </c>
       <c r="B19" s="25">
@@ -2418,7 +2421,7 @@
       </c>
       <c r="D19" s="25"/>
       <c r="E19" s="25" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F19" s="25">
         <v>1</v>
@@ -2433,14 +2436,14 @@
         <v>24</v>
       </c>
       <c r="J19" s="24" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K19" s="24" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L19" s="42"/>
       <c r="M19" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N19" s="25">
         <v>3</v>
@@ -2462,7 +2465,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>22</v>

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialMode" sheetId="1" r:id="rId1"/>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="62">
   <si>
     <t>id</t>
   </si>
@@ -303,6 +303,15 @@
   </si>
   <si>
     <t>埃及艳后</t>
+  </si>
+  <si>
+    <t>百搭</t>
+  </si>
+  <si>
+    <t>5个-jackpot</t>
+  </si>
+  <si>
+    <t>jackpot</t>
   </si>
 </sst>
 </file>
@@ -492,12 +501,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2154,7 +2163,7 @@
     </row>
     <row r="13" s="2" customFormat="1" ht="16.5" spans="1:17">
       <c r="A13" s="21" t="str">
-        <f t="shared" ref="A13:A20" si="1">B13&amp;C13</f>
+        <f t="shared" ref="A13:A22" si="1">B13&amp;C13</f>
         <v>1003002</v>
       </c>
       <c r="B13" s="15">
@@ -2484,8 +2493,12 @@
       </c>
       <c r="J20" s="21"/>
       <c r="K20" s="21"/>
-      <c r="L20" s="39"/>
-      <c r="M20" s="21"/>
+      <c r="L20" s="39">
+        <v>10140001</v>
+      </c>
+      <c r="M20" s="21" t="s">
+        <v>59</v>
+      </c>
       <c r="N20" s="27">
         <v>4</v>
       </c>
@@ -2495,36 +2508,94 @@
       <c r="Q20" s="45"/>
     </row>
     <row r="21" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A21" s="26"/>
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
-      <c r="L21" s="26"/>
-      <c r="M21" s="26"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
+      <c r="A21" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v>1014002</v>
+      </c>
+      <c r="B21" s="15">
+        <v>101400</v>
+      </c>
+      <c r="C21" s="15">
+        <v>2</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="15">
+        <v>1</v>
+      </c>
+      <c r="G21" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="21">
+        <v>2014001</v>
+      </c>
+      <c r="I21" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="J21" s="21"/>
+      <c r="K21" s="21"/>
+      <c r="L21" s="39">
+        <v>10140011</v>
+      </c>
+      <c r="M21" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="N21" s="27">
+        <v>4</v>
+      </c>
+      <c r="O21" s="27">
+        <v>3</v>
+      </c>
       <c r="Q21" s="45"/>
     </row>
-    <row r="22" s="3" customFormat="1" ht="16.5" spans="1:15">
-      <c r="A22" s="26"/>
-      <c r="B22" s="27"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="26"/>
-      <c r="J22" s="26"/>
-      <c r="K22" s="26"/>
-      <c r="L22" s="26"/>
-      <c r="M22" s="26"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
+    <row r="22" s="3" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A22" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v>1014003</v>
+      </c>
+      <c r="B22" s="15">
+        <v>101400</v>
+      </c>
+      <c r="C22" s="15">
+        <v>3</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="F22" s="15">
+        <v>1</v>
+      </c>
+      <c r="G22" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="21">
+        <v>2014001</v>
+      </c>
+      <c r="I22" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="J22" s="21"/>
+      <c r="K22" s="21"/>
+      <c r="L22" s="39">
+        <v>10140021</v>
+      </c>
+      <c r="M22" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="N22" s="27">
+        <v>4</v>
+      </c>
+      <c r="O22" s="27">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="45"/>
     </row>
     <row r="23" s="3" customFormat="1" ht="16.5" spans="1:15">
       <c r="A23" s="26"/>

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="24045" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialMode" sheetId="1" r:id="rId1"/>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="68">
   <si>
     <t>id</t>
   </si>
@@ -257,15 +257,30 @@
     <t>超级明星</t>
   </si>
   <si>
+    <t>改出不在中奖线的樱桃</t>
+  </si>
+  <si>
     <t>樱桃出现</t>
   </si>
   <si>
     <t>10030021|10030022</t>
   </si>
   <si>
+    <t>改出樱桃，必中奖</t>
+  </si>
+  <si>
     <t>幸运星模式_出倍率&amp;jackpot</t>
   </si>
   <si>
+    <t>10030041_20|10030042_10|10030043_5|10030044_2|10030045_1|</t>
+  </si>
+  <si>
+    <t>前两列必然中奖</t>
+  </si>
+  <si>
+    <t>最后一列改出百搭和jackpot</t>
+  </si>
+  <si>
     <t>麻将胡了</t>
   </si>
   <si>
@@ -306,6 +321,9 @@
   </si>
   <si>
     <t>百搭</t>
+  </si>
+  <si>
+    <t>高概率百搭</t>
   </si>
   <si>
     <t>5个-jackpot</t>
@@ -325,7 +343,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -341,12 +359,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -911,138 +923,138 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1129,7 +1141,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1139,7 +1150,7 @@
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2152,14 +2163,16 @@
       <c r="L12" s="39">
         <v>10030022</v>
       </c>
-      <c r="M12" s="21"/>
+      <c r="M12" s="21" t="s">
+        <v>43</v>
+      </c>
       <c r="N12" s="15">
         <v>3</v>
       </c>
       <c r="O12" s="15">
         <v>3</v>
       </c>
-      <c r="Q12" s="43"/>
+      <c r="Q12" s="42"/>
     </row>
     <row r="13" s="2" customFormat="1" ht="16.5" spans="1:17">
       <c r="A13" s="21" t="str">
@@ -2174,7 +2187,7 @@
       </c>
       <c r="D13" s="15"/>
       <c r="E13" s="15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F13" s="15">
         <v>1</v>
@@ -2191,16 +2204,18 @@
       <c r="J13" s="21"/>
       <c r="K13" s="21"/>
       <c r="L13" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="M13" s="21"/>
+        <v>45</v>
+      </c>
+      <c r="M13" s="21" t="s">
+        <v>46</v>
+      </c>
       <c r="N13" s="15">
         <v>3</v>
       </c>
       <c r="O13" s="15">
         <v>3</v>
       </c>
-      <c r="Q13" s="43"/>
+      <c r="Q13" s="42"/>
     </row>
     <row r="14" s="2" customFormat="1" ht="16.5" spans="1:17">
       <c r="A14" s="21" t="str">
@@ -2215,7 +2230,7 @@
       </c>
       <c r="D14" s="15"/>
       <c r="E14" s="15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F14" s="15">
         <v>1</v>
@@ -2229,19 +2244,25 @@
       <c r="I14" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
+      <c r="J14" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="K14" s="21" t="s">
+        <v>49</v>
+      </c>
       <c r="L14" s="39">
         <v>10030031</v>
       </c>
-      <c r="M14" s="40"/>
+      <c r="M14" s="21" t="s">
+        <v>50</v>
+      </c>
       <c r="N14" s="15">
         <v>3</v>
       </c>
       <c r="O14" s="15">
         <v>3</v>
       </c>
-      <c r="Q14" s="43"/>
+      <c r="Q14" s="42"/>
     </row>
     <row r="15" s="3" customFormat="1" ht="16.5" spans="1:15">
       <c r="A15" s="22" t="str">
@@ -2255,7 +2276,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E15" s="23" t="s">
         <v>22</v>
@@ -2274,11 +2295,11 @@
       </c>
       <c r="J15" s="22"/>
       <c r="K15" s="22"/>
-      <c r="L15" s="41" t="s">
-        <v>47</v>
+      <c r="L15" s="40" t="s">
+        <v>52</v>
       </c>
       <c r="M15" s="22" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="N15" s="27">
         <v>4</v>
@@ -2300,7 +2321,7 @@
       </c>
       <c r="D16" s="23"/>
       <c r="E16" s="23" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F16" s="23">
         <v>1</v>
@@ -2316,7 +2337,7 @@
       </c>
       <c r="J16" s="22"/>
       <c r="K16" s="22"/>
-      <c r="L16" s="41">
+      <c r="L16" s="40">
         <v>10070021</v>
       </c>
       <c r="M16" s="22" t="s">
@@ -2341,7 +2362,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E17" s="25" t="s">
         <v>22</v>
@@ -2360,11 +2381,11 @@
       </c>
       <c r="J17" s="24"/>
       <c r="K17" s="24"/>
-      <c r="L17" s="42">
+      <c r="L17" s="41">
         <v>10120011</v>
       </c>
       <c r="M17" s="24" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="N17" s="25">
         <v>3</v>
@@ -2372,7 +2393,7 @@
       <c r="O17" s="25">
         <v>5</v>
       </c>
-      <c r="Q17" s="44"/>
+      <c r="Q17" s="43"/>
     </row>
     <row r="18" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A18" s="24" t="str">
@@ -2387,7 +2408,7 @@
       </c>
       <c r="D18" s="25"/>
       <c r="E18" s="25" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F18" s="25">
         <v>1</v>
@@ -2403,11 +2424,11 @@
       </c>
       <c r="J18" s="24"/>
       <c r="K18" s="24"/>
-      <c r="L18" s="42">
+      <c r="L18" s="41">
         <v>10120021</v>
       </c>
       <c r="M18" s="24" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="N18" s="25">
         <v>3</v>
@@ -2415,7 +2436,7 @@
       <c r="O18" s="25">
         <v>5</v>
       </c>
-      <c r="Q18" s="44"/>
+      <c r="Q18" s="43"/>
     </row>
     <row r="19" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A19" s="24" t="str">
@@ -2430,7 +2451,7 @@
       </c>
       <c r="D19" s="25"/>
       <c r="E19" s="25" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F19" s="25">
         <v>1</v>
@@ -2445,14 +2466,14 @@
         <v>24</v>
       </c>
       <c r="J19" s="24" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K19" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="L19" s="42"/>
+        <v>61</v>
+      </c>
+      <c r="L19" s="41"/>
       <c r="M19" s="24" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="N19" s="25">
         <v>3</v>
@@ -2460,7 +2481,7 @@
       <c r="O19" s="25">
         <v>5</v>
       </c>
-      <c r="Q19" s="44"/>
+      <c r="Q19" s="43"/>
     </row>
     <row r="20" s="3" customFormat="1" ht="16.5" spans="1:17">
       <c r="A20" s="21" t="str">
@@ -2474,7 +2495,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>22</v>
@@ -2497,7 +2518,7 @@
         <v>10140001</v>
       </c>
       <c r="M20" s="21" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="N20" s="27">
         <v>4</v>
@@ -2505,7 +2526,7 @@
       <c r="O20" s="27">
         <v>3</v>
       </c>
-      <c r="Q20" s="45"/>
+      <c r="Q20" s="44"/>
     </row>
     <row r="21" s="3" customFormat="1" ht="16.5" spans="1:17">
       <c r="A21" s="21" t="str">
@@ -2519,7 +2540,7 @@
         <v>2</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E21" s="15" t="s">
         <v>22</v>
@@ -2542,7 +2563,7 @@
         <v>10140011</v>
       </c>
       <c r="M21" s="21" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="N21" s="27">
         <v>4</v>
@@ -2550,7 +2571,7 @@
       <c r="O21" s="27">
         <v>3</v>
       </c>
-      <c r="Q21" s="45"/>
+      <c r="Q21" s="44"/>
     </row>
     <row r="22" s="3" customFormat="1" ht="16.5" spans="1:17">
       <c r="A22" s="21" t="str">
@@ -2564,10 +2585,10 @@
         <v>3</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F22" s="15">
         <v>1</v>
@@ -2587,7 +2608,7 @@
         <v>10140021</v>
       </c>
       <c r="M22" s="21" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="N22" s="27">
         <v>4</v>
@@ -2595,7 +2616,7 @@
       <c r="O22" s="27">
         <v>3</v>
       </c>
-      <c r="Q22" s="45"/>
+      <c r="Q22" s="44"/>
     </row>
     <row r="23" s="3" customFormat="1" ht="16.5" spans="1:15">
       <c r="A23" s="26"/>
@@ -2615,105 +2636,105 @@
       <c r="O23" s="5"/>
     </row>
     <row r="32" ht="16.5" spans="19:19">
-      <c r="S32" s="46"/>
+      <c r="S32" s="45"/>
     </row>
     <row r="33" ht="16.5" spans="19:19">
-      <c r="S33" s="46"/>
+      <c r="S33" s="45"/>
     </row>
     <row r="34" ht="16.5" spans="19:19">
-      <c r="S34" s="46"/>
+      <c r="S34" s="45"/>
     </row>
     <row r="35" ht="16.5" spans="19:19">
-      <c r="S35" s="46"/>
+      <c r="S35" s="45"/>
     </row>
     <row r="36" ht="16.5" spans="19:19">
-      <c r="S36" s="46"/>
+      <c r="S36" s="45"/>
     </row>
     <row r="37" ht="16.5" spans="19:19">
-      <c r="S37" s="46"/>
+      <c r="S37" s="45"/>
     </row>
     <row r="47" ht="16.5" spans="19:20">
-      <c r="S47" s="47"/>
-      <c r="T47" s="47"/>
+      <c r="S47" s="46"/>
+      <c r="T47" s="46"/>
     </row>
     <row r="48" ht="16.5" spans="19:20">
-      <c r="S48" s="47"/>
-      <c r="T48" s="47"/>
+      <c r="S48" s="46"/>
+      <c r="T48" s="46"/>
     </row>
     <row r="49" ht="16.5" spans="19:20">
-      <c r="S49" s="47"/>
-      <c r="T49" s="47"/>
+      <c r="S49" s="46"/>
+      <c r="T49" s="46"/>
     </row>
     <row r="50" ht="16.5" spans="19:20">
-      <c r="S50" s="47"/>
-      <c r="T50" s="47"/>
+      <c r="S50" s="46"/>
+      <c r="T50" s="46"/>
     </row>
     <row r="51" ht="16.5" spans="19:20">
-      <c r="S51" s="47"/>
-      <c r="T51" s="47"/>
+      <c r="S51" s="46"/>
+      <c r="T51" s="46"/>
     </row>
     <row r="52" ht="16.5" spans="19:20">
-      <c r="S52" s="47"/>
-      <c r="T52" s="47"/>
+      <c r="S52" s="46"/>
+      <c r="T52" s="46"/>
     </row>
     <row r="53" ht="16.5" spans="19:20">
-      <c r="S53" s="47"/>
-      <c r="T53" s="47"/>
+      <c r="S53" s="46"/>
+      <c r="T53" s="46"/>
     </row>
     <row r="54" ht="16.5" spans="19:20">
-      <c r="S54" s="47"/>
-      <c r="T54" s="47"/>
+      <c r="S54" s="46"/>
+      <c r="T54" s="46"/>
     </row>
     <row r="55" ht="16.5" spans="20:20">
-      <c r="T55" s="47"/>
+      <c r="T55" s="46"/>
     </row>
     <row r="56" ht="16.5" spans="19:20">
-      <c r="S56" s="47"/>
-      <c r="T56" s="47"/>
+      <c r="S56" s="46"/>
+      <c r="T56" s="46"/>
     </row>
     <row r="57" ht="16.5" spans="19:20">
-      <c r="S57" s="47"/>
-      <c r="T57" s="47"/>
+      <c r="S57" s="46"/>
+      <c r="T57" s="46"/>
     </row>
     <row r="58" ht="16.5" spans="19:20">
-      <c r="S58" s="47"/>
-      <c r="T58" s="47"/>
+      <c r="S58" s="46"/>
+      <c r="T58" s="46"/>
     </row>
     <row r="59" ht="16.5" spans="19:20">
-      <c r="S59" s="47"/>
-      <c r="T59" s="47"/>
+      <c r="S59" s="46"/>
+      <c r="T59" s="46"/>
     </row>
     <row r="60" ht="16.5" spans="19:20">
-      <c r="S60" s="47"/>
-      <c r="T60" s="47"/>
+      <c r="S60" s="46"/>
+      <c r="T60" s="46"/>
     </row>
     <row r="61" ht="16.5" spans="19:20">
-      <c r="S61" s="47"/>
-      <c r="T61" s="47"/>
+      <c r="S61" s="46"/>
+      <c r="T61" s="46"/>
     </row>
     <row r="62" ht="16.5" spans="19:20">
-      <c r="S62" s="47"/>
-      <c r="T62" s="47"/>
+      <c r="S62" s="46"/>
+      <c r="T62" s="46"/>
     </row>
     <row r="63" ht="16.5" spans="19:20">
-      <c r="S63" s="47"/>
-      <c r="T63" s="47"/>
+      <c r="S63" s="46"/>
+      <c r="T63" s="46"/>
     </row>
     <row r="64" ht="16.5" spans="19:20">
-      <c r="S64" s="47"/>
-      <c r="T64" s="47"/>
+      <c r="S64" s="46"/>
+      <c r="T64" s="46"/>
     </row>
     <row r="65" ht="16.5" spans="19:20">
-      <c r="S65" s="47"/>
-      <c r="T65" s="47"/>
+      <c r="S65" s="46"/>
+      <c r="T65" s="46"/>
     </row>
     <row r="66" ht="16.5" spans="19:20">
-      <c r="S66" s="47"/>
-      <c r="T66" s="47"/>
+      <c r="S66" s="46"/>
+      <c r="T66" s="46"/>
     </row>
     <row r="67" ht="16.5" spans="19:20">
-      <c r="S67" s="47"/>
-      <c r="T67" s="47"/>
+      <c r="S67" s="46"/>
+      <c r="T67" s="46"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:K2">

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialMode" sheetId="1" r:id="rId1"/>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="70">
   <si>
     <t>id</t>
   </si>
@@ -320,7 +320,13 @@
     <t>埃及艳后</t>
   </si>
   <si>
+    <t>10140001|10140022</t>
+  </si>
+  <si>
     <t>百搭</t>
+  </si>
+  <si>
+    <t>10140011|10140022</t>
   </si>
   <si>
     <t>高概率百搭</t>
@@ -2514,11 +2520,11 @@
       </c>
       <c r="J20" s="21"/>
       <c r="K20" s="21"/>
-      <c r="L20" s="39">
-        <v>10140001</v>
+      <c r="L20" s="39" t="s">
+        <v>64</v>
       </c>
       <c r="M20" s="21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N20" s="27">
         <v>4</v>
@@ -2559,11 +2565,11 @@
       </c>
       <c r="J21" s="21"/>
       <c r="K21" s="21"/>
-      <c r="L21" s="39">
-        <v>10140011</v>
+      <c r="L21" s="39" t="s">
+        <v>66</v>
       </c>
       <c r="M21" s="21" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="N21" s="27">
         <v>4</v>
@@ -2588,7 +2594,7 @@
         <v>63</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F22" s="15">
         <v>1</v>
@@ -2608,7 +2614,7 @@
         <v>10140021</v>
       </c>
       <c r="M22" s="21" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="N22" s="27">
         <v>4</v>

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -320,13 +320,13 @@
     <t>埃及艳后</t>
   </si>
   <si>
-    <t>10140001|10140022</t>
+    <t>10140001|10140022|10140023</t>
   </si>
   <si>
     <t>百搭</t>
   </si>
   <si>
-    <t>10140011|10140022</t>
+    <t>10140011|10140022|10140023</t>
   </si>
   <si>
     <t>高概率百搭</t>

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="71">
   <si>
     <t>id</t>
   </si>
@@ -284,13 +284,16 @@
     <t>麻将胡了</t>
   </si>
   <si>
-    <t>10070011|10070031|10070032|10070033|10070034|10070035|10070036|10070037|10070038</t>
+    <t>10070011|10070012|10070031|10070032|10070033|10070034|10070035|10070036|10070037|10070038</t>
   </si>
   <si>
     <t>概率出免费|概率出黄金图标</t>
   </si>
   <si>
     <t>免费旋转-触发局</t>
+  </si>
+  <si>
+    <t>10070021|10070022|10070023|10070024</t>
   </si>
   <si>
     <t>财神</t>
@@ -519,12 +522,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2343,8 +2346,8 @@
       </c>
       <c r="J16" s="22"/>
       <c r="K16" s="22"/>
-      <c r="L16" s="40">
-        <v>10070021</v>
+      <c r="L16" s="40" t="s">
+        <v>55</v>
       </c>
       <c r="M16" s="22" t="s">
         <v>34</v>
@@ -2368,7 +2371,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E17" s="25" t="s">
         <v>22</v>
@@ -2391,7 +2394,7 @@
         <v>10120011</v>
       </c>
       <c r="M17" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N17" s="25">
         <v>3</v>
@@ -2414,7 +2417,7 @@
       </c>
       <c r="D18" s="25"/>
       <c r="E18" s="25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F18" s="25">
         <v>1</v>
@@ -2434,7 +2437,7 @@
         <v>10120021</v>
       </c>
       <c r="M18" s="24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N18" s="25">
         <v>3</v>
@@ -2457,7 +2460,7 @@
       </c>
       <c r="D19" s="25"/>
       <c r="E19" s="25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F19" s="25">
         <v>1</v>
@@ -2472,14 +2475,14 @@
         <v>24</v>
       </c>
       <c r="J19" s="24" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K19" s="24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L19" s="41"/>
       <c r="M19" s="24" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N19" s="25">
         <v>3</v>
@@ -2501,7 +2504,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>22</v>
@@ -2521,10 +2524,10 @@
       <c r="J20" s="21"/>
       <c r="K20" s="21"/>
       <c r="L20" s="39" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M20" s="21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N20" s="27">
         <v>4</v>
@@ -2546,7 +2549,7 @@
         <v>2</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E21" s="15" t="s">
         <v>22</v>
@@ -2566,10 +2569,10 @@
       <c r="J21" s="21"/>
       <c r="K21" s="21"/>
       <c r="L21" s="39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M21" s="21" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N21" s="27">
         <v>4</v>
@@ -2591,10 +2594,10 @@
         <v>3</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F22" s="15">
         <v>1</v>
@@ -2614,7 +2617,7 @@
         <v>10140021</v>
       </c>
       <c r="M22" s="21" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N22" s="27">
         <v>4</v>

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialMode" sheetId="1" r:id="rId1"/>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="72">
   <si>
     <t>id</t>
   </si>
@@ -272,10 +272,13 @@
     <t>幸运星模式_出倍率&amp;jackpot</t>
   </si>
   <si>
-    <t>10030041_20|10030042_10|10030043_5|10030044_2|10030045_1|</t>
+    <t>10030041_20|10030042_10|10030043_5|10030044_2|10030045_1</t>
   </si>
   <si>
     <t>前两列必然中奖</t>
+  </si>
+  <si>
+    <t>10030031|10030050</t>
   </si>
   <si>
     <t>最后一列改出百搭和jackpot</t>
@@ -2259,11 +2262,11 @@
       <c r="K14" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="L14" s="39">
-        <v>10030031</v>
+      <c r="L14" s="39" t="s">
+        <v>50</v>
       </c>
       <c r="M14" s="21" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N14" s="15">
         <v>3</v>
@@ -2285,7 +2288,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E15" s="23" t="s">
         <v>22</v>
@@ -2305,10 +2308,10 @@
       <c r="J15" s="22"/>
       <c r="K15" s="22"/>
       <c r="L15" s="40" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M15" s="22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N15" s="27">
         <v>4</v>
@@ -2330,7 +2333,7 @@
       </c>
       <c r="D16" s="23"/>
       <c r="E16" s="23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F16" s="23">
         <v>1</v>
@@ -2347,7 +2350,7 @@
       <c r="J16" s="22"/>
       <c r="K16" s="22"/>
       <c r="L16" s="40" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M16" s="22" t="s">
         <v>34</v>
@@ -2371,7 +2374,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E17" s="25" t="s">
         <v>22</v>
@@ -2394,7 +2397,7 @@
         <v>10120011</v>
       </c>
       <c r="M17" s="24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N17" s="25">
         <v>3</v>
@@ -2417,7 +2420,7 @@
       </c>
       <c r="D18" s="25"/>
       <c r="E18" s="25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F18" s="25">
         <v>1</v>
@@ -2437,7 +2440,7 @@
         <v>10120021</v>
       </c>
       <c r="M18" s="24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N18" s="25">
         <v>3</v>
@@ -2460,7 +2463,7 @@
       </c>
       <c r="D19" s="25"/>
       <c r="E19" s="25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F19" s="25">
         <v>1</v>
@@ -2475,14 +2478,14 @@
         <v>24</v>
       </c>
       <c r="J19" s="24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K19" s="24" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L19" s="41"/>
       <c r="M19" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N19" s="25">
         <v>3</v>
@@ -2504,7 +2507,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>22</v>
@@ -2524,10 +2527,10 @@
       <c r="J20" s="21"/>
       <c r="K20" s="21"/>
       <c r="L20" s="39" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M20" s="21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N20" s="27">
         <v>4</v>
@@ -2549,7 +2552,7 @@
         <v>2</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E21" s="15" t="s">
         <v>22</v>
@@ -2569,10 +2572,10 @@
       <c r="J21" s="21"/>
       <c r="K21" s="21"/>
       <c r="L21" s="39" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M21" s="21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="N21" s="27">
         <v>4</v>
@@ -2594,10 +2597,10 @@
         <v>3</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F22" s="15">
         <v>1</v>
@@ -2617,7 +2620,7 @@
         <v>10140021</v>
       </c>
       <c r="M22" s="21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="N22" s="27">
         <v>4</v>

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="78">
   <si>
     <t>id</t>
   </si>
@@ -342,6 +342,24 @@
   </si>
   <si>
     <t>jackpot</t>
+  </si>
+  <si>
+    <t>财富银行</t>
+  </si>
+  <si>
+    <t>10240011|10240012</t>
+  </si>
+  <si>
+    <t>10240021|10240022|10240023|10240024|10240025|10240026</t>
+  </si>
+  <si>
+    <t>10240031|10240032</t>
+  </si>
+  <si>
+    <t>10240051|10240052</t>
+  </si>
+  <si>
+    <t>10240071|10240072|10240073|10240074|10240075|10240076</t>
   </si>
 </sst>
 </file>
@@ -525,12 +543,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1066,7 +1084,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1115,27 +1133,26 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1738,20 +1755,20 @@
         <v>4</v>
       </c>
       <c r="I1" s="8"/>
-      <c r="J1" s="28" t="s">
+      <c r="J1" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="28"/>
-      <c r="L1" s="29" t="s">
+      <c r="K1" s="26"/>
+      <c r="L1" s="27" t="s">
         <v>6</v>
       </c>
       <c r="M1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="30" t="s">
+      <c r="N1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="30" t="s">
+      <c r="O1" s="28" t="s">
         <v>9</v>
       </c>
       <c r="Q1"/>
@@ -1776,18 +1793,18 @@
         <v>10</v>
       </c>
       <c r="I2" s="8"/>
-      <c r="J2" s="31" t="s">
+      <c r="J2" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="32"/>
-      <c r="L2" s="33" t="s">
+      <c r="K2" s="30"/>
+      <c r="L2" s="31" t="s">
         <v>12</v>
       </c>
       <c r="M2" s="8"/>
-      <c r="N2" s="27" t="s">
+      <c r="N2" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="27" t="s">
+      <c r="O2" s="32" t="s">
         <v>10</v>
       </c>
       <c r="Q2"/>
@@ -1812,18 +1829,18 @@
         <v>16</v>
       </c>
       <c r="I3" s="10"/>
-      <c r="J3" s="34" t="s">
+      <c r="J3" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="34"/>
-      <c r="L3" s="35" t="s">
+      <c r="K3" s="33"/>
+      <c r="L3" s="34" t="s">
         <v>18</v>
       </c>
       <c r="M3" s="10"/>
-      <c r="N3" s="27" t="s">
+      <c r="N3" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="27" t="s">
+      <c r="O3" s="32" t="s">
         <v>20</v>
       </c>
       <c r="Q3"/>
@@ -1837,12 +1854,12 @@
       <c r="G4" s="8"/>
       <c r="H4" s="9"/>
       <c r="I4" s="8"/>
-      <c r="J4" s="36"/>
-      <c r="K4" s="36"/>
-      <c r="L4" s="29"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="27"/>
       <c r="M4" s="8"/>
-      <c r="N4" s="27"/>
-      <c r="O4" s="27"/>
+      <c r="N4" s="32"/>
+      <c r="O4" s="32"/>
       <c r="Q4"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="16.5" spans="1:15">
@@ -1876,16 +1893,16 @@
       </c>
       <c r="J5" s="13"/>
       <c r="K5" s="13"/>
-      <c r="L5" s="37" t="s">
+      <c r="L5" s="36" t="s">
         <v>25</v>
       </c>
       <c r="M5" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="N5" s="27">
+      <c r="N5" s="32">
         <v>4</v>
       </c>
-      <c r="O5" s="27">
+      <c r="O5" s="32">
         <v>5</v>
       </c>
     </row>
@@ -1918,16 +1935,16 @@
       </c>
       <c r="J6" s="13"/>
       <c r="K6" s="13"/>
-      <c r="L6" s="38" t="s">
+      <c r="L6" s="37" t="s">
         <v>28</v>
       </c>
       <c r="M6" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="N6" s="27">
+      <c r="N6" s="32">
         <v>4</v>
       </c>
-      <c r="O6" s="27">
+      <c r="O6" s="32">
         <v>5</v>
       </c>
     </row>
@@ -1960,16 +1977,16 @@
       </c>
       <c r="J7" s="13"/>
       <c r="K7" s="13"/>
-      <c r="L7" s="37" t="s">
+      <c r="L7" s="36" t="s">
         <v>31</v>
       </c>
       <c r="M7" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="N7" s="27">
+      <c r="N7" s="32">
         <v>4</v>
       </c>
-      <c r="O7" s="27">
+      <c r="O7" s="32">
         <v>5</v>
       </c>
     </row>
@@ -2002,16 +2019,16 @@
       </c>
       <c r="J8" s="13"/>
       <c r="K8" s="13"/>
-      <c r="L8" s="37">
+      <c r="L8" s="36">
         <v>10010041</v>
       </c>
       <c r="M8" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="N8" s="27">
+      <c r="N8" s="32">
         <v>4</v>
       </c>
-      <c r="O8" s="27">
+      <c r="O8" s="32">
         <v>5</v>
       </c>
     </row>
@@ -2044,16 +2061,16 @@
       </c>
       <c r="J9" s="13"/>
       <c r="K9" s="13"/>
-      <c r="L9" s="37" t="s">
+      <c r="L9" s="36" t="s">
         <v>36</v>
       </c>
       <c r="M9" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="N9" s="27">
+      <c r="N9" s="32">
         <v>4</v>
       </c>
-      <c r="O9" s="27">
+      <c r="O9" s="32">
         <v>5</v>
       </c>
     </row>
@@ -2086,16 +2103,16 @@
       </c>
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
-      <c r="L10" s="37">
+      <c r="L10" s="36">
         <v>10010061</v>
       </c>
       <c r="M10" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="N10" s="27">
+      <c r="N10" s="32">
         <v>4</v>
       </c>
-      <c r="O10" s="27">
+      <c r="O10" s="32">
         <v>5</v>
       </c>
     </row>
@@ -2128,16 +2145,16 @@
       </c>
       <c r="J11" s="13"/>
       <c r="K11" s="13"/>
-      <c r="L11" s="38" t="s">
+      <c r="L11" s="37" t="s">
         <v>41</v>
       </c>
       <c r="M11" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="N11" s="27">
+      <c r="N11" s="32">
         <v>4</v>
       </c>
-      <c r="O11" s="27">
+      <c r="O11" s="32">
         <v>5</v>
       </c>
     </row>
@@ -2172,7 +2189,7 @@
       </c>
       <c r="J12" s="21"/>
       <c r="K12" s="21"/>
-      <c r="L12" s="39">
+      <c r="L12" s="38">
         <v>10030022</v>
       </c>
       <c r="M12" s="21" t="s">
@@ -2184,11 +2201,11 @@
       <c r="O12" s="15">
         <v>3</v>
       </c>
-      <c r="Q12" s="42"/>
+      <c r="Q12" s="41"/>
     </row>
     <row r="13" s="2" customFormat="1" ht="16.5" spans="1:17">
       <c r="A13" s="21" t="str">
-        <f t="shared" ref="A13:A22" si="1">B13&amp;C13</f>
+        <f t="shared" ref="A13:A29" si="1">B13&amp;C13</f>
         <v>1003002</v>
       </c>
       <c r="B13" s="15">
@@ -2215,7 +2232,7 @@
       </c>
       <c r="J13" s="21"/>
       <c r="K13" s="21"/>
-      <c r="L13" s="39" t="s">
+      <c r="L13" s="38" t="s">
         <v>45</v>
       </c>
       <c r="M13" s="21" t="s">
@@ -2227,7 +2244,7 @@
       <c r="O13" s="15">
         <v>3</v>
       </c>
-      <c r="Q13" s="42"/>
+      <c r="Q13" s="41"/>
     </row>
     <row r="14" s="2" customFormat="1" ht="16.5" spans="1:17">
       <c r="A14" s="21" t="str">
@@ -2262,7 +2279,7 @@
       <c r="K14" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="L14" s="39" t="s">
+      <c r="L14" s="38" t="s">
         <v>50</v>
       </c>
       <c r="M14" s="21" t="s">
@@ -2274,7 +2291,7 @@
       <c r="O14" s="15">
         <v>3</v>
       </c>
-      <c r="Q14" s="42"/>
+      <c r="Q14" s="41"/>
     </row>
     <row r="15" s="3" customFormat="1" ht="16.5" spans="1:15">
       <c r="A15" s="22" t="str">
@@ -2307,16 +2324,16 @@
       </c>
       <c r="J15" s="22"/>
       <c r="K15" s="22"/>
-      <c r="L15" s="40" t="s">
+      <c r="L15" s="39" t="s">
         <v>53</v>
       </c>
       <c r="M15" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="N15" s="27">
+      <c r="N15" s="32">
         <v>4</v>
       </c>
-      <c r="O15" s="27">
+      <c r="O15" s="32">
         <v>5</v>
       </c>
     </row>
@@ -2349,16 +2366,16 @@
       </c>
       <c r="J16" s="22"/>
       <c r="K16" s="22"/>
-      <c r="L16" s="40" t="s">
+      <c r="L16" s="39" t="s">
         <v>56</v>
       </c>
       <c r="M16" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="N16" s="27">
+      <c r="N16" s="32">
         <v>4</v>
       </c>
-      <c r="O16" s="27">
+      <c r="O16" s="32">
         <v>5</v>
       </c>
     </row>
@@ -2393,7 +2410,7 @@
       </c>
       <c r="J17" s="24"/>
       <c r="K17" s="24"/>
-      <c r="L17" s="41">
+      <c r="L17" s="40">
         <v>10120011</v>
       </c>
       <c r="M17" s="24" t="s">
@@ -2405,7 +2422,7 @@
       <c r="O17" s="25">
         <v>5</v>
       </c>
-      <c r="Q17" s="43"/>
+      <c r="Q17" s="42"/>
     </row>
     <row r="18" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A18" s="24" t="str">
@@ -2436,7 +2453,7 @@
       </c>
       <c r="J18" s="24"/>
       <c r="K18" s="24"/>
-      <c r="L18" s="41">
+      <c r="L18" s="40">
         <v>10120021</v>
       </c>
       <c r="M18" s="24" t="s">
@@ -2448,7 +2465,7 @@
       <c r="O18" s="25">
         <v>5</v>
       </c>
-      <c r="Q18" s="43"/>
+      <c r="Q18" s="42"/>
     </row>
     <row r="19" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A19" s="24" t="str">
@@ -2483,7 +2500,7 @@
       <c r="K19" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="L19" s="41"/>
+      <c r="L19" s="40"/>
       <c r="M19" s="24" t="s">
         <v>64</v>
       </c>
@@ -2493,7 +2510,7 @@
       <c r="O19" s="25">
         <v>5</v>
       </c>
-      <c r="Q19" s="43"/>
+      <c r="Q19" s="42"/>
     </row>
     <row r="20" s="3" customFormat="1" ht="16.5" spans="1:17">
       <c r="A20" s="21" t="str">
@@ -2526,19 +2543,19 @@
       </c>
       <c r="J20" s="21"/>
       <c r="K20" s="21"/>
-      <c r="L20" s="39" t="s">
+      <c r="L20" s="38" t="s">
         <v>66</v>
       </c>
       <c r="M20" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="N20" s="27">
+      <c r="N20" s="32">
         <v>4</v>
       </c>
-      <c r="O20" s="27">
+      <c r="O20" s="32">
         <v>3</v>
       </c>
-      <c r="Q20" s="44"/>
+      <c r="Q20" s="43"/>
     </row>
     <row r="21" s="3" customFormat="1" ht="16.5" spans="1:17">
       <c r="A21" s="21" t="str">
@@ -2571,19 +2588,19 @@
       </c>
       <c r="J21" s="21"/>
       <c r="K21" s="21"/>
-      <c r="L21" s="39" t="s">
+      <c r="L21" s="38" t="s">
         <v>68</v>
       </c>
       <c r="M21" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="N21" s="27">
+      <c r="N21" s="32">
         <v>4</v>
       </c>
-      <c r="O21" s="27">
+      <c r="O21" s="32">
         <v>3</v>
       </c>
-      <c r="Q21" s="44"/>
+      <c r="Q21" s="43"/>
     </row>
     <row r="22" s="3" customFormat="1" ht="16.5" spans="1:17">
       <c r="A22" s="21" t="str">
@@ -2616,137 +2633,416 @@
       </c>
       <c r="J22" s="21"/>
       <c r="K22" s="21"/>
-      <c r="L22" s="39">
+      <c r="L22" s="38">
         <v>10140021</v>
       </c>
       <c r="M22" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="N22" s="27">
+      <c r="N22" s="32">
         <v>4</v>
       </c>
-      <c r="O22" s="27">
+      <c r="O22" s="32">
         <v>3</v>
       </c>
-      <c r="Q22" s="44"/>
-    </row>
-    <row r="23" s="3" customFormat="1" ht="16.5" spans="1:15">
-      <c r="A23" s="26"/>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
-      <c r="K23" s="26"/>
-      <c r="L23" s="26"/>
-      <c r="M23" s="26"/>
-      <c r="N23" s="5"/>
-      <c r="O23" s="5"/>
+      <c r="Q22" s="43"/>
+    </row>
+    <row r="23" s="1" customFormat="1" ht="16.5" spans="1:15">
+      <c r="A23" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>1024001</v>
+      </c>
+      <c r="B23" s="14">
+        <v>102400</v>
+      </c>
+      <c r="C23" s="14">
+        <v>1</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" s="14">
+        <v>1</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="13">
+        <v>2024001</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="M23" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="N23" s="32">
+        <v>4</v>
+      </c>
+      <c r="O23" s="32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="16.5" spans="1:15">
+      <c r="A24" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>1024002</v>
+      </c>
+      <c r="B24" s="14">
+        <v>102400</v>
+      </c>
+      <c r="C24" s="14">
+        <v>2</v>
+      </c>
+      <c r="D24" s="14"/>
+      <c r="E24" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" s="14">
+        <v>1</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" s="13">
+        <v>2024001</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="37" t="s">
+        <v>74</v>
+      </c>
+      <c r="M24" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="N24" s="32">
+        <v>4</v>
+      </c>
+      <c r="O24" s="32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="16.5" spans="1:15">
+      <c r="A25" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>1024003</v>
+      </c>
+      <c r="B25" s="14">
+        <v>102400</v>
+      </c>
+      <c r="C25" s="14">
+        <v>3</v>
+      </c>
+      <c r="D25" s="14"/>
+      <c r="E25" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="F25" s="14">
+        <v>1</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="13">
+        <v>2024001</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="36" t="s">
+        <v>75</v>
+      </c>
+      <c r="M25" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="N25" s="32">
+        <v>4</v>
+      </c>
+      <c r="O25" s="32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="16.5" spans="1:15">
+      <c r="A26" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>1024004</v>
+      </c>
+      <c r="B26" s="14">
+        <v>102400</v>
+      </c>
+      <c r="C26" s="14">
+        <v>4</v>
+      </c>
+      <c r="D26" s="14"/>
+      <c r="E26" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="F26" s="19">
+        <v>1</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="13">
+        <v>2024001</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="36">
+        <v>10240041</v>
+      </c>
+      <c r="M26" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="N26" s="32">
+        <v>4</v>
+      </c>
+      <c r="O26" s="32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="16.5" spans="1:15">
+      <c r="A27" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>1024005</v>
+      </c>
+      <c r="B27" s="14">
+        <v>102400</v>
+      </c>
+      <c r="C27" s="14">
+        <v>5</v>
+      </c>
+      <c r="D27" s="14"/>
+      <c r="E27" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="F27" s="19">
+        <v>1</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="H27" s="13">
+        <v>2024001</v>
+      </c>
+      <c r="I27" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+      <c r="L27" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="M27" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="N27" s="32">
+        <v>4</v>
+      </c>
+      <c r="O27" s="32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="16.5" spans="1:15">
+      <c r="A28" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>1024006</v>
+      </c>
+      <c r="B28" s="14">
+        <v>102400</v>
+      </c>
+      <c r="C28" s="14">
+        <v>6</v>
+      </c>
+      <c r="D28" s="14"/>
+      <c r="E28" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="F28" s="19">
+        <v>1</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28" s="13">
+        <v>2024001</v>
+      </c>
+      <c r="I28" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+      <c r="L28" s="36">
+        <v>10240061</v>
+      </c>
+      <c r="M28" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="N28" s="32">
+        <v>4</v>
+      </c>
+      <c r="O28" s="32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="16.5" spans="1:15">
+      <c r="A29" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>1024007</v>
+      </c>
+      <c r="B29" s="14">
+        <v>102400</v>
+      </c>
+      <c r="C29" s="14">
+        <v>7</v>
+      </c>
+      <c r="D29" s="14"/>
+      <c r="E29" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F29" s="14">
+        <v>1</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="H29" s="13">
+        <v>2024001</v>
+      </c>
+      <c r="I29" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="37" t="s">
+        <v>77</v>
+      </c>
+      <c r="M29" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="N29" s="32">
+        <v>4</v>
+      </c>
+      <c r="O29" s="32">
+        <v>5</v>
+      </c>
     </row>
     <row r="32" ht="16.5" spans="19:19">
-      <c r="S32" s="45"/>
+      <c r="S32" s="44"/>
     </row>
     <row r="33" ht="16.5" spans="19:19">
-      <c r="S33" s="45"/>
+      <c r="S33" s="44"/>
     </row>
     <row r="34" ht="16.5" spans="19:19">
-      <c r="S34" s="45"/>
+      <c r="S34" s="44"/>
     </row>
     <row r="35" ht="16.5" spans="19:19">
-      <c r="S35" s="45"/>
+      <c r="S35" s="44"/>
     </row>
     <row r="36" ht="16.5" spans="19:19">
-      <c r="S36" s="45"/>
+      <c r="S36" s="44"/>
     </row>
     <row r="37" ht="16.5" spans="19:19">
-      <c r="S37" s="45"/>
+      <c r="S37" s="44"/>
     </row>
     <row r="47" ht="16.5" spans="19:20">
-      <c r="S47" s="46"/>
-      <c r="T47" s="46"/>
+      <c r="S47" s="45"/>
+      <c r="T47" s="45"/>
     </row>
     <row r="48" ht="16.5" spans="19:20">
-      <c r="S48" s="46"/>
-      <c r="T48" s="46"/>
+      <c r="S48" s="45"/>
+      <c r="T48" s="45"/>
     </row>
     <row r="49" ht="16.5" spans="19:20">
-      <c r="S49" s="46"/>
-      <c r="T49" s="46"/>
+      <c r="S49" s="45"/>
+      <c r="T49" s="45"/>
     </row>
     <row r="50" ht="16.5" spans="19:20">
-      <c r="S50" s="46"/>
-      <c r="T50" s="46"/>
+      <c r="S50" s="45"/>
+      <c r="T50" s="45"/>
     </row>
     <row r="51" ht="16.5" spans="19:20">
-      <c r="S51" s="46"/>
-      <c r="T51" s="46"/>
+      <c r="S51" s="45"/>
+      <c r="T51" s="45"/>
     </row>
     <row r="52" ht="16.5" spans="19:20">
-      <c r="S52" s="46"/>
-      <c r="T52" s="46"/>
+      <c r="S52" s="45"/>
+      <c r="T52" s="45"/>
     </row>
     <row r="53" ht="16.5" spans="19:20">
-      <c r="S53" s="46"/>
-      <c r="T53" s="46"/>
+      <c r="S53" s="45"/>
+      <c r="T53" s="45"/>
     </row>
     <row r="54" ht="16.5" spans="19:20">
-      <c r="S54" s="46"/>
-      <c r="T54" s="46"/>
+      <c r="S54" s="45"/>
+      <c r="T54" s="45"/>
     </row>
     <row r="55" ht="16.5" spans="20:20">
-      <c r="T55" s="46"/>
+      <c r="T55" s="45"/>
     </row>
     <row r="56" ht="16.5" spans="19:20">
-      <c r="S56" s="46"/>
-      <c r="T56" s="46"/>
+      <c r="S56" s="45"/>
+      <c r="T56" s="45"/>
     </row>
     <row r="57" ht="16.5" spans="19:20">
-      <c r="S57" s="46"/>
-      <c r="T57" s="46"/>
+      <c r="S57" s="45"/>
+      <c r="T57" s="45"/>
     </row>
     <row r="58" ht="16.5" spans="19:20">
-      <c r="S58" s="46"/>
-      <c r="T58" s="46"/>
+      <c r="S58" s="45"/>
+      <c r="T58" s="45"/>
     </row>
     <row r="59" ht="16.5" spans="19:20">
-      <c r="S59" s="46"/>
-      <c r="T59" s="46"/>
+      <c r="S59" s="45"/>
+      <c r="T59" s="45"/>
     </row>
     <row r="60" ht="16.5" spans="19:20">
-      <c r="S60" s="46"/>
-      <c r="T60" s="46"/>
+      <c r="S60" s="45"/>
+      <c r="T60" s="45"/>
     </row>
     <row r="61" ht="16.5" spans="19:20">
-      <c r="S61" s="46"/>
-      <c r="T61" s="46"/>
+      <c r="S61" s="45"/>
+      <c r="T61" s="45"/>
     </row>
     <row r="62" ht="16.5" spans="19:20">
-      <c r="S62" s="46"/>
-      <c r="T62" s="46"/>
+      <c r="S62" s="45"/>
+      <c r="T62" s="45"/>
     </row>
     <row r="63" ht="16.5" spans="19:20">
-      <c r="S63" s="46"/>
-      <c r="T63" s="46"/>
+      <c r="S63" s="45"/>
+      <c r="T63" s="45"/>
     </row>
     <row r="64" ht="16.5" spans="19:20">
-      <c r="S64" s="46"/>
-      <c r="T64" s="46"/>
+      <c r="S64" s="45"/>
+      <c r="T64" s="45"/>
     </row>
     <row r="65" ht="16.5" spans="19:20">
-      <c r="S65" s="46"/>
-      <c r="T65" s="46"/>
+      <c r="S65" s="45"/>
+      <c r="T65" s="45"/>
     </row>
     <row r="66" ht="16.5" spans="19:20">
-      <c r="S66" s="46"/>
-      <c r="T66" s="46"/>
+      <c r="S66" s="45"/>
+      <c r="T66" s="45"/>
     </row>
     <row r="67" ht="16.5" spans="19:20">
-      <c r="S67" s="46"/>
-      <c r="T67" s="46"/>
+      <c r="S67" s="45"/>
+      <c r="T67" s="45"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:K2">

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialMode" sheetId="1" r:id="rId1"/>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="94">
   <si>
     <t>id</t>
   </si>
@@ -360,6 +360,54 @@
   </si>
   <si>
     <t>10240071|10240072|10240073|10240074|10240075|10240076</t>
+  </si>
+  <si>
+    <t>圣诞狂欢夜</t>
+  </si>
+  <si>
+    <t>10170011|10170012|10170031|10170032|10170033|10170034|10170035|10170036|10170037|10170038</t>
+  </si>
+  <si>
+    <t>10170021|10170022|10170023|10170024</t>
+  </si>
+  <si>
+    <t>JACKPOT大奖</t>
+  </si>
+  <si>
+    <t>10170039|10170040</t>
+  </si>
+  <si>
+    <t>改出2个SCATTER+JACKPOT</t>
+  </si>
+  <si>
+    <t>雷神</t>
+  </si>
+  <si>
+    <t>改出2个SCATTER</t>
+  </si>
+  <si>
+    <t>免费</t>
+  </si>
+  <si>
+    <t>10220001|10220002|10220003</t>
+  </si>
+  <si>
+    <t>改出3个SCATTER</t>
+  </si>
+  <si>
+    <t>10220031|10220032</t>
+  </si>
+  <si>
+    <t>火焰免费</t>
+  </si>
+  <si>
+    <t>10220011|10220099|10220012</t>
+  </si>
+  <si>
+    <t>冰冻免费</t>
+  </si>
+  <si>
+    <t>10220021|10220099|10220012</t>
   </si>
 </sst>
 </file>
@@ -373,7 +421,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -389,12 +437,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -587,6 +629,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -612,18 +666,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -953,143 +995,144 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1097,11 +1140,39 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -1109,77 +1180,68 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1729,1320 +1791,1641 @@
     <col min="11" max="11" width="16.75" customWidth="1"/>
     <col min="12" max="12" width="53.25" customWidth="1"/>
     <col min="13" max="13" width="21.6083333333333" customWidth="1"/>
-    <col min="14" max="15" width="9" style="5"/>
+    <col min="14" max="15" width="9" style="6"/>
     <col min="16" max="16" width="15" customWidth="1"/>
-    <col min="17" max="17" width="23.75" style="6" customWidth="1"/>
+    <col min="17" max="17" width="23.75" style="7" customWidth="1"/>
     <col min="18" max="18" width="60.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:17">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="9" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="8"/>
-      <c r="H1" s="9" t="s">
+      <c r="G1" s="9"/>
+      <c r="H1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="8"/>
-      <c r="J1" s="26" t="s">
+      <c r="I1" s="9"/>
+      <c r="J1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="26"/>
-      <c r="L1" s="27" t="s">
+      <c r="K1" s="11"/>
+      <c r="L1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="28" t="s">
+      <c r="N1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="28" t="s">
+      <c r="O1" s="13" t="s">
         <v>9</v>
       </c>
       <c r="Q1"/>
     </row>
     <row r="2" ht="16.5" spans="1:17">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="9" t="s">
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="8"/>
-      <c r="H2" s="9" t="s">
+      <c r="G2" s="9"/>
+      <c r="H2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="8"/>
-      <c r="J2" s="29" t="s">
+      <c r="I2" s="9"/>
+      <c r="J2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="30"/>
-      <c r="L2" s="31" t="s">
+      <c r="K2" s="15"/>
+      <c r="L2" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="8"/>
-      <c r="N2" s="32" t="s">
+      <c r="M2" s="9"/>
+      <c r="N2" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="32" t="s">
+      <c r="O2" s="17" t="s">
         <v>10</v>
       </c>
       <c r="Q2"/>
     </row>
     <row r="3" ht="16.5" spans="1:17">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="11" t="s">
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="12" t="s">
+      <c r="G3" s="18"/>
+      <c r="H3" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="10"/>
-      <c r="J3" s="33" t="s">
+      <c r="I3" s="18"/>
+      <c r="J3" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="33"/>
-      <c r="L3" s="34" t="s">
+      <c r="K3" s="21"/>
+      <c r="L3" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="M3" s="10"/>
-      <c r="N3" s="32" t="s">
+      <c r="M3" s="18"/>
+      <c r="N3" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="32" t="s">
+      <c r="O3" s="17" t="s">
         <v>20</v>
       </c>
       <c r="Q3"/>
     </row>
-    <row r="4" ht="16.5" spans="2:17">
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
-      <c r="L4" s="27"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="32"/>
-      <c r="O4" s="32"/>
+    <row r="4" ht="16.5" spans="1:17">
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
       <c r="Q4"/>
     </row>
-    <row r="5" s="1" customFormat="1" ht="16.5" spans="1:15">
-      <c r="A5" s="13" t="str">
+    <row r="5" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A5" s="24" t="str">
         <f t="shared" ref="A5:A15" si="0">B5&amp;C5</f>
         <v>1001001</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="25">
         <v>100100</v>
       </c>
-      <c r="C5" s="14">
-        <v>1</v>
-      </c>
-      <c r="D5" s="14" t="s">
+      <c r="C5" s="25">
+        <v>1</v>
+      </c>
+      <c r="D5" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="14">
-        <v>1</v>
-      </c>
-      <c r="G5" s="13" t="s">
+      <c r="F5" s="25">
+        <v>1</v>
+      </c>
+      <c r="G5" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="24">
         <v>2001001</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="36" t="s">
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="M5" s="13" t="s">
+      <c r="M5" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="N5" s="32">
+      <c r="N5" s="17">
         <v>4</v>
       </c>
-      <c r="O5" s="32">
+      <c r="O5" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="16.5" spans="1:15">
-      <c r="A6" s="13" t="str">
+    <row r="6" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A6" s="24" t="str">
         <f t="shared" si="0"/>
         <v>1001002</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="25">
         <v>100100</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="25">
         <v>2</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="16" t="s">
+      <c r="D6" s="25"/>
+      <c r="E6" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="14">
-        <v>1</v>
-      </c>
-      <c r="G6" s="13" t="s">
+      <c r="F6" s="25">
+        <v>1</v>
+      </c>
+      <c r="G6" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="24">
         <v>2001001</v>
       </c>
-      <c r="I6" s="13" t="s">
+      <c r="I6" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="37" t="s">
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="M6" s="13" t="s">
+      <c r="M6" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="N6" s="32">
+      <c r="N6" s="17">
         <v>4</v>
       </c>
-      <c r="O6" s="32">
+      <c r="O6" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="16.5" spans="1:15">
-      <c r="A7" s="13" t="str">
+    <row r="7" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A7" s="24" t="str">
         <f t="shared" si="0"/>
         <v>1001003</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="25">
         <v>100100</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="25">
         <v>3</v>
       </c>
-      <c r="D7" s="14"/>
-      <c r="E7" s="17" t="s">
+      <c r="D7" s="25"/>
+      <c r="E7" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="14">
-        <v>1</v>
-      </c>
-      <c r="G7" s="13" t="s">
+      <c r="F7" s="25">
+        <v>1</v>
+      </c>
+      <c r="G7" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="24">
         <v>2001001</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="I7" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="36" t="s">
+      <c r="J7" s="24"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="M7" s="13" t="s">
+      <c r="M7" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="N7" s="32">
+      <c r="N7" s="17">
         <v>4</v>
       </c>
-      <c r="O7" s="32">
+      <c r="O7" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="16.5" spans="1:15">
-      <c r="A8" s="13" t="str">
+    <row r="8" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A8" s="24" t="str">
         <f t="shared" si="0"/>
         <v>1001004</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="25">
         <v>100100</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="25">
         <v>4</v>
       </c>
-      <c r="D8" s="14"/>
-      <c r="E8" s="18" t="s">
+      <c r="D8" s="25"/>
+      <c r="E8" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="19">
-        <v>1</v>
-      </c>
-      <c r="G8" s="13" t="s">
+      <c r="F8" s="32">
+        <v>1</v>
+      </c>
+      <c r="G8" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="24">
         <v>2001001</v>
       </c>
-      <c r="I8" s="13" t="s">
+      <c r="I8" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="36">
+      <c r="J8" s="24"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="27">
         <v>10010041</v>
       </c>
-      <c r="M8" s="13" t="s">
+      <c r="M8" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="N8" s="32">
+      <c r="N8" s="17">
         <v>4</v>
       </c>
-      <c r="O8" s="32">
+      <c r="O8" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="16.5" spans="1:15">
-      <c r="A9" s="13" t="str">
+    <row r="9" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A9" s="24" t="str">
         <f t="shared" si="0"/>
         <v>1001005</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="25">
         <v>100100</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="25">
         <v>5</v>
       </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="20" t="s">
+      <c r="D9" s="25"/>
+      <c r="E9" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="19">
-        <v>1</v>
-      </c>
-      <c r="G9" s="13" t="s">
+      <c r="F9" s="32">
+        <v>1</v>
+      </c>
+      <c r="G9" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="24">
         <v>2001001</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="I9" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="36" t="s">
+      <c r="J9" s="24"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="M9" s="13" t="s">
+      <c r="M9" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="N9" s="32">
+      <c r="N9" s="17">
         <v>4</v>
       </c>
-      <c r="O9" s="32">
+      <c r="O9" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="16.5" spans="1:15">
-      <c r="A10" s="13" t="str">
+    <row r="10" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A10" s="24" t="str">
         <f t="shared" si="0"/>
         <v>1001006</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="25">
         <v>100100</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="25">
         <v>6</v>
       </c>
-      <c r="D10" s="14"/>
-      <c r="E10" s="20" t="s">
+      <c r="D10" s="25"/>
+      <c r="E10" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="19">
-        <v>1</v>
-      </c>
-      <c r="G10" s="13" t="s">
+      <c r="F10" s="32">
+        <v>1</v>
+      </c>
+      <c r="G10" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="24">
         <v>2001001</v>
       </c>
-      <c r="I10" s="13" t="s">
+      <c r="I10" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="36">
+      <c r="J10" s="24"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="27">
         <v>10010061</v>
       </c>
-      <c r="M10" s="13" t="s">
+      <c r="M10" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="N10" s="32">
+      <c r="N10" s="17">
         <v>4</v>
       </c>
-      <c r="O10" s="32">
+      <c r="O10" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="16.5" spans="1:15">
-      <c r="A11" s="13" t="str">
+    <row r="11" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A11" s="24" t="str">
         <f t="shared" si="0"/>
         <v>1001007</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="25">
         <v>100100</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="25">
         <v>7</v>
       </c>
-      <c r="D11" s="14"/>
-      <c r="E11" s="16" t="s">
+      <c r="D11" s="25"/>
+      <c r="E11" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="14">
-        <v>1</v>
-      </c>
-      <c r="G11" s="13" t="s">
+      <c r="F11" s="25">
+        <v>1</v>
+      </c>
+      <c r="G11" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="24">
         <v>2001001</v>
       </c>
-      <c r="I11" s="13" t="s">
+      <c r="I11" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="37" t="s">
+      <c r="J11" s="24"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="M11" s="13" t="s">
+      <c r="M11" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="N11" s="32">
+      <c r="N11" s="17">
         <v>4</v>
       </c>
-      <c r="O11" s="32">
+      <c r="O11" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A12" s="21" t="str">
+      <c r="A12" s="34" t="str">
         <f t="shared" si="0"/>
         <v>1003001</v>
       </c>
-      <c r="B12" s="15">
+      <c r="B12" s="26">
         <v>100300</v>
       </c>
-      <c r="C12" s="15">
-        <v>1</v>
-      </c>
-      <c r="D12" s="15" t="s">
+      <c r="C12" s="26">
+        <v>1</v>
+      </c>
+      <c r="D12" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="15">
-        <v>1</v>
-      </c>
-      <c r="G12" s="21" t="s">
+      <c r="F12" s="26">
+        <v>1</v>
+      </c>
+      <c r="G12" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="H12" s="21">
+      <c r="H12" s="34">
         <v>2003001</v>
       </c>
-      <c r="I12" s="21" t="s">
+      <c r="I12" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="38">
+      <c r="J12" s="34"/>
+      <c r="K12" s="34"/>
+      <c r="L12" s="35">
         <v>10030022</v>
       </c>
-      <c r="M12" s="21" t="s">
+      <c r="M12" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="N12" s="15">
+      <c r="N12" s="26">
         <v>3</v>
       </c>
-      <c r="O12" s="15">
+      <c r="O12" s="26">
         <v>3</v>
       </c>
-      <c r="Q12" s="41"/>
+      <c r="Q12" s="36"/>
     </row>
     <row r="13" s="2" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A13" s="21" t="str">
-        <f t="shared" ref="A13:A29" si="1">B13&amp;C13</f>
+      <c r="A13" s="34" t="str">
+        <f t="shared" ref="A13:A30" si="1">B13&amp;C13</f>
         <v>1003002</v>
       </c>
-      <c r="B13" s="15">
+      <c r="B13" s="26">
         <v>100300</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="26">
         <v>2</v>
       </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15" t="s">
+      <c r="D13" s="26"/>
+      <c r="E13" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="15">
-        <v>1</v>
-      </c>
-      <c r="G13" s="21" t="s">
+      <c r="F13" s="26">
+        <v>1</v>
+      </c>
+      <c r="G13" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="H13" s="21">
+      <c r="H13" s="34">
         <v>2003001</v>
       </c>
-      <c r="I13" s="21" t="s">
+      <c r="I13" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="38" t="s">
+      <c r="J13" s="34"/>
+      <c r="K13" s="34"/>
+      <c r="L13" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="M13" s="21" t="s">
+      <c r="M13" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="N13" s="15">
+      <c r="N13" s="26">
         <v>3</v>
       </c>
-      <c r="O13" s="15">
+      <c r="O13" s="26">
         <v>3</v>
       </c>
-      <c r="Q13" s="41"/>
+      <c r="Q13" s="36"/>
     </row>
     <row r="14" s="2" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A14" s="21" t="str">
+      <c r="A14" s="34" t="str">
         <f t="shared" si="1"/>
         <v>1003003</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14" s="26">
         <v>100300</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="26">
         <v>3</v>
       </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15" t="s">
+      <c r="D14" s="26"/>
+      <c r="E14" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="15">
-        <v>1</v>
-      </c>
-      <c r="G14" s="21" t="s">
+      <c r="F14" s="26">
+        <v>1</v>
+      </c>
+      <c r="G14" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="H14" s="21">
+      <c r="H14" s="34">
         <v>2003002</v>
       </c>
-      <c r="I14" s="21" t="s">
+      <c r="I14" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="J14" s="21" t="s">
+      <c r="J14" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="K14" s="21" t="s">
+      <c r="K14" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="L14" s="38" t="s">
+      <c r="L14" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="M14" s="21" t="s">
+      <c r="M14" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="N14" s="15">
+      <c r="N14" s="26">
         <v>3</v>
       </c>
-      <c r="O14" s="15">
+      <c r="O14" s="26">
         <v>3</v>
       </c>
-      <c r="Q14" s="41"/>
-    </row>
-    <row r="15" s="3" customFormat="1" ht="16.5" spans="1:15">
-      <c r="A15" s="22" t="str">
+      <c r="Q14" s="36"/>
+    </row>
+    <row r="15" s="3" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A15" s="37" t="str">
         <f t="shared" si="1"/>
         <v>1007001</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B15" s="38">
         <v>100700</v>
       </c>
-      <c r="C15" s="23">
-        <v>1</v>
-      </c>
-      <c r="D15" s="23" t="s">
+      <c r="C15" s="38">
+        <v>1</v>
+      </c>
+      <c r="D15" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="23" t="s">
+      <c r="E15" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="23">
-        <v>1</v>
-      </c>
-      <c r="G15" s="22" t="s">
+      <c r="F15" s="38">
+        <v>1</v>
+      </c>
+      <c r="G15" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="H15" s="22">
+      <c r="H15" s="37">
         <v>2007001</v>
       </c>
-      <c r="I15" s="22" t="s">
+      <c r="I15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="22"/>
-      <c r="K15" s="22"/>
+      <c r="J15" s="37"/>
+      <c r="K15" s="37"/>
       <c r="L15" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="M15" s="22" t="s">
+      <c r="M15" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="N15" s="32">
+      <c r="N15" s="17">
         <v>4</v>
       </c>
-      <c r="O15" s="32">
+      <c r="O15" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="16" s="3" customFormat="1" ht="16.5" spans="1:15">
-      <c r="A16" s="22" t="str">
+    <row r="16" s="3" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A16" s="37" t="str">
         <f t="shared" si="1"/>
         <v>1007002</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B16" s="38">
         <v>100700</v>
       </c>
-      <c r="C16" s="23">
+      <c r="C16" s="38">
         <v>2</v>
       </c>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23" t="s">
+      <c r="D16" s="38"/>
+      <c r="E16" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="23">
-        <v>1</v>
-      </c>
-      <c r="G16" s="22" t="s">
+      <c r="F16" s="38">
+        <v>1</v>
+      </c>
+      <c r="G16" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="37">
         <v>2007001</v>
       </c>
-      <c r="I16" s="22" t="s">
+      <c r="I16" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
+      <c r="J16" s="37"/>
+      <c r="K16" s="37"/>
       <c r="L16" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="M16" s="22" t="s">
+      <c r="M16" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="N16" s="32">
+      <c r="N16" s="17">
         <v>4</v>
       </c>
-      <c r="O16" s="32">
+      <c r="O16" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="17" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A17" s="24" t="str">
+      <c r="A17" s="40" t="str">
         <f t="shared" si="1"/>
         <v>1012001</v>
       </c>
-      <c r="B17" s="25">
+      <c r="B17" s="41">
         <v>101200</v>
       </c>
-      <c r="C17" s="25">
-        <v>1</v>
-      </c>
-      <c r="D17" s="25" t="s">
+      <c r="C17" s="41">
+        <v>1</v>
+      </c>
+      <c r="D17" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="E17" s="25" t="s">
+      <c r="E17" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="25">
-        <v>1</v>
-      </c>
-      <c r="G17" s="24" t="s">
+      <c r="F17" s="41">
+        <v>1</v>
+      </c>
+      <c r="G17" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="H17" s="24">
+      <c r="H17" s="40">
         <v>2012001</v>
       </c>
-      <c r="I17" s="24" t="s">
+      <c r="I17" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="J17" s="24"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="40">
+      <c r="J17" s="40"/>
+      <c r="K17" s="40"/>
+      <c r="L17" s="42">
         <v>10120011</v>
       </c>
-      <c r="M17" s="24" t="s">
+      <c r="M17" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="N17" s="25">
+      <c r="N17" s="41">
         <v>3</v>
       </c>
-      <c r="O17" s="25">
+      <c r="O17" s="41">
         <v>5</v>
       </c>
-      <c r="Q17" s="42"/>
+      <c r="Q17" s="43"/>
     </row>
     <row r="18" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A18" s="24" t="str">
+      <c r="A18" s="40" t="str">
         <f t="shared" si="1"/>
         <v>1012002</v>
       </c>
-      <c r="B18" s="25">
+      <c r="B18" s="41">
         <v>101200</v>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="41">
         <v>2</v>
       </c>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25" t="s">
+      <c r="D18" s="41"/>
+      <c r="E18" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="25">
-        <v>1</v>
-      </c>
-      <c r="G18" s="24" t="s">
+      <c r="F18" s="41">
+        <v>1</v>
+      </c>
+      <c r="G18" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="H18" s="24">
+      <c r="H18" s="40">
         <v>2012001</v>
       </c>
-      <c r="I18" s="24" t="s">
+      <c r="I18" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="J18" s="24"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="40">
+      <c r="J18" s="40"/>
+      <c r="K18" s="40"/>
+      <c r="L18" s="42">
         <v>10120021</v>
       </c>
-      <c r="M18" s="24" t="s">
+      <c r="M18" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="N18" s="25">
+      <c r="N18" s="41">
         <v>3</v>
       </c>
-      <c r="O18" s="25">
+      <c r="O18" s="41">
         <v>5</v>
       </c>
-      <c r="Q18" s="42"/>
+      <c r="Q18" s="43"/>
     </row>
     <row r="19" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A19" s="24" t="str">
+      <c r="A19" s="40" t="str">
         <f t="shared" si="1"/>
         <v>1012003</v>
       </c>
-      <c r="B19" s="25">
+      <c r="B19" s="41">
         <v>101200</v>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="41">
         <v>3</v>
       </c>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25" t="s">
+      <c r="D19" s="41"/>
+      <c r="E19" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="F19" s="25">
-        <v>1</v>
-      </c>
-      <c r="G19" s="24" t="s">
+      <c r="F19" s="41">
+        <v>1</v>
+      </c>
+      <c r="G19" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="H19" s="24">
+      <c r="H19" s="40">
         <v>2012001</v>
       </c>
-      <c r="I19" s="24" t="s">
+      <c r="I19" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="J19" s="24" t="s">
+      <c r="J19" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="K19" s="24" t="s">
+      <c r="K19" s="40" t="s">
         <v>63</v>
       </c>
-      <c r="L19" s="40"/>
-      <c r="M19" s="24" t="s">
+      <c r="L19" s="42"/>
+      <c r="M19" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="N19" s="25">
+      <c r="N19" s="41">
         <v>3</v>
       </c>
-      <c r="O19" s="25">
+      <c r="O19" s="41">
         <v>5</v>
       </c>
-      <c r="Q19" s="42"/>
+      <c r="Q19" s="43"/>
     </row>
     <row r="20" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A20" s="21" t="str">
+      <c r="A20" s="34" t="str">
         <f t="shared" si="1"/>
         <v>1014001</v>
       </c>
-      <c r="B20" s="15">
+      <c r="B20" s="26">
         <v>101400</v>
       </c>
-      <c r="C20" s="15">
-        <v>1</v>
-      </c>
-      <c r="D20" s="15" t="s">
+      <c r="C20" s="26">
+        <v>1</v>
+      </c>
+      <c r="D20" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="F20" s="15">
-        <v>1</v>
-      </c>
-      <c r="G20" s="21" t="s">
+      <c r="F20" s="26">
+        <v>1</v>
+      </c>
+      <c r="G20" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="21">
+      <c r="H20" s="34">
         <v>2014001</v>
       </c>
-      <c r="I20" s="21" t="s">
+      <c r="I20" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="J20" s="21"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="38" t="s">
+      <c r="J20" s="34"/>
+      <c r="K20" s="34"/>
+      <c r="L20" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="M20" s="21" t="s">
+      <c r="M20" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="N20" s="32">
+      <c r="N20" s="17">
         <v>4</v>
       </c>
-      <c r="O20" s="32">
+      <c r="O20" s="17">
         <v>3</v>
       </c>
-      <c r="Q20" s="43"/>
+      <c r="Q20" s="44"/>
     </row>
     <row r="21" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A21" s="21" t="str">
+      <c r="A21" s="34" t="str">
         <f t="shared" si="1"/>
         <v>1014002</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21" s="26">
         <v>101400</v>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="26">
         <v>2</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D21" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E21" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="15">
-        <v>1</v>
-      </c>
-      <c r="G21" s="21" t="s">
+      <c r="F21" s="26">
+        <v>1</v>
+      </c>
+      <c r="G21" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="H21" s="21">
+      <c r="H21" s="34">
         <v>2014001</v>
       </c>
-      <c r="I21" s="21" t="s">
+      <c r="I21" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="J21" s="21"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="38" t="s">
+      <c r="J21" s="34"/>
+      <c r="K21" s="34"/>
+      <c r="L21" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="M21" s="21" t="s">
+      <c r="M21" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="N21" s="32">
+      <c r="N21" s="17">
         <v>4</v>
       </c>
-      <c r="O21" s="32">
+      <c r="O21" s="17">
         <v>3</v>
       </c>
-      <c r="Q21" s="43"/>
+      <c r="Q21" s="44"/>
     </row>
     <row r="22" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A22" s="21" t="str">
+      <c r="A22" s="34" t="str">
         <f t="shared" si="1"/>
         <v>1014003</v>
       </c>
-      <c r="B22" s="15">
+      <c r="B22" s="26">
         <v>101400</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="26">
         <v>3</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="E22" s="15" t="s">
+      <c r="E22" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="F22" s="15">
-        <v>1</v>
-      </c>
-      <c r="G22" s="21" t="s">
+      <c r="F22" s="26">
+        <v>1</v>
+      </c>
+      <c r="G22" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="H22" s="21">
+      <c r="H22" s="34">
         <v>2014001</v>
       </c>
-      <c r="I22" s="21" t="s">
+      <c r="I22" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="J22" s="21"/>
-      <c r="K22" s="21"/>
-      <c r="L22" s="38">
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="35">
         <v>10140021</v>
       </c>
-      <c r="M22" s="21" t="s">
+      <c r="M22" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="N22" s="32">
+      <c r="N22" s="17">
         <v>4</v>
       </c>
-      <c r="O22" s="32">
+      <c r="O22" s="17">
         <v>3</v>
       </c>
-      <c r="Q22" s="43"/>
-    </row>
-    <row r="23" s="1" customFormat="1" ht="16.5" spans="1:15">
-      <c r="A23" s="13" t="str">
+      <c r="Q22" s="44"/>
+    </row>
+    <row r="23" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A23" s="24" t="str">
         <f t="shared" si="1"/>
         <v>1024001</v>
       </c>
-      <c r="B23" s="14">
+      <c r="B23" s="25">
         <v>102400</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
-      </c>
-      <c r="D23" s="14" t="s">
+      <c r="C23" s="25">
+        <v>1</v>
+      </c>
+      <c r="D23" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E23" s="15" t="s">
+      <c r="E23" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="F23" s="14">
-        <v>1</v>
-      </c>
-      <c r="G23" s="13" t="s">
+      <c r="F23" s="25">
+        <v>1</v>
+      </c>
+      <c r="G23" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="H23" s="13">
+      <c r="H23" s="24">
         <v>2024001</v>
       </c>
-      <c r="I23" s="13" t="s">
+      <c r="I23" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="36" t="s">
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="M23" s="13" t="s">
+      <c r="M23" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="N23" s="32">
+      <c r="N23" s="17">
         <v>4</v>
       </c>
-      <c r="O23" s="32">
+      <c r="O23" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="16.5" spans="1:15">
-      <c r="A24" s="13" t="str">
+    <row r="24" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A24" s="24" t="str">
         <f t="shared" si="1"/>
         <v>1024002</v>
       </c>
-      <c r="B24" s="14">
+      <c r="B24" s="25">
         <v>102400</v>
       </c>
-      <c r="C24" s="14">
+      <c r="C24" s="25">
         <v>2</v>
       </c>
-      <c r="D24" s="14"/>
-      <c r="E24" s="16" t="s">
+      <c r="D24" s="25"/>
+      <c r="E24" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="14">
-        <v>1</v>
-      </c>
-      <c r="G24" s="13" t="s">
+      <c r="F24" s="25">
+        <v>1</v>
+      </c>
+      <c r="G24" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="H24" s="13">
+      <c r="H24" s="24">
         <v>2024001</v>
       </c>
-      <c r="I24" s="13" t="s">
+      <c r="I24" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
-      <c r="L24" s="37" t="s">
+      <c r="J24" s="24"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="M24" s="13" t="s">
+      <c r="M24" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="N24" s="32">
+      <c r="N24" s="17">
         <v>4</v>
       </c>
-      <c r="O24" s="32">
+      <c r="O24" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="16.5" spans="1:15">
-      <c r="A25" s="13" t="str">
+    <row r="25" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A25" s="24" t="str">
         <f t="shared" si="1"/>
         <v>1024003</v>
       </c>
-      <c r="B25" s="14">
+      <c r="B25" s="25">
         <v>102400</v>
       </c>
-      <c r="C25" s="14">
+      <c r="C25" s="25">
         <v>3</v>
       </c>
-      <c r="D25" s="14"/>
-      <c r="E25" s="17" t="s">
+      <c r="D25" s="25"/>
+      <c r="E25" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="F25" s="14">
-        <v>1</v>
-      </c>
-      <c r="G25" s="13" t="s">
+      <c r="F25" s="25">
+        <v>1</v>
+      </c>
+      <c r="G25" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="H25" s="13">
+      <c r="H25" s="24">
         <v>2024001</v>
       </c>
-      <c r="I25" s="13" t="s">
+      <c r="I25" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="J25" s="13"/>
-      <c r="K25" s="13"/>
-      <c r="L25" s="36" t="s">
+      <c r="J25" s="24"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="M25" s="13" t="s">
+      <c r="M25" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="N25" s="32">
+      <c r="N25" s="17">
         <v>4</v>
       </c>
-      <c r="O25" s="32">
+      <c r="O25" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" ht="16.5" spans="1:15">
-      <c r="A26" s="13" t="str">
+    <row r="26" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A26" s="24" t="str">
         <f t="shared" si="1"/>
         <v>1024004</v>
       </c>
-      <c r="B26" s="14">
+      <c r="B26" s="25">
         <v>102400</v>
       </c>
-      <c r="C26" s="14">
+      <c r="C26" s="25">
         <v>4</v>
       </c>
-      <c r="D26" s="14"/>
-      <c r="E26" s="18" t="s">
+      <c r="D26" s="25"/>
+      <c r="E26" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="F26" s="19">
-        <v>1</v>
-      </c>
-      <c r="G26" s="13" t="s">
+      <c r="F26" s="32">
+        <v>1</v>
+      </c>
+      <c r="G26" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="H26" s="13">
+      <c r="H26" s="24">
         <v>2024001</v>
       </c>
-      <c r="I26" s="13" t="s">
+      <c r="I26" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
-      <c r="L26" s="36">
+      <c r="J26" s="24"/>
+      <c r="K26" s="24"/>
+      <c r="L26" s="27">
         <v>10240041</v>
       </c>
-      <c r="M26" s="13" t="s">
+      <c r="M26" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="N26" s="32">
+      <c r="N26" s="17">
         <v>4</v>
       </c>
-      <c r="O26" s="32">
+      <c r="O26" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" ht="16.5" spans="1:15">
-      <c r="A27" s="13" t="str">
+    <row r="27" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A27" s="24" t="str">
         <f t="shared" si="1"/>
         <v>1024005</v>
       </c>
-      <c r="B27" s="14">
+      <c r="B27" s="25">
         <v>102400</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="25">
         <v>5</v>
       </c>
-      <c r="D27" s="14"/>
-      <c r="E27" s="20" t="s">
+      <c r="D27" s="25"/>
+      <c r="E27" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="F27" s="19">
-        <v>1</v>
-      </c>
-      <c r="G27" s="13" t="s">
+      <c r="F27" s="32">
+        <v>1</v>
+      </c>
+      <c r="G27" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="H27" s="13">
+      <c r="H27" s="24">
         <v>2024001</v>
       </c>
-      <c r="I27" s="13" t="s">
+      <c r="I27" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
-      <c r="L27" s="36" t="s">
+      <c r="J27" s="24"/>
+      <c r="K27" s="24"/>
+      <c r="L27" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="M27" s="13" t="s">
+      <c r="M27" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="N27" s="32">
+      <c r="N27" s="17">
         <v>4</v>
       </c>
-      <c r="O27" s="32">
+      <c r="O27" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" ht="16.5" spans="1:15">
-      <c r="A28" s="13" t="str">
+    <row r="28" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A28" s="24" t="str">
         <f t="shared" si="1"/>
         <v>1024006</v>
       </c>
-      <c r="B28" s="14">
+      <c r="B28" s="25">
         <v>102400</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="25">
         <v>6</v>
       </c>
-      <c r="D28" s="14"/>
-      <c r="E28" s="20" t="s">
+      <c r="D28" s="25"/>
+      <c r="E28" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="F28" s="19">
-        <v>1</v>
-      </c>
-      <c r="G28" s="13" t="s">
+      <c r="F28" s="32">
+        <v>1</v>
+      </c>
+      <c r="G28" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="H28" s="13">
+      <c r="H28" s="24">
         <v>2024001</v>
       </c>
-      <c r="I28" s="13" t="s">
+      <c r="I28" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="J28" s="13"/>
-      <c r="K28" s="13"/>
-      <c r="L28" s="36">
+      <c r="J28" s="24"/>
+      <c r="K28" s="24"/>
+      <c r="L28" s="27">
         <v>10240061</v>
       </c>
-      <c r="M28" s="13" t="s">
+      <c r="M28" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="N28" s="32">
+      <c r="N28" s="17">
         <v>4</v>
       </c>
-      <c r="O28" s="32">
+      <c r="O28" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" ht="16.5" spans="1:15">
-      <c r="A29" s="13" t="str">
+    <row r="29" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A29" s="24" t="str">
         <f t="shared" si="1"/>
         <v>1024007</v>
       </c>
-      <c r="B29" s="14">
+      <c r="B29" s="25">
         <v>102400</v>
       </c>
-      <c r="C29" s="14">
+      <c r="C29" s="25">
         <v>7</v>
       </c>
-      <c r="D29" s="14"/>
-      <c r="E29" s="16" t="s">
+      <c r="D29" s="25"/>
+      <c r="E29" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="F29" s="14">
-        <v>1</v>
-      </c>
-      <c r="G29" s="13" t="s">
+      <c r="F29" s="25">
+        <v>1</v>
+      </c>
+      <c r="G29" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="H29" s="13">
+      <c r="H29" s="24">
         <v>2024001</v>
       </c>
-      <c r="I29" s="13" t="s">
+      <c r="I29" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="J29" s="13"/>
-      <c r="K29" s="13"/>
-      <c r="L29" s="37" t="s">
+      <c r="J29" s="24"/>
+      <c r="K29" s="24"/>
+      <c r="L29" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="M29" s="13" t="s">
+      <c r="M29" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="N29" s="32">
+      <c r="N29" s="17">
         <v>4</v>
       </c>
-      <c r="O29" s="32">
+      <c r="O29" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="32" ht="16.5" spans="19:19">
-      <c r="S32" s="44"/>
-    </row>
-    <row r="33" ht="16.5" spans="19:19">
-      <c r="S33" s="44"/>
-    </row>
-    <row r="34" ht="16.5" spans="19:19">
-      <c r="S34" s="44"/>
-    </row>
-    <row r="35" ht="16.5" spans="19:19">
-      <c r="S35" s="44"/>
-    </row>
-    <row r="36" ht="16.5" spans="19:19">
-      <c r="S36" s="44"/>
-    </row>
-    <row r="37" ht="16.5" spans="19:19">
-      <c r="S37" s="44"/>
-    </row>
-    <row r="47" ht="16.5" spans="19:20">
-      <c r="S47" s="45"/>
-      <c r="T47" s="45"/>
-    </row>
-    <row r="48" ht="16.5" spans="19:20">
-      <c r="S48" s="45"/>
-      <c r="T48" s="45"/>
+    <row r="30" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A30" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v>1017001</v>
+      </c>
+      <c r="B30" s="5">
+        <v>101700</v>
+      </c>
+      <c r="C30" s="5">
+        <v>1</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F30" s="5">
+        <v>1</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H30" s="5">
+        <v>2017001</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="M30" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="N30" s="45">
+        <v>4</v>
+      </c>
+      <c r="O30" s="45">
+        <v>5</v>
+      </c>
+      <c r="Q30" s="46"/>
+    </row>
+    <row r="31" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A31" s="24" t="str">
+        <f t="shared" ref="A31:A37" si="2">B31&amp;C31</f>
+        <v>1017002</v>
+      </c>
+      <c r="B31" s="5">
+        <v>101700</v>
+      </c>
+      <c r="C31" s="5">
+        <v>2</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F31" s="5">
+        <v>1</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H31" s="5">
+        <v>2017001</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="M31" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="N31" s="45">
+        <v>4</v>
+      </c>
+      <c r="O31" s="45">
+        <v>5</v>
+      </c>
+      <c r="Q31" s="46"/>
+    </row>
+    <row r="32" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A32" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>1017003</v>
+      </c>
+      <c r="B32" s="5">
+        <v>101700</v>
+      </c>
+      <c r="C32" s="5">
+        <v>3</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="F32" s="5">
+        <v>1</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H32" s="5">
+        <v>2017001</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="M32" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="N32" s="45">
+        <v>4</v>
+      </c>
+      <c r="O32" s="45">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="46"/>
+    </row>
+    <row r="33" s="5" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A33" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>1022001</v>
+      </c>
+      <c r="B33" s="5">
+        <v>102200</v>
+      </c>
+      <c r="C33" s="5">
+        <v>1</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F33" s="5">
+        <v>1</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H33" s="5">
+        <v>2022001</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" s="47">
+        <v>10220031</v>
+      </c>
+      <c r="M33" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="N33" s="45">
+        <v>3</v>
+      </c>
+      <c r="O33" s="45">
+        <v>5</v>
+      </c>
+      <c r="Q33" s="46"/>
+    </row>
+    <row r="34" s="5" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A34" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>1022002</v>
+      </c>
+      <c r="B34" s="5">
+        <v>102200</v>
+      </c>
+      <c r="C34" s="5">
+        <v>2</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="F34" s="48">
+        <v>1</v>
+      </c>
+      <c r="G34" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="H34" s="5">
+        <v>2022001</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L34" s="50" t="s">
+        <v>87</v>
+      </c>
+      <c r="M34" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="N34" s="45">
+        <v>3</v>
+      </c>
+      <c r="O34" s="45">
+        <v>5</v>
+      </c>
+      <c r="Q34" s="46"/>
+    </row>
+    <row r="35" s="5" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A35" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>1022003</v>
+      </c>
+      <c r="B35" s="5">
+        <v>102200</v>
+      </c>
+      <c r="C35" s="5">
+        <v>3</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="F35" s="51">
+        <v>1</v>
+      </c>
+      <c r="G35" s="52" t="s">
+        <v>23</v>
+      </c>
+      <c r="H35" s="5">
+        <v>2022001</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L35" s="53" t="s">
+        <v>89</v>
+      </c>
+      <c r="M35" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="N35" s="45">
+        <v>3</v>
+      </c>
+      <c r="O35" s="45">
+        <v>5</v>
+      </c>
+      <c r="Q35" s="46"/>
+    </row>
+    <row r="36" s="5" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A36" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>1022004</v>
+      </c>
+      <c r="B36" s="5">
+        <v>102200</v>
+      </c>
+      <c r="C36" s="5">
+        <v>4</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F36" s="48">
+        <v>1</v>
+      </c>
+      <c r="G36" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="H36" s="5">
+        <v>2022001</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L36" s="50" t="s">
+        <v>91</v>
+      </c>
+      <c r="N36" s="45">
+        <v>3</v>
+      </c>
+      <c r="O36" s="45">
+        <v>5</v>
+      </c>
+      <c r="Q36" s="46"/>
+    </row>
+    <row r="37" s="5" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A37" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>1022005</v>
+      </c>
+      <c r="B37" s="5">
+        <v>102200</v>
+      </c>
+      <c r="C37" s="5">
+        <v>5</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="F37" s="5">
+        <v>1</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H37" s="5">
+        <v>2022001</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L37" s="50" t="s">
+        <v>93</v>
+      </c>
+      <c r="N37" s="45">
+        <v>3</v>
+      </c>
+      <c r="O37" s="45">
+        <v>5</v>
+      </c>
+      <c r="Q37" s="46"/>
+      <c r="S37" s="54"/>
+    </row>
+    <row r="47" ht="16.5" spans="1:20">
+      <c r="S47" s="55"/>
+      <c r="T47" s="55"/>
+    </row>
+    <row r="48" ht="16.5" spans="1:20">
+      <c r="S48" s="55"/>
+      <c r="T48" s="55"/>
     </row>
     <row r="49" ht="16.5" spans="19:20">
-      <c r="S49" s="45"/>
-      <c r="T49" s="45"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="55"/>
     </row>
     <row r="50" ht="16.5" spans="19:20">
-      <c r="S50" s="45"/>
-      <c r="T50" s="45"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="55"/>
     </row>
     <row r="51" ht="16.5" spans="19:20">
-      <c r="S51" s="45"/>
-      <c r="T51" s="45"/>
+      <c r="S51" s="55"/>
+      <c r="T51" s="55"/>
     </row>
     <row r="52" ht="16.5" spans="19:20">
-      <c r="S52" s="45"/>
-      <c r="T52" s="45"/>
+      <c r="S52" s="55"/>
+      <c r="T52" s="55"/>
     </row>
     <row r="53" ht="16.5" spans="19:20">
-      <c r="S53" s="45"/>
-      <c r="T53" s="45"/>
+      <c r="S53" s="55"/>
+      <c r="T53" s="55"/>
     </row>
     <row r="54" ht="16.5" spans="19:20">
-      <c r="S54" s="45"/>
-      <c r="T54" s="45"/>
-    </row>
-    <row r="55" ht="16.5" spans="20:20">
-      <c r="T55" s="45"/>
+      <c r="S54" s="55"/>
+      <c r="T54" s="55"/>
+    </row>
+    <row r="55" ht="16.5" spans="19:20">
+      <c r="T55" s="55"/>
     </row>
     <row r="56" ht="16.5" spans="19:20">
-      <c r="S56" s="45"/>
-      <c r="T56" s="45"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="55"/>
     </row>
     <row r="57" ht="16.5" spans="19:20">
-      <c r="S57" s="45"/>
-      <c r="T57" s="45"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="55"/>
     </row>
     <row r="58" ht="16.5" spans="19:20">
-      <c r="S58" s="45"/>
-      <c r="T58" s="45"/>
+      <c r="S58" s="55"/>
+      <c r="T58" s="55"/>
     </row>
     <row r="59" ht="16.5" spans="19:20">
-      <c r="S59" s="45"/>
-      <c r="T59" s="45"/>
+      <c r="S59" s="55"/>
+      <c r="T59" s="55"/>
     </row>
     <row r="60" ht="16.5" spans="19:20">
-      <c r="S60" s="45"/>
-      <c r="T60" s="45"/>
+      <c r="S60" s="55"/>
+      <c r="T60" s="55"/>
     </row>
     <row r="61" ht="16.5" spans="19:20">
-      <c r="S61" s="45"/>
-      <c r="T61" s="45"/>
+      <c r="S61" s="55"/>
+      <c r="T61" s="55"/>
     </row>
     <row r="62" ht="16.5" spans="19:20">
-      <c r="S62" s="45"/>
-      <c r="T62" s="45"/>
+      <c r="S62" s="55"/>
+      <c r="T62" s="55"/>
     </row>
     <row r="63" ht="16.5" spans="19:20">
-      <c r="S63" s="45"/>
-      <c r="T63" s="45"/>
+      <c r="S63" s="55"/>
+      <c r="T63" s="55"/>
     </row>
     <row r="64" ht="16.5" spans="19:20">
-      <c r="S64" s="45"/>
-      <c r="T64" s="45"/>
+      <c r="S64" s="55"/>
+      <c r="T64" s="55"/>
     </row>
     <row r="65" ht="16.5" spans="19:20">
-      <c r="S65" s="45"/>
-      <c r="T65" s="45"/>
+      <c r="S65" s="55"/>
+      <c r="T65" s="55"/>
     </row>
     <row r="66" ht="16.5" spans="19:20">
-      <c r="S66" s="45"/>
-      <c r="T66" s="45"/>
+      <c r="S66" s="55"/>
+      <c r="T66" s="55"/>
     </row>
     <row r="67" ht="16.5" spans="19:20">
-      <c r="S67" s="45"/>
-      <c r="T67" s="45"/>
+      <c r="S67" s="55"/>
+      <c r="T67" s="55"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:K2">

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="93">
   <si>
     <t>id</t>
   </si>
@@ -387,9 +387,6 @@
   </si>
   <si>
     <t>免费</t>
-  </si>
-  <si>
-    <t>10220001|10220002|10220003</t>
   </si>
   <si>
     <t>改出3个SCATTER</t>
@@ -1126,7 +1123,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1138,7 +1135,6 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1225,18 +1221,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1801,36 +1788,36 @@
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="9" t="s">
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="10" t="s">
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="9"/>
-      <c r="H1" s="10" t="s">
+      <c r="G1" s="5"/>
+      <c r="H1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="9"/>
-      <c r="J1" s="11" t="s">
+      <c r="I1" s="5"/>
+      <c r="J1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="11"/>
-      <c r="L1" s="12" t="s">
+      <c r="K1" s="10"/>
+      <c r="L1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="13" t="s">
+      <c r="N1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="O1" s="12" t="s">
         <v>9</v>
       </c>
       <c r="Q1"/>
@@ -1839,34 +1826,34 @@
       <c r="A2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="10" t="s">
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="9"/>
-      <c r="H2" s="10" t="s">
+      <c r="G2" s="5"/>
+      <c r="H2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="9"/>
-      <c r="J2" s="14" t="s">
+      <c r="I2" s="5"/>
+      <c r="J2" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="15"/>
-      <c r="L2" s="16" t="s">
+      <c r="K2" s="14"/>
+      <c r="L2" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="9"/>
-      <c r="N2" s="17" t="s">
+      <c r="M2" s="5"/>
+      <c r="N2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="17" t="s">
+      <c r="O2" s="16" t="s">
         <v>10</v>
       </c>
       <c r="Q2"/>
@@ -1875,1138 +1862,1138 @@
       <c r="A3" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="19" t="s">
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="18"/>
-      <c r="H3" s="20" t="s">
+      <c r="G3" s="17"/>
+      <c r="H3" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="18"/>
-      <c r="J3" s="21" t="s">
+      <c r="I3" s="17"/>
+      <c r="J3" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="21"/>
-      <c r="L3" s="22" t="s">
+      <c r="K3" s="20"/>
+      <c r="L3" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="M3" s="18"/>
-      <c r="N3" s="17" t="s">
+      <c r="M3" s="17"/>
+      <c r="N3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="17" t="s">
+      <c r="O3" s="16" t="s">
         <v>20</v>
       </c>
       <c r="Q3"/>
     </row>
     <row r="4" ht="16.5" spans="1:17">
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
       <c r="Q4"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A5" s="24" t="str">
+      <c r="A5" s="23" t="str">
         <f t="shared" ref="A5:A15" si="0">B5&amp;C5</f>
         <v>1001001</v>
       </c>
-      <c r="B5" s="25">
+      <c r="B5" s="24">
         <v>100100</v>
       </c>
-      <c r="C5" s="25">
-        <v>1</v>
-      </c>
-      <c r="D5" s="25" t="s">
+      <c r="C5" s="24">
+        <v>1</v>
+      </c>
+      <c r="D5" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="25">
-        <v>1</v>
-      </c>
-      <c r="G5" s="24" t="s">
+      <c r="F5" s="24">
+        <v>1</v>
+      </c>
+      <c r="G5" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="24">
+      <c r="H5" s="23">
         <v>2001001</v>
       </c>
-      <c r="I5" s="24" t="s">
+      <c r="I5" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="24"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="27" t="s">
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="M5" s="24" t="s">
+      <c r="M5" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="N5" s="17">
+      <c r="N5" s="16">
         <v>4</v>
       </c>
-      <c r="O5" s="17">
+      <c r="O5" s="16">
         <v>5</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A6" s="24" t="str">
+      <c r="A6" s="23" t="str">
         <f t="shared" si="0"/>
         <v>1001002</v>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="24">
         <v>100100</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="24">
         <v>2</v>
       </c>
-      <c r="D6" s="25"/>
-      <c r="E6" s="28" t="s">
+      <c r="D6" s="24"/>
+      <c r="E6" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="25">
-        <v>1</v>
-      </c>
-      <c r="G6" s="24" t="s">
+      <c r="F6" s="24">
+        <v>1</v>
+      </c>
+      <c r="G6" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="24">
+      <c r="H6" s="23">
         <v>2001001</v>
       </c>
-      <c r="I6" s="24" t="s">
+      <c r="I6" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="29" t="s">
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="M6" s="24" t="s">
+      <c r="M6" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="N6" s="17">
+      <c r="N6" s="16">
         <v>4</v>
       </c>
-      <c r="O6" s="17">
+      <c r="O6" s="16">
         <v>5</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A7" s="24" t="str">
+      <c r="A7" s="23" t="str">
         <f t="shared" si="0"/>
         <v>1001003</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="24">
         <v>100100</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="24">
         <v>3</v>
       </c>
-      <c r="D7" s="25"/>
-      <c r="E7" s="30" t="s">
+      <c r="D7" s="24"/>
+      <c r="E7" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="25">
-        <v>1</v>
-      </c>
-      <c r="G7" s="24" t="s">
+      <c r="F7" s="24">
+        <v>1</v>
+      </c>
+      <c r="G7" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="23">
         <v>2001001</v>
       </c>
-      <c r="I7" s="24" t="s">
+      <c r="I7" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="27" t="s">
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="M7" s="24" t="s">
+      <c r="M7" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="N7" s="17">
+      <c r="N7" s="16">
         <v>4</v>
       </c>
-      <c r="O7" s="17">
+      <c r="O7" s="16">
         <v>5</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A8" s="24" t="str">
+      <c r="A8" s="23" t="str">
         <f t="shared" si="0"/>
         <v>1001004</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="24">
         <v>100100</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="24">
         <v>4</v>
       </c>
-      <c r="D8" s="25"/>
-      <c r="E8" s="31" t="s">
+      <c r="D8" s="24"/>
+      <c r="E8" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="32">
-        <v>1</v>
-      </c>
-      <c r="G8" s="24" t="s">
+      <c r="F8" s="31">
+        <v>1</v>
+      </c>
+      <c r="G8" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="23">
         <v>2001001</v>
       </c>
-      <c r="I8" s="24" t="s">
+      <c r="I8" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="J8" s="24"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="27">
+      <c r="J8" s="23"/>
+      <c r="K8" s="23"/>
+      <c r="L8" s="26">
         <v>10010041</v>
       </c>
-      <c r="M8" s="24" t="s">
+      <c r="M8" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="N8" s="17">
+      <c r="N8" s="16">
         <v>4</v>
       </c>
-      <c r="O8" s="17">
+      <c r="O8" s="16">
         <v>5</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A9" s="24" t="str">
+      <c r="A9" s="23" t="str">
         <f t="shared" si="0"/>
         <v>1001005</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="24">
         <v>100100</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="24">
         <v>5</v>
       </c>
-      <c r="D9" s="25"/>
-      <c r="E9" s="33" t="s">
+      <c r="D9" s="24"/>
+      <c r="E9" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="32">
-        <v>1</v>
-      </c>
-      <c r="G9" s="24" t="s">
+      <c r="F9" s="31">
+        <v>1</v>
+      </c>
+      <c r="G9" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="23">
         <v>2001001</v>
       </c>
-      <c r="I9" s="24" t="s">
+      <c r="I9" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="J9" s="24"/>
-      <c r="K9" s="24"/>
-      <c r="L9" s="27" t="s">
+      <c r="J9" s="23"/>
+      <c r="K9" s="23"/>
+      <c r="L9" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="M9" s="24" t="s">
+      <c r="M9" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="N9" s="17">
+      <c r="N9" s="16">
         <v>4</v>
       </c>
-      <c r="O9" s="17">
+      <c r="O9" s="16">
         <v>5</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A10" s="24" t="str">
+      <c r="A10" s="23" t="str">
         <f t="shared" si="0"/>
         <v>1001006</v>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="24">
         <v>100100</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="24">
         <v>6</v>
       </c>
-      <c r="D10" s="25"/>
-      <c r="E10" s="33" t="s">
+      <c r="D10" s="24"/>
+      <c r="E10" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="32">
-        <v>1</v>
-      </c>
-      <c r="G10" s="24" t="s">
+      <c r="F10" s="31">
+        <v>1</v>
+      </c>
+      <c r="G10" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="24">
+      <c r="H10" s="23">
         <v>2001001</v>
       </c>
-      <c r="I10" s="24" t="s">
+      <c r="I10" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="27">
+      <c r="J10" s="23"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="26">
         <v>10010061</v>
       </c>
-      <c r="M10" s="24" t="s">
+      <c r="M10" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="N10" s="17">
+      <c r="N10" s="16">
         <v>4</v>
       </c>
-      <c r="O10" s="17">
+      <c r="O10" s="16">
         <v>5</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A11" s="24" t="str">
+      <c r="A11" s="23" t="str">
         <f t="shared" si="0"/>
         <v>1001007</v>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="24">
         <v>100100</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="24">
         <v>7</v>
       </c>
-      <c r="D11" s="25"/>
-      <c r="E11" s="28" t="s">
+      <c r="D11" s="24"/>
+      <c r="E11" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="25">
-        <v>1</v>
-      </c>
-      <c r="G11" s="24" t="s">
+      <c r="F11" s="24">
+        <v>1</v>
+      </c>
+      <c r="G11" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="H11" s="24">
+      <c r="H11" s="23">
         <v>2001001</v>
       </c>
-      <c r="I11" s="24" t="s">
+      <c r="I11" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="J11" s="24"/>
-      <c r="K11" s="24"/>
-      <c r="L11" s="29" t="s">
+      <c r="J11" s="23"/>
+      <c r="K11" s="23"/>
+      <c r="L11" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="M11" s="24" t="s">
+      <c r="M11" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="N11" s="17">
+      <c r="N11" s="16">
         <v>4</v>
       </c>
-      <c r="O11" s="17">
+      <c r="O11" s="16">
         <v>5</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A12" s="34" t="str">
+      <c r="A12" s="33" t="str">
         <f t="shared" si="0"/>
         <v>1003001</v>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="25">
         <v>100300</v>
       </c>
-      <c r="C12" s="26">
-        <v>1</v>
-      </c>
-      <c r="D12" s="26" t="s">
+      <c r="C12" s="25">
+        <v>1</v>
+      </c>
+      <c r="D12" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="26" t="s">
+      <c r="E12" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="26">
-        <v>1</v>
-      </c>
-      <c r="G12" s="34" t="s">
+      <c r="F12" s="25">
+        <v>1</v>
+      </c>
+      <c r="G12" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H12" s="34">
+      <c r="H12" s="33">
         <v>2003001</v>
       </c>
-      <c r="I12" s="34" t="s">
+      <c r="I12" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="J12" s="34"/>
-      <c r="K12" s="34"/>
-      <c r="L12" s="35">
+      <c r="J12" s="33"/>
+      <c r="K12" s="33"/>
+      <c r="L12" s="34">
         <v>10030022</v>
       </c>
-      <c r="M12" s="34" t="s">
+      <c r="M12" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="N12" s="26">
+      <c r="N12" s="25">
         <v>3</v>
       </c>
-      <c r="O12" s="26">
+      <c r="O12" s="25">
         <v>3</v>
       </c>
-      <c r="Q12" s="36"/>
+      <c r="Q12" s="35"/>
     </row>
     <row r="13" s="2" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A13" s="34" t="str">
+      <c r="A13" s="33" t="str">
         <f t="shared" ref="A13:A30" si="1">B13&amp;C13</f>
         <v>1003002</v>
       </c>
-      <c r="B13" s="26">
+      <c r="B13" s="25">
         <v>100300</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="25">
         <v>2</v>
       </c>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26" t="s">
+      <c r="D13" s="25"/>
+      <c r="E13" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="26">
-        <v>1</v>
-      </c>
-      <c r="G13" s="34" t="s">
+      <c r="F13" s="25">
+        <v>1</v>
+      </c>
+      <c r="G13" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H13" s="34">
+      <c r="H13" s="33">
         <v>2003001</v>
       </c>
-      <c r="I13" s="34" t="s">
+      <c r="I13" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="J13" s="34"/>
-      <c r="K13" s="34"/>
-      <c r="L13" s="35" t="s">
+      <c r="J13" s="33"/>
+      <c r="K13" s="33"/>
+      <c r="L13" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="M13" s="34" t="s">
+      <c r="M13" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="N13" s="26">
+      <c r="N13" s="25">
         <v>3</v>
       </c>
-      <c r="O13" s="26">
+      <c r="O13" s="25">
         <v>3</v>
       </c>
-      <c r="Q13" s="36"/>
+      <c r="Q13" s="35"/>
     </row>
     <row r="14" s="2" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A14" s="34" t="str">
+      <c r="A14" s="33" t="str">
         <f t="shared" si="1"/>
         <v>1003003</v>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="25">
         <v>100300</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="25">
         <v>3</v>
       </c>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26" t="s">
+      <c r="D14" s="25"/>
+      <c r="E14" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="26">
-        <v>1</v>
-      </c>
-      <c r="G14" s="34" t="s">
+      <c r="F14" s="25">
+        <v>1</v>
+      </c>
+      <c r="G14" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H14" s="34">
+      <c r="H14" s="33">
         <v>2003002</v>
       </c>
-      <c r="I14" s="34" t="s">
+      <c r="I14" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="J14" s="34" t="s">
+      <c r="J14" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="K14" s="34" t="s">
+      <c r="K14" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="L14" s="35" t="s">
+      <c r="L14" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="M14" s="34" t="s">
+      <c r="M14" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="N14" s="26">
+      <c r="N14" s="25">
         <v>3</v>
       </c>
-      <c r="O14" s="26">
+      <c r="O14" s="25">
         <v>3</v>
       </c>
-      <c r="Q14" s="36"/>
+      <c r="Q14" s="35"/>
     </row>
     <row r="15" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A15" s="37" t="str">
+      <c r="A15" s="36" t="str">
         <f t="shared" si="1"/>
         <v>1007001</v>
       </c>
-      <c r="B15" s="38">
+      <c r="B15" s="37">
         <v>100700</v>
       </c>
-      <c r="C15" s="38">
-        <v>1</v>
-      </c>
-      <c r="D15" s="38" t="s">
+      <c r="C15" s="37">
+        <v>1</v>
+      </c>
+      <c r="D15" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="38" t="s">
+      <c r="E15" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="38">
-        <v>1</v>
-      </c>
-      <c r="G15" s="37" t="s">
+      <c r="F15" s="37">
+        <v>1</v>
+      </c>
+      <c r="G15" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="H15" s="37">
+      <c r="H15" s="36">
         <v>2007001</v>
       </c>
-      <c r="I15" s="37" t="s">
+      <c r="I15" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="37"/>
-      <c r="K15" s="37"/>
-      <c r="L15" s="39" t="s">
+      <c r="J15" s="36"/>
+      <c r="K15" s="36"/>
+      <c r="L15" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="M15" s="37" t="s">
+      <c r="M15" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="N15" s="17">
+      <c r="N15" s="16">
         <v>4</v>
       </c>
-      <c r="O15" s="17">
+      <c r="O15" s="16">
         <v>5</v>
       </c>
     </row>
     <row r="16" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A16" s="37" t="str">
+      <c r="A16" s="36" t="str">
         <f t="shared" si="1"/>
         <v>1007002</v>
       </c>
-      <c r="B16" s="38">
+      <c r="B16" s="37">
         <v>100700</v>
       </c>
-      <c r="C16" s="38">
+      <c r="C16" s="37">
         <v>2</v>
       </c>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38" t="s">
+      <c r="D16" s="37"/>
+      <c r="E16" s="37" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="38">
-        <v>1</v>
-      </c>
-      <c r="G16" s="37" t="s">
+      <c r="F16" s="37">
+        <v>1</v>
+      </c>
+      <c r="G16" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="H16" s="37">
+      <c r="H16" s="36">
         <v>2007001</v>
       </c>
-      <c r="I16" s="37" t="s">
+      <c r="I16" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="J16" s="37"/>
-      <c r="K16" s="37"/>
-      <c r="L16" s="39" t="s">
+      <c r="J16" s="36"/>
+      <c r="K16" s="36"/>
+      <c r="L16" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="M16" s="37" t="s">
+      <c r="M16" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="N16" s="17">
+      <c r="N16" s="16">
         <v>4</v>
       </c>
-      <c r="O16" s="17">
+      <c r="O16" s="16">
         <v>5</v>
       </c>
     </row>
     <row r="17" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A17" s="40" t="str">
+      <c r="A17" s="39" t="str">
         <f t="shared" si="1"/>
         <v>1012001</v>
       </c>
-      <c r="B17" s="41">
+      <c r="B17" s="40">
         <v>101200</v>
       </c>
-      <c r="C17" s="41">
-        <v>1</v>
-      </c>
-      <c r="D17" s="41" t="s">
+      <c r="C17" s="40">
+        <v>1</v>
+      </c>
+      <c r="D17" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="E17" s="41" t="s">
+      <c r="E17" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="41">
-        <v>1</v>
-      </c>
-      <c r="G17" s="40" t="s">
+      <c r="F17" s="40">
+        <v>1</v>
+      </c>
+      <c r="G17" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="H17" s="40">
+      <c r="H17" s="39">
         <v>2012001</v>
       </c>
-      <c r="I17" s="40" t="s">
+      <c r="I17" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="J17" s="40"/>
-      <c r="K17" s="40"/>
-      <c r="L17" s="42">
+      <c r="J17" s="39"/>
+      <c r="K17" s="39"/>
+      <c r="L17" s="41">
         <v>10120011</v>
       </c>
-      <c r="M17" s="40" t="s">
+      <c r="M17" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="N17" s="41">
+      <c r="N17" s="40">
         <v>3</v>
       </c>
-      <c r="O17" s="41">
+      <c r="O17" s="40">
         <v>5</v>
       </c>
-      <c r="Q17" s="43"/>
+      <c r="Q17" s="42"/>
     </row>
     <row r="18" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A18" s="40" t="str">
+      <c r="A18" s="39" t="str">
         <f t="shared" si="1"/>
         <v>1012002</v>
       </c>
-      <c r="B18" s="41">
+      <c r="B18" s="40">
         <v>101200</v>
       </c>
-      <c r="C18" s="41">
+      <c r="C18" s="40">
         <v>2</v>
       </c>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41" t="s">
+      <c r="D18" s="40"/>
+      <c r="E18" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="41">
-        <v>1</v>
-      </c>
-      <c r="G18" s="40" t="s">
+      <c r="F18" s="40">
+        <v>1</v>
+      </c>
+      <c r="G18" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="H18" s="40">
+      <c r="H18" s="39">
         <v>2012001</v>
       </c>
-      <c r="I18" s="40" t="s">
+      <c r="I18" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="J18" s="40"/>
-      <c r="K18" s="40"/>
-      <c r="L18" s="42">
+      <c r="J18" s="39"/>
+      <c r="K18" s="39"/>
+      <c r="L18" s="41">
         <v>10120021</v>
       </c>
-      <c r="M18" s="40" t="s">
+      <c r="M18" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="N18" s="41">
+      <c r="N18" s="40">
         <v>3</v>
       </c>
-      <c r="O18" s="41">
+      <c r="O18" s="40">
         <v>5</v>
       </c>
-      <c r="Q18" s="43"/>
+      <c r="Q18" s="42"/>
     </row>
     <row r="19" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A19" s="40" t="str">
+      <c r="A19" s="39" t="str">
         <f t="shared" si="1"/>
         <v>1012003</v>
       </c>
-      <c r="B19" s="41">
+      <c r="B19" s="40">
         <v>101200</v>
       </c>
-      <c r="C19" s="41">
+      <c r="C19" s="40">
         <v>3</v>
       </c>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41" t="s">
+      <c r="D19" s="40"/>
+      <c r="E19" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="F19" s="41">
-        <v>1</v>
-      </c>
-      <c r="G19" s="40" t="s">
+      <c r="F19" s="40">
+        <v>1</v>
+      </c>
+      <c r="G19" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="H19" s="40">
+      <c r="H19" s="39">
         <v>2012001</v>
       </c>
-      <c r="I19" s="40" t="s">
+      <c r="I19" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="J19" s="40" t="s">
+      <c r="J19" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="K19" s="40" t="s">
+      <c r="K19" s="39" t="s">
         <v>63</v>
       </c>
-      <c r="L19" s="42"/>
-      <c r="M19" s="40" t="s">
+      <c r="L19" s="41"/>
+      <c r="M19" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="N19" s="41">
+      <c r="N19" s="40">
         <v>3</v>
       </c>
-      <c r="O19" s="41">
+      <c r="O19" s="40">
         <v>5</v>
       </c>
-      <c r="Q19" s="43"/>
+      <c r="Q19" s="42"/>
     </row>
     <row r="20" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A20" s="34" t="str">
+      <c r="A20" s="33" t="str">
         <f t="shared" si="1"/>
         <v>1014001</v>
       </c>
-      <c r="B20" s="26">
+      <c r="B20" s="25">
         <v>101400</v>
       </c>
-      <c r="C20" s="26">
-        <v>1</v>
-      </c>
-      <c r="D20" s="26" t="s">
+      <c r="C20" s="25">
+        <v>1</v>
+      </c>
+      <c r="D20" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="E20" s="26" t="s">
+      <c r="E20" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F20" s="26">
-        <v>1</v>
-      </c>
-      <c r="G20" s="34" t="s">
+      <c r="F20" s="25">
+        <v>1</v>
+      </c>
+      <c r="G20" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="34">
+      <c r="H20" s="33">
         <v>2014001</v>
       </c>
-      <c r="I20" s="34" t="s">
+      <c r="I20" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="J20" s="34"/>
-      <c r="K20" s="34"/>
-      <c r="L20" s="35" t="s">
+      <c r="J20" s="33"/>
+      <c r="K20" s="33"/>
+      <c r="L20" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="M20" s="34" t="s">
+      <c r="M20" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="N20" s="17">
+      <c r="N20" s="16">
         <v>4</v>
       </c>
-      <c r="O20" s="17">
+      <c r="O20" s="16">
         <v>3</v>
       </c>
-      <c r="Q20" s="44"/>
+      <c r="Q20" s="43"/>
     </row>
     <row r="21" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A21" s="34" t="str">
+      <c r="A21" s="33" t="str">
         <f t="shared" si="1"/>
         <v>1014002</v>
       </c>
-      <c r="B21" s="26">
+      <c r="B21" s="25">
         <v>101400</v>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="25">
         <v>2</v>
       </c>
-      <c r="D21" s="26" t="s">
+      <c r="D21" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="E21" s="26" t="s">
+      <c r="E21" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="26">
-        <v>1</v>
-      </c>
-      <c r="G21" s="34" t="s">
+      <c r="F21" s="25">
+        <v>1</v>
+      </c>
+      <c r="G21" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H21" s="34">
+      <c r="H21" s="33">
         <v>2014001</v>
       </c>
-      <c r="I21" s="34" t="s">
+      <c r="I21" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="J21" s="34"/>
-      <c r="K21" s="34"/>
-      <c r="L21" s="35" t="s">
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="M21" s="34" t="s">
+      <c r="M21" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="N21" s="17">
+      <c r="N21" s="16">
         <v>4</v>
       </c>
-      <c r="O21" s="17">
+      <c r="O21" s="16">
         <v>3</v>
       </c>
-      <c r="Q21" s="44"/>
+      <c r="Q21" s="43"/>
     </row>
     <row r="22" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A22" s="34" t="str">
+      <c r="A22" s="33" t="str">
         <f t="shared" si="1"/>
         <v>1014003</v>
       </c>
-      <c r="B22" s="26">
+      <c r="B22" s="25">
         <v>101400</v>
       </c>
-      <c r="C22" s="26">
+      <c r="C22" s="25">
         <v>3</v>
       </c>
-      <c r="D22" s="26" t="s">
+      <c r="D22" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="E22" s="26" t="s">
+      <c r="E22" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="F22" s="26">
-        <v>1</v>
-      </c>
-      <c r="G22" s="34" t="s">
+      <c r="F22" s="25">
+        <v>1</v>
+      </c>
+      <c r="G22" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H22" s="34">
+      <c r="H22" s="33">
         <v>2014001</v>
       </c>
-      <c r="I22" s="34" t="s">
+      <c r="I22" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="J22" s="34"/>
-      <c r="K22" s="34"/>
-      <c r="L22" s="35">
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="34">
         <v>10140021</v>
       </c>
-      <c r="M22" s="34" t="s">
+      <c r="M22" s="33" t="s">
         <v>71</v>
       </c>
-      <c r="N22" s="17">
+      <c r="N22" s="16">
         <v>4</v>
       </c>
-      <c r="O22" s="17">
+      <c r="O22" s="16">
         <v>3</v>
       </c>
-      <c r="Q22" s="44"/>
+      <c r="Q22" s="43"/>
     </row>
     <row r="23" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A23" s="24" t="str">
+      <c r="A23" s="23" t="str">
         <f t="shared" si="1"/>
         <v>1024001</v>
       </c>
-      <c r="B23" s="25">
+      <c r="B23" s="24">
         <v>102400</v>
       </c>
-      <c r="C23" s="25">
-        <v>1</v>
-      </c>
-      <c r="D23" s="25" t="s">
+      <c r="C23" s="24">
+        <v>1</v>
+      </c>
+      <c r="D23" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="E23" s="26" t="s">
+      <c r="E23" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F23" s="25">
-        <v>1</v>
-      </c>
-      <c r="G23" s="24" t="s">
+      <c r="F23" s="24">
+        <v>1</v>
+      </c>
+      <c r="G23" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="H23" s="24">
+      <c r="H23" s="23">
         <v>2024001</v>
       </c>
-      <c r="I23" s="24" t="s">
+      <c r="I23" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="27" t="s">
+      <c r="J23" s="23"/>
+      <c r="K23" s="23"/>
+      <c r="L23" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="M23" s="24" t="s">
+      <c r="M23" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="N23" s="17">
+      <c r="N23" s="16">
         <v>4</v>
       </c>
-      <c r="O23" s="17">
+      <c r="O23" s="16">
         <v>5</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A24" s="24" t="str">
+      <c r="A24" s="23" t="str">
         <f t="shared" si="1"/>
         <v>1024002</v>
       </c>
-      <c r="B24" s="25">
+      <c r="B24" s="24">
         <v>102400</v>
       </c>
-      <c r="C24" s="25">
+      <c r="C24" s="24">
         <v>2</v>
       </c>
-      <c r="D24" s="25"/>
-      <c r="E24" s="28" t="s">
+      <c r="D24" s="24"/>
+      <c r="E24" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="25">
-        <v>1</v>
-      </c>
-      <c r="G24" s="24" t="s">
+      <c r="F24" s="24">
+        <v>1</v>
+      </c>
+      <c r="G24" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="H24" s="24">
+      <c r="H24" s="23">
         <v>2024001</v>
       </c>
-      <c r="I24" s="24" t="s">
+      <c r="I24" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="J24" s="24"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="29" t="s">
+      <c r="J24" s="23"/>
+      <c r="K24" s="23"/>
+      <c r="L24" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="M24" s="24" t="s">
+      <c r="M24" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="N24" s="17">
+      <c r="N24" s="16">
         <v>4</v>
       </c>
-      <c r="O24" s="17">
+      <c r="O24" s="16">
         <v>5</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A25" s="24" t="str">
+      <c r="A25" s="23" t="str">
         <f t="shared" si="1"/>
         <v>1024003</v>
       </c>
-      <c r="B25" s="25">
+      <c r="B25" s="24">
         <v>102400</v>
       </c>
-      <c r="C25" s="25">
+      <c r="C25" s="24">
         <v>3</v>
       </c>
-      <c r="D25" s="25"/>
-      <c r="E25" s="30" t="s">
+      <c r="D25" s="24"/>
+      <c r="E25" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="F25" s="25">
-        <v>1</v>
-      </c>
-      <c r="G25" s="24" t="s">
+      <c r="F25" s="24">
+        <v>1</v>
+      </c>
+      <c r="G25" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="H25" s="24">
+      <c r="H25" s="23">
         <v>2024001</v>
       </c>
-      <c r="I25" s="24" t="s">
+      <c r="I25" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="J25" s="24"/>
-      <c r="K25" s="24"/>
-      <c r="L25" s="27" t="s">
+      <c r="J25" s="23"/>
+      <c r="K25" s="23"/>
+      <c r="L25" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="M25" s="24" t="s">
+      <c r="M25" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="N25" s="17">
+      <c r="N25" s="16">
         <v>4</v>
       </c>
-      <c r="O25" s="17">
+      <c r="O25" s="16">
         <v>5</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A26" s="24" t="str">
+      <c r="A26" s="23" t="str">
         <f t="shared" si="1"/>
         <v>1024004</v>
       </c>
-      <c r="B26" s="25">
+      <c r="B26" s="24">
         <v>102400</v>
       </c>
-      <c r="C26" s="25">
+      <c r="C26" s="24">
         <v>4</v>
       </c>
-      <c r="D26" s="25"/>
-      <c r="E26" s="31" t="s">
+      <c r="D26" s="24"/>
+      <c r="E26" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="F26" s="32">
-        <v>1</v>
-      </c>
-      <c r="G26" s="24" t="s">
+      <c r="F26" s="31">
+        <v>1</v>
+      </c>
+      <c r="G26" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="H26" s="24">
+      <c r="H26" s="23">
         <v>2024001</v>
       </c>
-      <c r="I26" s="24" t="s">
+      <c r="I26" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="J26" s="24"/>
-      <c r="K26" s="24"/>
-      <c r="L26" s="27">
+      <c r="J26" s="23"/>
+      <c r="K26" s="23"/>
+      <c r="L26" s="26">
         <v>10240041</v>
       </c>
-      <c r="M26" s="24" t="s">
+      <c r="M26" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="N26" s="17">
+      <c r="N26" s="16">
         <v>4</v>
       </c>
-      <c r="O26" s="17">
+      <c r="O26" s="16">
         <v>5</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A27" s="24" t="str">
+      <c r="A27" s="23" t="str">
         <f t="shared" si="1"/>
         <v>1024005</v>
       </c>
-      <c r="B27" s="25">
+      <c r="B27" s="24">
         <v>102400</v>
       </c>
-      <c r="C27" s="25">
+      <c r="C27" s="24">
         <v>5</v>
       </c>
-      <c r="D27" s="25"/>
-      <c r="E27" s="33" t="s">
+      <c r="D27" s="24"/>
+      <c r="E27" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="F27" s="32">
-        <v>1</v>
-      </c>
-      <c r="G27" s="24" t="s">
+      <c r="F27" s="31">
+        <v>1</v>
+      </c>
+      <c r="G27" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="H27" s="24">
+      <c r="H27" s="23">
         <v>2024001</v>
       </c>
-      <c r="I27" s="24" t="s">
+      <c r="I27" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="J27" s="24"/>
-      <c r="K27" s="24"/>
-      <c r="L27" s="27" t="s">
+      <c r="J27" s="23"/>
+      <c r="K27" s="23"/>
+      <c r="L27" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="M27" s="24" t="s">
+      <c r="M27" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="N27" s="17">
+      <c r="N27" s="16">
         <v>4</v>
       </c>
-      <c r="O27" s="17">
+      <c r="O27" s="16">
         <v>5</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A28" s="24" t="str">
+      <c r="A28" s="23" t="str">
         <f t="shared" si="1"/>
         <v>1024006</v>
       </c>
-      <c r="B28" s="25">
+      <c r="B28" s="24">
         <v>102400</v>
       </c>
-      <c r="C28" s="25">
+      <c r="C28" s="24">
         <v>6</v>
       </c>
-      <c r="D28" s="25"/>
-      <c r="E28" s="33" t="s">
+      <c r="D28" s="24"/>
+      <c r="E28" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="F28" s="32">
-        <v>1</v>
-      </c>
-      <c r="G28" s="24" t="s">
+      <c r="F28" s="31">
+        <v>1</v>
+      </c>
+      <c r="G28" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="H28" s="24">
+      <c r="H28" s="23">
         <v>2024001</v>
       </c>
-      <c r="I28" s="24" t="s">
+      <c r="I28" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="J28" s="24"/>
-      <c r="K28" s="24"/>
-      <c r="L28" s="27">
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="26">
         <v>10240061</v>
       </c>
-      <c r="M28" s="24" t="s">
+      <c r="M28" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="N28" s="17">
+      <c r="N28" s="16">
         <v>4</v>
       </c>
-      <c r="O28" s="17">
+      <c r="O28" s="16">
         <v>5</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A29" s="24" t="str">
+      <c r="A29" s="23" t="str">
         <f t="shared" si="1"/>
         <v>1024007</v>
       </c>
-      <c r="B29" s="25">
+      <c r="B29" s="24">
         <v>102400</v>
       </c>
-      <c r="C29" s="25">
+      <c r="C29" s="24">
         <v>7</v>
       </c>
-      <c r="D29" s="25"/>
-      <c r="E29" s="28" t="s">
+      <c r="D29" s="24"/>
+      <c r="E29" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="F29" s="25">
-        <v>1</v>
-      </c>
-      <c r="G29" s="24" t="s">
+      <c r="F29" s="24">
+        <v>1</v>
+      </c>
+      <c r="G29" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="H29" s="24">
+      <c r="H29" s="23">
         <v>2024001</v>
       </c>
-      <c r="I29" s="24" t="s">
+      <c r="I29" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="J29" s="24"/>
-      <c r="K29" s="24"/>
-      <c r="L29" s="29" t="s">
+      <c r="J29" s="23"/>
+      <c r="K29" s="23"/>
+      <c r="L29" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="M29" s="24" t="s">
+      <c r="M29" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="N29" s="17">
+      <c r="N29" s="16">
         <v>4</v>
       </c>
-      <c r="O29" s="17">
+      <c r="O29" s="16">
         <v>5</v>
       </c>
     </row>
     <row r="30" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A30" s="24" t="str">
+      <c r="A30" s="23" t="str">
         <f t="shared" si="1"/>
         <v>1017001</v>
       </c>
@@ -3016,40 +3003,40 @@
       <c r="C30" s="5">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="D30" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="E30" s="5" t="s">
         <v>22</v>
       </c>
       <c r="F30" s="5">
         <v>1</v>
       </c>
-      <c r="G30" s="9" t="s">
+      <c r="G30" s="5" t="s">
         <v>23</v>
       </c>
       <c r="H30" s="5">
         <v>2017001</v>
       </c>
-      <c r="I30" s="9" t="s">
+      <c r="I30" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L30" s="9" t="s">
+      <c r="L30" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="M30" s="9" t="s">
+      <c r="M30" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="N30" s="45">
+      <c r="N30" s="44">
         <v>4</v>
       </c>
-      <c r="O30" s="45">
+      <c r="O30" s="44">
         <v>5</v>
       </c>
-      <c r="Q30" s="46"/>
+      <c r="Q30" s="17"/>
     </row>
     <row r="31" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A31" s="24" t="str">
+      <c r="A31" s="23" t="str">
         <f t="shared" ref="A31:A37" si="2">B31&amp;C31</f>
         <v>1017002</v>
       </c>
@@ -3059,40 +3046,40 @@
       <c r="C31" s="5">
         <v>2</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="D31" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="E31" s="9" t="s">
+      <c r="E31" s="5" t="s">
         <v>55</v>
       </c>
       <c r="F31" s="5">
         <v>1</v>
       </c>
-      <c r="G31" s="9" t="s">
+      <c r="G31" s="5" t="s">
         <v>23</v>
       </c>
       <c r="H31" s="5">
         <v>2017001</v>
       </c>
-      <c r="I31" s="9" t="s">
+      <c r="I31" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L31" s="9" t="s">
+      <c r="L31" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="M31" s="9" t="s">
+      <c r="M31" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="N31" s="45">
+      <c r="N31" s="44">
         <v>4</v>
       </c>
-      <c r="O31" s="45">
+      <c r="O31" s="44">
         <v>5</v>
       </c>
-      <c r="Q31" s="46"/>
+      <c r="Q31" s="17"/>
     </row>
     <row r="32" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A32" s="24" t="str">
+      <c r="A32" s="23" t="str">
         <f t="shared" si="2"/>
         <v>1017003</v>
       </c>
@@ -3102,40 +3089,40 @@
       <c r="C32" s="5">
         <v>3</v>
       </c>
-      <c r="D32" s="9" t="s">
+      <c r="D32" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="E32" s="9" t="s">
+      <c r="E32" s="5" t="s">
         <v>81</v>
       </c>
       <c r="F32" s="5">
         <v>1</v>
       </c>
-      <c r="G32" s="9" t="s">
+      <c r="G32" s="5" t="s">
         <v>23</v>
       </c>
       <c r="H32" s="5">
         <v>2017001</v>
       </c>
-      <c r="I32" s="9" t="s">
+      <c r="I32" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L32" s="9" t="s">
+      <c r="L32" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="M32" s="9" t="s">
+      <c r="M32" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N32" s="45">
+      <c r="N32" s="44">
         <v>4</v>
       </c>
-      <c r="O32" s="45">
+      <c r="O32" s="44">
         <v>5</v>
       </c>
-      <c r="Q32" s="46"/>
+      <c r="Q32" s="17"/>
     </row>
     <row r="33" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A33" s="24" t="str">
+      <c r="A33" s="23" t="str">
         <f t="shared" si="2"/>
         <v>1022001</v>
       </c>
@@ -3145,40 +3132,40 @@
       <c r="C33" s="5">
         <v>1</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="D33" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="E33" s="5" t="s">
         <v>22</v>
       </c>
       <c r="F33" s="5">
         <v>1</v>
       </c>
-      <c r="G33" s="9" t="s">
+      <c r="G33" s="5" t="s">
         <v>23</v>
       </c>
       <c r="H33" s="5">
         <v>2022001</v>
       </c>
-      <c r="I33" s="9" t="s">
+      <c r="I33" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L33" s="47">
+      <c r="L33" s="45">
         <v>10220031</v>
       </c>
-      <c r="M33" s="9" t="s">
+      <c r="M33" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="N33" s="45">
+      <c r="N33" s="44">
         <v>3</v>
       </c>
-      <c r="O33" s="45">
+      <c r="O33" s="44">
         <v>5</v>
       </c>
-      <c r="Q33" s="46"/>
+      <c r="Q33" s="17"/>
     </row>
     <row r="34" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A34" s="24" t="str">
+      <c r="A34" s="23" t="str">
         <f t="shared" si="2"/>
         <v>1022002</v>
       </c>
@@ -3188,40 +3175,40 @@
       <c r="C34" s="5">
         <v>2</v>
       </c>
-      <c r="D34" s="9" t="s">
+      <c r="D34" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="E34" s="9" t="s">
+      <c r="E34" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="F34" s="48">
-        <v>1</v>
-      </c>
-      <c r="G34" s="49" t="s">
+      <c r="F34" s="16">
+        <v>1</v>
+      </c>
+      <c r="G34" s="46" t="s">
         <v>23</v>
       </c>
       <c r="H34" s="5">
         <v>2022001</v>
       </c>
-      <c r="I34" s="9" t="s">
+      <c r="I34" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L34" s="50" t="s">
+      <c r="L34" s="45">
+        <v>10220033</v>
+      </c>
+      <c r="M34" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="M34" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="N34" s="45">
+      <c r="N34" s="44">
         <v>3</v>
       </c>
-      <c r="O34" s="45">
+      <c r="O34" s="44">
         <v>5</v>
       </c>
-      <c r="Q34" s="46"/>
+      <c r="Q34" s="17"/>
     </row>
     <row r="35" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A35" s="24" t="str">
+      <c r="A35" s="23" t="str">
         <f t="shared" si="2"/>
         <v>1022003</v>
       </c>
@@ -3231,40 +3218,40 @@
       <c r="C35" s="5">
         <v>3</v>
       </c>
-      <c r="D35" s="9" t="s">
+      <c r="D35" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="E35" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F35" s="51">
-        <v>1</v>
-      </c>
-      <c r="G35" s="52" t="s">
+      <c r="F35" s="46">
+        <v>1</v>
+      </c>
+      <c r="G35" s="46" t="s">
         <v>23</v>
       </c>
       <c r="H35" s="5">
         <v>2022001</v>
       </c>
-      <c r="I35" s="9" t="s">
+      <c r="I35" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L35" s="53" t="s">
-        <v>89</v>
-      </c>
-      <c r="M35" s="9" t="s">
+      <c r="L35" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="M35" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N35" s="45">
+      <c r="N35" s="44">
         <v>3</v>
       </c>
-      <c r="O35" s="45">
+      <c r="O35" s="44">
         <v>5</v>
       </c>
-      <c r="Q35" s="46"/>
+      <c r="Q35" s="17"/>
     </row>
     <row r="36" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A36" s="24" t="str">
+      <c r="A36" s="23" t="str">
         <f t="shared" si="2"/>
         <v>1022004</v>
       </c>
@@ -3274,37 +3261,37 @@
       <c r="C36" s="5">
         <v>4</v>
       </c>
-      <c r="D36" s="9" t="s">
+      <c r="D36" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="E36" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="F36" s="48">
-        <v>1</v>
-      </c>
-      <c r="G36" s="49" t="s">
+      <c r="E36" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F36" s="16">
+        <v>1</v>
+      </c>
+      <c r="G36" s="46" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="5">
         <v>2022001</v>
       </c>
-      <c r="I36" s="9" t="s">
+      <c r="I36" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L36" s="50" t="s">
-        <v>91</v>
-      </c>
-      <c r="N36" s="45">
+      <c r="L36" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="N36" s="44">
         <v>3</v>
       </c>
-      <c r="O36" s="45">
+      <c r="O36" s="44">
         <v>5</v>
       </c>
-      <c r="Q36" s="46"/>
+      <c r="Q36" s="17"/>
     </row>
     <row r="37" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A37" s="24" t="str">
+      <c r="A37" s="23" t="str">
         <f t="shared" si="2"/>
         <v>1022005</v>
       </c>
@@ -3314,118 +3301,118 @@
       <c r="C37" s="5">
         <v>5</v>
       </c>
-      <c r="D37" s="9" t="s">
+      <c r="D37" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="E37" s="9" t="s">
-        <v>92</v>
+      <c r="E37" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="F37" s="5">
         <v>1</v>
       </c>
-      <c r="G37" s="9" t="s">
+      <c r="G37" s="5" t="s">
         <v>23</v>
       </c>
       <c r="H37" s="5">
         <v>2022001</v>
       </c>
-      <c r="I37" s="9" t="s">
+      <c r="I37" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L37" s="50" t="s">
-        <v>93</v>
-      </c>
-      <c r="N37" s="45">
+      <c r="L37" s="45" t="s">
+        <v>92</v>
+      </c>
+      <c r="N37" s="44">
         <v>3</v>
       </c>
-      <c r="O37" s="45">
+      <c r="O37" s="44">
         <v>5</v>
       </c>
-      <c r="Q37" s="46"/>
-      <c r="S37" s="54"/>
+      <c r="Q37" s="17"/>
+      <c r="S37" s="48"/>
     </row>
     <row r="47" ht="16.5" spans="1:20">
-      <c r="S47" s="55"/>
-      <c r="T47" s="55"/>
+      <c r="S47" s="49"/>
+      <c r="T47" s="49"/>
     </row>
     <row r="48" ht="16.5" spans="1:20">
-      <c r="S48" s="55"/>
-      <c r="T48" s="55"/>
+      <c r="S48" s="49"/>
+      <c r="T48" s="49"/>
     </row>
     <row r="49" ht="16.5" spans="19:20">
-      <c r="S49" s="55"/>
-      <c r="T49" s="55"/>
+      <c r="S49" s="49"/>
+      <c r="T49" s="49"/>
     </row>
     <row r="50" ht="16.5" spans="19:20">
-      <c r="S50" s="55"/>
-      <c r="T50" s="55"/>
+      <c r="S50" s="49"/>
+      <c r="T50" s="49"/>
     </row>
     <row r="51" ht="16.5" spans="19:20">
-      <c r="S51" s="55"/>
-      <c r="T51" s="55"/>
+      <c r="S51" s="49"/>
+      <c r="T51" s="49"/>
     </row>
     <row r="52" ht="16.5" spans="19:20">
-      <c r="S52" s="55"/>
-      <c r="T52" s="55"/>
+      <c r="S52" s="49"/>
+      <c r="T52" s="49"/>
     </row>
     <row r="53" ht="16.5" spans="19:20">
-      <c r="S53" s="55"/>
-      <c r="T53" s="55"/>
+      <c r="S53" s="49"/>
+      <c r="T53" s="49"/>
     </row>
     <row r="54" ht="16.5" spans="19:20">
-      <c r="S54" s="55"/>
-      <c r="T54" s="55"/>
+      <c r="S54" s="49"/>
+      <c r="T54" s="49"/>
     </row>
     <row r="55" ht="16.5" spans="19:20">
-      <c r="T55" s="55"/>
+      <c r="T55" s="49"/>
     </row>
     <row r="56" ht="16.5" spans="19:20">
-      <c r="S56" s="55"/>
-      <c r="T56" s="55"/>
+      <c r="S56" s="49"/>
+      <c r="T56" s="49"/>
     </row>
     <row r="57" ht="16.5" spans="19:20">
-      <c r="S57" s="55"/>
-      <c r="T57" s="55"/>
+      <c r="S57" s="49"/>
+      <c r="T57" s="49"/>
     </row>
     <row r="58" ht="16.5" spans="19:20">
-      <c r="S58" s="55"/>
-      <c r="T58" s="55"/>
+      <c r="S58" s="49"/>
+      <c r="T58" s="49"/>
     </row>
     <row r="59" ht="16.5" spans="19:20">
-      <c r="S59" s="55"/>
-      <c r="T59" s="55"/>
+      <c r="S59" s="49"/>
+      <c r="T59" s="49"/>
     </row>
     <row r="60" ht="16.5" spans="19:20">
-      <c r="S60" s="55"/>
-      <c r="T60" s="55"/>
+      <c r="S60" s="49"/>
+      <c r="T60" s="49"/>
     </row>
     <row r="61" ht="16.5" spans="19:20">
-      <c r="S61" s="55"/>
-      <c r="T61" s="55"/>
+      <c r="S61" s="49"/>
+      <c r="T61" s="49"/>
     </row>
     <row r="62" ht="16.5" spans="19:20">
-      <c r="S62" s="55"/>
-      <c r="T62" s="55"/>
+      <c r="S62" s="49"/>
+      <c r="T62" s="49"/>
     </row>
     <row r="63" ht="16.5" spans="19:20">
-      <c r="S63" s="55"/>
-      <c r="T63" s="55"/>
+      <c r="S63" s="49"/>
+      <c r="T63" s="49"/>
     </row>
     <row r="64" ht="16.5" spans="19:20">
-      <c r="S64" s="55"/>
-      <c r="T64" s="55"/>
+      <c r="S64" s="49"/>
+      <c r="T64" s="49"/>
     </row>
     <row r="65" ht="16.5" spans="19:20">
-      <c r="S65" s="55"/>
-      <c r="T65" s="55"/>
+      <c r="S65" s="49"/>
+      <c r="T65" s="49"/>
     </row>
     <row r="66" ht="16.5" spans="19:20">
-      <c r="S66" s="55"/>
-      <c r="T66" s="55"/>
+      <c r="S66" s="49"/>
+      <c r="T66" s="49"/>
     </row>
     <row r="67" ht="16.5" spans="19:20">
-      <c r="S67" s="55"/>
-      <c r="T67" s="55"/>
+      <c r="S67" s="49"/>
+      <c r="T67" s="49"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:K2">

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="97">
   <si>
     <t>id</t>
   </si>
@@ -405,6 +405,18 @@
   </si>
   <si>
     <t>10220021|10220099|10220012</t>
+  </si>
+  <si>
+    <t>杰克船长</t>
+  </si>
+  <si>
+    <t>小游戏</t>
+  </si>
+  <si>
+    <t>改出3个bonus</t>
+  </si>
+  <si>
+    <t>10210001|10210011</t>
   </si>
 </sst>
 </file>
@@ -3037,7 +3049,7 @@
     </row>
     <row r="31" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A31" s="23" t="str">
-        <f t="shared" ref="A31:A37" si="2">B31&amp;C31</f>
+        <f t="shared" ref="A31:A41" si="2">B31&amp;C31</f>
         <v>1017002</v>
       </c>
       <c r="B31" s="5">
@@ -3330,6 +3342,182 @@
       </c>
       <c r="Q37" s="17"/>
       <c r="S37" s="48"/>
+    </row>
+    <row r="38" s="5" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A38" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>1021001</v>
+      </c>
+      <c r="B38" s="5">
+        <v>102100</v>
+      </c>
+      <c r="C38" s="5">
+        <v>1</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F38" s="5">
+        <v>1</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H38" s="5">
+        <v>2021001</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L38" s="45">
+        <v>10210001</v>
+      </c>
+      <c r="M38" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N38" s="44">
+        <v>3</v>
+      </c>
+      <c r="O38" s="44">
+        <v>5</v>
+      </c>
+      <c r="Q38" s="17"/>
+      <c r="S38" s="48"/>
+    </row>
+    <row r="39" s="5" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A39" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>1021002</v>
+      </c>
+      <c r="B39" s="5">
+        <v>102100</v>
+      </c>
+      <c r="C39" s="5">
+        <v>2</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F39" s="5">
+        <v>1</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H39" s="5">
+        <v>2021001</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L39" s="45">
+        <v>10210031</v>
+      </c>
+      <c r="M39" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="N39" s="44">
+        <v>3</v>
+      </c>
+      <c r="O39" s="44">
+        <v>5</v>
+      </c>
+      <c r="Q39" s="17"/>
+      <c r="S39" s="48"/>
+    </row>
+    <row r="40" s="5" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A40" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>1021003</v>
+      </c>
+      <c r="B40" s="5">
+        <v>102100</v>
+      </c>
+      <c r="C40" s="5">
+        <v>3</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F40" s="5">
+        <v>1</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H40" s="5">
+        <v>2021001</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L40" s="45">
+        <v>10210041</v>
+      </c>
+      <c r="M40" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="N40" s="44">
+        <v>3</v>
+      </c>
+      <c r="O40" s="44">
+        <v>5</v>
+      </c>
+      <c r="Q40" s="17"/>
+      <c r="S40" s="48"/>
+    </row>
+    <row r="41" s="5" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A41" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>1021004</v>
+      </c>
+      <c r="B41" s="5">
+        <v>102100</v>
+      </c>
+      <c r="C41" s="5">
+        <v>4</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F41" s="5">
+        <v>1</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H41" s="5">
+        <v>2021001</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L41" s="45" t="s">
+        <v>96</v>
+      </c>
+      <c r="M41" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="N41" s="44">
+        <v>3</v>
+      </c>
+      <c r="O41" s="44">
+        <v>5</v>
+      </c>
+      <c r="Q41" s="17"/>
+      <c r="S41" s="48"/>
     </row>
     <row r="47" ht="16.5" spans="1:20">
       <c r="S47" s="49"/>

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="96">
   <si>
     <t>id</t>
   </si>
@@ -383,31 +383,28 @@
     <t>雷神</t>
   </si>
   <si>
+    <t>概率改出2个SCATTER</t>
+  </si>
+  <si>
+    <t>免费</t>
+  </si>
+  <si>
+    <t>改出3个SCATTER</t>
+  </si>
+  <si>
+    <t>10220031|10220032</t>
+  </si>
+  <si>
+    <t>火焰免费</t>
+  </si>
+  <si>
+    <t>冰冻免费</t>
+  </si>
+  <si>
+    <t>杰克船长</t>
+  </si>
+  <si>
     <t>改出2个SCATTER</t>
-  </si>
-  <si>
-    <t>免费</t>
-  </si>
-  <si>
-    <t>改出3个SCATTER</t>
-  </si>
-  <si>
-    <t>10220031|10220032</t>
-  </si>
-  <si>
-    <t>火焰免费</t>
-  </si>
-  <si>
-    <t>10220011|10220099|10220012</t>
-  </si>
-  <si>
-    <t>冰冻免费</t>
-  </si>
-  <si>
-    <t>10220021|10220099|10220012</t>
-  </si>
-  <si>
-    <t>杰克船长</t>
   </si>
   <si>
     <t>小游戏</t>
@@ -3163,7 +3160,7 @@
         <v>24</v>
       </c>
       <c r="L33" s="45">
-        <v>10220031</v>
+        <v>10220030</v>
       </c>
       <c r="M33" s="5" t="s">
         <v>85</v>
@@ -3291,8 +3288,8 @@
       <c r="I36" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L36" s="45" t="s">
-        <v>90</v>
+      <c r="L36" s="45">
+        <v>10220019</v>
       </c>
       <c r="N36" s="44">
         <v>3</v>
@@ -3317,7 +3314,7 @@
         <v>84</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F37" s="5">
         <v>1</v>
@@ -3331,8 +3328,8 @@
       <c r="I37" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L37" s="45" t="s">
-        <v>92</v>
+      <c r="L37" s="45">
+        <v>10220020</v>
       </c>
       <c r="N37" s="44">
         <v>3</v>
@@ -3355,7 +3352,7 @@
         <v>1</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E38" s="5" t="s">
         <v>22</v>
@@ -3376,7 +3373,7 @@
         <v>10210001</v>
       </c>
       <c r="M38" s="5" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="N38" s="44">
         <v>3</v>
@@ -3399,7 +3396,7 @@
         <v>2</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E39" s="5" t="s">
         <v>86</v>
@@ -3443,10 +3440,10 @@
         <v>3</v>
       </c>
       <c r="D40" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E40" s="5" t="s">
         <v>93</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>94</v>
       </c>
       <c r="F40" s="5">
         <v>1</v>
@@ -3464,7 +3461,7 @@
         <v>10210041</v>
       </c>
       <c r="M40" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N40" s="44">
         <v>3</v>
@@ -3487,7 +3484,7 @@
         <v>4</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E41" s="5" t="s">
         <v>81</v>
@@ -3505,7 +3502,7 @@
         <v>24</v>
       </c>
       <c r="L41" s="45" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M41" s="5" t="s">
         <v>83</v>

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="95">
   <si>
     <t>id</t>
   </si>
@@ -402,9 +402,6 @@
   </si>
   <si>
     <t>杰克船长</t>
-  </si>
-  <si>
-    <t>改出2个SCATTER</t>
   </si>
   <si>
     <t>小游戏</t>
@@ -3370,10 +3367,10 @@
         <v>24</v>
       </c>
       <c r="L38" s="45">
-        <v>10210001</v>
+        <v>10210051</v>
       </c>
       <c r="M38" s="5" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="N38" s="44">
         <v>3</v>
@@ -3443,7 +3440,7 @@
         <v>91</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F40" s="5">
         <v>1</v>
@@ -3461,7 +3458,7 @@
         <v>10210041</v>
       </c>
       <c r="M40" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N40" s="44">
         <v>3</v>
@@ -3502,7 +3499,7 @@
         <v>24</v>
       </c>
       <c r="L41" s="45" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M41" s="5" t="s">
         <v>83</v>

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="100">
   <si>
     <t>id</t>
   </si>
@@ -383,7 +383,10 @@
     <t>雷神</t>
   </si>
   <si>
-    <t>概率改出2个SCATTER</t>
+    <t>10220030|10220001</t>
+  </si>
+  <si>
+    <t>概率改出2个SCATTER、概率改出wild</t>
   </si>
   <si>
     <t>免费</t>
@@ -404,6 +407,9 @@
     <t>杰克船长</t>
   </si>
   <si>
+    <t>10210051|10210021</t>
+  </si>
+  <si>
     <t>小游戏</t>
   </si>
   <si>
@@ -411,6 +417,15 @@
   </si>
   <si>
     <t>10210001|10210011</t>
+  </si>
+  <si>
+    <t>篮球巨星</t>
+  </si>
+  <si>
+    <t>10180002|10180021</t>
+  </si>
+  <si>
+    <t>10180001|10180011</t>
   </si>
 </sst>
 </file>
@@ -3156,11 +3171,11 @@
       <c r="I33" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L33" s="45">
-        <v>10220030</v>
+      <c r="L33" s="45" t="s">
+        <v>85</v>
       </c>
       <c r="M33" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N33" s="44">
         <v>3</v>
@@ -3185,7 +3200,7 @@
         <v>84</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F34" s="16">
         <v>1</v>
@@ -3203,7 +3218,7 @@
         <v>10220033</v>
       </c>
       <c r="M34" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N34" s="44">
         <v>3</v>
@@ -3243,7 +3258,7 @@
         <v>24</v>
       </c>
       <c r="L35" s="47" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M35" s="5" t="s">
         <v>83</v>
@@ -3271,7 +3286,7 @@
         <v>84</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F36" s="16">
         <v>1</v>
@@ -3311,7 +3326,7 @@
         <v>84</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F37" s="5">
         <v>1</v>
@@ -3349,7 +3364,7 @@
         <v>1</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E38" s="5" t="s">
         <v>22</v>
@@ -3366,11 +3381,11 @@
       <c r="I38" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L38" s="45">
-        <v>10210051</v>
+      <c r="L38" s="45" t="s">
+        <v>93</v>
       </c>
       <c r="M38" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N38" s="44">
         <v>3</v>
@@ -3393,10 +3408,10 @@
         <v>2</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F39" s="5">
         <v>1</v>
@@ -3414,7 +3429,7 @@
         <v>10210031</v>
       </c>
       <c r="M39" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N39" s="44">
         <v>3</v>
@@ -3437,10 +3452,10 @@
         <v>3</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F40" s="5">
         <v>1</v>
@@ -3458,7 +3473,7 @@
         <v>10210041</v>
       </c>
       <c r="M40" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="N40" s="44">
         <v>3</v>
@@ -3481,7 +3496,7 @@
         <v>4</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E41" s="5" t="s">
         <v>81</v>
@@ -3499,7 +3514,7 @@
         <v>24</v>
       </c>
       <c r="L41" s="45" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="M41" s="5" t="s">
         <v>83</v>
@@ -3512,6 +3527,134 @@
       </c>
       <c r="Q41" s="17"/>
       <c r="S41" s="48"/>
+    </row>
+    <row r="42" s="5" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A42" s="23" t="str">
+        <f>B42&amp;C42</f>
+        <v>1018001</v>
+      </c>
+      <c r="B42" s="5">
+        <v>101800</v>
+      </c>
+      <c r="C42" s="5">
+        <v>1</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F42" s="5">
+        <v>1</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H42" s="5">
+        <v>2018001</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L42" s="45" t="s">
+        <v>98</v>
+      </c>
+      <c r="M42" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="N42" s="44">
+        <v>4</v>
+      </c>
+      <c r="O42" s="44">
+        <v>6</v>
+      </c>
+      <c r="Q42" s="17"/>
+      <c r="S42" s="48"/>
+    </row>
+    <row r="43" s="5" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A43" s="5" t="str">
+        <f>B43&amp;C43</f>
+        <v>1018002</v>
+      </c>
+      <c r="B43" s="5">
+        <v>101800</v>
+      </c>
+      <c r="C43" s="5">
+        <v>2</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F43" s="5">
+        <v>1</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H43" s="5">
+        <v>2018001</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L43" s="45">
+        <v>10180031</v>
+      </c>
+      <c r="M43" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="N43" s="44">
+        <v>4</v>
+      </c>
+      <c r="O43" s="44">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" ht="16.5" spans="1:20">
+      <c r="A44" s="5" t="str">
+        <f>B44&amp;C44</f>
+        <v>1018003</v>
+      </c>
+      <c r="B44" s="5">
+        <v>101800</v>
+      </c>
+      <c r="C44" s="5">
+        <v>3</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F44" s="5">
+        <v>1</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H44" s="5">
+        <v>2018001</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L44" s="45" t="s">
+        <v>99</v>
+      </c>
+      <c r="M44" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="N44" s="44">
+        <v>4</v>
+      </c>
+      <c r="O44" s="44">
+        <v>6</v>
+      </c>
     </row>
     <row r="47" ht="16.5" spans="1:20">
       <c r="S47" s="49"/>

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="104">
   <si>
     <t>id</t>
   </si>
@@ -426,6 +426,18 @@
   </si>
   <si>
     <t>10180001|10180011</t>
+  </si>
+  <si>
+    <t>寒冰王座</t>
+  </si>
+  <si>
+    <t>10250001|10250021</t>
+  </si>
+  <si>
+    <t>改出3个以上SCATTER</t>
+  </si>
+  <si>
+    <t>10250002|10250011</t>
   </si>
 </sst>
 </file>
@@ -3058,7 +3070,7 @@
     </row>
     <row r="31" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A31" s="23" t="str">
-        <f t="shared" ref="A31:A41" si="2">B31&amp;C31</f>
+        <f t="shared" ref="A31:A44" si="2">B31&amp;C31</f>
         <v>1017002</v>
       </c>
       <c r="B31" s="5">
@@ -3530,7 +3542,7 @@
     </row>
     <row r="42" s="5" customFormat="1" ht="16.5" spans="1:20">
       <c r="A42" s="23" t="str">
-        <f>B42&amp;C42</f>
+        <f t="shared" si="2"/>
         <v>1018001</v>
       </c>
       <c r="B42" s="5">
@@ -3574,7 +3586,7 @@
     </row>
     <row r="43" s="5" customFormat="1" ht="16.5" spans="1:20">
       <c r="A43" s="5" t="str">
-        <f>B43&amp;C43</f>
+        <f t="shared" si="2"/>
         <v>1018002</v>
       </c>
       <c r="B43" s="5">
@@ -3616,7 +3628,7 @@
     </row>
     <row r="44" ht="16.5" spans="1:20">
       <c r="A44" s="5" t="str">
-        <f>B44&amp;C44</f>
+        <f t="shared" si="2"/>
         <v>1018003</v>
       </c>
       <c r="B44" s="5">
@@ -3656,9 +3668,134 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" ht="16.5" spans="1:20">
-      <c r="S47" s="49"/>
-      <c r="T47" s="49"/>
+    <row r="45" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A45" s="5" t="str">
+        <f>B45&amp;C45</f>
+        <v>1025001</v>
+      </c>
+      <c r="B45" s="5">
+        <v>102500</v>
+      </c>
+      <c r="C45" s="5">
+        <v>1</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F45" s="5">
+        <v>1</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H45" s="5">
+        <v>2025001</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45" s="45" t="s">
+        <v>101</v>
+      </c>
+      <c r="M45" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="N45" s="44">
+        <v>3</v>
+      </c>
+      <c r="O45" s="44">
+        <v>5</v>
+      </c>
+      <c r="Q45" s="7"/>
+    </row>
+    <row r="46" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A46" s="5" t="str">
+        <f>B46&amp;C46</f>
+        <v>1025002</v>
+      </c>
+      <c r="B46" s="5">
+        <v>102500</v>
+      </c>
+      <c r="C46" s="5">
+        <v>2</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F46" s="5">
+        <v>1</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H46" s="5">
+        <v>2025001</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L46" s="45">
+        <v>10250031</v>
+      </c>
+      <c r="M46" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="N46" s="44">
+        <v>3</v>
+      </c>
+      <c r="O46" s="44">
+        <v>5</v>
+      </c>
+      <c r="Q46" s="7"/>
+    </row>
+    <row r="47" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A47" s="5" t="str">
+        <f>B47&amp;C47</f>
+        <v>1025003</v>
+      </c>
+      <c r="B47" s="5">
+        <v>102500</v>
+      </c>
+      <c r="C47" s="5">
+        <v>3</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F47" s="5">
+        <v>1</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H47" s="5">
+        <v>2025001</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L47" s="45" t="s">
+        <v>103</v>
+      </c>
+      <c r="M47" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="N47" s="44">
+        <v>3</v>
+      </c>
+      <c r="O47" s="44">
+        <v>5</v>
+      </c>
+      <c r="Q47" s="7"/>
     </row>
     <row r="48" ht="16.5" spans="1:20">
       <c r="S48" s="49"/>

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="107">
   <si>
     <t>id</t>
   </si>
@@ -438,6 +438,15 @@
   </si>
   <si>
     <t>10250002|10250011</t>
+  </si>
+  <si>
+    <t>蒸汽时代</t>
+  </si>
+  <si>
+    <t>10230001|10230021</t>
+  </si>
+  <si>
+    <t>10230002|10230011</t>
   </si>
 </sst>
 </file>
@@ -3070,7 +3079,7 @@
     </row>
     <row r="31" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A31" s="23" t="str">
-        <f t="shared" ref="A31:A44" si="2">B31&amp;C31</f>
+        <f t="shared" ref="A31:A47" si="2">B31&amp;C31</f>
         <v>1017002</v>
       </c>
       <c r="B31" s="5">
@@ -3154,7 +3163,7 @@
       </c>
       <c r="Q32" s="17"/>
     </row>
-    <row r="33" s="5" customFormat="1" ht="16.5" spans="1:20">
+    <row r="33" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A33" s="23" t="str">
         <f t="shared" si="2"/>
         <v>1022001</v>
@@ -3197,7 +3206,7 @@
       </c>
       <c r="Q33" s="17"/>
     </row>
-    <row r="34" s="5" customFormat="1" ht="16.5" spans="1:20">
+    <row r="34" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A34" s="23" t="str">
         <f t="shared" si="2"/>
         <v>1022002</v>
@@ -3240,7 +3249,7 @@
       </c>
       <c r="Q34" s="17"/>
     </row>
-    <row r="35" s="5" customFormat="1" ht="16.5" spans="1:20">
+    <row r="35" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A35" s="23" t="str">
         <f t="shared" si="2"/>
         <v>1022003</v>
@@ -3283,7 +3292,7 @@
       </c>
       <c r="Q35" s="17"/>
     </row>
-    <row r="36" s="5" customFormat="1" ht="16.5" spans="1:20">
+    <row r="36" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A36" s="23" t="str">
         <f t="shared" si="2"/>
         <v>1022004</v>
@@ -3323,7 +3332,7 @@
       </c>
       <c r="Q36" s="17"/>
     </row>
-    <row r="37" s="5" customFormat="1" ht="16.5" spans="1:20">
+    <row r="37" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A37" s="23" t="str">
         <f t="shared" si="2"/>
         <v>1022005</v>
@@ -3364,7 +3373,7 @@
       <c r="Q37" s="17"/>
       <c r="S37" s="48"/>
     </row>
-    <row r="38" s="5" customFormat="1" ht="16.5" spans="1:20">
+    <row r="38" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A38" s="23" t="str">
         <f t="shared" si="2"/>
         <v>1021001</v>
@@ -3408,7 +3417,7 @@
       <c r="Q38" s="17"/>
       <c r="S38" s="48"/>
     </row>
-    <row r="39" s="5" customFormat="1" ht="16.5" spans="1:20">
+    <row r="39" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A39" s="23" t="str">
         <f t="shared" si="2"/>
         <v>1021002</v>
@@ -3452,7 +3461,7 @@
       <c r="Q39" s="17"/>
       <c r="S39" s="48"/>
     </row>
-    <row r="40" s="5" customFormat="1" ht="16.5" spans="1:20">
+    <row r="40" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A40" s="23" t="str">
         <f t="shared" si="2"/>
         <v>1021003</v>
@@ -3496,7 +3505,7 @@
       <c r="Q40" s="17"/>
       <c r="S40" s="48"/>
     </row>
-    <row r="41" s="5" customFormat="1" ht="16.5" spans="1:20">
+    <row r="41" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A41" s="23" t="str">
         <f t="shared" si="2"/>
         <v>1021004</v>
@@ -3540,7 +3549,7 @@
       <c r="Q41" s="17"/>
       <c r="S41" s="48"/>
     </row>
-    <row r="42" s="5" customFormat="1" ht="16.5" spans="1:20">
+    <row r="42" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A42" s="23" t="str">
         <f t="shared" si="2"/>
         <v>1018001</v>
@@ -3584,7 +3593,7 @@
       <c r="Q42" s="17"/>
       <c r="S42" s="48"/>
     </row>
-    <row r="43" s="5" customFormat="1" ht="16.5" spans="1:20">
+    <row r="43" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A43" s="5" t="str">
         <f t="shared" si="2"/>
         <v>1018002</v>
@@ -3626,7 +3635,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" ht="16.5" spans="1:20">
+    <row r="44" ht="16.5" spans="1:19">
       <c r="A44" s="5" t="str">
         <f t="shared" si="2"/>
         <v>1018003</v>
@@ -3668,9 +3677,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" customFormat="1" ht="16.5" spans="1:20">
+    <row r="45" customFormat="1" ht="16.5" spans="1:19">
       <c r="A45" s="5" t="str">
-        <f>B45&amp;C45</f>
+        <f t="shared" si="2"/>
         <v>1025001</v>
       </c>
       <c r="B45" s="5">
@@ -3711,9 +3720,9 @@
       </c>
       <c r="Q45" s="7"/>
     </row>
-    <row r="46" customFormat="1" ht="16.5" spans="1:20">
+    <row r="46" customFormat="1" ht="16.5" spans="1:19">
       <c r="A46" s="5" t="str">
-        <f>B46&amp;C46</f>
+        <f t="shared" si="2"/>
         <v>1025002</v>
       </c>
       <c r="B46" s="5">
@@ -3754,9 +3763,9 @@
       </c>
       <c r="Q46" s="7"/>
     </row>
-    <row r="47" customFormat="1" ht="16.5" spans="1:20">
+    <row r="47" customFormat="1" ht="16.5" spans="1:19">
       <c r="A47" s="5" t="str">
-        <f>B47&amp;C47</f>
+        <f t="shared" si="2"/>
         <v>1025003</v>
       </c>
       <c r="B47" s="5">
@@ -3797,70 +3806,188 @@
       </c>
       <c r="Q47" s="7"/>
     </row>
-    <row r="48" ht="16.5" spans="1:20">
-      <c r="S48" s="49"/>
-      <c r="T48" s="49"/>
-    </row>
-    <row r="49" ht="16.5" spans="19:20">
-      <c r="S49" s="49"/>
-      <c r="T49" s="49"/>
-    </row>
-    <row r="50" ht="16.5" spans="19:20">
-      <c r="S50" s="49"/>
-      <c r="T50" s="49"/>
-    </row>
-    <row r="51" ht="16.5" spans="19:20">
+    <row r="48" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A48" s="5" t="str">
+        <f>B48&amp;C48</f>
+        <v>1023001</v>
+      </c>
+      <c r="B48" s="5">
+        <v>102300</v>
+      </c>
+      <c r="C48" s="5">
+        <v>1</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F48" s="5">
+        <v>1</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H48" s="5">
+        <v>2023001</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L48" s="45" t="s">
+        <v>105</v>
+      </c>
+      <c r="M48" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="N48" s="44">
+        <v>4</v>
+      </c>
+      <c r="O48" s="44">
+        <v>5</v>
+      </c>
+      <c r="Q48" s="7"/>
+    </row>
+    <row r="49" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A49" s="5" t="str">
+        <f>B49&amp;C49</f>
+        <v>1023002</v>
+      </c>
+      <c r="B49" s="5">
+        <v>102300</v>
+      </c>
+      <c r="C49" s="5">
+        <v>2</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F49" s="5">
+        <v>1</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H49" s="5">
+        <v>2023001</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L49" s="45">
+        <v>10230003</v>
+      </c>
+      <c r="M49" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="N49" s="44">
+        <v>4</v>
+      </c>
+      <c r="O49" s="44">
+        <v>5</v>
+      </c>
+      <c r="Q49" s="7"/>
+    </row>
+    <row r="50" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A50" s="5" t="str">
+        <f>B50&amp;C50</f>
+        <v>1023003</v>
+      </c>
+      <c r="B50" s="5">
+        <v>102300</v>
+      </c>
+      <c r="C50" s="5">
+        <v>3</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F50" s="5">
+        <v>1</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H50" s="5">
+        <v>2023001</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L50" s="45" t="s">
+        <v>106</v>
+      </c>
+      <c r="M50" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="N50" s="44">
+        <v>4</v>
+      </c>
+      <c r="O50" s="44">
+        <v>5</v>
+      </c>
+      <c r="Q50" s="7"/>
+    </row>
+    <row r="51" ht="16.5" spans="1:20">
       <c r="S51" s="49"/>
       <c r="T51" s="49"/>
     </row>
-    <row r="52" ht="16.5" spans="19:20">
+    <row r="52" ht="16.5" spans="1:20">
+      <c r="L52" s="5"/>
       <c r="S52" s="49"/>
       <c r="T52" s="49"/>
     </row>
-    <row r="53" ht="16.5" spans="19:20">
+    <row r="53" ht="16.5" spans="1:20">
       <c r="S53" s="49"/>
       <c r="T53" s="49"/>
     </row>
-    <row r="54" ht="16.5" spans="19:20">
+    <row r="54" ht="16.5" spans="1:20">
       <c r="S54" s="49"/>
       <c r="T54" s="49"/>
     </row>
-    <row r="55" ht="16.5" spans="19:20">
+    <row r="55" ht="16.5" spans="1:20">
       <c r="T55" s="49"/>
     </row>
-    <row r="56" ht="16.5" spans="19:20">
+    <row r="56" ht="16.5" spans="1:20">
       <c r="S56" s="49"/>
       <c r="T56" s="49"/>
     </row>
-    <row r="57" ht="16.5" spans="19:20">
+    <row r="57" ht="16.5" spans="1:20">
       <c r="S57" s="49"/>
       <c r="T57" s="49"/>
     </row>
-    <row r="58" ht="16.5" spans="19:20">
+    <row r="58" ht="16.5" spans="1:20">
       <c r="S58" s="49"/>
       <c r="T58" s="49"/>
     </row>
-    <row r="59" ht="16.5" spans="19:20">
+    <row r="59" ht="16.5" spans="1:20">
       <c r="S59" s="49"/>
       <c r="T59" s="49"/>
     </row>
-    <row r="60" ht="16.5" spans="19:20">
+    <row r="60" ht="16.5" spans="1:20">
       <c r="S60" s="49"/>
       <c r="T60" s="49"/>
     </row>
-    <row r="61" ht="16.5" spans="19:20">
+    <row r="61" ht="16.5" spans="1:20">
       <c r="S61" s="49"/>
       <c r="T61" s="49"/>
     </row>
-    <row r="62" ht="16.5" spans="19:20">
+    <row r="62" ht="16.5" spans="1:20">
       <c r="S62" s="49"/>
       <c r="T62" s="49"/>
     </row>
-    <row r="63" ht="16.5" spans="19:20">
+    <row r="63" ht="16.5" spans="1:20">
       <c r="S63" s="49"/>
       <c r="T63" s="49"/>
     </row>
-    <row r="64" ht="16.5" spans="19:20">
+    <row r="64" ht="16.5" spans="1:20">
       <c r="S64" s="49"/>
       <c r="T64" s="49"/>
     </row>

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="147">
   <si>
     <t>id</t>
   </si>
@@ -447,6 +447,126 @@
   </si>
   <si>
     <t>10230002|10230011</t>
+  </si>
+  <si>
+    <t>神马飞扬</t>
+  </si>
+  <si>
+    <t>概率改出wild</t>
+  </si>
+  <si>
+    <t>橘子福马模式</t>
+  </si>
+  <si>
+    <t>10340001|10340001|10340001|10340011|10340011</t>
+  </si>
+  <si>
+    <t>改出两个橘子or两个wind符号×3+改出1个橘子or1个wind符号×2</t>
+  </si>
+  <si>
+    <t>当第一次执行10340011修改出的符号出现的位置上有符号时，结束此模式，不执行第二次10340011</t>
+  </si>
+  <si>
+    <t>鞭炮福马模式</t>
+  </si>
+  <si>
+    <t>10340002|10340002|10340002|10340012|10340012</t>
+  </si>
+  <si>
+    <t>改出两个鞭炮or两个wind符号×3+改出1个鞭炮or1个wind符号×2</t>
+  </si>
+  <si>
+    <t>同上</t>
+  </si>
+  <si>
+    <t>红包福马模式</t>
+  </si>
+  <si>
+    <t>10340003|10340003|10340003|10340013|10340013</t>
+  </si>
+  <si>
+    <t>改出两个红包or两个wind符号×3+改出1个红包or1个wind符号×2</t>
+  </si>
+  <si>
+    <t>福袋福马模式</t>
+  </si>
+  <si>
+    <t>10340004|10340004|10340004|10340014|10340014</t>
+  </si>
+  <si>
+    <t>改出两个福袋or两个wind符号×3+改出1个福袋or1个wind符号×2</t>
+  </si>
+  <si>
+    <t>玉如意福马模式</t>
+  </si>
+  <si>
+    <t>10340005|10340005|10340005|10340015|10340015</t>
+  </si>
+  <si>
+    <t>改出两个玉如意or两个wind符号×3+改出1个玉如意or1个wind符号×2</t>
+  </si>
+  <si>
+    <t>元宝福马模式</t>
+  </si>
+  <si>
+    <t>10340006|10340006|10340006|10340016|10340016</t>
+  </si>
+  <si>
+    <t>改出两个元宝or两个wind符号×3+改出1个元宝or1个wind符号×2</t>
+  </si>
+  <si>
+    <t>橘子触发jackpot大奖</t>
+  </si>
+  <si>
+    <t>10340001|10340001|10340001|10340021|10340021|10340008</t>
+  </si>
+  <si>
+    <t>改出两个橘子or两个wind符号×3+改出1个橘子or1个wind符号×3</t>
+  </si>
+  <si>
+    <t>鞭炮触发jackpot大奖</t>
+  </si>
+  <si>
+    <t>10340002|10340002|10340002|10340022|10340022|10340008</t>
+  </si>
+  <si>
+    <t>改出两个鞭炮or两个wind符号×3+改出1个鞭炮or1个wind符号×3</t>
+  </si>
+  <si>
+    <t>红包触发jackpot大奖</t>
+  </si>
+  <si>
+    <t>10340003|10340003|10340003|10340023|10340023|10340008</t>
+  </si>
+  <si>
+    <t>改出两个红包or两个wind符号×3+改出1个红包or1个wind符号×3</t>
+  </si>
+  <si>
+    <t>福袋触发jackpot大奖</t>
+  </si>
+  <si>
+    <t>10340004|10340004|10340004|10340024|10340024|10340008</t>
+  </si>
+  <si>
+    <t>改出两个福袋or两个wind符号×3+改出1个福袋or1个wind符号×3</t>
+  </si>
+  <si>
+    <t>玉如意触发jackpot大奖</t>
+  </si>
+  <si>
+    <t>10340005|10340005|10340005|10340025|10340025|10340008</t>
+  </si>
+  <si>
+    <t>改出两个玉如意or两个wind符号×3+改出1个玉如意or1个wind符号×3</t>
+  </si>
+  <si>
+    <t>元宝触发jackpot大奖</t>
+  </si>
+  <si>
+    <t>10340006|10340006|10340006|10340026|10340026|10340008</t>
+  </si>
+  <si>
+    <t>改出两个元宝or两个wind符号×3+改出1个元宝or1个wind符号×3</t>
   </si>
 </sst>
 </file>
@@ -460,7 +580,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -476,6 +596,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -624,12 +750,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1034,133 +1160,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1273,7 +1399,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1807,7 +1933,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T67"/>
+  <dimension ref="A1:S84"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
@@ -3079,7 +3205,7 @@
     </row>
     <row r="31" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A31" s="23" t="str">
-        <f t="shared" ref="A31:A47" si="2">B31&amp;C31</f>
+        <f t="shared" ref="A31:A51" si="2">B31&amp;C31</f>
         <v>1017002</v>
       </c>
       <c r="B31" s="5">
@@ -3808,7 +3934,7 @@
     </row>
     <row r="48" customFormat="1" ht="16.5" spans="1:19">
       <c r="A48" s="5" t="str">
-        <f>B48&amp;C48</f>
+        <f t="shared" si="2"/>
         <v>1023001</v>
       </c>
       <c r="B48" s="5">
@@ -3849,9 +3975,9 @@
       </c>
       <c r="Q48" s="7"/>
     </row>
-    <row r="49" customFormat="1" ht="16.5" spans="1:20">
+    <row r="49" customFormat="1" ht="16.5" spans="1:17">
       <c r="A49" s="5" t="str">
-        <f>B49&amp;C49</f>
+        <f t="shared" si="2"/>
         <v>1023002</v>
       </c>
       <c r="B49" s="5">
@@ -3892,9 +4018,9 @@
       </c>
       <c r="Q49" s="7"/>
     </row>
-    <row r="50" customFormat="1" ht="16.5" spans="1:20">
+    <row r="50" customFormat="1" ht="16.5" spans="1:17">
       <c r="A50" s="5" t="str">
-        <f>B50&amp;C50</f>
+        <f t="shared" si="2"/>
         <v>1023003</v>
       </c>
       <c r="B50" s="5">
@@ -3935,73 +4061,918 @@
       </c>
       <c r="Q50" s="7"/>
     </row>
-    <row r="51" ht="16.5" spans="1:20">
-      <c r="S51" s="49"/>
-      <c r="T51" s="49"/>
-    </row>
-    <row r="52" ht="16.5" spans="1:20">
-      <c r="L52" s="5"/>
-      <c r="S52" s="49"/>
-      <c r="T52" s="49"/>
-    </row>
-    <row r="53" ht="16.5" spans="1:20">
-      <c r="S53" s="49"/>
-      <c r="T53" s="49"/>
-    </row>
-    <row r="54" ht="16.5" spans="1:20">
-      <c r="S54" s="49"/>
-      <c r="T54" s="49"/>
-    </row>
-    <row r="55" ht="16.5" spans="1:20">
-      <c r="T55" s="49"/>
-    </row>
-    <row r="56" ht="16.5" spans="1:20">
-      <c r="S56" s="49"/>
-      <c r="T56" s="49"/>
-    </row>
-    <row r="57" ht="16.5" spans="1:20">
-      <c r="S57" s="49"/>
-      <c r="T57" s="49"/>
-    </row>
-    <row r="58" ht="16.5" spans="1:20">
-      <c r="S58" s="49"/>
-      <c r="T58" s="49"/>
-    </row>
-    <row r="59" ht="16.5" spans="1:20">
-      <c r="S59" s="49"/>
-      <c r="T59" s="49"/>
-    </row>
-    <row r="60" ht="16.5" spans="1:20">
-      <c r="S60" s="49"/>
-      <c r="T60" s="49"/>
-    </row>
-    <row r="61" ht="16.5" spans="1:20">
-      <c r="S61" s="49"/>
-      <c r="T61" s="49"/>
-    </row>
-    <row r="62" ht="16.5" spans="1:20">
-      <c r="S62" s="49"/>
-      <c r="T62" s="49"/>
-    </row>
-    <row r="63" ht="16.5" spans="1:20">
-      <c r="S63" s="49"/>
-      <c r="T63" s="49"/>
-    </row>
-    <row r="64" ht="16.5" spans="1:20">
-      <c r="S64" s="49"/>
-      <c r="T64" s="49"/>
-    </row>
-    <row r="65" ht="16.5" spans="19:20">
-      <c r="S65" s="49"/>
-      <c r="T65" s="49"/>
-    </row>
-    <row r="66" ht="16.5" spans="19:20">
-      <c r="S66" s="49"/>
-      <c r="T66" s="49"/>
-    </row>
-    <row r="67" ht="16.5" spans="19:20">
-      <c r="S67" s="49"/>
-      <c r="T67" s="49"/>
+    <row r="51" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A51" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>1034001</v>
+      </c>
+      <c r="B51" s="5">
+        <v>103400</v>
+      </c>
+      <c r="C51" s="5">
+        <v>1</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F51" s="5">
+        <v>1</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H51" s="5">
+        <v>2034001</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L51" s="45">
+        <v>10340007</v>
+      </c>
+      <c r="M51" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="N51" s="44">
+        <v>3</v>
+      </c>
+      <c r="O51" s="44">
+        <v>3</v>
+      </c>
+      <c r="Q51" s="7"/>
+    </row>
+    <row r="52" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A52" s="5" t="str">
+        <f t="shared" ref="A52:A57" si="3">B52&amp;C52</f>
+        <v>1034002</v>
+      </c>
+      <c r="B52" s="5">
+        <v>103400</v>
+      </c>
+      <c r="C52" s="5">
+        <v>2</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F52" s="5">
+        <v>1</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H52" s="5">
+        <v>2034001</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L52" s="45" t="s">
+        <v>110</v>
+      </c>
+      <c r="M52" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="N52" s="44">
+        <v>3</v>
+      </c>
+      <c r="O52" s="44">
+        <v>3</v>
+      </c>
+      <c r="P52" s="49" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q52" s="7"/>
+    </row>
+    <row r="53" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A53" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1034003</v>
+      </c>
+      <c r="B53" s="5">
+        <v>103400</v>
+      </c>
+      <c r="C53" s="5">
+        <v>3</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="F53" s="5">
+        <v>1</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H53" s="5">
+        <v>2034001</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L53" s="45" t="s">
+        <v>114</v>
+      </c>
+      <c r="M53" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="N53" s="44">
+        <v>3</v>
+      </c>
+      <c r="O53" s="44">
+        <v>3</v>
+      </c>
+      <c r="P53" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q53" s="7"/>
+    </row>
+    <row r="54" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A54" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1034004</v>
+      </c>
+      <c r="B54" s="5">
+        <v>103400</v>
+      </c>
+      <c r="C54" s="5">
+        <v>4</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F54" s="5">
+        <v>1</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H54" s="5">
+        <v>2034001</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L54" s="45" t="s">
+        <v>118</v>
+      </c>
+      <c r="M54" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="N54" s="44">
+        <v>3</v>
+      </c>
+      <c r="O54" s="44">
+        <v>3</v>
+      </c>
+      <c r="P54" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q54" s="7"/>
+    </row>
+    <row r="55" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A55" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1034005</v>
+      </c>
+      <c r="B55" s="5">
+        <v>103400</v>
+      </c>
+      <c r="C55" s="5">
+        <v>5</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F55" s="5">
+        <v>1</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H55" s="5">
+        <v>2034001</v>
+      </c>
+      <c r="I55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L55" s="45" t="s">
+        <v>121</v>
+      </c>
+      <c r="M55" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="N55" s="44">
+        <v>3</v>
+      </c>
+      <c r="O55" s="44">
+        <v>3</v>
+      </c>
+      <c r="P55" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q55" s="7"/>
+    </row>
+    <row r="56" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A56" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1034006</v>
+      </c>
+      <c r="B56" s="5">
+        <v>103400</v>
+      </c>
+      <c r="C56" s="5">
+        <v>6</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F56" s="5">
+        <v>1</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H56" s="5">
+        <v>2034001</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L56" s="45" t="s">
+        <v>124</v>
+      </c>
+      <c r="M56" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="N56" s="44">
+        <v>3</v>
+      </c>
+      <c r="O56" s="44">
+        <v>3</v>
+      </c>
+      <c r="P56" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q56" s="7"/>
+    </row>
+    <row r="57" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A57" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1034007</v>
+      </c>
+      <c r="B57" s="5">
+        <v>103400</v>
+      </c>
+      <c r="C57" s="5">
+        <v>7</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F57" s="5">
+        <v>1</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H57" s="5">
+        <v>2034001</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L57" s="45" t="s">
+        <v>127</v>
+      </c>
+      <c r="M57" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="N57" s="44">
+        <v>3</v>
+      </c>
+      <c r="O57" s="44">
+        <v>3</v>
+      </c>
+      <c r="P57" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q57" s="7"/>
+    </row>
+    <row r="58" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A58" s="5" t="str">
+        <f t="shared" ref="A58:A63" si="4">B58&amp;C58</f>
+        <v>1034008</v>
+      </c>
+      <c r="B58" s="5">
+        <v>103400</v>
+      </c>
+      <c r="C58" s="5">
+        <v>8</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F58" s="5">
+        <v>1</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H58" s="5">
+        <v>2034001</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L58" s="45" t="s">
+        <v>130</v>
+      </c>
+      <c r="M58" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="N58" s="44">
+        <v>3</v>
+      </c>
+      <c r="O58" s="44">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="7"/>
+    </row>
+    <row r="59" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A59" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>1034009</v>
+      </c>
+      <c r="B59" s="5">
+        <v>103400</v>
+      </c>
+      <c r="C59" s="5">
+        <v>9</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F59" s="5">
+        <v>1</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H59" s="5">
+        <v>2034001</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L59" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="M59" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="N59" s="44">
+        <v>3</v>
+      </c>
+      <c r="O59" s="44">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="7"/>
+    </row>
+    <row r="60" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A60" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>10340010</v>
+      </c>
+      <c r="B60" s="5">
+        <v>103400</v>
+      </c>
+      <c r="C60" s="5">
+        <v>10</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F60" s="5">
+        <v>1</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H60" s="5">
+        <v>2034001</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L60" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="M60" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="N60" s="44">
+        <v>3</v>
+      </c>
+      <c r="O60" s="44">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="7"/>
+    </row>
+    <row r="61" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A61" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>10340011</v>
+      </c>
+      <c r="B61" s="5">
+        <v>103400</v>
+      </c>
+      <c r="C61" s="5">
+        <v>11</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="F61" s="5">
+        <v>1</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H61" s="5">
+        <v>2034001</v>
+      </c>
+      <c r="I61" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L61" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="M61" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="N61" s="44">
+        <v>3</v>
+      </c>
+      <c r="O61" s="44">
+        <v>3</v>
+      </c>
+      <c r="Q61" s="7"/>
+    </row>
+    <row r="62" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A62" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>10340012</v>
+      </c>
+      <c r="B62" s="5">
+        <v>103400</v>
+      </c>
+      <c r="C62" s="5">
+        <v>12</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F62" s="5">
+        <v>1</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H62" s="5">
+        <v>2034001</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L62" s="45" t="s">
+        <v>142</v>
+      </c>
+      <c r="M62" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="N62" s="44">
+        <v>3</v>
+      </c>
+      <c r="O62" s="44">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="7"/>
+    </row>
+    <row r="63" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A63" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>10340013</v>
+      </c>
+      <c r="B63" s="5">
+        <v>103400</v>
+      </c>
+      <c r="C63" s="5">
+        <v>13</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F63" s="5">
+        <v>1</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H63" s="5">
+        <v>2034001</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L63" s="45" t="s">
+        <v>145</v>
+      </c>
+      <c r="M63" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="N63" s="44">
+        <v>3</v>
+      </c>
+      <c r="O63" s="44">
+        <v>3</v>
+      </c>
+      <c r="Q63" s="7"/>
+    </row>
+    <row r="64" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A64" s="5"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="5"/>
+      <c r="G64" s="5"/>
+      <c r="H64" s="5"/>
+      <c r="I64" s="5"/>
+      <c r="L64" s="45"/>
+      <c r="M64" s="5"/>
+      <c r="N64" s="44"/>
+      <c r="O64" s="44"/>
+      <c r="Q64" s="7"/>
+    </row>
+    <row r="65" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A65" s="5"/>
+      <c r="B65" s="5"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="5"/>
+      <c r="E65" s="5"/>
+      <c r="F65" s="5"/>
+      <c r="G65" s="5"/>
+      <c r="H65" s="5"/>
+      <c r="I65" s="5"/>
+      <c r="L65" s="45"/>
+      <c r="M65" s="5"/>
+      <c r="N65" s="44"/>
+      <c r="O65" s="44"/>
+      <c r="Q65" s="7"/>
+    </row>
+    <row r="66" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A66" s="5"/>
+      <c r="B66" s="5"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="5"/>
+      <c r="F66" s="5"/>
+      <c r="G66" s="5"/>
+      <c r="H66" s="5"/>
+      <c r="I66" s="5"/>
+      <c r="L66" s="45"/>
+      <c r="M66" s="5"/>
+      <c r="N66" s="44"/>
+      <c r="O66" s="44"/>
+      <c r="Q66" s="7"/>
+    </row>
+    <row r="67" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A67" s="5"/>
+      <c r="B67" s="5"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="5"/>
+      <c r="F67" s="5"/>
+      <c r="G67" s="5"/>
+      <c r="H67" s="5"/>
+      <c r="I67" s="5"/>
+      <c r="L67" s="45"/>
+      <c r="M67" s="5"/>
+      <c r="N67" s="44"/>
+      <c r="O67" s="44"/>
+      <c r="Q67" s="7"/>
+    </row>
+    <row r="68" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A68" s="5"/>
+      <c r="B68" s="5"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="5"/>
+      <c r="F68" s="5"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5"/>
+      <c r="L68" s="45"/>
+      <c r="M68" s="5"/>
+      <c r="N68" s="44"/>
+      <c r="O68" s="44"/>
+      <c r="Q68" s="7"/>
+    </row>
+    <row r="69" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A69" s="5"/>
+      <c r="B69" s="5"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="5"/>
+      <c r="G69" s="5"/>
+      <c r="H69" s="5"/>
+      <c r="I69" s="5"/>
+      <c r="L69" s="45"/>
+      <c r="M69" s="5"/>
+      <c r="N69" s="44"/>
+      <c r="O69" s="44"/>
+      <c r="Q69" s="7"/>
+    </row>
+    <row r="70" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A70" s="5"/>
+      <c r="B70" s="5"/>
+      <c r="C70" s="5"/>
+      <c r="D70" s="5"/>
+      <c r="E70" s="5"/>
+      <c r="F70" s="5"/>
+      <c r="G70" s="5"/>
+      <c r="H70" s="5"/>
+      <c r="I70" s="5"/>
+      <c r="L70" s="45"/>
+      <c r="M70" s="5"/>
+      <c r="N70" s="44"/>
+      <c r="O70" s="44"/>
+      <c r="Q70" s="7"/>
+    </row>
+    <row r="71" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A71" s="5"/>
+      <c r="B71" s="5"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="5"/>
+      <c r="E71" s="5"/>
+      <c r="F71" s="5"/>
+      <c r="G71" s="5"/>
+      <c r="H71" s="5"/>
+      <c r="I71" s="5"/>
+      <c r="L71" s="45"/>
+      <c r="M71" s="5"/>
+      <c r="N71" s="44"/>
+      <c r="O71" s="44"/>
+      <c r="Q71" s="7"/>
+    </row>
+    <row r="72" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A72" s="5"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="5"/>
+      <c r="L72" s="45"/>
+      <c r="M72" s="5"/>
+      <c r="N72" s="44"/>
+      <c r="O72" s="44"/>
+      <c r="Q72" s="7"/>
+    </row>
+    <row r="73" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A73" s="5"/>
+      <c r="B73" s="5"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="5"/>
+      <c r="E73" s="5"/>
+      <c r="F73" s="5"/>
+      <c r="G73" s="5"/>
+      <c r="H73" s="5"/>
+      <c r="I73" s="5"/>
+      <c r="L73" s="45"/>
+      <c r="M73" s="5"/>
+      <c r="N73" s="44"/>
+      <c r="O73" s="44"/>
+      <c r="Q73" s="7"/>
+    </row>
+    <row r="74" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A74" s="5"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="5"/>
+      <c r="I74" s="5"/>
+      <c r="L74" s="45"/>
+      <c r="M74" s="5"/>
+      <c r="N74" s="44"/>
+      <c r="O74" s="44"/>
+      <c r="Q74" s="7"/>
+    </row>
+    <row r="75" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A75" s="5"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="5"/>
+      <c r="E75" s="5"/>
+      <c r="F75" s="5"/>
+      <c r="G75" s="5"/>
+      <c r="H75" s="5"/>
+      <c r="I75" s="5"/>
+      <c r="L75" s="45"/>
+      <c r="M75" s="5"/>
+      <c r="N75" s="44"/>
+      <c r="O75" s="44"/>
+      <c r="Q75" s="7"/>
+    </row>
+    <row r="76" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A76" s="5"/>
+      <c r="B76" s="5"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="5"/>
+      <c r="E76" s="5"/>
+      <c r="F76" s="5"/>
+      <c r="G76" s="5"/>
+      <c r="H76" s="5"/>
+      <c r="I76" s="5"/>
+      <c r="L76" s="45"/>
+      <c r="M76" s="5"/>
+      <c r="N76" s="44"/>
+      <c r="O76" s="44"/>
+      <c r="Q76" s="7"/>
+    </row>
+    <row r="77" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A77" s="5"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="5"/>
+      <c r="E77" s="5"/>
+      <c r="F77" s="5"/>
+      <c r="G77" s="5"/>
+      <c r="H77" s="5"/>
+      <c r="I77" s="5"/>
+      <c r="L77" s="45"/>
+      <c r="M77" s="5"/>
+      <c r="N77" s="44"/>
+      <c r="O77" s="44"/>
+      <c r="Q77" s="7"/>
+    </row>
+    <row r="78" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A78" s="5"/>
+      <c r="B78" s="5"/>
+      <c r="C78" s="5"/>
+      <c r="D78" s="5"/>
+      <c r="E78" s="5"/>
+      <c r="F78" s="5"/>
+      <c r="G78" s="5"/>
+      <c r="H78" s="5"/>
+      <c r="I78" s="5"/>
+      <c r="L78" s="45"/>
+      <c r="M78" s="5"/>
+      <c r="N78" s="44"/>
+      <c r="O78" s="44"/>
+      <c r="Q78" s="7"/>
+    </row>
+    <row r="79" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A79" s="5"/>
+      <c r="B79" s="5"/>
+      <c r="C79" s="5"/>
+      <c r="D79" s="5"/>
+      <c r="E79" s="5"/>
+      <c r="F79" s="5"/>
+      <c r="G79" s="5"/>
+      <c r="H79" s="5"/>
+      <c r="I79" s="5"/>
+      <c r="L79" s="45"/>
+      <c r="M79" s="5"/>
+      <c r="N79" s="44"/>
+      <c r="O79" s="44"/>
+      <c r="Q79" s="7"/>
+    </row>
+    <row r="80" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A80" s="5"/>
+      <c r="B80" s="5"/>
+      <c r="C80" s="5"/>
+      <c r="D80" s="5"/>
+      <c r="E80" s="5"/>
+      <c r="F80" s="5"/>
+      <c r="G80" s="5"/>
+      <c r="H80" s="5"/>
+      <c r="I80" s="5"/>
+      <c r="L80" s="45"/>
+      <c r="M80" s="5"/>
+      <c r="N80" s="44"/>
+      <c r="O80" s="44"/>
+      <c r="Q80" s="7"/>
+    </row>
+    <row r="81" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A81" s="5"/>
+      <c r="B81" s="5"/>
+      <c r="C81" s="5"/>
+      <c r="D81" s="5"/>
+      <c r="E81" s="5"/>
+      <c r="F81" s="5"/>
+      <c r="G81" s="5"/>
+      <c r="H81" s="5"/>
+      <c r="I81" s="5"/>
+      <c r="L81" s="45"/>
+      <c r="M81" s="5"/>
+      <c r="N81" s="44"/>
+      <c r="O81" s="44"/>
+      <c r="Q81" s="7"/>
+    </row>
+    <row r="82" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A82" s="5"/>
+      <c r="B82" s="5"/>
+      <c r="C82" s="5"/>
+      <c r="D82" s="5"/>
+      <c r="E82" s="5"/>
+      <c r="F82" s="5"/>
+      <c r="G82" s="5"/>
+      <c r="H82" s="5"/>
+      <c r="I82" s="5"/>
+      <c r="L82" s="45"/>
+      <c r="M82" s="5"/>
+      <c r="N82" s="44"/>
+      <c r="O82" s="44"/>
+      <c r="Q82" s="7"/>
+    </row>
+    <row r="83" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A83" s="5"/>
+      <c r="B83" s="5"/>
+      <c r="C83" s="5"/>
+      <c r="D83" s="5"/>
+      <c r="E83" s="5"/>
+      <c r="F83" s="5"/>
+      <c r="G83" s="5"/>
+      <c r="H83" s="5"/>
+      <c r="I83" s="5"/>
+      <c r="L83" s="45"/>
+      <c r="M83" s="5"/>
+      <c r="N83" s="44"/>
+      <c r="O83" s="44"/>
+      <c r="Q83" s="7"/>
+    </row>
+    <row r="84" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A84" s="5"/>
+      <c r="B84" s="5"/>
+      <c r="C84" s="5"/>
+      <c r="D84" s="5"/>
+      <c r="E84" s="5"/>
+      <c r="F84" s="5"/>
+      <c r="G84" s="5"/>
+      <c r="H84" s="5"/>
+      <c r="I84" s="5"/>
+      <c r="L84" s="45"/>
+      <c r="M84" s="5"/>
+      <c r="N84" s="44"/>
+      <c r="O84" s="44"/>
+      <c r="Q84" s="7"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:K2">

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -458,10 +458,10 @@
     <t>橘子福马模式</t>
   </si>
   <si>
-    <t>10340001|10340001|10340001|10340011|10340011</t>
-  </si>
-  <si>
-    <t>改出两个橘子or两个wind符号×3+改出1个橘子or1个wind符号×2</t>
+    <t>10340009|10340001|10340001|10340001|10340011|10340011</t>
+  </si>
+  <si>
+    <t>改出空格符号+改出两个橘子or两个wind符号×3+改出1个橘子or1个wind符号×2</t>
   </si>
   <si>
     <t>当第一次执行10340011修改出的符号出现的位置上有符号时，结束此模式，不执行第二次10340011</t>
@@ -470,10 +470,10 @@
     <t>鞭炮福马模式</t>
   </si>
   <si>
-    <t>10340002|10340002|10340002|10340012|10340012</t>
-  </si>
-  <si>
-    <t>改出两个鞭炮or两个wind符号×3+改出1个鞭炮or1个wind符号×2</t>
+    <t>10340009|10340002|10340002|10340002|10340012|10340012</t>
+  </si>
+  <si>
+    <t>改出空格符号+改出两个鞭炮or两个wind符号×3+改出1个鞭炮or1个wind符号×2</t>
   </si>
   <si>
     <t>同上</t>
@@ -482,91 +482,91 @@
     <t>红包福马模式</t>
   </si>
   <si>
-    <t>10340003|10340003|10340003|10340013|10340013</t>
-  </si>
-  <si>
-    <t>改出两个红包or两个wind符号×3+改出1个红包or1个wind符号×2</t>
+    <t>10340009|10340003|10340003|10340003|10340013|10340013</t>
+  </si>
+  <si>
+    <t>改出空格符号+改出两个红包or两个wind符号×3+改出1个红包or1个wind符号×2</t>
   </si>
   <si>
     <t>福袋福马模式</t>
   </si>
   <si>
-    <t>10340004|10340004|10340004|10340014|10340014</t>
-  </si>
-  <si>
-    <t>改出两个福袋or两个wind符号×3+改出1个福袋or1个wind符号×2</t>
+    <t>10340009|10340004|10340004|10340004|10340014|10340014</t>
+  </si>
+  <si>
+    <t>改出空格符号+改出两个福袋or两个wind符号×3+改出1个福袋or1个wind符号×2</t>
   </si>
   <si>
     <t>玉如意福马模式</t>
   </si>
   <si>
-    <t>10340005|10340005|10340005|10340015|10340015</t>
-  </si>
-  <si>
-    <t>改出两个玉如意or两个wind符号×3+改出1个玉如意or1个wind符号×2</t>
+    <t>10340009|10340005|10340005|10340005|10340015|10340015</t>
+  </si>
+  <si>
+    <t>改出空格符号+改出两个玉如意or两个wind符号×3+改出1个玉如意or1个wind符号×2</t>
   </si>
   <si>
     <t>元宝福马模式</t>
   </si>
   <si>
-    <t>10340006|10340006|10340006|10340016|10340016</t>
-  </si>
-  <si>
-    <t>改出两个元宝or两个wind符号×3+改出1个元宝or1个wind符号×2</t>
+    <t>10340009|10340006|10340006|10340006|10340016|10340016</t>
+  </si>
+  <si>
+    <t>改出空格符号+改出两个元宝or两个wind符号×3+改出1个元宝or1个wind符号×2</t>
   </si>
   <si>
     <t>橘子触发jackpot大奖</t>
   </si>
   <si>
-    <t>10340001|10340001|10340001|10340021|10340021|10340008</t>
-  </si>
-  <si>
-    <t>改出两个橘子or两个wind符号×3+改出1个橘子or1个wind符号×3</t>
+    <t>10340009|10340001|10340001|10340001|10340021|10340021|10340008</t>
+  </si>
+  <si>
+    <t>改出空格符号+改出两个橘子or两个wind符号×3+改出1个橘子or1个wind符号×3</t>
   </si>
   <si>
     <t>鞭炮触发jackpot大奖</t>
   </si>
   <si>
-    <t>10340002|10340002|10340002|10340022|10340022|10340008</t>
-  </si>
-  <si>
-    <t>改出两个鞭炮or两个wind符号×3+改出1个鞭炮or1个wind符号×3</t>
+    <t>10340009|10340002|10340002|10340002|10340022|10340022|10340008</t>
+  </si>
+  <si>
+    <t>改出空格符号+改出两个鞭炮or两个wind符号×3+改出1个鞭炮or1个wind符号×3</t>
   </si>
   <si>
     <t>红包触发jackpot大奖</t>
   </si>
   <si>
-    <t>10340003|10340003|10340003|10340023|10340023|10340008</t>
-  </si>
-  <si>
-    <t>改出两个红包or两个wind符号×3+改出1个红包or1个wind符号×3</t>
+    <t>10340009|10340003|10340003|10340003|10340023|10340023|10340008</t>
+  </si>
+  <si>
+    <t>改出空格符号+改出两个红包or两个wind符号×3+改出1个红包or1个wind符号×3</t>
   </si>
   <si>
     <t>福袋触发jackpot大奖</t>
   </si>
   <si>
-    <t>10340004|10340004|10340004|10340024|10340024|10340008</t>
-  </si>
-  <si>
-    <t>改出两个福袋or两个wind符号×3+改出1个福袋or1个wind符号×3</t>
+    <t>10340009|10340004|10340004|10340004|10340024|10340024|10340008</t>
+  </si>
+  <si>
+    <t>改出空格符号+改出两个福袋or两个wind符号×3+改出1个福袋or1个wind符号×3</t>
   </si>
   <si>
     <t>玉如意触发jackpot大奖</t>
   </si>
   <si>
-    <t>10340005|10340005|10340005|10340025|10340025|10340008</t>
-  </si>
-  <si>
-    <t>改出两个玉如意or两个wind符号×3+改出1个玉如意or1个wind符号×3</t>
+    <t>10340009|10340005|10340005|10340005|10340025|10340025|10340008</t>
+  </si>
+  <si>
+    <t>改出空格符号+改出两个玉如意or两个wind符号×3+改出1个玉如意or1个wind符号×3</t>
   </si>
   <si>
     <t>元宝触发jackpot大奖</t>
   </si>
   <si>
-    <t>10340006|10340006|10340006|10340026|10340026|10340008</t>
-  </si>
-  <si>
-    <t>改出两个元宝or两个wind符号×3+改出1个元宝or1个wind符号×3</t>
+    <t>10340009|10340006|10340006|10340006|10340026|10340026|10340008</t>
+  </si>
+  <si>
+    <t>改出空格符号+改出两个元宝or两个wind符号×3+改出1个元宝or1个wind符号×3</t>
   </si>
 </sst>
 </file>
@@ -750,12 +750,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="160">
   <si>
     <t>id</t>
   </si>
@@ -567,6 +567,45 @@
   </si>
   <si>
     <t>改出空格符号+改出两个元宝or两个wind符号×3+改出1个元宝or1个wind符号×3</t>
+  </si>
+  <si>
+    <t>金蛇招财</t>
+  </si>
+  <si>
+    <t>常规模式</t>
+  </si>
+  <si>
+    <t>10350014|10350001</t>
+  </si>
+  <si>
+    <t>改出奖金符号</t>
+  </si>
+  <si>
+    <t>金钱兔模式-触发</t>
+  </si>
+  <si>
+    <t>10350014|10350013</t>
+  </si>
+  <si>
+    <t>改出隐藏符号</t>
+  </si>
+  <si>
+    <t>10350014|10350012</t>
+  </si>
+  <si>
+    <t>改出奖池符号</t>
+  </si>
+  <si>
+    <t>金钱兔</t>
+  </si>
+  <si>
+    <t>10350114|10350101</t>
+  </si>
+  <si>
+    <t>10350114|10350113</t>
+  </si>
+  <si>
+    <t>10350114|10350112</t>
   </si>
 </sst>
 </file>
@@ -4639,99 +4678,261 @@
       <c r="Q63" s="7"/>
     </row>
     <row r="64" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A64" s="5"/>
-      <c r="B64" s="5"/>
-      <c r="C64" s="5"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
-      <c r="G64" s="5"/>
-      <c r="H64" s="5"/>
-      <c r="I64" s="5"/>
-      <c r="L64" s="45"/>
-      <c r="M64" s="5"/>
-      <c r="N64" s="44"/>
-      <c r="O64" s="44"/>
+      <c r="A64" s="5" t="str">
+        <f t="shared" ref="A64:A69" si="5">B64&amp;C64</f>
+        <v>1035001</v>
+      </c>
+      <c r="B64" s="5">
+        <v>103500</v>
+      </c>
+      <c r="C64" s="5">
+        <v>1</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="F64" s="5">
+        <v>1</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H64" s="5">
+        <v>2035001</v>
+      </c>
+      <c r="I64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L64" s="45" t="s">
+        <v>149</v>
+      </c>
+      <c r="M64" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="N64" s="44">
+        <v>4</v>
+      </c>
+      <c r="O64" s="44">
+        <v>3</v>
+      </c>
       <c r="Q64" s="7"/>
     </row>
     <row r="65" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A65" s="5"/>
-      <c r="B65" s="5"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="5"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="5"/>
-      <c r="H65" s="5"/>
-      <c r="I65" s="5"/>
-      <c r="L65" s="45"/>
-      <c r="M65" s="5"/>
-      <c r="N65" s="44"/>
-      <c r="O65" s="44"/>
+      <c r="A65" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>1035002</v>
+      </c>
+      <c r="B65" s="5">
+        <v>103500</v>
+      </c>
+      <c r="C65" s="5">
+        <v>2</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="F65" s="5">
+        <v>1</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H65" s="5">
+        <v>2035001</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L65" s="45" t="s">
+        <v>152</v>
+      </c>
+      <c r="M65" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="N65" s="44">
+        <v>4</v>
+      </c>
+      <c r="O65" s="44">
+        <v>3</v>
+      </c>
       <c r="Q65" s="7"/>
     </row>
     <row r="66" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A66" s="5"/>
-      <c r="B66" s="5"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="5"/>
-      <c r="E66" s="5"/>
-      <c r="F66" s="5"/>
-      <c r="G66" s="5"/>
-      <c r="H66" s="5"/>
-      <c r="I66" s="5"/>
-      <c r="L66" s="45"/>
-      <c r="M66" s="5"/>
-      <c r="N66" s="44"/>
-      <c r="O66" s="44"/>
+      <c r="A66" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>1035003</v>
+      </c>
+      <c r="B66" s="5">
+        <v>103500</v>
+      </c>
+      <c r="C66" s="5">
+        <v>3</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F66" s="5">
+        <v>1</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H66" s="5">
+        <v>2035011</v>
+      </c>
+      <c r="I66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L66" s="45" t="s">
+        <v>154</v>
+      </c>
+      <c r="M66" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="N66" s="44">
+        <v>4</v>
+      </c>
+      <c r="O66" s="44">
+        <v>3</v>
+      </c>
       <c r="Q66" s="7"/>
     </row>
     <row r="67" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A67" s="5"/>
-      <c r="B67" s="5"/>
-      <c r="C67" s="5"/>
-      <c r="D67" s="5"/>
-      <c r="E67" s="5"/>
-      <c r="F67" s="5"/>
-      <c r="G67" s="5"/>
-      <c r="H67" s="5"/>
-      <c r="I67" s="5"/>
-      <c r="L67" s="45"/>
-      <c r="M67" s="5"/>
-      <c r="N67" s="44"/>
-      <c r="O67" s="44"/>
+      <c r="A67" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>1035011</v>
+      </c>
+      <c r="B67" s="5">
+        <v>103501</v>
+      </c>
+      <c r="C67" s="5">
+        <v>1</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="F67" s="5">
+        <v>1</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H67" s="5">
+        <v>2035011</v>
+      </c>
+      <c r="I67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L67" s="45" t="s">
+        <v>157</v>
+      </c>
+      <c r="M67" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="N67" s="44">
+        <v>4</v>
+      </c>
+      <c r="O67" s="44">
+        <v>3</v>
+      </c>
       <c r="Q67" s="7"/>
     </row>
     <row r="68" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A68" s="5"/>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="5"/>
-      <c r="E68" s="5"/>
-      <c r="F68" s="5"/>
-      <c r="G68" s="5"/>
-      <c r="H68" s="5"/>
-      <c r="I68" s="5"/>
-      <c r="L68" s="45"/>
-      <c r="M68" s="5"/>
-      <c r="N68" s="44"/>
-      <c r="O68" s="44"/>
+      <c r="A68" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>1035012</v>
+      </c>
+      <c r="B68" s="5">
+        <v>103501</v>
+      </c>
+      <c r="C68" s="5">
+        <v>2</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="F68" s="5">
+        <v>1</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H68" s="5">
+        <v>2035011</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L68" s="45" t="s">
+        <v>158</v>
+      </c>
+      <c r="M68" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="N68" s="44">
+        <v>4</v>
+      </c>
+      <c r="O68" s="44">
+        <v>3</v>
+      </c>
       <c r="Q68" s="7"/>
     </row>
     <row r="69" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A69" s="5"/>
-      <c r="B69" s="5"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="5"/>
-      <c r="E69" s="5"/>
-      <c r="F69" s="5"/>
-      <c r="G69" s="5"/>
-      <c r="H69" s="5"/>
-      <c r="I69" s="5"/>
-      <c r="L69" s="45"/>
-      <c r="M69" s="5"/>
-      <c r="N69" s="44"/>
-      <c r="O69" s="44"/>
+      <c r="A69" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>1035013</v>
+      </c>
+      <c r="B69" s="5">
+        <v>103501</v>
+      </c>
+      <c r="C69" s="5">
+        <v>3</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F69" s="5">
+        <v>1</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H69" s="5">
+        <v>2035011</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L69" s="45" t="s">
+        <v>159</v>
+      </c>
+      <c r="M69" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="N69" s="44">
+        <v>4</v>
+      </c>
+      <c r="O69" s="44">
+        <v>3</v>
+      </c>
       <c r="Q69" s="7"/>
     </row>
     <row r="70" customFormat="1" ht="16.5" spans="1:17">

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -789,12 +789,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4744,7 +4744,7 @@
         <v>23</v>
       </c>
       <c r="H65" s="5">
-        <v>2035001</v>
+        <v>2035002</v>
       </c>
       <c r="I65" s="5" t="s">
         <v>24</v>
@@ -4873,7 +4873,7 @@
         <v>23</v>
       </c>
       <c r="H68" s="5">
-        <v>2035011</v>
+        <v>2035012</v>
       </c>
       <c r="I68" s="5" t="s">
         <v>24</v>

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialMode" sheetId="1" r:id="rId1"/>
@@ -789,12 +789,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4787,7 +4787,7 @@
         <v>23</v>
       </c>
       <c r="H66" s="5">
-        <v>2035011</v>
+        <v>2035001</v>
       </c>
       <c r="I66" s="5" t="s">
         <v>24</v>

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialMode" sheetId="1" r:id="rId1"/>

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -789,12 +789,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3782,7 +3782,7 @@
         <v>23</v>
       </c>
       <c r="H43" s="5">
-        <v>2018001</v>
+        <v>2018002</v>
       </c>
       <c r="I43" s="5" t="s">
         <v>24</v>

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -789,12 +789,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3487,7 +3487,7 @@
         <v>24</v>
       </c>
       <c r="L36" s="45">
-        <v>10220019</v>
+        <v>10220020</v>
       </c>
       <c r="N36" s="44">
         <v>3</v>
@@ -3527,7 +3527,7 @@
         <v>24</v>
       </c>
       <c r="L37" s="45">
-        <v>10220020</v>
+        <v>10220019</v>
       </c>
       <c r="N37" s="44">
         <v>3</v>

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -4167,7 +4167,7 @@
         <v>23</v>
       </c>
       <c r="H52" s="5">
-        <v>2034001</v>
+        <v>2034002</v>
       </c>
       <c r="I52" s="5" t="s">
         <v>24</v>
@@ -4213,7 +4213,7 @@
         <v>23</v>
       </c>
       <c r="H53" s="5">
-        <v>2034001</v>
+        <v>2034003</v>
       </c>
       <c r="I53" s="5" t="s">
         <v>24</v>
@@ -4259,7 +4259,7 @@
         <v>23</v>
       </c>
       <c r="H54" s="5">
-        <v>2034001</v>
+        <v>2034004</v>
       </c>
       <c r="I54" s="5" t="s">
         <v>24</v>
@@ -4305,7 +4305,7 @@
         <v>23</v>
       </c>
       <c r="H55" s="5">
-        <v>2034001</v>
+        <v>2034005</v>
       </c>
       <c r="I55" s="5" t="s">
         <v>24</v>
@@ -4351,7 +4351,7 @@
         <v>23</v>
       </c>
       <c r="H56" s="5">
-        <v>2034001</v>
+        <v>2034006</v>
       </c>
       <c r="I56" s="5" t="s">
         <v>24</v>
@@ -4397,7 +4397,7 @@
         <v>23</v>
       </c>
       <c r="H57" s="5">
-        <v>2034001</v>
+        <v>2034007</v>
       </c>
       <c r="I57" s="5" t="s">
         <v>24</v>
@@ -4443,7 +4443,7 @@
         <v>23</v>
       </c>
       <c r="H58" s="5">
-        <v>2034001</v>
+        <v>2034002</v>
       </c>
       <c r="I58" s="5" t="s">
         <v>24</v>
@@ -4486,7 +4486,7 @@
         <v>23</v>
       </c>
       <c r="H59" s="5">
-        <v>2034001</v>
+        <v>2034003</v>
       </c>
       <c r="I59" s="5" t="s">
         <v>24</v>
@@ -4529,7 +4529,7 @@
         <v>23</v>
       </c>
       <c r="H60" s="5">
-        <v>2034001</v>
+        <v>2034004</v>
       </c>
       <c r="I60" s="5" t="s">
         <v>24</v>
@@ -4572,7 +4572,7 @@
         <v>23</v>
       </c>
       <c r="H61" s="5">
-        <v>2034001</v>
+        <v>2034005</v>
       </c>
       <c r="I61" s="5" t="s">
         <v>24</v>
@@ -4615,7 +4615,7 @@
         <v>23</v>
       </c>
       <c r="H62" s="5">
-        <v>2034001</v>
+        <v>2034006</v>
       </c>
       <c r="I62" s="5" t="s">
         <v>24</v>
@@ -4658,7 +4658,7 @@
         <v>23</v>
       </c>
       <c r="H63" s="5">
-        <v>2034001</v>
+        <v>2034007</v>
       </c>
       <c r="I63" s="5" t="s">
         <v>24</v>

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="165">
   <si>
     <t>id</t>
   </si>
@@ -606,6 +606,21 @@
   </si>
   <si>
     <t>10350114|10350112</t>
+  </si>
+  <si>
+    <t>鼠鼠福福</t>
+  </si>
+  <si>
+    <t>10360001|10360003</t>
+  </si>
+  <si>
+    <t>概率改出wild符号+概率出现Jackpot符号</t>
+  </si>
+  <si>
+    <t>福鼠模式-触发</t>
+  </si>
+  <si>
+    <t>必出现3个Jackpot符号</t>
   </si>
 </sst>
 </file>
@@ -4936,51 +4951,132 @@
       <c r="Q69" s="7"/>
     </row>
     <row r="70" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A70" s="5"/>
-      <c r="B70" s="5"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="5"/>
-      <c r="E70" s="5"/>
-      <c r="F70" s="5"/>
-      <c r="G70" s="5"/>
-      <c r="H70" s="5"/>
-      <c r="I70" s="5"/>
-      <c r="L70" s="45"/>
-      <c r="M70" s="5"/>
-      <c r="N70" s="44"/>
-      <c r="O70" s="44"/>
+      <c r="A70" s="5" t="str">
+        <f>B70&amp;C70</f>
+        <v>1036001</v>
+      </c>
+      <c r="B70" s="5">
+        <v>103600</v>
+      </c>
+      <c r="C70" s="5">
+        <v>1</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="F70" s="5">
+        <v>1</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H70" s="5">
+        <v>2036001</v>
+      </c>
+      <c r="I70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L70" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="M70" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="N70" s="44">
+        <v>3</v>
+      </c>
+      <c r="O70" s="44">
+        <v>3</v>
+      </c>
       <c r="Q70" s="7"/>
     </row>
     <row r="71" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A71" s="5"/>
-      <c r="B71" s="5"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="5"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
-      <c r="G71" s="5"/>
-      <c r="H71" s="5"/>
-      <c r="I71" s="5"/>
-      <c r="L71" s="45"/>
-      <c r="M71" s="5"/>
-      <c r="N71" s="44"/>
-      <c r="O71" s="44"/>
+      <c r="A71" s="5" t="str">
+        <f>B71&amp;C71</f>
+        <v>1036002</v>
+      </c>
+      <c r="B71" s="5">
+        <v>103600</v>
+      </c>
+      <c r="C71" s="5">
+        <v>2</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="F71" s="5">
+        <v>1</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H71" s="5">
+        <v>2036002</v>
+      </c>
+      <c r="I71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L71" s="45">
+        <v>10360004</v>
+      </c>
+      <c r="M71" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="N71" s="44">
+        <v>3</v>
+      </c>
+      <c r="O71" s="44">
+        <v>3</v>
+      </c>
       <c r="Q71" s="7"/>
     </row>
     <row r="72" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A72" s="5"/>
-      <c r="B72" s="5"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
-      <c r="G72" s="5"/>
-      <c r="H72" s="5"/>
-      <c r="I72" s="5"/>
-      <c r="L72" s="45"/>
-      <c r="M72" s="5"/>
-      <c r="N72" s="44"/>
-      <c r="O72" s="44"/>
+      <c r="A72" s="5" t="str">
+        <f>B72&amp;C72</f>
+        <v>1036003</v>
+      </c>
+      <c r="B72" s="5">
+        <v>103600</v>
+      </c>
+      <c r="C72" s="5">
+        <v>3</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F72" s="5">
+        <v>1</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H72" s="5">
+        <v>2036001</v>
+      </c>
+      <c r="I72" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L72" s="45">
+        <v>10360002</v>
+      </c>
+      <c r="M72" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="N72" s="44">
+        <v>3</v>
+      </c>
+      <c r="O72" s="44">
+        <v>3</v>
+      </c>
       <c r="Q72" s="7"/>
     </row>
     <row r="73" customFormat="1" ht="16.5" spans="1:17">

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="128">
   <si>
     <t>id</t>
   </si>
@@ -455,118 +455,7 @@
     <t>概率改出wild</t>
   </si>
   <si>
-    <t>橘子福马模式</t>
-  </si>
-  <si>
-    <t>10340009|10340001|10340001|10340001|10340011|10340011</t>
-  </si>
-  <si>
-    <t>改出空格符号+改出两个橘子or两个wind符号×3+改出1个橘子or1个wind符号×2</t>
-  </si>
-  <si>
-    <t>当第一次执行10340011修改出的符号出现的位置上有符号时，结束此模式，不执行第二次10340011</t>
-  </si>
-  <si>
-    <t>鞭炮福马模式</t>
-  </si>
-  <si>
-    <t>10340009|10340002|10340002|10340002|10340012|10340012</t>
-  </si>
-  <si>
-    <t>改出空格符号+改出两个鞭炮or两个wind符号×3+改出1个鞭炮or1个wind符号×2</t>
-  </si>
-  <si>
-    <t>同上</t>
-  </si>
-  <si>
-    <t>红包福马模式</t>
-  </si>
-  <si>
-    <t>10340009|10340003|10340003|10340003|10340013|10340013</t>
-  </si>
-  <si>
-    <t>改出空格符号+改出两个红包or两个wind符号×3+改出1个红包or1个wind符号×2</t>
-  </si>
-  <si>
-    <t>福袋福马模式</t>
-  </si>
-  <si>
-    <t>10340009|10340004|10340004|10340004|10340014|10340014</t>
-  </si>
-  <si>
-    <t>改出空格符号+改出两个福袋or两个wind符号×3+改出1个福袋or1个wind符号×2</t>
-  </si>
-  <si>
-    <t>玉如意福马模式</t>
-  </si>
-  <si>
-    <t>10340009|10340005|10340005|10340005|10340015|10340015</t>
-  </si>
-  <si>
-    <t>改出空格符号+改出两个玉如意or两个wind符号×3+改出1个玉如意or1个wind符号×2</t>
-  </si>
-  <si>
-    <t>元宝福马模式</t>
-  </si>
-  <si>
-    <t>10340009|10340006|10340006|10340006|10340016|10340016</t>
-  </si>
-  <si>
-    <t>改出空格符号+改出两个元宝or两个wind符号×3+改出1个元宝or1个wind符号×2</t>
-  </si>
-  <si>
-    <t>橘子触发jackpot大奖</t>
-  </si>
-  <si>
-    <t>10340009|10340001|10340001|10340001|10340021|10340021|10340008</t>
-  </si>
-  <si>
-    <t>改出空格符号+改出两个橘子or两个wind符号×3+改出1个橘子or1个wind符号×3</t>
-  </si>
-  <si>
-    <t>鞭炮触发jackpot大奖</t>
-  </si>
-  <si>
-    <t>10340009|10340002|10340002|10340002|10340022|10340022|10340008</t>
-  </si>
-  <si>
-    <t>改出空格符号+改出两个鞭炮or两个wind符号×3+改出1个鞭炮or1个wind符号×3</t>
-  </si>
-  <si>
-    <t>红包触发jackpot大奖</t>
-  </si>
-  <si>
-    <t>10340009|10340003|10340003|10340003|10340023|10340023|10340008</t>
-  </si>
-  <si>
-    <t>改出空格符号+改出两个红包or两个wind符号×3+改出1个红包or1个wind符号×3</t>
-  </si>
-  <si>
-    <t>福袋触发jackpot大奖</t>
-  </si>
-  <si>
-    <t>10340009|10340004|10340004|10340004|10340024|10340024|10340008</t>
-  </si>
-  <si>
-    <t>改出空格符号+改出两个福袋or两个wind符号×3+改出1个福袋or1个wind符号×3</t>
-  </si>
-  <si>
-    <t>玉如意触发jackpot大奖</t>
-  </si>
-  <si>
-    <t>10340009|10340005|10340005|10340005|10340025|10340025|10340008</t>
-  </si>
-  <si>
-    <t>改出空格符号+改出两个玉如意or两个wind符号×3+改出1个玉如意or1个wind符号×3</t>
-  </si>
-  <si>
-    <t>元宝触发jackpot大奖</t>
-  </si>
-  <si>
-    <t>10340009|10340006|10340006|10340006|10340026|10340026|10340008</t>
-  </si>
-  <si>
-    <t>改出空格符号+改出两个元宝or两个wind符号×3+改出1个元宝or1个wind符号×3</t>
+    <t>福马模式</t>
   </si>
   <si>
     <t>金蛇招财</t>
@@ -1987,7 +1876,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S84"/>
+  <dimension ref="A1:S73"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
@@ -4160,7 +4049,7 @@
     </row>
     <row r="52" customFormat="1" ht="16.5" spans="1:17">
       <c r="A52" s="5" t="str">
-        <f t="shared" ref="A52:A57" si="3">B52&amp;C52</f>
+        <f>B52&amp;C52</f>
         <v>1034002</v>
       </c>
       <c r="B52" s="5">
@@ -4182,136 +4071,124 @@
         <v>23</v>
       </c>
       <c r="H52" s="5">
-        <v>2034002</v>
+        <v>2034001</v>
       </c>
       <c r="I52" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L52" s="45" t="s">
-        <v>110</v>
-      </c>
-      <c r="M52" s="5" t="s">
-        <v>111</v>
-      </c>
+      <c r="L52" s="45"/>
+      <c r="M52" s="5"/>
       <c r="N52" s="44">
         <v>3</v>
       </c>
       <c r="O52" s="44">
         <v>3</v>
       </c>
-      <c r="P52" s="49" t="s">
-        <v>112</v>
-      </c>
+      <c r="P52" s="49"/>
       <c r="Q52" s="7"/>
     </row>
     <row r="53" customFormat="1" ht="16.5" spans="1:17">
       <c r="A53" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>1034003</v>
+        <f t="shared" ref="A53:A61" si="3">B53&amp;C53</f>
+        <v>1035001</v>
       </c>
       <c r="B53" s="5">
-        <v>103400</v>
+        <v>103500</v>
       </c>
       <c r="C53" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E53" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F53" s="5">
+        <v>1</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H53" s="5">
+        <v>2035001</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L53" s="45" t="s">
+        <v>112</v>
+      </c>
+      <c r="M53" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="F53" s="5">
-        <v>1</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H53" s="5">
-        <v>2034003</v>
-      </c>
-      <c r="I53" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L53" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="M53" s="5" t="s">
-        <v>115</v>
-      </c>
       <c r="N53" s="44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O53" s="44">
         <v>3</v>
-      </c>
-      <c r="P53" s="49" t="s">
-        <v>116</v>
       </c>
       <c r="Q53" s="7"/>
     </row>
     <row r="54" customFormat="1" ht="16.5" spans="1:17">
       <c r="A54" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>1034004</v>
+        <v>1035002</v>
       </c>
       <c r="B54" s="5">
-        <v>103400</v>
+        <v>103500</v>
       </c>
       <c r="C54" s="5">
+        <v>2</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F54" s="5">
+        <v>1</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H54" s="5">
+        <v>2035002</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L54" s="45" t="s">
+        <v>115</v>
+      </c>
+      <c r="M54" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="N54" s="44">
         <v>4</v>
       </c>
-      <c r="D54" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="F54" s="5">
-        <v>1</v>
-      </c>
-      <c r="G54" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H54" s="5">
-        <v>2034004</v>
-      </c>
-      <c r="I54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L54" s="45" t="s">
-        <v>118</v>
-      </c>
-      <c r="M54" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="N54" s="44">
-        <v>3</v>
-      </c>
       <c r="O54" s="44">
         <v>3</v>
-      </c>
-      <c r="P54" s="49" t="s">
-        <v>116</v>
       </c>
       <c r="Q54" s="7"/>
     </row>
     <row r="55" customFormat="1" ht="16.5" spans="1:17">
       <c r="A55" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>1034005</v>
+        <v>1035003</v>
       </c>
       <c r="B55" s="5">
-        <v>103400</v>
+        <v>103500</v>
       </c>
       <c r="C55" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="F55" s="5">
         <v>1</v>
@@ -4320,44 +4197,41 @@
         <v>23</v>
       </c>
       <c r="H55" s="5">
-        <v>2034005</v>
+        <v>2035001</v>
       </c>
       <c r="I55" s="5" t="s">
         <v>24</v>
       </c>
       <c r="L55" s="45" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="M55" s="5" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="N55" s="44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O55" s="44">
         <v>3</v>
-      </c>
-      <c r="P55" s="49" t="s">
-        <v>116</v>
       </c>
       <c r="Q55" s="7"/>
     </row>
     <row r="56" customFormat="1" ht="16.5" spans="1:17">
       <c r="A56" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>1034006</v>
+        <v>1035011</v>
       </c>
       <c r="B56" s="5">
-        <v>103400</v>
+        <v>103501</v>
       </c>
       <c r="C56" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="F56" s="5">
         <v>1</v>
@@ -4366,44 +4240,41 @@
         <v>23</v>
       </c>
       <c r="H56" s="5">
-        <v>2034006</v>
+        <v>2035011</v>
       </c>
       <c r="I56" s="5" t="s">
         <v>24</v>
       </c>
       <c r="L56" s="45" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M56" s="5" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="N56" s="44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O56" s="44">
         <v>3</v>
-      </c>
-      <c r="P56" s="49" t="s">
-        <v>116</v>
       </c>
       <c r="Q56" s="7"/>
     </row>
     <row r="57" customFormat="1" ht="16.5" spans="1:17">
       <c r="A57" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>1034007</v>
+        <v>1035012</v>
       </c>
       <c r="B57" s="5">
-        <v>103400</v>
+        <v>103501</v>
       </c>
       <c r="C57" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="F57" s="5">
         <v>1</v>
@@ -4412,44 +4283,41 @@
         <v>23</v>
       </c>
       <c r="H57" s="5">
-        <v>2034007</v>
+        <v>2035012</v>
       </c>
       <c r="I57" s="5" t="s">
         <v>24</v>
       </c>
       <c r="L57" s="45" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="M57" s="5" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="N57" s="44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O57" s="44">
         <v>3</v>
-      </c>
-      <c r="P57" s="49" t="s">
-        <v>116</v>
       </c>
       <c r="Q57" s="7"/>
     </row>
     <row r="58" customFormat="1" ht="16.5" spans="1:17">
       <c r="A58" s="5" t="str">
-        <f t="shared" ref="A58:A63" si="4">B58&amp;C58</f>
-        <v>1034008</v>
+        <f t="shared" si="3"/>
+        <v>1035013</v>
       </c>
       <c r="B58" s="5">
-        <v>103400</v>
+        <v>103501</v>
       </c>
       <c r="C58" s="5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>129</v>
+        <v>81</v>
       </c>
       <c r="F58" s="5">
         <v>1</v>
@@ -4458,19 +4326,19 @@
         <v>23</v>
       </c>
       <c r="H58" s="5">
-        <v>2034002</v>
+        <v>2035011</v>
       </c>
       <c r="I58" s="5" t="s">
         <v>24</v>
       </c>
       <c r="L58" s="45" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="M58" s="5" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="N58" s="44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O58" s="44">
         <v>3</v>
@@ -4479,20 +4347,20 @@
     </row>
     <row r="59" customFormat="1" ht="16.5" spans="1:17">
       <c r="A59" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>1034009</v>
+        <f t="shared" si="3"/>
+        <v>1036001</v>
       </c>
       <c r="B59" s="5">
-        <v>103400</v>
+        <v>103600</v>
       </c>
       <c r="C59" s="5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="F59" s="5">
         <v>1</v>
@@ -4501,16 +4369,16 @@
         <v>23</v>
       </c>
       <c r="H59" s="5">
-        <v>2034003</v>
+        <v>2036001</v>
       </c>
       <c r="I59" s="5" t="s">
         <v>24</v>
       </c>
       <c r="L59" s="45" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="M59" s="5" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="N59" s="44">
         <v>3</v>
@@ -4522,20 +4390,20 @@
     </row>
     <row r="60" customFormat="1" ht="16.5" spans="1:17">
       <c r="A60" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>10340010</v>
+        <f t="shared" si="3"/>
+        <v>1036002</v>
       </c>
       <c r="B60" s="5">
-        <v>103400</v>
+        <v>103600</v>
       </c>
       <c r="C60" s="5">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="F60" s="5">
         <v>1</v>
@@ -4544,16 +4412,16 @@
         <v>23</v>
       </c>
       <c r="H60" s="5">
-        <v>2034004</v>
+        <v>2036002</v>
       </c>
       <c r="I60" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L60" s="45" t="s">
-        <v>136</v>
+      <c r="L60" s="45">
+        <v>10360004</v>
       </c>
       <c r="M60" s="5" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="N60" s="44">
         <v>3</v>
@@ -4565,20 +4433,20 @@
     </row>
     <row r="61" customFormat="1" ht="16.5" spans="1:17">
       <c r="A61" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>10340011</v>
+        <f t="shared" si="3"/>
+        <v>1036003</v>
       </c>
       <c r="B61" s="5">
-        <v>103400</v>
+        <v>103600</v>
       </c>
       <c r="C61" s="5">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="F61" s="5">
         <v>1</v>
@@ -4587,16 +4455,16 @@
         <v>23</v>
       </c>
       <c r="H61" s="5">
-        <v>2034005</v>
+        <v>2036001</v>
       </c>
       <c r="I61" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L61" s="45" t="s">
-        <v>139</v>
+      <c r="L61" s="45">
+        <v>10360002</v>
       </c>
       <c r="M61" s="5" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="N61" s="44">
         <v>3</v>
@@ -4607,476 +4475,179 @@
       <c r="Q61" s="7"/>
     </row>
     <row r="62" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A62" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>10340012</v>
-      </c>
-      <c r="B62" s="5">
-        <v>103400</v>
-      </c>
-      <c r="C62" s="5">
-        <v>12</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="F62" s="5">
-        <v>1</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H62" s="5">
-        <v>2034006</v>
-      </c>
-      <c r="I62" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L62" s="45" t="s">
-        <v>142</v>
-      </c>
-      <c r="M62" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="N62" s="44">
-        <v>3</v>
-      </c>
-      <c r="O62" s="44">
-        <v>3</v>
-      </c>
+      <c r="A62" s="5"/>
+      <c r="B62" s="5"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="5"/>
+      <c r="F62" s="5"/>
+      <c r="G62" s="5"/>
+      <c r="H62" s="5"/>
+      <c r="I62" s="5"/>
+      <c r="L62" s="45"/>
+      <c r="M62" s="5"/>
+      <c r="N62" s="44"/>
+      <c r="O62" s="44"/>
       <c r="Q62" s="7"/>
     </row>
     <row r="63" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A63" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>10340013</v>
-      </c>
-      <c r="B63" s="5">
-        <v>103400</v>
-      </c>
-      <c r="C63" s="5">
-        <v>13</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E63" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="F63" s="5">
-        <v>1</v>
-      </c>
-      <c r="G63" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H63" s="5">
-        <v>2034007</v>
-      </c>
-      <c r="I63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L63" s="45" t="s">
-        <v>145</v>
-      </c>
-      <c r="M63" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="N63" s="44">
-        <v>3</v>
-      </c>
-      <c r="O63" s="44">
-        <v>3</v>
-      </c>
+      <c r="A63" s="5"/>
+      <c r="B63" s="5"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="5"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="5"/>
+      <c r="I63" s="5"/>
+      <c r="L63" s="45"/>
+      <c r="M63" s="5"/>
+      <c r="N63" s="44"/>
+      <c r="O63" s="44"/>
       <c r="Q63" s="7"/>
     </row>
     <row r="64" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A64" s="5" t="str">
-        <f t="shared" ref="A64:A69" si="5">B64&amp;C64</f>
-        <v>1035001</v>
-      </c>
-      <c r="B64" s="5">
-        <v>103500</v>
-      </c>
-      <c r="C64" s="5">
-        <v>1</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="E64" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="F64" s="5">
-        <v>1</v>
-      </c>
-      <c r="G64" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H64" s="5">
-        <v>2035001</v>
-      </c>
-      <c r="I64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L64" s="45" t="s">
-        <v>149</v>
-      </c>
-      <c r="M64" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="N64" s="44">
-        <v>4</v>
-      </c>
-      <c r="O64" s="44">
-        <v>3</v>
-      </c>
+      <c r="A64" s="5"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="5"/>
+      <c r="G64" s="5"/>
+      <c r="H64" s="5"/>
+      <c r="I64" s="5"/>
+      <c r="L64" s="45"/>
+      <c r="M64" s="5"/>
+      <c r="N64" s="44"/>
+      <c r="O64" s="44"/>
       <c r="Q64" s="7"/>
     </row>
     <row r="65" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A65" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>1035002</v>
-      </c>
-      <c r="B65" s="5">
-        <v>103500</v>
-      </c>
-      <c r="C65" s="5">
-        <v>2</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="F65" s="5">
-        <v>1</v>
-      </c>
-      <c r="G65" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H65" s="5">
-        <v>2035002</v>
-      </c>
-      <c r="I65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L65" s="45" t="s">
-        <v>152</v>
-      </c>
-      <c r="M65" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="N65" s="44">
-        <v>4</v>
-      </c>
-      <c r="O65" s="44">
-        <v>3</v>
-      </c>
+      <c r="A65" s="5"/>
+      <c r="B65" s="5"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="5"/>
+      <c r="E65" s="5"/>
+      <c r="F65" s="5"/>
+      <c r="G65" s="5"/>
+      <c r="H65" s="5"/>
+      <c r="I65" s="5"/>
+      <c r="L65" s="45"/>
+      <c r="M65" s="5"/>
+      <c r="N65" s="44"/>
+      <c r="O65" s="44"/>
       <c r="Q65" s="7"/>
     </row>
     <row r="66" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A66" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>1035003</v>
-      </c>
-      <c r="B66" s="5">
-        <v>103500</v>
-      </c>
-      <c r="C66" s="5">
-        <v>3</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F66" s="5">
-        <v>1</v>
-      </c>
-      <c r="G66" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H66" s="5">
-        <v>2035001</v>
-      </c>
-      <c r="I66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L66" s="45" t="s">
-        <v>154</v>
-      </c>
-      <c r="M66" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="N66" s="44">
-        <v>4</v>
-      </c>
-      <c r="O66" s="44">
-        <v>3</v>
-      </c>
+      <c r="A66" s="5"/>
+      <c r="B66" s="5"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="5"/>
+      <c r="F66" s="5"/>
+      <c r="G66" s="5"/>
+      <c r="H66" s="5"/>
+      <c r="I66" s="5"/>
+      <c r="L66" s="45"/>
+      <c r="M66" s="5"/>
+      <c r="N66" s="44"/>
+      <c r="O66" s="44"/>
       <c r="Q66" s="7"/>
     </row>
     <row r="67" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A67" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>1035011</v>
-      </c>
-      <c r="B67" s="5">
-        <v>103501</v>
-      </c>
-      <c r="C67" s="5">
-        <v>1</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="E67" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="F67" s="5">
-        <v>1</v>
-      </c>
-      <c r="G67" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H67" s="5">
-        <v>2035011</v>
-      </c>
-      <c r="I67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L67" s="45" t="s">
-        <v>157</v>
-      </c>
-      <c r="M67" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="N67" s="44">
-        <v>4</v>
-      </c>
-      <c r="O67" s="44">
-        <v>3</v>
-      </c>
+      <c r="A67" s="5"/>
+      <c r="B67" s="5"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="5"/>
+      <c r="F67" s="5"/>
+      <c r="G67" s="5"/>
+      <c r="H67" s="5"/>
+      <c r="I67" s="5"/>
+      <c r="L67" s="45"/>
+      <c r="M67" s="5"/>
+      <c r="N67" s="44"/>
+      <c r="O67" s="44"/>
       <c r="Q67" s="7"/>
     </row>
     <row r="68" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A68" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>1035012</v>
-      </c>
-      <c r="B68" s="5">
-        <v>103501</v>
-      </c>
-      <c r="C68" s="5">
-        <v>2</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="F68" s="5">
-        <v>1</v>
-      </c>
-      <c r="G68" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H68" s="5">
-        <v>2035012</v>
-      </c>
-      <c r="I68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L68" s="45" t="s">
-        <v>158</v>
-      </c>
-      <c r="M68" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="N68" s="44">
-        <v>4</v>
-      </c>
-      <c r="O68" s="44">
-        <v>3</v>
-      </c>
+      <c r="A68" s="5"/>
+      <c r="B68" s="5"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="5"/>
+      <c r="F68" s="5"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5"/>
+      <c r="L68" s="45"/>
+      <c r="M68" s="5"/>
+      <c r="N68" s="44"/>
+      <c r="O68" s="44"/>
       <c r="Q68" s="7"/>
     </row>
     <row r="69" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A69" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>1035013</v>
-      </c>
-      <c r="B69" s="5">
-        <v>103501</v>
-      </c>
-      <c r="C69" s="5">
-        <v>3</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="E69" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F69" s="5">
-        <v>1</v>
-      </c>
-      <c r="G69" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H69" s="5">
-        <v>2035011</v>
-      </c>
-      <c r="I69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L69" s="45" t="s">
-        <v>159</v>
-      </c>
-      <c r="M69" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="N69" s="44">
-        <v>4</v>
-      </c>
-      <c r="O69" s="44">
-        <v>3</v>
-      </c>
+      <c r="A69" s="5"/>
+      <c r="B69" s="5"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="5"/>
+      <c r="G69" s="5"/>
+      <c r="H69" s="5"/>
+      <c r="I69" s="5"/>
+      <c r="L69" s="45"/>
+      <c r="M69" s="5"/>
+      <c r="N69" s="44"/>
+      <c r="O69" s="44"/>
       <c r="Q69" s="7"/>
     </row>
     <row r="70" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A70" s="5" t="str">
-        <f>B70&amp;C70</f>
-        <v>1036001</v>
-      </c>
-      <c r="B70" s="5">
-        <v>103600</v>
-      </c>
-      <c r="C70" s="5">
-        <v>1</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="F70" s="5">
-        <v>1</v>
-      </c>
-      <c r="G70" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H70" s="5">
-        <v>2036001</v>
-      </c>
-      <c r="I70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L70" s="45" t="s">
-        <v>161</v>
-      </c>
-      <c r="M70" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="N70" s="44">
-        <v>3</v>
-      </c>
-      <c r="O70" s="44">
-        <v>3</v>
-      </c>
+      <c r="A70" s="5"/>
+      <c r="B70" s="5"/>
+      <c r="C70" s="5"/>
+      <c r="D70" s="5"/>
+      <c r="E70" s="5"/>
+      <c r="F70" s="5"/>
+      <c r="G70" s="5"/>
+      <c r="H70" s="5"/>
+      <c r="I70" s="5"/>
+      <c r="L70" s="45"/>
+      <c r="M70" s="5"/>
+      <c r="N70" s="44"/>
+      <c r="O70" s="44"/>
       <c r="Q70" s="7"/>
     </row>
     <row r="71" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A71" s="5" t="str">
-        <f>B71&amp;C71</f>
-        <v>1036002</v>
-      </c>
-      <c r="B71" s="5">
-        <v>103600</v>
-      </c>
-      <c r="C71" s="5">
-        <v>2</v>
-      </c>
-      <c r="D71" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="F71" s="5">
-        <v>1</v>
-      </c>
-      <c r="G71" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H71" s="5">
-        <v>2036002</v>
-      </c>
-      <c r="I71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L71" s="45">
-        <v>10360004</v>
-      </c>
-      <c r="M71" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="N71" s="44">
-        <v>3</v>
-      </c>
-      <c r="O71" s="44">
-        <v>3</v>
-      </c>
+      <c r="A71" s="5"/>
+      <c r="B71" s="5"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="5"/>
+      <c r="E71" s="5"/>
+      <c r="F71" s="5"/>
+      <c r="G71" s="5"/>
+      <c r="H71" s="5"/>
+      <c r="I71" s="5"/>
+      <c r="L71" s="45"/>
+      <c r="M71" s="5"/>
+      <c r="N71" s="44"/>
+      <c r="O71" s="44"/>
       <c r="Q71" s="7"/>
     </row>
     <row r="72" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A72" s="5" t="str">
-        <f>B72&amp;C72</f>
-        <v>1036003</v>
-      </c>
-      <c r="B72" s="5">
-        <v>103600</v>
-      </c>
-      <c r="C72" s="5">
-        <v>3</v>
-      </c>
-      <c r="D72" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="E72" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F72" s="5">
-        <v>1</v>
-      </c>
-      <c r="G72" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H72" s="5">
-        <v>2036001</v>
-      </c>
-      <c r="I72" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L72" s="45">
-        <v>10360002</v>
-      </c>
-      <c r="M72" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="N72" s="44">
-        <v>3</v>
-      </c>
-      <c r="O72" s="44">
-        <v>3</v>
-      </c>
+      <c r="A72" s="5"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="5"/>
+      <c r="L72" s="45"/>
+      <c r="M72" s="5"/>
+      <c r="N72" s="44"/>
+      <c r="O72" s="44"/>
       <c r="Q72" s="7"/>
     </row>
     <row r="73" customFormat="1" ht="16.5" spans="1:17">
@@ -5094,182 +4665,6 @@
       <c r="N73" s="44"/>
       <c r="O73" s="44"/>
       <c r="Q73" s="7"/>
-    </row>
-    <row r="74" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A74" s="5"/>
-      <c r="B74" s="5"/>
-      <c r="C74" s="5"/>
-      <c r="D74" s="5"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
-      <c r="G74" s="5"/>
-      <c r="H74" s="5"/>
-      <c r="I74" s="5"/>
-      <c r="L74" s="45"/>
-      <c r="M74" s="5"/>
-      <c r="N74" s="44"/>
-      <c r="O74" s="44"/>
-      <c r="Q74" s="7"/>
-    </row>
-    <row r="75" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A75" s="5"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
-      <c r="D75" s="5"/>
-      <c r="E75" s="5"/>
-      <c r="F75" s="5"/>
-      <c r="G75" s="5"/>
-      <c r="H75" s="5"/>
-      <c r="I75" s="5"/>
-      <c r="L75" s="45"/>
-      <c r="M75" s="5"/>
-      <c r="N75" s="44"/>
-      <c r="O75" s="44"/>
-      <c r="Q75" s="7"/>
-    </row>
-    <row r="76" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A76" s="5"/>
-      <c r="B76" s="5"/>
-      <c r="C76" s="5"/>
-      <c r="D76" s="5"/>
-      <c r="E76" s="5"/>
-      <c r="F76" s="5"/>
-      <c r="G76" s="5"/>
-      <c r="H76" s="5"/>
-      <c r="I76" s="5"/>
-      <c r="L76" s="45"/>
-      <c r="M76" s="5"/>
-      <c r="N76" s="44"/>
-      <c r="O76" s="44"/>
-      <c r="Q76" s="7"/>
-    </row>
-    <row r="77" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A77" s="5"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="5"/>
-      <c r="D77" s="5"/>
-      <c r="E77" s="5"/>
-      <c r="F77" s="5"/>
-      <c r="G77" s="5"/>
-      <c r="H77" s="5"/>
-      <c r="I77" s="5"/>
-      <c r="L77" s="45"/>
-      <c r="M77" s="5"/>
-      <c r="N77" s="44"/>
-      <c r="O77" s="44"/>
-      <c r="Q77" s="7"/>
-    </row>
-    <row r="78" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A78" s="5"/>
-      <c r="B78" s="5"/>
-      <c r="C78" s="5"/>
-      <c r="D78" s="5"/>
-      <c r="E78" s="5"/>
-      <c r="F78" s="5"/>
-      <c r="G78" s="5"/>
-      <c r="H78" s="5"/>
-      <c r="I78" s="5"/>
-      <c r="L78" s="45"/>
-      <c r="M78" s="5"/>
-      <c r="N78" s="44"/>
-      <c r="O78" s="44"/>
-      <c r="Q78" s="7"/>
-    </row>
-    <row r="79" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A79" s="5"/>
-      <c r="B79" s="5"/>
-      <c r="C79" s="5"/>
-      <c r="D79" s="5"/>
-      <c r="E79" s="5"/>
-      <c r="F79" s="5"/>
-      <c r="G79" s="5"/>
-      <c r="H79" s="5"/>
-      <c r="I79" s="5"/>
-      <c r="L79" s="45"/>
-      <c r="M79" s="5"/>
-      <c r="N79" s="44"/>
-      <c r="O79" s="44"/>
-      <c r="Q79" s="7"/>
-    </row>
-    <row r="80" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A80" s="5"/>
-      <c r="B80" s="5"/>
-      <c r="C80" s="5"/>
-      <c r="D80" s="5"/>
-      <c r="E80" s="5"/>
-      <c r="F80" s="5"/>
-      <c r="G80" s="5"/>
-      <c r="H80" s="5"/>
-      <c r="I80" s="5"/>
-      <c r="L80" s="45"/>
-      <c r="M80" s="5"/>
-      <c r="N80" s="44"/>
-      <c r="O80" s="44"/>
-      <c r="Q80" s="7"/>
-    </row>
-    <row r="81" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A81" s="5"/>
-      <c r="B81" s="5"/>
-      <c r="C81" s="5"/>
-      <c r="D81" s="5"/>
-      <c r="E81" s="5"/>
-      <c r="F81" s="5"/>
-      <c r="G81" s="5"/>
-      <c r="H81" s="5"/>
-      <c r="I81" s="5"/>
-      <c r="L81" s="45"/>
-      <c r="M81" s="5"/>
-      <c r="N81" s="44"/>
-      <c r="O81" s="44"/>
-      <c r="Q81" s="7"/>
-    </row>
-    <row r="82" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A82" s="5"/>
-      <c r="B82" s="5"/>
-      <c r="C82" s="5"/>
-      <c r="D82" s="5"/>
-      <c r="E82" s="5"/>
-      <c r="F82" s="5"/>
-      <c r="G82" s="5"/>
-      <c r="H82" s="5"/>
-      <c r="I82" s="5"/>
-      <c r="L82" s="45"/>
-      <c r="M82" s="5"/>
-      <c r="N82" s="44"/>
-      <c r="O82" s="44"/>
-      <c r="Q82" s="7"/>
-    </row>
-    <row r="83" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A83" s="5"/>
-      <c r="B83" s="5"/>
-      <c r="C83" s="5"/>
-      <c r="D83" s="5"/>
-      <c r="E83" s="5"/>
-      <c r="F83" s="5"/>
-      <c r="G83" s="5"/>
-      <c r="H83" s="5"/>
-      <c r="I83" s="5"/>
-      <c r="L83" s="45"/>
-      <c r="M83" s="5"/>
-      <c r="N83" s="44"/>
-      <c r="O83" s="44"/>
-      <c r="Q83" s="7"/>
-    </row>
-    <row r="84" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A84" s="5"/>
-      <c r="B84" s="5"/>
-      <c r="C84" s="5"/>
-      <c r="D84" s="5"/>
-      <c r="E84" s="5"/>
-      <c r="F84" s="5"/>
-      <c r="G84" s="5"/>
-      <c r="H84" s="5"/>
-      <c r="I84" s="5"/>
-      <c r="L84" s="45"/>
-      <c r="M84" s="5"/>
-      <c r="N84" s="44"/>
-      <c r="O84" s="44"/>
-      <c r="Q84" s="7"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:K2">

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="135">
   <si>
     <t>id</t>
   </si>
@@ -510,6 +510,27 @@
   </si>
   <si>
     <t>必出现3个Jackpot符号</t>
+  </si>
+  <si>
+    <t>王牌dj</t>
+  </si>
+  <si>
+    <t>10280001|10280003|10280006|10280007|10280008</t>
+  </si>
+  <si>
+    <t>概率出现wild+概率改出2个SCATTER+概率改出占据2、3、4个格子符号</t>
+  </si>
+  <si>
+    <t>免费游戏-触发局</t>
+  </si>
+  <si>
+    <t>10280004|10280009</t>
+  </si>
+  <si>
+    <t>虎虎生财</t>
+  </si>
+  <si>
+    <t>福虎模式</t>
   </si>
 </sst>
 </file>
@@ -3148,7 +3169,7 @@
     </row>
     <row r="31" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A31" s="23" t="str">
-        <f t="shared" ref="A31:A51" si="2">B31&amp;C31</f>
+        <f t="shared" ref="A31:A52" si="2">B31&amp;C31</f>
         <v>1017002</v>
       </c>
       <c r="B31" s="5">
@@ -4049,7 +4070,7 @@
     </row>
     <row r="52" customFormat="1" ht="16.5" spans="1:17">
       <c r="A52" s="5" t="str">
-        <f>B52&amp;C52</f>
+        <f t="shared" si="2"/>
         <v>1034002</v>
       </c>
       <c r="B52" s="5">
@@ -4089,7 +4110,7 @@
     </row>
     <row r="53" customFormat="1" ht="16.5" spans="1:17">
       <c r="A53" s="5" t="str">
-        <f t="shared" ref="A53:A61" si="3">B53&amp;C53</f>
+        <f t="shared" ref="A53:A66" si="3">B53&amp;C53</f>
         <v>1035001</v>
       </c>
       <c r="B53" s="5">
@@ -4475,83 +4496,215 @@
       <c r="Q61" s="7"/>
     </row>
     <row r="62" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A62" s="5"/>
-      <c r="B62" s="5"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="5"/>
-      <c r="H62" s="5"/>
-      <c r="I62" s="5"/>
-      <c r="L62" s="45"/>
-      <c r="M62" s="5"/>
-      <c r="N62" s="44"/>
-      <c r="O62" s="44"/>
+      <c r="A62" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1028001</v>
+      </c>
+      <c r="B62" s="5">
+        <v>102800</v>
+      </c>
+      <c r="C62" s="5">
+        <v>1</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F62" s="5">
+        <v>1</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H62" s="5">
+        <v>2028001</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L62" s="45" t="s">
+        <v>129</v>
+      </c>
+      <c r="M62" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="N62" s="44">
+        <v>5</v>
+      </c>
+      <c r="O62" s="44">
+        <v>6</v>
+      </c>
       <c r="Q62" s="7"/>
     </row>
     <row r="63" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A63" s="5"/>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
-      <c r="H63" s="5"/>
-      <c r="I63" s="5"/>
-      <c r="L63" s="45"/>
-      <c r="M63" s="5"/>
-      <c r="N63" s="44"/>
-      <c r="O63" s="44"/>
+      <c r="A63" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1028002</v>
+      </c>
+      <c r="B63" s="5">
+        <v>102800</v>
+      </c>
+      <c r="C63" s="5">
+        <v>2</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F63" s="5">
+        <v>1</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H63" s="5">
+        <v>2028001</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L63" s="45">
+        <v>10280002</v>
+      </c>
+      <c r="M63" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="N63" s="44">
+        <v>5</v>
+      </c>
+      <c r="O63" s="44">
+        <v>6</v>
+      </c>
       <c r="Q63" s="7"/>
     </row>
     <row r="64" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A64" s="5"/>
-      <c r="B64" s="5"/>
-      <c r="C64" s="5"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
-      <c r="G64" s="5"/>
-      <c r="H64" s="5"/>
-      <c r="I64" s="5"/>
-      <c r="L64" s="45"/>
-      <c r="M64" s="5"/>
-      <c r="N64" s="44"/>
-      <c r="O64" s="44"/>
+      <c r="A64" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1028003</v>
+      </c>
+      <c r="B64" s="5">
+        <v>102800</v>
+      </c>
+      <c r="C64" s="5">
+        <v>3</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F64" s="5">
+        <v>1</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H64" s="5">
+        <v>2028001</v>
+      </c>
+      <c r="I64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L64" s="45" t="s">
+        <v>132</v>
+      </c>
+      <c r="M64" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="N64" s="44">
+        <v>5</v>
+      </c>
+      <c r="O64" s="44">
+        <v>6</v>
+      </c>
       <c r="Q64" s="7"/>
     </row>
     <row r="65" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A65" s="5"/>
-      <c r="B65" s="5"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="5"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="5"/>
-      <c r="H65" s="5"/>
-      <c r="I65" s="5"/>
-      <c r="L65" s="45"/>
-      <c r="M65" s="5"/>
-      <c r="N65" s="44"/>
-      <c r="O65" s="44"/>
+      <c r="A65" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1034011</v>
+      </c>
+      <c r="B65" s="5">
+        <v>103401</v>
+      </c>
+      <c r="C65" s="5">
+        <v>1</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F65" s="5">
+        <v>1</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H65" s="5">
+        <v>2034011</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L65" s="45">
+        <v>10340007</v>
+      </c>
+      <c r="M65" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="N65" s="44">
+        <v>3</v>
+      </c>
+      <c r="O65" s="44">
+        <v>3</v>
+      </c>
       <c r="Q65" s="7"/>
     </row>
     <row r="66" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A66" s="5"/>
-      <c r="B66" s="5"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="5"/>
-      <c r="E66" s="5"/>
-      <c r="F66" s="5"/>
-      <c r="G66" s="5"/>
-      <c r="H66" s="5"/>
-      <c r="I66" s="5"/>
+      <c r="A66" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1034012</v>
+      </c>
+      <c r="B66" s="5">
+        <v>103401</v>
+      </c>
+      <c r="C66" s="5">
+        <v>2</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F66" s="5">
+        <v>1</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H66" s="5">
+        <v>2034011</v>
+      </c>
+      <c r="I66" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="L66" s="45"/>
       <c r="M66" s="5"/>
-      <c r="N66" s="44"/>
-      <c r="O66" s="44"/>
+      <c r="N66" s="44">
+        <v>3</v>
+      </c>
+      <c r="O66" s="44">
+        <v>3</v>
+      </c>
+      <c r="P66" s="49"/>
       <c r="Q66" s="7"/>
     </row>
     <row r="67" customFormat="1" ht="16.5" spans="1:17">

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="146">
   <si>
     <t>id</t>
   </si>
@@ -531,6 +531,39 @@
   </si>
   <si>
     <t>福虎模式</t>
+  </si>
+  <si>
+    <t>l宙斯vs哈迪斯</t>
+  </si>
+  <si>
+    <t>10200001|10200002|10200003|10200004|10200005|10200006|10200007</t>
+  </si>
+  <si>
+    <t>概率出现wild+概率在1234轴上改出v1234+概率第1轴改出1个scatter+概率第3轴改出1个scatter</t>
+  </si>
+  <si>
+    <t>10200008|10200009|10200010</t>
+  </si>
+  <si>
+    <t>第1轴改出1个scatter+第3轴改出1个scatter+第1轴改出5个scatter</t>
+  </si>
+  <si>
+    <t>10200006|10200007|10200011</t>
+  </si>
+  <si>
+    <t>第1轴改出1个scatter+第3轴改出1个scatter+第5轴改出奖池符号</t>
+  </si>
+  <si>
+    <t>宙斯模式</t>
+  </si>
+  <si>
+    <t>改出39符号，用于触发免费游戏宙斯</t>
+  </si>
+  <si>
+    <t>哈迪斯模式</t>
+  </si>
+  <si>
+    <t>改出40符号，用于触发免费游戏哈迪斯</t>
   </si>
 </sst>
 </file>
@@ -725,7 +758,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="44">
+  <fills count="45">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -747,6 +780,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -777,12 +822,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1130,7 +1169,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1154,16 +1193,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1172,109 +1211,111 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1283,24 +1324,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -1311,22 +1352,22 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1334,11 +1375,11 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1364,6 +1405,22 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1910,14 +1967,14 @@
     <col min="11" max="11" width="16.75" customWidth="1"/>
     <col min="12" max="12" width="53.25" customWidth="1"/>
     <col min="13" max="13" width="21.6083333333333" customWidth="1"/>
-    <col min="14" max="15" width="9" style="6"/>
+    <col min="14" max="15" width="9" style="8"/>
     <col min="16" max="16" width="15" customWidth="1"/>
-    <col min="17" max="17" width="23.75" style="7" customWidth="1"/>
+    <col min="17" max="17" width="23.75" style="9" customWidth="1"/>
     <col min="18" max="18" width="60.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:17">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
@@ -1928,34 +1985,34 @@
       </c>
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="11" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="5"/>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="11" t="s">
         <v>4</v>
       </c>
       <c r="I1" s="5"/>
-      <c r="J1" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="10"/>
-      <c r="L1" s="11" t="s">
+      <c r="J1" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="12"/>
+      <c r="L1" s="13" t="s">
         <v>6</v>
       </c>
       <c r="M1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="N1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="O1" s="14" t="s">
         <v>9</v>
       </c>
       <c r="Q1"/>
     </row>
     <row r="2" ht="16.5" spans="1:17">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="10" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -1966,62 +2023,62 @@
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="11" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="5"/>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="11" t="s">
         <v>10</v>
       </c>
       <c r="I2" s="5"/>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="14"/>
-      <c r="L2" s="15" t="s">
+      <c r="K2" s="16"/>
+      <c r="L2" s="17" t="s">
         <v>12</v>
       </c>
       <c r="M2" s="5"/>
-      <c r="N2" s="16" t="s">
+      <c r="N2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="16" t="s">
+      <c r="O2" s="18" t="s">
         <v>10</v>
       </c>
       <c r="Q2"/>
     </row>
     <row r="3" ht="16.5" spans="1:17">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="18" t="s">
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="17"/>
-      <c r="H3" s="19" t="s">
+      <c r="G3" s="19"/>
+      <c r="H3" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="20" t="s">
+      <c r="I3" s="19"/>
+      <c r="J3" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="20"/>
-      <c r="L3" s="21" t="s">
+      <c r="K3" s="22"/>
+      <c r="L3" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="M3" s="17"/>
-      <c r="N3" s="16" t="s">
+      <c r="M3" s="19"/>
+      <c r="N3" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="16" t="s">
+      <c r="O3" s="18" t="s">
         <v>20</v>
       </c>
       <c r="Q3"/>
@@ -2031,1101 +2088,1101 @@
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="9"/>
+      <c r="F4" s="11"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="9"/>
+      <c r="H4" s="11"/>
       <c r="I4" s="5"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="11"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="13"/>
       <c r="M4" s="5"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="18"/>
       <c r="Q4"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A5" s="23" t="str">
+      <c r="A5" s="25" t="str">
         <f t="shared" ref="A5:A15" si="0">B5&amp;C5</f>
         <v>1001001</v>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="26">
         <v>100100</v>
       </c>
-      <c r="C5" s="24">
-        <v>1</v>
-      </c>
-      <c r="D5" s="24" t="s">
+      <c r="C5" s="26">
+        <v>1</v>
+      </c>
+      <c r="D5" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E5" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="24">
-        <v>1</v>
-      </c>
-      <c r="G5" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="23">
+      <c r="F5" s="26">
+        <v>1</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="25">
         <v>2001001</v>
       </c>
-      <c r="I5" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="23"/>
-      <c r="K5" s="23"/>
-      <c r="L5" s="26" t="s">
+      <c r="I5" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="M5" s="23" t="s">
+      <c r="M5" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="N5" s="16">
+      <c r="N5" s="18">
         <v>4</v>
       </c>
-      <c r="O5" s="16">
+      <c r="O5" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A6" s="23" t="str">
+      <c r="A6" s="25" t="str">
         <f t="shared" si="0"/>
         <v>1001002</v>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="26">
         <v>100100</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="26">
         <v>2</v>
       </c>
-      <c r="D6" s="24"/>
-      <c r="E6" s="27" t="s">
+      <c r="D6" s="26"/>
+      <c r="E6" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="24">
-        <v>1</v>
-      </c>
-      <c r="G6" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="23">
+      <c r="F6" s="26">
+        <v>1</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="25">
         <v>2001001</v>
       </c>
-      <c r="I6" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="28" t="s">
+      <c r="I6" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="M6" s="23" t="s">
+      <c r="M6" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="N6" s="16">
+      <c r="N6" s="18">
         <v>4</v>
       </c>
-      <c r="O6" s="16">
+      <c r="O6" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A7" s="23" t="str">
+      <c r="A7" s="25" t="str">
         <f t="shared" si="0"/>
         <v>1001003</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="26">
         <v>100100</v>
       </c>
-      <c r="C7" s="24">
-        <v>3</v>
-      </c>
-      <c r="D7" s="24"/>
-      <c r="E7" s="29" t="s">
+      <c r="C7" s="26">
+        <v>3</v>
+      </c>
+      <c r="D7" s="26"/>
+      <c r="E7" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="24">
-        <v>1</v>
-      </c>
-      <c r="G7" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="23">
+      <c r="F7" s="26">
+        <v>1</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="25">
         <v>2001001</v>
       </c>
-      <c r="I7" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="26" t="s">
+      <c r="I7" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="M7" s="23" t="s">
+      <c r="M7" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="N7" s="16">
+      <c r="N7" s="18">
         <v>4</v>
       </c>
-      <c r="O7" s="16">
+      <c r="O7" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A8" s="23" t="str">
+      <c r="A8" s="25" t="str">
         <f t="shared" si="0"/>
         <v>1001004</v>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="26">
         <v>100100</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="26">
         <v>4</v>
       </c>
-      <c r="D8" s="24"/>
-      <c r="E8" s="30" t="s">
+      <c r="D8" s="26"/>
+      <c r="E8" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="31">
-        <v>1</v>
-      </c>
-      <c r="G8" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="23">
+      <c r="F8" s="33">
+        <v>1</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="25">
         <v>2001001</v>
       </c>
-      <c r="I8" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" s="23"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="26">
+      <c r="I8" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="28">
         <v>10010041</v>
       </c>
-      <c r="M8" s="23" t="s">
+      <c r="M8" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="N8" s="16">
+      <c r="N8" s="18">
         <v>4</v>
       </c>
-      <c r="O8" s="16">
+      <c r="O8" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A9" s="23" t="str">
+      <c r="A9" s="25" t="str">
         <f t="shared" si="0"/>
         <v>1001005</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="26">
         <v>100100</v>
       </c>
-      <c r="C9" s="24">
-        <v>5</v>
-      </c>
-      <c r="D9" s="24"/>
-      <c r="E9" s="32" t="s">
+      <c r="C9" s="26">
+        <v>5</v>
+      </c>
+      <c r="D9" s="26"/>
+      <c r="E9" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="31">
-        <v>1</v>
-      </c>
-      <c r="G9" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="23">
+      <c r="F9" s="33">
+        <v>1</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="25">
         <v>2001001</v>
       </c>
-      <c r="I9" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" s="23"/>
-      <c r="K9" s="23"/>
-      <c r="L9" s="26" t="s">
+      <c r="I9" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="M9" s="23" t="s">
+      <c r="M9" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N9" s="16">
+      <c r="N9" s="18">
         <v>4</v>
       </c>
-      <c r="O9" s="16">
+      <c r="O9" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A10" s="23" t="str">
+      <c r="A10" s="25" t="str">
         <f t="shared" si="0"/>
         <v>1001006</v>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="26">
         <v>100100</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="26">
         <v>6</v>
       </c>
-      <c r="D10" s="24"/>
-      <c r="E10" s="32" t="s">
+      <c r="D10" s="26"/>
+      <c r="E10" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="31">
-        <v>1</v>
-      </c>
-      <c r="G10" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="23">
+      <c r="F10" s="33">
+        <v>1</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="25">
         <v>2001001</v>
       </c>
-      <c r="I10" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J10" s="23"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="26">
+      <c r="I10" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="28">
         <v>10010061</v>
       </c>
-      <c r="M10" s="23" t="s">
+      <c r="M10" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="N10" s="16">
+      <c r="N10" s="18">
         <v>4</v>
       </c>
-      <c r="O10" s="16">
+      <c r="O10" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A11" s="23" t="str">
+      <c r="A11" s="25" t="str">
         <f t="shared" si="0"/>
         <v>1001007</v>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="26">
         <v>100100</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="26">
         <v>7</v>
       </c>
-      <c r="D11" s="24"/>
-      <c r="E11" s="27" t="s">
+      <c r="D11" s="26"/>
+      <c r="E11" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="24">
-        <v>1</v>
-      </c>
-      <c r="G11" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" s="23">
+      <c r="F11" s="26">
+        <v>1</v>
+      </c>
+      <c r="G11" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="25">
         <v>2001001</v>
       </c>
-      <c r="I11" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J11" s="23"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="28" t="s">
+      <c r="I11" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="M11" s="23" t="s">
+      <c r="M11" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="N11" s="16">
+      <c r="N11" s="18">
         <v>4</v>
       </c>
-      <c r="O11" s="16">
+      <c r="O11" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A12" s="33" t="str">
+      <c r="A12" s="35" t="str">
         <f t="shared" si="0"/>
         <v>1003001</v>
       </c>
-      <c r="B12" s="25">
+      <c r="B12" s="27">
         <v>100300</v>
       </c>
-      <c r="C12" s="25">
-        <v>1</v>
-      </c>
-      <c r="D12" s="25" t="s">
+      <c r="C12" s="27">
+        <v>1</v>
+      </c>
+      <c r="D12" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="E12" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="25">
-        <v>1</v>
-      </c>
-      <c r="G12" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H12" s="33">
+      <c r="F12" s="27">
+        <v>1</v>
+      </c>
+      <c r="G12" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="35">
         <v>2003001</v>
       </c>
-      <c r="I12" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" s="33"/>
-      <c r="K12" s="33"/>
-      <c r="L12" s="34">
+      <c r="I12" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" s="35"/>
+      <c r="K12" s="35"/>
+      <c r="L12" s="36">
         <v>10030022</v>
       </c>
-      <c r="M12" s="33" t="s">
+      <c r="M12" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="N12" s="25">
-        <v>3</v>
-      </c>
-      <c r="O12" s="25">
-        <v>3</v>
-      </c>
-      <c r="Q12" s="35"/>
+      <c r="N12" s="27">
+        <v>3</v>
+      </c>
+      <c r="O12" s="27">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="37"/>
     </row>
     <row r="13" s="2" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A13" s="33" t="str">
+      <c r="A13" s="35" t="str">
         <f t="shared" ref="A13:A30" si="1">B13&amp;C13</f>
         <v>1003002</v>
       </c>
-      <c r="B13" s="25">
+      <c r="B13" s="27">
         <v>100300</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="27">
         <v>2</v>
       </c>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25" t="s">
+      <c r="D13" s="27"/>
+      <c r="E13" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="25">
-        <v>1</v>
-      </c>
-      <c r="G13" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H13" s="33">
+      <c r="F13" s="27">
+        <v>1</v>
+      </c>
+      <c r="G13" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="35">
         <v>2003001</v>
       </c>
-      <c r="I13" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="J13" s="33"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="34" t="s">
+      <c r="I13" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" s="35"/>
+      <c r="K13" s="35"/>
+      <c r="L13" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="M13" s="33" t="s">
+      <c r="M13" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="N13" s="25">
-        <v>3</v>
-      </c>
-      <c r="O13" s="25">
-        <v>3</v>
-      </c>
-      <c r="Q13" s="35"/>
+      <c r="N13" s="27">
+        <v>3</v>
+      </c>
+      <c r="O13" s="27">
+        <v>3</v>
+      </c>
+      <c r="Q13" s="37"/>
     </row>
     <row r="14" s="2" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A14" s="33" t="str">
+      <c r="A14" s="35" t="str">
         <f t="shared" si="1"/>
         <v>1003003</v>
       </c>
-      <c r="B14" s="25">
+      <c r="B14" s="27">
         <v>100300</v>
       </c>
-      <c r="C14" s="25">
-        <v>3</v>
-      </c>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25" t="s">
+      <c r="C14" s="27">
+        <v>3</v>
+      </c>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="25">
-        <v>1</v>
-      </c>
-      <c r="G14" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H14" s="33">
+      <c r="F14" s="27">
+        <v>1</v>
+      </c>
+      <c r="G14" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="35">
         <v>2003002</v>
       </c>
-      <c r="I14" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="J14" s="33" t="s">
+      <c r="I14" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="K14" s="33" t="s">
+      <c r="K14" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="L14" s="34" t="s">
+      <c r="L14" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="M14" s="33" t="s">
+      <c r="M14" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="N14" s="25">
-        <v>3</v>
-      </c>
-      <c r="O14" s="25">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="35"/>
+      <c r="N14" s="27">
+        <v>3</v>
+      </c>
+      <c r="O14" s="27">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="37"/>
     </row>
     <row r="15" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A15" s="36" t="str">
+      <c r="A15" s="38" t="str">
         <f t="shared" si="1"/>
         <v>1007001</v>
       </c>
-      <c r="B15" s="37">
+      <c r="B15" s="39">
         <v>100700</v>
       </c>
-      <c r="C15" s="37">
-        <v>1</v>
-      </c>
-      <c r="D15" s="37" t="s">
+      <c r="C15" s="39">
+        <v>1</v>
+      </c>
+      <c r="D15" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="37" t="s">
+      <c r="E15" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="37">
-        <v>1</v>
-      </c>
-      <c r="G15" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="H15" s="36">
+      <c r="F15" s="39">
+        <v>1</v>
+      </c>
+      <c r="G15" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="38">
         <v>2007001</v>
       </c>
-      <c r="I15" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="J15" s="36"/>
-      <c r="K15" s="36"/>
-      <c r="L15" s="38" t="s">
+      <c r="I15" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" s="38"/>
+      <c r="K15" s="38"/>
+      <c r="L15" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="M15" s="36" t="s">
+      <c r="M15" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="N15" s="16">
+      <c r="N15" s="18">
         <v>4</v>
       </c>
-      <c r="O15" s="16">
+      <c r="O15" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="16" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A16" s="36" t="str">
+      <c r="A16" s="38" t="str">
         <f t="shared" si="1"/>
         <v>1007002</v>
       </c>
-      <c r="B16" s="37">
+      <c r="B16" s="39">
         <v>100700</v>
       </c>
-      <c r="C16" s="37">
+      <c r="C16" s="39">
         <v>2</v>
       </c>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37" t="s">
+      <c r="D16" s="39"/>
+      <c r="E16" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="37">
-        <v>1</v>
-      </c>
-      <c r="G16" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="H16" s="36">
+      <c r="F16" s="39">
+        <v>1</v>
+      </c>
+      <c r="G16" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="38">
         <v>2007001</v>
       </c>
-      <c r="I16" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="J16" s="36"/>
-      <c r="K16" s="36"/>
-      <c r="L16" s="38" t="s">
+      <c r="I16" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="J16" s="38"/>
+      <c r="K16" s="38"/>
+      <c r="L16" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="M16" s="36" t="s">
+      <c r="M16" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="N16" s="16">
+      <c r="N16" s="18">
         <v>4</v>
       </c>
-      <c r="O16" s="16">
+      <c r="O16" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="17" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A17" s="39" t="str">
+      <c r="A17" s="41" t="str">
         <f t="shared" si="1"/>
         <v>1012001</v>
       </c>
-      <c r="B17" s="40">
+      <c r="B17" s="42">
         <v>101200</v>
       </c>
-      <c r="C17" s="40">
-        <v>1</v>
-      </c>
-      <c r="D17" s="40" t="s">
+      <c r="C17" s="42">
+        <v>1</v>
+      </c>
+      <c r="D17" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="E17" s="40" t="s">
+      <c r="E17" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="40">
-        <v>1</v>
-      </c>
-      <c r="G17" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="H17" s="39">
+      <c r="F17" s="42">
+        <v>1</v>
+      </c>
+      <c r="G17" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="41">
         <v>2012001</v>
       </c>
-      <c r="I17" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="J17" s="39"/>
-      <c r="K17" s="39"/>
-      <c r="L17" s="41">
+      <c r="I17" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="J17" s="41"/>
+      <c r="K17" s="41"/>
+      <c r="L17" s="43">
         <v>10120011</v>
       </c>
-      <c r="M17" s="39" t="s">
+      <c r="M17" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="N17" s="40">
-        <v>3</v>
-      </c>
-      <c r="O17" s="40">
-        <v>5</v>
-      </c>
-      <c r="Q17" s="42"/>
+      <c r="N17" s="42">
+        <v>3</v>
+      </c>
+      <c r="O17" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="44"/>
     </row>
     <row r="18" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A18" s="39" t="str">
+      <c r="A18" s="41" t="str">
         <f t="shared" si="1"/>
         <v>1012002</v>
       </c>
-      <c r="B18" s="40">
+      <c r="B18" s="42">
         <v>101200</v>
       </c>
-      <c r="C18" s="40">
+      <c r="C18" s="42">
         <v>2</v>
       </c>
-      <c r="D18" s="40"/>
-      <c r="E18" s="40" t="s">
+      <c r="D18" s="42"/>
+      <c r="E18" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="40">
-        <v>1</v>
-      </c>
-      <c r="G18" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="H18" s="39">
+      <c r="F18" s="42">
+        <v>1</v>
+      </c>
+      <c r="G18" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="41">
         <v>2012001</v>
       </c>
-      <c r="I18" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="J18" s="39"/>
-      <c r="K18" s="39"/>
-      <c r="L18" s="41">
+      <c r="I18" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="J18" s="41"/>
+      <c r="K18" s="41"/>
+      <c r="L18" s="43">
         <v>10120021</v>
       </c>
-      <c r="M18" s="39" t="s">
+      <c r="M18" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="N18" s="40">
-        <v>3</v>
-      </c>
-      <c r="O18" s="40">
-        <v>5</v>
-      </c>
-      <c r="Q18" s="42"/>
+      <c r="N18" s="42">
+        <v>3</v>
+      </c>
+      <c r="O18" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="44"/>
     </row>
     <row r="19" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A19" s="39" t="str">
+      <c r="A19" s="41" t="str">
         <f t="shared" si="1"/>
         <v>1012003</v>
       </c>
-      <c r="B19" s="40">
+      <c r="B19" s="42">
         <v>101200</v>
       </c>
-      <c r="C19" s="40">
-        <v>3</v>
-      </c>
-      <c r="D19" s="40"/>
-      <c r="E19" s="40" t="s">
+      <c r="C19" s="42">
+        <v>3</v>
+      </c>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="F19" s="40">
-        <v>1</v>
-      </c>
-      <c r="G19" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="H19" s="39">
+      <c r="F19" s="42">
+        <v>1</v>
+      </c>
+      <c r="G19" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="41">
         <v>2012001</v>
       </c>
-      <c r="I19" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="J19" s="39" t="s">
+      <c r="I19" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="J19" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="K19" s="39" t="s">
+      <c r="K19" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="L19" s="41"/>
-      <c r="M19" s="39" t="s">
+      <c r="L19" s="43"/>
+      <c r="M19" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="N19" s="40">
-        <v>3</v>
-      </c>
-      <c r="O19" s="40">
-        <v>5</v>
-      </c>
-      <c r="Q19" s="42"/>
+      <c r="N19" s="42">
+        <v>3</v>
+      </c>
+      <c r="O19" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q19" s="44"/>
     </row>
     <row r="20" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A20" s="33" t="str">
+      <c r="A20" s="35" t="str">
         <f t="shared" si="1"/>
         <v>1014001</v>
       </c>
-      <c r="B20" s="25">
+      <c r="B20" s="27">
         <v>101400</v>
       </c>
-      <c r="C20" s="25">
-        <v>1</v>
-      </c>
-      <c r="D20" s="25" t="s">
+      <c r="C20" s="27">
+        <v>1</v>
+      </c>
+      <c r="D20" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="E20" s="25" t="s">
+      <c r="E20" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="F20" s="25">
-        <v>1</v>
-      </c>
-      <c r="G20" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H20" s="33">
+      <c r="F20" s="27">
+        <v>1</v>
+      </c>
+      <c r="G20" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="35">
         <v>2014001</v>
       </c>
-      <c r="I20" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="J20" s="33"/>
-      <c r="K20" s="33"/>
-      <c r="L20" s="34" t="s">
+      <c r="I20" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="J20" s="35"/>
+      <c r="K20" s="35"/>
+      <c r="L20" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="M20" s="33" t="s">
+      <c r="M20" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="N20" s="16">
+      <c r="N20" s="18">
         <v>4</v>
       </c>
-      <c r="O20" s="16">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="43"/>
+      <c r="O20" s="18">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="45"/>
     </row>
     <row r="21" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A21" s="33" t="str">
+      <c r="A21" s="35" t="str">
         <f t="shared" si="1"/>
         <v>1014002</v>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="27">
         <v>101400</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="27">
         <v>2</v>
       </c>
-      <c r="D21" s="25" t="s">
+      <c r="D21" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="E21" s="25" t="s">
+      <c r="E21" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="25">
-        <v>1</v>
-      </c>
-      <c r="G21" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H21" s="33">
+      <c r="F21" s="27">
+        <v>1</v>
+      </c>
+      <c r="G21" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="35">
         <v>2014001</v>
       </c>
-      <c r="I21" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="34" t="s">
+      <c r="I21" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="J21" s="35"/>
+      <c r="K21" s="35"/>
+      <c r="L21" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="M21" s="33" t="s">
+      <c r="M21" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="N21" s="16">
+      <c r="N21" s="18">
         <v>4</v>
       </c>
-      <c r="O21" s="16">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="43"/>
+      <c r="O21" s="18">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="45"/>
     </row>
     <row r="22" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A22" s="33" t="str">
+      <c r="A22" s="35" t="str">
         <f t="shared" si="1"/>
         <v>1014003</v>
       </c>
-      <c r="B22" s="25">
+      <c r="B22" s="27">
         <v>101400</v>
       </c>
-      <c r="C22" s="25">
-        <v>3</v>
-      </c>
-      <c r="D22" s="25" t="s">
+      <c r="C22" s="27">
+        <v>3</v>
+      </c>
+      <c r="D22" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="E22" s="25" t="s">
+      <c r="E22" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="F22" s="25">
-        <v>1</v>
-      </c>
-      <c r="G22" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H22" s="33">
+      <c r="F22" s="27">
+        <v>1</v>
+      </c>
+      <c r="G22" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="35">
         <v>2014001</v>
       </c>
-      <c r="I22" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="34">
+      <c r="I22" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="36">
         <v>10140021</v>
       </c>
-      <c r="M22" s="33" t="s">
+      <c r="M22" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="N22" s="16">
+      <c r="N22" s="18">
         <v>4</v>
       </c>
-      <c r="O22" s="16">
-        <v>3</v>
-      </c>
-      <c r="Q22" s="43"/>
+      <c r="O22" s="18">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="45"/>
     </row>
     <row r="23" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A23" s="23" t="str">
+      <c r="A23" s="25" t="str">
         <f t="shared" si="1"/>
         <v>1024001</v>
       </c>
-      <c r="B23" s="24">
+      <c r="B23" s="26">
         <v>102400</v>
       </c>
-      <c r="C23" s="24">
-        <v>1</v>
-      </c>
-      <c r="D23" s="24" t="s">
+      <c r="C23" s="26">
+        <v>1</v>
+      </c>
+      <c r="D23" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="E23" s="25" t="s">
+      <c r="E23" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="F23" s="24">
-        <v>1</v>
-      </c>
-      <c r="G23" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H23" s="23">
+      <c r="F23" s="26">
+        <v>1</v>
+      </c>
+      <c r="G23" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="25">
         <v>2024001</v>
       </c>
-      <c r="I23" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J23" s="23"/>
-      <c r="K23" s="23"/>
-      <c r="L23" s="26" t="s">
+      <c r="I23" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J23" s="25"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="M23" s="23" t="s">
+      <c r="M23" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="N23" s="16">
+      <c r="N23" s="18">
         <v>4</v>
       </c>
-      <c r="O23" s="16">
+      <c r="O23" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A24" s="23" t="str">
+      <c r="A24" s="25" t="str">
         <f t="shared" si="1"/>
         <v>1024002</v>
       </c>
-      <c r="B24" s="24">
+      <c r="B24" s="26">
         <v>102400</v>
       </c>
-      <c r="C24" s="24">
+      <c r="C24" s="26">
         <v>2</v>
       </c>
-      <c r="D24" s="24"/>
-      <c r="E24" s="27" t="s">
+      <c r="D24" s="26"/>
+      <c r="E24" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="24">
-        <v>1</v>
-      </c>
-      <c r="G24" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H24" s="23">
+      <c r="F24" s="26">
+        <v>1</v>
+      </c>
+      <c r="G24" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" s="25">
         <v>2024001</v>
       </c>
-      <c r="I24" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J24" s="23"/>
-      <c r="K24" s="23"/>
-      <c r="L24" s="28" t="s">
+      <c r="I24" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="M24" s="23" t="s">
+      <c r="M24" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="N24" s="16">
+      <c r="N24" s="18">
         <v>4</v>
       </c>
-      <c r="O24" s="16">
+      <c r="O24" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A25" s="23" t="str">
+      <c r="A25" s="25" t="str">
         <f t="shared" si="1"/>
         <v>1024003</v>
       </c>
-      <c r="B25" s="24">
+      <c r="B25" s="26">
         <v>102400</v>
       </c>
-      <c r="C25" s="24">
-        <v>3</v>
-      </c>
-      <c r="D25" s="24"/>
-      <c r="E25" s="29" t="s">
+      <c r="C25" s="26">
+        <v>3</v>
+      </c>
+      <c r="D25" s="26"/>
+      <c r="E25" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="F25" s="24">
-        <v>1</v>
-      </c>
-      <c r="G25" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H25" s="23">
+      <c r="F25" s="26">
+        <v>1</v>
+      </c>
+      <c r="G25" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="25">
         <v>2024001</v>
       </c>
-      <c r="I25" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J25" s="23"/>
-      <c r="K25" s="23"/>
-      <c r="L25" s="26" t="s">
+      <c r="I25" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J25" s="25"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="M25" s="23" t="s">
+      <c r="M25" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="N25" s="16">
+      <c r="N25" s="18">
         <v>4</v>
       </c>
-      <c r="O25" s="16">
+      <c r="O25" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A26" s="23" t="str">
+      <c r="A26" s="25" t="str">
         <f t="shared" si="1"/>
         <v>1024004</v>
       </c>
-      <c r="B26" s="24">
+      <c r="B26" s="26">
         <v>102400</v>
       </c>
-      <c r="C26" s="24">
+      <c r="C26" s="26">
         <v>4</v>
       </c>
-      <c r="D26" s="24"/>
-      <c r="E26" s="30" t="s">
+      <c r="D26" s="26"/>
+      <c r="E26" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="F26" s="31">
-        <v>1</v>
-      </c>
-      <c r="G26" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H26" s="23">
+      <c r="F26" s="33">
+        <v>1</v>
+      </c>
+      <c r="G26" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="25">
         <v>2024001</v>
       </c>
-      <c r="I26" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J26" s="23"/>
-      <c r="K26" s="23"/>
-      <c r="L26" s="26">
+      <c r="I26" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J26" s="25"/>
+      <c r="K26" s="25"/>
+      <c r="L26" s="28">
         <v>10240041</v>
       </c>
-      <c r="M26" s="23" t="s">
+      <c r="M26" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="N26" s="16">
+      <c r="N26" s="18">
         <v>4</v>
       </c>
-      <c r="O26" s="16">
+      <c r="O26" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A27" s="23" t="str">
+      <c r="A27" s="25" t="str">
         <f t="shared" si="1"/>
         <v>1024005</v>
       </c>
-      <c r="B27" s="24">
+      <c r="B27" s="26">
         <v>102400</v>
       </c>
-      <c r="C27" s="24">
-        <v>5</v>
-      </c>
-      <c r="D27" s="24"/>
-      <c r="E27" s="32" t="s">
+      <c r="C27" s="26">
+        <v>5</v>
+      </c>
+      <c r="D27" s="26"/>
+      <c r="E27" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="F27" s="31">
-        <v>1</v>
-      </c>
-      <c r="G27" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H27" s="23">
+      <c r="F27" s="33">
+        <v>1</v>
+      </c>
+      <c r="G27" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H27" s="25">
         <v>2024001</v>
       </c>
-      <c r="I27" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J27" s="23"/>
-      <c r="K27" s="23"/>
-      <c r="L27" s="26" t="s">
+      <c r="I27" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J27" s="25"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="M27" s="23" t="s">
+      <c r="M27" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N27" s="16">
+      <c r="N27" s="18">
         <v>4</v>
       </c>
-      <c r="O27" s="16">
+      <c r="O27" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A28" s="23" t="str">
+      <c r="A28" s="25" t="str">
         <f t="shared" si="1"/>
         <v>1024006</v>
       </c>
-      <c r="B28" s="24">
+      <c r="B28" s="26">
         <v>102400</v>
       </c>
-      <c r="C28" s="24">
+      <c r="C28" s="26">
         <v>6</v>
       </c>
-      <c r="D28" s="24"/>
-      <c r="E28" s="32" t="s">
+      <c r="D28" s="26"/>
+      <c r="E28" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="F28" s="31">
-        <v>1</v>
-      </c>
-      <c r="G28" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H28" s="23">
+      <c r="F28" s="33">
+        <v>1</v>
+      </c>
+      <c r="G28" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28" s="25">
         <v>2024001</v>
       </c>
-      <c r="I28" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="26">
+      <c r="I28" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J28" s="25"/>
+      <c r="K28" s="25"/>
+      <c r="L28" s="28">
         <v>10240061</v>
       </c>
-      <c r="M28" s="23" t="s">
+      <c r="M28" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="N28" s="16">
+      <c r="N28" s="18">
         <v>4</v>
       </c>
-      <c r="O28" s="16">
+      <c r="O28" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A29" s="23" t="str">
+      <c r="A29" s="25" t="str">
         <f t="shared" si="1"/>
         <v>1024007</v>
       </c>
-      <c r="B29" s="24">
+      <c r="B29" s="26">
         <v>102400</v>
       </c>
-      <c r="C29" s="24">
+      <c r="C29" s="26">
         <v>7</v>
       </c>
-      <c r="D29" s="24"/>
-      <c r="E29" s="27" t="s">
+      <c r="D29" s="26"/>
+      <c r="E29" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="F29" s="24">
-        <v>1</v>
-      </c>
-      <c r="G29" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H29" s="23">
+      <c r="F29" s="26">
+        <v>1</v>
+      </c>
+      <c r="G29" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H29" s="25">
         <v>2024001</v>
       </c>
-      <c r="I29" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J29" s="23"/>
-      <c r="K29" s="23"/>
-      <c r="L29" s="28" t="s">
+      <c r="I29" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J29" s="25"/>
+      <c r="K29" s="25"/>
+      <c r="L29" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="M29" s="23" t="s">
+      <c r="M29" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="N29" s="16">
+      <c r="N29" s="18">
         <v>4</v>
       </c>
-      <c r="O29" s="16">
+      <c r="O29" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="30" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A30" s="23" t="str">
+      <c r="A30" s="25" t="str">
         <f t="shared" si="1"/>
         <v>1017001</v>
       </c>
@@ -3159,16 +3216,16 @@
       <c r="M30" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="N30" s="44">
+      <c r="N30" s="46">
         <v>4</v>
       </c>
-      <c r="O30" s="44">
-        <v>5</v>
-      </c>
-      <c r="Q30" s="17"/>
+      <c r="O30" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q30" s="19"/>
     </row>
     <row r="31" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A31" s="23" t="str">
+      <c r="A31" s="25" t="str">
         <f t="shared" ref="A31:A52" si="2">B31&amp;C31</f>
         <v>1017002</v>
       </c>
@@ -3202,16 +3259,16 @@
       <c r="M31" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="N31" s="44">
+      <c r="N31" s="46">
         <v>4</v>
       </c>
-      <c r="O31" s="44">
-        <v>5</v>
-      </c>
-      <c r="Q31" s="17"/>
+      <c r="O31" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q31" s="19"/>
     </row>
     <row r="32" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A32" s="23" t="str">
+      <c r="A32" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1017003</v>
       </c>
@@ -3245,16 +3302,16 @@
       <c r="M32" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N32" s="44">
+      <c r="N32" s="46">
         <v>4</v>
       </c>
-      <c r="O32" s="44">
-        <v>5</v>
-      </c>
-      <c r="Q32" s="17"/>
+      <c r="O32" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="19"/>
     </row>
     <row r="33" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A33" s="23" t="str">
+      <c r="A33" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1022001</v>
       </c>
@@ -3282,22 +3339,22 @@
       <c r="I33" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L33" s="45" t="s">
+      <c r="L33" s="47" t="s">
         <v>85</v>
       </c>
       <c r="M33" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N33" s="44">
-        <v>3</v>
-      </c>
-      <c r="O33" s="44">
-        <v>5</v>
-      </c>
-      <c r="Q33" s="17"/>
+      <c r="N33" s="46">
+        <v>3</v>
+      </c>
+      <c r="O33" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q33" s="19"/>
     </row>
     <row r="34" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A34" s="23" t="str">
+      <c r="A34" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1022002</v>
       </c>
@@ -3313,10 +3370,10 @@
       <c r="E34" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="F34" s="16">
-        <v>1</v>
-      </c>
-      <c r="G34" s="46" t="s">
+      <c r="F34" s="18">
+        <v>1</v>
+      </c>
+      <c r="G34" s="48" t="s">
         <v>23</v>
       </c>
       <c r="H34" s="5">
@@ -3325,22 +3382,22 @@
       <c r="I34" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L34" s="45">
+      <c r="L34" s="47">
         <v>10220033</v>
       </c>
       <c r="M34" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N34" s="44">
-        <v>3</v>
-      </c>
-      <c r="O34" s="44">
-        <v>5</v>
-      </c>
-      <c r="Q34" s="17"/>
+      <c r="N34" s="46">
+        <v>3</v>
+      </c>
+      <c r="O34" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q34" s="19"/>
     </row>
     <row r="35" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A35" s="23" t="str">
+      <c r="A35" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1022003</v>
       </c>
@@ -3356,10 +3413,10 @@
       <c r="E35" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F35" s="46">
-        <v>1</v>
-      </c>
-      <c r="G35" s="46" t="s">
+      <c r="F35" s="48">
+        <v>1</v>
+      </c>
+      <c r="G35" s="48" t="s">
         <v>23</v>
       </c>
       <c r="H35" s="5">
@@ -3368,22 +3425,22 @@
       <c r="I35" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L35" s="47" t="s">
+      <c r="L35" s="49" t="s">
         <v>89</v>
       </c>
       <c r="M35" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N35" s="44">
-        <v>3</v>
-      </c>
-      <c r="O35" s="44">
-        <v>5</v>
-      </c>
-      <c r="Q35" s="17"/>
+      <c r="N35" s="46">
+        <v>3</v>
+      </c>
+      <c r="O35" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q35" s="19"/>
     </row>
     <row r="36" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A36" s="23" t="str">
+      <c r="A36" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1022004</v>
       </c>
@@ -3399,10 +3456,10 @@
       <c r="E36" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F36" s="16">
-        <v>1</v>
-      </c>
-      <c r="G36" s="46" t="s">
+      <c r="F36" s="18">
+        <v>1</v>
+      </c>
+      <c r="G36" s="48" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="5">
@@ -3411,19 +3468,19 @@
       <c r="I36" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L36" s="45">
+      <c r="L36" s="47">
         <v>10220020</v>
       </c>
-      <c r="N36" s="44">
-        <v>3</v>
-      </c>
-      <c r="O36" s="44">
-        <v>5</v>
-      </c>
-      <c r="Q36" s="17"/>
+      <c r="N36" s="46">
+        <v>3</v>
+      </c>
+      <c r="O36" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q36" s="19"/>
     </row>
     <row r="37" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A37" s="23" t="str">
+      <c r="A37" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1022005</v>
       </c>
@@ -3451,20 +3508,20 @@
       <c r="I37" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L37" s="45">
+      <c r="L37" s="47">
         <v>10220019</v>
       </c>
-      <c r="N37" s="44">
-        <v>3</v>
-      </c>
-      <c r="O37" s="44">
-        <v>5</v>
-      </c>
-      <c r="Q37" s="17"/>
-      <c r="S37" s="48"/>
+      <c r="N37" s="46">
+        <v>3</v>
+      </c>
+      <c r="O37" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q37" s="19"/>
+      <c r="S37" s="50"/>
     </row>
     <row r="38" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A38" s="23" t="str">
+      <c r="A38" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1021001</v>
       </c>
@@ -3492,23 +3549,23 @@
       <c r="I38" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L38" s="45" t="s">
+      <c r="L38" s="47" t="s">
         <v>93</v>
       </c>
       <c r="M38" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N38" s="44">
-        <v>3</v>
-      </c>
-      <c r="O38" s="44">
-        <v>5</v>
-      </c>
-      <c r="Q38" s="17"/>
-      <c r="S38" s="48"/>
+      <c r="N38" s="46">
+        <v>3</v>
+      </c>
+      <c r="O38" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q38" s="19"/>
+      <c r="S38" s="50"/>
     </row>
     <row r="39" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A39" s="23" t="str">
+      <c r="A39" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1021002</v>
       </c>
@@ -3536,23 +3593,23 @@
       <c r="I39" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L39" s="45">
+      <c r="L39" s="47">
         <v>10210031</v>
       </c>
       <c r="M39" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N39" s="44">
-        <v>3</v>
-      </c>
-      <c r="O39" s="44">
-        <v>5</v>
-      </c>
-      <c r="Q39" s="17"/>
-      <c r="S39" s="48"/>
+      <c r="N39" s="46">
+        <v>3</v>
+      </c>
+      <c r="O39" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q39" s="19"/>
+      <c r="S39" s="50"/>
     </row>
     <row r="40" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A40" s="23" t="str">
+      <c r="A40" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1021003</v>
       </c>
@@ -3580,23 +3637,23 @@
       <c r="I40" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L40" s="45">
+      <c r="L40" s="47">
         <v>10210041</v>
       </c>
       <c r="M40" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="N40" s="44">
-        <v>3</v>
-      </c>
-      <c r="O40" s="44">
-        <v>5</v>
-      </c>
-      <c r="Q40" s="17"/>
-      <c r="S40" s="48"/>
+      <c r="N40" s="46">
+        <v>3</v>
+      </c>
+      <c r="O40" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q40" s="19"/>
+      <c r="S40" s="50"/>
     </row>
     <row r="41" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A41" s="23" t="str">
+      <c r="A41" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1021004</v>
       </c>
@@ -3624,23 +3681,23 @@
       <c r="I41" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L41" s="45" t="s">
+      <c r="L41" s="47" t="s">
         <v>96</v>
       </c>
       <c r="M41" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N41" s="44">
-        <v>3</v>
-      </c>
-      <c r="O41" s="44">
-        <v>5</v>
-      </c>
-      <c r="Q41" s="17"/>
-      <c r="S41" s="48"/>
+      <c r="N41" s="46">
+        <v>3</v>
+      </c>
+      <c r="O41" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q41" s="19"/>
+      <c r="S41" s="50"/>
     </row>
     <row r="42" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A42" s="23" t="str">
+      <c r="A42" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1018001</v>
       </c>
@@ -3668,20 +3725,20 @@
       <c r="I42" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L42" s="45" t="s">
+      <c r="L42" s="47" t="s">
         <v>98</v>
       </c>
       <c r="M42" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N42" s="44">
+      <c r="N42" s="46">
         <v>4</v>
       </c>
-      <c r="O42" s="44">
+      <c r="O42" s="46">
         <v>6</v>
       </c>
-      <c r="Q42" s="17"/>
-      <c r="S42" s="48"/>
+      <c r="Q42" s="19"/>
+      <c r="S42" s="50"/>
     </row>
     <row r="43" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A43" s="5" t="str">
@@ -3712,16 +3769,16 @@
       <c r="I43" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L43" s="45">
+      <c r="L43" s="47">
         <v>10180031</v>
       </c>
       <c r="M43" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N43" s="44">
+      <c r="N43" s="46">
         <v>4</v>
       </c>
-      <c r="O43" s="44">
+      <c r="O43" s="46">
         <v>6</v>
       </c>
     </row>
@@ -3754,16 +3811,16 @@
       <c r="I44" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L44" s="45" t="s">
+      <c r="L44" s="47" t="s">
         <v>99</v>
       </c>
       <c r="M44" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N44" s="44">
+      <c r="N44" s="46">
         <v>4</v>
       </c>
-      <c r="O44" s="44">
+      <c r="O44" s="46">
         <v>6</v>
       </c>
     </row>
@@ -3796,19 +3853,19 @@
       <c r="I45" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L45" s="45" t="s">
+      <c r="L45" s="47" t="s">
         <v>101</v>
       </c>
       <c r="M45" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N45" s="44">
-        <v>3</v>
-      </c>
-      <c r="O45" s="44">
-        <v>5</v>
-      </c>
-      <c r="Q45" s="7"/>
+      <c r="N45" s="46">
+        <v>3</v>
+      </c>
+      <c r="O45" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q45" s="9"/>
     </row>
     <row r="46" customFormat="1" ht="16.5" spans="1:19">
       <c r="A46" s="5" t="str">
@@ -3839,19 +3896,19 @@
       <c r="I46" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L46" s="45">
+      <c r="L46" s="47">
         <v>10250031</v>
       </c>
       <c r="M46" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="N46" s="44">
-        <v>3</v>
-      </c>
-      <c r="O46" s="44">
-        <v>5</v>
-      </c>
-      <c r="Q46" s="7"/>
+      <c r="N46" s="46">
+        <v>3</v>
+      </c>
+      <c r="O46" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q46" s="9"/>
     </row>
     <row r="47" customFormat="1" ht="16.5" spans="1:19">
       <c r="A47" s="5" t="str">
@@ -3882,19 +3939,19 @@
       <c r="I47" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L47" s="45" t="s">
+      <c r="L47" s="47" t="s">
         <v>103</v>
       </c>
       <c r="M47" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N47" s="44">
-        <v>3</v>
-      </c>
-      <c r="O47" s="44">
-        <v>5</v>
-      </c>
-      <c r="Q47" s="7"/>
+      <c r="N47" s="46">
+        <v>3</v>
+      </c>
+      <c r="O47" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q47" s="9"/>
     </row>
     <row r="48" customFormat="1" ht="16.5" spans="1:19">
       <c r="A48" s="5" t="str">
@@ -3925,19 +3982,19 @@
       <c r="I48" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L48" s="45" t="s">
+      <c r="L48" s="47" t="s">
         <v>105</v>
       </c>
       <c r="M48" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N48" s="44">
+      <c r="N48" s="46">
         <v>4</v>
       </c>
-      <c r="O48" s="44">
-        <v>5</v>
-      </c>
-      <c r="Q48" s="7"/>
+      <c r="O48" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q48" s="9"/>
     </row>
     <row r="49" customFormat="1" ht="16.5" spans="1:17">
       <c r="A49" s="5" t="str">
@@ -3968,19 +4025,19 @@
       <c r="I49" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L49" s="45">
+      <c r="L49" s="47">
         <v>10230003</v>
       </c>
       <c r="M49" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="N49" s="44">
+      <c r="N49" s="46">
         <v>4</v>
       </c>
-      <c r="O49" s="44">
-        <v>5</v>
-      </c>
-      <c r="Q49" s="7"/>
+      <c r="O49" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q49" s="9"/>
     </row>
     <row r="50" customFormat="1" ht="16.5" spans="1:17">
       <c r="A50" s="5" t="str">
@@ -4011,19 +4068,19 @@
       <c r="I50" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L50" s="45" t="s">
+      <c r="L50" s="47" t="s">
         <v>106</v>
       </c>
       <c r="M50" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N50" s="44">
+      <c r="N50" s="46">
         <v>4</v>
       </c>
-      <c r="O50" s="44">
-        <v>5</v>
-      </c>
-      <c r="Q50" s="7"/>
+      <c r="O50" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q50" s="9"/>
     </row>
     <row r="51" customFormat="1" ht="16.5" spans="1:17">
       <c r="A51" s="5" t="str">
@@ -4054,19 +4111,19 @@
       <c r="I51" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L51" s="45">
+      <c r="L51" s="47">
         <v>10340007</v>
       </c>
       <c r="M51" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="N51" s="44">
-        <v>3</v>
-      </c>
-      <c r="O51" s="44">
-        <v>3</v>
-      </c>
-      <c r="Q51" s="7"/>
+      <c r="N51" s="46">
+        <v>3</v>
+      </c>
+      <c r="O51" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q51" s="9"/>
     </row>
     <row r="52" customFormat="1" ht="16.5" spans="1:17">
       <c r="A52" s="5" t="str">
@@ -4097,20 +4154,20 @@
       <c r="I52" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L52" s="45"/>
+      <c r="L52" s="47"/>
       <c r="M52" s="5"/>
-      <c r="N52" s="44">
-        <v>3</v>
-      </c>
-      <c r="O52" s="44">
-        <v>3</v>
-      </c>
-      <c r="P52" s="49"/>
-      <c r="Q52" s="7"/>
+      <c r="N52" s="46">
+        <v>3</v>
+      </c>
+      <c r="O52" s="46">
+        <v>3</v>
+      </c>
+      <c r="P52" s="51"/>
+      <c r="Q52" s="9"/>
     </row>
     <row r="53" customFormat="1" ht="16.5" spans="1:17">
       <c r="A53" s="5" t="str">
-        <f t="shared" ref="A53:A66" si="3">B53&amp;C53</f>
+        <f t="shared" ref="A53:A71" si="3">B53&amp;C53</f>
         <v>1035001</v>
       </c>
       <c r="B53" s="5">
@@ -4137,19 +4194,19 @@
       <c r="I53" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L53" s="45" t="s">
+      <c r="L53" s="47" t="s">
         <v>112</v>
       </c>
       <c r="M53" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="N53" s="44">
+      <c r="N53" s="46">
         <v>4</v>
       </c>
-      <c r="O53" s="44">
-        <v>3</v>
-      </c>
-      <c r="Q53" s="7"/>
+      <c r="O53" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q53" s="9"/>
     </row>
     <row r="54" customFormat="1" ht="16.5" spans="1:17">
       <c r="A54" s="5" t="str">
@@ -4180,19 +4237,19 @@
       <c r="I54" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L54" s="45" t="s">
+      <c r="L54" s="47" t="s">
         <v>115</v>
       </c>
       <c r="M54" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="N54" s="44">
+      <c r="N54" s="46">
         <v>4</v>
       </c>
-      <c r="O54" s="44">
-        <v>3</v>
-      </c>
-      <c r="Q54" s="7"/>
+      <c r="O54" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="9"/>
     </row>
     <row r="55" customFormat="1" ht="16.5" spans="1:17">
       <c r="A55" s="5" t="str">
@@ -4223,19 +4280,19 @@
       <c r="I55" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L55" s="45" t="s">
+      <c r="L55" s="47" t="s">
         <v>117</v>
       </c>
       <c r="M55" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="N55" s="44">
+      <c r="N55" s="46">
         <v>4</v>
       </c>
-      <c r="O55" s="44">
-        <v>3</v>
-      </c>
-      <c r="Q55" s="7"/>
+      <c r="O55" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q55" s="9"/>
     </row>
     <row r="56" customFormat="1" ht="16.5" spans="1:17">
       <c r="A56" s="5" t="str">
@@ -4266,19 +4323,19 @@
       <c r="I56" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L56" s="45" t="s">
+      <c r="L56" s="47" t="s">
         <v>120</v>
       </c>
       <c r="M56" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="N56" s="44">
+      <c r="N56" s="46">
         <v>4</v>
       </c>
-      <c r="O56" s="44">
-        <v>3</v>
-      </c>
-      <c r="Q56" s="7"/>
+      <c r="O56" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q56" s="9"/>
     </row>
     <row r="57" customFormat="1" ht="16.5" spans="1:17">
       <c r="A57" s="5" t="str">
@@ -4309,19 +4366,19 @@
       <c r="I57" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L57" s="45" t="s">
+      <c r="L57" s="47" t="s">
         <v>121</v>
       </c>
       <c r="M57" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="N57" s="44">
+      <c r="N57" s="46">
         <v>4</v>
       </c>
-      <c r="O57" s="44">
-        <v>3</v>
-      </c>
-      <c r="Q57" s="7"/>
+      <c r="O57" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="9"/>
     </row>
     <row r="58" customFormat="1" ht="16.5" spans="1:17">
       <c r="A58" s="5" t="str">
@@ -4352,19 +4409,19 @@
       <c r="I58" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L58" s="45" t="s">
+      <c r="L58" s="47" t="s">
         <v>122</v>
       </c>
       <c r="M58" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="N58" s="44">
+      <c r="N58" s="46">
         <v>4</v>
       </c>
-      <c r="O58" s="44">
-        <v>3</v>
-      </c>
-      <c r="Q58" s="7"/>
+      <c r="O58" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="9"/>
     </row>
     <row r="59" customFormat="1" ht="16.5" spans="1:17">
       <c r="A59" s="5" t="str">
@@ -4395,19 +4452,19 @@
       <c r="I59" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L59" s="45" t="s">
+      <c r="L59" s="47" t="s">
         <v>124</v>
       </c>
       <c r="M59" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="N59" s="44">
-        <v>3</v>
-      </c>
-      <c r="O59" s="44">
-        <v>3</v>
-      </c>
-      <c r="Q59" s="7"/>
+      <c r="N59" s="46">
+        <v>3</v>
+      </c>
+      <c r="O59" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="9"/>
     </row>
     <row r="60" customFormat="1" ht="16.5" spans="1:17">
       <c r="A60" s="5" t="str">
@@ -4438,19 +4495,19 @@
       <c r="I60" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L60" s="45">
+      <c r="L60" s="47">
         <v>10360004</v>
       </c>
       <c r="M60" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="N60" s="44">
-        <v>3</v>
-      </c>
-      <c r="O60" s="44">
-        <v>3</v>
-      </c>
-      <c r="Q60" s="7"/>
+      <c r="N60" s="46">
+        <v>3</v>
+      </c>
+      <c r="O60" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="9"/>
     </row>
     <row r="61" customFormat="1" ht="16.5" spans="1:17">
       <c r="A61" s="5" t="str">
@@ -4481,19 +4538,19 @@
       <c r="I61" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L61" s="45">
+      <c r="L61" s="47">
         <v>10360002</v>
       </c>
       <c r="M61" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="N61" s="44">
-        <v>3</v>
-      </c>
-      <c r="O61" s="44">
-        <v>3</v>
-      </c>
-      <c r="Q61" s="7"/>
+      <c r="N61" s="46">
+        <v>3</v>
+      </c>
+      <c r="O61" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q61" s="9"/>
     </row>
     <row r="62" customFormat="1" ht="16.5" spans="1:17">
       <c r="A62" s="5" t="str">
@@ -4524,19 +4581,19 @@
       <c r="I62" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L62" s="45" t="s">
+      <c r="L62" s="47" t="s">
         <v>129</v>
       </c>
       <c r="M62" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="N62" s="44">
-        <v>5</v>
-      </c>
-      <c r="O62" s="44">
+      <c r="N62" s="46">
+        <v>5</v>
+      </c>
+      <c r="O62" s="46">
         <v>6</v>
       </c>
-      <c r="Q62" s="7"/>
+      <c r="Q62" s="9"/>
     </row>
     <row r="63" customFormat="1" ht="16.5" spans="1:17">
       <c r="A63" s="5" t="str">
@@ -4567,19 +4624,19 @@
       <c r="I63" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L63" s="45">
+      <c r="L63" s="47">
         <v>10280002</v>
       </c>
       <c r="M63" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="N63" s="44">
-        <v>5</v>
-      </c>
-      <c r="O63" s="44">
+      <c r="N63" s="46">
+        <v>5</v>
+      </c>
+      <c r="O63" s="46">
         <v>6</v>
       </c>
-      <c r="Q63" s="7"/>
+      <c r="Q63" s="9"/>
     </row>
     <row r="64" customFormat="1" ht="16.5" spans="1:17">
       <c r="A64" s="5" t="str">
@@ -4610,19 +4667,19 @@
       <c r="I64" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L64" s="45" t="s">
+      <c r="L64" s="47" t="s">
         <v>132</v>
       </c>
       <c r="M64" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N64" s="44">
-        <v>5</v>
-      </c>
-      <c r="O64" s="44">
+      <c r="N64" s="46">
+        <v>5</v>
+      </c>
+      <c r="O64" s="46">
         <v>6</v>
       </c>
-      <c r="Q64" s="7"/>
+      <c r="Q64" s="9"/>
     </row>
     <row r="65" customFormat="1" ht="16.5" spans="1:17">
       <c r="A65" s="5" t="str">
@@ -4653,19 +4710,19 @@
       <c r="I65" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L65" s="45">
+      <c r="L65" s="47">
         <v>10340007</v>
       </c>
       <c r="M65" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="N65" s="44">
-        <v>3</v>
-      </c>
-      <c r="O65" s="44">
-        <v>3</v>
-      </c>
-      <c r="Q65" s="7"/>
+      <c r="N65" s="46">
+        <v>3</v>
+      </c>
+      <c r="O65" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q65" s="9"/>
     </row>
     <row r="66" customFormat="1" ht="16.5" spans="1:17">
       <c r="A66" s="5" t="str">
@@ -4696,96 +4753,231 @@
       <c r="I66" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L66" s="45"/>
+      <c r="L66" s="47"/>
       <c r="M66" s="5"/>
-      <c r="N66" s="44">
-        <v>3</v>
-      </c>
-      <c r="O66" s="44">
-        <v>3</v>
-      </c>
-      <c r="P66" s="49"/>
-      <c r="Q66" s="7"/>
-    </row>
-    <row r="67" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A67" s="5"/>
-      <c r="B67" s="5"/>
-      <c r="C67" s="5"/>
-      <c r="D67" s="5"/>
-      <c r="E67" s="5"/>
-      <c r="F67" s="5"/>
-      <c r="G67" s="5"/>
-      <c r="H67" s="5"/>
-      <c r="I67" s="5"/>
-      <c r="L67" s="45"/>
-      <c r="M67" s="5"/>
-      <c r="N67" s="44"/>
-      <c r="O67" s="44"/>
-      <c r="Q67" s="7"/>
+      <c r="N66" s="46">
+        <v>3</v>
+      </c>
+      <c r="O66" s="46">
+        <v>3</v>
+      </c>
+      <c r="P66" s="51"/>
+      <c r="Q66" s="9"/>
+    </row>
+    <row r="67" s="6" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A67" s="52" t="str">
+        <f t="shared" si="3"/>
+        <v>1020001</v>
+      </c>
+      <c r="B67" s="52">
+        <v>102000</v>
+      </c>
+      <c r="C67" s="52">
+        <v>1</v>
+      </c>
+      <c r="D67" s="52" t="s">
+        <v>135</v>
+      </c>
+      <c r="E67" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="F67" s="52">
+        <v>1</v>
+      </c>
+      <c r="G67" s="52" t="s">
+        <v>23</v>
+      </c>
+      <c r="H67" s="52">
+        <v>2020001</v>
+      </c>
+      <c r="I67" s="52" t="s">
+        <v>24</v>
+      </c>
+      <c r="L67" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="M67" s="52" t="s">
+        <v>137</v>
+      </c>
+      <c r="N67" s="54">
+        <v>5</v>
+      </c>
+      <c r="O67" s="54">
+        <v>5</v>
+      </c>
+      <c r="Q67" s="55"/>
     </row>
     <row r="68" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A68" s="5"/>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="5"/>
-      <c r="E68" s="5"/>
-      <c r="F68" s="5"/>
-      <c r="G68" s="5"/>
-      <c r="H68" s="5"/>
-      <c r="I68" s="5"/>
-      <c r="L68" s="45"/>
-      <c r="M68" s="5"/>
-      <c r="N68" s="44"/>
-      <c r="O68" s="44"/>
-      <c r="Q68" s="7"/>
+      <c r="A68" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1020002</v>
+      </c>
+      <c r="B68" s="5">
+        <v>102000</v>
+      </c>
+      <c r="C68" s="5">
+        <v>2</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F68" s="5">
+        <v>1</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H68" s="5">
+        <v>2020001</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L68" s="47" t="s">
+        <v>138</v>
+      </c>
+      <c r="M68" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="N68" s="46">
+        <v>5</v>
+      </c>
+      <c r="O68" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q68" s="9"/>
     </row>
     <row r="69" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A69" s="5"/>
-      <c r="B69" s="5"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="5"/>
-      <c r="E69" s="5"/>
-      <c r="F69" s="5"/>
-      <c r="G69" s="5"/>
-      <c r="H69" s="5"/>
-      <c r="I69" s="5"/>
-      <c r="L69" s="45"/>
-      <c r="M69" s="5"/>
-      <c r="N69" s="44"/>
-      <c r="O69" s="44"/>
-      <c r="Q69" s="7"/>
-    </row>
-    <row r="70" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A70" s="5"/>
-      <c r="B70" s="5"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="5"/>
-      <c r="E70" s="5"/>
-      <c r="F70" s="5"/>
-      <c r="G70" s="5"/>
-      <c r="H70" s="5"/>
-      <c r="I70" s="5"/>
-      <c r="L70" s="45"/>
-      <c r="M70" s="5"/>
-      <c r="N70" s="44"/>
-      <c r="O70" s="44"/>
-      <c r="Q70" s="7"/>
+      <c r="A69" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1020003</v>
+      </c>
+      <c r="B69" s="5">
+        <v>102000</v>
+      </c>
+      <c r="C69" s="5">
+        <v>3</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F69" s="5">
+        <v>1</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H69" s="5">
+        <v>2020001</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L69" s="47" t="s">
+        <v>140</v>
+      </c>
+      <c r="M69" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="N69" s="46">
+        <v>5</v>
+      </c>
+      <c r="O69" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q69" s="9"/>
+    </row>
+    <row r="70" s="7" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A70" s="56" t="str">
+        <f t="shared" si="3"/>
+        <v>1020004</v>
+      </c>
+      <c r="B70" s="56">
+        <v>102000</v>
+      </c>
+      <c r="C70" s="56">
+        <v>4</v>
+      </c>
+      <c r="D70" s="56" t="s">
+        <v>135</v>
+      </c>
+      <c r="E70" s="56" t="s">
+        <v>142</v>
+      </c>
+      <c r="F70" s="56">
+        <v>1</v>
+      </c>
+      <c r="G70" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="H70" s="56">
+        <v>2020002</v>
+      </c>
+      <c r="I70" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="L70" s="57">
+        <v>10200016</v>
+      </c>
+      <c r="M70" s="56" t="s">
+        <v>143</v>
+      </c>
+      <c r="N70" s="58">
+        <v>5</v>
+      </c>
+      <c r="O70" s="58">
+        <v>5</v>
+      </c>
+      <c r="Q70" s="59"/>
     </row>
     <row r="71" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A71" s="5"/>
-      <c r="B71" s="5"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="5"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
-      <c r="G71" s="5"/>
-      <c r="H71" s="5"/>
-      <c r="I71" s="5"/>
-      <c r="L71" s="45"/>
-      <c r="M71" s="5"/>
-      <c r="N71" s="44"/>
-      <c r="O71" s="44"/>
-      <c r="Q71" s="7"/>
+      <c r="A71" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1020005</v>
+      </c>
+      <c r="B71" s="5">
+        <v>102000</v>
+      </c>
+      <c r="C71" s="5">
+        <v>5</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F71" s="5">
+        <v>1</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H71" s="5">
+        <v>2020003</v>
+      </c>
+      <c r="I71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L71" s="47">
+        <v>10200021</v>
+      </c>
+      <c r="M71" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="N71" s="46">
+        <v>5</v>
+      </c>
+      <c r="O71" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q71" s="9"/>
     </row>
     <row r="72" customFormat="1" ht="16.5" spans="1:17">
       <c r="A72" s="5"/>
@@ -4797,11 +4989,11 @@
       <c r="G72" s="5"/>
       <c r="H72" s="5"/>
       <c r="I72" s="5"/>
-      <c r="L72" s="45"/>
+      <c r="L72" s="47"/>
       <c r="M72" s="5"/>
-      <c r="N72" s="44"/>
-      <c r="O72" s="44"/>
-      <c r="Q72" s="7"/>
+      <c r="N72" s="46"/>
+      <c r="O72" s="46"/>
+      <c r="Q72" s="9"/>
     </row>
     <row r="73" customFormat="1" ht="16.5" spans="1:17">
       <c r="A73" s="5"/>
@@ -4813,11 +5005,11 @@
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
       <c r="I73" s="5"/>
-      <c r="L73" s="45"/>
+      <c r="L73" s="47"/>
       <c r="M73" s="5"/>
-      <c r="N73" s="44"/>
-      <c r="O73" s="44"/>
-      <c r="Q73" s="7"/>
+      <c r="N73" s="46"/>
+      <c r="O73" s="46"/>
+      <c r="Q73" s="9"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:K2">

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -464,7 +464,7 @@
     <t>常规模式</t>
   </si>
   <si>
-    <t>10350014|10350001</t>
+    <t>10350003|10350014|10350001</t>
   </si>
   <si>
     <t>改出奖金符号</t>
@@ -488,7 +488,7 @@
     <t>金钱兔</t>
   </si>
   <si>
-    <t>10350114|10350101</t>
+    <t>10350103|10350114|10350101</t>
   </si>
   <si>
     <t>10350114|10350113</t>
@@ -1234,13 +1234,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1343,6 +1344,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1889,14 +1901,14 @@
     <col min="11" max="11" width="16.75" customWidth="1"/>
     <col min="12" max="12" width="53.25" customWidth="1"/>
     <col min="13" max="13" width="21.6083333333333" customWidth="1"/>
-    <col min="14" max="15" width="9" style="6"/>
+    <col min="14" max="15" width="9" style="7"/>
     <col min="16" max="16" width="15" customWidth="1"/>
-    <col min="17" max="17" width="23.75" style="7" customWidth="1"/>
+    <col min="17" max="17" width="23.75" style="8" customWidth="1"/>
     <col min="18" max="18" width="60.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:17">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
@@ -1907,34 +1919,34 @@
       </c>
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="5"/>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="10" t="s">
         <v>4</v>
       </c>
       <c r="I1" s="5"/>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="10"/>
-      <c r="L1" s="11" t="s">
+      <c r="K1" s="11"/>
+      <c r="L1" s="12" t="s">
         <v>6</v>
       </c>
       <c r="M1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="N1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="O1" s="13" t="s">
         <v>9</v>
       </c>
       <c r="Q1"/>
     </row>
     <row r="2" ht="16.5" spans="1:17">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -1945,62 +1957,62 @@
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="5"/>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="10" t="s">
         <v>10</v>
       </c>
       <c r="I2" s="5"/>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="14"/>
-      <c r="L2" s="15" t="s">
+      <c r="K2" s="15"/>
+      <c r="L2" s="16" t="s">
         <v>12</v>
       </c>
       <c r="M2" s="5"/>
-      <c r="N2" s="16" t="s">
+      <c r="N2" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="16" t="s">
+      <c r="O2" s="17" t="s">
         <v>10</v>
       </c>
       <c r="Q2"/>
     </row>
     <row r="3" ht="16.5" spans="1:17">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="18" t="s">
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="17"/>
-      <c r="H3" s="19" t="s">
+      <c r="G3" s="18"/>
+      <c r="H3" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="20" t="s">
+      <c r="I3" s="18"/>
+      <c r="J3" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="20"/>
-      <c r="L3" s="21" t="s">
+      <c r="K3" s="21"/>
+      <c r="L3" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="M3" s="17"/>
-      <c r="N3" s="16" t="s">
+      <c r="M3" s="18"/>
+      <c r="N3" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="16" t="s">
+      <c r="O3" s="17" t="s">
         <v>20</v>
       </c>
       <c r="Q3"/>
@@ -2010,1101 +2022,1101 @@
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="9"/>
+      <c r="F4" s="10"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="9"/>
+      <c r="H4" s="10"/>
       <c r="I4" s="5"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="11"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="12"/>
       <c r="M4" s="5"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
       <c r="Q4"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A5" s="23" t="str">
+      <c r="A5" s="24" t="str">
         <f t="shared" ref="A5:A15" si="0">B5&amp;C5</f>
         <v>1001001</v>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="25">
         <v>100100</v>
       </c>
-      <c r="C5" s="24">
-        <v>1</v>
-      </c>
-      <c r="D5" s="24" t="s">
+      <c r="C5" s="25">
+        <v>1</v>
+      </c>
+      <c r="D5" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E5" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="24">
-        <v>1</v>
-      </c>
-      <c r="G5" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="23">
+      <c r="F5" s="25">
+        <v>1</v>
+      </c>
+      <c r="G5" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="24">
         <v>2001001</v>
       </c>
-      <c r="I5" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="23"/>
-      <c r="K5" s="23"/>
-      <c r="L5" s="26" t="s">
+      <c r="I5" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="M5" s="23" t="s">
+      <c r="M5" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="N5" s="16">
+      <c r="N5" s="17">
         <v>4</v>
       </c>
-      <c r="O5" s="16">
+      <c r="O5" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A6" s="23" t="str">
+      <c r="A6" s="24" t="str">
         <f t="shared" si="0"/>
         <v>1001002</v>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="25">
         <v>100100</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="25">
         <v>2</v>
       </c>
-      <c r="D6" s="24"/>
-      <c r="E6" s="27" t="s">
+      <c r="D6" s="25"/>
+      <c r="E6" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="24">
-        <v>1</v>
-      </c>
-      <c r="G6" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="23">
+      <c r="F6" s="25">
+        <v>1</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="24">
         <v>2001001</v>
       </c>
-      <c r="I6" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="28" t="s">
+      <c r="I6" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="M6" s="23" t="s">
+      <c r="M6" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="N6" s="16">
+      <c r="N6" s="17">
         <v>4</v>
       </c>
-      <c r="O6" s="16">
+      <c r="O6" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A7" s="23" t="str">
+      <c r="A7" s="24" t="str">
         <f t="shared" si="0"/>
         <v>1001003</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="25">
         <v>100100</v>
       </c>
-      <c r="C7" s="24">
-        <v>3</v>
-      </c>
-      <c r="D7" s="24"/>
-      <c r="E7" s="29" t="s">
+      <c r="C7" s="25">
+        <v>3</v>
+      </c>
+      <c r="D7" s="25"/>
+      <c r="E7" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="24">
-        <v>1</v>
-      </c>
-      <c r="G7" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="23">
+      <c r="F7" s="25">
+        <v>1</v>
+      </c>
+      <c r="G7" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="24">
         <v>2001001</v>
       </c>
-      <c r="I7" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="26" t="s">
+      <c r="I7" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="24"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="M7" s="23" t="s">
+      <c r="M7" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="N7" s="16">
+      <c r="N7" s="17">
         <v>4</v>
       </c>
-      <c r="O7" s="16">
+      <c r="O7" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A8" s="23" t="str">
+      <c r="A8" s="24" t="str">
         <f t="shared" si="0"/>
         <v>1001004</v>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="25">
         <v>100100</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="25">
         <v>4</v>
       </c>
-      <c r="D8" s="24"/>
-      <c r="E8" s="30" t="s">
+      <c r="D8" s="25"/>
+      <c r="E8" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="31">
-        <v>1</v>
-      </c>
-      <c r="G8" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="23">
+      <c r="F8" s="32">
+        <v>1</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="24">
         <v>2001001</v>
       </c>
-      <c r="I8" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" s="23"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="26">
+      <c r="I8" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="24"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="27">
         <v>10010041</v>
       </c>
-      <c r="M8" s="23" t="s">
+      <c r="M8" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="N8" s="16">
+      <c r="N8" s="17">
         <v>4</v>
       </c>
-      <c r="O8" s="16">
+      <c r="O8" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A9" s="23" t="str">
+      <c r="A9" s="24" t="str">
         <f t="shared" si="0"/>
         <v>1001005</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="25">
         <v>100100</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="25">
         <v>5</v>
       </c>
-      <c r="D9" s="24"/>
-      <c r="E9" s="32" t="s">
+      <c r="D9" s="25"/>
+      <c r="E9" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="31">
-        <v>1</v>
-      </c>
-      <c r="G9" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="23">
+      <c r="F9" s="32">
+        <v>1</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="24">
         <v>2001001</v>
       </c>
-      <c r="I9" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" s="23"/>
-      <c r="K9" s="23"/>
-      <c r="L9" s="26" t="s">
+      <c r="I9" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" s="24"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="M9" s="23" t="s">
+      <c r="M9" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="N9" s="16">
+      <c r="N9" s="17">
         <v>4</v>
       </c>
-      <c r="O9" s="16">
+      <c r="O9" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A10" s="23" t="str">
+      <c r="A10" s="24" t="str">
         <f t="shared" si="0"/>
         <v>1001006</v>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="25">
         <v>100100</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="25">
         <v>6</v>
       </c>
-      <c r="D10" s="24"/>
-      <c r="E10" s="32" t="s">
+      <c r="D10" s="25"/>
+      <c r="E10" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="31">
-        <v>1</v>
-      </c>
-      <c r="G10" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="23">
+      <c r="F10" s="32">
+        <v>1</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="24">
         <v>2001001</v>
       </c>
-      <c r="I10" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J10" s="23"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="26">
+      <c r="I10" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" s="24"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="27">
         <v>10010061</v>
       </c>
-      <c r="M10" s="23" t="s">
+      <c r="M10" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="N10" s="16">
+      <c r="N10" s="17">
         <v>4</v>
       </c>
-      <c r="O10" s="16">
+      <c r="O10" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A11" s="23" t="str">
+      <c r="A11" s="24" t="str">
         <f t="shared" si="0"/>
         <v>1001007</v>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="25">
         <v>100100</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="25">
         <v>7</v>
       </c>
-      <c r="D11" s="24"/>
-      <c r="E11" s="27" t="s">
+      <c r="D11" s="25"/>
+      <c r="E11" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="24">
-        <v>1</v>
-      </c>
-      <c r="G11" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" s="23">
+      <c r="F11" s="25">
+        <v>1</v>
+      </c>
+      <c r="G11" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="24">
         <v>2001001</v>
       </c>
-      <c r="I11" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J11" s="23"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="28" t="s">
+      <c r="I11" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="J11" s="24"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="M11" s="23" t="s">
+      <c r="M11" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="N11" s="16">
+      <c r="N11" s="17">
         <v>4</v>
       </c>
-      <c r="O11" s="16">
+      <c r="O11" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A12" s="33" t="str">
+      <c r="A12" s="34" t="str">
         <f t="shared" si="0"/>
         <v>1003001</v>
       </c>
-      <c r="B12" s="25">
+      <c r="B12" s="26">
         <v>100300</v>
       </c>
-      <c r="C12" s="25">
-        <v>1</v>
-      </c>
-      <c r="D12" s="25" t="s">
+      <c r="C12" s="26">
+        <v>1</v>
+      </c>
+      <c r="D12" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="E12" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="25">
-        <v>1</v>
-      </c>
-      <c r="G12" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H12" s="33">
+      <c r="F12" s="26">
+        <v>1</v>
+      </c>
+      <c r="G12" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="34">
         <v>2003001</v>
       </c>
-      <c r="I12" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" s="33"/>
-      <c r="K12" s="33"/>
-      <c r="L12" s="34">
+      <c r="I12" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" s="34"/>
+      <c r="K12" s="34"/>
+      <c r="L12" s="35">
         <v>10030022</v>
       </c>
-      <c r="M12" s="33" t="s">
+      <c r="M12" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="N12" s="25">
-        <v>3</v>
-      </c>
-      <c r="O12" s="25">
-        <v>3</v>
-      </c>
-      <c r="Q12" s="35"/>
+      <c r="N12" s="26">
+        <v>3</v>
+      </c>
+      <c r="O12" s="26">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="36"/>
     </row>
     <row r="13" s="2" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A13" s="33" t="str">
+      <c r="A13" s="34" t="str">
         <f t="shared" ref="A13:A30" si="1">B13&amp;C13</f>
         <v>1003002</v>
       </c>
-      <c r="B13" s="25">
+      <c r="B13" s="26">
         <v>100300</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="26">
         <v>2</v>
       </c>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25" t="s">
+      <c r="D13" s="26"/>
+      <c r="E13" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="25">
-        <v>1</v>
-      </c>
-      <c r="G13" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H13" s="33">
+      <c r="F13" s="26">
+        <v>1</v>
+      </c>
+      <c r="G13" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="34">
         <v>2003001</v>
       </c>
-      <c r="I13" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="J13" s="33"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="34" t="s">
+      <c r="I13" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" s="34"/>
+      <c r="K13" s="34"/>
+      <c r="L13" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="M13" s="33" t="s">
+      <c r="M13" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="N13" s="25">
-        <v>3</v>
-      </c>
-      <c r="O13" s="25">
-        <v>3</v>
-      </c>
-      <c r="Q13" s="35"/>
+      <c r="N13" s="26">
+        <v>3</v>
+      </c>
+      <c r="O13" s="26">
+        <v>3</v>
+      </c>
+      <c r="Q13" s="36"/>
     </row>
     <row r="14" s="2" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A14" s="33" t="str">
+      <c r="A14" s="34" t="str">
         <f t="shared" si="1"/>
         <v>1003003</v>
       </c>
-      <c r="B14" s="25">
+      <c r="B14" s="26">
         <v>100300</v>
       </c>
-      <c r="C14" s="25">
-        <v>3</v>
-      </c>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25" t="s">
+      <c r="C14" s="26">
+        <v>3</v>
+      </c>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="25">
-        <v>1</v>
-      </c>
-      <c r="G14" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H14" s="33">
+      <c r="F14" s="26">
+        <v>1</v>
+      </c>
+      <c r="G14" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="34">
         <v>2003002</v>
       </c>
-      <c r="I14" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="J14" s="33" t="s">
+      <c r="I14" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="K14" s="33" t="s">
+      <c r="K14" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="L14" s="34" t="s">
+      <c r="L14" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="M14" s="33" t="s">
+      <c r="M14" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="N14" s="25">
-        <v>3</v>
-      </c>
-      <c r="O14" s="25">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="35"/>
+      <c r="N14" s="26">
+        <v>3</v>
+      </c>
+      <c r="O14" s="26">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="36"/>
     </row>
     <row r="15" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A15" s="36" t="str">
+      <c r="A15" s="37" t="str">
         <f t="shared" si="1"/>
         <v>1007001</v>
       </c>
-      <c r="B15" s="37">
+      <c r="B15" s="38">
         <v>100700</v>
       </c>
-      <c r="C15" s="37">
-        <v>1</v>
-      </c>
-      <c r="D15" s="37" t="s">
+      <c r="C15" s="38">
+        <v>1</v>
+      </c>
+      <c r="D15" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="37" t="s">
+      <c r="E15" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="37">
-        <v>1</v>
-      </c>
-      <c r="G15" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="H15" s="36">
+      <c r="F15" s="38">
+        <v>1</v>
+      </c>
+      <c r="G15" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="37">
         <v>2007001</v>
       </c>
-      <c r="I15" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="J15" s="36"/>
-      <c r="K15" s="36"/>
-      <c r="L15" s="38" t="s">
+      <c r="I15" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" s="37"/>
+      <c r="K15" s="37"/>
+      <c r="L15" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="M15" s="36" t="s">
+      <c r="M15" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="N15" s="16">
+      <c r="N15" s="17">
         <v>4</v>
       </c>
-      <c r="O15" s="16">
+      <c r="O15" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="16" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A16" s="36" t="str">
+      <c r="A16" s="37" t="str">
         <f t="shared" si="1"/>
         <v>1007002</v>
       </c>
-      <c r="B16" s="37">
+      <c r="B16" s="38">
         <v>100700</v>
       </c>
-      <c r="C16" s="37">
+      <c r="C16" s="38">
         <v>2</v>
       </c>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37" t="s">
+      <c r="D16" s="38"/>
+      <c r="E16" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="37">
-        <v>1</v>
-      </c>
-      <c r="G16" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="H16" s="36">
+      <c r="F16" s="38">
+        <v>1</v>
+      </c>
+      <c r="G16" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="37">
         <v>2007001</v>
       </c>
-      <c r="I16" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="J16" s="36"/>
-      <c r="K16" s="36"/>
-      <c r="L16" s="38" t="s">
+      <c r="I16" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="J16" s="37"/>
+      <c r="K16" s="37"/>
+      <c r="L16" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="M16" s="36" t="s">
+      <c r="M16" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="N16" s="16">
+      <c r="N16" s="17">
         <v>4</v>
       </c>
-      <c r="O16" s="16">
+      <c r="O16" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="17" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A17" s="39" t="str">
+      <c r="A17" s="40" t="str">
         <f t="shared" si="1"/>
         <v>1012001</v>
       </c>
-      <c r="B17" s="40">
+      <c r="B17" s="41">
         <v>101200</v>
       </c>
-      <c r="C17" s="40">
-        <v>1</v>
-      </c>
-      <c r="D17" s="40" t="s">
+      <c r="C17" s="41">
+        <v>1</v>
+      </c>
+      <c r="D17" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="E17" s="40" t="s">
+      <c r="E17" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="40">
-        <v>1</v>
-      </c>
-      <c r="G17" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="H17" s="39">
+      <c r="F17" s="41">
+        <v>1</v>
+      </c>
+      <c r="G17" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="40">
         <v>2012001</v>
       </c>
-      <c r="I17" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="J17" s="39"/>
-      <c r="K17" s="39"/>
-      <c r="L17" s="41">
+      <c r="I17" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="J17" s="40"/>
+      <c r="K17" s="40"/>
+      <c r="L17" s="42">
         <v>10120011</v>
       </c>
-      <c r="M17" s="39" t="s">
+      <c r="M17" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="N17" s="40">
-        <v>3</v>
-      </c>
-      <c r="O17" s="40">
+      <c r="N17" s="41">
+        <v>3</v>
+      </c>
+      <c r="O17" s="41">
         <v>5</v>
       </c>
-      <c r="Q17" s="42"/>
+      <c r="Q17" s="43"/>
     </row>
     <row r="18" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A18" s="39" t="str">
+      <c r="A18" s="40" t="str">
         <f t="shared" si="1"/>
         <v>1012002</v>
       </c>
-      <c r="B18" s="40">
+      <c r="B18" s="41">
         <v>101200</v>
       </c>
-      <c r="C18" s="40">
+      <c r="C18" s="41">
         <v>2</v>
       </c>
-      <c r="D18" s="40"/>
-      <c r="E18" s="40" t="s">
+      <c r="D18" s="41"/>
+      <c r="E18" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="40">
-        <v>1</v>
-      </c>
-      <c r="G18" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="H18" s="39">
+      <c r="F18" s="41">
+        <v>1</v>
+      </c>
+      <c r="G18" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="40">
         <v>2012001</v>
       </c>
-      <c r="I18" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="J18" s="39"/>
-      <c r="K18" s="39"/>
-      <c r="L18" s="41">
+      <c r="I18" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="J18" s="40"/>
+      <c r="K18" s="40"/>
+      <c r="L18" s="42">
         <v>10120021</v>
       </c>
-      <c r="M18" s="39" t="s">
+      <c r="M18" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="N18" s="40">
-        <v>3</v>
-      </c>
-      <c r="O18" s="40">
+      <c r="N18" s="41">
+        <v>3</v>
+      </c>
+      <c r="O18" s="41">
         <v>5</v>
       </c>
-      <c r="Q18" s="42"/>
+      <c r="Q18" s="43"/>
     </row>
     <row r="19" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A19" s="39" t="str">
+      <c r="A19" s="40" t="str">
         <f t="shared" si="1"/>
         <v>1012003</v>
       </c>
-      <c r="B19" s="40">
+      <c r="B19" s="41">
         <v>101200</v>
       </c>
-      <c r="C19" s="40">
-        <v>3</v>
-      </c>
-      <c r="D19" s="40"/>
-      <c r="E19" s="40" t="s">
+      <c r="C19" s="41">
+        <v>3</v>
+      </c>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="F19" s="40">
-        <v>1</v>
-      </c>
-      <c r="G19" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="H19" s="39">
+      <c r="F19" s="41">
+        <v>1</v>
+      </c>
+      <c r="G19" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="40">
         <v>2012001</v>
       </c>
-      <c r="I19" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="J19" s="39" t="s">
+      <c r="I19" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="J19" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="K19" s="39" t="s">
+      <c r="K19" s="40" t="s">
         <v>63</v>
       </c>
-      <c r="L19" s="41"/>
-      <c r="M19" s="39" t="s">
+      <c r="L19" s="42"/>
+      <c r="M19" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="N19" s="40">
-        <v>3</v>
-      </c>
-      <c r="O19" s="40">
+      <c r="N19" s="41">
+        <v>3</v>
+      </c>
+      <c r="O19" s="41">
         <v>5</v>
       </c>
-      <c r="Q19" s="42"/>
+      <c r="Q19" s="43"/>
     </row>
     <row r="20" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A20" s="33" t="str">
+      <c r="A20" s="34" t="str">
         <f t="shared" si="1"/>
         <v>1014001</v>
       </c>
-      <c r="B20" s="25">
+      <c r="B20" s="26">
         <v>101400</v>
       </c>
-      <c r="C20" s="25">
-        <v>1</v>
-      </c>
-      <c r="D20" s="25" t="s">
+      <c r="C20" s="26">
+        <v>1</v>
+      </c>
+      <c r="D20" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="E20" s="25" t="s">
+      <c r="E20" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="F20" s="25">
-        <v>1</v>
-      </c>
-      <c r="G20" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H20" s="33">
+      <c r="F20" s="26">
+        <v>1</v>
+      </c>
+      <c r="G20" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="34">
         <v>2014001</v>
       </c>
-      <c r="I20" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="J20" s="33"/>
-      <c r="K20" s="33"/>
-      <c r="L20" s="34" t="s">
+      <c r="I20" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="J20" s="34"/>
+      <c r="K20" s="34"/>
+      <c r="L20" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="M20" s="33" t="s">
+      <c r="M20" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="N20" s="16">
+      <c r="N20" s="17">
         <v>4</v>
       </c>
-      <c r="O20" s="16">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="43"/>
+      <c r="O20" s="17">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="44"/>
     </row>
     <row r="21" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A21" s="33" t="str">
+      <c r="A21" s="34" t="str">
         <f t="shared" si="1"/>
         <v>1014002</v>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="26">
         <v>101400</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="26">
         <v>2</v>
       </c>
-      <c r="D21" s="25" t="s">
+      <c r="D21" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="E21" s="25" t="s">
+      <c r="E21" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="25">
-        <v>1</v>
-      </c>
-      <c r="G21" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H21" s="33">
+      <c r="F21" s="26">
+        <v>1</v>
+      </c>
+      <c r="G21" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="34">
         <v>2014001</v>
       </c>
-      <c r="I21" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="34" t="s">
+      <c r="I21" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="J21" s="34"/>
+      <c r="K21" s="34"/>
+      <c r="L21" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="M21" s="33" t="s">
+      <c r="M21" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="N21" s="16">
+      <c r="N21" s="17">
         <v>4</v>
       </c>
-      <c r="O21" s="16">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="43"/>
+      <c r="O21" s="17">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="44"/>
     </row>
     <row r="22" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A22" s="33" t="str">
+      <c r="A22" s="34" t="str">
         <f t="shared" si="1"/>
         <v>1014003</v>
       </c>
-      <c r="B22" s="25">
+      <c r="B22" s="26">
         <v>101400</v>
       </c>
-      <c r="C22" s="25">
-        <v>3</v>
-      </c>
-      <c r="D22" s="25" t="s">
+      <c r="C22" s="26">
+        <v>3</v>
+      </c>
+      <c r="D22" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="E22" s="25" t="s">
+      <c r="E22" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="F22" s="25">
-        <v>1</v>
-      </c>
-      <c r="G22" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H22" s="33">
+      <c r="F22" s="26">
+        <v>1</v>
+      </c>
+      <c r="G22" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="34">
         <v>2014001</v>
       </c>
-      <c r="I22" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="34">
+      <c r="I22" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="35">
         <v>10140021</v>
       </c>
-      <c r="M22" s="33" t="s">
+      <c r="M22" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="N22" s="16">
+      <c r="N22" s="17">
         <v>4</v>
       </c>
-      <c r="O22" s="16">
-        <v>3</v>
-      </c>
-      <c r="Q22" s="43"/>
+      <c r="O22" s="17">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="44"/>
     </row>
     <row r="23" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A23" s="23" t="str">
+      <c r="A23" s="24" t="str">
         <f t="shared" si="1"/>
         <v>1024001</v>
       </c>
-      <c r="B23" s="24">
+      <c r="B23" s="25">
         <v>102400</v>
       </c>
-      <c r="C23" s="24">
-        <v>1</v>
-      </c>
-      <c r="D23" s="24" t="s">
+      <c r="C23" s="25">
+        <v>1</v>
+      </c>
+      <c r="D23" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E23" s="25" t="s">
+      <c r="E23" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="F23" s="24">
-        <v>1</v>
-      </c>
-      <c r="G23" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H23" s="23">
+      <c r="F23" s="25">
+        <v>1</v>
+      </c>
+      <c r="G23" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="24">
         <v>2024001</v>
       </c>
-      <c r="I23" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J23" s="23"/>
-      <c r="K23" s="23"/>
-      <c r="L23" s="26" t="s">
+      <c r="I23" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="M23" s="23" t="s">
+      <c r="M23" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="N23" s="16">
+      <c r="N23" s="17">
         <v>4</v>
       </c>
-      <c r="O23" s="16">
+      <c r="O23" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A24" s="23" t="str">
+      <c r="A24" s="24" t="str">
         <f t="shared" si="1"/>
         <v>1024002</v>
       </c>
-      <c r="B24" s="24">
+      <c r="B24" s="25">
         <v>102400</v>
       </c>
-      <c r="C24" s="24">
+      <c r="C24" s="25">
         <v>2</v>
       </c>
-      <c r="D24" s="24"/>
-      <c r="E24" s="27" t="s">
+      <c r="D24" s="25"/>
+      <c r="E24" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="24">
-        <v>1</v>
-      </c>
-      <c r="G24" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H24" s="23">
+      <c r="F24" s="25">
+        <v>1</v>
+      </c>
+      <c r="G24" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" s="24">
         <v>2024001</v>
       </c>
-      <c r="I24" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J24" s="23"/>
-      <c r="K24" s="23"/>
-      <c r="L24" s="28" t="s">
+      <c r="I24" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="J24" s="24"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="M24" s="23" t="s">
+      <c r="M24" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="N24" s="16">
+      <c r="N24" s="17">
         <v>4</v>
       </c>
-      <c r="O24" s="16">
+      <c r="O24" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A25" s="23" t="str">
+      <c r="A25" s="24" t="str">
         <f t="shared" si="1"/>
         <v>1024003</v>
       </c>
-      <c r="B25" s="24">
+      <c r="B25" s="25">
         <v>102400</v>
       </c>
-      <c r="C25" s="24">
-        <v>3</v>
-      </c>
-      <c r="D25" s="24"/>
-      <c r="E25" s="29" t="s">
+      <c r="C25" s="25">
+        <v>3</v>
+      </c>
+      <c r="D25" s="25"/>
+      <c r="E25" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="F25" s="24">
-        <v>1</v>
-      </c>
-      <c r="G25" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H25" s="23">
+      <c r="F25" s="25">
+        <v>1</v>
+      </c>
+      <c r="G25" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="24">
         <v>2024001</v>
       </c>
-      <c r="I25" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J25" s="23"/>
-      <c r="K25" s="23"/>
-      <c r="L25" s="26" t="s">
+      <c r="I25" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="J25" s="24"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="M25" s="23" t="s">
+      <c r="M25" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="N25" s="16">
+      <c r="N25" s="17">
         <v>4</v>
       </c>
-      <c r="O25" s="16">
+      <c r="O25" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A26" s="23" t="str">
+      <c r="A26" s="24" t="str">
         <f t="shared" si="1"/>
         <v>1024004</v>
       </c>
-      <c r="B26" s="24">
+      <c r="B26" s="25">
         <v>102400</v>
       </c>
-      <c r="C26" s="24">
+      <c r="C26" s="25">
         <v>4</v>
       </c>
-      <c r="D26" s="24"/>
-      <c r="E26" s="30" t="s">
+      <c r="D26" s="25"/>
+      <c r="E26" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="F26" s="31">
-        <v>1</v>
-      </c>
-      <c r="G26" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H26" s="23">
+      <c r="F26" s="32">
+        <v>1</v>
+      </c>
+      <c r="G26" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="24">
         <v>2024001</v>
       </c>
-      <c r="I26" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J26" s="23"/>
-      <c r="K26" s="23"/>
-      <c r="L26" s="26">
+      <c r="I26" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="J26" s="24"/>
+      <c r="K26" s="24"/>
+      <c r="L26" s="27">
         <v>10240041</v>
       </c>
-      <c r="M26" s="23" t="s">
+      <c r="M26" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="N26" s="16">
+      <c r="N26" s="17">
         <v>4</v>
       </c>
-      <c r="O26" s="16">
+      <c r="O26" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A27" s="23" t="str">
+      <c r="A27" s="24" t="str">
         <f t="shared" si="1"/>
         <v>1024005</v>
       </c>
-      <c r="B27" s="24">
+      <c r="B27" s="25">
         <v>102400</v>
       </c>
-      <c r="C27" s="24">
+      <c r="C27" s="25">
         <v>5</v>
       </c>
-      <c r="D27" s="24"/>
-      <c r="E27" s="32" t="s">
+      <c r="D27" s="25"/>
+      <c r="E27" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="F27" s="31">
-        <v>1</v>
-      </c>
-      <c r="G27" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H27" s="23">
+      <c r="F27" s="32">
+        <v>1</v>
+      </c>
+      <c r="G27" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H27" s="24">
         <v>2024001</v>
       </c>
-      <c r="I27" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J27" s="23"/>
-      <c r="K27" s="23"/>
-      <c r="L27" s="26" t="s">
+      <c r="I27" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="J27" s="24"/>
+      <c r="K27" s="24"/>
+      <c r="L27" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="M27" s="23" t="s">
+      <c r="M27" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="N27" s="16">
+      <c r="N27" s="17">
         <v>4</v>
       </c>
-      <c r="O27" s="16">
+      <c r="O27" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A28" s="23" t="str">
+      <c r="A28" s="24" t="str">
         <f t="shared" si="1"/>
         <v>1024006</v>
       </c>
-      <c r="B28" s="24">
+      <c r="B28" s="25">
         <v>102400</v>
       </c>
-      <c r="C28" s="24">
+      <c r="C28" s="25">
         <v>6</v>
       </c>
-      <c r="D28" s="24"/>
-      <c r="E28" s="32" t="s">
+      <c r="D28" s="25"/>
+      <c r="E28" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="F28" s="31">
-        <v>1</v>
-      </c>
-      <c r="G28" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H28" s="23">
+      <c r="F28" s="32">
+        <v>1</v>
+      </c>
+      <c r="G28" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28" s="24">
         <v>2024001</v>
       </c>
-      <c r="I28" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="26">
+      <c r="I28" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="J28" s="24"/>
+      <c r="K28" s="24"/>
+      <c r="L28" s="27">
         <v>10240061</v>
       </c>
-      <c r="M28" s="23" t="s">
+      <c r="M28" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="N28" s="16">
+      <c r="N28" s="17">
         <v>4</v>
       </c>
-      <c r="O28" s="16">
+      <c r="O28" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A29" s="23" t="str">
+      <c r="A29" s="24" t="str">
         <f t="shared" si="1"/>
         <v>1024007</v>
       </c>
-      <c r="B29" s="24">
+      <c r="B29" s="25">
         <v>102400</v>
       </c>
-      <c r="C29" s="24">
+      <c r="C29" s="25">
         <v>7</v>
       </c>
-      <c r="D29" s="24"/>
-      <c r="E29" s="27" t="s">
+      <c r="D29" s="25"/>
+      <c r="E29" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="F29" s="24">
-        <v>1</v>
-      </c>
-      <c r="G29" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H29" s="23">
+      <c r="F29" s="25">
+        <v>1</v>
+      </c>
+      <c r="G29" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H29" s="24">
         <v>2024001</v>
       </c>
-      <c r="I29" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J29" s="23"/>
-      <c r="K29" s="23"/>
-      <c r="L29" s="28" t="s">
+      <c r="I29" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="J29" s="24"/>
+      <c r="K29" s="24"/>
+      <c r="L29" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="M29" s="23" t="s">
+      <c r="M29" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="N29" s="16">
+      <c r="N29" s="17">
         <v>4</v>
       </c>
-      <c r="O29" s="16">
+      <c r="O29" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="30" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A30" s="23" t="str">
+      <c r="A30" s="24" t="str">
         <f t="shared" si="1"/>
         <v>1017001</v>
       </c>
@@ -3138,17 +3150,17 @@
       <c r="M30" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="N30" s="44">
+      <c r="N30" s="45">
         <v>4</v>
       </c>
-      <c r="O30" s="44">
+      <c r="O30" s="45">
         <v>5</v>
       </c>
-      <c r="Q30" s="17"/>
+      <c r="Q30" s="18"/>
     </row>
     <row r="31" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A31" s="23" t="str">
-        <f t="shared" ref="A31:A51" si="2">B31&amp;C31</f>
+      <c r="A31" s="24" t="str">
+        <f t="shared" ref="A31:A53" si="2">B31&amp;C31</f>
         <v>1017002</v>
       </c>
       <c r="B31" s="5">
@@ -3181,16 +3193,16 @@
       <c r="M31" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="N31" s="44">
+      <c r="N31" s="45">
         <v>4</v>
       </c>
-      <c r="O31" s="44">
+      <c r="O31" s="45">
         <v>5</v>
       </c>
-      <c r="Q31" s="17"/>
+      <c r="Q31" s="18"/>
     </row>
     <row r="32" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A32" s="23" t="str">
+      <c r="A32" s="24" t="str">
         <f t="shared" si="2"/>
         <v>1017003</v>
       </c>
@@ -3224,16 +3236,16 @@
       <c r="M32" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N32" s="44">
+      <c r="N32" s="45">
         <v>4</v>
       </c>
-      <c r="O32" s="44">
+      <c r="O32" s="45">
         <v>5</v>
       </c>
-      <c r="Q32" s="17"/>
+      <c r="Q32" s="18"/>
     </row>
     <row r="33" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A33" s="23" t="str">
+      <c r="A33" s="24" t="str">
         <f t="shared" si="2"/>
         <v>1022001</v>
       </c>
@@ -3261,22 +3273,22 @@
       <c r="I33" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L33" s="45" t="s">
+      <c r="L33" s="46" t="s">
         <v>85</v>
       </c>
       <c r="M33" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N33" s="44">
-        <v>3</v>
-      </c>
-      <c r="O33" s="44">
+      <c r="N33" s="45">
+        <v>3</v>
+      </c>
+      <c r="O33" s="45">
         <v>5</v>
       </c>
-      <c r="Q33" s="17"/>
+      <c r="Q33" s="18"/>
     </row>
     <row r="34" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A34" s="23" t="str">
+      <c r="A34" s="24" t="str">
         <f t="shared" si="2"/>
         <v>1022002</v>
       </c>
@@ -3292,10 +3304,10 @@
       <c r="E34" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="F34" s="16">
-        <v>1</v>
-      </c>
-      <c r="G34" s="46" t="s">
+      <c r="F34" s="17">
+        <v>1</v>
+      </c>
+      <c r="G34" s="47" t="s">
         <v>23</v>
       </c>
       <c r="H34" s="5">
@@ -3304,22 +3316,22 @@
       <c r="I34" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L34" s="45">
+      <c r="L34" s="46">
         <v>10220033</v>
       </c>
       <c r="M34" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N34" s="44">
-        <v>3</v>
-      </c>
-      <c r="O34" s="44">
+      <c r="N34" s="45">
+        <v>3</v>
+      </c>
+      <c r="O34" s="45">
         <v>5</v>
       </c>
-      <c r="Q34" s="17"/>
+      <c r="Q34" s="18"/>
     </row>
     <row r="35" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A35" s="23" t="str">
+      <c r="A35" s="24" t="str">
         <f t="shared" si="2"/>
         <v>1022003</v>
       </c>
@@ -3335,10 +3347,10 @@
       <c r="E35" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F35" s="46">
-        <v>1</v>
-      </c>
-      <c r="G35" s="46" t="s">
+      <c r="F35" s="47">
+        <v>1</v>
+      </c>
+      <c r="G35" s="47" t="s">
         <v>23</v>
       </c>
       <c r="H35" s="5">
@@ -3347,22 +3359,22 @@
       <c r="I35" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L35" s="47" t="s">
+      <c r="L35" s="48" t="s">
         <v>89</v>
       </c>
       <c r="M35" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N35" s="44">
-        <v>3</v>
-      </c>
-      <c r="O35" s="44">
+      <c r="N35" s="45">
+        <v>3</v>
+      </c>
+      <c r="O35" s="45">
         <v>5</v>
       </c>
-      <c r="Q35" s="17"/>
+      <c r="Q35" s="18"/>
     </row>
     <row r="36" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A36" s="23" t="str">
+      <c r="A36" s="24" t="str">
         <f t="shared" si="2"/>
         <v>1022004</v>
       </c>
@@ -3378,10 +3390,10 @@
       <c r="E36" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F36" s="16">
-        <v>1</v>
-      </c>
-      <c r="G36" s="46" t="s">
+      <c r="F36" s="17">
+        <v>1</v>
+      </c>
+      <c r="G36" s="47" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="5">
@@ -3390,19 +3402,19 @@
       <c r="I36" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L36" s="45">
+      <c r="L36" s="46">
         <v>10220020</v>
       </c>
-      <c r="N36" s="44">
-        <v>3</v>
-      </c>
-      <c r="O36" s="44">
+      <c r="N36" s="45">
+        <v>3</v>
+      </c>
+      <c r="O36" s="45">
         <v>5</v>
       </c>
-      <c r="Q36" s="17"/>
+      <c r="Q36" s="18"/>
     </row>
     <row r="37" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A37" s="23" t="str">
+      <c r="A37" s="24" t="str">
         <f t="shared" si="2"/>
         <v>1022005</v>
       </c>
@@ -3430,20 +3442,20 @@
       <c r="I37" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L37" s="45">
+      <c r="L37" s="46">
         <v>10220019</v>
       </c>
-      <c r="N37" s="44">
-        <v>3</v>
-      </c>
-      <c r="O37" s="44">
+      <c r="N37" s="45">
+        <v>3</v>
+      </c>
+      <c r="O37" s="45">
         <v>5</v>
       </c>
-      <c r="Q37" s="17"/>
-      <c r="S37" s="48"/>
+      <c r="Q37" s="18"/>
+      <c r="S37" s="49"/>
     </row>
     <row r="38" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A38" s="23" t="str">
+      <c r="A38" s="24" t="str">
         <f t="shared" si="2"/>
         <v>1021001</v>
       </c>
@@ -3471,23 +3483,23 @@
       <c r="I38" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L38" s="45" t="s">
+      <c r="L38" s="46" t="s">
         <v>93</v>
       </c>
       <c r="M38" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N38" s="44">
-        <v>3</v>
-      </c>
-      <c r="O38" s="44">
+      <c r="N38" s="45">
+        <v>3</v>
+      </c>
+      <c r="O38" s="45">
         <v>5</v>
       </c>
-      <c r="Q38" s="17"/>
-      <c r="S38" s="48"/>
+      <c r="Q38" s="18"/>
+      <c r="S38" s="49"/>
     </row>
     <row r="39" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A39" s="23" t="str">
+      <c r="A39" s="24" t="str">
         <f t="shared" si="2"/>
         <v>1021002</v>
       </c>
@@ -3515,23 +3527,23 @@
       <c r="I39" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L39" s="45">
+      <c r="L39" s="46">
         <v>10210031</v>
       </c>
       <c r="M39" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N39" s="44">
-        <v>3</v>
-      </c>
-      <c r="O39" s="44">
+      <c r="N39" s="45">
+        <v>3</v>
+      </c>
+      <c r="O39" s="45">
         <v>5</v>
       </c>
-      <c r="Q39" s="17"/>
-      <c r="S39" s="48"/>
+      <c r="Q39" s="18"/>
+      <c r="S39" s="49"/>
     </row>
     <row r="40" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A40" s="23" t="str">
+      <c r="A40" s="24" t="str">
         <f t="shared" si="2"/>
         <v>1021003</v>
       </c>
@@ -3559,23 +3571,23 @@
       <c r="I40" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L40" s="45">
+      <c r="L40" s="46">
         <v>10210041</v>
       </c>
       <c r="M40" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="N40" s="44">
-        <v>3</v>
-      </c>
-      <c r="O40" s="44">
+      <c r="N40" s="45">
+        <v>3</v>
+      </c>
+      <c r="O40" s="45">
         <v>5</v>
       </c>
-      <c r="Q40" s="17"/>
-      <c r="S40" s="48"/>
+      <c r="Q40" s="18"/>
+      <c r="S40" s="49"/>
     </row>
     <row r="41" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A41" s="23" t="str">
+      <c r="A41" s="24" t="str">
         <f t="shared" si="2"/>
         <v>1021004</v>
       </c>
@@ -3603,23 +3615,23 @@
       <c r="I41" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L41" s="45" t="s">
+      <c r="L41" s="46" t="s">
         <v>96</v>
       </c>
       <c r="M41" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N41" s="44">
-        <v>3</v>
-      </c>
-      <c r="O41" s="44">
+      <c r="N41" s="45">
+        <v>3</v>
+      </c>
+      <c r="O41" s="45">
         <v>5</v>
       </c>
-      <c r="Q41" s="17"/>
-      <c r="S41" s="48"/>
+      <c r="Q41" s="18"/>
+      <c r="S41" s="49"/>
     </row>
     <row r="42" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A42" s="23" t="str">
+      <c r="A42" s="24" t="str">
         <f t="shared" si="2"/>
         <v>1018001</v>
       </c>
@@ -3647,20 +3659,20 @@
       <c r="I42" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L42" s="45" t="s">
+      <c r="L42" s="46" t="s">
         <v>98</v>
       </c>
       <c r="M42" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N42" s="44">
+      <c r="N42" s="45">
         <v>4</v>
       </c>
-      <c r="O42" s="44">
+      <c r="O42" s="45">
         <v>6</v>
       </c>
-      <c r="Q42" s="17"/>
-      <c r="S42" s="48"/>
+      <c r="Q42" s="18"/>
+      <c r="S42" s="49"/>
     </row>
     <row r="43" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A43" s="5" t="str">
@@ -3691,16 +3703,16 @@
       <c r="I43" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L43" s="45">
+      <c r="L43" s="46">
         <v>10180031</v>
       </c>
       <c r="M43" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N43" s="44">
+      <c r="N43" s="45">
         <v>4</v>
       </c>
-      <c r="O43" s="44">
+      <c r="O43" s="45">
         <v>6</v>
       </c>
     </row>
@@ -3733,16 +3745,16 @@
       <c r="I44" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L44" s="45" t="s">
+      <c r="L44" s="46" t="s">
         <v>99</v>
       </c>
       <c r="M44" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N44" s="44">
+      <c r="N44" s="45">
         <v>4</v>
       </c>
-      <c r="O44" s="44">
+      <c r="O44" s="45">
         <v>6</v>
       </c>
     </row>
@@ -3775,19 +3787,19 @@
       <c r="I45" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L45" s="45" t="s">
+      <c r="L45" s="46" t="s">
         <v>101</v>
       </c>
       <c r="M45" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N45" s="44">
-        <v>3</v>
-      </c>
-      <c r="O45" s="44">
+      <c r="N45" s="45">
+        <v>3</v>
+      </c>
+      <c r="O45" s="45">
         <v>5</v>
       </c>
-      <c r="Q45" s="7"/>
+      <c r="Q45" s="8"/>
     </row>
     <row r="46" customFormat="1" ht="16.5" spans="1:19">
       <c r="A46" s="5" t="str">
@@ -3818,19 +3830,19 @@
       <c r="I46" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L46" s="45">
+      <c r="L46" s="46">
         <v>10250031</v>
       </c>
       <c r="M46" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="N46" s="44">
-        <v>3</v>
-      </c>
-      <c r="O46" s="44">
+      <c r="N46" s="45">
+        <v>3</v>
+      </c>
+      <c r="O46" s="45">
         <v>5</v>
       </c>
-      <c r="Q46" s="7"/>
+      <c r="Q46" s="8"/>
     </row>
     <row r="47" customFormat="1" ht="16.5" spans="1:19">
       <c r="A47" s="5" t="str">
@@ -3861,19 +3873,19 @@
       <c r="I47" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L47" s="45" t="s">
+      <c r="L47" s="46" t="s">
         <v>103</v>
       </c>
       <c r="M47" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N47" s="44">
-        <v>3</v>
-      </c>
-      <c r="O47" s="44">
+      <c r="N47" s="45">
+        <v>3</v>
+      </c>
+      <c r="O47" s="45">
         <v>5</v>
       </c>
-      <c r="Q47" s="7"/>
+      <c r="Q47" s="8"/>
     </row>
     <row r="48" customFormat="1" ht="16.5" spans="1:19">
       <c r="A48" s="5" t="str">
@@ -3904,19 +3916,19 @@
       <c r="I48" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L48" s="45" t="s">
+      <c r="L48" s="46" t="s">
         <v>105</v>
       </c>
       <c r="M48" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N48" s="44">
+      <c r="N48" s="45">
         <v>4</v>
       </c>
-      <c r="O48" s="44">
+      <c r="O48" s="45">
         <v>5</v>
       </c>
-      <c r="Q48" s="7"/>
+      <c r="Q48" s="8"/>
     </row>
     <row r="49" customFormat="1" ht="16.5" spans="1:17">
       <c r="A49" s="5" t="str">
@@ -3947,19 +3959,19 @@
       <c r="I49" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L49" s="45">
+      <c r="L49" s="46">
         <v>10230003</v>
       </c>
       <c r="M49" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="N49" s="44">
+      <c r="N49" s="45">
         <v>4</v>
       </c>
-      <c r="O49" s="44">
+      <c r="O49" s="45">
         <v>5</v>
       </c>
-      <c r="Q49" s="7"/>
+      <c r="Q49" s="8"/>
     </row>
     <row r="50" customFormat="1" ht="16.5" spans="1:17">
       <c r="A50" s="5" t="str">
@@ -3990,19 +4002,19 @@
       <c r="I50" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L50" s="45" t="s">
+      <c r="L50" s="46" t="s">
         <v>106</v>
       </c>
       <c r="M50" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N50" s="44">
+      <c r="N50" s="45">
         <v>4</v>
       </c>
-      <c r="O50" s="44">
+      <c r="O50" s="45">
         <v>5</v>
       </c>
-      <c r="Q50" s="7"/>
+      <c r="Q50" s="8"/>
     </row>
     <row r="51" customFormat="1" ht="16.5" spans="1:17">
       <c r="A51" s="5" t="str">
@@ -4033,23 +4045,23 @@
       <c r="I51" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L51" s="45">
+      <c r="L51" s="46">
         <v>10340007</v>
       </c>
       <c r="M51" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="N51" s="44">
-        <v>3</v>
-      </c>
-      <c r="O51" s="44">
-        <v>3</v>
-      </c>
-      <c r="Q51" s="7"/>
+      <c r="N51" s="45">
+        <v>3</v>
+      </c>
+      <c r="O51" s="45">
+        <v>3</v>
+      </c>
+      <c r="Q51" s="8"/>
     </row>
     <row r="52" customFormat="1" ht="16.5" spans="1:17">
       <c r="A52" s="5" t="str">
-        <f>B52&amp;C52</f>
+        <f t="shared" si="2"/>
         <v>1034002</v>
       </c>
       <c r="B52" s="5">
@@ -4076,63 +4088,63 @@
       <c r="I52" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L52" s="45"/>
+      <c r="L52" s="46"/>
       <c r="M52" s="5"/>
-      <c r="N52" s="44">
-        <v>3</v>
-      </c>
-      <c r="O52" s="44">
-        <v>3</v>
-      </c>
-      <c r="P52" s="49"/>
-      <c r="Q52" s="7"/>
-    </row>
-    <row r="53" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A53" s="5" t="str">
-        <f t="shared" ref="A53:A61" si="3">B53&amp;C53</f>
+      <c r="N52" s="45">
+        <v>3</v>
+      </c>
+      <c r="O52" s="45">
+        <v>3</v>
+      </c>
+      <c r="P52" s="50"/>
+      <c r="Q52" s="8"/>
+    </row>
+    <row r="53" s="6" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A53" s="51" t="str">
+        <f t="shared" si="2"/>
         <v>1035001</v>
       </c>
-      <c r="B53" s="5">
+      <c r="B53" s="51">
         <v>103500</v>
       </c>
-      <c r="C53" s="5">
-        <v>1</v>
-      </c>
-      <c r="D53" s="5" t="s">
+      <c r="C53" s="51">
+        <v>1</v>
+      </c>
+      <c r="D53" s="51" t="s">
         <v>110</v>
       </c>
-      <c r="E53" s="5" t="s">
+      <c r="E53" s="51" t="s">
         <v>111</v>
       </c>
-      <c r="F53" s="5">
-        <v>1</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H53" s="5">
+      <c r="F53" s="51">
+        <v>1</v>
+      </c>
+      <c r="G53" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="H53" s="51">
         <v>2035001</v>
       </c>
-      <c r="I53" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L53" s="45" t="s">
+      <c r="I53" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="L53" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="M53" s="5" t="s">
+      <c r="M53" s="51" t="s">
         <v>113</v>
       </c>
-      <c r="N53" s="44">
+      <c r="N53" s="53">
         <v>4</v>
       </c>
-      <c r="O53" s="44">
-        <v>3</v>
-      </c>
-      <c r="Q53" s="7"/>
+      <c r="O53" s="53">
+        <v>3</v>
+      </c>
+      <c r="Q53" s="54"/>
     </row>
     <row r="54" customFormat="1" ht="16.5" spans="1:17">
       <c r="A54" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="A53:A61" si="3">B54&amp;C54</f>
         <v>1035002</v>
       </c>
       <c r="B54" s="5">
@@ -4159,19 +4171,19 @@
       <c r="I54" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L54" s="45" t="s">
+      <c r="L54" s="46" t="s">
         <v>115</v>
       </c>
       <c r="M54" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="N54" s="44">
+      <c r="N54" s="45">
         <v>4</v>
       </c>
-      <c r="O54" s="44">
-        <v>3</v>
-      </c>
-      <c r="Q54" s="7"/>
+      <c r="O54" s="45">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="8"/>
     </row>
     <row r="55" customFormat="1" ht="16.5" spans="1:17">
       <c r="A55" s="5" t="str">
@@ -4202,23 +4214,22 @@
       <c r="I55" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L55" s="45" t="s">
+      <c r="L55" s="46" t="s">
         <v>117</v>
       </c>
       <c r="M55" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="N55" s="44">
+      <c r="N55" s="45">
         <v>4</v>
       </c>
-      <c r="O55" s="44">
-        <v>3</v>
-      </c>
-      <c r="Q55" s="7"/>
+      <c r="O55" s="45">
+        <v>3</v>
+      </c>
+      <c r="Q55" s="8"/>
     </row>
     <row r="56" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A56" s="5" t="str">
-        <f t="shared" si="3"/>
+      <c r="A56" s="55">
         <v>1035011</v>
       </c>
       <c r="B56" s="5">
@@ -4245,19 +4256,19 @@
       <c r="I56" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L56" s="45" t="s">
+      <c r="L56" s="46" t="s">
         <v>120</v>
       </c>
       <c r="M56" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="N56" s="44">
+      <c r="N56" s="45">
         <v>4</v>
       </c>
-      <c r="O56" s="44">
-        <v>3</v>
-      </c>
-      <c r="Q56" s="7"/>
+      <c r="O56" s="45">
+        <v>3</v>
+      </c>
+      <c r="Q56" s="8"/>
     </row>
     <row r="57" customFormat="1" ht="16.5" spans="1:17">
       <c r="A57" s="5" t="str">
@@ -4288,19 +4299,19 @@
       <c r="I57" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L57" s="45" t="s">
+      <c r="L57" s="46" t="s">
         <v>121</v>
       </c>
       <c r="M57" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="N57" s="44">
+      <c r="N57" s="45">
         <v>4</v>
       </c>
-      <c r="O57" s="44">
-        <v>3</v>
-      </c>
-      <c r="Q57" s="7"/>
+      <c r="O57" s="45">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="8"/>
     </row>
     <row r="58" customFormat="1" ht="16.5" spans="1:17">
       <c r="A58" s="5" t="str">
@@ -4331,19 +4342,19 @@
       <c r="I58" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L58" s="45" t="s">
+      <c r="L58" s="46" t="s">
         <v>122</v>
       </c>
       <c r="M58" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="N58" s="44">
+      <c r="N58" s="45">
         <v>4</v>
       </c>
-      <c r="O58" s="44">
-        <v>3</v>
-      </c>
-      <c r="Q58" s="7"/>
+      <c r="O58" s="45">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="8"/>
     </row>
     <row r="59" customFormat="1" ht="16.5" spans="1:17">
       <c r="A59" s="5" t="str">
@@ -4374,19 +4385,19 @@
       <c r="I59" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L59" s="45" t="s">
+      <c r="L59" s="46" t="s">
         <v>124</v>
       </c>
       <c r="M59" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="N59" s="44">
-        <v>3</v>
-      </c>
-      <c r="O59" s="44">
-        <v>3</v>
-      </c>
-      <c r="Q59" s="7"/>
+      <c r="N59" s="45">
+        <v>3</v>
+      </c>
+      <c r="O59" s="45">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="8"/>
     </row>
     <row r="60" customFormat="1" ht="16.5" spans="1:17">
       <c r="A60" s="5" t="str">
@@ -4417,19 +4428,19 @@
       <c r="I60" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L60" s="45">
+      <c r="L60" s="46">
         <v>10360004</v>
       </c>
       <c r="M60" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="N60" s="44">
-        <v>3</v>
-      </c>
-      <c r="O60" s="44">
-        <v>3</v>
-      </c>
-      <c r="Q60" s="7"/>
+      <c r="N60" s="45">
+        <v>3</v>
+      </c>
+      <c r="O60" s="45">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="8"/>
     </row>
     <row r="61" customFormat="1" ht="16.5" spans="1:17">
       <c r="A61" s="5" t="str">
@@ -4460,19 +4471,19 @@
       <c r="I61" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L61" s="45">
+      <c r="L61" s="46">
         <v>10360002</v>
       </c>
       <c r="M61" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="N61" s="44">
-        <v>3</v>
-      </c>
-      <c r="O61" s="44">
-        <v>3</v>
-      </c>
-      <c r="Q61" s="7"/>
+      <c r="N61" s="45">
+        <v>3</v>
+      </c>
+      <c r="O61" s="45">
+        <v>3</v>
+      </c>
+      <c r="Q61" s="8"/>
     </row>
     <row r="62" customFormat="1" ht="16.5" spans="1:17">
       <c r="A62" s="5"/>
@@ -4484,11 +4495,11 @@
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
       <c r="I62" s="5"/>
-      <c r="L62" s="45"/>
+      <c r="L62" s="46"/>
       <c r="M62" s="5"/>
-      <c r="N62" s="44"/>
-      <c r="O62" s="44"/>
-      <c r="Q62" s="7"/>
+      <c r="N62" s="45"/>
+      <c r="O62" s="45"/>
+      <c r="Q62" s="8"/>
     </row>
     <row r="63" customFormat="1" ht="16.5" spans="1:17">
       <c r="A63" s="5"/>
@@ -4500,11 +4511,11 @@
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
       <c r="I63" s="5"/>
-      <c r="L63" s="45"/>
+      <c r="L63" s="46"/>
       <c r="M63" s="5"/>
-      <c r="N63" s="44"/>
-      <c r="O63" s="44"/>
-      <c r="Q63" s="7"/>
+      <c r="N63" s="45"/>
+      <c r="O63" s="45"/>
+      <c r="Q63" s="8"/>
     </row>
     <row r="64" customFormat="1" ht="16.5" spans="1:17">
       <c r="A64" s="5"/>
@@ -4516,11 +4527,11 @@
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
       <c r="I64" s="5"/>
-      <c r="L64" s="45"/>
+      <c r="L64" s="46"/>
       <c r="M64" s="5"/>
-      <c r="N64" s="44"/>
-      <c r="O64" s="44"/>
-      <c r="Q64" s="7"/>
+      <c r="N64" s="45"/>
+      <c r="O64" s="45"/>
+      <c r="Q64" s="8"/>
     </row>
     <row r="65" customFormat="1" ht="16.5" spans="1:17">
       <c r="A65" s="5"/>
@@ -4532,11 +4543,11 @@
       <c r="G65" s="5"/>
       <c r="H65" s="5"/>
       <c r="I65" s="5"/>
-      <c r="L65" s="45"/>
+      <c r="L65" s="46"/>
       <c r="M65" s="5"/>
-      <c r="N65" s="44"/>
-      <c r="O65" s="44"/>
-      <c r="Q65" s="7"/>
+      <c r="N65" s="45"/>
+      <c r="O65" s="45"/>
+      <c r="Q65" s="8"/>
     </row>
     <row r="66" customFormat="1" ht="16.5" spans="1:17">
       <c r="A66" s="5"/>
@@ -4548,11 +4559,11 @@
       <c r="G66" s="5"/>
       <c r="H66" s="5"/>
       <c r="I66" s="5"/>
-      <c r="L66" s="45"/>
+      <c r="L66" s="46"/>
       <c r="M66" s="5"/>
-      <c r="N66" s="44"/>
-      <c r="O66" s="44"/>
-      <c r="Q66" s="7"/>
+      <c r="N66" s="45"/>
+      <c r="O66" s="45"/>
+      <c r="Q66" s="8"/>
     </row>
     <row r="67" customFormat="1" ht="16.5" spans="1:17">
       <c r="A67" s="5"/>
@@ -4564,11 +4575,11 @@
       <c r="G67" s="5"/>
       <c r="H67" s="5"/>
       <c r="I67" s="5"/>
-      <c r="L67" s="45"/>
+      <c r="L67" s="46"/>
       <c r="M67" s="5"/>
-      <c r="N67" s="44"/>
-      <c r="O67" s="44"/>
-      <c r="Q67" s="7"/>
+      <c r="N67" s="45"/>
+      <c r="O67" s="45"/>
+      <c r="Q67" s="8"/>
     </row>
     <row r="68" customFormat="1" ht="16.5" spans="1:17">
       <c r="A68" s="5"/>
@@ -4580,11 +4591,11 @@
       <c r="G68" s="5"/>
       <c r="H68" s="5"/>
       <c r="I68" s="5"/>
-      <c r="L68" s="45"/>
+      <c r="L68" s="46"/>
       <c r="M68" s="5"/>
-      <c r="N68" s="44"/>
-      <c r="O68" s="44"/>
-      <c r="Q68" s="7"/>
+      <c r="N68" s="45"/>
+      <c r="O68" s="45"/>
+      <c r="Q68" s="8"/>
     </row>
     <row r="69" customFormat="1" ht="16.5" spans="1:17">
       <c r="A69" s="5"/>
@@ -4596,11 +4607,11 @@
       <c r="G69" s="5"/>
       <c r="H69" s="5"/>
       <c r="I69" s="5"/>
-      <c r="L69" s="45"/>
+      <c r="L69" s="46"/>
       <c r="M69" s="5"/>
-      <c r="N69" s="44"/>
-      <c r="O69" s="44"/>
-      <c r="Q69" s="7"/>
+      <c r="N69" s="45"/>
+      <c r="O69" s="45"/>
+      <c r="Q69" s="8"/>
     </row>
     <row r="70" customFormat="1" ht="16.5" spans="1:17">
       <c r="A70" s="5"/>
@@ -4612,11 +4623,11 @@
       <c r="G70" s="5"/>
       <c r="H70" s="5"/>
       <c r="I70" s="5"/>
-      <c r="L70" s="45"/>
+      <c r="L70" s="46"/>
       <c r="M70" s="5"/>
-      <c r="N70" s="44"/>
-      <c r="O70" s="44"/>
-      <c r="Q70" s="7"/>
+      <c r="N70" s="45"/>
+      <c r="O70" s="45"/>
+      <c r="Q70" s="8"/>
     </row>
     <row r="71" customFormat="1" ht="16.5" spans="1:17">
       <c r="A71" s="5"/>
@@ -4628,11 +4639,11 @@
       <c r="G71" s="5"/>
       <c r="H71" s="5"/>
       <c r="I71" s="5"/>
-      <c r="L71" s="45"/>
+      <c r="L71" s="46"/>
       <c r="M71" s="5"/>
-      <c r="N71" s="44"/>
-      <c r="O71" s="44"/>
-      <c r="Q71" s="7"/>
+      <c r="N71" s="45"/>
+      <c r="O71" s="45"/>
+      <c r="Q71" s="8"/>
     </row>
     <row r="72" customFormat="1" ht="16.5" spans="1:17">
       <c r="A72" s="5"/>
@@ -4644,11 +4655,11 @@
       <c r="G72" s="5"/>
       <c r="H72" s="5"/>
       <c r="I72" s="5"/>
-      <c r="L72" s="45"/>
+      <c r="L72" s="46"/>
       <c r="M72" s="5"/>
-      <c r="N72" s="44"/>
-      <c r="O72" s="44"/>
-      <c r="Q72" s="7"/>
+      <c r="N72" s="45"/>
+      <c r="O72" s="45"/>
+      <c r="Q72" s="8"/>
     </row>
     <row r="73" customFormat="1" ht="16.5" spans="1:17">
       <c r="A73" s="5"/>
@@ -4660,11 +4671,11 @@
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
       <c r="I73" s="5"/>
-      <c r="L73" s="45"/>
+      <c r="L73" s="46"/>
       <c r="M73" s="5"/>
-      <c r="N73" s="44"/>
-      <c r="O73" s="44"/>
-      <c r="Q73" s="7"/>
+      <c r="N73" s="45"/>
+      <c r="O73" s="45"/>
+      <c r="Q73" s="8"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:K2">

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="146">
   <si>
     <t>id</t>
   </si>
@@ -510,6 +510,60 @@
   </si>
   <si>
     <t>必出现3个Jackpot符号</t>
+  </si>
+  <si>
+    <t>王牌dj</t>
+  </si>
+  <si>
+    <t>10280001|10280003|10280006|10280007|10280008</t>
+  </si>
+  <si>
+    <t>概率出现wild+概率改出2个SCATTER+概率改出占据2、3、4个格子符号</t>
+  </si>
+  <si>
+    <t>免费游戏-触发局</t>
+  </si>
+  <si>
+    <t>10280004|10280009</t>
+  </si>
+  <si>
+    <t>虎虎生财</t>
+  </si>
+  <si>
+    <t>福虎模式</t>
+  </si>
+  <si>
+    <t>l宙斯vs哈迪斯</t>
+  </si>
+  <si>
+    <t>10200001|10200002|10200003|10200004|10200005|10200006|10200007</t>
+  </si>
+  <si>
+    <t>概率出现wild+概率在1234轴上改出v1234+概率第1轴改出1个scatter+概率第3轴改出1个scatter</t>
+  </si>
+  <si>
+    <t>10200008|10200009|10200010</t>
+  </si>
+  <si>
+    <t>第1轴改出1个scatter+第3轴改出1个scatter+第1轴改出5个scatter</t>
+  </si>
+  <si>
+    <t>10200006|10200007|10200011</t>
+  </si>
+  <si>
+    <t>第1轴改出1个scatter+第3轴改出1个scatter+第5轴改出奖池符号</t>
+  </si>
+  <si>
+    <t>宙斯模式</t>
+  </si>
+  <si>
+    <t>改出39符号，用于触发免费游戏宙斯</t>
+  </si>
+  <si>
+    <t>哈迪斯模式</t>
+  </si>
+  <si>
+    <t>改出40符号，用于触发免费游戏哈迪斯</t>
   </si>
 </sst>
 </file>
@@ -704,7 +758,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="44">
+  <fills count="45">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -726,6 +780,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -756,12 +822,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1109,7 +1169,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1133,16 +1193,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1151,110 +1211,111 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1263,24 +1324,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -1291,22 +1352,22 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1314,11 +1375,11 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1344,17 +1405,22 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1901,14 +1967,14 @@
     <col min="11" max="11" width="16.75" customWidth="1"/>
     <col min="12" max="12" width="53.25" customWidth="1"/>
     <col min="13" max="13" width="21.6083333333333" customWidth="1"/>
-    <col min="14" max="15" width="9" style="7"/>
+    <col min="14" max="15" width="9" style="8"/>
     <col min="16" max="16" width="15" customWidth="1"/>
-    <col min="17" max="17" width="23.75" style="8" customWidth="1"/>
+    <col min="17" max="17" width="23.75" style="9" customWidth="1"/>
     <col min="18" max="18" width="60.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:17">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
@@ -1919,34 +1985,34 @@
       </c>
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="11" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="5"/>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="11" t="s">
         <v>4</v>
       </c>
       <c r="I1" s="5"/>
-      <c r="J1" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="11"/>
-      <c r="L1" s="12" t="s">
+      <c r="J1" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="12"/>
+      <c r="L1" s="13" t="s">
         <v>6</v>
       </c>
       <c r="M1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="13" t="s">
+      <c r="N1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="O1" s="14" t="s">
         <v>9</v>
       </c>
       <c r="Q1"/>
     </row>
     <row r="2" ht="16.5" spans="1:17">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -1957,62 +2023,62 @@
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="11" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="5"/>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="11" t="s">
         <v>10</v>
       </c>
       <c r="I2" s="5"/>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="15"/>
-      <c r="L2" s="16" t="s">
+      <c r="K2" s="16"/>
+      <c r="L2" s="17" t="s">
         <v>12</v>
       </c>
       <c r="M2" s="5"/>
-      <c r="N2" s="17" t="s">
+      <c r="N2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="17" t="s">
+      <c r="O2" s="18" t="s">
         <v>10</v>
       </c>
       <c r="Q2"/>
     </row>
     <row r="3" ht="16.5" spans="1:17">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="19" t="s">
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="18"/>
-      <c r="H3" s="20" t="s">
+      <c r="G3" s="19"/>
+      <c r="H3" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="18"/>
-      <c r="J3" s="21" t="s">
+      <c r="I3" s="19"/>
+      <c r="J3" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="21"/>
-      <c r="L3" s="22" t="s">
+      <c r="K3" s="22"/>
+      <c r="L3" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="M3" s="18"/>
-      <c r="N3" s="17" t="s">
+      <c r="M3" s="19"/>
+      <c r="N3" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="17" t="s">
+      <c r="O3" s="18" t="s">
         <v>20</v>
       </c>
       <c r="Q3"/>
@@ -2022,1101 +2088,1101 @@
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="10"/>
+      <c r="F4" s="11"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="10"/>
+      <c r="H4" s="11"/>
       <c r="I4" s="5"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="12"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="13"/>
       <c r="M4" s="5"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="18"/>
       <c r="Q4"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A5" s="24" t="str">
+      <c r="A5" s="25" t="str">
         <f t="shared" ref="A5:A15" si="0">B5&amp;C5</f>
         <v>1001001</v>
       </c>
-      <c r="B5" s="25">
+      <c r="B5" s="26">
         <v>100100</v>
       </c>
-      <c r="C5" s="25">
-        <v>1</v>
-      </c>
-      <c r="D5" s="25" t="s">
+      <c r="C5" s="26">
+        <v>1</v>
+      </c>
+      <c r="D5" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="25">
-        <v>1</v>
-      </c>
-      <c r="G5" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="24">
+      <c r="F5" s="26">
+        <v>1</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="25">
         <v>2001001</v>
       </c>
-      <c r="I5" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="24"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="27" t="s">
+      <c r="I5" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="M5" s="24" t="s">
+      <c r="M5" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="N5" s="17">
+      <c r="N5" s="18">
         <v>4</v>
       </c>
-      <c r="O5" s="17">
+      <c r="O5" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A6" s="24" t="str">
+      <c r="A6" s="25" t="str">
         <f t="shared" si="0"/>
         <v>1001002</v>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="26">
         <v>100100</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="26">
         <v>2</v>
       </c>
-      <c r="D6" s="25"/>
-      <c r="E6" s="28" t="s">
+      <c r="D6" s="26"/>
+      <c r="E6" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="25">
-        <v>1</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="24">
+      <c r="F6" s="26">
+        <v>1</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="25">
         <v>2001001</v>
       </c>
-      <c r="I6" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="29" t="s">
+      <c r="I6" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="M6" s="24" t="s">
+      <c r="M6" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="N6" s="17">
+      <c r="N6" s="18">
         <v>4</v>
       </c>
-      <c r="O6" s="17">
+      <c r="O6" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A7" s="24" t="str">
+      <c r="A7" s="25" t="str">
         <f t="shared" si="0"/>
         <v>1001003</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="26">
         <v>100100</v>
       </c>
-      <c r="C7" s="25">
-        <v>3</v>
-      </c>
-      <c r="D7" s="25"/>
-      <c r="E7" s="30" t="s">
+      <c r="C7" s="26">
+        <v>3</v>
+      </c>
+      <c r="D7" s="26"/>
+      <c r="E7" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="25">
-        <v>1</v>
-      </c>
-      <c r="G7" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="24">
+      <c r="F7" s="26">
+        <v>1</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="25">
         <v>2001001</v>
       </c>
-      <c r="I7" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="27" t="s">
+      <c r="I7" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="M7" s="24" t="s">
+      <c r="M7" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="N7" s="17">
+      <c r="N7" s="18">
         <v>4</v>
       </c>
-      <c r="O7" s="17">
+      <c r="O7" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A8" s="24" t="str">
+      <c r="A8" s="25" t="str">
         <f t="shared" si="0"/>
         <v>1001004</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="26">
         <v>100100</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="26">
         <v>4</v>
       </c>
-      <c r="D8" s="25"/>
-      <c r="E8" s="31" t="s">
+      <c r="D8" s="26"/>
+      <c r="E8" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="32">
-        <v>1</v>
-      </c>
-      <c r="G8" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="24">
+      <c r="F8" s="33">
+        <v>1</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="25">
         <v>2001001</v>
       </c>
-      <c r="I8" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" s="24"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="27">
+      <c r="I8" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="28">
         <v>10010041</v>
       </c>
-      <c r="M8" s="24" t="s">
+      <c r="M8" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="N8" s="17">
+      <c r="N8" s="18">
         <v>4</v>
       </c>
-      <c r="O8" s="17">
+      <c r="O8" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A9" s="24" t="str">
+      <c r="A9" s="25" t="str">
         <f t="shared" si="0"/>
         <v>1001005</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="26">
         <v>100100</v>
       </c>
-      <c r="C9" s="25">
-        <v>5</v>
-      </c>
-      <c r="D9" s="25"/>
-      <c r="E9" s="33" t="s">
+      <c r="C9" s="26">
+        <v>5</v>
+      </c>
+      <c r="D9" s="26"/>
+      <c r="E9" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="32">
-        <v>1</v>
-      </c>
-      <c r="G9" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="24">
+      <c r="F9" s="33">
+        <v>1</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="25">
         <v>2001001</v>
       </c>
-      <c r="I9" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" s="24"/>
-      <c r="K9" s="24"/>
-      <c r="L9" s="27" t="s">
+      <c r="I9" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="M9" s="24" t="s">
+      <c r="M9" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N9" s="17">
+      <c r="N9" s="18">
         <v>4</v>
       </c>
-      <c r="O9" s="17">
+      <c r="O9" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A10" s="24" t="str">
+      <c r="A10" s="25" t="str">
         <f t="shared" si="0"/>
         <v>1001006</v>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="26">
         <v>100100</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="26">
         <v>6</v>
       </c>
-      <c r="D10" s="25"/>
-      <c r="E10" s="33" t="s">
+      <c r="D10" s="26"/>
+      <c r="E10" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="32">
-        <v>1</v>
-      </c>
-      <c r="G10" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="24">
+      <c r="F10" s="33">
+        <v>1</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="25">
         <v>2001001</v>
       </c>
-      <c r="I10" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="27">
+      <c r="I10" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="28">
         <v>10010061</v>
       </c>
-      <c r="M10" s="24" t="s">
+      <c r="M10" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="N10" s="17">
+      <c r="N10" s="18">
         <v>4</v>
       </c>
-      <c r="O10" s="17">
+      <c r="O10" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A11" s="24" t="str">
+      <c r="A11" s="25" t="str">
         <f t="shared" si="0"/>
         <v>1001007</v>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="26">
         <v>100100</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="26">
         <v>7</v>
       </c>
-      <c r="D11" s="25"/>
-      <c r="E11" s="28" t="s">
+      <c r="D11" s="26"/>
+      <c r="E11" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="25">
-        <v>1</v>
-      </c>
-      <c r="G11" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" s="24">
+      <c r="F11" s="26">
+        <v>1</v>
+      </c>
+      <c r="G11" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="25">
         <v>2001001</v>
       </c>
-      <c r="I11" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="J11" s="24"/>
-      <c r="K11" s="24"/>
-      <c r="L11" s="29" t="s">
+      <c r="I11" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="M11" s="24" t="s">
+      <c r="M11" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="N11" s="17">
+      <c r="N11" s="18">
         <v>4</v>
       </c>
-      <c r="O11" s="17">
+      <c r="O11" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A12" s="34" t="str">
+      <c r="A12" s="35" t="str">
         <f t="shared" si="0"/>
         <v>1003001</v>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="27">
         <v>100300</v>
       </c>
-      <c r="C12" s="26">
-        <v>1</v>
-      </c>
-      <c r="D12" s="26" t="s">
+      <c r="C12" s="27">
+        <v>1</v>
+      </c>
+      <c r="D12" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="26" t="s">
+      <c r="E12" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="26">
-        <v>1</v>
-      </c>
-      <c r="G12" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="H12" s="34">
+      <c r="F12" s="27">
+        <v>1</v>
+      </c>
+      <c r="G12" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="35">
         <v>2003001</v>
       </c>
-      <c r="I12" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" s="34"/>
-      <c r="K12" s="34"/>
-      <c r="L12" s="35">
+      <c r="I12" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" s="35"/>
+      <c r="K12" s="35"/>
+      <c r="L12" s="36">
         <v>10030022</v>
       </c>
-      <c r="M12" s="34" t="s">
+      <c r="M12" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="N12" s="26">
-        <v>3</v>
-      </c>
-      <c r="O12" s="26">
-        <v>3</v>
-      </c>
-      <c r="Q12" s="36"/>
+      <c r="N12" s="27">
+        <v>3</v>
+      </c>
+      <c r="O12" s="27">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="37"/>
     </row>
     <row r="13" s="2" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A13" s="34" t="str">
+      <c r="A13" s="35" t="str">
         <f t="shared" ref="A13:A30" si="1">B13&amp;C13</f>
         <v>1003002</v>
       </c>
-      <c r="B13" s="26">
+      <c r="B13" s="27">
         <v>100300</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="27">
         <v>2</v>
       </c>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26" t="s">
+      <c r="D13" s="27"/>
+      <c r="E13" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="26">
-        <v>1</v>
-      </c>
-      <c r="G13" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="H13" s="34">
+      <c r="F13" s="27">
+        <v>1</v>
+      </c>
+      <c r="G13" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="35">
         <v>2003001</v>
       </c>
-      <c r="I13" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="J13" s="34"/>
-      <c r="K13" s="34"/>
-      <c r="L13" s="35" t="s">
+      <c r="I13" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" s="35"/>
+      <c r="K13" s="35"/>
+      <c r="L13" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="M13" s="34" t="s">
+      <c r="M13" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="N13" s="26">
-        <v>3</v>
-      </c>
-      <c r="O13" s="26">
-        <v>3</v>
-      </c>
-      <c r="Q13" s="36"/>
+      <c r="N13" s="27">
+        <v>3</v>
+      </c>
+      <c r="O13" s="27">
+        <v>3</v>
+      </c>
+      <c r="Q13" s="37"/>
     </row>
     <row r="14" s="2" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A14" s="34" t="str">
+      <c r="A14" s="35" t="str">
         <f t="shared" si="1"/>
         <v>1003003</v>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="27">
         <v>100300</v>
       </c>
-      <c r="C14" s="26">
-        <v>3</v>
-      </c>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26" t="s">
+      <c r="C14" s="27">
+        <v>3</v>
+      </c>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="26">
-        <v>1</v>
-      </c>
-      <c r="G14" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="H14" s="34">
+      <c r="F14" s="27">
+        <v>1</v>
+      </c>
+      <c r="G14" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="35">
         <v>2003002</v>
       </c>
-      <c r="I14" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="J14" s="34" t="s">
+      <c r="I14" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="K14" s="34" t="s">
+      <c r="K14" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="L14" s="35" t="s">
+      <c r="L14" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="M14" s="34" t="s">
+      <c r="M14" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="N14" s="26">
-        <v>3</v>
-      </c>
-      <c r="O14" s="26">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="36"/>
+      <c r="N14" s="27">
+        <v>3</v>
+      </c>
+      <c r="O14" s="27">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="37"/>
     </row>
     <row r="15" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A15" s="37" t="str">
+      <c r="A15" s="38" t="str">
         <f t="shared" si="1"/>
         <v>1007001</v>
       </c>
-      <c r="B15" s="38">
+      <c r="B15" s="39">
         <v>100700</v>
       </c>
-      <c r="C15" s="38">
-        <v>1</v>
-      </c>
-      <c r="D15" s="38" t="s">
+      <c r="C15" s="39">
+        <v>1</v>
+      </c>
+      <c r="D15" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="38" t="s">
+      <c r="E15" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="38">
-        <v>1</v>
-      </c>
-      <c r="G15" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="H15" s="37">
+      <c r="F15" s="39">
+        <v>1</v>
+      </c>
+      <c r="G15" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="38">
         <v>2007001</v>
       </c>
-      <c r="I15" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="J15" s="37"/>
-      <c r="K15" s="37"/>
-      <c r="L15" s="39" t="s">
+      <c r="I15" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" s="38"/>
+      <c r="K15" s="38"/>
+      <c r="L15" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="M15" s="37" t="s">
+      <c r="M15" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="N15" s="17">
+      <c r="N15" s="18">
         <v>4</v>
       </c>
-      <c r="O15" s="17">
+      <c r="O15" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="16" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A16" s="37" t="str">
+      <c r="A16" s="38" t="str">
         <f t="shared" si="1"/>
         <v>1007002</v>
       </c>
-      <c r="B16" s="38">
+      <c r="B16" s="39">
         <v>100700</v>
       </c>
-      <c r="C16" s="38">
+      <c r="C16" s="39">
         <v>2</v>
       </c>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38" t="s">
+      <c r="D16" s="39"/>
+      <c r="E16" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="38">
-        <v>1</v>
-      </c>
-      <c r="G16" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="H16" s="37">
+      <c r="F16" s="39">
+        <v>1</v>
+      </c>
+      <c r="G16" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="38">
         <v>2007001</v>
       </c>
-      <c r="I16" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="J16" s="37"/>
-      <c r="K16" s="37"/>
-      <c r="L16" s="39" t="s">
+      <c r="I16" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="J16" s="38"/>
+      <c r="K16" s="38"/>
+      <c r="L16" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="M16" s="37" t="s">
+      <c r="M16" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="N16" s="17">
+      <c r="N16" s="18">
         <v>4</v>
       </c>
-      <c r="O16" s="17">
+      <c r="O16" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="17" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A17" s="40" t="str">
+      <c r="A17" s="41" t="str">
         <f t="shared" si="1"/>
         <v>1012001</v>
       </c>
-      <c r="B17" s="41">
+      <c r="B17" s="42">
         <v>101200</v>
       </c>
-      <c r="C17" s="41">
-        <v>1</v>
-      </c>
-      <c r="D17" s="41" t="s">
+      <c r="C17" s="42">
+        <v>1</v>
+      </c>
+      <c r="D17" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="E17" s="41" t="s">
+      <c r="E17" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="41">
-        <v>1</v>
-      </c>
-      <c r="G17" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="H17" s="40">
+      <c r="F17" s="42">
+        <v>1</v>
+      </c>
+      <c r="G17" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="41">
         <v>2012001</v>
       </c>
-      <c r="I17" s="40" t="s">
-        <v>24</v>
-      </c>
-      <c r="J17" s="40"/>
-      <c r="K17" s="40"/>
-      <c r="L17" s="42">
+      <c r="I17" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="J17" s="41"/>
+      <c r="K17" s="41"/>
+      <c r="L17" s="43">
         <v>10120011</v>
       </c>
-      <c r="M17" s="40" t="s">
+      <c r="M17" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="N17" s="41">
-        <v>3</v>
-      </c>
-      <c r="O17" s="41">
-        <v>5</v>
-      </c>
-      <c r="Q17" s="43"/>
+      <c r="N17" s="42">
+        <v>3</v>
+      </c>
+      <c r="O17" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="44"/>
     </row>
     <row r="18" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A18" s="40" t="str">
+      <c r="A18" s="41" t="str">
         <f t="shared" si="1"/>
         <v>1012002</v>
       </c>
-      <c r="B18" s="41">
+      <c r="B18" s="42">
         <v>101200</v>
       </c>
-      <c r="C18" s="41">
+      <c r="C18" s="42">
         <v>2</v>
       </c>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41" t="s">
+      <c r="D18" s="42"/>
+      <c r="E18" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="41">
-        <v>1</v>
-      </c>
-      <c r="G18" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="H18" s="40">
+      <c r="F18" s="42">
+        <v>1</v>
+      </c>
+      <c r="G18" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="41">
         <v>2012001</v>
       </c>
-      <c r="I18" s="40" t="s">
-        <v>24</v>
-      </c>
-      <c r="J18" s="40"/>
-      <c r="K18" s="40"/>
-      <c r="L18" s="42">
+      <c r="I18" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="J18" s="41"/>
+      <c r="K18" s="41"/>
+      <c r="L18" s="43">
         <v>10120021</v>
       </c>
-      <c r="M18" s="40" t="s">
+      <c r="M18" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="N18" s="41">
-        <v>3</v>
-      </c>
-      <c r="O18" s="41">
-        <v>5</v>
-      </c>
-      <c r="Q18" s="43"/>
+      <c r="N18" s="42">
+        <v>3</v>
+      </c>
+      <c r="O18" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="44"/>
     </row>
     <row r="19" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A19" s="40" t="str">
+      <c r="A19" s="41" t="str">
         <f t="shared" si="1"/>
         <v>1012003</v>
       </c>
-      <c r="B19" s="41">
+      <c r="B19" s="42">
         <v>101200</v>
       </c>
-      <c r="C19" s="41">
-        <v>3</v>
-      </c>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41" t="s">
+      <c r="C19" s="42">
+        <v>3</v>
+      </c>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="F19" s="41">
-        <v>1</v>
-      </c>
-      <c r="G19" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="H19" s="40">
+      <c r="F19" s="42">
+        <v>1</v>
+      </c>
+      <c r="G19" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="41">
         <v>2012001</v>
       </c>
-      <c r="I19" s="40" t="s">
-        <v>24</v>
-      </c>
-      <c r="J19" s="40" t="s">
+      <c r="I19" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="J19" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="K19" s="40" t="s">
+      <c r="K19" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="L19" s="42"/>
-      <c r="M19" s="40" t="s">
+      <c r="L19" s="43"/>
+      <c r="M19" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="N19" s="41">
-        <v>3</v>
-      </c>
-      <c r="O19" s="41">
-        <v>5</v>
-      </c>
-      <c r="Q19" s="43"/>
+      <c r="N19" s="42">
+        <v>3</v>
+      </c>
+      <c r="O19" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q19" s="44"/>
     </row>
     <row r="20" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A20" s="34" t="str">
+      <c r="A20" s="35" t="str">
         <f t="shared" si="1"/>
         <v>1014001</v>
       </c>
-      <c r="B20" s="26">
+      <c r="B20" s="27">
         <v>101400</v>
       </c>
-      <c r="C20" s="26">
-        <v>1</v>
-      </c>
-      <c r="D20" s="26" t="s">
+      <c r="C20" s="27">
+        <v>1</v>
+      </c>
+      <c r="D20" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="E20" s="26" t="s">
+      <c r="E20" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="F20" s="26">
-        <v>1</v>
-      </c>
-      <c r="G20" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="H20" s="34">
+      <c r="F20" s="27">
+        <v>1</v>
+      </c>
+      <c r="G20" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="35">
         <v>2014001</v>
       </c>
-      <c r="I20" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="J20" s="34"/>
-      <c r="K20" s="34"/>
-      <c r="L20" s="35" t="s">
+      <c r="I20" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="J20" s="35"/>
+      <c r="K20" s="35"/>
+      <c r="L20" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="M20" s="34" t="s">
+      <c r="M20" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="N20" s="17">
+      <c r="N20" s="18">
         <v>4</v>
       </c>
-      <c r="O20" s="17">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="44"/>
+      <c r="O20" s="18">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="45"/>
     </row>
     <row r="21" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A21" s="34" t="str">
+      <c r="A21" s="35" t="str">
         <f t="shared" si="1"/>
         <v>1014002</v>
       </c>
-      <c r="B21" s="26">
+      <c r="B21" s="27">
         <v>101400</v>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="27">
         <v>2</v>
       </c>
-      <c r="D21" s="26" t="s">
+      <c r="D21" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="E21" s="26" t="s">
+      <c r="E21" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="26">
-        <v>1</v>
-      </c>
-      <c r="G21" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="H21" s="34">
+      <c r="F21" s="27">
+        <v>1</v>
+      </c>
+      <c r="G21" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="35">
         <v>2014001</v>
       </c>
-      <c r="I21" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="J21" s="34"/>
-      <c r="K21" s="34"/>
-      <c r="L21" s="35" t="s">
+      <c r="I21" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="J21" s="35"/>
+      <c r="K21" s="35"/>
+      <c r="L21" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="M21" s="34" t="s">
+      <c r="M21" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="N21" s="17">
+      <c r="N21" s="18">
         <v>4</v>
       </c>
-      <c r="O21" s="17">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="44"/>
+      <c r="O21" s="18">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="45"/>
     </row>
     <row r="22" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A22" s="34" t="str">
+      <c r="A22" s="35" t="str">
         <f t="shared" si="1"/>
         <v>1014003</v>
       </c>
-      <c r="B22" s="26">
+      <c r="B22" s="27">
         <v>101400</v>
       </c>
-      <c r="C22" s="26">
-        <v>3</v>
-      </c>
-      <c r="D22" s="26" t="s">
+      <c r="C22" s="27">
+        <v>3</v>
+      </c>
+      <c r="D22" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="E22" s="26" t="s">
+      <c r="E22" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="F22" s="26">
-        <v>1</v>
-      </c>
-      <c r="G22" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="H22" s="34">
+      <c r="F22" s="27">
+        <v>1</v>
+      </c>
+      <c r="G22" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="35">
         <v>2014001</v>
       </c>
-      <c r="I22" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="J22" s="34"/>
-      <c r="K22" s="34"/>
-      <c r="L22" s="35">
+      <c r="I22" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="36">
         <v>10140021</v>
       </c>
-      <c r="M22" s="34" t="s">
+      <c r="M22" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="N22" s="17">
+      <c r="N22" s="18">
         <v>4</v>
       </c>
-      <c r="O22" s="17">
-        <v>3</v>
-      </c>
-      <c r="Q22" s="44"/>
+      <c r="O22" s="18">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="45"/>
     </row>
     <row r="23" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A23" s="24" t="str">
+      <c r="A23" s="25" t="str">
         <f t="shared" si="1"/>
         <v>1024001</v>
       </c>
-      <c r="B23" s="25">
+      <c r="B23" s="26">
         <v>102400</v>
       </c>
-      <c r="C23" s="25">
-        <v>1</v>
-      </c>
-      <c r="D23" s="25" t="s">
+      <c r="C23" s="26">
+        <v>1</v>
+      </c>
+      <c r="D23" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="E23" s="26" t="s">
+      <c r="E23" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="F23" s="25">
-        <v>1</v>
-      </c>
-      <c r="G23" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H23" s="24">
+      <c r="F23" s="26">
+        <v>1</v>
+      </c>
+      <c r="G23" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="25">
         <v>2024001</v>
       </c>
-      <c r="I23" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="27" t="s">
+      <c r="I23" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J23" s="25"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="M23" s="24" t="s">
+      <c r="M23" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="N23" s="17">
+      <c r="N23" s="18">
         <v>4</v>
       </c>
-      <c r="O23" s="17">
+      <c r="O23" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A24" s="24" t="str">
+      <c r="A24" s="25" t="str">
         <f t="shared" si="1"/>
         <v>1024002</v>
       </c>
-      <c r="B24" s="25">
+      <c r="B24" s="26">
         <v>102400</v>
       </c>
-      <c r="C24" s="25">
+      <c r="C24" s="26">
         <v>2</v>
       </c>
-      <c r="D24" s="25"/>
-      <c r="E24" s="28" t="s">
+      <c r="D24" s="26"/>
+      <c r="E24" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="25">
-        <v>1</v>
-      </c>
-      <c r="G24" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H24" s="24">
+      <c r="F24" s="26">
+        <v>1</v>
+      </c>
+      <c r="G24" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" s="25">
         <v>2024001</v>
       </c>
-      <c r="I24" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="J24" s="24"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="29" t="s">
+      <c r="I24" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="M24" s="24" t="s">
+      <c r="M24" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="N24" s="17">
+      <c r="N24" s="18">
         <v>4</v>
       </c>
-      <c r="O24" s="17">
+      <c r="O24" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A25" s="24" t="str">
+      <c r="A25" s="25" t="str">
         <f t="shared" si="1"/>
         <v>1024003</v>
       </c>
-      <c r="B25" s="25">
+      <c r="B25" s="26">
         <v>102400</v>
       </c>
-      <c r="C25" s="25">
-        <v>3</v>
-      </c>
-      <c r="D25" s="25"/>
-      <c r="E25" s="30" t="s">
+      <c r="C25" s="26">
+        <v>3</v>
+      </c>
+      <c r="D25" s="26"/>
+      <c r="E25" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="F25" s="25">
-        <v>1</v>
-      </c>
-      <c r="G25" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H25" s="24">
+      <c r="F25" s="26">
+        <v>1</v>
+      </c>
+      <c r="G25" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="25">
         <v>2024001</v>
       </c>
-      <c r="I25" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="J25" s="24"/>
-      <c r="K25" s="24"/>
-      <c r="L25" s="27" t="s">
+      <c r="I25" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J25" s="25"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="M25" s="24" t="s">
+      <c r="M25" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="N25" s="17">
+      <c r="N25" s="18">
         <v>4</v>
       </c>
-      <c r="O25" s="17">
+      <c r="O25" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A26" s="24" t="str">
+      <c r="A26" s="25" t="str">
         <f t="shared" si="1"/>
         <v>1024004</v>
       </c>
-      <c r="B26" s="25">
+      <c r="B26" s="26">
         <v>102400</v>
       </c>
-      <c r="C26" s="25">
+      <c r="C26" s="26">
         <v>4</v>
       </c>
-      <c r="D26" s="25"/>
-      <c r="E26" s="31" t="s">
+      <c r="D26" s="26"/>
+      <c r="E26" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="F26" s="32">
-        <v>1</v>
-      </c>
-      <c r="G26" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H26" s="24">
+      <c r="F26" s="33">
+        <v>1</v>
+      </c>
+      <c r="G26" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="25">
         <v>2024001</v>
       </c>
-      <c r="I26" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="J26" s="24"/>
-      <c r="K26" s="24"/>
-      <c r="L26" s="27">
+      <c r="I26" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J26" s="25"/>
+      <c r="K26" s="25"/>
+      <c r="L26" s="28">
         <v>10240041</v>
       </c>
-      <c r="M26" s="24" t="s">
+      <c r="M26" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="N26" s="17">
+      <c r="N26" s="18">
         <v>4</v>
       </c>
-      <c r="O26" s="17">
+      <c r="O26" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A27" s="24" t="str">
+      <c r="A27" s="25" t="str">
         <f t="shared" si="1"/>
         <v>1024005</v>
       </c>
-      <c r="B27" s="25">
+      <c r="B27" s="26">
         <v>102400</v>
       </c>
-      <c r="C27" s="25">
-        <v>5</v>
-      </c>
-      <c r="D27" s="25"/>
-      <c r="E27" s="33" t="s">
+      <c r="C27" s="26">
+        <v>5</v>
+      </c>
+      <c r="D27" s="26"/>
+      <c r="E27" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="F27" s="32">
-        <v>1</v>
-      </c>
-      <c r="G27" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H27" s="24">
+      <c r="F27" s="33">
+        <v>1</v>
+      </c>
+      <c r="G27" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H27" s="25">
         <v>2024001</v>
       </c>
-      <c r="I27" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="J27" s="24"/>
-      <c r="K27" s="24"/>
-      <c r="L27" s="27" t="s">
+      <c r="I27" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J27" s="25"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="M27" s="24" t="s">
+      <c r="M27" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N27" s="17">
+      <c r="N27" s="18">
         <v>4</v>
       </c>
-      <c r="O27" s="17">
+      <c r="O27" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A28" s="24" t="str">
+      <c r="A28" s="25" t="str">
         <f t="shared" si="1"/>
         <v>1024006</v>
       </c>
-      <c r="B28" s="25">
+      <c r="B28" s="26">
         <v>102400</v>
       </c>
-      <c r="C28" s="25">
+      <c r="C28" s="26">
         <v>6</v>
       </c>
-      <c r="D28" s="25"/>
-      <c r="E28" s="33" t="s">
+      <c r="D28" s="26"/>
+      <c r="E28" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="F28" s="32">
-        <v>1</v>
-      </c>
-      <c r="G28" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H28" s="24">
+      <c r="F28" s="33">
+        <v>1</v>
+      </c>
+      <c r="G28" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28" s="25">
         <v>2024001</v>
       </c>
-      <c r="I28" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="J28" s="24"/>
-      <c r="K28" s="24"/>
-      <c r="L28" s="27">
+      <c r="I28" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J28" s="25"/>
+      <c r="K28" s="25"/>
+      <c r="L28" s="28">
         <v>10240061</v>
       </c>
-      <c r="M28" s="24" t="s">
+      <c r="M28" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="N28" s="17">
+      <c r="N28" s="18">
         <v>4</v>
       </c>
-      <c r="O28" s="17">
+      <c r="O28" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A29" s="24" t="str">
+      <c r="A29" s="25" t="str">
         <f t="shared" si="1"/>
         <v>1024007</v>
       </c>
-      <c r="B29" s="25">
+      <c r="B29" s="26">
         <v>102400</v>
       </c>
-      <c r="C29" s="25">
+      <c r="C29" s="26">
         <v>7</v>
       </c>
-      <c r="D29" s="25"/>
-      <c r="E29" s="28" t="s">
+      <c r="D29" s="26"/>
+      <c r="E29" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="F29" s="25">
-        <v>1</v>
-      </c>
-      <c r="G29" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H29" s="24">
+      <c r="F29" s="26">
+        <v>1</v>
+      </c>
+      <c r="G29" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H29" s="25">
         <v>2024001</v>
       </c>
-      <c r="I29" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="J29" s="24"/>
-      <c r="K29" s="24"/>
-      <c r="L29" s="29" t="s">
+      <c r="I29" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J29" s="25"/>
+      <c r="K29" s="25"/>
+      <c r="L29" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="M29" s="24" t="s">
+      <c r="M29" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="N29" s="17">
+      <c r="N29" s="18">
         <v>4</v>
       </c>
-      <c r="O29" s="17">
+      <c r="O29" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="30" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A30" s="24" t="str">
+      <c r="A30" s="25" t="str">
         <f t="shared" si="1"/>
         <v>1017001</v>
       </c>
@@ -3150,17 +3216,17 @@
       <c r="M30" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="N30" s="45">
+      <c r="N30" s="46">
         <v>4</v>
       </c>
-      <c r="O30" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q30" s="18"/>
+      <c r="O30" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q30" s="19"/>
     </row>
     <row r="31" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A31" s="24" t="str">
-        <f t="shared" ref="A31:A53" si="2">B31&amp;C31</f>
+      <c r="A31" s="25" t="str">
+        <f t="shared" ref="A31:A52" si="2">B31&amp;C31</f>
         <v>1017002</v>
       </c>
       <c r="B31" s="5">
@@ -3193,16 +3259,16 @@
       <c r="M31" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="N31" s="45">
+      <c r="N31" s="46">
         <v>4</v>
       </c>
-      <c r="O31" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q31" s="18"/>
+      <c r="O31" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q31" s="19"/>
     </row>
     <row r="32" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A32" s="24" t="str">
+      <c r="A32" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1017003</v>
       </c>
@@ -3236,16 +3302,16 @@
       <c r="M32" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N32" s="45">
+      <c r="N32" s="46">
         <v>4</v>
       </c>
-      <c r="O32" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q32" s="18"/>
+      <c r="O32" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="19"/>
     </row>
     <row r="33" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A33" s="24" t="str">
+      <c r="A33" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1022001</v>
       </c>
@@ -3273,22 +3339,22 @@
       <c r="I33" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L33" s="46" t="s">
+      <c r="L33" s="47" t="s">
         <v>85</v>
       </c>
       <c r="M33" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N33" s="45">
-        <v>3</v>
-      </c>
-      <c r="O33" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q33" s="18"/>
+      <c r="N33" s="46">
+        <v>3</v>
+      </c>
+      <c r="O33" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q33" s="19"/>
     </row>
     <row r="34" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A34" s="24" t="str">
+      <c r="A34" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1022002</v>
       </c>
@@ -3304,10 +3370,10 @@
       <c r="E34" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="F34" s="17">
-        <v>1</v>
-      </c>
-      <c r="G34" s="47" t="s">
+      <c r="F34" s="18">
+        <v>1</v>
+      </c>
+      <c r="G34" s="48" t="s">
         <v>23</v>
       </c>
       <c r="H34" s="5">
@@ -3316,22 +3382,22 @@
       <c r="I34" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L34" s="46">
+      <c r="L34" s="47">
         <v>10220033</v>
       </c>
       <c r="M34" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N34" s="45">
-        <v>3</v>
-      </c>
-      <c r="O34" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q34" s="18"/>
+      <c r="N34" s="46">
+        <v>3</v>
+      </c>
+      <c r="O34" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q34" s="19"/>
     </row>
     <row r="35" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A35" s="24" t="str">
+      <c r="A35" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1022003</v>
       </c>
@@ -3347,10 +3413,10 @@
       <c r="E35" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F35" s="47">
-        <v>1</v>
-      </c>
-      <c r="G35" s="47" t="s">
+      <c r="F35" s="48">
+        <v>1</v>
+      </c>
+      <c r="G35" s="48" t="s">
         <v>23</v>
       </c>
       <c r="H35" s="5">
@@ -3359,22 +3425,22 @@
       <c r="I35" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L35" s="48" t="s">
+      <c r="L35" s="49" t="s">
         <v>89</v>
       </c>
       <c r="M35" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N35" s="45">
-        <v>3</v>
-      </c>
-      <c r="O35" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q35" s="18"/>
+      <c r="N35" s="46">
+        <v>3</v>
+      </c>
+      <c r="O35" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q35" s="19"/>
     </row>
     <row r="36" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A36" s="24" t="str">
+      <c r="A36" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1022004</v>
       </c>
@@ -3390,10 +3456,10 @@
       <c r="E36" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F36" s="17">
-        <v>1</v>
-      </c>
-      <c r="G36" s="47" t="s">
+      <c r="F36" s="18">
+        <v>1</v>
+      </c>
+      <c r="G36" s="48" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="5">
@@ -3402,19 +3468,19 @@
       <c r="I36" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L36" s="46">
+      <c r="L36" s="47">
         <v>10220020</v>
       </c>
-      <c r="N36" s="45">
-        <v>3</v>
-      </c>
-      <c r="O36" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q36" s="18"/>
+      <c r="N36" s="46">
+        <v>3</v>
+      </c>
+      <c r="O36" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q36" s="19"/>
     </row>
     <row r="37" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A37" s="24" t="str">
+      <c r="A37" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1022005</v>
       </c>
@@ -3442,20 +3508,20 @@
       <c r="I37" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L37" s="46">
+      <c r="L37" s="47">
         <v>10220019</v>
       </c>
-      <c r="N37" s="45">
-        <v>3</v>
-      </c>
-      <c r="O37" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q37" s="18"/>
-      <c r="S37" s="49"/>
+      <c r="N37" s="46">
+        <v>3</v>
+      </c>
+      <c r="O37" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q37" s="19"/>
+      <c r="S37" s="50"/>
     </row>
     <row r="38" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A38" s="24" t="str">
+      <c r="A38" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1021001</v>
       </c>
@@ -3483,23 +3549,23 @@
       <c r="I38" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L38" s="46" t="s">
+      <c r="L38" s="47" t="s">
         <v>93</v>
       </c>
       <c r="M38" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N38" s="45">
-        <v>3</v>
-      </c>
-      <c r="O38" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q38" s="18"/>
-      <c r="S38" s="49"/>
+      <c r="N38" s="46">
+        <v>3</v>
+      </c>
+      <c r="O38" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q38" s="19"/>
+      <c r="S38" s="50"/>
     </row>
     <row r="39" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A39" s="24" t="str">
+      <c r="A39" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1021002</v>
       </c>
@@ -3527,23 +3593,23 @@
       <c r="I39" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L39" s="46">
+      <c r="L39" s="47">
         <v>10210031</v>
       </c>
       <c r="M39" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N39" s="45">
-        <v>3</v>
-      </c>
-      <c r="O39" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q39" s="18"/>
-      <c r="S39" s="49"/>
+      <c r="N39" s="46">
+        <v>3</v>
+      </c>
+      <c r="O39" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q39" s="19"/>
+      <c r="S39" s="50"/>
     </row>
     <row r="40" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A40" s="24" t="str">
+      <c r="A40" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1021003</v>
       </c>
@@ -3571,23 +3637,23 @@
       <c r="I40" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L40" s="46">
+      <c r="L40" s="47">
         <v>10210041</v>
       </c>
       <c r="M40" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="N40" s="45">
-        <v>3</v>
-      </c>
-      <c r="O40" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q40" s="18"/>
-      <c r="S40" s="49"/>
+      <c r="N40" s="46">
+        <v>3</v>
+      </c>
+      <c r="O40" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q40" s="19"/>
+      <c r="S40" s="50"/>
     </row>
     <row r="41" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A41" s="24" t="str">
+      <c r="A41" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1021004</v>
       </c>
@@ -3615,23 +3681,23 @@
       <c r="I41" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L41" s="46" t="s">
+      <c r="L41" s="47" t="s">
         <v>96</v>
       </c>
       <c r="M41" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N41" s="45">
-        <v>3</v>
-      </c>
-      <c r="O41" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q41" s="18"/>
-      <c r="S41" s="49"/>
+      <c r="N41" s="46">
+        <v>3</v>
+      </c>
+      <c r="O41" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q41" s="19"/>
+      <c r="S41" s="50"/>
     </row>
     <row r="42" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A42" s="24" t="str">
+      <c r="A42" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1018001</v>
       </c>
@@ -3659,20 +3725,20 @@
       <c r="I42" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L42" s="46" t="s">
+      <c r="L42" s="47" t="s">
         <v>98</v>
       </c>
       <c r="M42" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N42" s="45">
+      <c r="N42" s="46">
         <v>4</v>
       </c>
-      <c r="O42" s="45">
+      <c r="O42" s="46">
         <v>6</v>
       </c>
-      <c r="Q42" s="18"/>
-      <c r="S42" s="49"/>
+      <c r="Q42" s="19"/>
+      <c r="S42" s="50"/>
     </row>
     <row r="43" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A43" s="5" t="str">
@@ -3703,16 +3769,16 @@
       <c r="I43" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L43" s="46">
+      <c r="L43" s="47">
         <v>10180031</v>
       </c>
       <c r="M43" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N43" s="45">
+      <c r="N43" s="46">
         <v>4</v>
       </c>
-      <c r="O43" s="45">
+      <c r="O43" s="46">
         <v>6</v>
       </c>
     </row>
@@ -3745,16 +3811,16 @@
       <c r="I44" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L44" s="46" t="s">
+      <c r="L44" s="47" t="s">
         <v>99</v>
       </c>
       <c r="M44" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N44" s="45">
+      <c r="N44" s="46">
         <v>4</v>
       </c>
-      <c r="O44" s="45">
+      <c r="O44" s="46">
         <v>6</v>
       </c>
     </row>
@@ -3787,19 +3853,19 @@
       <c r="I45" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L45" s="46" t="s">
+      <c r="L45" s="47" t="s">
         <v>101</v>
       </c>
       <c r="M45" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N45" s="45">
-        <v>3</v>
-      </c>
-      <c r="O45" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q45" s="8"/>
+      <c r="N45" s="46">
+        <v>3</v>
+      </c>
+      <c r="O45" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q45" s="9"/>
     </row>
     <row r="46" customFormat="1" ht="16.5" spans="1:19">
       <c r="A46" s="5" t="str">
@@ -3830,19 +3896,19 @@
       <c r="I46" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L46" s="46">
+      <c r="L46" s="47">
         <v>10250031</v>
       </c>
       <c r="M46" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="N46" s="45">
-        <v>3</v>
-      </c>
-      <c r="O46" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q46" s="8"/>
+      <c r="N46" s="46">
+        <v>3</v>
+      </c>
+      <c r="O46" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q46" s="9"/>
     </row>
     <row r="47" customFormat="1" ht="16.5" spans="1:19">
       <c r="A47" s="5" t="str">
@@ -3873,19 +3939,19 @@
       <c r="I47" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L47" s="46" t="s">
+      <c r="L47" s="47" t="s">
         <v>103</v>
       </c>
       <c r="M47" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N47" s="45">
-        <v>3</v>
-      </c>
-      <c r="O47" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q47" s="8"/>
+      <c r="N47" s="46">
+        <v>3</v>
+      </c>
+      <c r="O47" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q47" s="9"/>
     </row>
     <row r="48" customFormat="1" ht="16.5" spans="1:19">
       <c r="A48" s="5" t="str">
@@ -3916,19 +3982,19 @@
       <c r="I48" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L48" s="46" t="s">
+      <c r="L48" s="47" t="s">
         <v>105</v>
       </c>
       <c r="M48" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N48" s="45">
+      <c r="N48" s="46">
         <v>4</v>
       </c>
-      <c r="O48" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q48" s="8"/>
+      <c r="O48" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q48" s="9"/>
     </row>
     <row r="49" customFormat="1" ht="16.5" spans="1:17">
       <c r="A49" s="5" t="str">
@@ -3959,19 +4025,19 @@
       <c r="I49" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L49" s="46">
+      <c r="L49" s="47">
         <v>10230003</v>
       </c>
       <c r="M49" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="N49" s="45">
+      <c r="N49" s="46">
         <v>4</v>
       </c>
-      <c r="O49" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q49" s="8"/>
+      <c r="O49" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q49" s="9"/>
     </row>
     <row r="50" customFormat="1" ht="16.5" spans="1:17">
       <c r="A50" s="5" t="str">
@@ -4002,19 +4068,19 @@
       <c r="I50" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L50" s="46" t="s">
+      <c r="L50" s="47" t="s">
         <v>106</v>
       </c>
       <c r="M50" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N50" s="45">
+      <c r="N50" s="46">
         <v>4</v>
       </c>
-      <c r="O50" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q50" s="8"/>
+      <c r="O50" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q50" s="9"/>
     </row>
     <row r="51" customFormat="1" ht="16.5" spans="1:17">
       <c r="A51" s="5" t="str">
@@ -4045,19 +4111,19 @@
       <c r="I51" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L51" s="46">
+      <c r="L51" s="47">
         <v>10340007</v>
       </c>
       <c r="M51" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="N51" s="45">
-        <v>3</v>
-      </c>
-      <c r="O51" s="45">
-        <v>3</v>
-      </c>
-      <c r="Q51" s="8"/>
+      <c r="N51" s="46">
+        <v>3</v>
+      </c>
+      <c r="O51" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q51" s="9"/>
     </row>
     <row r="52" customFormat="1" ht="16.5" spans="1:17">
       <c r="A52" s="5" t="str">
@@ -4088,63 +4154,63 @@
       <c r="I52" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L52" s="46"/>
+      <c r="L52" s="47"/>
       <c r="M52" s="5"/>
-      <c r="N52" s="45">
-        <v>3</v>
-      </c>
-      <c r="O52" s="45">
-        <v>3</v>
-      </c>
-      <c r="P52" s="50"/>
-      <c r="Q52" s="8"/>
-    </row>
-    <row r="53" s="6" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A53" s="51" t="str">
-        <f t="shared" si="2"/>
+      <c r="N52" s="46">
+        <v>3</v>
+      </c>
+      <c r="O52" s="46">
+        <v>3</v>
+      </c>
+      <c r="P52" s="51"/>
+      <c r="Q52" s="9"/>
+    </row>
+    <row r="53" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A53" s="5" t="str">
+        <f t="shared" ref="A53:A71" si="3">B53&amp;C53</f>
         <v>1035001</v>
       </c>
-      <c r="B53" s="51">
+      <c r="B53" s="5">
         <v>103500</v>
       </c>
-      <c r="C53" s="51">
-        <v>1</v>
-      </c>
-      <c r="D53" s="51" t="s">
+      <c r="C53" s="5">
+        <v>1</v>
+      </c>
+      <c r="D53" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="E53" s="51" t="s">
+      <c r="E53" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="F53" s="51">
-        <v>1</v>
-      </c>
-      <c r="G53" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="H53" s="51">
+      <c r="F53" s="5">
+        <v>1</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H53" s="5">
         <v>2035001</v>
       </c>
-      <c r="I53" s="51" t="s">
-        <v>24</v>
-      </c>
-      <c r="L53" s="52" t="s">
+      <c r="I53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L53" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="M53" s="51" t="s">
+      <c r="M53" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="N53" s="53">
+      <c r="N53" s="46">
         <v>4</v>
       </c>
-      <c r="O53" s="53">
-        <v>3</v>
-      </c>
-      <c r="Q53" s="54"/>
+      <c r="O53" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q53" s="9"/>
     </row>
     <row r="54" customFormat="1" ht="16.5" spans="1:17">
       <c r="A54" s="5" t="str">
-        <f t="shared" ref="A53:A61" si="3">B54&amp;C54</f>
+        <f t="shared" si="3"/>
         <v>1035002</v>
       </c>
       <c r="B54" s="5">
@@ -4171,19 +4237,19 @@
       <c r="I54" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L54" s="46" t="s">
+      <c r="L54" s="47" t="s">
         <v>115</v>
       </c>
       <c r="M54" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="N54" s="45">
+      <c r="N54" s="46">
         <v>4</v>
       </c>
-      <c r="O54" s="45">
-        <v>3</v>
-      </c>
-      <c r="Q54" s="8"/>
+      <c r="O54" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="9"/>
     </row>
     <row r="55" customFormat="1" ht="16.5" spans="1:17">
       <c r="A55" s="5" t="str">
@@ -4214,22 +4280,23 @@
       <c r="I55" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L55" s="46" t="s">
+      <c r="L55" s="47" t="s">
         <v>117</v>
       </c>
       <c r="M55" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="N55" s="45">
+      <c r="N55" s="46">
         <v>4</v>
       </c>
-      <c r="O55" s="45">
-        <v>3</v>
-      </c>
-      <c r="Q55" s="8"/>
+      <c r="O55" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q55" s="9"/>
     </row>
     <row r="56" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A56" s="55">
+      <c r="A56" s="5" t="str">
+        <f t="shared" si="3"/>
         <v>1035011</v>
       </c>
       <c r="B56" s="5">
@@ -4256,19 +4323,19 @@
       <c r="I56" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L56" s="46" t="s">
+      <c r="L56" s="47" t="s">
         <v>120</v>
       </c>
       <c r="M56" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="N56" s="45">
+      <c r="N56" s="46">
         <v>4</v>
       </c>
-      <c r="O56" s="45">
-        <v>3</v>
-      </c>
-      <c r="Q56" s="8"/>
+      <c r="O56" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q56" s="9"/>
     </row>
     <row r="57" customFormat="1" ht="16.5" spans="1:17">
       <c r="A57" s="5" t="str">
@@ -4299,19 +4366,19 @@
       <c r="I57" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L57" s="46" t="s">
+      <c r="L57" s="47" t="s">
         <v>121</v>
       </c>
       <c r="M57" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="N57" s="45">
+      <c r="N57" s="46">
         <v>4</v>
       </c>
-      <c r="O57" s="45">
-        <v>3</v>
-      </c>
-      <c r="Q57" s="8"/>
+      <c r="O57" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="9"/>
     </row>
     <row r="58" customFormat="1" ht="16.5" spans="1:17">
       <c r="A58" s="5" t="str">
@@ -4342,19 +4409,19 @@
       <c r="I58" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L58" s="46" t="s">
+      <c r="L58" s="47" t="s">
         <v>122</v>
       </c>
       <c r="M58" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="N58" s="45">
+      <c r="N58" s="46">
         <v>4</v>
       </c>
-      <c r="O58" s="45">
-        <v>3</v>
-      </c>
-      <c r="Q58" s="8"/>
+      <c r="O58" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="9"/>
     </row>
     <row r="59" customFormat="1" ht="16.5" spans="1:17">
       <c r="A59" s="5" t="str">
@@ -4385,19 +4452,19 @@
       <c r="I59" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L59" s="46" t="s">
+      <c r="L59" s="47" t="s">
         <v>124</v>
       </c>
       <c r="M59" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="N59" s="45">
-        <v>3</v>
-      </c>
-      <c r="O59" s="45">
-        <v>3</v>
-      </c>
-      <c r="Q59" s="8"/>
+      <c r="N59" s="46">
+        <v>3</v>
+      </c>
+      <c r="O59" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="9"/>
     </row>
     <row r="60" customFormat="1" ht="16.5" spans="1:17">
       <c r="A60" s="5" t="str">
@@ -4428,19 +4495,19 @@
       <c r="I60" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L60" s="46">
+      <c r="L60" s="47">
         <v>10360004</v>
       </c>
       <c r="M60" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="N60" s="45">
-        <v>3</v>
-      </c>
-      <c r="O60" s="45">
-        <v>3</v>
-      </c>
-      <c r="Q60" s="8"/>
+      <c r="N60" s="46">
+        <v>3</v>
+      </c>
+      <c r="O60" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="9"/>
     </row>
     <row r="61" customFormat="1" ht="16.5" spans="1:17">
       <c r="A61" s="5" t="str">
@@ -4471,179 +4538,446 @@
       <c r="I61" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L61" s="46">
+      <c r="L61" s="47">
         <v>10360002</v>
       </c>
       <c r="M61" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="N61" s="45">
-        <v>3</v>
-      </c>
-      <c r="O61" s="45">
-        <v>3</v>
-      </c>
-      <c r="Q61" s="8"/>
+      <c r="N61" s="46">
+        <v>3</v>
+      </c>
+      <c r="O61" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q61" s="9"/>
     </row>
     <row r="62" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A62" s="5"/>
-      <c r="B62" s="5"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="5"/>
-      <c r="H62" s="5"/>
-      <c r="I62" s="5"/>
-      <c r="L62" s="46"/>
-      <c r="M62" s="5"/>
-      <c r="N62" s="45"/>
-      <c r="O62" s="45"/>
-      <c r="Q62" s="8"/>
+      <c r="A62" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1028001</v>
+      </c>
+      <c r="B62" s="5">
+        <v>102800</v>
+      </c>
+      <c r="C62" s="5">
+        <v>1</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F62" s="5">
+        <v>1</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H62" s="5">
+        <v>2028001</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L62" s="47" t="s">
+        <v>129</v>
+      </c>
+      <c r="M62" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="N62" s="46">
+        <v>5</v>
+      </c>
+      <c r="O62" s="46">
+        <v>6</v>
+      </c>
+      <c r="Q62" s="9"/>
     </row>
     <row r="63" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A63" s="5"/>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
-      <c r="H63" s="5"/>
-      <c r="I63" s="5"/>
-      <c r="L63" s="46"/>
-      <c r="M63" s="5"/>
-      <c r="N63" s="45"/>
-      <c r="O63" s="45"/>
-      <c r="Q63" s="8"/>
+      <c r="A63" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1028002</v>
+      </c>
+      <c r="B63" s="5">
+        <v>102800</v>
+      </c>
+      <c r="C63" s="5">
+        <v>2</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F63" s="5">
+        <v>1</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H63" s="5">
+        <v>2028001</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L63" s="47">
+        <v>10280002</v>
+      </c>
+      <c r="M63" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="N63" s="46">
+        <v>5</v>
+      </c>
+      <c r="O63" s="46">
+        <v>6</v>
+      </c>
+      <c r="Q63" s="9"/>
     </row>
     <row r="64" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A64" s="5"/>
-      <c r="B64" s="5"/>
-      <c r="C64" s="5"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
-      <c r="G64" s="5"/>
-      <c r="H64" s="5"/>
-      <c r="I64" s="5"/>
-      <c r="L64" s="46"/>
-      <c r="M64" s="5"/>
-      <c r="N64" s="45"/>
-      <c r="O64" s="45"/>
-      <c r="Q64" s="8"/>
+      <c r="A64" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1028003</v>
+      </c>
+      <c r="B64" s="5">
+        <v>102800</v>
+      </c>
+      <c r="C64" s="5">
+        <v>3</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F64" s="5">
+        <v>1</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H64" s="5">
+        <v>2028001</v>
+      </c>
+      <c r="I64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L64" s="47" t="s">
+        <v>132</v>
+      </c>
+      <c r="M64" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="N64" s="46">
+        <v>5</v>
+      </c>
+      <c r="O64" s="46">
+        <v>6</v>
+      </c>
+      <c r="Q64" s="9"/>
     </row>
     <row r="65" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A65" s="5"/>
-      <c r="B65" s="5"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="5"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="5"/>
-      <c r="H65" s="5"/>
-      <c r="I65" s="5"/>
-      <c r="L65" s="46"/>
-      <c r="M65" s="5"/>
-      <c r="N65" s="45"/>
-      <c r="O65" s="45"/>
-      <c r="Q65" s="8"/>
+      <c r="A65" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1034011</v>
+      </c>
+      <c r="B65" s="5">
+        <v>103401</v>
+      </c>
+      <c r="C65" s="5">
+        <v>1</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F65" s="5">
+        <v>1</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H65" s="5">
+        <v>2034011</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L65" s="47">
+        <v>10340007</v>
+      </c>
+      <c r="M65" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="N65" s="46">
+        <v>3</v>
+      </c>
+      <c r="O65" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q65" s="9"/>
     </row>
     <row r="66" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A66" s="5"/>
-      <c r="B66" s="5"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="5"/>
-      <c r="E66" s="5"/>
-      <c r="F66" s="5"/>
-      <c r="G66" s="5"/>
-      <c r="H66" s="5"/>
-      <c r="I66" s="5"/>
-      <c r="L66" s="46"/>
+      <c r="A66" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1034012</v>
+      </c>
+      <c r="B66" s="5">
+        <v>103401</v>
+      </c>
+      <c r="C66" s="5">
+        <v>2</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F66" s="5">
+        <v>1</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H66" s="5">
+        <v>2034011</v>
+      </c>
+      <c r="I66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L66" s="47"/>
       <c r="M66" s="5"/>
-      <c r="N66" s="45"/>
-      <c r="O66" s="45"/>
-      <c r="Q66" s="8"/>
-    </row>
-    <row r="67" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A67" s="5"/>
-      <c r="B67" s="5"/>
-      <c r="C67" s="5"/>
-      <c r="D67" s="5"/>
-      <c r="E67" s="5"/>
-      <c r="F67" s="5"/>
-      <c r="G67" s="5"/>
-      <c r="H67" s="5"/>
-      <c r="I67" s="5"/>
-      <c r="L67" s="46"/>
-      <c r="M67" s="5"/>
-      <c r="N67" s="45"/>
-      <c r="O67" s="45"/>
-      <c r="Q67" s="8"/>
+      <c r="N66" s="46">
+        <v>3</v>
+      </c>
+      <c r="O66" s="46">
+        <v>3</v>
+      </c>
+      <c r="P66" s="51"/>
+      <c r="Q66" s="9"/>
+    </row>
+    <row r="67" s="6" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A67" s="52" t="str">
+        <f t="shared" si="3"/>
+        <v>1020001</v>
+      </c>
+      <c r="B67" s="52">
+        <v>102000</v>
+      </c>
+      <c r="C67" s="52">
+        <v>1</v>
+      </c>
+      <c r="D67" s="52" t="s">
+        <v>135</v>
+      </c>
+      <c r="E67" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="F67" s="52">
+        <v>1</v>
+      </c>
+      <c r="G67" s="52" t="s">
+        <v>23</v>
+      </c>
+      <c r="H67" s="52">
+        <v>2020001</v>
+      </c>
+      <c r="I67" s="52" t="s">
+        <v>24</v>
+      </c>
+      <c r="L67" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="M67" s="52" t="s">
+        <v>137</v>
+      </c>
+      <c r="N67" s="54">
+        <v>5</v>
+      </c>
+      <c r="O67" s="54">
+        <v>5</v>
+      </c>
+      <c r="Q67" s="55"/>
     </row>
     <row r="68" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A68" s="5"/>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="5"/>
-      <c r="E68" s="5"/>
-      <c r="F68" s="5"/>
-      <c r="G68" s="5"/>
-      <c r="H68" s="5"/>
-      <c r="I68" s="5"/>
-      <c r="L68" s="46"/>
-      <c r="M68" s="5"/>
-      <c r="N68" s="45"/>
-      <c r="O68" s="45"/>
-      <c r="Q68" s="8"/>
+      <c r="A68" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1020002</v>
+      </c>
+      <c r="B68" s="5">
+        <v>102000</v>
+      </c>
+      <c r="C68" s="5">
+        <v>2</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F68" s="5">
+        <v>1</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H68" s="5">
+        <v>2020001</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L68" s="47" t="s">
+        <v>138</v>
+      </c>
+      <c r="M68" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="N68" s="46">
+        <v>5</v>
+      </c>
+      <c r="O68" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q68" s="9"/>
     </row>
     <row r="69" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A69" s="5"/>
-      <c r="B69" s="5"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="5"/>
-      <c r="E69" s="5"/>
-      <c r="F69" s="5"/>
-      <c r="G69" s="5"/>
-      <c r="H69" s="5"/>
-      <c r="I69" s="5"/>
-      <c r="L69" s="46"/>
-      <c r="M69" s="5"/>
-      <c r="N69" s="45"/>
-      <c r="O69" s="45"/>
-      <c r="Q69" s="8"/>
-    </row>
-    <row r="70" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A70" s="5"/>
-      <c r="B70" s="5"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="5"/>
-      <c r="E70" s="5"/>
-      <c r="F70" s="5"/>
-      <c r="G70" s="5"/>
-      <c r="H70" s="5"/>
-      <c r="I70" s="5"/>
-      <c r="L70" s="46"/>
-      <c r="M70" s="5"/>
-      <c r="N70" s="45"/>
-      <c r="O70" s="45"/>
-      <c r="Q70" s="8"/>
+      <c r="A69" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1020003</v>
+      </c>
+      <c r="B69" s="5">
+        <v>102000</v>
+      </c>
+      <c r="C69" s="5">
+        <v>3</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F69" s="5">
+        <v>1</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H69" s="5">
+        <v>2020001</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L69" s="47" t="s">
+        <v>140</v>
+      </c>
+      <c r="M69" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="N69" s="46">
+        <v>5</v>
+      </c>
+      <c r="O69" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q69" s="9"/>
+    </row>
+    <row r="70" s="7" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A70" s="56" t="str">
+        <f t="shared" si="3"/>
+        <v>1020004</v>
+      </c>
+      <c r="B70" s="56">
+        <v>102000</v>
+      </c>
+      <c r="C70" s="56">
+        <v>4</v>
+      </c>
+      <c r="D70" s="56" t="s">
+        <v>135</v>
+      </c>
+      <c r="E70" s="56" t="s">
+        <v>142</v>
+      </c>
+      <c r="F70" s="56">
+        <v>1</v>
+      </c>
+      <c r="G70" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="H70" s="56">
+        <v>2020002</v>
+      </c>
+      <c r="I70" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="L70" s="57">
+        <v>10200016</v>
+      </c>
+      <c r="M70" s="56" t="s">
+        <v>143</v>
+      </c>
+      <c r="N70" s="58">
+        <v>5</v>
+      </c>
+      <c r="O70" s="58">
+        <v>5</v>
+      </c>
+      <c r="Q70" s="59"/>
     </row>
     <row r="71" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A71" s="5"/>
-      <c r="B71" s="5"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="5"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
-      <c r="G71" s="5"/>
-      <c r="H71" s="5"/>
-      <c r="I71" s="5"/>
-      <c r="L71" s="46"/>
-      <c r="M71" s="5"/>
-      <c r="N71" s="45"/>
-      <c r="O71" s="45"/>
-      <c r="Q71" s="8"/>
+      <c r="A71" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1020005</v>
+      </c>
+      <c r="B71" s="5">
+        <v>102000</v>
+      </c>
+      <c r="C71" s="5">
+        <v>5</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F71" s="5">
+        <v>1</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H71" s="5">
+        <v>2020003</v>
+      </c>
+      <c r="I71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L71" s="47">
+        <v>10200021</v>
+      </c>
+      <c r="M71" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="N71" s="46">
+        <v>5</v>
+      </c>
+      <c r="O71" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q71" s="9"/>
     </row>
     <row r="72" customFormat="1" ht="16.5" spans="1:17">
       <c r="A72" s="5"/>
@@ -4655,11 +4989,11 @@
       <c r="G72" s="5"/>
       <c r="H72" s="5"/>
       <c r="I72" s="5"/>
-      <c r="L72" s="46"/>
+      <c r="L72" s="47"/>
       <c r="M72" s="5"/>
-      <c r="N72" s="45"/>
-      <c r="O72" s="45"/>
-      <c r="Q72" s="8"/>
+      <c r="N72" s="46"/>
+      <c r="O72" s="46"/>
+      <c r="Q72" s="9"/>
     </row>
     <row r="73" customFormat="1" ht="16.5" spans="1:17">
       <c r="A73" s="5"/>
@@ -4671,11 +5005,11 @@
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
       <c r="I73" s="5"/>
-      <c r="L73" s="46"/>
+      <c r="L73" s="47"/>
       <c r="M73" s="5"/>
-      <c r="N73" s="45"/>
-      <c r="O73" s="45"/>
-      <c r="Q73" s="8"/>
+      <c r="N73" s="46"/>
+      <c r="O73" s="46"/>
+      <c r="Q73" s="9"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:K2">

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="128">
   <si>
     <t>id</t>
   </si>
@@ -1234,7 +1234,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1345,12 +1345,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1888,7 +1882,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S73"/>
+  <dimension ref="A1:S74"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
@@ -4100,82 +4094,78 @@
       <c r="Q52" s="8"/>
     </row>
     <row r="53" s="6" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A53" s="51" t="str">
-        <f t="shared" si="2"/>
+      <c r="A53" s="5" t="str">
+        <f>B53&amp;C53</f>
+        <v>1034003</v>
+      </c>
+      <c r="B53" s="5">
+        <v>103400</v>
+      </c>
+      <c r="C53" s="5">
+        <v>3</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F53" s="51">
+        <v>1</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H53" s="5">
+        <v>2034001</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L53" s="48"/>
+      <c r="M53" s="51"/>
+      <c r="N53" s="45">
+        <v>3</v>
+      </c>
+      <c r="O53" s="45">
+        <v>3</v>
+      </c>
+      <c r="Q53" s="52"/>
+    </row>
+    <row r="54" s="6" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A54" s="51" t="str">
+        <f>B54&amp;C54</f>
         <v>1035001</v>
       </c>
-      <c r="B53" s="51">
+      <c r="B54" s="51">
         <v>103500</v>
       </c>
-      <c r="C53" s="51">
-        <v>1</v>
-      </c>
-      <c r="D53" s="51" t="s">
+      <c r="C54" s="51">
+        <v>1</v>
+      </c>
+      <c r="D54" s="51" t="s">
         <v>110</v>
       </c>
-      <c r="E53" s="51" t="s">
+      <c r="E54" s="51" t="s">
         <v>111</v>
       </c>
-      <c r="F53" s="51">
-        <v>1</v>
-      </c>
-      <c r="G53" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="H53" s="51">
+      <c r="F54" s="51">
+        <v>1</v>
+      </c>
+      <c r="G54" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="H54" s="51">
         <v>2035001</v>
       </c>
-      <c r="I53" s="51" t="s">
-        <v>24</v>
-      </c>
-      <c r="L53" s="52" t="s">
+      <c r="I54" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="L54" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="M53" s="51" t="s">
+      <c r="M54" s="51" t="s">
         <v>113</v>
-      </c>
-      <c r="N53" s="53">
-        <v>4</v>
-      </c>
-      <c r="O53" s="53">
-        <v>3</v>
-      </c>
-      <c r="Q53" s="54"/>
-    </row>
-    <row r="54" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A54" s="5" t="str">
-        <f t="shared" ref="A53:A61" si="3">B54&amp;C54</f>
-        <v>1035002</v>
-      </c>
-      <c r="B54" s="5">
-        <v>103500</v>
-      </c>
-      <c r="C54" s="5">
-        <v>2</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="F54" s="5">
-        <v>1</v>
-      </c>
-      <c r="G54" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H54" s="5">
-        <v>2035002</v>
-      </c>
-      <c r="I54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L54" s="46" t="s">
-        <v>115</v>
-      </c>
-      <c r="M54" s="5" t="s">
-        <v>116</v>
       </c>
       <c r="N54" s="45">
         <v>4</v>
@@ -4183,84 +4173,85 @@
       <c r="O54" s="45">
         <v>3</v>
       </c>
-      <c r="Q54" s="8"/>
+      <c r="Q54" s="52"/>
     </row>
     <row r="55" customFormat="1" ht="16.5" spans="1:17">
       <c r="A55" s="5" t="str">
+        <f t="shared" ref="A54:A62" si="3">B55&amp;C55</f>
+        <v>1035002</v>
+      </c>
+      <c r="B55" s="5">
+        <v>103500</v>
+      </c>
+      <c r="C55" s="5">
+        <v>2</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F55" s="5">
+        <v>1</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H55" s="5">
+        <v>2035002</v>
+      </c>
+      <c r="I55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L55" s="46" t="s">
+        <v>115</v>
+      </c>
+      <c r="M55" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="N55" s="45">
+        <v>4</v>
+      </c>
+      <c r="O55" s="45">
+        <v>3</v>
+      </c>
+      <c r="Q55" s="8"/>
+    </row>
+    <row r="56" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A56" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1035003</v>
       </c>
-      <c r="B55" s="5">
+      <c r="B56" s="5">
         <v>103500</v>
       </c>
-      <c r="C55" s="5">
-        <v>3</v>
-      </c>
-      <c r="D55" s="5" t="s">
+      <c r="C56" s="5">
+        <v>3</v>
+      </c>
+      <c r="D56" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="E55" s="5" t="s">
+      <c r="E56" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F55" s="5">
-        <v>1</v>
-      </c>
-      <c r="G55" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H55" s="5">
+      <c r="F56" s="5">
+        <v>1</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H56" s="5">
         <v>2035001</v>
       </c>
-      <c r="I55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L55" s="46" t="s">
+      <c r="I56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L56" s="46" t="s">
         <v>117</v>
       </c>
-      <c r="M55" s="5" t="s">
+      <c r="M56" s="5" t="s">
         <v>118</v>
-      </c>
-      <c r="N55" s="45">
-        <v>4</v>
-      </c>
-      <c r="O55" s="45">
-        <v>3</v>
-      </c>
-      <c r="Q55" s="8"/>
-    </row>
-    <row r="56" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A56" s="55">
-        <v>1035011</v>
-      </c>
-      <c r="B56" s="5">
-        <v>103501</v>
-      </c>
-      <c r="C56" s="5">
-        <v>1</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="F56" s="5">
-        <v>1</v>
-      </c>
-      <c r="G56" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H56" s="5">
-        <v>2035011</v>
-      </c>
-      <c r="I56" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L56" s="46" t="s">
-        <v>120</v>
-      </c>
-      <c r="M56" s="5" t="s">
-        <v>113</v>
       </c>
       <c r="N56" s="45">
         <v>4</v>
@@ -4271,21 +4262,20 @@
       <c r="Q56" s="8"/>
     </row>
     <row r="57" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A57" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>1035012</v>
+      <c r="A57" s="53">
+        <v>1035011</v>
       </c>
       <c r="B57" s="5">
         <v>103501</v>
       </c>
       <c r="C57" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>119</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F57" s="5">
         <v>1</v>
@@ -4294,16 +4284,16 @@
         <v>23</v>
       </c>
       <c r="H57" s="5">
-        <v>2035012</v>
+        <v>2035011</v>
       </c>
       <c r="I57" s="5" t="s">
         <v>24</v>
       </c>
       <c r="L57" s="46" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M57" s="5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="N57" s="45">
         <v>4</v>
@@ -4316,19 +4306,19 @@
     <row r="58" customFormat="1" ht="16.5" spans="1:17">
       <c r="A58" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>1035013</v>
+        <v>1035012</v>
       </c>
       <c r="B58" s="5">
         <v>103501</v>
       </c>
       <c r="C58" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D58" s="5" t="s">
         <v>119</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="F58" s="5">
         <v>1</v>
@@ -4337,16 +4327,16 @@
         <v>23</v>
       </c>
       <c r="H58" s="5">
-        <v>2035011</v>
+        <v>2035012</v>
       </c>
       <c r="I58" s="5" t="s">
         <v>24</v>
       </c>
       <c r="L58" s="46" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M58" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="N58" s="45">
         <v>4</v>
@@ -4359,19 +4349,19 @@
     <row r="59" customFormat="1" ht="16.5" spans="1:17">
       <c r="A59" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>1036001</v>
+        <v>1035013</v>
       </c>
       <c r="B59" s="5">
-        <v>103600</v>
+        <v>103501</v>
       </c>
       <c r="C59" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="F59" s="5">
         <v>1</v>
@@ -4380,19 +4370,19 @@
         <v>23</v>
       </c>
       <c r="H59" s="5">
-        <v>2036001</v>
+        <v>2035011</v>
       </c>
       <c r="I59" s="5" t="s">
         <v>24</v>
       </c>
       <c r="L59" s="46" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M59" s="5" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="N59" s="45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O59" s="45">
         <v>3</v>
@@ -4402,19 +4392,19 @@
     <row r="60" customFormat="1" ht="16.5" spans="1:17">
       <c r="A60" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>1036002</v>
+        <v>1036001</v>
       </c>
       <c r="B60" s="5">
         <v>103600</v>
       </c>
       <c r="C60" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>123</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="F60" s="5">
         <v>1</v>
@@ -4423,16 +4413,16 @@
         <v>23</v>
       </c>
       <c r="H60" s="5">
-        <v>2036002</v>
+        <v>2036001</v>
       </c>
       <c r="I60" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L60" s="46">
-        <v>10360004</v>
+      <c r="L60" s="46" t="s">
+        <v>124</v>
       </c>
       <c r="M60" s="5" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="N60" s="45">
         <v>3</v>
@@ -4445,60 +4435,87 @@
     <row r="61" customFormat="1" ht="16.5" spans="1:17">
       <c r="A61" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>1036003</v>
+        <v>1036002</v>
       </c>
       <c r="B61" s="5">
         <v>103600</v>
       </c>
       <c r="C61" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>123</v>
       </c>
       <c r="E61" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F61" s="5">
+        <v>1</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H61" s="5">
+        <v>2036002</v>
+      </c>
+      <c r="I61" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L61" s="46">
+        <v>10360004</v>
+      </c>
+      <c r="M61" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="N61" s="45">
+        <v>3</v>
+      </c>
+      <c r="O61" s="45">
+        <v>3</v>
+      </c>
+      <c r="Q61" s="8"/>
+    </row>
+    <row r="62" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A62" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1036003</v>
+      </c>
+      <c r="B62" s="5">
+        <v>103600</v>
+      </c>
+      <c r="C62" s="5">
+        <v>3</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E62" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F61" s="5">
-        <v>1</v>
-      </c>
-      <c r="G61" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H61" s="5">
+      <c r="F62" s="5">
+        <v>1</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H62" s="5">
         <v>2036001</v>
       </c>
-      <c r="I61" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L61" s="46">
+      <c r="I62" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L62" s="46">
         <v>10360002</v>
       </c>
-      <c r="M61" s="5" t="s">
+      <c r="M62" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="N61" s="45">
-        <v>3</v>
-      </c>
-      <c r="O61" s="45">
-        <v>3</v>
-      </c>
-      <c r="Q61" s="8"/>
-    </row>
-    <row r="62" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A62" s="5"/>
-      <c r="B62" s="5"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="5"/>
-      <c r="H62" s="5"/>
-      <c r="I62" s="5"/>
-      <c r="L62" s="46"/>
-      <c r="M62" s="5"/>
-      <c r="N62" s="45"/>
-      <c r="O62" s="45"/>
+      <c r="N62" s="45">
+        <v>3</v>
+      </c>
+      <c r="O62" s="45">
+        <v>3</v>
+      </c>
       <c r="Q62" s="8"/>
     </row>
     <row r="63" customFormat="1" ht="16.5" spans="1:17">
@@ -4676,6 +4693,22 @@
       <c r="N73" s="45"/>
       <c r="O73" s="45"/>
       <c r="Q73" s="8"/>
+    </row>
+    <row r="74" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A74" s="5"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="5"/>
+      <c r="I74" s="5"/>
+      <c r="L74" s="46"/>
+      <c r="M74" s="5"/>
+      <c r="N74" s="45"/>
+      <c r="O74" s="45"/>
+      <c r="Q74" s="8"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:K2">

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="155">
   <si>
     <t>id</t>
   </si>
@@ -510,6 +510,87 @@
   </si>
   <si>
     <t>必出现3个Jackpot符号</t>
+  </si>
+  <si>
+    <t>王牌dj</t>
+  </si>
+  <si>
+    <t>10280001|10280003|10280006|10280007|10280008</t>
+  </si>
+  <si>
+    <t>概率出现wild+概率改出2个SCATTER+概率改出占据2、3、4个格子符号</t>
+  </si>
+  <si>
+    <t>免费游戏-触发局</t>
+  </si>
+  <si>
+    <t>10280004|10280009</t>
+  </si>
+  <si>
+    <t>虎虎生财</t>
+  </si>
+  <si>
+    <t>福虎模式</t>
+  </si>
+  <si>
+    <t>l宙斯vs哈迪斯</t>
+  </si>
+  <si>
+    <t>10200001|10200002|10200003|10200004|10200005|10200006|10200007</t>
+  </si>
+  <si>
+    <t>概率出现wild+概率在1234轴上改出v1234+概率第1轴改出1个scatter+概率第3轴改出1个scatter</t>
+  </si>
+  <si>
+    <t>10200008|10200009|10200010</t>
+  </si>
+  <si>
+    <t>第1轴改出1个scatter+第3轴改出1个scatter+第1轴改出5个scatter</t>
+  </si>
+  <si>
+    <t>10200006|10200007|10200011</t>
+  </si>
+  <si>
+    <t>第1轴改出1个scatter+第3轴改出1个scatter+第5轴改出奖池符号</t>
+  </si>
+  <si>
+    <t>宙斯模式</t>
+  </si>
+  <si>
+    <t>改出39符号，用于触发免费游戏宙斯</t>
+  </si>
+  <si>
+    <t>哈迪斯模式</t>
+  </si>
+  <si>
+    <t>改出40符号，用于触发免费游戏哈迪斯</t>
+  </si>
+  <si>
+    <t>恶魔之子</t>
+  </si>
+  <si>
+    <t>10380001_1|10380004_1|10380005_1</t>
+  </si>
+  <si>
+    <t>概率改出wild+概率改出奖金符号+改出奖池符号</t>
+  </si>
+  <si>
+    <t>改出wild</t>
+  </si>
+  <si>
+    <t>收集金币</t>
+  </si>
+  <si>
+    <t>10380003|10380006</t>
+  </si>
+  <si>
+    <t>改出18图标+改出金币符号</t>
+  </si>
+  <si>
+    <t>10380003|10380005</t>
+  </si>
+  <si>
+    <t>改出18图标+改出奖池符号</t>
   </si>
 </sst>
 </file>
@@ -704,7 +785,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="44">
+  <fills count="45">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -726,6 +807,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -756,12 +849,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1109,7 +1196,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1133,16 +1220,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1151,110 +1238,111 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1263,24 +1351,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -1291,22 +1379,22 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1314,11 +1402,11 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1344,11 +1432,22 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1882,7 +1981,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S74"/>
+  <dimension ref="A1:S77"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
@@ -1895,14 +1994,14 @@
     <col min="11" max="11" width="16.75" customWidth="1"/>
     <col min="12" max="12" width="53.25" customWidth="1"/>
     <col min="13" max="13" width="21.6083333333333" customWidth="1"/>
-    <col min="14" max="15" width="9" style="7"/>
+    <col min="14" max="15" width="9" style="8"/>
     <col min="16" max="16" width="15" customWidth="1"/>
-    <col min="17" max="17" width="23.75" style="8" customWidth="1"/>
+    <col min="17" max="17" width="23.75" style="9" customWidth="1"/>
     <col min="18" max="18" width="60.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:17">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
@@ -1913,34 +2012,34 @@
       </c>
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="11" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="5"/>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="11" t="s">
         <v>4</v>
       </c>
       <c r="I1" s="5"/>
-      <c r="J1" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="11"/>
-      <c r="L1" s="12" t="s">
+      <c r="J1" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="12"/>
+      <c r="L1" s="13" t="s">
         <v>6</v>
       </c>
       <c r="M1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="13" t="s">
+      <c r="N1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="O1" s="14" t="s">
         <v>9</v>
       </c>
       <c r="Q1"/>
     </row>
     <row r="2" ht="16.5" spans="1:17">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -1951,62 +2050,62 @@
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="11" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="5"/>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="11" t="s">
         <v>10</v>
       </c>
       <c r="I2" s="5"/>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="15"/>
-      <c r="L2" s="16" t="s">
+      <c r="K2" s="16"/>
+      <c r="L2" s="17" t="s">
         <v>12</v>
       </c>
       <c r="M2" s="5"/>
-      <c r="N2" s="17" t="s">
+      <c r="N2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="17" t="s">
+      <c r="O2" s="18" t="s">
         <v>10</v>
       </c>
       <c r="Q2"/>
     </row>
     <row r="3" ht="16.5" spans="1:17">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="19" t="s">
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="18"/>
-      <c r="H3" s="20" t="s">
+      <c r="G3" s="19"/>
+      <c r="H3" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="18"/>
-      <c r="J3" s="21" t="s">
+      <c r="I3" s="19"/>
+      <c r="J3" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="21"/>
-      <c r="L3" s="22" t="s">
+      <c r="K3" s="22"/>
+      <c r="L3" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="M3" s="18"/>
-      <c r="N3" s="17" t="s">
+      <c r="M3" s="19"/>
+      <c r="N3" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="17" t="s">
+      <c r="O3" s="18" t="s">
         <v>20</v>
       </c>
       <c r="Q3"/>
@@ -2016,1101 +2115,1101 @@
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="10"/>
+      <c r="F4" s="11"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="10"/>
+      <c r="H4" s="11"/>
       <c r="I4" s="5"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="12"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="13"/>
       <c r="M4" s="5"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="18"/>
       <c r="Q4"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A5" s="24" t="str">
+      <c r="A5" s="25" t="str">
         <f t="shared" ref="A5:A15" si="0">B5&amp;C5</f>
         <v>1001001</v>
       </c>
-      <c r="B5" s="25">
+      <c r="B5" s="26">
         <v>100100</v>
       </c>
-      <c r="C5" s="25">
-        <v>1</v>
-      </c>
-      <c r="D5" s="25" t="s">
+      <c r="C5" s="26">
+        <v>1</v>
+      </c>
+      <c r="D5" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="25">
-        <v>1</v>
-      </c>
-      <c r="G5" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="24">
+      <c r="F5" s="26">
+        <v>1</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="25">
         <v>2001001</v>
       </c>
-      <c r="I5" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="24"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="27" t="s">
+      <c r="I5" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="M5" s="24" t="s">
+      <c r="M5" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="N5" s="17">
+      <c r="N5" s="18">
         <v>4</v>
       </c>
-      <c r="O5" s="17">
+      <c r="O5" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A6" s="24" t="str">
+      <c r="A6" s="25" t="str">
         <f t="shared" si="0"/>
         <v>1001002</v>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="26">
         <v>100100</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="26">
         <v>2</v>
       </c>
-      <c r="D6" s="25"/>
-      <c r="E6" s="28" t="s">
+      <c r="D6" s="26"/>
+      <c r="E6" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="25">
-        <v>1</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="24">
+      <c r="F6" s="26">
+        <v>1</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="25">
         <v>2001001</v>
       </c>
-      <c r="I6" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="29" t="s">
+      <c r="I6" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="M6" s="24" t="s">
+      <c r="M6" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="N6" s="17">
+      <c r="N6" s="18">
         <v>4</v>
       </c>
-      <c r="O6" s="17">
+      <c r="O6" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A7" s="24" t="str">
+      <c r="A7" s="25" t="str">
         <f t="shared" si="0"/>
         <v>1001003</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="26">
         <v>100100</v>
       </c>
-      <c r="C7" s="25">
-        <v>3</v>
-      </c>
-      <c r="D7" s="25"/>
-      <c r="E7" s="30" t="s">
+      <c r="C7" s="26">
+        <v>3</v>
+      </c>
+      <c r="D7" s="26"/>
+      <c r="E7" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="25">
-        <v>1</v>
-      </c>
-      <c r="G7" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="24">
+      <c r="F7" s="26">
+        <v>1</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="25">
         <v>2001001</v>
       </c>
-      <c r="I7" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="27" t="s">
+      <c r="I7" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="M7" s="24" t="s">
+      <c r="M7" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="N7" s="17">
+      <c r="N7" s="18">
         <v>4</v>
       </c>
-      <c r="O7" s="17">
+      <c r="O7" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A8" s="24" t="str">
+      <c r="A8" s="25" t="str">
         <f t="shared" si="0"/>
         <v>1001004</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="26">
         <v>100100</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="26">
         <v>4</v>
       </c>
-      <c r="D8" s="25"/>
-      <c r="E8" s="31" t="s">
+      <c r="D8" s="26"/>
+      <c r="E8" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="32">
-        <v>1</v>
-      </c>
-      <c r="G8" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="24">
+      <c r="F8" s="33">
+        <v>1</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="25">
         <v>2001001</v>
       </c>
-      <c r="I8" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" s="24"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="27">
+      <c r="I8" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="28">
         <v>10010041</v>
       </c>
-      <c r="M8" s="24" t="s">
+      <c r="M8" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="N8" s="17">
+      <c r="N8" s="18">
         <v>4</v>
       </c>
-      <c r="O8" s="17">
+      <c r="O8" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A9" s="24" t="str">
+      <c r="A9" s="25" t="str">
         <f t="shared" si="0"/>
         <v>1001005</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="26">
         <v>100100</v>
       </c>
-      <c r="C9" s="25">
-        <v>5</v>
-      </c>
-      <c r="D9" s="25"/>
-      <c r="E9" s="33" t="s">
+      <c r="C9" s="26">
+        <v>5</v>
+      </c>
+      <c r="D9" s="26"/>
+      <c r="E9" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="32">
-        <v>1</v>
-      </c>
-      <c r="G9" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="24">
+      <c r="F9" s="33">
+        <v>1</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="25">
         <v>2001001</v>
       </c>
-      <c r="I9" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" s="24"/>
-      <c r="K9" s="24"/>
-      <c r="L9" s="27" t="s">
+      <c r="I9" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="M9" s="24" t="s">
+      <c r="M9" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N9" s="17">
+      <c r="N9" s="18">
         <v>4</v>
       </c>
-      <c r="O9" s="17">
+      <c r="O9" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A10" s="24" t="str">
+      <c r="A10" s="25" t="str">
         <f t="shared" si="0"/>
         <v>1001006</v>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="26">
         <v>100100</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="26">
         <v>6</v>
       </c>
-      <c r="D10" s="25"/>
-      <c r="E10" s="33" t="s">
+      <c r="D10" s="26"/>
+      <c r="E10" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="32">
-        <v>1</v>
-      </c>
-      <c r="G10" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="24">
+      <c r="F10" s="33">
+        <v>1</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="25">
         <v>2001001</v>
       </c>
-      <c r="I10" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="27">
+      <c r="I10" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="28">
         <v>10010061</v>
       </c>
-      <c r="M10" s="24" t="s">
+      <c r="M10" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="N10" s="17">
+      <c r="N10" s="18">
         <v>4</v>
       </c>
-      <c r="O10" s="17">
+      <c r="O10" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A11" s="24" t="str">
+      <c r="A11" s="25" t="str">
         <f t="shared" si="0"/>
         <v>1001007</v>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="26">
         <v>100100</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="26">
         <v>7</v>
       </c>
-      <c r="D11" s="25"/>
-      <c r="E11" s="28" t="s">
+      <c r="D11" s="26"/>
+      <c r="E11" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="25">
-        <v>1</v>
-      </c>
-      <c r="G11" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" s="24">
+      <c r="F11" s="26">
+        <v>1</v>
+      </c>
+      <c r="G11" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="25">
         <v>2001001</v>
       </c>
-      <c r="I11" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="J11" s="24"/>
-      <c r="K11" s="24"/>
-      <c r="L11" s="29" t="s">
+      <c r="I11" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="M11" s="24" t="s">
+      <c r="M11" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="N11" s="17">
+      <c r="N11" s="18">
         <v>4</v>
       </c>
-      <c r="O11" s="17">
+      <c r="O11" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A12" s="34" t="str">
+      <c r="A12" s="35" t="str">
         <f t="shared" si="0"/>
         <v>1003001</v>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="27">
         <v>100300</v>
       </c>
-      <c r="C12" s="26">
-        <v>1</v>
-      </c>
-      <c r="D12" s="26" t="s">
+      <c r="C12" s="27">
+        <v>1</v>
+      </c>
+      <c r="D12" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="26" t="s">
+      <c r="E12" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="26">
-        <v>1</v>
-      </c>
-      <c r="G12" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="H12" s="34">
+      <c r="F12" s="27">
+        <v>1</v>
+      </c>
+      <c r="G12" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="35">
         <v>2003001</v>
       </c>
-      <c r="I12" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" s="34"/>
-      <c r="K12" s="34"/>
-      <c r="L12" s="35">
+      <c r="I12" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" s="35"/>
+      <c r="K12" s="35"/>
+      <c r="L12" s="36">
         <v>10030022</v>
       </c>
-      <c r="M12" s="34" t="s">
+      <c r="M12" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="N12" s="26">
-        <v>3</v>
-      </c>
-      <c r="O12" s="26">
-        <v>3</v>
-      </c>
-      <c r="Q12" s="36"/>
+      <c r="N12" s="27">
+        <v>3</v>
+      </c>
+      <c r="O12" s="27">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="37"/>
     </row>
     <row r="13" s="2" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A13" s="34" t="str">
+      <c r="A13" s="35" t="str">
         <f t="shared" ref="A13:A30" si="1">B13&amp;C13</f>
         <v>1003002</v>
       </c>
-      <c r="B13" s="26">
+      <c r="B13" s="27">
         <v>100300</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="27">
         <v>2</v>
       </c>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26" t="s">
+      <c r="D13" s="27"/>
+      <c r="E13" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="26">
-        <v>1</v>
-      </c>
-      <c r="G13" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="H13" s="34">
+      <c r="F13" s="27">
+        <v>1</v>
+      </c>
+      <c r="G13" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="35">
         <v>2003001</v>
       </c>
-      <c r="I13" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="J13" s="34"/>
-      <c r="K13" s="34"/>
-      <c r="L13" s="35" t="s">
+      <c r="I13" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" s="35"/>
+      <c r="K13" s="35"/>
+      <c r="L13" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="M13" s="34" t="s">
+      <c r="M13" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="N13" s="26">
-        <v>3</v>
-      </c>
-      <c r="O13" s="26">
-        <v>3</v>
-      </c>
-      <c r="Q13" s="36"/>
+      <c r="N13" s="27">
+        <v>3</v>
+      </c>
+      <c r="O13" s="27">
+        <v>3</v>
+      </c>
+      <c r="Q13" s="37"/>
     </row>
     <row r="14" s="2" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A14" s="34" t="str">
+      <c r="A14" s="35" t="str">
         <f t="shared" si="1"/>
         <v>1003003</v>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="27">
         <v>100300</v>
       </c>
-      <c r="C14" s="26">
-        <v>3</v>
-      </c>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26" t="s">
+      <c r="C14" s="27">
+        <v>3</v>
+      </c>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="26">
-        <v>1</v>
-      </c>
-      <c r="G14" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="H14" s="34">
+      <c r="F14" s="27">
+        <v>1</v>
+      </c>
+      <c r="G14" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="35">
         <v>2003002</v>
       </c>
-      <c r="I14" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="J14" s="34" t="s">
+      <c r="I14" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="K14" s="34" t="s">
+      <c r="K14" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="L14" s="35" t="s">
+      <c r="L14" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="M14" s="34" t="s">
+      <c r="M14" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="N14" s="26">
-        <v>3</v>
-      </c>
-      <c r="O14" s="26">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="36"/>
+      <c r="N14" s="27">
+        <v>3</v>
+      </c>
+      <c r="O14" s="27">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="37"/>
     </row>
     <row r="15" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A15" s="37" t="str">
+      <c r="A15" s="38" t="str">
         <f t="shared" si="1"/>
         <v>1007001</v>
       </c>
-      <c r="B15" s="38">
+      <c r="B15" s="39">
         <v>100700</v>
       </c>
-      <c r="C15" s="38">
-        <v>1</v>
-      </c>
-      <c r="D15" s="38" t="s">
+      <c r="C15" s="39">
+        <v>1</v>
+      </c>
+      <c r="D15" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="38" t="s">
+      <c r="E15" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="38">
-        <v>1</v>
-      </c>
-      <c r="G15" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="H15" s="37">
+      <c r="F15" s="39">
+        <v>1</v>
+      </c>
+      <c r="G15" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="38">
         <v>2007001</v>
       </c>
-      <c r="I15" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="J15" s="37"/>
-      <c r="K15" s="37"/>
-      <c r="L15" s="39" t="s">
+      <c r="I15" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" s="38"/>
+      <c r="K15" s="38"/>
+      <c r="L15" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="M15" s="37" t="s">
+      <c r="M15" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="N15" s="17">
+      <c r="N15" s="18">
         <v>4</v>
       </c>
-      <c r="O15" s="17">
+      <c r="O15" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="16" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A16" s="37" t="str">
+      <c r="A16" s="38" t="str">
         <f t="shared" si="1"/>
         <v>1007002</v>
       </c>
-      <c r="B16" s="38">
+      <c r="B16" s="39">
         <v>100700</v>
       </c>
-      <c r="C16" s="38">
+      <c r="C16" s="39">
         <v>2</v>
       </c>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38" t="s">
+      <c r="D16" s="39"/>
+      <c r="E16" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="38">
-        <v>1</v>
-      </c>
-      <c r="G16" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="H16" s="37">
+      <c r="F16" s="39">
+        <v>1</v>
+      </c>
+      <c r="G16" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="38">
         <v>2007001</v>
       </c>
-      <c r="I16" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="J16" s="37"/>
-      <c r="K16" s="37"/>
-      <c r="L16" s="39" t="s">
+      <c r="I16" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="J16" s="38"/>
+      <c r="K16" s="38"/>
+      <c r="L16" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="M16" s="37" t="s">
+      <c r="M16" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="N16" s="17">
+      <c r="N16" s="18">
         <v>4</v>
       </c>
-      <c r="O16" s="17">
+      <c r="O16" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="17" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A17" s="40" t="str">
+      <c r="A17" s="41" t="str">
         <f t="shared" si="1"/>
         <v>1012001</v>
       </c>
-      <c r="B17" s="41">
+      <c r="B17" s="42">
         <v>101200</v>
       </c>
-      <c r="C17" s="41">
-        <v>1</v>
-      </c>
-      <c r="D17" s="41" t="s">
+      <c r="C17" s="42">
+        <v>1</v>
+      </c>
+      <c r="D17" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="E17" s="41" t="s">
+      <c r="E17" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="41">
-        <v>1</v>
-      </c>
-      <c r="G17" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="H17" s="40">
+      <c r="F17" s="42">
+        <v>1</v>
+      </c>
+      <c r="G17" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="41">
         <v>2012001</v>
       </c>
-      <c r="I17" s="40" t="s">
-        <v>24</v>
-      </c>
-      <c r="J17" s="40"/>
-      <c r="K17" s="40"/>
-      <c r="L17" s="42">
+      <c r="I17" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="J17" s="41"/>
+      <c r="K17" s="41"/>
+      <c r="L17" s="43">
         <v>10120011</v>
       </c>
-      <c r="M17" s="40" t="s">
+      <c r="M17" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="N17" s="41">
-        <v>3</v>
-      </c>
-      <c r="O17" s="41">
-        <v>5</v>
-      </c>
-      <c r="Q17" s="43"/>
+      <c r="N17" s="42">
+        <v>3</v>
+      </c>
+      <c r="O17" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="44"/>
     </row>
     <row r="18" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A18" s="40" t="str">
+      <c r="A18" s="41" t="str">
         <f t="shared" si="1"/>
         <v>1012002</v>
       </c>
-      <c r="B18" s="41">
+      <c r="B18" s="42">
         <v>101200</v>
       </c>
-      <c r="C18" s="41">
+      <c r="C18" s="42">
         <v>2</v>
       </c>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41" t="s">
+      <c r="D18" s="42"/>
+      <c r="E18" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="41">
-        <v>1</v>
-      </c>
-      <c r="G18" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="H18" s="40">
+      <c r="F18" s="42">
+        <v>1</v>
+      </c>
+      <c r="G18" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="41">
         <v>2012001</v>
       </c>
-      <c r="I18" s="40" t="s">
-        <v>24</v>
-      </c>
-      <c r="J18" s="40"/>
-      <c r="K18" s="40"/>
-      <c r="L18" s="42">
+      <c r="I18" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="J18" s="41"/>
+      <c r="K18" s="41"/>
+      <c r="L18" s="43">
         <v>10120021</v>
       </c>
-      <c r="M18" s="40" t="s">
+      <c r="M18" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="N18" s="41">
-        <v>3</v>
-      </c>
-      <c r="O18" s="41">
-        <v>5</v>
-      </c>
-      <c r="Q18" s="43"/>
+      <c r="N18" s="42">
+        <v>3</v>
+      </c>
+      <c r="O18" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="44"/>
     </row>
     <row r="19" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A19" s="40" t="str">
+      <c r="A19" s="41" t="str">
         <f t="shared" si="1"/>
         <v>1012003</v>
       </c>
-      <c r="B19" s="41">
+      <c r="B19" s="42">
         <v>101200</v>
       </c>
-      <c r="C19" s="41">
-        <v>3</v>
-      </c>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41" t="s">
+      <c r="C19" s="42">
+        <v>3</v>
+      </c>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="F19" s="41">
-        <v>1</v>
-      </c>
-      <c r="G19" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="H19" s="40">
+      <c r="F19" s="42">
+        <v>1</v>
+      </c>
+      <c r="G19" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="41">
         <v>2012001</v>
       </c>
-      <c r="I19" s="40" t="s">
-        <v>24</v>
-      </c>
-      <c r="J19" s="40" t="s">
+      <c r="I19" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="J19" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="K19" s="40" t="s">
+      <c r="K19" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="L19" s="42"/>
-      <c r="M19" s="40" t="s">
+      <c r="L19" s="43"/>
+      <c r="M19" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="N19" s="41">
-        <v>3</v>
-      </c>
-      <c r="O19" s="41">
-        <v>5</v>
-      </c>
-      <c r="Q19" s="43"/>
+      <c r="N19" s="42">
+        <v>3</v>
+      </c>
+      <c r="O19" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q19" s="44"/>
     </row>
     <row r="20" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A20" s="34" t="str">
+      <c r="A20" s="35" t="str">
         <f t="shared" si="1"/>
         <v>1014001</v>
       </c>
-      <c r="B20" s="26">
+      <c r="B20" s="27">
         <v>101400</v>
       </c>
-      <c r="C20" s="26">
-        <v>1</v>
-      </c>
-      <c r="D20" s="26" t="s">
+      <c r="C20" s="27">
+        <v>1</v>
+      </c>
+      <c r="D20" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="E20" s="26" t="s">
+      <c r="E20" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="F20" s="26">
-        <v>1</v>
-      </c>
-      <c r="G20" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="H20" s="34">
+      <c r="F20" s="27">
+        <v>1</v>
+      </c>
+      <c r="G20" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="35">
         <v>2014001</v>
       </c>
-      <c r="I20" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="J20" s="34"/>
-      <c r="K20" s="34"/>
-      <c r="L20" s="35" t="s">
+      <c r="I20" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="J20" s="35"/>
+      <c r="K20" s="35"/>
+      <c r="L20" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="M20" s="34" t="s">
+      <c r="M20" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="N20" s="17">
+      <c r="N20" s="18">
         <v>4</v>
       </c>
-      <c r="O20" s="17">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="44"/>
+      <c r="O20" s="18">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="45"/>
     </row>
     <row r="21" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A21" s="34" t="str">
+      <c r="A21" s="35" t="str">
         <f t="shared" si="1"/>
         <v>1014002</v>
       </c>
-      <c r="B21" s="26">
+      <c r="B21" s="27">
         <v>101400</v>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="27">
         <v>2</v>
       </c>
-      <c r="D21" s="26" t="s">
+      <c r="D21" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="E21" s="26" t="s">
+      <c r="E21" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="26">
-        <v>1</v>
-      </c>
-      <c r="G21" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="H21" s="34">
+      <c r="F21" s="27">
+        <v>1</v>
+      </c>
+      <c r="G21" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="35">
         <v>2014001</v>
       </c>
-      <c r="I21" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="J21" s="34"/>
-      <c r="K21" s="34"/>
-      <c r="L21" s="35" t="s">
+      <c r="I21" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="J21" s="35"/>
+      <c r="K21" s="35"/>
+      <c r="L21" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="M21" s="34" t="s">
+      <c r="M21" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="N21" s="17">
+      <c r="N21" s="18">
         <v>4</v>
       </c>
-      <c r="O21" s="17">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="44"/>
+      <c r="O21" s="18">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="45"/>
     </row>
     <row r="22" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A22" s="34" t="str">
+      <c r="A22" s="35" t="str">
         <f t="shared" si="1"/>
         <v>1014003</v>
       </c>
-      <c r="B22" s="26">
+      <c r="B22" s="27">
         <v>101400</v>
       </c>
-      <c r="C22" s="26">
-        <v>3</v>
-      </c>
-      <c r="D22" s="26" t="s">
+      <c r="C22" s="27">
+        <v>3</v>
+      </c>
+      <c r="D22" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="E22" s="26" t="s">
+      <c r="E22" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="F22" s="26">
-        <v>1</v>
-      </c>
-      <c r="G22" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="H22" s="34">
+      <c r="F22" s="27">
+        <v>1</v>
+      </c>
+      <c r="G22" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="35">
         <v>2014001</v>
       </c>
-      <c r="I22" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="J22" s="34"/>
-      <c r="K22" s="34"/>
-      <c r="L22" s="35">
+      <c r="I22" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="36">
         <v>10140021</v>
       </c>
-      <c r="M22" s="34" t="s">
+      <c r="M22" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="N22" s="17">
+      <c r="N22" s="18">
         <v>4</v>
       </c>
-      <c r="O22" s="17">
-        <v>3</v>
-      </c>
-      <c r="Q22" s="44"/>
+      <c r="O22" s="18">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="45"/>
     </row>
     <row r="23" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A23" s="24" t="str">
+      <c r="A23" s="25" t="str">
         <f t="shared" si="1"/>
         <v>1024001</v>
       </c>
-      <c r="B23" s="25">
+      <c r="B23" s="26">
         <v>102400</v>
       </c>
-      <c r="C23" s="25">
-        <v>1</v>
-      </c>
-      <c r="D23" s="25" t="s">
+      <c r="C23" s="26">
+        <v>1</v>
+      </c>
+      <c r="D23" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="E23" s="26" t="s">
+      <c r="E23" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="F23" s="25">
-        <v>1</v>
-      </c>
-      <c r="G23" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H23" s="24">
+      <c r="F23" s="26">
+        <v>1</v>
+      </c>
+      <c r="G23" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="25">
         <v>2024001</v>
       </c>
-      <c r="I23" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="27" t="s">
+      <c r="I23" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J23" s="25"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="M23" s="24" t="s">
+      <c r="M23" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="N23" s="17">
+      <c r="N23" s="18">
         <v>4</v>
       </c>
-      <c r="O23" s="17">
+      <c r="O23" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A24" s="24" t="str">
+      <c r="A24" s="25" t="str">
         <f t="shared" si="1"/>
         <v>1024002</v>
       </c>
-      <c r="B24" s="25">
+      <c r="B24" s="26">
         <v>102400</v>
       </c>
-      <c r="C24" s="25">
+      <c r="C24" s="26">
         <v>2</v>
       </c>
-      <c r="D24" s="25"/>
-      <c r="E24" s="28" t="s">
+      <c r="D24" s="26"/>
+      <c r="E24" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="25">
-        <v>1</v>
-      </c>
-      <c r="G24" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H24" s="24">
+      <c r="F24" s="26">
+        <v>1</v>
+      </c>
+      <c r="G24" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" s="25">
         <v>2024001</v>
       </c>
-      <c r="I24" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="J24" s="24"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="29" t="s">
+      <c r="I24" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="M24" s="24" t="s">
+      <c r="M24" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="N24" s="17">
+      <c r="N24" s="18">
         <v>4</v>
       </c>
-      <c r="O24" s="17">
+      <c r="O24" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A25" s="24" t="str">
+      <c r="A25" s="25" t="str">
         <f t="shared" si="1"/>
         <v>1024003</v>
       </c>
-      <c r="B25" s="25">
+      <c r="B25" s="26">
         <v>102400</v>
       </c>
-      <c r="C25" s="25">
-        <v>3</v>
-      </c>
-      <c r="D25" s="25"/>
-      <c r="E25" s="30" t="s">
+      <c r="C25" s="26">
+        <v>3</v>
+      </c>
+      <c r="D25" s="26"/>
+      <c r="E25" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="F25" s="25">
-        <v>1</v>
-      </c>
-      <c r="G25" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H25" s="24">
+      <c r="F25" s="26">
+        <v>1</v>
+      </c>
+      <c r="G25" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="25">
         <v>2024001</v>
       </c>
-      <c r="I25" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="J25" s="24"/>
-      <c r="K25" s="24"/>
-      <c r="L25" s="27" t="s">
+      <c r="I25" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J25" s="25"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="M25" s="24" t="s">
+      <c r="M25" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="N25" s="17">
+      <c r="N25" s="18">
         <v>4</v>
       </c>
-      <c r="O25" s="17">
+      <c r="O25" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A26" s="24" t="str">
+      <c r="A26" s="25" t="str">
         <f t="shared" si="1"/>
         <v>1024004</v>
       </c>
-      <c r="B26" s="25">
+      <c r="B26" s="26">
         <v>102400</v>
       </c>
-      <c r="C26" s="25">
+      <c r="C26" s="26">
         <v>4</v>
       </c>
-      <c r="D26" s="25"/>
-      <c r="E26" s="31" t="s">
+      <c r="D26" s="26"/>
+      <c r="E26" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="F26" s="32">
-        <v>1</v>
-      </c>
-      <c r="G26" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H26" s="24">
+      <c r="F26" s="33">
+        <v>1</v>
+      </c>
+      <c r="G26" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="25">
         <v>2024001</v>
       </c>
-      <c r="I26" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="J26" s="24"/>
-      <c r="K26" s="24"/>
-      <c r="L26" s="27">
+      <c r="I26" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J26" s="25"/>
+      <c r="K26" s="25"/>
+      <c r="L26" s="28">
         <v>10240041</v>
       </c>
-      <c r="M26" s="24" t="s">
+      <c r="M26" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="N26" s="17">
+      <c r="N26" s="18">
         <v>4</v>
       </c>
-      <c r="O26" s="17">
+      <c r="O26" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A27" s="24" t="str">
+      <c r="A27" s="25" t="str">
         <f t="shared" si="1"/>
         <v>1024005</v>
       </c>
-      <c r="B27" s="25">
+      <c r="B27" s="26">
         <v>102400</v>
       </c>
-      <c r="C27" s="25">
-        <v>5</v>
-      </c>
-      <c r="D27" s="25"/>
-      <c r="E27" s="33" t="s">
+      <c r="C27" s="26">
+        <v>5</v>
+      </c>
+      <c r="D27" s="26"/>
+      <c r="E27" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="F27" s="32">
-        <v>1</v>
-      </c>
-      <c r="G27" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H27" s="24">
+      <c r="F27" s="33">
+        <v>1</v>
+      </c>
+      <c r="G27" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H27" s="25">
         <v>2024001</v>
       </c>
-      <c r="I27" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="J27" s="24"/>
-      <c r="K27" s="24"/>
-      <c r="L27" s="27" t="s">
+      <c r="I27" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J27" s="25"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="M27" s="24" t="s">
+      <c r="M27" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N27" s="17">
+      <c r="N27" s="18">
         <v>4</v>
       </c>
-      <c r="O27" s="17">
+      <c r="O27" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A28" s="24" t="str">
+      <c r="A28" s="25" t="str">
         <f t="shared" si="1"/>
         <v>1024006</v>
       </c>
-      <c r="B28" s="25">
+      <c r="B28" s="26">
         <v>102400</v>
       </c>
-      <c r="C28" s="25">
+      <c r="C28" s="26">
         <v>6</v>
       </c>
-      <c r="D28" s="25"/>
-      <c r="E28" s="33" t="s">
+      <c r="D28" s="26"/>
+      <c r="E28" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="F28" s="32">
-        <v>1</v>
-      </c>
-      <c r="G28" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H28" s="24">
+      <c r="F28" s="33">
+        <v>1</v>
+      </c>
+      <c r="G28" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28" s="25">
         <v>2024001</v>
       </c>
-      <c r="I28" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="J28" s="24"/>
-      <c r="K28" s="24"/>
-      <c r="L28" s="27">
+      <c r="I28" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J28" s="25"/>
+      <c r="K28" s="25"/>
+      <c r="L28" s="28">
         <v>10240061</v>
       </c>
-      <c r="M28" s="24" t="s">
+      <c r="M28" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="N28" s="17">
+      <c r="N28" s="18">
         <v>4</v>
       </c>
-      <c r="O28" s="17">
+      <c r="O28" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A29" s="24" t="str">
+      <c r="A29" s="25" t="str">
         <f t="shared" si="1"/>
         <v>1024007</v>
       </c>
-      <c r="B29" s="25">
+      <c r="B29" s="26">
         <v>102400</v>
       </c>
-      <c r="C29" s="25">
+      <c r="C29" s="26">
         <v>7</v>
       </c>
-      <c r="D29" s="25"/>
-      <c r="E29" s="28" t="s">
+      <c r="D29" s="26"/>
+      <c r="E29" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="F29" s="25">
-        <v>1</v>
-      </c>
-      <c r="G29" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H29" s="24">
+      <c r="F29" s="26">
+        <v>1</v>
+      </c>
+      <c r="G29" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H29" s="25">
         <v>2024001</v>
       </c>
-      <c r="I29" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="J29" s="24"/>
-      <c r="K29" s="24"/>
-      <c r="L29" s="29" t="s">
+      <c r="I29" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J29" s="25"/>
+      <c r="K29" s="25"/>
+      <c r="L29" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="M29" s="24" t="s">
+      <c r="M29" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="N29" s="17">
+      <c r="N29" s="18">
         <v>4</v>
       </c>
-      <c r="O29" s="17">
+      <c r="O29" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="30" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A30" s="24" t="str">
+      <c r="A30" s="25" t="str">
         <f t="shared" si="1"/>
         <v>1017001</v>
       </c>
@@ -3144,16 +3243,16 @@
       <c r="M30" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="N30" s="45">
+      <c r="N30" s="46">
         <v>4</v>
       </c>
-      <c r="O30" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q30" s="18"/>
+      <c r="O30" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q30" s="19"/>
     </row>
     <row r="31" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A31" s="24" t="str">
+      <c r="A31" s="25" t="str">
         <f t="shared" ref="A31:A53" si="2">B31&amp;C31</f>
         <v>1017002</v>
       </c>
@@ -3187,16 +3286,16 @@
       <c r="M31" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="N31" s="45">
+      <c r="N31" s="46">
         <v>4</v>
       </c>
-      <c r="O31" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q31" s="18"/>
+      <c r="O31" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q31" s="19"/>
     </row>
     <row r="32" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A32" s="24" t="str">
+      <c r="A32" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1017003</v>
       </c>
@@ -3230,16 +3329,16 @@
       <c r="M32" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N32" s="45">
+      <c r="N32" s="46">
         <v>4</v>
       </c>
-      <c r="O32" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q32" s="18"/>
+      <c r="O32" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="19"/>
     </row>
     <row r="33" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A33" s="24" t="str">
+      <c r="A33" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1022001</v>
       </c>
@@ -3267,22 +3366,22 @@
       <c r="I33" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L33" s="46" t="s">
+      <c r="L33" s="47" t="s">
         <v>85</v>
       </c>
       <c r="M33" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N33" s="45">
-        <v>3</v>
-      </c>
-      <c r="O33" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q33" s="18"/>
+      <c r="N33" s="46">
+        <v>3</v>
+      </c>
+      <c r="O33" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q33" s="19"/>
     </row>
     <row r="34" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A34" s="24" t="str">
+      <c r="A34" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1022002</v>
       </c>
@@ -3298,10 +3397,10 @@
       <c r="E34" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="F34" s="17">
-        <v>1</v>
-      </c>
-      <c r="G34" s="47" t="s">
+      <c r="F34" s="18">
+        <v>1</v>
+      </c>
+      <c r="G34" s="48" t="s">
         <v>23</v>
       </c>
       <c r="H34" s="5">
@@ -3310,22 +3409,22 @@
       <c r="I34" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L34" s="46">
+      <c r="L34" s="47">
         <v>10220033</v>
       </c>
       <c r="M34" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N34" s="45">
-        <v>3</v>
-      </c>
-      <c r="O34" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q34" s="18"/>
+      <c r="N34" s="46">
+        <v>3</v>
+      </c>
+      <c r="O34" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q34" s="19"/>
     </row>
     <row r="35" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A35" s="24" t="str">
+      <c r="A35" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1022003</v>
       </c>
@@ -3341,10 +3440,10 @@
       <c r="E35" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F35" s="47">
-        <v>1</v>
-      </c>
-      <c r="G35" s="47" t="s">
+      <c r="F35" s="48">
+        <v>1</v>
+      </c>
+      <c r="G35" s="48" t="s">
         <v>23</v>
       </c>
       <c r="H35" s="5">
@@ -3353,22 +3452,22 @@
       <c r="I35" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L35" s="48" t="s">
+      <c r="L35" s="49" t="s">
         <v>89</v>
       </c>
       <c r="M35" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N35" s="45">
-        <v>3</v>
-      </c>
-      <c r="O35" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q35" s="18"/>
+      <c r="N35" s="46">
+        <v>3</v>
+      </c>
+      <c r="O35" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q35" s="19"/>
     </row>
     <row r="36" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A36" s="24" t="str">
+      <c r="A36" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1022004</v>
       </c>
@@ -3384,10 +3483,10 @@
       <c r="E36" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F36" s="17">
-        <v>1</v>
-      </c>
-      <c r="G36" s="47" t="s">
+      <c r="F36" s="18">
+        <v>1</v>
+      </c>
+      <c r="G36" s="48" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="5">
@@ -3396,19 +3495,19 @@
       <c r="I36" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L36" s="46">
+      <c r="L36" s="47">
         <v>10220020</v>
       </c>
-      <c r="N36" s="45">
-        <v>3</v>
-      </c>
-      <c r="O36" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q36" s="18"/>
+      <c r="N36" s="46">
+        <v>3</v>
+      </c>
+      <c r="O36" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q36" s="19"/>
     </row>
     <row r="37" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A37" s="24" t="str">
+      <c r="A37" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1022005</v>
       </c>
@@ -3436,20 +3535,20 @@
       <c r="I37" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L37" s="46">
+      <c r="L37" s="47">
         <v>10220019</v>
       </c>
-      <c r="N37" s="45">
-        <v>3</v>
-      </c>
-      <c r="O37" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q37" s="18"/>
-      <c r="S37" s="49"/>
+      <c r="N37" s="46">
+        <v>3</v>
+      </c>
+      <c r="O37" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q37" s="19"/>
+      <c r="S37" s="50"/>
     </row>
     <row r="38" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A38" s="24" t="str">
+      <c r="A38" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1021001</v>
       </c>
@@ -3477,23 +3576,23 @@
       <c r="I38" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L38" s="46" t="s">
+      <c r="L38" s="47" t="s">
         <v>93</v>
       </c>
       <c r="M38" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N38" s="45">
-        <v>3</v>
-      </c>
-      <c r="O38" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q38" s="18"/>
-      <c r="S38" s="49"/>
+      <c r="N38" s="46">
+        <v>3</v>
+      </c>
+      <c r="O38" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q38" s="19"/>
+      <c r="S38" s="50"/>
     </row>
     <row r="39" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A39" s="24" t="str">
+      <c r="A39" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1021002</v>
       </c>
@@ -3521,23 +3620,23 @@
       <c r="I39" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L39" s="46">
+      <c r="L39" s="47">
         <v>10210031</v>
       </c>
       <c r="M39" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N39" s="45">
-        <v>3</v>
-      </c>
-      <c r="O39" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q39" s="18"/>
-      <c r="S39" s="49"/>
+      <c r="N39" s="46">
+        <v>3</v>
+      </c>
+      <c r="O39" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q39" s="19"/>
+      <c r="S39" s="50"/>
     </row>
     <row r="40" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A40" s="24" t="str">
+      <c r="A40" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1021003</v>
       </c>
@@ -3565,23 +3664,23 @@
       <c r="I40" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L40" s="46">
+      <c r="L40" s="47">
         <v>10210041</v>
       </c>
       <c r="M40" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="N40" s="45">
-        <v>3</v>
-      </c>
-      <c r="O40" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q40" s="18"/>
-      <c r="S40" s="49"/>
+      <c r="N40" s="46">
+        <v>3</v>
+      </c>
+      <c r="O40" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q40" s="19"/>
+      <c r="S40" s="50"/>
     </row>
     <row r="41" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A41" s="24" t="str">
+      <c r="A41" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1021004</v>
       </c>
@@ -3609,23 +3708,23 @@
       <c r="I41" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L41" s="46" t="s">
+      <c r="L41" s="47" t="s">
         <v>96</v>
       </c>
       <c r="M41" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N41" s="45">
-        <v>3</v>
-      </c>
-      <c r="O41" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q41" s="18"/>
-      <c r="S41" s="49"/>
+      <c r="N41" s="46">
+        <v>3</v>
+      </c>
+      <c r="O41" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q41" s="19"/>
+      <c r="S41" s="50"/>
     </row>
     <row r="42" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A42" s="24" t="str">
+      <c r="A42" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1018001</v>
       </c>
@@ -3653,20 +3752,20 @@
       <c r="I42" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L42" s="46" t="s">
+      <c r="L42" s="47" t="s">
         <v>98</v>
       </c>
       <c r="M42" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N42" s="45">
+      <c r="N42" s="46">
         <v>4</v>
       </c>
-      <c r="O42" s="45">
+      <c r="O42" s="46">
         <v>6</v>
       </c>
-      <c r="Q42" s="18"/>
-      <c r="S42" s="49"/>
+      <c r="Q42" s="19"/>
+      <c r="S42" s="50"/>
     </row>
     <row r="43" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A43" s="5" t="str">
@@ -3697,16 +3796,16 @@
       <c r="I43" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L43" s="46">
+      <c r="L43" s="47">
         <v>10180031</v>
       </c>
       <c r="M43" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N43" s="45">
+      <c r="N43" s="46">
         <v>4</v>
       </c>
-      <c r="O43" s="45">
+      <c r="O43" s="46">
         <v>6</v>
       </c>
     </row>
@@ -3739,16 +3838,16 @@
       <c r="I44" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L44" s="46" t="s">
+      <c r="L44" s="47" t="s">
         <v>99</v>
       </c>
       <c r="M44" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N44" s="45">
+      <c r="N44" s="46">
         <v>4</v>
       </c>
-      <c r="O44" s="45">
+      <c r="O44" s="46">
         <v>6</v>
       </c>
     </row>
@@ -3781,19 +3880,19 @@
       <c r="I45" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L45" s="46" t="s">
+      <c r="L45" s="47" t="s">
         <v>101</v>
       </c>
       <c r="M45" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N45" s="45">
-        <v>3</v>
-      </c>
-      <c r="O45" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q45" s="8"/>
+      <c r="N45" s="46">
+        <v>3</v>
+      </c>
+      <c r="O45" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q45" s="9"/>
     </row>
     <row r="46" customFormat="1" ht="16.5" spans="1:19">
       <c r="A46" s="5" t="str">
@@ -3824,19 +3923,19 @@
       <c r="I46" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L46" s="46">
+      <c r="L46" s="47">
         <v>10250031</v>
       </c>
       <c r="M46" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="N46" s="45">
-        <v>3</v>
-      </c>
-      <c r="O46" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q46" s="8"/>
+      <c r="N46" s="46">
+        <v>3</v>
+      </c>
+      <c r="O46" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q46" s="9"/>
     </row>
     <row r="47" customFormat="1" ht="16.5" spans="1:19">
       <c r="A47" s="5" t="str">
@@ -3867,19 +3966,19 @@
       <c r="I47" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L47" s="46" t="s">
+      <c r="L47" s="47" t="s">
         <v>103</v>
       </c>
       <c r="M47" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N47" s="45">
-        <v>3</v>
-      </c>
-      <c r="O47" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q47" s="8"/>
+      <c r="N47" s="46">
+        <v>3</v>
+      </c>
+      <c r="O47" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q47" s="9"/>
     </row>
     <row r="48" customFormat="1" ht="16.5" spans="1:19">
       <c r="A48" s="5" t="str">
@@ -3910,19 +4009,19 @@
       <c r="I48" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L48" s="46" t="s">
+      <c r="L48" s="47" t="s">
         <v>105</v>
       </c>
       <c r="M48" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N48" s="45">
+      <c r="N48" s="46">
         <v>4</v>
       </c>
-      <c r="O48" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q48" s="8"/>
+      <c r="O48" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q48" s="9"/>
     </row>
     <row r="49" customFormat="1" ht="16.5" spans="1:17">
       <c r="A49" s="5" t="str">
@@ -3953,19 +4052,19 @@
       <c r="I49" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L49" s="46">
+      <c r="L49" s="47">
         <v>10230003</v>
       </c>
       <c r="M49" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="N49" s="45">
+      <c r="N49" s="46">
         <v>4</v>
       </c>
-      <c r="O49" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q49" s="8"/>
+      <c r="O49" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q49" s="9"/>
     </row>
     <row r="50" customFormat="1" ht="16.5" spans="1:17">
       <c r="A50" s="5" t="str">
@@ -3996,19 +4095,19 @@
       <c r="I50" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L50" s="46" t="s">
+      <c r="L50" s="47" t="s">
         <v>106</v>
       </c>
       <c r="M50" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N50" s="45">
+      <c r="N50" s="46">
         <v>4</v>
       </c>
-      <c r="O50" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q50" s="8"/>
+      <c r="O50" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q50" s="9"/>
     </row>
     <row r="51" customFormat="1" ht="16.5" spans="1:17">
       <c r="A51" s="5" t="str">
@@ -4039,19 +4138,19 @@
       <c r="I51" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L51" s="46">
+      <c r="L51" s="47">
         <v>10340007</v>
       </c>
       <c r="M51" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="N51" s="45">
-        <v>3</v>
-      </c>
-      <c r="O51" s="45">
-        <v>3</v>
-      </c>
-      <c r="Q51" s="8"/>
+      <c r="N51" s="46">
+        <v>3</v>
+      </c>
+      <c r="O51" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q51" s="9"/>
     </row>
     <row r="52" customFormat="1" ht="16.5" spans="1:17">
       <c r="A52" s="5" t="str">
@@ -4082,20 +4181,20 @@
       <c r="I52" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L52" s="46"/>
+      <c r="L52" s="47"/>
       <c r="M52" s="5"/>
-      <c r="N52" s="45">
-        <v>3</v>
-      </c>
-      <c r="O52" s="45">
-        <v>3</v>
-      </c>
-      <c r="P52" s="50"/>
-      <c r="Q52" s="8"/>
-    </row>
-    <row r="53" s="6" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N52" s="46">
+        <v>3</v>
+      </c>
+      <c r="O52" s="46">
+        <v>3</v>
+      </c>
+      <c r="P52" s="51"/>
+      <c r="Q52" s="9"/>
+    </row>
+    <row r="53" customFormat="1" ht="16.5" spans="1:17">
       <c r="A53" s="5" t="str">
-        <f>B53&amp;C53</f>
+        <f t="shared" si="2"/>
         <v>1034003</v>
       </c>
       <c r="B53" s="5">
@@ -4110,7 +4209,7 @@
       <c r="E53" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F53" s="51">
+      <c r="F53" s="5">
         <v>1</v>
       </c>
       <c r="G53" s="5" t="s">
@@ -4122,62 +4221,62 @@
       <c r="I53" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L53" s="48"/>
-      <c r="M53" s="51"/>
-      <c r="N53" s="45">
-        <v>3</v>
-      </c>
-      <c r="O53" s="45">
-        <v>3</v>
-      </c>
-      <c r="Q53" s="52"/>
-    </row>
-    <row r="54" s="6" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A54" s="51" t="str">
-        <f>B54&amp;C54</f>
+      <c r="L53" s="47"/>
+      <c r="M53" s="5"/>
+      <c r="N53" s="46">
+        <v>3</v>
+      </c>
+      <c r="O53" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q53" s="9"/>
+    </row>
+    <row r="54" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A54" s="5" t="str">
+        <f t="shared" ref="A54:A77" si="3">B54&amp;C54</f>
         <v>1035001</v>
       </c>
-      <c r="B54" s="51">
+      <c r="B54" s="5">
         <v>103500</v>
       </c>
-      <c r="C54" s="51">
-        <v>1</v>
-      </c>
-      <c r="D54" s="51" t="s">
+      <c r="C54" s="5">
+        <v>1</v>
+      </c>
+      <c r="D54" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="E54" s="51" t="s">
+      <c r="E54" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="F54" s="51">
-        <v>1</v>
-      </c>
-      <c r="G54" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="H54" s="51">
+      <c r="F54" s="5">
+        <v>1</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H54" s="5">
         <v>2035001</v>
       </c>
-      <c r="I54" s="51" t="s">
-        <v>24</v>
-      </c>
-      <c r="L54" s="48" t="s">
+      <c r="I54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L54" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="M54" s="51" t="s">
+      <c r="M54" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="N54" s="45">
+      <c r="N54" s="46">
         <v>4</v>
       </c>
-      <c r="O54" s="45">
-        <v>3</v>
-      </c>
-      <c r="Q54" s="52"/>
+      <c r="O54" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="9"/>
     </row>
     <row r="55" customFormat="1" ht="16.5" spans="1:17">
       <c r="A55" s="5" t="str">
-        <f t="shared" ref="A54:A62" si="3">B55&amp;C55</f>
+        <f t="shared" si="3"/>
         <v>1035002</v>
       </c>
       <c r="B55" s="5">
@@ -4204,19 +4303,19 @@
       <c r="I55" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L55" s="46" t="s">
+      <c r="L55" s="47" t="s">
         <v>115</v>
       </c>
       <c r="M55" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="N55" s="45">
+      <c r="N55" s="46">
         <v>4</v>
       </c>
-      <c r="O55" s="45">
-        <v>3</v>
-      </c>
-      <c r="Q55" s="8"/>
+      <c r="O55" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q55" s="9"/>
     </row>
     <row r="56" customFormat="1" ht="16.5" spans="1:17">
       <c r="A56" s="5" t="str">
@@ -4247,22 +4346,23 @@
       <c r="I56" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L56" s="46" t="s">
+      <c r="L56" s="47" t="s">
         <v>117</v>
       </c>
       <c r="M56" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="N56" s="45">
+      <c r="N56" s="46">
         <v>4</v>
       </c>
-      <c r="O56" s="45">
-        <v>3</v>
-      </c>
-      <c r="Q56" s="8"/>
+      <c r="O56" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q56" s="9"/>
     </row>
     <row r="57" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A57" s="53">
+      <c r="A57" s="5" t="str">
+        <f t="shared" si="3"/>
         <v>1035011</v>
       </c>
       <c r="B57" s="5">
@@ -4289,19 +4389,19 @@
       <c r="I57" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L57" s="46" t="s">
+      <c r="L57" s="47" t="s">
         <v>120</v>
       </c>
       <c r="M57" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="N57" s="45">
+      <c r="N57" s="46">
         <v>4</v>
       </c>
-      <c r="O57" s="45">
-        <v>3</v>
-      </c>
-      <c r="Q57" s="8"/>
+      <c r="O57" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="9"/>
     </row>
     <row r="58" customFormat="1" ht="16.5" spans="1:17">
       <c r="A58" s="5" t="str">
@@ -4332,19 +4432,19 @@
       <c r="I58" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L58" s="46" t="s">
+      <c r="L58" s="47" t="s">
         <v>121</v>
       </c>
       <c r="M58" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="N58" s="45">
+      <c r="N58" s="46">
         <v>4</v>
       </c>
-      <c r="O58" s="45">
-        <v>3</v>
-      </c>
-      <c r="Q58" s="8"/>
+      <c r="O58" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="9"/>
     </row>
     <row r="59" customFormat="1" ht="16.5" spans="1:17">
       <c r="A59" s="5" t="str">
@@ -4375,19 +4475,19 @@
       <c r="I59" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L59" s="46" t="s">
+      <c r="L59" s="47" t="s">
         <v>122</v>
       </c>
       <c r="M59" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="N59" s="45">
+      <c r="N59" s="46">
         <v>4</v>
       </c>
-      <c r="O59" s="45">
-        <v>3</v>
-      </c>
-      <c r="Q59" s="8"/>
+      <c r="O59" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="9"/>
     </row>
     <row r="60" customFormat="1" ht="16.5" spans="1:17">
       <c r="A60" s="5" t="str">
@@ -4418,19 +4518,19 @@
       <c r="I60" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L60" s="46" t="s">
+      <c r="L60" s="47" t="s">
         <v>124</v>
       </c>
       <c r="M60" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="N60" s="45">
-        <v>3</v>
-      </c>
-      <c r="O60" s="45">
-        <v>3</v>
-      </c>
-      <c r="Q60" s="8"/>
+      <c r="N60" s="46">
+        <v>3</v>
+      </c>
+      <c r="O60" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="9"/>
     </row>
     <row r="61" customFormat="1" ht="16.5" spans="1:17">
       <c r="A61" s="5" t="str">
@@ -4461,19 +4561,19 @@
       <c r="I61" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L61" s="46">
+      <c r="L61" s="47">
         <v>10360004</v>
       </c>
       <c r="M61" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="N61" s="45">
-        <v>3</v>
-      </c>
-      <c r="O61" s="45">
-        <v>3</v>
-      </c>
-      <c r="Q61" s="8"/>
+      <c r="N61" s="46">
+        <v>3</v>
+      </c>
+      <c r="O61" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q61" s="9"/>
     </row>
     <row r="62" customFormat="1" ht="16.5" spans="1:17">
       <c r="A62" s="5" t="str">
@@ -4504,211 +4604,660 @@
       <c r="I62" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L62" s="46">
+      <c r="L62" s="47">
         <v>10360002</v>
       </c>
       <c r="M62" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="N62" s="45">
-        <v>3</v>
-      </c>
-      <c r="O62" s="45">
-        <v>3</v>
-      </c>
-      <c r="Q62" s="8"/>
+      <c r="N62" s="46">
+        <v>3</v>
+      </c>
+      <c r="O62" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="9"/>
     </row>
     <row r="63" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A63" s="5"/>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
-      <c r="H63" s="5"/>
-      <c r="I63" s="5"/>
-      <c r="L63" s="46"/>
-      <c r="M63" s="5"/>
-      <c r="N63" s="45"/>
-      <c r="O63" s="45"/>
-      <c r="Q63" s="8"/>
+      <c r="A63" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1028001</v>
+      </c>
+      <c r="B63" s="5">
+        <v>102800</v>
+      </c>
+      <c r="C63" s="5">
+        <v>1</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F63" s="5">
+        <v>1</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H63" s="5">
+        <v>2028001</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L63" s="47" t="s">
+        <v>129</v>
+      </c>
+      <c r="M63" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="N63" s="46">
+        <v>5</v>
+      </c>
+      <c r="O63" s="46">
+        <v>6</v>
+      </c>
+      <c r="Q63" s="9"/>
     </row>
     <row r="64" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A64" s="5"/>
-      <c r="B64" s="5"/>
-      <c r="C64" s="5"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
-      <c r="G64" s="5"/>
-      <c r="H64" s="5"/>
-      <c r="I64" s="5"/>
-      <c r="L64" s="46"/>
-      <c r="M64" s="5"/>
-      <c r="N64" s="45"/>
-      <c r="O64" s="45"/>
-      <c r="Q64" s="8"/>
+      <c r="A64" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1028002</v>
+      </c>
+      <c r="B64" s="5">
+        <v>102800</v>
+      </c>
+      <c r="C64" s="5">
+        <v>2</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F64" s="5">
+        <v>1</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H64" s="5">
+        <v>2028001</v>
+      </c>
+      <c r="I64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L64" s="47">
+        <v>10280002</v>
+      </c>
+      <c r="M64" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="N64" s="46">
+        <v>5</v>
+      </c>
+      <c r="O64" s="46">
+        <v>6</v>
+      </c>
+      <c r="Q64" s="9"/>
     </row>
     <row r="65" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A65" s="5"/>
-      <c r="B65" s="5"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="5"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="5"/>
-      <c r="H65" s="5"/>
-      <c r="I65" s="5"/>
-      <c r="L65" s="46"/>
-      <c r="M65" s="5"/>
-      <c r="N65" s="45"/>
-      <c r="O65" s="45"/>
-      <c r="Q65" s="8"/>
+      <c r="A65" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1028003</v>
+      </c>
+      <c r="B65" s="5">
+        <v>102800</v>
+      </c>
+      <c r="C65" s="5">
+        <v>3</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F65" s="5">
+        <v>1</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H65" s="5">
+        <v>2028001</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L65" s="47" t="s">
+        <v>132</v>
+      </c>
+      <c r="M65" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="N65" s="46">
+        <v>5</v>
+      </c>
+      <c r="O65" s="46">
+        <v>6</v>
+      </c>
+      <c r="Q65" s="9"/>
     </row>
     <row r="66" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A66" s="5"/>
-      <c r="B66" s="5"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="5"/>
-      <c r="E66" s="5"/>
-      <c r="F66" s="5"/>
-      <c r="G66" s="5"/>
-      <c r="H66" s="5"/>
-      <c r="I66" s="5"/>
-      <c r="L66" s="46"/>
-      <c r="M66" s="5"/>
-      <c r="N66" s="45"/>
-      <c r="O66" s="45"/>
-      <c r="Q66" s="8"/>
+      <c r="A66" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1034011</v>
+      </c>
+      <c r="B66" s="5">
+        <v>103401</v>
+      </c>
+      <c r="C66" s="5">
+        <v>1</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F66" s="5">
+        <v>1</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H66" s="5">
+        <v>2034011</v>
+      </c>
+      <c r="I66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L66" s="47">
+        <v>10340007</v>
+      </c>
+      <c r="M66" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="N66" s="46">
+        <v>3</v>
+      </c>
+      <c r="O66" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="9"/>
     </row>
     <row r="67" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A67" s="5"/>
-      <c r="B67" s="5"/>
-      <c r="C67" s="5"/>
-      <c r="D67" s="5"/>
-      <c r="E67" s="5"/>
-      <c r="F67" s="5"/>
-      <c r="G67" s="5"/>
-      <c r="H67" s="5"/>
-      <c r="I67" s="5"/>
-      <c r="L67" s="46"/>
+      <c r="A67" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1034012</v>
+      </c>
+      <c r="B67" s="5">
+        <v>103401</v>
+      </c>
+      <c r="C67" s="5">
+        <v>2</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F67" s="5">
+        <v>1</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H67" s="5">
+        <v>2034011</v>
+      </c>
+      <c r="I67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L67" s="47"/>
       <c r="M67" s="5"/>
-      <c r="N67" s="45"/>
-      <c r="O67" s="45"/>
-      <c r="Q67" s="8"/>
-    </row>
-    <row r="68" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A68" s="5"/>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="5"/>
-      <c r="E68" s="5"/>
-      <c r="F68" s="5"/>
-      <c r="G68" s="5"/>
-      <c r="H68" s="5"/>
-      <c r="I68" s="5"/>
-      <c r="L68" s="46"/>
+      <c r="N67" s="46">
+        <v>3</v>
+      </c>
+      <c r="O67" s="46">
+        <v>3</v>
+      </c>
+      <c r="P67" s="51"/>
+      <c r="Q67" s="9"/>
+    </row>
+    <row r="68" s="6" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A68" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1034013</v>
+      </c>
+      <c r="B68" s="5">
+        <v>103401</v>
+      </c>
+      <c r="C68" s="5">
+        <v>3</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F68" s="5">
+        <v>1</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H68" s="5">
+        <v>2034011</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J68"/>
+      <c r="K68"/>
+      <c r="L68" s="47"/>
       <c r="M68" s="5"/>
-      <c r="N68" s="45"/>
-      <c r="O68" s="45"/>
-      <c r="Q68" s="8"/>
-    </row>
-    <row r="69" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A69" s="5"/>
-      <c r="B69" s="5"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="5"/>
-      <c r="E69" s="5"/>
-      <c r="F69" s="5"/>
-      <c r="G69" s="5"/>
-      <c r="H69" s="5"/>
-      <c r="I69" s="5"/>
-      <c r="L69" s="46"/>
-      <c r="M69" s="5"/>
-      <c r="N69" s="45"/>
-      <c r="O69" s="45"/>
-      <c r="Q69" s="8"/>
+      <c r="N68" s="46">
+        <v>4</v>
+      </c>
+      <c r="O68" s="46">
+        <v>4</v>
+      </c>
+      <c r="Q68" s="52"/>
+    </row>
+    <row r="69" s="6" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A69" s="53" t="str">
+        <f t="shared" si="3"/>
+        <v>1020001</v>
+      </c>
+      <c r="B69" s="53">
+        <v>102000</v>
+      </c>
+      <c r="C69" s="53">
+        <v>1</v>
+      </c>
+      <c r="D69" s="53" t="s">
+        <v>135</v>
+      </c>
+      <c r="E69" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="F69" s="53">
+        <v>1</v>
+      </c>
+      <c r="G69" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="H69" s="53">
+        <v>2020001</v>
+      </c>
+      <c r="I69" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="L69" s="54" t="s">
+        <v>136</v>
+      </c>
+      <c r="M69" s="53" t="s">
+        <v>137</v>
+      </c>
+      <c r="N69" s="55">
+        <v>5</v>
+      </c>
+      <c r="O69" s="55">
+        <v>5</v>
+      </c>
+      <c r="Q69" s="52"/>
     </row>
     <row r="70" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A70" s="5"/>
-      <c r="B70" s="5"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="5"/>
-      <c r="E70" s="5"/>
-      <c r="F70" s="5"/>
-      <c r="G70" s="5"/>
-      <c r="H70" s="5"/>
-      <c r="I70" s="5"/>
-      <c r="L70" s="46"/>
-      <c r="M70" s="5"/>
-      <c r="N70" s="45"/>
-      <c r="O70" s="45"/>
-      <c r="Q70" s="8"/>
+      <c r="A70" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1020002</v>
+      </c>
+      <c r="B70" s="5">
+        <v>102000</v>
+      </c>
+      <c r="C70" s="5">
+        <v>2</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F70" s="5">
+        <v>1</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H70" s="5">
+        <v>2020001</v>
+      </c>
+      <c r="I70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L70" s="47" t="s">
+        <v>138</v>
+      </c>
+      <c r="M70" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="N70" s="46">
+        <v>5</v>
+      </c>
+      <c r="O70" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q70" s="9"/>
     </row>
     <row r="71" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A71" s="5"/>
-      <c r="B71" s="5"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="5"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
-      <c r="G71" s="5"/>
-      <c r="H71" s="5"/>
-      <c r="I71" s="5"/>
-      <c r="L71" s="46"/>
-      <c r="M71" s="5"/>
-      <c r="N71" s="45"/>
-      <c r="O71" s="45"/>
-      <c r="Q71" s="8"/>
-    </row>
-    <row r="72" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A72" s="5"/>
-      <c r="B72" s="5"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
-      <c r="G72" s="5"/>
-      <c r="H72" s="5"/>
-      <c r="I72" s="5"/>
-      <c r="L72" s="46"/>
-      <c r="M72" s="5"/>
-      <c r="N72" s="45"/>
-      <c r="O72" s="45"/>
-      <c r="Q72" s="8"/>
+      <c r="A71" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1020003</v>
+      </c>
+      <c r="B71" s="5">
+        <v>102000</v>
+      </c>
+      <c r="C71" s="5">
+        <v>3</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F71" s="5">
+        <v>1</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H71" s="5">
+        <v>2020001</v>
+      </c>
+      <c r="I71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L71" s="47" t="s">
+        <v>140</v>
+      </c>
+      <c r="M71" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="N71" s="46">
+        <v>5</v>
+      </c>
+      <c r="O71" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q71" s="9"/>
+    </row>
+    <row r="72" s="7" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A72" s="56" t="str">
+        <f t="shared" si="3"/>
+        <v>1020004</v>
+      </c>
+      <c r="B72" s="56">
+        <v>102000</v>
+      </c>
+      <c r="C72" s="56">
+        <v>4</v>
+      </c>
+      <c r="D72" s="56" t="s">
+        <v>135</v>
+      </c>
+      <c r="E72" s="56" t="s">
+        <v>142</v>
+      </c>
+      <c r="F72" s="56">
+        <v>1</v>
+      </c>
+      <c r="G72" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="H72" s="56">
+        <v>2020002</v>
+      </c>
+      <c r="I72" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="L72" s="57">
+        <v>10200016</v>
+      </c>
+      <c r="M72" s="56" t="s">
+        <v>143</v>
+      </c>
+      <c r="N72" s="58">
+        <v>5</v>
+      </c>
+      <c r="O72" s="58">
+        <v>5</v>
+      </c>
+      <c r="Q72" s="59"/>
     </row>
     <row r="73" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A73" s="5"/>
-      <c r="B73" s="5"/>
-      <c r="C73" s="5"/>
-      <c r="D73" s="5"/>
-      <c r="E73" s="5"/>
-      <c r="F73" s="5"/>
-      <c r="G73" s="5"/>
-      <c r="H73" s="5"/>
-      <c r="I73" s="5"/>
-      <c r="L73" s="46"/>
-      <c r="M73" s="5"/>
-      <c r="N73" s="45"/>
-      <c r="O73" s="45"/>
-      <c r="Q73" s="8"/>
+      <c r="A73" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1020005</v>
+      </c>
+      <c r="B73" s="5">
+        <v>102000</v>
+      </c>
+      <c r="C73" s="5">
+        <v>5</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F73" s="5">
+        <v>1</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H73" s="5">
+        <v>2020003</v>
+      </c>
+      <c r="I73" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L73" s="47">
+        <v>10200021</v>
+      </c>
+      <c r="M73" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="N73" s="46">
+        <v>5</v>
+      </c>
+      <c r="O73" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q73" s="9"/>
     </row>
     <row r="74" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A74" s="5"/>
-      <c r="B74" s="5"/>
-      <c r="C74" s="5"/>
-      <c r="D74" s="5"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
-      <c r="G74" s="5"/>
-      <c r="H74" s="5"/>
-      <c r="I74" s="5"/>
-      <c r="L74" s="46"/>
-      <c r="M74" s="5"/>
-      <c r="N74" s="45"/>
-      <c r="O74" s="45"/>
-      <c r="Q74" s="8"/>
+      <c r="A74" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1038001</v>
+      </c>
+      <c r="B74" s="5">
+        <v>103800</v>
+      </c>
+      <c r="C74" s="5">
+        <v>1</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F74" s="5">
+        <v>1</v>
+      </c>
+      <c r="G74" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H74" s="5">
+        <v>2038001</v>
+      </c>
+      <c r="I74" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J74" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="L74" s="47"/>
+      <c r="M74" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="N74" s="46">
+        <v>3</v>
+      </c>
+      <c r="O74" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q74" s="9"/>
+    </row>
+    <row r="75" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A75" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1038002</v>
+      </c>
+      <c r="B75" s="5">
+        <v>103800</v>
+      </c>
+      <c r="C75" s="5">
+        <v>2</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F75" s="5">
+        <v>1</v>
+      </c>
+      <c r="G75" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H75" s="5">
+        <v>2038001</v>
+      </c>
+      <c r="I75" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L75" s="47">
+        <v>10380002</v>
+      </c>
+      <c r="M75" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="N75" s="46">
+        <v>3</v>
+      </c>
+      <c r="O75" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q75" s="9"/>
+    </row>
+    <row r="76" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A76" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1038004</v>
+      </c>
+      <c r="B76" s="5">
+        <v>103800</v>
+      </c>
+      <c r="C76" s="5">
+        <v>4</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="F76" s="5">
+        <v>1</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H76" s="5">
+        <v>2038001</v>
+      </c>
+      <c r="I76" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L76" s="47" t="s">
+        <v>151</v>
+      </c>
+      <c r="M76" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="N76" s="46">
+        <v>3</v>
+      </c>
+      <c r="O76" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q76" s="9"/>
+    </row>
+    <row r="77" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A77" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1038003</v>
+      </c>
+      <c r="B77" s="5">
+        <v>103800</v>
+      </c>
+      <c r="C77" s="5">
+        <v>3</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F77" s="5">
+        <v>1</v>
+      </c>
+      <c r="G77" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H77" s="5">
+        <v>2038001</v>
+      </c>
+      <c r="I77" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L77" s="47" t="s">
+        <v>153</v>
+      </c>
+      <c r="M77" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="N77" s="46">
+        <v>3</v>
+      </c>
+      <c r="O77" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q77" s="9"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:K2">

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="161">
   <si>
     <t>id</t>
   </si>
@@ -591,6 +591,24 @@
   </si>
   <si>
     <t>改出18图标+改出奖池符号</t>
+  </si>
+  <si>
+    <t>象财神</t>
+  </si>
+  <si>
+    <t>10270001|10270002</t>
+  </si>
+  <si>
+    <t>概率改出百搭符号+概率改出scatter符号</t>
+  </si>
+  <si>
+    <t>改出3个以上scatter符号</t>
+  </si>
+  <si>
+    <t>10270006|10270005</t>
+  </si>
+  <si>
+    <t>改出两个scatter+奖池符号</t>
   </si>
 </sst>
 </file>
@@ -1981,7 +1999,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S77"/>
+  <dimension ref="A1:S80"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
@@ -5259,6 +5277,135 @@
       </c>
       <c r="Q77" s="9"/>
     </row>
+    <row r="78" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A78" s="5" t="str">
+        <f>B78&amp;C78</f>
+        <v>1027001</v>
+      </c>
+      <c r="B78" s="5">
+        <v>102700</v>
+      </c>
+      <c r="C78" s="5">
+        <v>1</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F78" s="5">
+        <v>1</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H78" s="5">
+        <v>2027001</v>
+      </c>
+      <c r="I78" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L78" s="47" t="s">
+        <v>156</v>
+      </c>
+      <c r="M78" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="N78" s="46">
+        <v>3</v>
+      </c>
+      <c r="O78" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q78" s="9"/>
+    </row>
+    <row r="79" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A79" s="5" t="str">
+        <f>B79&amp;C79</f>
+        <v>1027002</v>
+      </c>
+      <c r="B79" s="5">
+        <v>102700</v>
+      </c>
+      <c r="C79" s="5">
+        <v>2</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F79" s="5">
+        <v>1</v>
+      </c>
+      <c r="G79" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H79" s="5">
+        <v>2027001</v>
+      </c>
+      <c r="I79" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L79" s="47">
+        <v>10270003</v>
+      </c>
+      <c r="M79" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="N79" s="46">
+        <v>3</v>
+      </c>
+      <c r="O79" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q79" s="9"/>
+    </row>
+    <row r="80" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A80" s="5" t="str">
+        <f>B80&amp;C80</f>
+        <v>1027003</v>
+      </c>
+      <c r="B80" s="5">
+        <v>102700</v>
+      </c>
+      <c r="C80" s="5">
+        <v>3</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F80" s="5">
+        <v>1</v>
+      </c>
+      <c r="G80" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H80" s="5">
+        <v>2027001</v>
+      </c>
+      <c r="I80" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L80" s="47" t="s">
+        <v>159</v>
+      </c>
+      <c r="M80" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="N80" s="46">
+        <v>3</v>
+      </c>
+      <c r="O80" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q80" s="9"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="J2:K2">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="177">
   <si>
     <t>id</t>
   </si>
@@ -609,6 +609,54 @@
   </si>
   <si>
     <t>改出两个scatter+奖池符号</t>
+  </si>
+  <si>
+    <t>10倍金牛</t>
+  </si>
+  <si>
+    <t>概率改出百搭符号</t>
+  </si>
+  <si>
+    <t>金牛赐福-触发局</t>
+  </si>
+  <si>
+    <t>绿巨人</t>
+  </si>
+  <si>
+    <t>10310001|10310007|10310011</t>
+  </si>
+  <si>
+    <t>概率在第二轴或第四轴改出百搭wild+概率改出2个SCATTER+概率在第一轴上改出bonus</t>
+  </si>
+  <si>
+    <t>概率改出3个以上SCATTER</t>
+  </si>
+  <si>
+    <t>10310012|10310013</t>
+  </si>
+  <si>
+    <t>在第一轴改出1个bonus+在第五轴改出1个bonus</t>
+  </si>
+  <si>
+    <t>10310010|10310014</t>
+  </si>
+  <si>
+    <t>前四轴改出2个SCATTER+10310015</t>
+  </si>
+  <si>
+    <t>第三轴出现wild</t>
+  </si>
+  <si>
+    <t>在第三轴改出18符号</t>
+  </si>
+  <si>
+    <t>第二三四轴出现wild</t>
+  </si>
+  <si>
+    <t>10310002|10310003|10310004</t>
+  </si>
+  <si>
+    <t>在第二轴改出18符号+在第三轴改出18符号+在第四轴改出18符号</t>
   </si>
 </sst>
 </file>
@@ -1999,7 +2047,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S80"/>
+  <dimension ref="A1:S89"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
@@ -4251,7 +4299,7 @@
     </row>
     <row r="54" customFormat="1" ht="16.5" spans="1:17">
       <c r="A54" s="5" t="str">
-        <f t="shared" ref="A54:A77" si="3">B54&amp;C54</f>
+        <f t="shared" ref="A54:A83" si="3">B54&amp;C54</f>
         <v>1035001</v>
       </c>
       <c r="B54" s="5">
@@ -5279,7 +5327,7 @@
     </row>
     <row r="78" customFormat="1" ht="16.5" spans="1:17">
       <c r="A78" s="5" t="str">
-        <f>B78&amp;C78</f>
+        <f t="shared" si="3"/>
         <v>1027001</v>
       </c>
       <c r="B78" s="5">
@@ -5322,7 +5370,7 @@
     </row>
     <row r="79" customFormat="1" ht="16.5" spans="1:17">
       <c r="A79" s="5" t="str">
-        <f>B79&amp;C79</f>
+        <f t="shared" si="3"/>
         <v>1027002</v>
       </c>
       <c r="B79" s="5">
@@ -5365,7 +5413,7 @@
     </row>
     <row r="80" customFormat="1" ht="16.5" spans="1:17">
       <c r="A80" s="5" t="str">
-        <f>B80&amp;C80</f>
+        <f t="shared" si="3"/>
         <v>1027003</v>
       </c>
       <c r="B80" s="5">
@@ -5405,6 +5453,389 @@
         <v>5</v>
       </c>
       <c r="Q80" s="9"/>
+    </row>
+    <row r="81" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A81" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1037001</v>
+      </c>
+      <c r="B81" s="5">
+        <v>103700</v>
+      </c>
+      <c r="C81" s="5">
+        <v>1</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="E81" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F81" s="5">
+        <v>1</v>
+      </c>
+      <c r="G81" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H81" s="5">
+        <v>2037001</v>
+      </c>
+      <c r="I81" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L81" s="47">
+        <v>10370001</v>
+      </c>
+      <c r="M81" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="N81" s="46">
+        <v>4</v>
+      </c>
+      <c r="O81" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="9"/>
+    </row>
+    <row r="82" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A82" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1037002</v>
+      </c>
+      <c r="B82" s="5">
+        <v>103700</v>
+      </c>
+      <c r="C82" s="5">
+        <v>2</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="F82" s="5">
+        <v>1</v>
+      </c>
+      <c r="G82" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H82" s="5">
+        <v>2037001</v>
+      </c>
+      <c r="I82" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L82" s="47">
+        <v>10370003</v>
+      </c>
+      <c r="M82" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="N82" s="46">
+        <v>4</v>
+      </c>
+      <c r="O82" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q82" s="9"/>
+    </row>
+    <row r="83" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A83" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1037003</v>
+      </c>
+      <c r="B83" s="5">
+        <v>103700</v>
+      </c>
+      <c r="C83" s="5">
+        <v>3</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F83" s="5">
+        <v>1</v>
+      </c>
+      <c r="G83" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H83" s="5">
+        <v>2037002</v>
+      </c>
+      <c r="I83" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L83" s="47"/>
+      <c r="M83" s="5"/>
+      <c r="N83" s="46">
+        <v>4</v>
+      </c>
+      <c r="O83" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="9"/>
+    </row>
+    <row r="84" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A84" s="5" t="str">
+        <f t="shared" ref="A84:A89" si="4">B84&amp;C84</f>
+        <v>1031001</v>
+      </c>
+      <c r="B84" s="5">
+        <v>103100</v>
+      </c>
+      <c r="C84" s="5">
+        <v>1</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F84" s="5">
+        <v>1</v>
+      </c>
+      <c r="G84" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H84" s="5">
+        <v>2031001</v>
+      </c>
+      <c r="I84" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L84" s="47" t="s">
+        <v>165</v>
+      </c>
+      <c r="M84" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="N84" s="46">
+        <v>3</v>
+      </c>
+      <c r="O84" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q84" s="9"/>
+    </row>
+    <row r="85" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A85" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>1031002</v>
+      </c>
+      <c r="B85" s="5">
+        <v>103100</v>
+      </c>
+      <c r="C85" s="5">
+        <v>2</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F85" s="5">
+        <v>2</v>
+      </c>
+      <c r="G85" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H85" s="5">
+        <v>2031001</v>
+      </c>
+      <c r="I85" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L85" s="47">
+        <v>10310008</v>
+      </c>
+      <c r="M85" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="N85" s="46">
+        <v>3</v>
+      </c>
+      <c r="O85" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q85" s="9"/>
+    </row>
+    <row r="86" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A86" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>1031003</v>
+      </c>
+      <c r="B86" s="5">
+        <v>103100</v>
+      </c>
+      <c r="C86" s="5">
+        <v>3</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F86" s="5">
+        <v>3</v>
+      </c>
+      <c r="G86" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H86" s="5">
+        <v>2031001</v>
+      </c>
+      <c r="I86" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L86" s="47" t="s">
+        <v>168</v>
+      </c>
+      <c r="M86" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="N86" s="46">
+        <v>3</v>
+      </c>
+      <c r="O86" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q86" s="9"/>
+    </row>
+    <row r="87" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A87" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>1031004</v>
+      </c>
+      <c r="B87" s="5">
+        <v>103100</v>
+      </c>
+      <c r="C87" s="5">
+        <v>4</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F87" s="5">
+        <v>4</v>
+      </c>
+      <c r="G87" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H87" s="5">
+        <v>2031001</v>
+      </c>
+      <c r="I87" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L87" s="47" t="s">
+        <v>170</v>
+      </c>
+      <c r="M87" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="N87" s="46">
+        <v>3</v>
+      </c>
+      <c r="O87" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q87" s="9"/>
+    </row>
+    <row r="88" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A88" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>1031005</v>
+      </c>
+      <c r="B88" s="5">
+        <v>103100</v>
+      </c>
+      <c r="C88" s="5">
+        <v>5</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="F88" s="5">
+        <v>5</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H88" s="5">
+        <v>2031001</v>
+      </c>
+      <c r="I88" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L88" s="47">
+        <v>10310003</v>
+      </c>
+      <c r="M88" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="N88" s="46">
+        <v>3</v>
+      </c>
+      <c r="O88" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q88" s="9"/>
+    </row>
+    <row r="89" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A89" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>1031006</v>
+      </c>
+      <c r="B89" s="5">
+        <v>103100</v>
+      </c>
+      <c r="C89" s="5">
+        <v>6</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="F89" s="5">
+        <v>6</v>
+      </c>
+      <c r="G89" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H89" s="5">
+        <v>2031001</v>
+      </c>
+      <c r="I89" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L89" s="47" t="s">
+        <v>175</v>
+      </c>
+      <c r="M89" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="N89" s="46">
+        <v>3</v>
+      </c>
+      <c r="O89" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q89" s="9"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:K2">

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialMode" sheetId="1" r:id="rId1"/>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="187">
   <si>
     <t>id</t>
   </si>
@@ -657,6 +657,36 @@
   </si>
   <si>
     <t>在第二轴改出18符号+在第三轴改出18符号+在第四轴改出18符号</t>
+  </si>
+  <si>
+    <t>潘金莲</t>
+  </si>
+  <si>
+    <t>10400001|10400006|10400007</t>
+  </si>
+  <si>
+    <t>概率改出百搭符号+概率在第二轴改出1个scatter+概率第三轴改出1个scatter</t>
+  </si>
+  <si>
+    <t>10400003|10400004|10400005</t>
+  </si>
+  <si>
+    <t>在第二轴改出1个scatter+在第三轴改出1个scatter+在第四轴改出1个scatter</t>
+  </si>
+  <si>
+    <t>10400003|10400005|10400009</t>
+  </si>
+  <si>
+    <t>在第二轴改出1个scatter+在第四轴改出1个scatter+第五轴改出奖池符号</t>
+  </si>
+  <si>
+    <t>愤怒的小鸡</t>
+  </si>
+  <si>
+    <t>10390001|10390004</t>
+  </si>
+  <si>
+    <t>10390005|10390006</t>
   </si>
 </sst>
 </file>
@@ -1387,7 +1417,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1396,6 +1426,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1514,6 +1545,7 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2047,7 +2079,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S89"/>
+  <dimension ref="A1:S95"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
@@ -2060,14 +2092,14 @@
     <col min="11" max="11" width="16.75" customWidth="1"/>
     <col min="12" max="12" width="53.25" customWidth="1"/>
     <col min="13" max="13" width="21.6083333333333" customWidth="1"/>
-    <col min="14" max="15" width="9" style="8"/>
+    <col min="14" max="15" width="9" style="9"/>
     <col min="16" max="16" width="15" customWidth="1"/>
-    <col min="17" max="17" width="23.75" style="9" customWidth="1"/>
+    <col min="17" max="17" width="23.75" style="10" customWidth="1"/>
     <col min="18" max="18" width="60.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:17">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
@@ -2078,34 +2110,34 @@
       </c>
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="12" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="5"/>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="12" t="s">
         <v>4</v>
       </c>
       <c r="I1" s="5"/>
-      <c r="J1" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="12"/>
-      <c r="L1" s="13" t="s">
+      <c r="J1" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="13"/>
+      <c r="L1" s="14" t="s">
         <v>6</v>
       </c>
       <c r="M1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="N1" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="O1" s="15" t="s">
         <v>9</v>
       </c>
       <c r="Q1"/>
     </row>
     <row r="2" ht="16.5" spans="1:17">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -2116,62 +2148,62 @@
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="12" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="5"/>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="12" t="s">
         <v>10</v>
       </c>
       <c r="I2" s="5"/>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="16"/>
-      <c r="L2" s="17" t="s">
+      <c r="K2" s="17"/>
+      <c r="L2" s="18" t="s">
         <v>12</v>
       </c>
       <c r="M2" s="5"/>
-      <c r="N2" s="18" t="s">
+      <c r="N2" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="18" t="s">
+      <c r="O2" s="19" t="s">
         <v>10</v>
       </c>
       <c r="Q2"/>
     </row>
     <row r="3" ht="16.5" spans="1:17">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="20" t="s">
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="19"/>
-      <c r="H3" s="21" t="s">
+      <c r="G3" s="20"/>
+      <c r="H3" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="19"/>
-      <c r="J3" s="22" t="s">
+      <c r="I3" s="20"/>
+      <c r="J3" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="22"/>
-      <c r="L3" s="23" t="s">
+      <c r="K3" s="23"/>
+      <c r="L3" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="M3" s="19"/>
-      <c r="N3" s="18" t="s">
+      <c r="M3" s="20"/>
+      <c r="N3" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="18" t="s">
+      <c r="O3" s="19" t="s">
         <v>20</v>
       </c>
       <c r="Q3"/>
@@ -2181,1101 +2213,1101 @@
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="11"/>
+      <c r="F4" s="12"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="11"/>
+      <c r="H4" s="12"/>
       <c r="I4" s="5"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="13"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="14"/>
       <c r="M4" s="5"/>
-      <c r="N4" s="18"/>
-      <c r="O4" s="18"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
       <c r="Q4"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A5" s="25" t="str">
+      <c r="A5" s="26" t="str">
         <f t="shared" ref="A5:A15" si="0">B5&amp;C5</f>
         <v>1001001</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="27">
         <v>100100</v>
       </c>
-      <c r="C5" s="26">
-        <v>1</v>
-      </c>
-      <c r="D5" s="26" t="s">
+      <c r="C5" s="27">
+        <v>1</v>
+      </c>
+      <c r="D5" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="26">
-        <v>1</v>
-      </c>
-      <c r="G5" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="25">
+      <c r="F5" s="27">
+        <v>1</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="26">
         <v>2001001</v>
       </c>
-      <c r="I5" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="28" t="s">
+      <c r="I5" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="26"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="M5" s="25" t="s">
+      <c r="M5" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="N5" s="18">
+      <c r="N5" s="19">
         <v>4</v>
       </c>
-      <c r="O5" s="18">
+      <c r="O5" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A6" s="25" t="str">
+      <c r="A6" s="26" t="str">
         <f t="shared" si="0"/>
         <v>1001002</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="27">
         <v>100100</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="27">
         <v>2</v>
       </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="29" t="s">
+      <c r="D6" s="27"/>
+      <c r="E6" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="26">
-        <v>1</v>
-      </c>
-      <c r="G6" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="25">
+      <c r="F6" s="27">
+        <v>1</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="26">
         <v>2001001</v>
       </c>
-      <c r="I6" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="30" t="s">
+      <c r="I6" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="M6" s="25" t="s">
+      <c r="M6" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="N6" s="18">
+      <c r="N6" s="19">
         <v>4</v>
       </c>
-      <c r="O6" s="18">
+      <c r="O6" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A7" s="25" t="str">
+      <c r="A7" s="26" t="str">
         <f t="shared" si="0"/>
         <v>1001003</v>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="27">
         <v>100100</v>
       </c>
-      <c r="C7" s="26">
-        <v>3</v>
-      </c>
-      <c r="D7" s="26"/>
-      <c r="E7" s="31" t="s">
+      <c r="C7" s="27">
+        <v>3</v>
+      </c>
+      <c r="D7" s="27"/>
+      <c r="E7" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="26">
-        <v>1</v>
-      </c>
-      <c r="G7" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="25">
+      <c r="F7" s="27">
+        <v>1</v>
+      </c>
+      <c r="G7" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="26">
         <v>2001001</v>
       </c>
-      <c r="I7" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="L7" s="28" t="s">
+      <c r="I7" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="M7" s="25" t="s">
+      <c r="M7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="N7" s="18">
+      <c r="N7" s="19">
         <v>4</v>
       </c>
-      <c r="O7" s="18">
+      <c r="O7" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A8" s="25" t="str">
+      <c r="A8" s="26" t="str">
         <f t="shared" si="0"/>
         <v>1001004</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="27">
         <v>100100</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="27">
         <v>4</v>
       </c>
-      <c r="D8" s="26"/>
-      <c r="E8" s="32" t="s">
+      <c r="D8" s="27"/>
+      <c r="E8" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="33">
-        <v>1</v>
-      </c>
-      <c r="G8" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="25">
+      <c r="F8" s="34">
+        <v>1</v>
+      </c>
+      <c r="G8" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="26">
         <v>2001001</v>
       </c>
-      <c r="I8" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="L8" s="28">
+      <c r="I8" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="29">
         <v>10010041</v>
       </c>
-      <c r="M8" s="25" t="s">
+      <c r="M8" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="N8" s="18">
+      <c r="N8" s="19">
         <v>4</v>
       </c>
-      <c r="O8" s="18">
+      <c r="O8" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A9" s="25" t="str">
+      <c r="A9" s="26" t="str">
         <f t="shared" si="0"/>
         <v>1001005</v>
       </c>
-      <c r="B9" s="26">
+      <c r="B9" s="27">
         <v>100100</v>
       </c>
-      <c r="C9" s="26">
-        <v>5</v>
-      </c>
-      <c r="D9" s="26"/>
-      <c r="E9" s="34" t="s">
+      <c r="C9" s="27">
+        <v>5</v>
+      </c>
+      <c r="D9" s="27"/>
+      <c r="E9" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="33">
-        <v>1</v>
-      </c>
-      <c r="G9" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="25">
+      <c r="F9" s="34">
+        <v>1</v>
+      </c>
+      <c r="G9" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="26">
         <v>2001001</v>
       </c>
-      <c r="I9" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="28" t="s">
+      <c r="I9" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="M9" s="25" t="s">
+      <c r="M9" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="N9" s="18">
+      <c r="N9" s="19">
         <v>4</v>
       </c>
-      <c r="O9" s="18">
+      <c r="O9" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A10" s="25" t="str">
+      <c r="A10" s="26" t="str">
         <f t="shared" si="0"/>
         <v>1001006</v>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="27">
         <v>100100</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="27">
         <v>6</v>
       </c>
-      <c r="D10" s="26"/>
-      <c r="E10" s="34" t="s">
+      <c r="D10" s="27"/>
+      <c r="E10" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="33">
-        <v>1</v>
-      </c>
-      <c r="G10" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="25">
+      <c r="F10" s="34">
+        <v>1</v>
+      </c>
+      <c r="G10" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="26">
         <v>2001001</v>
       </c>
-      <c r="I10" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="L10" s="28">
+      <c r="I10" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="29">
         <v>10010061</v>
       </c>
-      <c r="M10" s="25" t="s">
+      <c r="M10" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="N10" s="18">
+      <c r="N10" s="19">
         <v>4</v>
       </c>
-      <c r="O10" s="18">
+      <c r="O10" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A11" s="25" t="str">
+      <c r="A11" s="26" t="str">
         <f t="shared" si="0"/>
         <v>1001007</v>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="27">
         <v>100100</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="27">
         <v>7</v>
       </c>
-      <c r="D11" s="26"/>
-      <c r="E11" s="29" t="s">
+      <c r="D11" s="27"/>
+      <c r="E11" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="26">
-        <v>1</v>
-      </c>
-      <c r="G11" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" s="25">
+      <c r="F11" s="27">
+        <v>1</v>
+      </c>
+      <c r="G11" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="26">
         <v>2001001</v>
       </c>
-      <c r="I11" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="30" t="s">
+      <c r="I11" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="M11" s="25" t="s">
+      <c r="M11" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="N11" s="18">
+      <c r="N11" s="19">
         <v>4</v>
       </c>
-      <c r="O11" s="18">
+      <c r="O11" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A12" s="35" t="str">
+      <c r="A12" s="36" t="str">
         <f t="shared" si="0"/>
         <v>1003001</v>
       </c>
-      <c r="B12" s="27">
+      <c r="B12" s="28">
         <v>100300</v>
       </c>
-      <c r="C12" s="27">
-        <v>1</v>
-      </c>
-      <c r="D12" s="27" t="s">
+      <c r="C12" s="28">
+        <v>1</v>
+      </c>
+      <c r="D12" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="27" t="s">
+      <c r="E12" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="27">
-        <v>1</v>
-      </c>
-      <c r="G12" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="H12" s="35">
+      <c r="F12" s="28">
+        <v>1</v>
+      </c>
+      <c r="G12" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="36">
         <v>2003001</v>
       </c>
-      <c r="I12" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" s="35"/>
-      <c r="K12" s="35"/>
-      <c r="L12" s="36">
+      <c r="I12" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" s="36"/>
+      <c r="K12" s="36"/>
+      <c r="L12" s="37">
         <v>10030022</v>
       </c>
-      <c r="M12" s="35" t="s">
+      <c r="M12" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="N12" s="27">
-        <v>3</v>
-      </c>
-      <c r="O12" s="27">
-        <v>3</v>
-      </c>
-      <c r="Q12" s="37"/>
+      <c r="N12" s="28">
+        <v>3</v>
+      </c>
+      <c r="O12" s="28">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="38"/>
     </row>
     <row r="13" s="2" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A13" s="35" t="str">
+      <c r="A13" s="36" t="str">
         <f t="shared" ref="A13:A30" si="1">B13&amp;C13</f>
         <v>1003002</v>
       </c>
-      <c r="B13" s="27">
+      <c r="B13" s="28">
         <v>100300</v>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="28">
         <v>2</v>
       </c>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27" t="s">
+      <c r="D13" s="28"/>
+      <c r="E13" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="27">
-        <v>1</v>
-      </c>
-      <c r="G13" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="H13" s="35">
+      <c r="F13" s="28">
+        <v>1</v>
+      </c>
+      <c r="G13" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="36">
         <v>2003001</v>
       </c>
-      <c r="I13" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="J13" s="35"/>
-      <c r="K13" s="35"/>
-      <c r="L13" s="36" t="s">
+      <c r="I13" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" s="36"/>
+      <c r="K13" s="36"/>
+      <c r="L13" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="M13" s="35" t="s">
+      <c r="M13" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="N13" s="27">
-        <v>3</v>
-      </c>
-      <c r="O13" s="27">
-        <v>3</v>
-      </c>
-      <c r="Q13" s="37"/>
+      <c r="N13" s="28">
+        <v>3</v>
+      </c>
+      <c r="O13" s="28">
+        <v>3</v>
+      </c>
+      <c r="Q13" s="38"/>
     </row>
     <row r="14" s="2" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A14" s="35" t="str">
+      <c r="A14" s="36" t="str">
         <f t="shared" si="1"/>
         <v>1003003</v>
       </c>
-      <c r="B14" s="27">
+      <c r="B14" s="28">
         <v>100300</v>
       </c>
-      <c r="C14" s="27">
-        <v>3</v>
-      </c>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27" t="s">
+      <c r="C14" s="28">
+        <v>3</v>
+      </c>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="27">
-        <v>1</v>
-      </c>
-      <c r="G14" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="H14" s="35">
+      <c r="F14" s="28">
+        <v>1</v>
+      </c>
+      <c r="G14" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="36">
         <v>2003002</v>
       </c>
-      <c r="I14" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="J14" s="35" t="s">
+      <c r="I14" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="K14" s="35" t="s">
+      <c r="K14" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="L14" s="36" t="s">
+      <c r="L14" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="M14" s="35" t="s">
+      <c r="M14" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="N14" s="27">
-        <v>3</v>
-      </c>
-      <c r="O14" s="27">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="37"/>
+      <c r="N14" s="28">
+        <v>3</v>
+      </c>
+      <c r="O14" s="28">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="38"/>
     </row>
     <row r="15" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A15" s="38" t="str">
+      <c r="A15" s="39" t="str">
         <f t="shared" si="1"/>
         <v>1007001</v>
       </c>
-      <c r="B15" s="39">
+      <c r="B15" s="40">
         <v>100700</v>
       </c>
-      <c r="C15" s="39">
-        <v>1</v>
-      </c>
-      <c r="D15" s="39" t="s">
+      <c r="C15" s="40">
+        <v>1</v>
+      </c>
+      <c r="D15" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="39" t="s">
+      <c r="E15" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="39">
-        <v>1</v>
-      </c>
-      <c r="G15" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="H15" s="38">
+      <c r="F15" s="40">
+        <v>1</v>
+      </c>
+      <c r="G15" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="39">
         <v>2007001</v>
       </c>
-      <c r="I15" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="J15" s="38"/>
-      <c r="K15" s="38"/>
-      <c r="L15" s="40" t="s">
+      <c r="I15" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" s="39"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="M15" s="38" t="s">
+      <c r="M15" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="N15" s="18">
+      <c r="N15" s="19">
         <v>4</v>
       </c>
-      <c r="O15" s="18">
+      <c r="O15" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="16" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A16" s="38" t="str">
+      <c r="A16" s="39" t="str">
         <f t="shared" si="1"/>
         <v>1007002</v>
       </c>
-      <c r="B16" s="39">
+      <c r="B16" s="40">
         <v>100700</v>
       </c>
-      <c r="C16" s="39">
+      <c r="C16" s="40">
         <v>2</v>
       </c>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39" t="s">
+      <c r="D16" s="40"/>
+      <c r="E16" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="39">
-        <v>1</v>
-      </c>
-      <c r="G16" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="H16" s="38">
+      <c r="F16" s="40">
+        <v>1</v>
+      </c>
+      <c r="G16" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="39">
         <v>2007001</v>
       </c>
-      <c r="I16" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="J16" s="38"/>
-      <c r="K16" s="38"/>
-      <c r="L16" s="40" t="s">
+      <c r="I16" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="J16" s="39"/>
+      <c r="K16" s="39"/>
+      <c r="L16" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="M16" s="38" t="s">
+      <c r="M16" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="N16" s="18">
+      <c r="N16" s="19">
         <v>4</v>
       </c>
-      <c r="O16" s="18">
+      <c r="O16" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="17" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A17" s="41" t="str">
+      <c r="A17" s="42" t="str">
         <f t="shared" si="1"/>
         <v>1012001</v>
       </c>
-      <c r="B17" s="42">
+      <c r="B17" s="43">
         <v>101200</v>
       </c>
-      <c r="C17" s="42">
-        <v>1</v>
-      </c>
-      <c r="D17" s="42" t="s">
+      <c r="C17" s="43">
+        <v>1</v>
+      </c>
+      <c r="D17" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="E17" s="42" t="s">
+      <c r="E17" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="42">
-        <v>1</v>
-      </c>
-      <c r="G17" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="H17" s="41">
+      <c r="F17" s="43">
+        <v>1</v>
+      </c>
+      <c r="G17" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="42">
         <v>2012001</v>
       </c>
-      <c r="I17" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="J17" s="41"/>
-      <c r="K17" s="41"/>
-      <c r="L17" s="43">
+      <c r="I17" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="J17" s="42"/>
+      <c r="K17" s="42"/>
+      <c r="L17" s="44">
         <v>10120011</v>
       </c>
-      <c r="M17" s="41" t="s">
+      <c r="M17" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="N17" s="42">
-        <v>3</v>
-      </c>
-      <c r="O17" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q17" s="44"/>
+      <c r="N17" s="43">
+        <v>3</v>
+      </c>
+      <c r="O17" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="45"/>
     </row>
     <row r="18" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A18" s="41" t="str">
+      <c r="A18" s="42" t="str">
         <f t="shared" si="1"/>
         <v>1012002</v>
       </c>
-      <c r="B18" s="42">
+      <c r="B18" s="43">
         <v>101200</v>
       </c>
-      <c r="C18" s="42">
+      <c r="C18" s="43">
         <v>2</v>
       </c>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42" t="s">
+      <c r="D18" s="43"/>
+      <c r="E18" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="42">
-        <v>1</v>
-      </c>
-      <c r="G18" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="H18" s="41">
+      <c r="F18" s="43">
+        <v>1</v>
+      </c>
+      <c r="G18" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="42">
         <v>2012001</v>
       </c>
-      <c r="I18" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="J18" s="41"/>
-      <c r="K18" s="41"/>
-      <c r="L18" s="43">
+      <c r="I18" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="J18" s="42"/>
+      <c r="K18" s="42"/>
+      <c r="L18" s="44">
         <v>10120021</v>
       </c>
-      <c r="M18" s="41" t="s">
+      <c r="M18" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="N18" s="42">
-        <v>3</v>
-      </c>
-      <c r="O18" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q18" s="44"/>
+      <c r="N18" s="43">
+        <v>3</v>
+      </c>
+      <c r="O18" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="45"/>
     </row>
     <row r="19" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A19" s="41" t="str">
+      <c r="A19" s="42" t="str">
         <f t="shared" si="1"/>
         <v>1012003</v>
       </c>
-      <c r="B19" s="42">
+      <c r="B19" s="43">
         <v>101200</v>
       </c>
-      <c r="C19" s="42">
-        <v>3</v>
-      </c>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42" t="s">
+      <c r="C19" s="43">
+        <v>3</v>
+      </c>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="F19" s="42">
-        <v>1</v>
-      </c>
-      <c r="G19" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="H19" s="41">
+      <c r="F19" s="43">
+        <v>1</v>
+      </c>
+      <c r="G19" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="42">
         <v>2012001</v>
       </c>
-      <c r="I19" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="J19" s="41" t="s">
+      <c r="I19" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="J19" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="K19" s="41" t="s">
+      <c r="K19" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="L19" s="43"/>
-      <c r="M19" s="41" t="s">
+      <c r="L19" s="44"/>
+      <c r="M19" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="N19" s="42">
-        <v>3</v>
-      </c>
-      <c r="O19" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q19" s="44"/>
+      <c r="N19" s="43">
+        <v>3</v>
+      </c>
+      <c r="O19" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q19" s="45"/>
     </row>
     <row r="20" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A20" s="35" t="str">
+      <c r="A20" s="36" t="str">
         <f t="shared" si="1"/>
         <v>1014001</v>
       </c>
-      <c r="B20" s="27">
+      <c r="B20" s="28">
         <v>101400</v>
       </c>
-      <c r="C20" s="27">
-        <v>1</v>
-      </c>
-      <c r="D20" s="27" t="s">
+      <c r="C20" s="28">
+        <v>1</v>
+      </c>
+      <c r="D20" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="E20" s="27" t="s">
+      <c r="E20" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="F20" s="27">
-        <v>1</v>
-      </c>
-      <c r="G20" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="H20" s="35">
+      <c r="F20" s="28">
+        <v>1</v>
+      </c>
+      <c r="G20" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="36">
         <v>2014001</v>
       </c>
-      <c r="I20" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="J20" s="35"/>
-      <c r="K20" s="35"/>
-      <c r="L20" s="36" t="s">
+      <c r="I20" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="J20" s="36"/>
+      <c r="K20" s="36"/>
+      <c r="L20" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="M20" s="35" t="s">
+      <c r="M20" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="N20" s="18">
+      <c r="N20" s="19">
         <v>4</v>
       </c>
-      <c r="O20" s="18">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="45"/>
+      <c r="O20" s="19">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="46"/>
     </row>
     <row r="21" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A21" s="35" t="str">
+      <c r="A21" s="36" t="str">
         <f t="shared" si="1"/>
         <v>1014002</v>
       </c>
-      <c r="B21" s="27">
+      <c r="B21" s="28">
         <v>101400</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="28">
         <v>2</v>
       </c>
-      <c r="D21" s="27" t="s">
+      <c r="D21" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="E21" s="27" t="s">
+      <c r="E21" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="27">
-        <v>1</v>
-      </c>
-      <c r="G21" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="H21" s="35">
+      <c r="F21" s="28">
+        <v>1</v>
+      </c>
+      <c r="G21" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="36">
         <v>2014001</v>
       </c>
-      <c r="I21" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="J21" s="35"/>
-      <c r="K21" s="35"/>
-      <c r="L21" s="36" t="s">
+      <c r="I21" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="J21" s="36"/>
+      <c r="K21" s="36"/>
+      <c r="L21" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="M21" s="35" t="s">
+      <c r="M21" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="N21" s="18">
+      <c r="N21" s="19">
         <v>4</v>
       </c>
-      <c r="O21" s="18">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="45"/>
+      <c r="O21" s="19">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="46"/>
     </row>
     <row r="22" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A22" s="35" t="str">
+      <c r="A22" s="36" t="str">
         <f t="shared" si="1"/>
         <v>1014003</v>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="28">
         <v>101400</v>
       </c>
-      <c r="C22" s="27">
-        <v>3</v>
-      </c>
-      <c r="D22" s="27" t="s">
+      <c r="C22" s="28">
+        <v>3</v>
+      </c>
+      <c r="D22" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="E22" s="27" t="s">
+      <c r="E22" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="F22" s="27">
-        <v>1</v>
-      </c>
-      <c r="G22" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="H22" s="35">
+      <c r="F22" s="28">
+        <v>1</v>
+      </c>
+      <c r="G22" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="36">
         <v>2014001</v>
       </c>
-      <c r="I22" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="J22" s="35"/>
-      <c r="K22" s="35"/>
-      <c r="L22" s="36">
+      <c r="I22" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="J22" s="36"/>
+      <c r="K22" s="36"/>
+      <c r="L22" s="37">
         <v>10140021</v>
       </c>
-      <c r="M22" s="35" t="s">
+      <c r="M22" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="N22" s="18">
+      <c r="N22" s="19">
         <v>4</v>
       </c>
-      <c r="O22" s="18">
-        <v>3</v>
-      </c>
-      <c r="Q22" s="45"/>
+      <c r="O22" s="19">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="46"/>
     </row>
     <row r="23" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A23" s="25" t="str">
+      <c r="A23" s="26" t="str">
         <f t="shared" si="1"/>
         <v>1024001</v>
       </c>
-      <c r="B23" s="26">
+      <c r="B23" s="27">
         <v>102400</v>
       </c>
-      <c r="C23" s="26">
-        <v>1</v>
-      </c>
-      <c r="D23" s="26" t="s">
+      <c r="C23" s="27">
+        <v>1</v>
+      </c>
+      <c r="D23" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="E23" s="27" t="s">
+      <c r="E23" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="F23" s="26">
-        <v>1</v>
-      </c>
-      <c r="G23" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H23" s="25">
+      <c r="F23" s="27">
+        <v>1</v>
+      </c>
+      <c r="G23" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="26">
         <v>2024001</v>
       </c>
-      <c r="I23" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="J23" s="25"/>
-      <c r="K23" s="25"/>
-      <c r="L23" s="28" t="s">
+      <c r="I23" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="M23" s="25" t="s">
+      <c r="M23" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="N23" s="18">
+      <c r="N23" s="19">
         <v>4</v>
       </c>
-      <c r="O23" s="18">
+      <c r="O23" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A24" s="25" t="str">
+      <c r="A24" s="26" t="str">
         <f t="shared" si="1"/>
         <v>1024002</v>
       </c>
-      <c r="B24" s="26">
+      <c r="B24" s="27">
         <v>102400</v>
       </c>
-      <c r="C24" s="26">
+      <c r="C24" s="27">
         <v>2</v>
       </c>
-      <c r="D24" s="26"/>
-      <c r="E24" s="29" t="s">
+      <c r="D24" s="27"/>
+      <c r="E24" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="26">
-        <v>1</v>
-      </c>
-      <c r="G24" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H24" s="25">
+      <c r="F24" s="27">
+        <v>1</v>
+      </c>
+      <c r="G24" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" s="26">
         <v>2024001</v>
       </c>
-      <c r="I24" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="J24" s="25"/>
-      <c r="K24" s="25"/>
-      <c r="L24" s="30" t="s">
+      <c r="I24" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J24" s="26"/>
+      <c r="K24" s="26"/>
+      <c r="L24" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="M24" s="25" t="s">
+      <c r="M24" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="N24" s="18">
+      <c r="N24" s="19">
         <v>4</v>
       </c>
-      <c r="O24" s="18">
+      <c r="O24" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A25" s="25" t="str">
+      <c r="A25" s="26" t="str">
         <f t="shared" si="1"/>
         <v>1024003</v>
       </c>
-      <c r="B25" s="26">
+      <c r="B25" s="27">
         <v>102400</v>
       </c>
-      <c r="C25" s="26">
-        <v>3</v>
-      </c>
-      <c r="D25" s="26"/>
-      <c r="E25" s="31" t="s">
+      <c r="C25" s="27">
+        <v>3</v>
+      </c>
+      <c r="D25" s="27"/>
+      <c r="E25" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F25" s="26">
-        <v>1</v>
-      </c>
-      <c r="G25" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H25" s="25">
+      <c r="F25" s="27">
+        <v>1</v>
+      </c>
+      <c r="G25" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="26">
         <v>2024001</v>
       </c>
-      <c r="I25" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="J25" s="25"/>
-      <c r="K25" s="25"/>
-      <c r="L25" s="28" t="s">
+      <c r="I25" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J25" s="26"/>
+      <c r="K25" s="26"/>
+      <c r="L25" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="M25" s="25" t="s">
+      <c r="M25" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="N25" s="18">
+      <c r="N25" s="19">
         <v>4</v>
       </c>
-      <c r="O25" s="18">
+      <c r="O25" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A26" s="25" t="str">
+      <c r="A26" s="26" t="str">
         <f t="shared" si="1"/>
         <v>1024004</v>
       </c>
-      <c r="B26" s="26">
+      <c r="B26" s="27">
         <v>102400</v>
       </c>
-      <c r="C26" s="26">
+      <c r="C26" s="27">
         <v>4</v>
       </c>
-      <c r="D26" s="26"/>
-      <c r="E26" s="32" t="s">
+      <c r="D26" s="27"/>
+      <c r="E26" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="F26" s="33">
-        <v>1</v>
-      </c>
-      <c r="G26" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H26" s="25">
+      <c r="F26" s="34">
+        <v>1</v>
+      </c>
+      <c r="G26" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="26">
         <v>2024001</v>
       </c>
-      <c r="I26" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="J26" s="25"/>
-      <c r="K26" s="25"/>
-      <c r="L26" s="28">
+      <c r="I26" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J26" s="26"/>
+      <c r="K26" s="26"/>
+      <c r="L26" s="29">
         <v>10240041</v>
       </c>
-      <c r="M26" s="25" t="s">
+      <c r="M26" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="N26" s="18">
+      <c r="N26" s="19">
         <v>4</v>
       </c>
-      <c r="O26" s="18">
+      <c r="O26" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A27" s="25" t="str">
+      <c r="A27" s="26" t="str">
         <f t="shared" si="1"/>
         <v>1024005</v>
       </c>
-      <c r="B27" s="26">
+      <c r="B27" s="27">
         <v>102400</v>
       </c>
-      <c r="C27" s="26">
-        <v>5</v>
-      </c>
-      <c r="D27" s="26"/>
-      <c r="E27" s="34" t="s">
+      <c r="C27" s="27">
+        <v>5</v>
+      </c>
+      <c r="D27" s="27"/>
+      <c r="E27" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="F27" s="33">
-        <v>1</v>
-      </c>
-      <c r="G27" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H27" s="25">
+      <c r="F27" s="34">
+        <v>1</v>
+      </c>
+      <c r="G27" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H27" s="26">
         <v>2024001</v>
       </c>
-      <c r="I27" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="J27" s="25"/>
-      <c r="K27" s="25"/>
-      <c r="L27" s="28" t="s">
+      <c r="I27" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J27" s="26"/>
+      <c r="K27" s="26"/>
+      <c r="L27" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="M27" s="25" t="s">
+      <c r="M27" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="N27" s="18">
+      <c r="N27" s="19">
         <v>4</v>
       </c>
-      <c r="O27" s="18">
+      <c r="O27" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A28" s="25" t="str">
+      <c r="A28" s="26" t="str">
         <f t="shared" si="1"/>
         <v>1024006</v>
       </c>
-      <c r="B28" s="26">
+      <c r="B28" s="27">
         <v>102400</v>
       </c>
-      <c r="C28" s="26">
+      <c r="C28" s="27">
         <v>6</v>
       </c>
-      <c r="D28" s="26"/>
-      <c r="E28" s="34" t="s">
+      <c r="D28" s="27"/>
+      <c r="E28" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="F28" s="33">
-        <v>1</v>
-      </c>
-      <c r="G28" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H28" s="25">
+      <c r="F28" s="34">
+        <v>1</v>
+      </c>
+      <c r="G28" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28" s="26">
         <v>2024001</v>
       </c>
-      <c r="I28" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="J28" s="25"/>
-      <c r="K28" s="25"/>
-      <c r="L28" s="28">
+      <c r="I28" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J28" s="26"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="29">
         <v>10240061</v>
       </c>
-      <c r="M28" s="25" t="s">
+      <c r="M28" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="N28" s="18">
+      <c r="N28" s="19">
         <v>4</v>
       </c>
-      <c r="O28" s="18">
+      <c r="O28" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A29" s="25" t="str">
+      <c r="A29" s="26" t="str">
         <f t="shared" si="1"/>
         <v>1024007</v>
       </c>
-      <c r="B29" s="26">
+      <c r="B29" s="27">
         <v>102400</v>
       </c>
-      <c r="C29" s="26">
+      <c r="C29" s="27">
         <v>7</v>
       </c>
-      <c r="D29" s="26"/>
-      <c r="E29" s="29" t="s">
+      <c r="D29" s="27"/>
+      <c r="E29" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="F29" s="26">
-        <v>1</v>
-      </c>
-      <c r="G29" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H29" s="25">
+      <c r="F29" s="27">
+        <v>1</v>
+      </c>
+      <c r="G29" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H29" s="26">
         <v>2024001</v>
       </c>
-      <c r="I29" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="J29" s="25"/>
-      <c r="K29" s="25"/>
-      <c r="L29" s="30" t="s">
+      <c r="I29" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J29" s="26"/>
+      <c r="K29" s="26"/>
+      <c r="L29" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="M29" s="25" t="s">
+      <c r="M29" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="N29" s="18">
+      <c r="N29" s="19">
         <v>4</v>
       </c>
-      <c r="O29" s="18">
+      <c r="O29" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="30" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A30" s="25" t="str">
+      <c r="A30" s="26" t="str">
         <f t="shared" si="1"/>
         <v>1017001</v>
       </c>
@@ -3309,16 +3341,16 @@
       <c r="M30" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="N30" s="46">
+      <c r="N30" s="47">
         <v>4</v>
       </c>
-      <c r="O30" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q30" s="19"/>
+      <c r="O30" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q30" s="20"/>
     </row>
     <row r="31" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A31" s="25" t="str">
+      <c r="A31" s="26" t="str">
         <f t="shared" ref="A31:A53" si="2">B31&amp;C31</f>
         <v>1017002</v>
       </c>
@@ -3352,16 +3384,16 @@
       <c r="M31" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="N31" s="46">
+      <c r="N31" s="47">
         <v>4</v>
       </c>
-      <c r="O31" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q31" s="19"/>
+      <c r="O31" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q31" s="20"/>
     </row>
     <row r="32" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A32" s="25" t="str">
+      <c r="A32" s="26" t="str">
         <f t="shared" si="2"/>
         <v>1017003</v>
       </c>
@@ -3395,16 +3427,16 @@
       <c r="M32" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N32" s="46">
+      <c r="N32" s="47">
         <v>4</v>
       </c>
-      <c r="O32" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q32" s="19"/>
+      <c r="O32" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="20"/>
     </row>
     <row r="33" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A33" s="25" t="str">
+      <c r="A33" s="26" t="str">
         <f t="shared" si="2"/>
         <v>1022001</v>
       </c>
@@ -3432,22 +3464,22 @@
       <c r="I33" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L33" s="47" t="s">
+      <c r="L33" s="48" t="s">
         <v>85</v>
       </c>
       <c r="M33" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N33" s="46">
-        <v>3</v>
-      </c>
-      <c r="O33" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q33" s="19"/>
+      <c r="N33" s="47">
+        <v>3</v>
+      </c>
+      <c r="O33" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q33" s="20"/>
     </row>
     <row r="34" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A34" s="25" t="str">
+      <c r="A34" s="26" t="str">
         <f t="shared" si="2"/>
         <v>1022002</v>
       </c>
@@ -3463,10 +3495,10 @@
       <c r="E34" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="F34" s="18">
-        <v>1</v>
-      </c>
-      <c r="G34" s="48" t="s">
+      <c r="F34" s="19">
+        <v>1</v>
+      </c>
+      <c r="G34" s="49" t="s">
         <v>23</v>
       </c>
       <c r="H34" s="5">
@@ -3475,22 +3507,22 @@
       <c r="I34" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L34" s="47">
+      <c r="L34" s="48">
         <v>10220033</v>
       </c>
       <c r="M34" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N34" s="46">
-        <v>3</v>
-      </c>
-      <c r="O34" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q34" s="19"/>
+      <c r="N34" s="47">
+        <v>3</v>
+      </c>
+      <c r="O34" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q34" s="20"/>
     </row>
     <row r="35" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A35" s="25" t="str">
+      <c r="A35" s="26" t="str">
         <f t="shared" si="2"/>
         <v>1022003</v>
       </c>
@@ -3506,10 +3538,10 @@
       <c r="E35" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F35" s="48">
-        <v>1</v>
-      </c>
-      <c r="G35" s="48" t="s">
+      <c r="F35" s="49">
+        <v>1</v>
+      </c>
+      <c r="G35" s="49" t="s">
         <v>23</v>
       </c>
       <c r="H35" s="5">
@@ -3518,22 +3550,22 @@
       <c r="I35" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L35" s="49" t="s">
+      <c r="L35" s="50" t="s">
         <v>89</v>
       </c>
       <c r="M35" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N35" s="46">
-        <v>3</v>
-      </c>
-      <c r="O35" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q35" s="19"/>
+      <c r="N35" s="47">
+        <v>3</v>
+      </c>
+      <c r="O35" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q35" s="20"/>
     </row>
     <row r="36" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A36" s="25" t="str">
+      <c r="A36" s="26" t="str">
         <f t="shared" si="2"/>
         <v>1022004</v>
       </c>
@@ -3549,10 +3581,10 @@
       <c r="E36" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F36" s="18">
-        <v>1</v>
-      </c>
-      <c r="G36" s="48" t="s">
+      <c r="F36" s="19">
+        <v>1</v>
+      </c>
+      <c r="G36" s="49" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="5">
@@ -3561,19 +3593,19 @@
       <c r="I36" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L36" s="47">
+      <c r="L36" s="48">
         <v>10220020</v>
       </c>
-      <c r="N36" s="46">
-        <v>3</v>
-      </c>
-      <c r="O36" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q36" s="19"/>
+      <c r="N36" s="47">
+        <v>3</v>
+      </c>
+      <c r="O36" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q36" s="20"/>
     </row>
     <row r="37" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A37" s="25" t="str">
+      <c r="A37" s="26" t="str">
         <f t="shared" si="2"/>
         <v>1022005</v>
       </c>
@@ -3601,20 +3633,20 @@
       <c r="I37" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L37" s="47">
+      <c r="L37" s="48">
         <v>10220019</v>
       </c>
-      <c r="N37" s="46">
-        <v>3</v>
-      </c>
-      <c r="O37" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q37" s="19"/>
-      <c r="S37" s="50"/>
+      <c r="N37" s="47">
+        <v>3</v>
+      </c>
+      <c r="O37" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q37" s="20"/>
+      <c r="S37" s="51"/>
     </row>
     <row r="38" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A38" s="25" t="str">
+      <c r="A38" s="26" t="str">
         <f t="shared" si="2"/>
         <v>1021001</v>
       </c>
@@ -3642,23 +3674,23 @@
       <c r="I38" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L38" s="47" t="s">
+      <c r="L38" s="48" t="s">
         <v>93</v>
       </c>
       <c r="M38" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N38" s="46">
-        <v>3</v>
-      </c>
-      <c r="O38" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q38" s="19"/>
-      <c r="S38" s="50"/>
+      <c r="N38" s="47">
+        <v>3</v>
+      </c>
+      <c r="O38" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q38" s="20"/>
+      <c r="S38" s="51"/>
     </row>
     <row r="39" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A39" s="25" t="str">
+      <c r="A39" s="26" t="str">
         <f t="shared" si="2"/>
         <v>1021002</v>
       </c>
@@ -3686,23 +3718,23 @@
       <c r="I39" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L39" s="47">
+      <c r="L39" s="48">
         <v>10210031</v>
       </c>
       <c r="M39" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N39" s="46">
-        <v>3</v>
-      </c>
-      <c r="O39" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q39" s="19"/>
-      <c r="S39" s="50"/>
+      <c r="N39" s="47">
+        <v>3</v>
+      </c>
+      <c r="O39" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q39" s="20"/>
+      <c r="S39" s="51"/>
     </row>
     <row r="40" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A40" s="25" t="str">
+      <c r="A40" s="26" t="str">
         <f t="shared" si="2"/>
         <v>1021003</v>
       </c>
@@ -3730,23 +3762,23 @@
       <c r="I40" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L40" s="47">
+      <c r="L40" s="48">
         <v>10210041</v>
       </c>
       <c r="M40" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="N40" s="46">
-        <v>3</v>
-      </c>
-      <c r="O40" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q40" s="19"/>
-      <c r="S40" s="50"/>
+      <c r="N40" s="47">
+        <v>3</v>
+      </c>
+      <c r="O40" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q40" s="20"/>
+      <c r="S40" s="51"/>
     </row>
     <row r="41" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A41" s="25" t="str">
+      <c r="A41" s="26" t="str">
         <f t="shared" si="2"/>
         <v>1021004</v>
       </c>
@@ -3774,23 +3806,23 @@
       <c r="I41" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L41" s="47" t="s">
+      <c r="L41" s="48" t="s">
         <v>96</v>
       </c>
       <c r="M41" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N41" s="46">
-        <v>3</v>
-      </c>
-      <c r="O41" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q41" s="19"/>
-      <c r="S41" s="50"/>
+      <c r="N41" s="47">
+        <v>3</v>
+      </c>
+      <c r="O41" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q41" s="20"/>
+      <c r="S41" s="51"/>
     </row>
     <row r="42" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A42" s="25" t="str">
+      <c r="A42" s="26" t="str">
         <f t="shared" si="2"/>
         <v>1018001</v>
       </c>
@@ -3818,20 +3850,20 @@
       <c r="I42" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L42" s="47" t="s">
+      <c r="L42" s="48" t="s">
         <v>98</v>
       </c>
       <c r="M42" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N42" s="46">
+      <c r="N42" s="47">
         <v>4</v>
       </c>
-      <c r="O42" s="46">
+      <c r="O42" s="47">
         <v>6</v>
       </c>
-      <c r="Q42" s="19"/>
-      <c r="S42" s="50"/>
+      <c r="Q42" s="20"/>
+      <c r="S42" s="51"/>
     </row>
     <row r="43" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A43" s="5" t="str">
@@ -3862,16 +3894,16 @@
       <c r="I43" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L43" s="47">
+      <c r="L43" s="48">
         <v>10180031</v>
       </c>
       <c r="M43" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N43" s="46">
+      <c r="N43" s="47">
         <v>4</v>
       </c>
-      <c r="O43" s="46">
+      <c r="O43" s="47">
         <v>6</v>
       </c>
     </row>
@@ -3904,16 +3936,16 @@
       <c r="I44" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L44" s="47" t="s">
+      <c r="L44" s="48" t="s">
         <v>99</v>
       </c>
       <c r="M44" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N44" s="46">
+      <c r="N44" s="47">
         <v>4</v>
       </c>
-      <c r="O44" s="46">
+      <c r="O44" s="47">
         <v>6</v>
       </c>
     </row>
@@ -3946,19 +3978,19 @@
       <c r="I45" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L45" s="47" t="s">
+      <c r="L45" s="48" t="s">
         <v>101</v>
       </c>
       <c r="M45" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N45" s="46">
-        <v>3</v>
-      </c>
-      <c r="O45" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q45" s="9"/>
+      <c r="N45" s="47">
+        <v>3</v>
+      </c>
+      <c r="O45" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q45" s="10"/>
     </row>
     <row r="46" customFormat="1" ht="16.5" spans="1:19">
       <c r="A46" s="5" t="str">
@@ -3989,19 +4021,19 @@
       <c r="I46" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L46" s="47">
+      <c r="L46" s="48">
         <v>10250031</v>
       </c>
       <c r="M46" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="N46" s="46">
-        <v>3</v>
-      </c>
-      <c r="O46" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q46" s="9"/>
+      <c r="N46" s="47">
+        <v>3</v>
+      </c>
+      <c r="O46" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q46" s="10"/>
     </row>
     <row r="47" customFormat="1" ht="16.5" spans="1:19">
       <c r="A47" s="5" t="str">
@@ -4032,19 +4064,19 @@
       <c r="I47" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L47" s="47" t="s">
+      <c r="L47" s="48" t="s">
         <v>103</v>
       </c>
       <c r="M47" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N47" s="46">
-        <v>3</v>
-      </c>
-      <c r="O47" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q47" s="9"/>
+      <c r="N47" s="47">
+        <v>3</v>
+      </c>
+      <c r="O47" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q47" s="10"/>
     </row>
     <row r="48" customFormat="1" ht="16.5" spans="1:19">
       <c r="A48" s="5" t="str">
@@ -4075,19 +4107,19 @@
       <c r="I48" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L48" s="47" t="s">
+      <c r="L48" s="48" t="s">
         <v>105</v>
       </c>
       <c r="M48" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N48" s="46">
+      <c r="N48" s="47">
         <v>4</v>
       </c>
-      <c r="O48" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q48" s="9"/>
+      <c r="O48" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q48" s="10"/>
     </row>
     <row r="49" customFormat="1" ht="16.5" spans="1:17">
       <c r="A49" s="5" t="str">
@@ -4118,19 +4150,19 @@
       <c r="I49" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L49" s="47">
+      <c r="L49" s="48">
         <v>10230003</v>
       </c>
       <c r="M49" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="N49" s="46">
+      <c r="N49" s="47">
         <v>4</v>
       </c>
-      <c r="O49" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q49" s="9"/>
+      <c r="O49" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q49" s="10"/>
     </row>
     <row r="50" customFormat="1" ht="16.5" spans="1:17">
       <c r="A50" s="5" t="str">
@@ -4161,19 +4193,19 @@
       <c r="I50" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L50" s="47" t="s">
+      <c r="L50" s="48" t="s">
         <v>106</v>
       </c>
       <c r="M50" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N50" s="46">
+      <c r="N50" s="47">
         <v>4</v>
       </c>
-      <c r="O50" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q50" s="9"/>
+      <c r="O50" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q50" s="10"/>
     </row>
     <row r="51" customFormat="1" ht="16.5" spans="1:17">
       <c r="A51" s="5" t="str">
@@ -4204,19 +4236,19 @@
       <c r="I51" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L51" s="47">
+      <c r="L51" s="48">
         <v>10340007</v>
       </c>
       <c r="M51" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="N51" s="46">
-        <v>3</v>
-      </c>
-      <c r="O51" s="46">
-        <v>3</v>
-      </c>
-      <c r="Q51" s="9"/>
+      <c r="N51" s="47">
+        <v>3</v>
+      </c>
+      <c r="O51" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q51" s="10"/>
     </row>
     <row r="52" customFormat="1" ht="16.5" spans="1:17">
       <c r="A52" s="5" t="str">
@@ -4247,16 +4279,16 @@
       <c r="I52" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L52" s="47"/>
+      <c r="L52" s="48"/>
       <c r="M52" s="5"/>
-      <c r="N52" s="46">
-        <v>3</v>
-      </c>
-      <c r="O52" s="46">
-        <v>3</v>
-      </c>
-      <c r="P52" s="51"/>
-      <c r="Q52" s="9"/>
+      <c r="N52" s="47">
+        <v>3</v>
+      </c>
+      <c r="O52" s="47">
+        <v>3</v>
+      </c>
+      <c r="P52" s="52"/>
+      <c r="Q52" s="10"/>
     </row>
     <row r="53" customFormat="1" ht="16.5" spans="1:17">
       <c r="A53" s="5" t="str">
@@ -4287,15 +4319,15 @@
       <c r="I53" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L53" s="47"/>
+      <c r="L53" s="48"/>
       <c r="M53" s="5"/>
-      <c r="N53" s="46">
-        <v>3</v>
-      </c>
-      <c r="O53" s="46">
-        <v>3</v>
-      </c>
-      <c r="Q53" s="9"/>
+      <c r="N53" s="47">
+        <v>3</v>
+      </c>
+      <c r="O53" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q53" s="10"/>
     </row>
     <row r="54" customFormat="1" ht="16.5" spans="1:17">
       <c r="A54" s="5" t="str">
@@ -4326,19 +4358,19 @@
       <c r="I54" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L54" s="47" t="s">
+      <c r="L54" s="48" t="s">
         <v>112</v>
       </c>
       <c r="M54" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="N54" s="46">
+      <c r="N54" s="47">
         <v>4</v>
       </c>
-      <c r="O54" s="46">
-        <v>3</v>
-      </c>
-      <c r="Q54" s="9"/>
+      <c r="O54" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="10"/>
     </row>
     <row r="55" customFormat="1" ht="16.5" spans="1:17">
       <c r="A55" s="5" t="str">
@@ -4369,19 +4401,19 @@
       <c r="I55" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L55" s="47" t="s">
+      <c r="L55" s="48" t="s">
         <v>115</v>
       </c>
       <c r="M55" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="N55" s="46">
+      <c r="N55" s="47">
         <v>4</v>
       </c>
-      <c r="O55" s="46">
-        <v>3</v>
-      </c>
-      <c r="Q55" s="9"/>
+      <c r="O55" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q55" s="10"/>
     </row>
     <row r="56" customFormat="1" ht="16.5" spans="1:17">
       <c r="A56" s="5" t="str">
@@ -4412,19 +4444,19 @@
       <c r="I56" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L56" s="47" t="s">
+      <c r="L56" s="48" t="s">
         <v>117</v>
       </c>
       <c r="M56" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="N56" s="46">
+      <c r="N56" s="47">
         <v>4</v>
       </c>
-      <c r="O56" s="46">
-        <v>3</v>
-      </c>
-      <c r="Q56" s="9"/>
+      <c r="O56" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q56" s="10"/>
     </row>
     <row r="57" customFormat="1" ht="16.5" spans="1:17">
       <c r="A57" s="5" t="str">
@@ -4455,19 +4487,19 @@
       <c r="I57" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L57" s="47" t="s">
+      <c r="L57" s="48" t="s">
         <v>120</v>
       </c>
       <c r="M57" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="N57" s="46">
+      <c r="N57" s="47">
         <v>4</v>
       </c>
-      <c r="O57" s="46">
-        <v>3</v>
-      </c>
-      <c r="Q57" s="9"/>
+      <c r="O57" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="10"/>
     </row>
     <row r="58" customFormat="1" ht="16.5" spans="1:17">
       <c r="A58" s="5" t="str">
@@ -4498,19 +4530,19 @@
       <c r="I58" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L58" s="47" t="s">
+      <c r="L58" s="48" t="s">
         <v>121</v>
       </c>
       <c r="M58" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="N58" s="46">
+      <c r="N58" s="47">
         <v>4</v>
       </c>
-      <c r="O58" s="46">
-        <v>3</v>
-      </c>
-      <c r="Q58" s="9"/>
+      <c r="O58" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="10"/>
     </row>
     <row r="59" customFormat="1" ht="16.5" spans="1:17">
       <c r="A59" s="5" t="str">
@@ -4541,19 +4573,19 @@
       <c r="I59" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L59" s="47" t="s">
+      <c r="L59" s="48" t="s">
         <v>122</v>
       </c>
       <c r="M59" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="N59" s="46">
+      <c r="N59" s="47">
         <v>4</v>
       </c>
-      <c r="O59" s="46">
-        <v>3</v>
-      </c>
-      <c r="Q59" s="9"/>
+      <c r="O59" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="10"/>
     </row>
     <row r="60" customFormat="1" ht="16.5" spans="1:17">
       <c r="A60" s="5" t="str">
@@ -4584,19 +4616,19 @@
       <c r="I60" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L60" s="47" t="s">
+      <c r="L60" s="48" t="s">
         <v>124</v>
       </c>
       <c r="M60" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="N60" s="46">
-        <v>3</v>
-      </c>
-      <c r="O60" s="46">
-        <v>3</v>
-      </c>
-      <c r="Q60" s="9"/>
+      <c r="N60" s="47">
+        <v>3</v>
+      </c>
+      <c r="O60" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="10"/>
     </row>
     <row r="61" customFormat="1" ht="16.5" spans="1:17">
       <c r="A61" s="5" t="str">
@@ -4627,19 +4659,19 @@
       <c r="I61" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L61" s="47">
+      <c r="L61" s="48">
         <v>10360004</v>
       </c>
       <c r="M61" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="N61" s="46">
-        <v>3</v>
-      </c>
-      <c r="O61" s="46">
-        <v>3</v>
-      </c>
-      <c r="Q61" s="9"/>
+      <c r="N61" s="47">
+        <v>3</v>
+      </c>
+      <c r="O61" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q61" s="10"/>
     </row>
     <row r="62" customFormat="1" ht="16.5" spans="1:17">
       <c r="A62" s="5" t="str">
@@ -4670,19 +4702,19 @@
       <c r="I62" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L62" s="47">
+      <c r="L62" s="48">
         <v>10360002</v>
       </c>
       <c r="M62" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="N62" s="46">
-        <v>3</v>
-      </c>
-      <c r="O62" s="46">
-        <v>3</v>
-      </c>
-      <c r="Q62" s="9"/>
+      <c r="N62" s="47">
+        <v>3</v>
+      </c>
+      <c r="O62" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="10"/>
     </row>
     <row r="63" customFormat="1" ht="16.5" spans="1:17">
       <c r="A63" s="5" t="str">
@@ -4713,19 +4745,19 @@
       <c r="I63" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L63" s="47" t="s">
+      <c r="L63" s="48" t="s">
         <v>129</v>
       </c>
       <c r="M63" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="N63" s="46">
-        <v>5</v>
-      </c>
-      <c r="O63" s="46">
+      <c r="N63" s="47">
+        <v>5</v>
+      </c>
+      <c r="O63" s="47">
         <v>6</v>
       </c>
-      <c r="Q63" s="9"/>
+      <c r="Q63" s="10"/>
     </row>
     <row r="64" customFormat="1" ht="16.5" spans="1:17">
       <c r="A64" s="5" t="str">
@@ -4756,19 +4788,19 @@
       <c r="I64" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L64" s="47">
+      <c r="L64" s="48">
         <v>10280002</v>
       </c>
       <c r="M64" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="N64" s="46">
-        <v>5</v>
-      </c>
-      <c r="O64" s="46">
+      <c r="N64" s="47">
+        <v>5</v>
+      </c>
+      <c r="O64" s="47">
         <v>6</v>
       </c>
-      <c r="Q64" s="9"/>
+      <c r="Q64" s="10"/>
     </row>
     <row r="65" customFormat="1" ht="16.5" spans="1:17">
       <c r="A65" s="5" t="str">
@@ -4799,19 +4831,19 @@
       <c r="I65" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L65" s="47" t="s">
+      <c r="L65" s="48" t="s">
         <v>132</v>
       </c>
       <c r="M65" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N65" s="46">
-        <v>5</v>
-      </c>
-      <c r="O65" s="46">
+      <c r="N65" s="47">
+        <v>5</v>
+      </c>
+      <c r="O65" s="47">
         <v>6</v>
       </c>
-      <c r="Q65" s="9"/>
+      <c r="Q65" s="10"/>
     </row>
     <row r="66" customFormat="1" ht="16.5" spans="1:17">
       <c r="A66" s="5" t="str">
@@ -4842,19 +4874,19 @@
       <c r="I66" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L66" s="47">
+      <c r="L66" s="48">
         <v>10340007</v>
       </c>
       <c r="M66" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="N66" s="46">
-        <v>3</v>
-      </c>
-      <c r="O66" s="46">
-        <v>3</v>
-      </c>
-      <c r="Q66" s="9"/>
+      <c r="N66" s="47">
+        <v>3</v>
+      </c>
+      <c r="O66" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="10"/>
     </row>
     <row r="67" customFormat="1" ht="16.5" spans="1:17">
       <c r="A67" s="5" t="str">
@@ -4885,16 +4917,16 @@
       <c r="I67" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L67" s="47"/>
+      <c r="L67" s="48"/>
       <c r="M67" s="5"/>
-      <c r="N67" s="46">
-        <v>3</v>
-      </c>
-      <c r="O67" s="46">
-        <v>3</v>
-      </c>
-      <c r="P67" s="51"/>
-      <c r="Q67" s="9"/>
+      <c r="N67" s="47">
+        <v>3</v>
+      </c>
+      <c r="O67" s="47">
+        <v>3</v>
+      </c>
+      <c r="P67" s="52"/>
+      <c r="Q67" s="10"/>
     </row>
     <row r="68" s="6" customFormat="1" ht="16.5" spans="1:17">
       <c r="A68" s="5" t="str">
@@ -4927,58 +4959,58 @@
       </c>
       <c r="J68"/>
       <c r="K68"/>
-      <c r="L68" s="47"/>
+      <c r="L68" s="48"/>
       <c r="M68" s="5"/>
-      <c r="N68" s="46">
+      <c r="N68" s="47">
         <v>4</v>
       </c>
-      <c r="O68" s="46">
+      <c r="O68" s="47">
         <v>4</v>
       </c>
-      <c r="Q68" s="52"/>
+      <c r="Q68" s="53"/>
     </row>
     <row r="69" s="6" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A69" s="53" t="str">
+      <c r="A69" s="54" t="str">
         <f t="shared" si="3"/>
         <v>1020001</v>
       </c>
-      <c r="B69" s="53">
+      <c r="B69" s="54">
         <v>102000</v>
       </c>
-      <c r="C69" s="53">
-        <v>1</v>
-      </c>
-      <c r="D69" s="53" t="s">
+      <c r="C69" s="54">
+        <v>1</v>
+      </c>
+      <c r="D69" s="54" t="s">
         <v>135</v>
       </c>
-      <c r="E69" s="53" t="s">
+      <c r="E69" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="F69" s="53">
-        <v>1</v>
-      </c>
-      <c r="G69" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="H69" s="53">
+      <c r="F69" s="54">
+        <v>1</v>
+      </c>
+      <c r="G69" s="54" t="s">
+        <v>23</v>
+      </c>
+      <c r="H69" s="54">
         <v>2020001</v>
       </c>
-      <c r="I69" s="53" t="s">
-        <v>24</v>
-      </c>
-      <c r="L69" s="54" t="s">
+      <c r="I69" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="L69" s="55" t="s">
         <v>136</v>
       </c>
-      <c r="M69" s="53" t="s">
+      <c r="M69" s="54" t="s">
         <v>137</v>
       </c>
-      <c r="N69" s="55">
-        <v>5</v>
-      </c>
-      <c r="O69" s="55">
-        <v>5</v>
-      </c>
-      <c r="Q69" s="52"/>
+      <c r="N69" s="56">
+        <v>5</v>
+      </c>
+      <c r="O69" s="56">
+        <v>5</v>
+      </c>
+      <c r="Q69" s="53"/>
     </row>
     <row r="70" customFormat="1" ht="16.5" spans="1:17">
       <c r="A70" s="5" t="str">
@@ -5009,19 +5041,19 @@
       <c r="I70" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L70" s="47" t="s">
+      <c r="L70" s="48" t="s">
         <v>138</v>
       </c>
       <c r="M70" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="N70" s="46">
-        <v>5</v>
-      </c>
-      <c r="O70" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q70" s="9"/>
+      <c r="N70" s="47">
+        <v>5</v>
+      </c>
+      <c r="O70" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q70" s="10"/>
     </row>
     <row r="71" customFormat="1" ht="16.5" spans="1:17">
       <c r="A71" s="5" t="str">
@@ -5052,62 +5084,62 @@
       <c r="I71" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L71" s="47" t="s">
+      <c r="L71" s="48" t="s">
         <v>140</v>
       </c>
       <c r="M71" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="N71" s="46">
-        <v>5</v>
-      </c>
-      <c r="O71" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q71" s="9"/>
+      <c r="N71" s="47">
+        <v>5</v>
+      </c>
+      <c r="O71" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q71" s="10"/>
     </row>
     <row r="72" s="7" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A72" s="56" t="str">
+      <c r="A72" s="57" t="str">
         <f t="shared" si="3"/>
         <v>1020004</v>
       </c>
-      <c r="B72" s="56">
+      <c r="B72" s="57">
         <v>102000</v>
       </c>
-      <c r="C72" s="56">
+      <c r="C72" s="57">
         <v>4</v>
       </c>
-      <c r="D72" s="56" t="s">
+      <c r="D72" s="57" t="s">
         <v>135</v>
       </c>
-      <c r="E72" s="56" t="s">
+      <c r="E72" s="57" t="s">
         <v>142</v>
       </c>
-      <c r="F72" s="56">
-        <v>1</v>
-      </c>
-      <c r="G72" s="56" t="s">
-        <v>23</v>
-      </c>
-      <c r="H72" s="56">
+      <c r="F72" s="57">
+        <v>1</v>
+      </c>
+      <c r="G72" s="57" t="s">
+        <v>23</v>
+      </c>
+      <c r="H72" s="57">
         <v>2020002</v>
       </c>
-      <c r="I72" s="56" t="s">
-        <v>24</v>
-      </c>
-      <c r="L72" s="57">
+      <c r="I72" s="57" t="s">
+        <v>24</v>
+      </c>
+      <c r="L72" s="58">
         <v>10200016</v>
       </c>
-      <c r="M72" s="56" t="s">
+      <c r="M72" s="57" t="s">
         <v>143</v>
       </c>
-      <c r="N72" s="58">
-        <v>5</v>
-      </c>
-      <c r="O72" s="58">
-        <v>5</v>
-      </c>
-      <c r="Q72" s="59"/>
+      <c r="N72" s="59">
+        <v>5</v>
+      </c>
+      <c r="O72" s="59">
+        <v>5</v>
+      </c>
+      <c r="Q72" s="60"/>
     </row>
     <row r="73" customFormat="1" ht="16.5" spans="1:17">
       <c r="A73" s="5" t="str">
@@ -5138,19 +5170,19 @@
       <c r="I73" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L73" s="47">
+      <c r="L73" s="48">
         <v>10200021</v>
       </c>
       <c r="M73" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="N73" s="46">
-        <v>5</v>
-      </c>
-      <c r="O73" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q73" s="9"/>
+      <c r="N73" s="47">
+        <v>5</v>
+      </c>
+      <c r="O73" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q73" s="10"/>
     </row>
     <row r="74" customFormat="1" ht="16.5" spans="1:17">
       <c r="A74" s="5" t="str">
@@ -5184,17 +5216,17 @@
       <c r="J74" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="L74" s="47"/>
+      <c r="L74" s="48"/>
       <c r="M74" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="N74" s="46">
-        <v>3</v>
-      </c>
-      <c r="O74" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q74" s="9"/>
+      <c r="N74" s="47">
+        <v>3</v>
+      </c>
+      <c r="O74" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q74" s="10"/>
     </row>
     <row r="75" customFormat="1" ht="16.5" spans="1:17">
       <c r="A75" s="5" t="str">
@@ -5225,19 +5257,19 @@
       <c r="I75" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L75" s="47">
+      <c r="L75" s="48">
         <v>10380002</v>
       </c>
       <c r="M75" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="N75" s="46">
-        <v>3</v>
-      </c>
-      <c r="O75" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q75" s="9"/>
+      <c r="N75" s="47">
+        <v>3</v>
+      </c>
+      <c r="O75" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q75" s="10"/>
     </row>
     <row r="76" customFormat="1" ht="16.5" spans="1:17">
       <c r="A76" s="5" t="str">
@@ -5268,19 +5300,19 @@
       <c r="I76" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L76" s="47" t="s">
+      <c r="L76" s="48" t="s">
         <v>151</v>
       </c>
       <c r="M76" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="N76" s="46">
-        <v>3</v>
-      </c>
-      <c r="O76" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q76" s="9"/>
+      <c r="N76" s="47">
+        <v>3</v>
+      </c>
+      <c r="O76" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q76" s="10"/>
     </row>
     <row r="77" customFormat="1" ht="16.5" spans="1:17">
       <c r="A77" s="5" t="str">
@@ -5311,19 +5343,19 @@
       <c r="I77" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L77" s="47" t="s">
+      <c r="L77" s="48" t="s">
         <v>153</v>
       </c>
       <c r="M77" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="N77" s="46">
-        <v>3</v>
-      </c>
-      <c r="O77" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q77" s="9"/>
+      <c r="N77" s="47">
+        <v>3</v>
+      </c>
+      <c r="O77" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q77" s="10"/>
     </row>
     <row r="78" customFormat="1" ht="16.5" spans="1:17">
       <c r="A78" s="5" t="str">
@@ -5354,19 +5386,19 @@
       <c r="I78" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L78" s="47" t="s">
+      <c r="L78" s="48" t="s">
         <v>156</v>
       </c>
       <c r="M78" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="N78" s="46">
-        <v>3</v>
-      </c>
-      <c r="O78" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q78" s="9"/>
+      <c r="N78" s="47">
+        <v>3</v>
+      </c>
+      <c r="O78" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q78" s="10"/>
     </row>
     <row r="79" customFormat="1" ht="16.5" spans="1:17">
       <c r="A79" s="5" t="str">
@@ -5397,19 +5429,19 @@
       <c r="I79" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L79" s="47">
+      <c r="L79" s="48">
         <v>10270003</v>
       </c>
       <c r="M79" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="N79" s="46">
-        <v>3</v>
-      </c>
-      <c r="O79" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q79" s="9"/>
+      <c r="N79" s="47">
+        <v>3</v>
+      </c>
+      <c r="O79" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q79" s="10"/>
     </row>
     <row r="80" customFormat="1" ht="16.5" spans="1:17">
       <c r="A80" s="5" t="str">
@@ -5440,19 +5472,19 @@
       <c r="I80" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L80" s="47" t="s">
+      <c r="L80" s="48" t="s">
         <v>159</v>
       </c>
       <c r="M80" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="N80" s="46">
-        <v>3</v>
-      </c>
-      <c r="O80" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q80" s="9"/>
+      <c r="N80" s="47">
+        <v>3</v>
+      </c>
+      <c r="O80" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q80" s="10"/>
     </row>
     <row r="81" customFormat="1" ht="16.5" spans="1:17">
       <c r="A81" s="5" t="str">
@@ -5483,19 +5515,19 @@
       <c r="I81" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L81" s="47">
+      <c r="L81" s="48">
         <v>10370001</v>
       </c>
       <c r="M81" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="N81" s="46">
+      <c r="N81" s="47">
         <v>4</v>
       </c>
-      <c r="O81" s="46">
-        <v>3</v>
-      </c>
-      <c r="Q81" s="9"/>
+      <c r="O81" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="10"/>
     </row>
     <row r="82" customFormat="1" ht="16.5" spans="1:17">
       <c r="A82" s="5" t="str">
@@ -5526,19 +5558,19 @@
       <c r="I82" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L82" s="47">
+      <c r="L82" s="48">
         <v>10370003</v>
       </c>
       <c r="M82" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="N82" s="46">
+      <c r="N82" s="47">
         <v>4</v>
       </c>
-      <c r="O82" s="46">
-        <v>3</v>
-      </c>
-      <c r="Q82" s="9"/>
+      <c r="O82" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q82" s="10"/>
     </row>
     <row r="83" customFormat="1" ht="16.5" spans="1:17">
       <c r="A83" s="5" t="str">
@@ -5569,19 +5601,19 @@
       <c r="I83" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L83" s="47"/>
+      <c r="L83" s="48"/>
       <c r="M83" s="5"/>
-      <c r="N83" s="46">
+      <c r="N83" s="47">
         <v>4</v>
       </c>
-      <c r="O83" s="46">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="9"/>
+      <c r="O83" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="10"/>
     </row>
     <row r="84" customFormat="1" ht="16.5" spans="1:17">
       <c r="A84" s="5" t="str">
-        <f t="shared" ref="A84:A89" si="4">B84&amp;C84</f>
+        <f t="shared" ref="A84:A92" si="4">B84&amp;C84</f>
         <v>1031001</v>
       </c>
       <c r="B84" s="5">
@@ -5608,19 +5640,19 @@
       <c r="I84" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L84" s="47" t="s">
+      <c r="L84" s="48" t="s">
         <v>165</v>
       </c>
       <c r="M84" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="N84" s="46">
-        <v>3</v>
-      </c>
-      <c r="O84" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q84" s="9"/>
+      <c r="N84" s="47">
+        <v>3</v>
+      </c>
+      <c r="O84" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q84" s="10"/>
     </row>
     <row r="85" customFormat="1" ht="16.5" spans="1:17">
       <c r="A85" s="5" t="str">
@@ -5640,7 +5672,7 @@
         <v>131</v>
       </c>
       <c r="F85" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G85" s="5" t="s">
         <v>23</v>
@@ -5651,19 +5683,19 @@
       <c r="I85" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L85" s="47">
+      <c r="L85" s="48">
         <v>10310008</v>
       </c>
       <c r="M85" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="N85" s="46">
-        <v>3</v>
-      </c>
-      <c r="O85" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q85" s="9"/>
+      <c r="N85" s="47">
+        <v>3</v>
+      </c>
+      <c r="O85" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q85" s="10"/>
     </row>
     <row r="86" customFormat="1" ht="16.5" spans="1:17">
       <c r="A86" s="5" t="str">
@@ -5683,7 +5715,7 @@
         <v>94</v>
       </c>
       <c r="F86" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G86" s="5" t="s">
         <v>23</v>
@@ -5694,19 +5726,19 @@
       <c r="I86" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L86" s="47" t="s">
+      <c r="L86" s="48" t="s">
         <v>168</v>
       </c>
       <c r="M86" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="N86" s="46">
-        <v>3</v>
-      </c>
-      <c r="O86" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q86" s="9"/>
+      <c r="N86" s="47">
+        <v>3</v>
+      </c>
+      <c r="O86" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q86" s="10"/>
     </row>
     <row r="87" customFormat="1" ht="16.5" spans="1:17">
       <c r="A87" s="5" t="str">
@@ -5726,7 +5758,7 @@
         <v>81</v>
       </c>
       <c r="F87" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G87" s="5" t="s">
         <v>23</v>
@@ -5737,19 +5769,19 @@
       <c r="I87" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L87" s="47" t="s">
+      <c r="L87" s="48" t="s">
         <v>170</v>
       </c>
       <c r="M87" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="N87" s="46">
-        <v>3</v>
-      </c>
-      <c r="O87" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q87" s="9"/>
+      <c r="N87" s="47">
+        <v>3</v>
+      </c>
+      <c r="O87" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q87" s="10"/>
     </row>
     <row r="88" customFormat="1" ht="16.5" spans="1:17">
       <c r="A88" s="5" t="str">
@@ -5769,7 +5801,7 @@
         <v>172</v>
       </c>
       <c r="F88" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G88" s="5" t="s">
         <v>23</v>
@@ -5780,19 +5812,19 @@
       <c r="I88" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L88" s="47">
+      <c r="L88" s="48">
         <v>10310003</v>
       </c>
       <c r="M88" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="N88" s="46">
-        <v>3</v>
-      </c>
-      <c r="O88" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q88" s="9"/>
+      <c r="N88" s="47">
+        <v>3</v>
+      </c>
+      <c r="O88" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q88" s="10"/>
     </row>
     <row r="89" customFormat="1" ht="16.5" spans="1:17">
       <c r="A89" s="5" t="str">
@@ -5812,7 +5844,7 @@
         <v>174</v>
       </c>
       <c r="F89" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G89" s="5" t="s">
         <v>23</v>
@@ -5823,19 +5855,277 @@
       <c r="I89" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L89" s="47" t="s">
+      <c r="L89" s="48" t="s">
         <v>175</v>
       </c>
       <c r="M89" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="N89" s="46">
-        <v>3</v>
-      </c>
-      <c r="O89" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q89" s="9"/>
+      <c r="N89" s="47">
+        <v>3</v>
+      </c>
+      <c r="O89" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q89" s="10"/>
+    </row>
+    <row r="90" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A90" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>1040001</v>
+      </c>
+      <c r="B90" s="5">
+        <v>104000</v>
+      </c>
+      <c r="C90" s="5">
+        <v>1</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F90" s="5">
+        <v>1</v>
+      </c>
+      <c r="G90" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H90" s="5">
+        <v>2040001</v>
+      </c>
+      <c r="I90" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L90" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="M90" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="N90" s="47">
+        <v>3</v>
+      </c>
+      <c r="O90" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q90" s="10"/>
+    </row>
+    <row r="91" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A91" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>1040002</v>
+      </c>
+      <c r="B91" s="5">
+        <v>104000</v>
+      </c>
+      <c r="C91" s="5">
+        <v>2</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E91" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F91" s="5">
+        <v>1</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H91" s="5">
+        <v>2040001</v>
+      </c>
+      <c r="I91" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L91" s="48" t="s">
+        <v>180</v>
+      </c>
+      <c r="M91" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="N91" s="47">
+        <v>3</v>
+      </c>
+      <c r="O91" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q91" s="10"/>
+    </row>
+    <row r="92" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A92" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>1040003</v>
+      </c>
+      <c r="B92" s="5">
+        <v>104000</v>
+      </c>
+      <c r="C92" s="5">
+        <v>3</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E92" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F92" s="5">
+        <v>1</v>
+      </c>
+      <c r="G92" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H92" s="5">
+        <v>2040001</v>
+      </c>
+      <c r="I92" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L92" s="48" t="s">
+        <v>182</v>
+      </c>
+      <c r="M92" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="N92" s="47">
+        <v>3</v>
+      </c>
+      <c r="O92" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q92" s="10"/>
+    </row>
+    <row r="93" s="8" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A93" s="5" t="str">
+        <f>B93&amp;C93</f>
+        <v>1039001</v>
+      </c>
+      <c r="B93" s="8">
+        <v>103900</v>
+      </c>
+      <c r="C93" s="5">
+        <v>1</v>
+      </c>
+      <c r="D93" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F93" s="5">
+        <v>1</v>
+      </c>
+      <c r="G93" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H93" s="8">
+        <v>2039001</v>
+      </c>
+      <c r="I93" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L93" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="M93" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="N93" s="47">
+        <v>3</v>
+      </c>
+      <c r="O93" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q93" s="61"/>
+    </row>
+    <row r="94" s="8" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A94" s="5" t="str">
+        <f>B94&amp;C94</f>
+        <v>1039002</v>
+      </c>
+      <c r="B94" s="8">
+        <v>103900</v>
+      </c>
+      <c r="C94" s="5">
+        <v>2</v>
+      </c>
+      <c r="D94" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="E94" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F94" s="5">
+        <v>1</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H94" s="8">
+        <v>2039001</v>
+      </c>
+      <c r="I94" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L94" s="48">
+        <v>10390003</v>
+      </c>
+      <c r="M94" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="N94" s="47">
+        <v>3</v>
+      </c>
+      <c r="O94" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q94" s="61"/>
+    </row>
+    <row r="95" s="8" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A95" s="5" t="str">
+        <f>B95&amp;C95</f>
+        <v>1039003</v>
+      </c>
+      <c r="B95" s="8">
+        <v>103900</v>
+      </c>
+      <c r="C95" s="5">
+        <v>3</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="E95" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F95" s="5">
+        <v>1</v>
+      </c>
+      <c r="G95" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H95" s="8">
+        <v>2039001</v>
+      </c>
+      <c r="I95" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L95" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="M95" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="N95" s="47">
+        <v>3</v>
+      </c>
+      <c r="O95" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q95" s="61"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:K2">

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="193">
   <si>
     <t>id</t>
   </si>
@@ -687,6 +687,24 @@
   </si>
   <si>
     <t>10390005|10390006</t>
+  </si>
+  <si>
+    <t>热血足球</t>
+  </si>
+  <si>
+    <t>10160001|10160003|10160005|10160006|10160007</t>
+  </si>
+  <si>
+    <t>概率出现wild+概率改出3个SCATTER+概率改出占据2、3、4个格子符号</t>
+  </si>
+  <si>
+    <t>改出4个以上SCATTER</t>
+  </si>
+  <si>
+    <t>10160004|10160009</t>
+  </si>
+  <si>
+    <t>改出3个SCATTER+奖池符号</t>
   </si>
 </sst>
 </file>
@@ -1417,7 +1435,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1426,7 +1444,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1545,7 +1562,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2079,7 +2098,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S95"/>
+  <dimension ref="A1:S112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
@@ -2092,14 +2111,14 @@
     <col min="11" max="11" width="16.75" customWidth="1"/>
     <col min="12" max="12" width="53.25" customWidth="1"/>
     <col min="13" max="13" width="21.6083333333333" customWidth="1"/>
-    <col min="14" max="15" width="9" style="9"/>
+    <col min="14" max="15" width="9" style="8"/>
     <col min="16" max="16" width="15" customWidth="1"/>
-    <col min="17" max="17" width="23.75" style="10" customWidth="1"/>
+    <col min="17" max="17" width="23.75" style="9" customWidth="1"/>
     <col min="18" max="18" width="60.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:17">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
@@ -2110,34 +2129,34 @@
       </c>
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="11" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="5"/>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="11" t="s">
         <v>4</v>
       </c>
       <c r="I1" s="5"/>
-      <c r="J1" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="13"/>
-      <c r="L1" s="14" t="s">
+      <c r="J1" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="12"/>
+      <c r="L1" s="13" t="s">
         <v>6</v>
       </c>
       <c r="M1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="15" t="s">
+      <c r="N1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="15" t="s">
+      <c r="O1" s="14" t="s">
         <v>9</v>
       </c>
       <c r="Q1"/>
     </row>
     <row r="2" ht="16.5" spans="1:17">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -2148,62 +2167,62 @@
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="11" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="5"/>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="11" t="s">
         <v>10</v>
       </c>
       <c r="I2" s="5"/>
-      <c r="J2" s="16" t="s">
+      <c r="J2" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="17"/>
-      <c r="L2" s="18" t="s">
+      <c r="K2" s="16"/>
+      <c r="L2" s="17" t="s">
         <v>12</v>
       </c>
       <c r="M2" s="5"/>
-      <c r="N2" s="19" t="s">
+      <c r="N2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="19" t="s">
+      <c r="O2" s="18" t="s">
         <v>10</v>
       </c>
       <c r="Q2"/>
     </row>
     <row r="3" ht="16.5" spans="1:17">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="21" t="s">
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="20"/>
-      <c r="H3" s="22" t="s">
+      <c r="G3" s="19"/>
+      <c r="H3" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="20"/>
-      <c r="J3" s="23" t="s">
+      <c r="I3" s="19"/>
+      <c r="J3" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="23"/>
-      <c r="L3" s="24" t="s">
+      <c r="K3" s="22"/>
+      <c r="L3" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="M3" s="20"/>
-      <c r="N3" s="19" t="s">
+      <c r="M3" s="19"/>
+      <c r="N3" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="19" t="s">
+      <c r="O3" s="18" t="s">
         <v>20</v>
       </c>
       <c r="Q3"/>
@@ -2213,1101 +2232,1101 @@
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="12"/>
+      <c r="F4" s="11"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="12"/>
+      <c r="H4" s="11"/>
       <c r="I4" s="5"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="14"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="13"/>
       <c r="M4" s="5"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="18"/>
       <c r="Q4"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A5" s="26" t="str">
+      <c r="A5" s="25" t="str">
         <f t="shared" ref="A5:A15" si="0">B5&amp;C5</f>
         <v>1001001</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="26">
         <v>100100</v>
       </c>
-      <c r="C5" s="27">
-        <v>1</v>
-      </c>
-      <c r="D5" s="27" t="s">
+      <c r="C5" s="26">
+        <v>1</v>
+      </c>
+      <c r="D5" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="E5" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="27">
-        <v>1</v>
-      </c>
-      <c r="G5" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="26">
+      <c r="F5" s="26">
+        <v>1</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="25">
         <v>2001001</v>
       </c>
-      <c r="I5" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="29" t="s">
+      <c r="I5" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="M5" s="26" t="s">
+      <c r="M5" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="N5" s="19">
+      <c r="N5" s="18">
         <v>4</v>
       </c>
-      <c r="O5" s="19">
+      <c r="O5" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A6" s="26" t="str">
+      <c r="A6" s="25" t="str">
         <f t="shared" si="0"/>
         <v>1001002</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="26">
         <v>100100</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="26">
         <v>2</v>
       </c>
-      <c r="D6" s="27"/>
-      <c r="E6" s="30" t="s">
+      <c r="D6" s="26"/>
+      <c r="E6" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="27">
-        <v>1</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="26">
+      <c r="F6" s="26">
+        <v>1</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="25">
         <v>2001001</v>
       </c>
-      <c r="I6" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="31" t="s">
+      <c r="I6" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="M6" s="26" t="s">
+      <c r="M6" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="N6" s="19">
+      <c r="N6" s="18">
         <v>4</v>
       </c>
-      <c r="O6" s="19">
+      <c r="O6" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A7" s="26" t="str">
+      <c r="A7" s="25" t="str">
         <f t="shared" si="0"/>
         <v>1001003</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="26">
         <v>100100</v>
       </c>
-      <c r="C7" s="27">
-        <v>3</v>
-      </c>
-      <c r="D7" s="27"/>
-      <c r="E7" s="32" t="s">
+      <c r="C7" s="26">
+        <v>3</v>
+      </c>
+      <c r="D7" s="26"/>
+      <c r="E7" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="27">
-        <v>1</v>
-      </c>
-      <c r="G7" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="26">
+      <c r="F7" s="26">
+        <v>1</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="25">
         <v>2001001</v>
       </c>
-      <c r="I7" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="29" t="s">
+      <c r="I7" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="M7" s="26" t="s">
+      <c r="M7" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="N7" s="19">
+      <c r="N7" s="18">
         <v>4</v>
       </c>
-      <c r="O7" s="19">
+      <c r="O7" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A8" s="26" t="str">
+      <c r="A8" s="25" t="str">
         <f t="shared" si="0"/>
         <v>1001004</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="26">
         <v>100100</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="26">
         <v>4</v>
       </c>
-      <c r="D8" s="27"/>
-      <c r="E8" s="33" t="s">
+      <c r="D8" s="26"/>
+      <c r="E8" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="34">
-        <v>1</v>
-      </c>
-      <c r="G8" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="26">
+      <c r="F8" s="33">
+        <v>1</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="25">
         <v>2001001</v>
       </c>
-      <c r="I8" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" s="26"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="29">
+      <c r="I8" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="28">
         <v>10010041</v>
       </c>
-      <c r="M8" s="26" t="s">
+      <c r="M8" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="N8" s="19">
+      <c r="N8" s="18">
         <v>4</v>
       </c>
-      <c r="O8" s="19">
+      <c r="O8" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A9" s="26" t="str">
+      <c r="A9" s="25" t="str">
         <f t="shared" si="0"/>
         <v>1001005</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="26">
         <v>100100</v>
       </c>
-      <c r="C9" s="27">
-        <v>5</v>
-      </c>
-      <c r="D9" s="27"/>
-      <c r="E9" s="35" t="s">
+      <c r="C9" s="26">
+        <v>5</v>
+      </c>
+      <c r="D9" s="26"/>
+      <c r="E9" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="34">
-        <v>1</v>
-      </c>
-      <c r="G9" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="26">
+      <c r="F9" s="33">
+        <v>1</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="25">
         <v>2001001</v>
       </c>
-      <c r="I9" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" s="26"/>
-      <c r="K9" s="26"/>
-      <c r="L9" s="29" t="s">
+      <c r="I9" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="M9" s="26" t="s">
+      <c r="M9" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N9" s="19">
+      <c r="N9" s="18">
         <v>4</v>
       </c>
-      <c r="O9" s="19">
+      <c r="O9" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A10" s="26" t="str">
+      <c r="A10" s="25" t="str">
         <f t="shared" si="0"/>
         <v>1001006</v>
       </c>
-      <c r="B10" s="27">
+      <c r="B10" s="26">
         <v>100100</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="26">
         <v>6</v>
       </c>
-      <c r="D10" s="27"/>
-      <c r="E10" s="35" t="s">
+      <c r="D10" s="26"/>
+      <c r="E10" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="34">
-        <v>1</v>
-      </c>
-      <c r="G10" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="26">
+      <c r="F10" s="33">
+        <v>1</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="25">
         <v>2001001</v>
       </c>
-      <c r="I10" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="J10" s="26"/>
-      <c r="K10" s="26"/>
-      <c r="L10" s="29">
+      <c r="I10" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="28">
         <v>10010061</v>
       </c>
-      <c r="M10" s="26" t="s">
+      <c r="M10" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="N10" s="19">
+      <c r="N10" s="18">
         <v>4</v>
       </c>
-      <c r="O10" s="19">
+      <c r="O10" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A11" s="26" t="str">
+      <c r="A11" s="25" t="str">
         <f t="shared" si="0"/>
         <v>1001007</v>
       </c>
-      <c r="B11" s="27">
+      <c r="B11" s="26">
         <v>100100</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="26">
         <v>7</v>
       </c>
-      <c r="D11" s="27"/>
-      <c r="E11" s="30" t="s">
+      <c r="D11" s="26"/>
+      <c r="E11" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="27">
-        <v>1</v>
-      </c>
-      <c r="G11" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" s="26">
+      <c r="F11" s="26">
+        <v>1</v>
+      </c>
+      <c r="G11" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="25">
         <v>2001001</v>
       </c>
-      <c r="I11" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="J11" s="26"/>
-      <c r="K11" s="26"/>
-      <c r="L11" s="31" t="s">
+      <c r="I11" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="M11" s="26" t="s">
+      <c r="M11" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="N11" s="19">
+      <c r="N11" s="18">
         <v>4</v>
       </c>
-      <c r="O11" s="19">
+      <c r="O11" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A12" s="36" t="str">
+      <c r="A12" s="35" t="str">
         <f t="shared" si="0"/>
         <v>1003001</v>
       </c>
-      <c r="B12" s="28">
+      <c r="B12" s="27">
         <v>100300</v>
       </c>
-      <c r="C12" s="28">
-        <v>1</v>
-      </c>
-      <c r="D12" s="28" t="s">
+      <c r="C12" s="27">
+        <v>1</v>
+      </c>
+      <c r="D12" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="28" t="s">
+      <c r="E12" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="28">
-        <v>1</v>
-      </c>
-      <c r="G12" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="H12" s="36">
+      <c r="F12" s="27">
+        <v>1</v>
+      </c>
+      <c r="G12" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="35">
         <v>2003001</v>
       </c>
-      <c r="I12" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" s="36"/>
-      <c r="K12" s="36"/>
-      <c r="L12" s="37">
+      <c r="I12" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" s="35"/>
+      <c r="K12" s="35"/>
+      <c r="L12" s="36">
         <v>10030022</v>
       </c>
-      <c r="M12" s="36" t="s">
+      <c r="M12" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="N12" s="28">
-        <v>3</v>
-      </c>
-      <c r="O12" s="28">
-        <v>3</v>
-      </c>
-      <c r="Q12" s="38"/>
+      <c r="N12" s="27">
+        <v>3</v>
+      </c>
+      <c r="O12" s="27">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="37"/>
     </row>
     <row r="13" s="2" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A13" s="36" t="str">
+      <c r="A13" s="35" t="str">
         <f t="shared" ref="A13:A30" si="1">B13&amp;C13</f>
         <v>1003002</v>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="27">
         <v>100300</v>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="27">
         <v>2</v>
       </c>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28" t="s">
+      <c r="D13" s="27"/>
+      <c r="E13" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="28">
-        <v>1</v>
-      </c>
-      <c r="G13" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="H13" s="36">
+      <c r="F13" s="27">
+        <v>1</v>
+      </c>
+      <c r="G13" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="35">
         <v>2003001</v>
       </c>
-      <c r="I13" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="J13" s="36"/>
-      <c r="K13" s="36"/>
-      <c r="L13" s="37" t="s">
+      <c r="I13" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" s="35"/>
+      <c r="K13" s="35"/>
+      <c r="L13" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="M13" s="36" t="s">
+      <c r="M13" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="N13" s="28">
-        <v>3</v>
-      </c>
-      <c r="O13" s="28">
-        <v>3</v>
-      </c>
-      <c r="Q13" s="38"/>
+      <c r="N13" s="27">
+        <v>3</v>
+      </c>
+      <c r="O13" s="27">
+        <v>3</v>
+      </c>
+      <c r="Q13" s="37"/>
     </row>
     <row r="14" s="2" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A14" s="36" t="str">
+      <c r="A14" s="35" t="str">
         <f t="shared" si="1"/>
         <v>1003003</v>
       </c>
-      <c r="B14" s="28">
+      <c r="B14" s="27">
         <v>100300</v>
       </c>
-      <c r="C14" s="28">
-        <v>3</v>
-      </c>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28" t="s">
+      <c r="C14" s="27">
+        <v>3</v>
+      </c>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="28">
-        <v>1</v>
-      </c>
-      <c r="G14" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="H14" s="36">
+      <c r="F14" s="27">
+        <v>1</v>
+      </c>
+      <c r="G14" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="35">
         <v>2003002</v>
       </c>
-      <c r="I14" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="J14" s="36" t="s">
+      <c r="I14" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="K14" s="36" t="s">
+      <c r="K14" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="L14" s="37" t="s">
+      <c r="L14" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="M14" s="36" t="s">
+      <c r="M14" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="N14" s="28">
-        <v>3</v>
-      </c>
-      <c r="O14" s="28">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="38"/>
+      <c r="N14" s="27">
+        <v>3</v>
+      </c>
+      <c r="O14" s="27">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="37"/>
     </row>
     <row r="15" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A15" s="39" t="str">
+      <c r="A15" s="38" t="str">
         <f t="shared" si="1"/>
         <v>1007001</v>
       </c>
-      <c r="B15" s="40">
+      <c r="B15" s="39">
         <v>100700</v>
       </c>
-      <c r="C15" s="40">
-        <v>1</v>
-      </c>
-      <c r="D15" s="40" t="s">
+      <c r="C15" s="39">
+        <v>1</v>
+      </c>
+      <c r="D15" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="40" t="s">
+      <c r="E15" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="40">
-        <v>1</v>
-      </c>
-      <c r="G15" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="H15" s="39">
+      <c r="F15" s="39">
+        <v>1</v>
+      </c>
+      <c r="G15" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="38">
         <v>2007001</v>
       </c>
-      <c r="I15" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="J15" s="39"/>
-      <c r="K15" s="39"/>
-      <c r="L15" s="41" t="s">
+      <c r="I15" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" s="38"/>
+      <c r="K15" s="38"/>
+      <c r="L15" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="M15" s="39" t="s">
+      <c r="M15" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="N15" s="19">
+      <c r="N15" s="18">
         <v>4</v>
       </c>
-      <c r="O15" s="19">
+      <c r="O15" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="16" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A16" s="39" t="str">
+      <c r="A16" s="38" t="str">
         <f t="shared" si="1"/>
         <v>1007002</v>
       </c>
-      <c r="B16" s="40">
+      <c r="B16" s="39">
         <v>100700</v>
       </c>
-      <c r="C16" s="40">
+      <c r="C16" s="39">
         <v>2</v>
       </c>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40" t="s">
+      <c r="D16" s="39"/>
+      <c r="E16" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="40">
-        <v>1</v>
-      </c>
-      <c r="G16" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="H16" s="39">
+      <c r="F16" s="39">
+        <v>1</v>
+      </c>
+      <c r="G16" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="38">
         <v>2007001</v>
       </c>
-      <c r="I16" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="J16" s="39"/>
-      <c r="K16" s="39"/>
-      <c r="L16" s="41" t="s">
+      <c r="I16" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="J16" s="38"/>
+      <c r="K16" s="38"/>
+      <c r="L16" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="M16" s="39" t="s">
+      <c r="M16" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="N16" s="19">
+      <c r="N16" s="18">
         <v>4</v>
       </c>
-      <c r="O16" s="19">
+      <c r="O16" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="17" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A17" s="42" t="str">
+      <c r="A17" s="41" t="str">
         <f t="shared" si="1"/>
         <v>1012001</v>
       </c>
-      <c r="B17" s="43">
+      <c r="B17" s="42">
         <v>101200</v>
       </c>
-      <c r="C17" s="43">
-        <v>1</v>
-      </c>
-      <c r="D17" s="43" t="s">
+      <c r="C17" s="42">
+        <v>1</v>
+      </c>
+      <c r="D17" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="E17" s="43" t="s">
+      <c r="E17" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="43">
-        <v>1</v>
-      </c>
-      <c r="G17" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="H17" s="42">
+      <c r="F17" s="42">
+        <v>1</v>
+      </c>
+      <c r="G17" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="41">
         <v>2012001</v>
       </c>
-      <c r="I17" s="42" t="s">
-        <v>24</v>
-      </c>
-      <c r="J17" s="42"/>
-      <c r="K17" s="42"/>
-      <c r="L17" s="44">
+      <c r="I17" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="J17" s="41"/>
+      <c r="K17" s="41"/>
+      <c r="L17" s="43">
         <v>10120011</v>
       </c>
-      <c r="M17" s="42" t="s">
+      <c r="M17" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="N17" s="43">
-        <v>3</v>
-      </c>
-      <c r="O17" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q17" s="45"/>
+      <c r="N17" s="42">
+        <v>3</v>
+      </c>
+      <c r="O17" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="44"/>
     </row>
     <row r="18" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A18" s="42" t="str">
+      <c r="A18" s="41" t="str">
         <f t="shared" si="1"/>
         <v>1012002</v>
       </c>
-      <c r="B18" s="43">
+      <c r="B18" s="42">
         <v>101200</v>
       </c>
-      <c r="C18" s="43">
+      <c r="C18" s="42">
         <v>2</v>
       </c>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43" t="s">
+      <c r="D18" s="42"/>
+      <c r="E18" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="43">
-        <v>1</v>
-      </c>
-      <c r="G18" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="H18" s="42">
+      <c r="F18" s="42">
+        <v>1</v>
+      </c>
+      <c r="G18" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="41">
         <v>2012001</v>
       </c>
-      <c r="I18" s="42" t="s">
-        <v>24</v>
-      </c>
-      <c r="J18" s="42"/>
-      <c r="K18" s="42"/>
-      <c r="L18" s="44">
+      <c r="I18" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="J18" s="41"/>
+      <c r="K18" s="41"/>
+      <c r="L18" s="43">
         <v>10120021</v>
       </c>
-      <c r="M18" s="42" t="s">
+      <c r="M18" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="N18" s="43">
-        <v>3</v>
-      </c>
-      <c r="O18" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q18" s="45"/>
+      <c r="N18" s="42">
+        <v>3</v>
+      </c>
+      <c r="O18" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="44"/>
     </row>
     <row r="19" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A19" s="42" t="str">
+      <c r="A19" s="41" t="str">
         <f t="shared" si="1"/>
         <v>1012003</v>
       </c>
-      <c r="B19" s="43">
+      <c r="B19" s="42">
         <v>101200</v>
       </c>
-      <c r="C19" s="43">
-        <v>3</v>
-      </c>
-      <c r="D19" s="43"/>
-      <c r="E19" s="43" t="s">
+      <c r="C19" s="42">
+        <v>3</v>
+      </c>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="F19" s="43">
-        <v>1</v>
-      </c>
-      <c r="G19" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="H19" s="42">
+      <c r="F19" s="42">
+        <v>1</v>
+      </c>
+      <c r="G19" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="41">
         <v>2012001</v>
       </c>
-      <c r="I19" s="42" t="s">
-        <v>24</v>
-      </c>
-      <c r="J19" s="42" t="s">
+      <c r="I19" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="J19" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="K19" s="42" t="s">
+      <c r="K19" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="L19" s="44"/>
-      <c r="M19" s="42" t="s">
+      <c r="L19" s="43"/>
+      <c r="M19" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="N19" s="43">
-        <v>3</v>
-      </c>
-      <c r="O19" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q19" s="45"/>
+      <c r="N19" s="42">
+        <v>3</v>
+      </c>
+      <c r="O19" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q19" s="44"/>
     </row>
     <row r="20" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A20" s="36" t="str">
+      <c r="A20" s="35" t="str">
         <f t="shared" si="1"/>
         <v>1014001</v>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="27">
         <v>101400</v>
       </c>
-      <c r="C20" s="28">
-        <v>1</v>
-      </c>
-      <c r="D20" s="28" t="s">
+      <c r="C20" s="27">
+        <v>1</v>
+      </c>
+      <c r="D20" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="E20" s="28" t="s">
+      <c r="E20" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="F20" s="28">
-        <v>1</v>
-      </c>
-      <c r="G20" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="H20" s="36">
+      <c r="F20" s="27">
+        <v>1</v>
+      </c>
+      <c r="G20" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="35">
         <v>2014001</v>
       </c>
-      <c r="I20" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="J20" s="36"/>
-      <c r="K20" s="36"/>
-      <c r="L20" s="37" t="s">
+      <c r="I20" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="J20" s="35"/>
+      <c r="K20" s="35"/>
+      <c r="L20" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="M20" s="36" t="s">
+      <c r="M20" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="N20" s="19">
+      <c r="N20" s="18">
         <v>4</v>
       </c>
-      <c r="O20" s="19">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="46"/>
+      <c r="O20" s="18">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="45"/>
     </row>
     <row r="21" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A21" s="36" t="str">
+      <c r="A21" s="35" t="str">
         <f t="shared" si="1"/>
         <v>1014002</v>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="27">
         <v>101400</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="27">
         <v>2</v>
       </c>
-      <c r="D21" s="28" t="s">
+      <c r="D21" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="E21" s="28" t="s">
+      <c r="E21" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="28">
-        <v>1</v>
-      </c>
-      <c r="G21" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="H21" s="36">
+      <c r="F21" s="27">
+        <v>1</v>
+      </c>
+      <c r="G21" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="35">
         <v>2014001</v>
       </c>
-      <c r="I21" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="J21" s="36"/>
-      <c r="K21" s="36"/>
-      <c r="L21" s="37" t="s">
+      <c r="I21" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="J21" s="35"/>
+      <c r="K21" s="35"/>
+      <c r="L21" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="M21" s="36" t="s">
+      <c r="M21" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="N21" s="19">
+      <c r="N21" s="18">
         <v>4</v>
       </c>
-      <c r="O21" s="19">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="46"/>
+      <c r="O21" s="18">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="45"/>
     </row>
     <row r="22" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A22" s="36" t="str">
+      <c r="A22" s="35" t="str">
         <f t="shared" si="1"/>
         <v>1014003</v>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="27">
         <v>101400</v>
       </c>
-      <c r="C22" s="28">
-        <v>3</v>
-      </c>
-      <c r="D22" s="28" t="s">
+      <c r="C22" s="27">
+        <v>3</v>
+      </c>
+      <c r="D22" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="E22" s="28" t="s">
+      <c r="E22" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="F22" s="28">
-        <v>1</v>
-      </c>
-      <c r="G22" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="H22" s="36">
+      <c r="F22" s="27">
+        <v>1</v>
+      </c>
+      <c r="G22" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="35">
         <v>2014001</v>
       </c>
-      <c r="I22" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="J22" s="36"/>
-      <c r="K22" s="36"/>
-      <c r="L22" s="37">
+      <c r="I22" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="36">
         <v>10140021</v>
       </c>
-      <c r="M22" s="36" t="s">
+      <c r="M22" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="N22" s="19">
+      <c r="N22" s="18">
         <v>4</v>
       </c>
-      <c r="O22" s="19">
-        <v>3</v>
-      </c>
-      <c r="Q22" s="46"/>
+      <c r="O22" s="18">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="45"/>
     </row>
     <row r="23" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A23" s="26" t="str">
+      <c r="A23" s="25" t="str">
         <f t="shared" si="1"/>
         <v>1024001</v>
       </c>
-      <c r="B23" s="27">
+      <c r="B23" s="26">
         <v>102400</v>
       </c>
-      <c r="C23" s="27">
-        <v>1</v>
-      </c>
-      <c r="D23" s="27" t="s">
+      <c r="C23" s="26">
+        <v>1</v>
+      </c>
+      <c r="D23" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="E23" s="28" t="s">
+      <c r="E23" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="F23" s="27">
-        <v>1</v>
-      </c>
-      <c r="G23" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="H23" s="26">
+      <c r="F23" s="26">
+        <v>1</v>
+      </c>
+      <c r="G23" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="25">
         <v>2024001</v>
       </c>
-      <c r="I23" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="J23" s="26"/>
-      <c r="K23" s="26"/>
-      <c r="L23" s="29" t="s">
+      <c r="I23" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J23" s="25"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="M23" s="26" t="s">
+      <c r="M23" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="N23" s="19">
+      <c r="N23" s="18">
         <v>4</v>
       </c>
-      <c r="O23" s="19">
+      <c r="O23" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A24" s="26" t="str">
+      <c r="A24" s="25" t="str">
         <f t="shared" si="1"/>
         <v>1024002</v>
       </c>
-      <c r="B24" s="27">
+      <c r="B24" s="26">
         <v>102400</v>
       </c>
-      <c r="C24" s="27">
+      <c r="C24" s="26">
         <v>2</v>
       </c>
-      <c r="D24" s="27"/>
-      <c r="E24" s="30" t="s">
+      <c r="D24" s="26"/>
+      <c r="E24" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="27">
-        <v>1</v>
-      </c>
-      <c r="G24" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="H24" s="26">
+      <c r="F24" s="26">
+        <v>1</v>
+      </c>
+      <c r="G24" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" s="25">
         <v>2024001</v>
       </c>
-      <c r="I24" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="J24" s="26"/>
-      <c r="K24" s="26"/>
-      <c r="L24" s="31" t="s">
+      <c r="I24" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="M24" s="26" t="s">
+      <c r="M24" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="N24" s="19">
+      <c r="N24" s="18">
         <v>4</v>
       </c>
-      <c r="O24" s="19">
+      <c r="O24" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A25" s="26" t="str">
+      <c r="A25" s="25" t="str">
         <f t="shared" si="1"/>
         <v>1024003</v>
       </c>
-      <c r="B25" s="27">
+      <c r="B25" s="26">
         <v>102400</v>
       </c>
-      <c r="C25" s="27">
-        <v>3</v>
-      </c>
-      <c r="D25" s="27"/>
-      <c r="E25" s="32" t="s">
+      <c r="C25" s="26">
+        <v>3</v>
+      </c>
+      <c r="D25" s="26"/>
+      <c r="E25" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="F25" s="27">
-        <v>1</v>
-      </c>
-      <c r="G25" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="H25" s="26">
+      <c r="F25" s="26">
+        <v>1</v>
+      </c>
+      <c r="G25" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="25">
         <v>2024001</v>
       </c>
-      <c r="I25" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="J25" s="26"/>
-      <c r="K25" s="26"/>
-      <c r="L25" s="29" t="s">
+      <c r="I25" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J25" s="25"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="M25" s="26" t="s">
+      <c r="M25" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="N25" s="19">
+      <c r="N25" s="18">
         <v>4</v>
       </c>
-      <c r="O25" s="19">
+      <c r="O25" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A26" s="26" t="str">
+      <c r="A26" s="25" t="str">
         <f t="shared" si="1"/>
         <v>1024004</v>
       </c>
-      <c r="B26" s="27">
+      <c r="B26" s="26">
         <v>102400</v>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="26">
         <v>4</v>
       </c>
-      <c r="D26" s="27"/>
-      <c r="E26" s="33" t="s">
+      <c r="D26" s="26"/>
+      <c r="E26" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="F26" s="34">
-        <v>1</v>
-      </c>
-      <c r="G26" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="H26" s="26">
+      <c r="F26" s="33">
+        <v>1</v>
+      </c>
+      <c r="G26" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="25">
         <v>2024001</v>
       </c>
-      <c r="I26" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="J26" s="26"/>
-      <c r="K26" s="26"/>
-      <c r="L26" s="29">
+      <c r="I26" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J26" s="25"/>
+      <c r="K26" s="25"/>
+      <c r="L26" s="28">
         <v>10240041</v>
       </c>
-      <c r="M26" s="26" t="s">
+      <c r="M26" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="N26" s="19">
+      <c r="N26" s="18">
         <v>4</v>
       </c>
-      <c r="O26" s="19">
+      <c r="O26" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A27" s="26" t="str">
+      <c r="A27" s="25" t="str">
         <f t="shared" si="1"/>
         <v>1024005</v>
       </c>
-      <c r="B27" s="27">
+      <c r="B27" s="26">
         <v>102400</v>
       </c>
-      <c r="C27" s="27">
-        <v>5</v>
-      </c>
-      <c r="D27" s="27"/>
-      <c r="E27" s="35" t="s">
+      <c r="C27" s="26">
+        <v>5</v>
+      </c>
+      <c r="D27" s="26"/>
+      <c r="E27" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="F27" s="34">
-        <v>1</v>
-      </c>
-      <c r="G27" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="H27" s="26">
+      <c r="F27" s="33">
+        <v>1</v>
+      </c>
+      <c r="G27" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H27" s="25">
         <v>2024001</v>
       </c>
-      <c r="I27" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="J27" s="26"/>
-      <c r="K27" s="26"/>
-      <c r="L27" s="29" t="s">
+      <c r="I27" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J27" s="25"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="M27" s="26" t="s">
+      <c r="M27" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="N27" s="19">
+      <c r="N27" s="18">
         <v>4</v>
       </c>
-      <c r="O27" s="19">
+      <c r="O27" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A28" s="26" t="str">
+      <c r="A28" s="25" t="str">
         <f t="shared" si="1"/>
         <v>1024006</v>
       </c>
-      <c r="B28" s="27">
+      <c r="B28" s="26">
         <v>102400</v>
       </c>
-      <c r="C28" s="27">
+      <c r="C28" s="26">
         <v>6</v>
       </c>
-      <c r="D28" s="27"/>
-      <c r="E28" s="35" t="s">
+      <c r="D28" s="26"/>
+      <c r="E28" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="F28" s="34">
-        <v>1</v>
-      </c>
-      <c r="G28" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="H28" s="26">
+      <c r="F28" s="33">
+        <v>1</v>
+      </c>
+      <c r="G28" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28" s="25">
         <v>2024001</v>
       </c>
-      <c r="I28" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="J28" s="26"/>
-      <c r="K28" s="26"/>
-      <c r="L28" s="29">
+      <c r="I28" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J28" s="25"/>
+      <c r="K28" s="25"/>
+      <c r="L28" s="28">
         <v>10240061</v>
       </c>
-      <c r="M28" s="26" t="s">
+      <c r="M28" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="N28" s="19">
+      <c r="N28" s="18">
         <v>4</v>
       </c>
-      <c r="O28" s="19">
+      <c r="O28" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A29" s="26" t="str">
+      <c r="A29" s="25" t="str">
         <f t="shared" si="1"/>
         <v>1024007</v>
       </c>
-      <c r="B29" s="27">
+      <c r="B29" s="26">
         <v>102400</v>
       </c>
-      <c r="C29" s="27">
+      <c r="C29" s="26">
         <v>7</v>
       </c>
-      <c r="D29" s="27"/>
-      <c r="E29" s="30" t="s">
+      <c r="D29" s="26"/>
+      <c r="E29" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="F29" s="27">
-        <v>1</v>
-      </c>
-      <c r="G29" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="H29" s="26">
+      <c r="F29" s="26">
+        <v>1</v>
+      </c>
+      <c r="G29" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H29" s="25">
         <v>2024001</v>
       </c>
-      <c r="I29" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="J29" s="26"/>
-      <c r="K29" s="26"/>
-      <c r="L29" s="31" t="s">
+      <c r="I29" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J29" s="25"/>
+      <c r="K29" s="25"/>
+      <c r="L29" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="M29" s="26" t="s">
+      <c r="M29" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="N29" s="19">
+      <c r="N29" s="18">
         <v>4</v>
       </c>
-      <c r="O29" s="19">
+      <c r="O29" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="30" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A30" s="26" t="str">
+      <c r="A30" s="25" t="str">
         <f t="shared" si="1"/>
         <v>1017001</v>
       </c>
@@ -3341,16 +3360,16 @@
       <c r="M30" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="N30" s="47">
+      <c r="N30" s="46">
         <v>4</v>
       </c>
-      <c r="O30" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q30" s="20"/>
+      <c r="O30" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q30" s="19"/>
     </row>
     <row r="31" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A31" s="26" t="str">
+      <c r="A31" s="25" t="str">
         <f t="shared" ref="A31:A53" si="2">B31&amp;C31</f>
         <v>1017002</v>
       </c>
@@ -3384,16 +3403,16 @@
       <c r="M31" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="N31" s="47">
+      <c r="N31" s="46">
         <v>4</v>
       </c>
-      <c r="O31" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q31" s="20"/>
+      <c r="O31" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q31" s="19"/>
     </row>
     <row r="32" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A32" s="26" t="str">
+      <c r="A32" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1017003</v>
       </c>
@@ -3427,16 +3446,16 @@
       <c r="M32" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N32" s="47">
+      <c r="N32" s="46">
         <v>4</v>
       </c>
-      <c r="O32" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q32" s="20"/>
+      <c r="O32" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="19"/>
     </row>
     <row r="33" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A33" s="26" t="str">
+      <c r="A33" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1022001</v>
       </c>
@@ -3464,22 +3483,22 @@
       <c r="I33" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L33" s="48" t="s">
+      <c r="L33" s="47" t="s">
         <v>85</v>
       </c>
       <c r="M33" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N33" s="47">
-        <v>3</v>
-      </c>
-      <c r="O33" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q33" s="20"/>
+      <c r="N33" s="46">
+        <v>3</v>
+      </c>
+      <c r="O33" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q33" s="19"/>
     </row>
     <row r="34" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A34" s="26" t="str">
+      <c r="A34" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1022002</v>
       </c>
@@ -3495,10 +3514,10 @@
       <c r="E34" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="F34" s="19">
-        <v>1</v>
-      </c>
-      <c r="G34" s="49" t="s">
+      <c r="F34" s="18">
+        <v>1</v>
+      </c>
+      <c r="G34" s="48" t="s">
         <v>23</v>
       </c>
       <c r="H34" s="5">
@@ -3507,22 +3526,22 @@
       <c r="I34" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L34" s="48">
+      <c r="L34" s="47">
         <v>10220033</v>
       </c>
       <c r="M34" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N34" s="47">
-        <v>3</v>
-      </c>
-      <c r="O34" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q34" s="20"/>
+      <c r="N34" s="46">
+        <v>3</v>
+      </c>
+      <c r="O34" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q34" s="19"/>
     </row>
     <row r="35" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A35" s="26" t="str">
+      <c r="A35" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1022003</v>
       </c>
@@ -3538,10 +3557,10 @@
       <c r="E35" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F35" s="49">
-        <v>1</v>
-      </c>
-      <c r="G35" s="49" t="s">
+      <c r="F35" s="48">
+        <v>1</v>
+      </c>
+      <c r="G35" s="48" t="s">
         <v>23</v>
       </c>
       <c r="H35" s="5">
@@ -3550,22 +3569,22 @@
       <c r="I35" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L35" s="50" t="s">
+      <c r="L35" s="49" t="s">
         <v>89</v>
       </c>
       <c r="M35" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N35" s="47">
-        <v>3</v>
-      </c>
-      <c r="O35" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q35" s="20"/>
+      <c r="N35" s="46">
+        <v>3</v>
+      </c>
+      <c r="O35" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q35" s="19"/>
     </row>
     <row r="36" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A36" s="26" t="str">
+      <c r="A36" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1022004</v>
       </c>
@@ -3581,10 +3600,10 @@
       <c r="E36" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F36" s="19">
-        <v>1</v>
-      </c>
-      <c r="G36" s="49" t="s">
+      <c r="F36" s="18">
+        <v>1</v>
+      </c>
+      <c r="G36" s="48" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="5">
@@ -3593,19 +3612,19 @@
       <c r="I36" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L36" s="48">
+      <c r="L36" s="47">
         <v>10220020</v>
       </c>
-      <c r="N36" s="47">
-        <v>3</v>
-      </c>
-      <c r="O36" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q36" s="20"/>
+      <c r="N36" s="46">
+        <v>3</v>
+      </c>
+      <c r="O36" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q36" s="19"/>
     </row>
     <row r="37" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A37" s="26" t="str">
+      <c r="A37" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1022005</v>
       </c>
@@ -3633,20 +3652,20 @@
       <c r="I37" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L37" s="48">
+      <c r="L37" s="47">
         <v>10220019</v>
       </c>
-      <c r="N37" s="47">
-        <v>3</v>
-      </c>
-      <c r="O37" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q37" s="20"/>
-      <c r="S37" s="51"/>
+      <c r="N37" s="46">
+        <v>3</v>
+      </c>
+      <c r="O37" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q37" s="19"/>
+      <c r="S37" s="50"/>
     </row>
     <row r="38" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A38" s="26" t="str">
+      <c r="A38" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1021001</v>
       </c>
@@ -3674,23 +3693,23 @@
       <c r="I38" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L38" s="48" t="s">
+      <c r="L38" s="47" t="s">
         <v>93</v>
       </c>
       <c r="M38" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N38" s="47">
-        <v>3</v>
-      </c>
-      <c r="O38" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q38" s="20"/>
-      <c r="S38" s="51"/>
+      <c r="N38" s="46">
+        <v>3</v>
+      </c>
+      <c r="O38" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q38" s="19"/>
+      <c r="S38" s="50"/>
     </row>
     <row r="39" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A39" s="26" t="str">
+      <c r="A39" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1021002</v>
       </c>
@@ -3718,23 +3737,23 @@
       <c r="I39" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L39" s="48">
+      <c r="L39" s="47">
         <v>10210031</v>
       </c>
       <c r="M39" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N39" s="47">
-        <v>3</v>
-      </c>
-      <c r="O39" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q39" s="20"/>
-      <c r="S39" s="51"/>
+      <c r="N39" s="46">
+        <v>3</v>
+      </c>
+      <c r="O39" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q39" s="19"/>
+      <c r="S39" s="50"/>
     </row>
     <row r="40" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A40" s="26" t="str">
+      <c r="A40" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1021003</v>
       </c>
@@ -3762,23 +3781,23 @@
       <c r="I40" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L40" s="48">
+      <c r="L40" s="47">
         <v>10210041</v>
       </c>
       <c r="M40" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="N40" s="47">
-        <v>3</v>
-      </c>
-      <c r="O40" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q40" s="20"/>
-      <c r="S40" s="51"/>
+      <c r="N40" s="46">
+        <v>3</v>
+      </c>
+      <c r="O40" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q40" s="19"/>
+      <c r="S40" s="50"/>
     </row>
     <row r="41" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A41" s="26" t="str">
+      <c r="A41" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1021004</v>
       </c>
@@ -3806,23 +3825,23 @@
       <c r="I41" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L41" s="48" t="s">
+      <c r="L41" s="47" t="s">
         <v>96</v>
       </c>
       <c r="M41" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N41" s="47">
-        <v>3</v>
-      </c>
-      <c r="O41" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q41" s="20"/>
-      <c r="S41" s="51"/>
+      <c r="N41" s="46">
+        <v>3</v>
+      </c>
+      <c r="O41" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q41" s="19"/>
+      <c r="S41" s="50"/>
     </row>
     <row r="42" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A42" s="26" t="str">
+      <c r="A42" s="25" t="str">
         <f t="shared" si="2"/>
         <v>1018001</v>
       </c>
@@ -3850,20 +3869,20 @@
       <c r="I42" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L42" s="48" t="s">
+      <c r="L42" s="47" t="s">
         <v>98</v>
       </c>
       <c r="M42" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N42" s="47">
+      <c r="N42" s="46">
         <v>4</v>
       </c>
-      <c r="O42" s="47">
+      <c r="O42" s="46">
         <v>6</v>
       </c>
-      <c r="Q42" s="20"/>
-      <c r="S42" s="51"/>
+      <c r="Q42" s="19"/>
+      <c r="S42" s="50"/>
     </row>
     <row r="43" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A43" s="5" t="str">
@@ -3894,16 +3913,16 @@
       <c r="I43" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L43" s="48">
+      <c r="L43" s="47">
         <v>10180031</v>
       </c>
       <c r="M43" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N43" s="47">
+      <c r="N43" s="46">
         <v>4</v>
       </c>
-      <c r="O43" s="47">
+      <c r="O43" s="46">
         <v>6</v>
       </c>
     </row>
@@ -3936,16 +3955,16 @@
       <c r="I44" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L44" s="48" t="s">
+      <c r="L44" s="47" t="s">
         <v>99</v>
       </c>
       <c r="M44" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N44" s="47">
+      <c r="N44" s="46">
         <v>4</v>
       </c>
-      <c r="O44" s="47">
+      <c r="O44" s="46">
         <v>6</v>
       </c>
     </row>
@@ -3978,19 +3997,19 @@
       <c r="I45" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L45" s="48" t="s">
+      <c r="L45" s="47" t="s">
         <v>101</v>
       </c>
       <c r="M45" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N45" s="47">
-        <v>3</v>
-      </c>
-      <c r="O45" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q45" s="10"/>
+      <c r="N45" s="46">
+        <v>3</v>
+      </c>
+      <c r="O45" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q45" s="9"/>
     </row>
     <row r="46" customFormat="1" ht="16.5" spans="1:19">
       <c r="A46" s="5" t="str">
@@ -4021,19 +4040,19 @@
       <c r="I46" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L46" s="48">
+      <c r="L46" s="47">
         <v>10250031</v>
       </c>
       <c r="M46" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="N46" s="47">
-        <v>3</v>
-      </c>
-      <c r="O46" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q46" s="10"/>
+      <c r="N46" s="46">
+        <v>3</v>
+      </c>
+      <c r="O46" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q46" s="9"/>
     </row>
     <row r="47" customFormat="1" ht="16.5" spans="1:19">
       <c r="A47" s="5" t="str">
@@ -4064,19 +4083,19 @@
       <c r="I47" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L47" s="48" t="s">
+      <c r="L47" s="47" t="s">
         <v>103</v>
       </c>
       <c r="M47" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N47" s="47">
-        <v>3</v>
-      </c>
-      <c r="O47" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q47" s="10"/>
+      <c r="N47" s="46">
+        <v>3</v>
+      </c>
+      <c r="O47" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q47" s="9"/>
     </row>
     <row r="48" customFormat="1" ht="16.5" spans="1:19">
       <c r="A48" s="5" t="str">
@@ -4107,19 +4126,19 @@
       <c r="I48" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L48" s="48" t="s">
+      <c r="L48" s="47" t="s">
         <v>105</v>
       </c>
       <c r="M48" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N48" s="47">
+      <c r="N48" s="46">
         <v>4</v>
       </c>
-      <c r="O48" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q48" s="10"/>
+      <c r="O48" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q48" s="9"/>
     </row>
     <row r="49" customFormat="1" ht="16.5" spans="1:17">
       <c r="A49" s="5" t="str">
@@ -4150,19 +4169,19 @@
       <c r="I49" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L49" s="48">
+      <c r="L49" s="47">
         <v>10230003</v>
       </c>
       <c r="M49" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="N49" s="47">
+      <c r="N49" s="46">
         <v>4</v>
       </c>
-      <c r="O49" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q49" s="10"/>
+      <c r="O49" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q49" s="9"/>
     </row>
     <row r="50" customFormat="1" ht="16.5" spans="1:17">
       <c r="A50" s="5" t="str">
@@ -4193,19 +4212,19 @@
       <c r="I50" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L50" s="48" t="s">
+      <c r="L50" s="47" t="s">
         <v>106</v>
       </c>
       <c r="M50" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N50" s="47">
+      <c r="N50" s="46">
         <v>4</v>
       </c>
-      <c r="O50" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q50" s="10"/>
+      <c r="O50" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q50" s="9"/>
     </row>
     <row r="51" customFormat="1" ht="16.5" spans="1:17">
       <c r="A51" s="5" t="str">
@@ -4236,19 +4255,19 @@
       <c r="I51" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L51" s="48">
+      <c r="L51" s="47">
         <v>10340007</v>
       </c>
       <c r="M51" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="N51" s="47">
-        <v>3</v>
-      </c>
-      <c r="O51" s="47">
-        <v>3</v>
-      </c>
-      <c r="Q51" s="10"/>
+      <c r="N51" s="46">
+        <v>3</v>
+      </c>
+      <c r="O51" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q51" s="9"/>
     </row>
     <row r="52" customFormat="1" ht="16.5" spans="1:17">
       <c r="A52" s="5" t="str">
@@ -4279,16 +4298,16 @@
       <c r="I52" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L52" s="48"/>
+      <c r="L52" s="47"/>
       <c r="M52" s="5"/>
-      <c r="N52" s="47">
-        <v>3</v>
-      </c>
-      <c r="O52" s="47">
-        <v>3</v>
-      </c>
-      <c r="P52" s="52"/>
-      <c r="Q52" s="10"/>
+      <c r="N52" s="46">
+        <v>3</v>
+      </c>
+      <c r="O52" s="46">
+        <v>3</v>
+      </c>
+      <c r="P52" s="51"/>
+      <c r="Q52" s="9"/>
     </row>
     <row r="53" customFormat="1" ht="16.5" spans="1:17">
       <c r="A53" s="5" t="str">
@@ -4319,15 +4338,15 @@
       <c r="I53" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L53" s="48"/>
+      <c r="L53" s="47"/>
       <c r="M53" s="5"/>
-      <c r="N53" s="47">
-        <v>3</v>
-      </c>
-      <c r="O53" s="47">
-        <v>3</v>
-      </c>
-      <c r="Q53" s="10"/>
+      <c r="N53" s="46">
+        <v>3</v>
+      </c>
+      <c r="O53" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q53" s="9"/>
     </row>
     <row r="54" customFormat="1" ht="16.5" spans="1:17">
       <c r="A54" s="5" t="str">
@@ -4358,19 +4377,19 @@
       <c r="I54" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L54" s="48" t="s">
+      <c r="L54" s="47" t="s">
         <v>112</v>
       </c>
       <c r="M54" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="N54" s="47">
+      <c r="N54" s="46">
         <v>4</v>
       </c>
-      <c r="O54" s="47">
-        <v>3</v>
-      </c>
-      <c r="Q54" s="10"/>
+      <c r="O54" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="9"/>
     </row>
     <row r="55" customFormat="1" ht="16.5" spans="1:17">
       <c r="A55" s="5" t="str">
@@ -4401,19 +4420,19 @@
       <c r="I55" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L55" s="48" t="s">
+      <c r="L55" s="47" t="s">
         <v>115</v>
       </c>
       <c r="M55" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="N55" s="47">
+      <c r="N55" s="46">
         <v>4</v>
       </c>
-      <c r="O55" s="47">
-        <v>3</v>
-      </c>
-      <c r="Q55" s="10"/>
+      <c r="O55" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q55" s="9"/>
     </row>
     <row r="56" customFormat="1" ht="16.5" spans="1:17">
       <c r="A56" s="5" t="str">
@@ -4444,19 +4463,19 @@
       <c r="I56" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L56" s="48" t="s">
+      <c r="L56" s="47" t="s">
         <v>117</v>
       </c>
       <c r="M56" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="N56" s="47">
+      <c r="N56" s="46">
         <v>4</v>
       </c>
-      <c r="O56" s="47">
-        <v>3</v>
-      </c>
-      <c r="Q56" s="10"/>
+      <c r="O56" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q56" s="9"/>
     </row>
     <row r="57" customFormat="1" ht="16.5" spans="1:17">
       <c r="A57" s="5" t="str">
@@ -4487,19 +4506,19 @@
       <c r="I57" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L57" s="48" t="s">
+      <c r="L57" s="47" t="s">
         <v>120</v>
       </c>
       <c r="M57" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="N57" s="47">
+      <c r="N57" s="46">
         <v>4</v>
       </c>
-      <c r="O57" s="47">
-        <v>3</v>
-      </c>
-      <c r="Q57" s="10"/>
+      <c r="O57" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="9"/>
     </row>
     <row r="58" customFormat="1" ht="16.5" spans="1:17">
       <c r="A58" s="5" t="str">
@@ -4530,19 +4549,19 @@
       <c r="I58" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L58" s="48" t="s">
+      <c r="L58" s="47" t="s">
         <v>121</v>
       </c>
       <c r="M58" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="N58" s="47">
+      <c r="N58" s="46">
         <v>4</v>
       </c>
-      <c r="O58" s="47">
-        <v>3</v>
-      </c>
-      <c r="Q58" s="10"/>
+      <c r="O58" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="9"/>
     </row>
     <row r="59" customFormat="1" ht="16.5" spans="1:17">
       <c r="A59" s="5" t="str">
@@ -4573,19 +4592,19 @@
       <c r="I59" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L59" s="48" t="s">
+      <c r="L59" s="47" t="s">
         <v>122</v>
       </c>
       <c r="M59" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="N59" s="47">
+      <c r="N59" s="46">
         <v>4</v>
       </c>
-      <c r="O59" s="47">
-        <v>3</v>
-      </c>
-      <c r="Q59" s="10"/>
+      <c r="O59" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="9"/>
     </row>
     <row r="60" customFormat="1" ht="16.5" spans="1:17">
       <c r="A60" s="5" t="str">
@@ -4616,19 +4635,19 @@
       <c r="I60" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L60" s="48" t="s">
+      <c r="L60" s="47" t="s">
         <v>124</v>
       </c>
       <c r="M60" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="N60" s="47">
-        <v>3</v>
-      </c>
-      <c r="O60" s="47">
-        <v>3</v>
-      </c>
-      <c r="Q60" s="10"/>
+      <c r="N60" s="46">
+        <v>3</v>
+      </c>
+      <c r="O60" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="9"/>
     </row>
     <row r="61" customFormat="1" ht="16.5" spans="1:17">
       <c r="A61" s="5" t="str">
@@ -4659,19 +4678,19 @@
       <c r="I61" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L61" s="48">
+      <c r="L61" s="47">
         <v>10360004</v>
       </c>
       <c r="M61" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="N61" s="47">
-        <v>3</v>
-      </c>
-      <c r="O61" s="47">
-        <v>3</v>
-      </c>
-      <c r="Q61" s="10"/>
+      <c r="N61" s="46">
+        <v>3</v>
+      </c>
+      <c r="O61" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q61" s="9"/>
     </row>
     <row r="62" customFormat="1" ht="16.5" spans="1:17">
       <c r="A62" s="5" t="str">
@@ -4702,19 +4721,19 @@
       <c r="I62" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L62" s="48">
+      <c r="L62" s="47">
         <v>10360002</v>
       </c>
       <c r="M62" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="N62" s="47">
-        <v>3</v>
-      </c>
-      <c r="O62" s="47">
-        <v>3</v>
-      </c>
-      <c r="Q62" s="10"/>
+      <c r="N62" s="46">
+        <v>3</v>
+      </c>
+      <c r="O62" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="9"/>
     </row>
     <row r="63" customFormat="1" ht="16.5" spans="1:17">
       <c r="A63" s="5" t="str">
@@ -4745,19 +4764,19 @@
       <c r="I63" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L63" s="48" t="s">
+      <c r="L63" s="47" t="s">
         <v>129</v>
       </c>
       <c r="M63" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="N63" s="47">
-        <v>5</v>
-      </c>
-      <c r="O63" s="47">
+      <c r="N63" s="46">
+        <v>5</v>
+      </c>
+      <c r="O63" s="46">
         <v>6</v>
       </c>
-      <c r="Q63" s="10"/>
+      <c r="Q63" s="9"/>
     </row>
     <row r="64" customFormat="1" ht="16.5" spans="1:17">
       <c r="A64" s="5" t="str">
@@ -4788,19 +4807,19 @@
       <c r="I64" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L64" s="48">
+      <c r="L64" s="47">
         <v>10280002</v>
       </c>
       <c r="M64" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="N64" s="47">
-        <v>5</v>
-      </c>
-      <c r="O64" s="47">
+      <c r="N64" s="46">
+        <v>5</v>
+      </c>
+      <c r="O64" s="46">
         <v>6</v>
       </c>
-      <c r="Q64" s="10"/>
+      <c r="Q64" s="9"/>
     </row>
     <row r="65" customFormat="1" ht="16.5" spans="1:17">
       <c r="A65" s="5" t="str">
@@ -4831,19 +4850,19 @@
       <c r="I65" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L65" s="48" t="s">
+      <c r="L65" s="47" t="s">
         <v>132</v>
       </c>
       <c r="M65" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N65" s="47">
-        <v>5</v>
-      </c>
-      <c r="O65" s="47">
+      <c r="N65" s="46">
+        <v>5</v>
+      </c>
+      <c r="O65" s="46">
         <v>6</v>
       </c>
-      <c r="Q65" s="10"/>
+      <c r="Q65" s="9"/>
     </row>
     <row r="66" customFormat="1" ht="16.5" spans="1:17">
       <c r="A66" s="5" t="str">
@@ -4874,19 +4893,19 @@
       <c r="I66" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L66" s="48">
+      <c r="L66" s="47">
         <v>10340007</v>
       </c>
       <c r="M66" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="N66" s="47">
-        <v>3</v>
-      </c>
-      <c r="O66" s="47">
-        <v>3</v>
-      </c>
-      <c r="Q66" s="10"/>
+      <c r="N66" s="46">
+        <v>3</v>
+      </c>
+      <c r="O66" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="9"/>
     </row>
     <row r="67" customFormat="1" ht="16.5" spans="1:17">
       <c r="A67" s="5" t="str">
@@ -4917,16 +4936,16 @@
       <c r="I67" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L67" s="48"/>
+      <c r="L67" s="47"/>
       <c r="M67" s="5"/>
-      <c r="N67" s="47">
-        <v>3</v>
-      </c>
-      <c r="O67" s="47">
-        <v>3</v>
-      </c>
-      <c r="P67" s="52"/>
-      <c r="Q67" s="10"/>
+      <c r="N67" s="46">
+        <v>3</v>
+      </c>
+      <c r="O67" s="46">
+        <v>3</v>
+      </c>
+      <c r="P67" s="51"/>
+      <c r="Q67" s="9"/>
     </row>
     <row r="68" s="6" customFormat="1" ht="16.5" spans="1:17">
       <c r="A68" s="5" t="str">
@@ -4959,58 +4978,58 @@
       </c>
       <c r="J68"/>
       <c r="K68"/>
-      <c r="L68" s="48"/>
+      <c r="L68" s="47"/>
       <c r="M68" s="5"/>
-      <c r="N68" s="47">
+      <c r="N68" s="46">
         <v>4</v>
       </c>
-      <c r="O68" s="47">
+      <c r="O68" s="46">
         <v>4</v>
       </c>
-      <c r="Q68" s="53"/>
+      <c r="Q68" s="52"/>
     </row>
     <row r="69" s="6" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A69" s="54" t="str">
+      <c r="A69" s="53" t="str">
         <f t="shared" si="3"/>
         <v>1020001</v>
       </c>
-      <c r="B69" s="54">
+      <c r="B69" s="53">
         <v>102000</v>
       </c>
-      <c r="C69" s="54">
-        <v>1</v>
-      </c>
-      <c r="D69" s="54" t="s">
+      <c r="C69" s="53">
+        <v>1</v>
+      </c>
+      <c r="D69" s="53" t="s">
         <v>135</v>
       </c>
-      <c r="E69" s="54" t="s">
+      <c r="E69" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="F69" s="54">
-        <v>1</v>
-      </c>
-      <c r="G69" s="54" t="s">
-        <v>23</v>
-      </c>
-      <c r="H69" s="54">
+      <c r="F69" s="53">
+        <v>1</v>
+      </c>
+      <c r="G69" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="H69" s="53">
         <v>2020001</v>
       </c>
-      <c r="I69" s="54" t="s">
-        <v>24</v>
-      </c>
-      <c r="L69" s="55" t="s">
+      <c r="I69" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="L69" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="M69" s="54" t="s">
+      <c r="M69" s="53" t="s">
         <v>137</v>
       </c>
-      <c r="N69" s="56">
-        <v>5</v>
-      </c>
-      <c r="O69" s="56">
-        <v>5</v>
-      </c>
-      <c r="Q69" s="53"/>
+      <c r="N69" s="55">
+        <v>5</v>
+      </c>
+      <c r="O69" s="55">
+        <v>5</v>
+      </c>
+      <c r="Q69" s="52"/>
     </row>
     <row r="70" customFormat="1" ht="16.5" spans="1:17">
       <c r="A70" s="5" t="str">
@@ -5041,19 +5060,19 @@
       <c r="I70" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L70" s="48" t="s">
+      <c r="L70" s="47" t="s">
         <v>138</v>
       </c>
       <c r="M70" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="N70" s="47">
-        <v>5</v>
-      </c>
-      <c r="O70" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q70" s="10"/>
+      <c r="N70" s="46">
+        <v>5</v>
+      </c>
+      <c r="O70" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q70" s="9"/>
     </row>
     <row r="71" customFormat="1" ht="16.5" spans="1:17">
       <c r="A71" s="5" t="str">
@@ -5084,62 +5103,62 @@
       <c r="I71" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L71" s="48" t="s">
+      <c r="L71" s="47" t="s">
         <v>140</v>
       </c>
       <c r="M71" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="N71" s="47">
-        <v>5</v>
-      </c>
-      <c r="O71" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q71" s="10"/>
+      <c r="N71" s="46">
+        <v>5</v>
+      </c>
+      <c r="O71" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q71" s="9"/>
     </row>
     <row r="72" s="7" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A72" s="57" t="str">
+      <c r="A72" s="56" t="str">
         <f t="shared" si="3"/>
         <v>1020004</v>
       </c>
-      <c r="B72" s="57">
+      <c r="B72" s="56">
         <v>102000</v>
       </c>
-      <c r="C72" s="57">
+      <c r="C72" s="56">
         <v>4</v>
       </c>
-      <c r="D72" s="57" t="s">
+      <c r="D72" s="56" t="s">
         <v>135</v>
       </c>
-      <c r="E72" s="57" t="s">
+      <c r="E72" s="56" t="s">
         <v>142</v>
       </c>
-      <c r="F72" s="57">
-        <v>1</v>
-      </c>
-      <c r="G72" s="57" t="s">
-        <v>23</v>
-      </c>
-      <c r="H72" s="57">
+      <c r="F72" s="56">
+        <v>1</v>
+      </c>
+      <c r="G72" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="H72" s="56">
         <v>2020002</v>
       </c>
-      <c r="I72" s="57" t="s">
-        <v>24</v>
-      </c>
-      <c r="L72" s="58">
+      <c r="I72" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="L72" s="57">
         <v>10200016</v>
       </c>
-      <c r="M72" s="57" t="s">
+      <c r="M72" s="56" t="s">
         <v>143</v>
       </c>
-      <c r="N72" s="59">
-        <v>5</v>
-      </c>
-      <c r="O72" s="59">
-        <v>5</v>
-      </c>
-      <c r="Q72" s="60"/>
+      <c r="N72" s="58">
+        <v>5</v>
+      </c>
+      <c r="O72" s="58">
+        <v>5</v>
+      </c>
+      <c r="Q72" s="59"/>
     </row>
     <row r="73" customFormat="1" ht="16.5" spans="1:17">
       <c r="A73" s="5" t="str">
@@ -5170,19 +5189,19 @@
       <c r="I73" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L73" s="48">
+      <c r="L73" s="47">
         <v>10200021</v>
       </c>
       <c r="M73" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="N73" s="47">
-        <v>5</v>
-      </c>
-      <c r="O73" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q73" s="10"/>
+      <c r="N73" s="46">
+        <v>5</v>
+      </c>
+      <c r="O73" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q73" s="9"/>
     </row>
     <row r="74" customFormat="1" ht="16.5" spans="1:17">
       <c r="A74" s="5" t="str">
@@ -5216,17 +5235,17 @@
       <c r="J74" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="L74" s="48"/>
+      <c r="L74" s="47"/>
       <c r="M74" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="N74" s="47">
-        <v>3</v>
-      </c>
-      <c r="O74" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q74" s="10"/>
+      <c r="N74" s="46">
+        <v>3</v>
+      </c>
+      <c r="O74" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q74" s="9"/>
     </row>
     <row r="75" customFormat="1" ht="16.5" spans="1:17">
       <c r="A75" s="5" t="str">
@@ -5257,19 +5276,19 @@
       <c r="I75" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L75" s="48">
+      <c r="L75" s="47">
         <v>10380002</v>
       </c>
       <c r="M75" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="N75" s="47">
-        <v>3</v>
-      </c>
-      <c r="O75" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q75" s="10"/>
+      <c r="N75" s="46">
+        <v>3</v>
+      </c>
+      <c r="O75" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q75" s="9"/>
     </row>
     <row r="76" customFormat="1" ht="16.5" spans="1:17">
       <c r="A76" s="5" t="str">
@@ -5300,19 +5319,19 @@
       <c r="I76" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L76" s="48" t="s">
+      <c r="L76" s="47" t="s">
         <v>151</v>
       </c>
       <c r="M76" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="N76" s="47">
-        <v>3</v>
-      </c>
-      <c r="O76" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q76" s="10"/>
+      <c r="N76" s="46">
+        <v>3</v>
+      </c>
+      <c r="O76" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q76" s="9"/>
     </row>
     <row r="77" customFormat="1" ht="16.5" spans="1:17">
       <c r="A77" s="5" t="str">
@@ -5343,19 +5362,19 @@
       <c r="I77" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L77" s="48" t="s">
+      <c r="L77" s="47" t="s">
         <v>153</v>
       </c>
       <c r="M77" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="N77" s="47">
-        <v>3</v>
-      </c>
-      <c r="O77" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q77" s="10"/>
+      <c r="N77" s="46">
+        <v>3</v>
+      </c>
+      <c r="O77" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q77" s="9"/>
     </row>
     <row r="78" customFormat="1" ht="16.5" spans="1:17">
       <c r="A78" s="5" t="str">
@@ -5386,19 +5405,19 @@
       <c r="I78" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L78" s="48" t="s">
+      <c r="L78" s="47" t="s">
         <v>156</v>
       </c>
       <c r="M78" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="N78" s="47">
-        <v>3</v>
-      </c>
-      <c r="O78" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q78" s="10"/>
+      <c r="N78" s="46">
+        <v>3</v>
+      </c>
+      <c r="O78" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q78" s="9"/>
     </row>
     <row r="79" customFormat="1" ht="16.5" spans="1:17">
       <c r="A79" s="5" t="str">
@@ -5429,19 +5448,19 @@
       <c r="I79" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L79" s="48">
+      <c r="L79" s="47">
         <v>10270003</v>
       </c>
       <c r="M79" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="N79" s="47">
-        <v>3</v>
-      </c>
-      <c r="O79" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q79" s="10"/>
+      <c r="N79" s="46">
+        <v>3</v>
+      </c>
+      <c r="O79" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q79" s="9"/>
     </row>
     <row r="80" customFormat="1" ht="16.5" spans="1:17">
       <c r="A80" s="5" t="str">
@@ -5472,19 +5491,19 @@
       <c r="I80" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L80" s="48" t="s">
+      <c r="L80" s="47" t="s">
         <v>159</v>
       </c>
       <c r="M80" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="N80" s="47">
-        <v>3</v>
-      </c>
-      <c r="O80" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q80" s="10"/>
+      <c r="N80" s="46">
+        <v>3</v>
+      </c>
+      <c r="O80" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q80" s="9"/>
     </row>
     <row r="81" customFormat="1" ht="16.5" spans="1:17">
       <c r="A81" s="5" t="str">
@@ -5515,19 +5534,19 @@
       <c r="I81" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L81" s="48">
+      <c r="L81" s="47">
         <v>10370001</v>
       </c>
       <c r="M81" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="N81" s="47">
+      <c r="N81" s="46">
         <v>4</v>
       </c>
-      <c r="O81" s="47">
-        <v>3</v>
-      </c>
-      <c r="Q81" s="10"/>
+      <c r="O81" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="9"/>
     </row>
     <row r="82" customFormat="1" ht="16.5" spans="1:17">
       <c r="A82" s="5" t="str">
@@ -5558,19 +5577,19 @@
       <c r="I82" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L82" s="48">
+      <c r="L82" s="47">
         <v>10370003</v>
       </c>
       <c r="M82" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="N82" s="47">
+      <c r="N82" s="46">
         <v>4</v>
       </c>
-      <c r="O82" s="47">
-        <v>3</v>
-      </c>
-      <c r="Q82" s="10"/>
+      <c r="O82" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q82" s="9"/>
     </row>
     <row r="83" customFormat="1" ht="16.5" spans="1:17">
       <c r="A83" s="5" t="str">
@@ -5601,19 +5620,19 @@
       <c r="I83" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L83" s="48"/>
+      <c r="L83" s="47"/>
       <c r="M83" s="5"/>
-      <c r="N83" s="47">
+      <c r="N83" s="46">
         <v>4</v>
       </c>
-      <c r="O83" s="47">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="10"/>
+      <c r="O83" s="46">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="9"/>
     </row>
     <row r="84" customFormat="1" ht="16.5" spans="1:17">
       <c r="A84" s="5" t="str">
-        <f t="shared" ref="A84:A92" si="4">B84&amp;C84</f>
+        <f t="shared" ref="A84:A95" si="4">B84&amp;C84</f>
         <v>1031001</v>
       </c>
       <c r="B84" s="5">
@@ -5640,19 +5659,19 @@
       <c r="I84" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L84" s="48" t="s">
+      <c r="L84" s="47" t="s">
         <v>165</v>
       </c>
       <c r="M84" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="N84" s="47">
-        <v>3</v>
-      </c>
-      <c r="O84" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q84" s="10"/>
+      <c r="N84" s="46">
+        <v>3</v>
+      </c>
+      <c r="O84" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q84" s="9"/>
     </row>
     <row r="85" customFormat="1" ht="16.5" spans="1:17">
       <c r="A85" s="5" t="str">
@@ -5683,19 +5702,19 @@
       <c r="I85" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L85" s="48">
+      <c r="L85" s="47">
         <v>10310008</v>
       </c>
       <c r="M85" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="N85" s="47">
-        <v>3</v>
-      </c>
-      <c r="O85" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q85" s="10"/>
+      <c r="N85" s="46">
+        <v>3</v>
+      </c>
+      <c r="O85" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q85" s="9"/>
     </row>
     <row r="86" customFormat="1" ht="16.5" spans="1:17">
       <c r="A86" s="5" t="str">
@@ -5726,19 +5745,19 @@
       <c r="I86" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L86" s="48" t="s">
+      <c r="L86" s="47" t="s">
         <v>168</v>
       </c>
       <c r="M86" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="N86" s="47">
-        <v>3</v>
-      </c>
-      <c r="O86" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q86" s="10"/>
+      <c r="N86" s="46">
+        <v>3</v>
+      </c>
+      <c r="O86" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q86" s="9"/>
     </row>
     <row r="87" customFormat="1" ht="16.5" spans="1:17">
       <c r="A87" s="5" t="str">
@@ -5769,19 +5788,19 @@
       <c r="I87" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L87" s="48" t="s">
+      <c r="L87" s="47" t="s">
         <v>170</v>
       </c>
       <c r="M87" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="N87" s="47">
-        <v>3</v>
-      </c>
-      <c r="O87" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q87" s="10"/>
+      <c r="N87" s="46">
+        <v>3</v>
+      </c>
+      <c r="O87" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q87" s="9"/>
     </row>
     <row r="88" customFormat="1" ht="16.5" spans="1:17">
       <c r="A88" s="5" t="str">
@@ -5812,19 +5831,19 @@
       <c r="I88" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L88" s="48">
+      <c r="L88" s="47">
         <v>10310003</v>
       </c>
       <c r="M88" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="N88" s="47">
-        <v>3</v>
-      </c>
-      <c r="O88" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q88" s="10"/>
+      <c r="N88" s="46">
+        <v>3</v>
+      </c>
+      <c r="O88" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q88" s="9"/>
     </row>
     <row r="89" customFormat="1" ht="16.5" spans="1:17">
       <c r="A89" s="5" t="str">
@@ -5855,19 +5874,19 @@
       <c r="I89" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L89" s="48" t="s">
+      <c r="L89" s="47" t="s">
         <v>175</v>
       </c>
       <c r="M89" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="N89" s="47">
-        <v>3</v>
-      </c>
-      <c r="O89" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q89" s="10"/>
+      <c r="N89" s="46">
+        <v>3</v>
+      </c>
+      <c r="O89" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q89" s="9"/>
     </row>
     <row r="90" customFormat="1" ht="16.5" spans="1:17">
       <c r="A90" s="5" t="str">
@@ -5898,19 +5917,19 @@
       <c r="I90" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L90" s="48" t="s">
+      <c r="L90" s="47" t="s">
         <v>178</v>
       </c>
       <c r="M90" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="N90" s="47">
-        <v>3</v>
-      </c>
-      <c r="O90" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q90" s="10"/>
+      <c r="N90" s="46">
+        <v>3</v>
+      </c>
+      <c r="O90" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q90" s="9"/>
     </row>
     <row r="91" customFormat="1" ht="16.5" spans="1:17">
       <c r="A91" s="5" t="str">
@@ -5941,19 +5960,19 @@
       <c r="I91" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L91" s="48" t="s">
+      <c r="L91" s="47" t="s">
         <v>180</v>
       </c>
       <c r="M91" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="N91" s="47">
-        <v>3</v>
-      </c>
-      <c r="O91" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q91" s="10"/>
+      <c r="N91" s="46">
+        <v>3</v>
+      </c>
+      <c r="O91" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q91" s="9"/>
     </row>
     <row r="92" customFormat="1" ht="16.5" spans="1:17">
       <c r="A92" s="5" t="str">
@@ -5984,32 +6003,32 @@
       <c r="I92" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L92" s="48" t="s">
+      <c r="L92" s="47" t="s">
         <v>182</v>
       </c>
       <c r="M92" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="N92" s="47">
-        <v>3</v>
-      </c>
-      <c r="O92" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q92" s="10"/>
-    </row>
-    <row r="93" s="8" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N92" s="46">
+        <v>3</v>
+      </c>
+      <c r="O92" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q92" s="9"/>
+    </row>
+    <row r="93" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A93" s="5" t="str">
-        <f>B93&amp;C93</f>
+        <f t="shared" si="4"/>
         <v>1039001</v>
       </c>
-      <c r="B93" s="8">
+      <c r="B93" s="5">
         <v>103900</v>
       </c>
       <c r="C93" s="5">
         <v>1</v>
       </c>
-      <c r="D93" s="8" t="s">
+      <c r="D93" s="5" t="s">
         <v>184</v>
       </c>
       <c r="E93" s="5" t="s">
@@ -6021,38 +6040,38 @@
       <c r="G93" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H93" s="8">
+      <c r="H93" s="5">
         <v>2039001</v>
       </c>
       <c r="I93" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L93" s="8" t="s">
+      <c r="L93" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="M93" s="8" t="s">
+      <c r="M93" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="N93" s="47">
-        <v>3</v>
-      </c>
-      <c r="O93" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q93" s="61"/>
-    </row>
-    <row r="94" s="8" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N93" s="46">
+        <v>3</v>
+      </c>
+      <c r="O93" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q93" s="19"/>
+    </row>
+    <row r="94" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A94" s="5" t="str">
-        <f>B94&amp;C94</f>
+        <f t="shared" si="4"/>
         <v>1039002</v>
       </c>
-      <c r="B94" s="8">
+      <c r="B94" s="5">
         <v>103900</v>
       </c>
       <c r="C94" s="5">
         <v>2</v>
       </c>
-      <c r="D94" s="8" t="s">
+      <c r="D94" s="5" t="s">
         <v>184</v>
       </c>
       <c r="E94" s="5" t="s">
@@ -6064,38 +6083,38 @@
       <c r="G94" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H94" s="8">
+      <c r="H94" s="5">
         <v>2039001</v>
       </c>
       <c r="I94" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L94" s="48">
+      <c r="L94" s="47">
         <v>10390003</v>
       </c>
-      <c r="M94" s="8" t="s">
+      <c r="M94" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="N94" s="47">
-        <v>3</v>
-      </c>
-      <c r="O94" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q94" s="61"/>
-    </row>
-    <row r="95" s="8" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N94" s="46">
+        <v>3</v>
+      </c>
+      <c r="O94" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q94" s="19"/>
+    </row>
+    <row r="95" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A95" s="5" t="str">
-        <f>B95&amp;C95</f>
+        <f t="shared" si="4"/>
         <v>1039003</v>
       </c>
-      <c r="B95" s="8">
+      <c r="B95" s="5">
         <v>103900</v>
       </c>
       <c r="C95" s="5">
         <v>3</v>
       </c>
-      <c r="D95" s="8" t="s">
+      <c r="D95" s="5" t="s">
         <v>184</v>
       </c>
       <c r="E95" s="5" t="s">
@@ -6107,25 +6126,225 @@
       <c r="G95" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H95" s="8">
+      <c r="H95" s="5">
         <v>2039001</v>
       </c>
       <c r="I95" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L95" s="8" t="s">
+      <c r="L95" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="M95" s="8" t="s">
+      <c r="M95" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N95" s="47">
-        <v>3</v>
-      </c>
-      <c r="O95" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q95" s="61"/>
+      <c r="N95" s="46">
+        <v>3</v>
+      </c>
+      <c r="O95" s="46">
+        <v>5</v>
+      </c>
+      <c r="Q95" s="19"/>
+    </row>
+    <row r="96" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A96" s="5" t="str">
+        <f>B96&amp;C96</f>
+        <v>1016001</v>
+      </c>
+      <c r="B96" s="5">
+        <v>101600</v>
+      </c>
+      <c r="C96" s="5">
+        <v>1</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="E96" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F96" s="5">
+        <v>1</v>
+      </c>
+      <c r="G96" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H96" s="5">
+        <v>2016001</v>
+      </c>
+      <c r="I96" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L96" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="M96" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="N96" s="46">
+        <v>6</v>
+      </c>
+      <c r="O96" s="46">
+        <v>6</v>
+      </c>
+      <c r="Q96" s="19"/>
+    </row>
+    <row r="97" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A97" s="5" t="str">
+        <f>B97&amp;C97</f>
+        <v>1016002</v>
+      </c>
+      <c r="B97" s="5">
+        <v>101600</v>
+      </c>
+      <c r="C97" s="5">
+        <v>2</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F97" s="5">
+        <v>1</v>
+      </c>
+      <c r="G97" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H97" s="5">
+        <v>2016001</v>
+      </c>
+      <c r="I97" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L97" s="60">
+        <v>10160002</v>
+      </c>
+      <c r="M97" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="N97" s="46">
+        <v>6</v>
+      </c>
+      <c r="O97" s="46">
+        <v>6</v>
+      </c>
+      <c r="Q97" s="19"/>
+    </row>
+    <row r="98" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A98" s="5" t="str">
+        <f>B98&amp;C98</f>
+        <v>1016003</v>
+      </c>
+      <c r="B98" s="5">
+        <v>101600</v>
+      </c>
+      <c r="C98" s="5">
+        <v>3</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F98" s="5">
+        <v>1</v>
+      </c>
+      <c r="G98" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H98" s="5">
+        <v>2016001</v>
+      </c>
+      <c r="I98" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J98" s="5"/>
+      <c r="L98" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="M98" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="N98" s="46">
+        <v>6</v>
+      </c>
+      <c r="O98" s="46">
+        <v>6</v>
+      </c>
+      <c r="Q98" s="19"/>
+    </row>
+    <row r="99" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N99" s="46"/>
+      <c r="O99" s="46"/>
+      <c r="Q99" s="19"/>
+    </row>
+    <row r="100" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N100" s="46"/>
+      <c r="O100" s="46"/>
+      <c r="Q100" s="19"/>
+    </row>
+    <row r="101" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N101" s="46"/>
+      <c r="O101" s="46"/>
+      <c r="Q101" s="19"/>
+    </row>
+    <row r="102" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N102" s="46"/>
+      <c r="O102" s="46"/>
+      <c r="Q102" s="19"/>
+    </row>
+    <row r="103" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N103" s="46"/>
+      <c r="O103" s="46"/>
+      <c r="Q103" s="19"/>
+    </row>
+    <row r="104" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N104" s="46"/>
+      <c r="O104" s="46"/>
+      <c r="Q104" s="19"/>
+    </row>
+    <row r="105" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N105" s="46"/>
+      <c r="O105" s="46"/>
+      <c r="Q105" s="19"/>
+    </row>
+    <row r="106" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N106" s="46"/>
+      <c r="O106" s="46"/>
+      <c r="Q106" s="19"/>
+    </row>
+    <row r="107" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N107" s="46"/>
+      <c r="O107" s="46"/>
+      <c r="Q107" s="19"/>
+    </row>
+    <row r="108" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N108" s="46"/>
+      <c r="O108" s="46"/>
+      <c r="Q108" s="19"/>
+    </row>
+    <row r="109" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N109" s="46"/>
+      <c r="O109" s="46"/>
+      <c r="Q109" s="19"/>
+    </row>
+    <row r="110" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N110" s="46"/>
+      <c r="O110" s="46"/>
+      <c r="Q110" s="19"/>
+    </row>
+    <row r="111" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N111" s="46"/>
+      <c r="O111" s="46"/>
+      <c r="Q111" s="19"/>
+    </row>
+    <row r="112" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N112" s="46"/>
+      <c r="O112" s="46"/>
+      <c r="Q112" s="19"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:K2">

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="206">
   <si>
     <t>id</t>
   </si>
@@ -705,6 +705,45 @@
   </si>
   <si>
     <t>改出3个SCATTER+奖池符号</t>
+  </si>
+  <si>
+    <t>狼月</t>
+  </si>
+  <si>
+    <t>10150001|10150004</t>
+  </si>
+  <si>
+    <t>概率改出百搭wild符号+概率改出scatter符号</t>
+  </si>
+  <si>
+    <t>许愿百搭模式</t>
+  </si>
+  <si>
+    <t>10150009_10|10150010_10|10150011_10|10150012_10|10150013_10|10150014_5|10150015_5|10150016_5|10150017_5|10150018_5|10150019_5|10150020_5|10150021_5|10150022_5|10150023_5|10150024_1|10150025_1|10150026_1|10150027_1|10150028_1|10150029_1</t>
+  </si>
+  <si>
+    <t>10150003|10150008</t>
+  </si>
+  <si>
+    <t>改出2个SCATTER+奖池符号</t>
+  </si>
+  <si>
+    <t>高赔付免费</t>
+  </si>
+  <si>
+    <t>改出20符号</t>
+  </si>
+  <si>
+    <t>固定堆叠免费</t>
+  </si>
+  <si>
+    <t>改出21符号</t>
+  </si>
+  <si>
+    <t>递增奖励免费</t>
+  </si>
+  <si>
+    <t>改出22符号</t>
   </si>
 </sst>
 </file>
@@ -5632,7 +5671,7 @@
     </row>
     <row r="84" customFormat="1" ht="16.5" spans="1:17">
       <c r="A84" s="5" t="str">
-        <f t="shared" ref="A84:A95" si="4">B84&amp;C84</f>
+        <f t="shared" ref="A84:A98" si="4">B84&amp;C84</f>
         <v>1031001</v>
       </c>
       <c r="B84" s="5">
@@ -6148,7 +6187,7 @@
     </row>
     <row r="96" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A96" s="5" t="str">
-        <f>B96&amp;C96</f>
+        <f t="shared" si="4"/>
         <v>1016001</v>
       </c>
       <c r="B96" s="5">
@@ -6191,7 +6230,7 @@
     </row>
     <row r="97" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A97" s="5" t="str">
-        <f>B97&amp;C97</f>
+        <f t="shared" si="4"/>
         <v>1016002</v>
       </c>
       <c r="B97" s="5">
@@ -6218,7 +6257,7 @@
       <c r="I97" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L97" s="60">
+      <c r="L97" s="47">
         <v>10160002</v>
       </c>
       <c r="M97" s="5" t="s">
@@ -6234,7 +6273,7 @@
     </row>
     <row r="98" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A98" s="5" t="str">
-        <f>B98&amp;C98</f>
+        <f t="shared" si="4"/>
         <v>1016003</v>
       </c>
       <c r="B98" s="5">
@@ -6277,38 +6316,304 @@
       <c r="Q98" s="19"/>
     </row>
     <row r="99" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="N99" s="46"/>
-      <c r="O99" s="46"/>
+      <c r="A99" s="5" t="str">
+        <f>B99&amp;C99</f>
+        <v>1015001</v>
+      </c>
+      <c r="B99" s="5">
+        <v>101500</v>
+      </c>
+      <c r="C99" s="5">
+        <v>1</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E99" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F99" s="5">
+        <v>1</v>
+      </c>
+      <c r="G99" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H99" s="5">
+        <v>2015001</v>
+      </c>
+      <c r="I99" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L99" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="M99" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="N99" s="46">
+        <v>3</v>
+      </c>
+      <c r="O99" s="46">
+        <v>5</v>
+      </c>
       <c r="Q99" s="19"/>
     </row>
     <row r="100" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="N100" s="46"/>
-      <c r="O100" s="46"/>
+      <c r="A100" s="5" t="str">
+        <f>B100&amp;C100</f>
+        <v>1015002</v>
+      </c>
+      <c r="B100" s="5">
+        <v>101500</v>
+      </c>
+      <c r="C100" s="5">
+        <v>2</v>
+      </c>
+      <c r="D100" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E100" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="F100" s="5">
+        <v>1</v>
+      </c>
+      <c r="G100" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H100" s="5">
+        <v>2015001</v>
+      </c>
+      <c r="I100" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J100" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="M100" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="N100" s="46">
+        <v>3</v>
+      </c>
+      <c r="O100" s="46">
+        <v>5</v>
+      </c>
       <c r="Q100" s="19"/>
     </row>
     <row r="101" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="N101" s="46"/>
-      <c r="O101" s="46"/>
+      <c r="A101" s="5" t="str">
+        <f>B101&amp;C101</f>
+        <v>1015003</v>
+      </c>
+      <c r="B101" s="5">
+        <v>101500</v>
+      </c>
+      <c r="C101" s="5">
+        <v>3</v>
+      </c>
+      <c r="D101" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E101" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F101" s="5">
+        <v>1</v>
+      </c>
+      <c r="G101" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H101" s="5">
+        <v>2015001</v>
+      </c>
+      <c r="I101" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L101" s="60">
+        <v>10150002</v>
+      </c>
+      <c r="M101" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="N101" s="46">
+        <v>3</v>
+      </c>
+      <c r="O101" s="46">
+        <v>5</v>
+      </c>
       <c r="Q101" s="19"/>
     </row>
     <row r="102" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="N102" s="46"/>
-      <c r="O102" s="46"/>
+      <c r="A102" s="5" t="str">
+        <f>B102&amp;C102</f>
+        <v>1015004</v>
+      </c>
+      <c r="B102" s="5">
+        <v>101500</v>
+      </c>
+      <c r="C102" s="5">
+        <v>4</v>
+      </c>
+      <c r="D102" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E102" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F102" s="5">
+        <v>1</v>
+      </c>
+      <c r="G102" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H102" s="5">
+        <v>2015001</v>
+      </c>
+      <c r="I102" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L102" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="M102" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="N102" s="46">
+        <v>3</v>
+      </c>
+      <c r="O102" s="46">
+        <v>5</v>
+      </c>
       <c r="Q102" s="19"/>
     </row>
     <row r="103" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="N103" s="46"/>
-      <c r="O103" s="46"/>
+      <c r="A103" s="5" t="str">
+        <f>B103&amp;C103</f>
+        <v>1015005</v>
+      </c>
+      <c r="B103" s="5">
+        <v>101500</v>
+      </c>
+      <c r="C103" s="5">
+        <v>5</v>
+      </c>
+      <c r="D103" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E103" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="F103" s="5">
+        <v>1</v>
+      </c>
+      <c r="G103" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H103" s="5">
+        <v>2015002</v>
+      </c>
+      <c r="I103" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L103" s="60">
+        <v>10150005</v>
+      </c>
+      <c r="M103" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="N103" s="46">
+        <v>3</v>
+      </c>
+      <c r="O103" s="46">
+        <v>5</v>
+      </c>
       <c r="Q103" s="19"/>
     </row>
     <row r="104" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="N104" s="46"/>
-      <c r="O104" s="46"/>
+      <c r="A104" s="5" t="str">
+        <f>B104&amp;C104</f>
+        <v>1015006</v>
+      </c>
+      <c r="B104" s="5">
+        <v>101500</v>
+      </c>
+      <c r="C104" s="5">
+        <v>6</v>
+      </c>
+      <c r="D104" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E104" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="F104" s="5">
+        <v>1</v>
+      </c>
+      <c r="G104" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H104" s="5">
+        <v>2015001</v>
+      </c>
+      <c r="I104" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L104" s="60">
+        <v>10150006</v>
+      </c>
+      <c r="M104" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="N104" s="46">
+        <v>3</v>
+      </c>
+      <c r="O104" s="46">
+        <v>5</v>
+      </c>
       <c r="Q104" s="19"/>
     </row>
     <row r="105" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="N105" s="46"/>
-      <c r="O105" s="46"/>
+      <c r="A105" s="5" t="str">
+        <f>B105&amp;C105</f>
+        <v>1015007</v>
+      </c>
+      <c r="B105" s="5">
+        <v>101500</v>
+      </c>
+      <c r="C105" s="5">
+        <v>7</v>
+      </c>
+      <c r="D105" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E105" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="F105" s="5">
+        <v>1</v>
+      </c>
+      <c r="G105" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H105" s="5">
+        <v>2015001</v>
+      </c>
+      <c r="I105" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L105" s="60">
+        <v>10150007</v>
+      </c>
+      <c r="M105" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="N105" s="46">
+        <v>3</v>
+      </c>
+      <c r="O105" s="46">
+        <v>5</v>
+      </c>
       <c r="Q105" s="19"/>
     </row>
     <row r="106" s="5" customFormat="1" ht="16.5" spans="1:17">

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="209">
   <si>
     <t>id</t>
   </si>
@@ -614,10 +614,19 @@
     <t>10倍金牛</t>
   </si>
   <si>
-    <t>概率改出百搭符号</t>
+    <t>10370001|10370003</t>
+  </si>
+  <si>
+    <t>概率改出百搭符号+异形位置改为不中奖图案</t>
   </si>
   <si>
     <t>金牛赐福-触发局</t>
+  </si>
+  <si>
+    <t>10370002|10370003</t>
+  </si>
+  <si>
+    <t>异形位置改为不中奖图案</t>
   </si>
   <si>
     <t>绿巨人</t>
@@ -1474,7 +1483,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1601,9 +1610,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5573,11 +5579,11 @@
       <c r="I81" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L81" s="47">
-        <v>10370001</v>
+      <c r="L81" s="47" t="s">
+        <v>162</v>
       </c>
       <c r="M81" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N81" s="46">
         <v>4</v>
@@ -5602,25 +5608,25 @@
         <v>161</v>
       </c>
       <c r="E82" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F82" s="5">
+        <v>1</v>
+      </c>
+      <c r="G82" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H82" s="5">
+        <v>2037002</v>
+      </c>
+      <c r="I82" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L82" s="47" t="s">
+        <v>165</v>
+      </c>
+      <c r="M82" s="5" t="s">
         <v>163</v>
-      </c>
-      <c r="F82" s="5">
-        <v>1</v>
-      </c>
-      <c r="G82" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H82" s="5">
-        <v>2037001</v>
-      </c>
-      <c r="I82" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L82" s="47">
-        <v>10370003</v>
-      </c>
-      <c r="M82" s="5" t="s">
-        <v>116</v>
       </c>
       <c r="N82" s="46">
         <v>4</v>
@@ -5659,8 +5665,12 @@
       <c r="I83" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L83" s="47"/>
-      <c r="M83" s="5"/>
+      <c r="L83" s="47">
+        <v>10370003</v>
+      </c>
+      <c r="M83" s="5" t="s">
+        <v>166</v>
+      </c>
       <c r="N83" s="46">
         <v>4</v>
       </c>
@@ -5671,7 +5681,7 @@
     </row>
     <row r="84" customFormat="1" ht="16.5" spans="1:17">
       <c r="A84" s="5" t="str">
-        <f t="shared" ref="A84:A98" si="4">B84&amp;C84</f>
+        <f t="shared" ref="A84:A105" si="4">B84&amp;C84</f>
         <v>1031001</v>
       </c>
       <c r="B84" s="5">
@@ -5681,7 +5691,7 @@
         <v>1</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>111</v>
@@ -5699,10 +5709,10 @@
         <v>24</v>
       </c>
       <c r="L84" s="47" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="M84" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="N84" s="46">
         <v>3</v>
@@ -5724,7 +5734,7 @@
         <v>2</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E85" s="5" t="s">
         <v>131</v>
@@ -5745,7 +5755,7 @@
         <v>10310008</v>
       </c>
       <c r="M85" s="5" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="N85" s="46">
         <v>3</v>
@@ -5767,7 +5777,7 @@
         <v>3</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E86" s="5" t="s">
         <v>94</v>
@@ -5785,10 +5795,10 @@
         <v>24</v>
       </c>
       <c r="L86" s="47" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="M86" s="5" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="N86" s="46">
         <v>3</v>
@@ -5810,7 +5820,7 @@
         <v>4</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E87" s="5" t="s">
         <v>81</v>
@@ -5828,10 +5838,10 @@
         <v>24</v>
       </c>
       <c r="L87" s="47" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="M87" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="N87" s="46">
         <v>3</v>
@@ -5853,10 +5863,10 @@
         <v>5</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F88" s="5">
         <v>1</v>
@@ -5874,7 +5884,7 @@
         <v>10310003</v>
       </c>
       <c r="M88" s="5" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="N88" s="46">
         <v>3</v>
@@ -5896,10 +5906,10 @@
         <v>6</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F89" s="5">
         <v>1</v>
@@ -5914,10 +5924,10 @@
         <v>24</v>
       </c>
       <c r="L89" s="47" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="M89" s="5" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N89" s="46">
         <v>3</v>
@@ -5939,7 +5949,7 @@
         <v>1</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E90" s="5" t="s">
         <v>111</v>
@@ -5957,10 +5967,10 @@
         <v>24</v>
       </c>
       <c r="L90" s="47" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="M90" s="5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="N90" s="46">
         <v>3</v>
@@ -5982,7 +5992,7 @@
         <v>2</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E91" s="5" t="s">
         <v>131</v>
@@ -6000,10 +6010,10 @@
         <v>24</v>
       </c>
       <c r="L91" s="47" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="M91" s="5" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="N91" s="46">
         <v>3</v>
@@ -6025,7 +6035,7 @@
         <v>3</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E92" s="5" t="s">
         <v>81</v>
@@ -6043,10 +6053,10 @@
         <v>24</v>
       </c>
       <c r="L92" s="47" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="M92" s="5" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="N92" s="46">
         <v>3</v>
@@ -6068,7 +6078,7 @@
         <v>1</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E93" s="5" t="s">
         <v>111</v>
@@ -6086,7 +6096,7 @@
         <v>24</v>
       </c>
       <c r="L93" s="5" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="M93" s="5" t="s">
         <v>157</v>
@@ -6111,7 +6121,7 @@
         <v>2</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E94" s="5" t="s">
         <v>131</v>
@@ -6154,7 +6164,7 @@
         <v>3</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E95" s="5" t="s">
         <v>81</v>
@@ -6172,7 +6182,7 @@
         <v>24</v>
       </c>
       <c r="L95" s="5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="M95" s="5" t="s">
         <v>83</v>
@@ -6197,7 +6207,7 @@
         <v>1</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E96" s="5" t="s">
         <v>111</v>
@@ -6215,10 +6225,10 @@
         <v>24</v>
       </c>
       <c r="L96" s="5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="M96" s="5" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="N96" s="46">
         <v>6</v>
@@ -6240,7 +6250,7 @@
         <v>2</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E97" s="5" t="s">
         <v>131</v>
@@ -6261,7 +6271,7 @@
         <v>10160002</v>
       </c>
       <c r="M97" s="5" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="N97" s="46">
         <v>6</v>
@@ -6283,7 +6293,7 @@
         <v>3</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E98" s="5" t="s">
         <v>81</v>
@@ -6302,10 +6312,10 @@
       </c>
       <c r="J98" s="5"/>
       <c r="L98" s="5" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="M98" s="5" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="N98" s="46">
         <v>6</v>
@@ -6317,7 +6327,7 @@
     </row>
     <row r="99" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A99" s="5" t="str">
-        <f>B99&amp;C99</f>
+        <f t="shared" si="4"/>
         <v>1015001</v>
       </c>
       <c r="B99" s="5">
@@ -6327,7 +6337,7 @@
         <v>1</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E99" s="5" t="s">
         <v>111</v>
@@ -6345,10 +6355,10 @@
         <v>24</v>
       </c>
       <c r="L99" s="5" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="M99" s="5" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="N99" s="46">
         <v>3</v>
@@ -6360,7 +6370,7 @@
     </row>
     <row r="100" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A100" s="5" t="str">
-        <f>B100&amp;C100</f>
+        <f t="shared" si="4"/>
         <v>1015002</v>
       </c>
       <c r="B100" s="5">
@@ -6370,10 +6380,10 @@
         <v>2</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F100" s="5">
         <v>1</v>
@@ -6388,7 +6398,7 @@
         <v>24</v>
       </c>
       <c r="J100" s="5" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="M100" s="5" t="s">
         <v>108</v>
@@ -6403,7 +6413,7 @@
     </row>
     <row r="101" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A101" s="5" t="str">
-        <f>B101&amp;C101</f>
+        <f t="shared" si="4"/>
         <v>1015003</v>
       </c>
       <c r="B101" s="5">
@@ -6413,7 +6423,7 @@
         <v>3</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E101" s="5" t="s">
         <v>131</v>
@@ -6430,7 +6440,7 @@
       <c r="I101" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L101" s="60">
+      <c r="L101" s="47">
         <v>10150002</v>
       </c>
       <c r="M101" s="5" t="s">
@@ -6446,7 +6456,7 @@
     </row>
     <row r="102" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A102" s="5" t="str">
-        <f>B102&amp;C102</f>
+        <f t="shared" si="4"/>
         <v>1015004</v>
       </c>
       <c r="B102" s="5">
@@ -6456,7 +6466,7 @@
         <v>4</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E102" s="5" t="s">
         <v>81</v>
@@ -6474,10 +6484,10 @@
         <v>24</v>
       </c>
       <c r="L102" s="5" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="M102" s="5" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="N102" s="46">
         <v>3</v>
@@ -6489,7 +6499,7 @@
     </row>
     <row r="103" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A103" s="5" t="str">
-        <f>B103&amp;C103</f>
+        <f t="shared" si="4"/>
         <v>1015005</v>
       </c>
       <c r="B103" s="5">
@@ -6499,10 +6509,10 @@
         <v>5</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F103" s="5">
         <v>1</v>
@@ -6516,11 +6526,11 @@
       <c r="I103" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L103" s="60">
+      <c r="L103" s="47">
         <v>10150005</v>
       </c>
       <c r="M103" s="5" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="N103" s="46">
         <v>3</v>
@@ -6532,7 +6542,7 @@
     </row>
     <row r="104" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A104" s="5" t="str">
-        <f>B104&amp;C104</f>
+        <f t="shared" si="4"/>
         <v>1015006</v>
       </c>
       <c r="B104" s="5">
@@ -6542,10 +6552,10 @@
         <v>6</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F104" s="5">
         <v>1</v>
@@ -6559,11 +6569,11 @@
       <c r="I104" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L104" s="60">
+      <c r="L104" s="47">
         <v>10150006</v>
       </c>
       <c r="M104" s="5" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N104" s="46">
         <v>3</v>
@@ -6575,7 +6585,7 @@
     </row>
     <row r="105" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A105" s="5" t="str">
-        <f>B105&amp;C105</f>
+        <f t="shared" si="4"/>
         <v>1015007</v>
       </c>
       <c r="B105" s="5">
@@ -6585,10 +6595,10 @@
         <v>7</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F105" s="5">
         <v>1</v>
@@ -6602,11 +6612,11 @@
       <c r="I105" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L105" s="60">
+      <c r="L105" s="47">
         <v>10150007</v>
       </c>
       <c r="M105" s="5" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="N105" s="46">
         <v>3</v>

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialMode" sheetId="1" r:id="rId1"/>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="128">
   <si>
     <t>id</t>
   </si>
@@ -1882,7 +1882,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S74"/>
+  <dimension ref="A1:S76"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
@@ -2371,7 +2371,7 @@
     </row>
     <row r="13" s="2" customFormat="1" ht="16.5" spans="1:17">
       <c r="A13" s="34" t="str">
-        <f t="shared" ref="A13:A30" si="1">B13&amp;C13</f>
+        <f t="shared" si="0"/>
         <v>1003002</v>
       </c>
       <c r="B13" s="26">
@@ -2414,7 +2414,7 @@
     </row>
     <row r="14" s="2" customFormat="1" ht="16.5" spans="1:17">
       <c r="A14" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1003003</v>
       </c>
       <c r="B14" s="26">
@@ -2461,7 +2461,7 @@
     </row>
     <row r="15" s="3" customFormat="1" ht="16.5" spans="1:17">
       <c r="A15" s="37" t="str">
-        <f t="shared" si="1"/>
+        <f>B15&amp;C15</f>
         <v>1007001</v>
       </c>
       <c r="B15" s="38">
@@ -2505,7 +2505,7 @@
     </row>
     <row r="16" s="3" customFormat="1" ht="16.5" spans="1:17">
       <c r="A16" s="37" t="str">
-        <f t="shared" si="1"/>
+        <f>B16&amp;C16</f>
         <v>1007002</v>
       </c>
       <c r="B16" s="38">
@@ -2547,7 +2547,7 @@
     </row>
     <row r="17" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A17" s="40" t="str">
-        <f t="shared" si="1"/>
+        <f>B17&amp;C17</f>
         <v>1012001</v>
       </c>
       <c r="B17" s="41">
@@ -2592,7 +2592,7 @@
     </row>
     <row r="18" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A18" s="40" t="str">
-        <f t="shared" si="1"/>
+        <f>B18&amp;C18</f>
         <v>1012002</v>
       </c>
       <c r="B18" s="41">
@@ -2635,7 +2635,7 @@
     </row>
     <row r="19" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A19" s="40" t="str">
-        <f t="shared" si="1"/>
+        <f>B19&amp;C19</f>
         <v>1012003</v>
       </c>
       <c r="B19" s="41">
@@ -2678,241 +2678,247 @@
       </c>
       <c r="Q19" s="43"/>
     </row>
-    <row r="20" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A20" s="34" t="str">
-        <f t="shared" si="1"/>
+    <row r="20" s="4" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A20" s="40" t="str">
+        <f>B20&amp;C20</f>
+        <v>1012004</v>
+      </c>
+      <c r="B20" s="41">
+        <v>101200</v>
+      </c>
+      <c r="C20" s="41">
+        <v>4</v>
+      </c>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="F20" s="41">
+        <v>1</v>
+      </c>
+      <c r="G20" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="40">
+        <v>2012001</v>
+      </c>
+      <c r="I20" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="J20" s="40" t="s">
+        <v>62</v>
+      </c>
+      <c r="K20" s="40" t="s">
+        <v>63</v>
+      </c>
+      <c r="L20" s="42"/>
+      <c r="M20" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="N20" s="41">
+        <v>3</v>
+      </c>
+      <c r="O20" s="41">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="43"/>
+    </row>
+    <row r="21" s="4" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A21" s="40" t="str">
+        <f>B21&amp;C21</f>
+        <v>1012005</v>
+      </c>
+      <c r="B21" s="41">
+        <v>101200</v>
+      </c>
+      <c r="C21" s="41">
+        <v>5</v>
+      </c>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" s="41">
+        <v>1</v>
+      </c>
+      <c r="G21" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="40">
+        <v>2012001</v>
+      </c>
+      <c r="I21" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="J21" s="40" t="s">
+        <v>62</v>
+      </c>
+      <c r="K21" s="40" t="s">
+        <v>63</v>
+      </c>
+      <c r="L21" s="42"/>
+      <c r="M21" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="N21" s="41">
+        <v>3</v>
+      </c>
+      <c r="O21" s="41">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="43"/>
+    </row>
+    <row r="22" s="3" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A22" s="34" t="str">
+        <f t="shared" ref="A22:A32" si="1">B22&amp;C22</f>
         <v>1014001</v>
       </c>
-      <c r="B20" s="26">
+      <c r="B22" s="26">
         <v>101400</v>
       </c>
-      <c r="C20" s="26">
-        <v>1</v>
-      </c>
-      <c r="D20" s="26" t="s">
+      <c r="C22" s="26">
+        <v>1</v>
+      </c>
+      <c r="D22" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="E20" s="26" t="s">
+      <c r="E22" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="F20" s="26">
-        <v>1</v>
-      </c>
-      <c r="G20" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="H20" s="34">
+      <c r="F22" s="26">
+        <v>1</v>
+      </c>
+      <c r="G22" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="34">
         <v>2014001</v>
       </c>
-      <c r="I20" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="J20" s="34"/>
-      <c r="K20" s="34"/>
-      <c r="L20" s="35" t="s">
+      <c r="I22" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="M20" s="34" t="s">
+      <c r="M22" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="N20" s="17">
+      <c r="N22" s="17">
         <v>4</v>
       </c>
-      <c r="O20" s="17">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="44"/>
-    </row>
-    <row r="21" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A21" s="34" t="str">
+      <c r="O22" s="17">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="44"/>
+    </row>
+    <row r="23" s="3" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A23" s="34" t="str">
         <f t="shared" si="1"/>
         <v>1014002</v>
       </c>
-      <c r="B21" s="26">
+      <c r="B23" s="26">
         <v>101400</v>
       </c>
-      <c r="C21" s="26">
+      <c r="C23" s="26">
         <v>2</v>
       </c>
-      <c r="D21" s="26" t="s">
+      <c r="D23" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="E21" s="26" t="s">
+      <c r="E23" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="26">
-        <v>1</v>
-      </c>
-      <c r="G21" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="H21" s="34">
+      <c r="F23" s="26">
+        <v>1</v>
+      </c>
+      <c r="G23" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="34">
         <v>2014001</v>
       </c>
-      <c r="I21" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="J21" s="34"/>
-      <c r="K21" s="34"/>
-      <c r="L21" s="35" t="s">
+      <c r="I23" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="J23" s="34"/>
+      <c r="K23" s="34"/>
+      <c r="L23" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="M21" s="34" t="s">
+      <c r="M23" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="N21" s="17">
+      <c r="N23" s="17">
         <v>4</v>
       </c>
-      <c r="O21" s="17">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="44"/>
-    </row>
-    <row r="22" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A22" s="34" t="str">
+      <c r="O23" s="17">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="44"/>
+    </row>
+    <row r="24" s="3" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A24" s="34" t="str">
         <f t="shared" si="1"/>
         <v>1014003</v>
       </c>
-      <c r="B22" s="26">
+      <c r="B24" s="26">
         <v>101400</v>
       </c>
-      <c r="C22" s="26">
-        <v>3</v>
-      </c>
-      <c r="D22" s="26" t="s">
+      <c r="C24" s="26">
+        <v>3</v>
+      </c>
+      <c r="D24" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="E22" s="26" t="s">
+      <c r="E24" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="F22" s="26">
-        <v>1</v>
-      </c>
-      <c r="G22" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="H22" s="34">
+      <c r="F24" s="26">
+        <v>1</v>
+      </c>
+      <c r="G24" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" s="34">
         <v>2014001</v>
       </c>
-      <c r="I22" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="J22" s="34"/>
-      <c r="K22" s="34"/>
-      <c r="L22" s="35">
+      <c r="I24" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="J24" s="34"/>
+      <c r="K24" s="34"/>
+      <c r="L24" s="35">
         <v>10140021</v>
       </c>
-      <c r="M22" s="34" t="s">
+      <c r="M24" s="34" t="s">
         <v>71</v>
-      </c>
-      <c r="N22" s="17">
-        <v>4</v>
-      </c>
-      <c r="O22" s="17">
-        <v>3</v>
-      </c>
-      <c r="Q22" s="44"/>
-    </row>
-    <row r="23" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A23" s="24" t="str">
-        <f t="shared" si="1"/>
-        <v>1024001</v>
-      </c>
-      <c r="B23" s="25">
-        <v>102400</v>
-      </c>
-      <c r="C23" s="25">
-        <v>1</v>
-      </c>
-      <c r="D23" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="F23" s="25">
-        <v>1</v>
-      </c>
-      <c r="G23" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H23" s="24">
-        <v>2024001</v>
-      </c>
-      <c r="I23" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="27" t="s">
-        <v>73</v>
-      </c>
-      <c r="M23" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="N23" s="17">
-        <v>4</v>
-      </c>
-      <c r="O23" s="17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A24" s="24" t="str">
-        <f t="shared" si="1"/>
-        <v>1024002</v>
-      </c>
-      <c r="B24" s="25">
-        <v>102400</v>
-      </c>
-      <c r="C24" s="25">
-        <v>2</v>
-      </c>
-      <c r="D24" s="25"/>
-      <c r="E24" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="F24" s="25">
-        <v>1</v>
-      </c>
-      <c r="G24" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H24" s="24">
-        <v>2024001</v>
-      </c>
-      <c r="I24" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="J24" s="24"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="M24" s="24" t="s">
-        <v>29</v>
       </c>
       <c r="N24" s="17">
         <v>4</v>
       </c>
       <c r="O24" s="17">
-        <v>5</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="Q24" s="44"/>
     </row>
     <row r="25" s="1" customFormat="1" ht="16.5" spans="1:17">
       <c r="A25" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>1024003</v>
+        <v>1024001</v>
       </c>
       <c r="B25" s="25">
         <v>102400</v>
       </c>
       <c r="C25" s="25">
-        <v>3</v>
-      </c>
-      <c r="D25" s="25"/>
-      <c r="E25" s="30" t="s">
-        <v>30</v>
+        <v>1</v>
+      </c>
+      <c r="D25" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="E25" s="26" t="s">
+        <v>22</v>
       </c>
       <c r="F25" s="25">
         <v>1</v>
@@ -2929,10 +2935,10 @@
       <c r="J25" s="24"/>
       <c r="K25" s="24"/>
       <c r="L25" s="27" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="M25" s="24" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N25" s="17">
         <v>4</v>
@@ -2944,19 +2950,19 @@
     <row r="26" s="1" customFormat="1" ht="16.5" spans="1:17">
       <c r="A26" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>1024004</v>
+        <v>1024002</v>
       </c>
       <c r="B26" s="25">
         <v>102400</v>
       </c>
       <c r="C26" s="25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D26" s="25"/>
-      <c r="E26" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="F26" s="32">
+      <c r="E26" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" s="25">
         <v>1</v>
       </c>
       <c r="G26" s="24" t="s">
@@ -2970,11 +2976,11 @@
       </c>
       <c r="J26" s="24"/>
       <c r="K26" s="24"/>
-      <c r="L26" s="27">
-        <v>10240041</v>
+      <c r="L26" s="29" t="s">
+        <v>74</v>
       </c>
       <c r="M26" s="24" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="N26" s="17">
         <v>4</v>
@@ -2986,19 +2992,19 @@
     <row r="27" s="1" customFormat="1" ht="16.5" spans="1:17">
       <c r="A27" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>1024005</v>
+        <v>1024003</v>
       </c>
       <c r="B27" s="25">
         <v>102400</v>
       </c>
       <c r="C27" s="25">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D27" s="25"/>
-      <c r="E27" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="F27" s="32">
+      <c r="E27" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="F27" s="25">
         <v>1</v>
       </c>
       <c r="G27" s="24" t="s">
@@ -3013,10 +3019,10 @@
       <c r="J27" s="24"/>
       <c r="K27" s="24"/>
       <c r="L27" s="27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M27" s="24" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="N27" s="17">
         <v>4</v>
@@ -3028,17 +3034,17 @@
     <row r="28" s="1" customFormat="1" ht="16.5" spans="1:17">
       <c r="A28" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>1024006</v>
+        <v>1024004</v>
       </c>
       <c r="B28" s="25">
         <v>102400</v>
       </c>
       <c r="C28" s="25">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D28" s="25"/>
-      <c r="E28" s="33" t="s">
-        <v>38</v>
+      <c r="E28" s="31" t="s">
+        <v>33</v>
       </c>
       <c r="F28" s="32">
         <v>1</v>
@@ -3055,10 +3061,10 @@
       <c r="J28" s="24"/>
       <c r="K28" s="24"/>
       <c r="L28" s="27">
-        <v>10240061</v>
+        <v>10240041</v>
       </c>
       <c r="M28" s="24" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="N28" s="17">
         <v>4</v>
@@ -3070,19 +3076,19 @@
     <row r="29" s="1" customFormat="1" ht="16.5" spans="1:17">
       <c r="A29" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>1024007</v>
+        <v>1024005</v>
       </c>
       <c r="B29" s="25">
         <v>102400</v>
       </c>
       <c r="C29" s="25">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D29" s="25"/>
-      <c r="E29" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="F29" s="25">
+      <c r="E29" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="F29" s="32">
         <v>1</v>
       </c>
       <c r="G29" s="24" t="s">
@@ -3096,11 +3102,11 @@
       </c>
       <c r="J29" s="24"/>
       <c r="K29" s="24"/>
-      <c r="L29" s="29" t="s">
-        <v>77</v>
+      <c r="L29" s="27" t="s">
+        <v>76</v>
       </c>
       <c r="M29" s="24" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="N29" s="17">
         <v>4</v>
@@ -3109,108 +3115,106 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" s="5" customFormat="1" ht="16.5" spans="1:17">
+    <row r="30" s="1" customFormat="1" ht="16.5" spans="1:17">
       <c r="A30" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>1017001</v>
-      </c>
-      <c r="B30" s="5">
-        <v>101700</v>
-      </c>
-      <c r="C30" s="5">
-        <v>1</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F30" s="5">
-        <v>1</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H30" s="5">
-        <v>2017001</v>
-      </c>
-      <c r="I30" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L30" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="M30" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="N30" s="45">
+        <v>1024006</v>
+      </c>
+      <c r="B30" s="25">
+        <v>102400</v>
+      </c>
+      <c r="C30" s="25">
+        <v>6</v>
+      </c>
+      <c r="D30" s="25"/>
+      <c r="E30" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="F30" s="32">
+        <v>1</v>
+      </c>
+      <c r="G30" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H30" s="24">
+        <v>2024001</v>
+      </c>
+      <c r="I30" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="J30" s="24"/>
+      <c r="K30" s="24"/>
+      <c r="L30" s="27">
+        <v>10240061</v>
+      </c>
+      <c r="M30" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="N30" s="17">
         <v>4</v>
       </c>
-      <c r="O30" s="45">
+      <c r="O30" s="17">
         <v>5</v>
       </c>
-      <c r="Q30" s="18"/>
-    </row>
-    <row r="31" s="5" customFormat="1" ht="16.5" spans="1:17">
+    </row>
+    <row r="31" s="1" customFormat="1" ht="16.5" spans="1:17">
       <c r="A31" s="24" t="str">
-        <f t="shared" ref="A31:A53" si="2">B31&amp;C31</f>
-        <v>1017002</v>
-      </c>
-      <c r="B31" s="5">
-        <v>101700</v>
-      </c>
-      <c r="C31" s="5">
-        <v>2</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F31" s="5">
-        <v>1</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H31" s="5">
-        <v>2017001</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L31" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="M31" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="N31" s="45">
+        <f t="shared" si="1"/>
+        <v>1024007</v>
+      </c>
+      <c r="B31" s="25">
+        <v>102400</v>
+      </c>
+      <c r="C31" s="25">
+        <v>7</v>
+      </c>
+      <c r="D31" s="25"/>
+      <c r="E31" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="F31" s="25">
+        <v>1</v>
+      </c>
+      <c r="G31" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H31" s="24">
+        <v>2024001</v>
+      </c>
+      <c r="I31" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="J31" s="24"/>
+      <c r="K31" s="24"/>
+      <c r="L31" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="M31" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="N31" s="17">
         <v>4</v>
       </c>
-      <c r="O31" s="45">
+      <c r="O31" s="17">
         <v>5</v>
       </c>
-      <c r="Q31" s="18"/>
     </row>
     <row r="32" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A32" s="24" t="str">
-        <f t="shared" si="2"/>
-        <v>1017003</v>
+        <f t="shared" si="1"/>
+        <v>1017001</v>
       </c>
       <c r="B32" s="5">
         <v>101700</v>
       </c>
       <c r="C32" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>78</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="F32" s="5">
         <v>1</v>
@@ -3225,10 +3229,10 @@
         <v>24</v>
       </c>
       <c r="L32" s="5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="M32" s="5" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="N32" s="45">
         <v>4</v>
@@ -3240,20 +3244,20 @@
     </row>
     <row r="33" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A33" s="24" t="str">
-        <f t="shared" si="2"/>
-        <v>1022001</v>
+        <f t="shared" ref="A33:A56" si="2">B33&amp;C33</f>
+        <v>1017002</v>
       </c>
       <c r="B33" s="5">
-        <v>102200</v>
+        <v>101700</v>
       </c>
       <c r="C33" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="F33" s="5">
         <v>1</v>
@@ -3262,19 +3266,19 @@
         <v>23</v>
       </c>
       <c r="H33" s="5">
-        <v>2022001</v>
+        <v>2017001</v>
       </c>
       <c r="I33" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L33" s="46" t="s">
-        <v>85</v>
+      <c r="L33" s="5" t="s">
+        <v>80</v>
       </c>
       <c r="M33" s="5" t="s">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="N33" s="45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O33" s="45">
         <v>5</v>
@@ -3284,40 +3288,40 @@
     <row r="34" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A34" s="24" t="str">
         <f t="shared" si="2"/>
-        <v>1022002</v>
+        <v>1017003</v>
       </c>
       <c r="B34" s="5">
-        <v>102200</v>
+        <v>101700</v>
       </c>
       <c r="C34" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="F34" s="17">
-        <v>1</v>
-      </c>
-      <c r="G34" s="47" t="s">
+        <v>81</v>
+      </c>
+      <c r="F34" s="5">
+        <v>1</v>
+      </c>
+      <c r="G34" s="5" t="s">
         <v>23</v>
       </c>
       <c r="H34" s="5">
-        <v>2022001</v>
+        <v>2017001</v>
       </c>
       <c r="I34" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L34" s="46">
-        <v>10220033</v>
+      <c r="L34" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="M34" s="5" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="N34" s="45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O34" s="45">
         <v>5</v>
@@ -3327,24 +3331,24 @@
     <row r="35" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A35" s="24" t="str">
         <f t="shared" si="2"/>
-        <v>1022003</v>
+        <v>1022001</v>
       </c>
       <c r="B35" s="5">
         <v>102200</v>
       </c>
       <c r="C35" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>84</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F35" s="47">
-        <v>1</v>
-      </c>
-      <c r="G35" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" s="5">
+        <v>1</v>
+      </c>
+      <c r="G35" s="5" t="s">
         <v>23</v>
       </c>
       <c r="H35" s="5">
@@ -3353,11 +3357,11 @@
       <c r="I35" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L35" s="48" t="s">
-        <v>89</v>
+      <c r="L35" s="46" t="s">
+        <v>85</v>
       </c>
       <c r="M35" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="N35" s="45">
         <v>3</v>
@@ -3370,19 +3374,19 @@
     <row r="36" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A36" s="24" t="str">
         <f t="shared" si="2"/>
-        <v>1022004</v>
+        <v>1022002</v>
       </c>
       <c r="B36" s="5">
         <v>102200</v>
       </c>
       <c r="C36" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>84</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F36" s="17">
         <v>1</v>
@@ -3397,7 +3401,10 @@
         <v>24</v>
       </c>
       <c r="L36" s="46">
-        <v>10220020</v>
+        <v>10220033</v>
+      </c>
+      <c r="M36" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="N36" s="45">
         <v>3</v>
@@ -3410,24 +3417,24 @@
     <row r="37" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A37" s="24" t="str">
         <f t="shared" si="2"/>
-        <v>1022005</v>
+        <v>1022003</v>
       </c>
       <c r="B37" s="5">
         <v>102200</v>
       </c>
       <c r="C37" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>84</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="F37" s="5">
-        <v>1</v>
-      </c>
-      <c r="G37" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F37" s="47">
+        <v>1</v>
+      </c>
+      <c r="G37" s="47" t="s">
         <v>23</v>
       </c>
       <c r="H37" s="5">
@@ -3436,8 +3443,11 @@
       <c r="I37" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L37" s="46">
-        <v>10220019</v>
+      <c r="L37" s="48" t="s">
+        <v>89</v>
+      </c>
+      <c r="M37" s="5" t="s">
+        <v>83</v>
       </c>
       <c r="N37" s="45">
         <v>3</v>
@@ -3446,42 +3456,38 @@
         <v>5</v>
       </c>
       <c r="Q37" s="18"/>
-      <c r="S37" s="49"/>
     </row>
     <row r="38" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A38" s="24" t="str">
         <f t="shared" si="2"/>
-        <v>1021001</v>
+        <v>1022004</v>
       </c>
       <c r="B38" s="5">
-        <v>102100</v>
+        <v>102200</v>
       </c>
       <c r="C38" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F38" s="5">
-        <v>1</v>
-      </c>
-      <c r="G38" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="F38" s="17">
+        <v>1</v>
+      </c>
+      <c r="G38" s="47" t="s">
         <v>23</v>
       </c>
       <c r="H38" s="5">
-        <v>2021001</v>
+        <v>2022001</v>
       </c>
       <c r="I38" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L38" s="46" t="s">
-        <v>93</v>
-      </c>
-      <c r="M38" s="5" t="s">
-        <v>86</v>
+      <c r="L38" s="46">
+        <v>10220020</v>
       </c>
       <c r="N38" s="45">
         <v>3</v>
@@ -3490,24 +3496,23 @@
         <v>5</v>
       </c>
       <c r="Q38" s="18"/>
-      <c r="S38" s="49"/>
     </row>
     <row r="39" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A39" s="24" t="str">
         <f t="shared" si="2"/>
-        <v>1021002</v>
+        <v>1022005</v>
       </c>
       <c r="B39" s="5">
-        <v>102100</v>
+        <v>102200</v>
       </c>
       <c r="C39" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F39" s="5">
         <v>1</v>
@@ -3516,16 +3521,13 @@
         <v>23</v>
       </c>
       <c r="H39" s="5">
-        <v>2021001</v>
+        <v>2022001</v>
       </c>
       <c r="I39" s="5" t="s">
         <v>24</v>
       </c>
       <c r="L39" s="46">
-        <v>10210031</v>
-      </c>
-      <c r="M39" s="5" t="s">
-        <v>88</v>
+        <v>10220019</v>
       </c>
       <c r="N39" s="45">
         <v>3</v>
@@ -3539,19 +3541,19 @@
     <row r="40" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A40" s="24" t="str">
         <f t="shared" si="2"/>
-        <v>1021003</v>
+        <v>1021001</v>
       </c>
       <c r="B40" s="5">
         <v>102100</v>
       </c>
       <c r="C40" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>92</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="F40" s="5">
         <v>1</v>
@@ -3565,11 +3567,11 @@
       <c r="I40" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L40" s="46">
-        <v>10210041</v>
+      <c r="L40" s="46" t="s">
+        <v>93</v>
       </c>
       <c r="M40" s="5" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="N40" s="45">
         <v>3</v>
@@ -3583,19 +3585,19 @@
     <row r="41" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A41" s="24" t="str">
         <f t="shared" si="2"/>
-        <v>1021004</v>
+        <v>1021002</v>
       </c>
       <c r="B41" s="5">
         <v>102100</v>
       </c>
       <c r="C41" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>92</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F41" s="5">
         <v>1</v>
@@ -3609,11 +3611,11 @@
       <c r="I41" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L41" s="46" t="s">
-        <v>96</v>
+      <c r="L41" s="46">
+        <v>10210031</v>
       </c>
       <c r="M41" s="5" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="N41" s="45">
         <v>3</v>
@@ -3627,19 +3629,19 @@
     <row r="42" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A42" s="24" t="str">
         <f t="shared" si="2"/>
-        <v>1018001</v>
+        <v>1021003</v>
       </c>
       <c r="B42" s="5">
-        <v>101800</v>
+        <v>102100</v>
       </c>
       <c r="C42" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="F42" s="5">
         <v>1</v>
@@ -3648,212 +3650,214 @@
         <v>23</v>
       </c>
       <c r="H42" s="5">
-        <v>2018001</v>
+        <v>2021001</v>
       </c>
       <c r="I42" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L42" s="46" t="s">
-        <v>98</v>
+      <c r="L42" s="46">
+        <v>10210041</v>
       </c>
       <c r="M42" s="5" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="N42" s="45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O42" s="45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q42" s="18"/>
       <c r="S42" s="49"/>
     </row>
     <row r="43" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A43" s="5" t="str">
+      <c r="A43" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>1021004</v>
+      </c>
+      <c r="B43" s="5">
+        <v>102100</v>
+      </c>
+      <c r="C43" s="5">
+        <v>4</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F43" s="5">
+        <v>1</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H43" s="5">
+        <v>2021001</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L43" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="M43" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="N43" s="45">
+        <v>3</v>
+      </c>
+      <c r="O43" s="45">
+        <v>5</v>
+      </c>
+      <c r="Q43" s="18"/>
+      <c r="S43" s="49"/>
+    </row>
+    <row r="44" s="5" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A44" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>1018001</v>
+      </c>
+      <c r="B44" s="5">
+        <v>101800</v>
+      </c>
+      <c r="C44" s="5">
+        <v>1</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F44" s="5">
+        <v>1</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H44" s="5">
+        <v>2018001</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L44" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="M44" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="N44" s="45">
+        <v>4</v>
+      </c>
+      <c r="O44" s="45">
+        <v>6</v>
+      </c>
+      <c r="Q44" s="18"/>
+      <c r="S44" s="49"/>
+    </row>
+    <row r="45" s="5" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A45" s="5" t="str">
         <f t="shared" si="2"/>
         <v>1018002</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B45" s="5">
         <v>101800</v>
       </c>
-      <c r="C43" s="5">
+      <c r="C45" s="5">
         <v>2</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="D45" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="E45" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="F43" s="5">
-        <v>1</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H43" s="5">
+      <c r="F45" s="5">
+        <v>1</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H45" s="5">
         <v>2018002</v>
       </c>
-      <c r="I43" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L43" s="46">
+      <c r="I45" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45" s="46">
         <v>10180031</v>
       </c>
-      <c r="M43" s="5" t="s">
+      <c r="M45" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N43" s="45">
+      <c r="N45" s="45">
         <v>4</v>
       </c>
-      <c r="O43" s="45">
+      <c r="O45" s="45">
         <v>6</v>
       </c>
     </row>
-    <row r="44" ht="16.5" spans="1:19">
-      <c r="A44" s="5" t="str">
+    <row r="46" ht="16.5" spans="1:19">
+      <c r="A46" s="5" t="str">
         <f t="shared" si="2"/>
         <v>1018003</v>
       </c>
-      <c r="B44" s="5">
+      <c r="B46" s="5">
         <v>101800</v>
       </c>
-      <c r="C44" s="5">
-        <v>3</v>
-      </c>
-      <c r="D44" s="5" t="s">
+      <c r="C46" s="5">
+        <v>3</v>
+      </c>
+      <c r="D46" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="E46" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F44" s="5">
-        <v>1</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H44" s="5">
+      <c r="F46" s="5">
+        <v>1</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H46" s="5">
         <v>2018001</v>
       </c>
-      <c r="I44" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L44" s="46" t="s">
+      <c r="I46" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L46" s="46" t="s">
         <v>99</v>
       </c>
-      <c r="M44" s="5" t="s">
+      <c r="M46" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N44" s="45">
+      <c r="N46" s="45">
         <v>4</v>
       </c>
-      <c r="O44" s="45">
+      <c r="O46" s="45">
         <v>6</v>
       </c>
-    </row>
-    <row r="45" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A45" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>1025001</v>
-      </c>
-      <c r="B45" s="5">
-        <v>102500</v>
-      </c>
-      <c r="C45" s="5">
-        <v>1</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F45" s="5">
-        <v>1</v>
-      </c>
-      <c r="G45" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H45" s="5">
-        <v>2025001</v>
-      </c>
-      <c r="I45" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L45" s="46" t="s">
-        <v>101</v>
-      </c>
-      <c r="M45" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="N45" s="45">
-        <v>3</v>
-      </c>
-      <c r="O45" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q45" s="8"/>
-    </row>
-    <row r="46" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A46" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>1025002</v>
-      </c>
-      <c r="B46" s="5">
-        <v>102500</v>
-      </c>
-      <c r="C46" s="5">
-        <v>2</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F46" s="5">
-        <v>1</v>
-      </c>
-      <c r="G46" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H46" s="5">
-        <v>2025001</v>
-      </c>
-      <c r="I46" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L46" s="46">
-        <v>10250031</v>
-      </c>
-      <c r="M46" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="N46" s="45">
-        <v>3</v>
-      </c>
-      <c r="O46" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q46" s="8"/>
     </row>
     <row r="47" customFormat="1" ht="16.5" spans="1:19">
       <c r="A47" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>1025003</v>
+        <v>1025001</v>
       </c>
       <c r="B47" s="5">
         <v>102500</v>
       </c>
       <c r="C47" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>100</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="F47" s="5">
         <v>1</v>
@@ -3868,10 +3872,10 @@
         <v>24</v>
       </c>
       <c r="L47" s="46" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M47" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="N47" s="45">
         <v>3</v>
@@ -3884,19 +3888,19 @@
     <row r="48" customFormat="1" ht="16.5" spans="1:19">
       <c r="A48" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>1023001</v>
+        <v>1025002</v>
       </c>
       <c r="B48" s="5">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C48" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="F48" s="5">
         <v>1</v>
@@ -3905,19 +3909,19 @@
         <v>23</v>
       </c>
       <c r="H48" s="5">
-        <v>2023001</v>
+        <v>2025001</v>
       </c>
       <c r="I48" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L48" s="46" t="s">
-        <v>105</v>
+      <c r="L48" s="46">
+        <v>10250031</v>
       </c>
       <c r="M48" s="5" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="N48" s="45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O48" s="45">
         <v>5</v>
@@ -3927,19 +3931,19 @@
     <row r="49" customFormat="1" ht="16.5" spans="1:17">
       <c r="A49" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>1023002</v>
+        <v>1025003</v>
       </c>
       <c r="B49" s="5">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C49" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="F49" s="5">
         <v>1</v>
@@ -3948,19 +3952,19 @@
         <v>23</v>
       </c>
       <c r="H49" s="5">
-        <v>2023001</v>
+        <v>2025001</v>
       </c>
       <c r="I49" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L49" s="46">
-        <v>10230003</v>
+      <c r="L49" s="46" t="s">
+        <v>103</v>
       </c>
       <c r="M49" s="5" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="N49" s="45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O49" s="45">
         <v>5</v>
@@ -3970,19 +3974,19 @@
     <row r="50" customFormat="1" ht="16.5" spans="1:17">
       <c r="A50" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>1023003</v>
+        <v>1023001</v>
       </c>
       <c r="B50" s="5">
         <v>102300</v>
       </c>
       <c r="C50" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>104</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="F50" s="5">
         <v>1</v>
@@ -3997,10 +4001,10 @@
         <v>24</v>
       </c>
       <c r="L50" s="46" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M50" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="N50" s="45">
         <v>4</v>
@@ -4013,19 +4017,19 @@
     <row r="51" customFormat="1" ht="16.5" spans="1:17">
       <c r="A51" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>1034001</v>
+        <v>1023002</v>
       </c>
       <c r="B51" s="5">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C51" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="F51" s="5">
         <v>1</v>
@@ -4034,41 +4038,41 @@
         <v>23</v>
       </c>
       <c r="H51" s="5">
-        <v>2034001</v>
+        <v>2023001</v>
       </c>
       <c r="I51" s="5" t="s">
         <v>24</v>
       </c>
       <c r="L51" s="46">
-        <v>10340007</v>
+        <v>10230003</v>
       </c>
       <c r="M51" s="5" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="N51" s="45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O51" s="45">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q51" s="8"/>
     </row>
     <row r="52" customFormat="1" ht="16.5" spans="1:17">
       <c r="A52" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>1034002</v>
+        <v>1023003</v>
       </c>
       <c r="B52" s="5">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C52" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="F52" s="5">
         <v>1</v>
@@ -4077,40 +4081,43 @@
         <v>23</v>
       </c>
       <c r="H52" s="5">
-        <v>2034001</v>
+        <v>2023001</v>
       </c>
       <c r="I52" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L52" s="46"/>
-      <c r="M52" s="5"/>
+      <c r="L52" s="46" t="s">
+        <v>106</v>
+      </c>
+      <c r="M52" s="5" t="s">
+        <v>83</v>
+      </c>
       <c r="N52" s="45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O52" s="45">
-        <v>3</v>
-      </c>
-      <c r="P52" s="50"/>
+        <v>5</v>
+      </c>
       <c r="Q52" s="8"/>
     </row>
-    <row r="53" s="6" customFormat="1" ht="16.5" spans="1:17">
+    <row r="53" customFormat="1" ht="16.5" spans="1:17">
       <c r="A53" s="5" t="str">
-        <f>B53&amp;C53</f>
-        <v>1034003</v>
+        <f t="shared" si="2"/>
+        <v>1034001</v>
       </c>
       <c r="B53" s="5">
         <v>103400</v>
       </c>
       <c r="C53" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>107</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F53" s="51">
+        <v>22</v>
+      </c>
+      <c r="F53" s="5">
         <v>1</v>
       </c>
       <c r="G53" s="5" t="s">
@@ -4122,136 +4129,133 @@
       <c r="I53" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L53" s="48"/>
-      <c r="M53" s="51"/>
+      <c r="L53" s="46">
+        <v>10340007</v>
+      </c>
+      <c r="M53" s="5" t="s">
+        <v>108</v>
+      </c>
       <c r="N53" s="45">
         <v>3</v>
       </c>
       <c r="O53" s="45">
         <v>3</v>
       </c>
-      <c r="Q53" s="52"/>
-    </row>
-    <row r="54" s="6" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A54" s="51" t="str">
-        <f>B54&amp;C54</f>
+      <c r="Q53" s="8"/>
+    </row>
+    <row r="54" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A54" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>1034002</v>
+      </c>
+      <c r="B54" s="5">
+        <v>103400</v>
+      </c>
+      <c r="C54" s="5">
+        <v>2</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F54" s="5">
+        <v>1</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H54" s="5">
+        <v>2034001</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L54" s="46"/>
+      <c r="M54" s="5"/>
+      <c r="N54" s="45">
+        <v>3</v>
+      </c>
+      <c r="O54" s="45">
+        <v>3</v>
+      </c>
+      <c r="P54" s="50"/>
+      <c r="Q54" s="8"/>
+    </row>
+    <row r="55" s="6" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A55" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>1034003</v>
+      </c>
+      <c r="B55" s="5">
+        <v>103400</v>
+      </c>
+      <c r="C55" s="5">
+        <v>3</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F55" s="51">
+        <v>1</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H55" s="5">
+        <v>2034001</v>
+      </c>
+      <c r="I55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L55" s="48"/>
+      <c r="M55" s="51"/>
+      <c r="N55" s="45">
+        <v>3</v>
+      </c>
+      <c r="O55" s="45">
+        <v>3</v>
+      </c>
+      <c r="Q55" s="52"/>
+    </row>
+    <row r="56" s="6" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A56" s="51" t="str">
+        <f t="shared" si="2"/>
         <v>1035001</v>
       </c>
-      <c r="B54" s="51">
+      <c r="B56" s="51">
         <v>103500</v>
       </c>
-      <c r="C54" s="51">
-        <v>1</v>
-      </c>
-      <c r="D54" s="51" t="s">
+      <c r="C56" s="51">
+        <v>1</v>
+      </c>
+      <c r="D56" s="51" t="s">
         <v>110</v>
       </c>
-      <c r="E54" s="51" t="s">
+      <c r="E56" s="51" t="s">
         <v>111</v>
       </c>
-      <c r="F54" s="51">
-        <v>1</v>
-      </c>
-      <c r="G54" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="H54" s="51">
+      <c r="F56" s="51">
+        <v>1</v>
+      </c>
+      <c r="G56" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="H56" s="51">
         <v>2035001</v>
       </c>
-      <c r="I54" s="51" t="s">
-        <v>24</v>
-      </c>
-      <c r="L54" s="48" t="s">
+      <c r="I56" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="L56" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="M54" s="51" t="s">
+      <c r="M56" s="51" t="s">
         <v>113</v>
-      </c>
-      <c r="N54" s="45">
-        <v>4</v>
-      </c>
-      <c r="O54" s="45">
-        <v>3</v>
-      </c>
-      <c r="Q54" s="52"/>
-    </row>
-    <row r="55" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A55" s="5" t="str">
-        <f t="shared" ref="A54:A62" si="3">B55&amp;C55</f>
-        <v>1035002</v>
-      </c>
-      <c r="B55" s="5">
-        <v>103500</v>
-      </c>
-      <c r="C55" s="5">
-        <v>2</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="F55" s="5">
-        <v>1</v>
-      </c>
-      <c r="G55" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H55" s="5">
-        <v>2035002</v>
-      </c>
-      <c r="I55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L55" s="46" t="s">
-        <v>115</v>
-      </c>
-      <c r="M55" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="N55" s="45">
-        <v>4</v>
-      </c>
-      <c r="O55" s="45">
-        <v>3</v>
-      </c>
-      <c r="Q55" s="8"/>
-    </row>
-    <row r="56" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A56" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>1035003</v>
-      </c>
-      <c r="B56" s="5">
-        <v>103500</v>
-      </c>
-      <c r="C56" s="5">
-        <v>3</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F56" s="5">
-        <v>1</v>
-      </c>
-      <c r="G56" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H56" s="5">
-        <v>2035001</v>
-      </c>
-      <c r="I56" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L56" s="46" t="s">
-        <v>117</v>
-      </c>
-      <c r="M56" s="5" t="s">
-        <v>118</v>
       </c>
       <c r="N56" s="45">
         <v>4</v>
@@ -4259,23 +4263,24 @@
       <c r="O56" s="45">
         <v>3</v>
       </c>
-      <c r="Q56" s="8"/>
+      <c r="Q56" s="52"/>
     </row>
     <row r="57" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A57" s="53">
-        <v>1035011</v>
+      <c r="A57" s="5" t="str">
+        <f t="shared" ref="A56:A64" si="3">B57&amp;C57</f>
+        <v>1035002</v>
       </c>
       <c r="B57" s="5">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C57" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F57" s="5">
         <v>1</v>
@@ -4284,16 +4289,16 @@
         <v>23</v>
       </c>
       <c r="H57" s="5">
-        <v>2035011</v>
+        <v>2035002</v>
       </c>
       <c r="I57" s="5" t="s">
         <v>24</v>
       </c>
       <c r="L57" s="46" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="M57" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="N57" s="45">
         <v>4</v>
@@ -4306,19 +4311,19 @@
     <row r="58" customFormat="1" ht="16.5" spans="1:17">
       <c r="A58" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>1035012</v>
+        <v>1035003</v>
       </c>
       <c r="B58" s="5">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C58" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="F58" s="5">
         <v>1</v>
@@ -4327,16 +4332,16 @@
         <v>23</v>
       </c>
       <c r="H58" s="5">
-        <v>2035012</v>
+        <v>2035001</v>
       </c>
       <c r="I58" s="5" t="s">
         <v>24</v>
       </c>
       <c r="L58" s="46" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="M58" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N58" s="45">
         <v>4</v>
@@ -4347,21 +4352,20 @@
       <c r="Q58" s="8"/>
     </row>
     <row r="59" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A59" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>1035013</v>
+      <c r="A59" s="53">
+        <v>1035011</v>
       </c>
       <c r="B59" s="5">
         <v>103501</v>
       </c>
       <c r="C59" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>119</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="F59" s="5">
         <v>1</v>
@@ -4376,10 +4380,10 @@
         <v>24</v>
       </c>
       <c r="L59" s="46" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M59" s="5" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="N59" s="45">
         <v>4</v>
@@ -4392,19 +4396,19 @@
     <row r="60" customFormat="1" ht="16.5" spans="1:17">
       <c r="A60" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>1036001</v>
+        <v>1035012</v>
       </c>
       <c r="B60" s="5">
-        <v>103600</v>
+        <v>103501</v>
       </c>
       <c r="C60" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F60" s="5">
         <v>1</v>
@@ -4413,19 +4417,19 @@
         <v>23</v>
       </c>
       <c r="H60" s="5">
-        <v>2036001</v>
+        <v>2035012</v>
       </c>
       <c r="I60" s="5" t="s">
         <v>24</v>
       </c>
       <c r="L60" s="46" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="M60" s="5" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="N60" s="45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O60" s="45">
         <v>3</v>
@@ -4435,19 +4439,19 @@
     <row r="61" customFormat="1" ht="16.5" spans="1:17">
       <c r="A61" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>1036002</v>
+        <v>1035013</v>
       </c>
       <c r="B61" s="5">
-        <v>103600</v>
+        <v>103501</v>
       </c>
       <c r="C61" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="F61" s="5">
         <v>1</v>
@@ -4456,19 +4460,19 @@
         <v>23</v>
       </c>
       <c r="H61" s="5">
-        <v>2036002</v>
+        <v>2035011</v>
       </c>
       <c r="I61" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L61" s="46">
-        <v>10360004</v>
+      <c r="L61" s="46" t="s">
+        <v>122</v>
       </c>
       <c r="M61" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N61" s="45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O61" s="45">
         <v>3</v>
@@ -4478,19 +4482,19 @@
     <row r="62" customFormat="1" ht="16.5" spans="1:17">
       <c r="A62" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>1036003</v>
+        <v>1036001</v>
       </c>
       <c r="B62" s="5">
         <v>103600</v>
       </c>
       <c r="C62" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>123</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="F62" s="5">
         <v>1</v>
@@ -4504,50 +4508,104 @@
       <c r="I62" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L62" s="46">
+      <c r="L62" s="46" t="s">
+        <v>124</v>
+      </c>
+      <c r="M62" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="N62" s="45">
+        <v>3</v>
+      </c>
+      <c r="O62" s="45">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="8"/>
+    </row>
+    <row r="63" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A63" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1036002</v>
+      </c>
+      <c r="B63" s="5">
+        <v>103600</v>
+      </c>
+      <c r="C63" s="5">
+        <v>2</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F63" s="5">
+        <v>1</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H63" s="5">
+        <v>2036002</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L63" s="46">
+        <v>10360004</v>
+      </c>
+      <c r="M63" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="N63" s="45">
+        <v>3</v>
+      </c>
+      <c r="O63" s="45">
+        <v>3</v>
+      </c>
+      <c r="Q63" s="8"/>
+    </row>
+    <row r="64" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A64" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1036003</v>
+      </c>
+      <c r="B64" s="5">
+        <v>103600</v>
+      </c>
+      <c r="C64" s="5">
+        <v>3</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F64" s="5">
+        <v>1</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H64" s="5">
+        <v>2036001</v>
+      </c>
+      <c r="I64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L64" s="46">
         <v>10360002</v>
       </c>
-      <c r="M62" s="5" t="s">
+      <c r="M64" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="N62" s="45">
-        <v>3</v>
-      </c>
-      <c r="O62" s="45">
-        <v>3</v>
-      </c>
-      <c r="Q62" s="8"/>
-    </row>
-    <row r="63" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A63" s="5"/>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
-      <c r="H63" s="5"/>
-      <c r="I63" s="5"/>
-      <c r="L63" s="46"/>
-      <c r="M63" s="5"/>
-      <c r="N63" s="45"/>
-      <c r="O63" s="45"/>
-      <c r="Q63" s="8"/>
-    </row>
-    <row r="64" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A64" s="5"/>
-      <c r="B64" s="5"/>
-      <c r="C64" s="5"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
-      <c r="G64" s="5"/>
-      <c r="H64" s="5"/>
-      <c r="I64" s="5"/>
-      <c r="L64" s="46"/>
-      <c r="M64" s="5"/>
-      <c r="N64" s="45"/>
-      <c r="O64" s="45"/>
+      <c r="N64" s="45">
+        <v>3</v>
+      </c>
+      <c r="O64" s="45">
+        <v>3</v>
+      </c>
       <c r="Q64" s="8"/>
     </row>
     <row r="65" customFormat="1" ht="16.5" spans="1:17">
@@ -4709,6 +4767,38 @@
       <c r="N74" s="45"/>
       <c r="O74" s="45"/>
       <c r="Q74" s="8"/>
+    </row>
+    <row r="75" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A75" s="5"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="5"/>
+      <c r="E75" s="5"/>
+      <c r="F75" s="5"/>
+      <c r="G75" s="5"/>
+      <c r="H75" s="5"/>
+      <c r="I75" s="5"/>
+      <c r="L75" s="46"/>
+      <c r="M75" s="5"/>
+      <c r="N75" s="45"/>
+      <c r="O75" s="45"/>
+      <c r="Q75" s="8"/>
+    </row>
+    <row r="76" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A76" s="5"/>
+      <c r="B76" s="5"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="5"/>
+      <c r="E76" s="5"/>
+      <c r="F76" s="5"/>
+      <c r="G76" s="5"/>
+      <c r="H76" s="5"/>
+      <c r="I76" s="5"/>
+      <c r="L76" s="46"/>
+      <c r="M76" s="5"/>
+      <c r="N76" s="45"/>
+      <c r="O76" s="45"/>
+      <c r="Q76" s="8"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:K2">

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="213">
   <si>
     <t>id</t>
   </si>
@@ -753,6 +753,18 @@
   </si>
   <si>
     <t>改出22符号</t>
+  </si>
+  <si>
+    <t>寻宝黄金城</t>
+  </si>
+  <si>
+    <t>10260001|10260004|10260005|10260006|10260007</t>
+  </si>
+  <si>
+    <t>概率改出百搭wild符号+概率改出scatter符号+概率改出占据2、3、4个格子符号</t>
+  </si>
+  <si>
+    <t>10260003|10260008</t>
   </si>
 </sst>
 </file>
@@ -1483,7 +1495,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1610,6 +1622,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -6627,18 +6642,132 @@
       <c r="Q105" s="19"/>
     </row>
     <row r="106" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="N106" s="46"/>
-      <c r="O106" s="46"/>
+      <c r="A106" s="5" t="str">
+        <f>B106&amp;C106</f>
+        <v>1026001</v>
+      </c>
+      <c r="B106" s="5">
+        <v>102600</v>
+      </c>
+      <c r="C106" s="5">
+        <v>1</v>
+      </c>
+      <c r="D106" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="E106" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F106" s="5">
+        <v>1</v>
+      </c>
+      <c r="G106" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H106" s="5">
+        <v>2026001</v>
+      </c>
+      <c r="I106" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L106" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="M106" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="N106" s="46">
+        <v>6</v>
+      </c>
+      <c r="O106" s="46">
+        <v>5</v>
+      </c>
       <c r="Q106" s="19"/>
     </row>
     <row r="107" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="N107" s="46"/>
-      <c r="O107" s="46"/>
+      <c r="A107" s="5" t="str">
+        <f>B107&amp;C107</f>
+        <v>1026002</v>
+      </c>
+      <c r="B107" s="5">
+        <v>102600</v>
+      </c>
+      <c r="C107" s="5">
+        <v>2</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="E107" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F107" s="5">
+        <v>1</v>
+      </c>
+      <c r="G107" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H107" s="5">
+        <v>2026001</v>
+      </c>
+      <c r="I107" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L107" s="60">
+        <v>10260002</v>
+      </c>
+      <c r="M107" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="N107" s="46">
+        <v>6</v>
+      </c>
+      <c r="O107" s="46">
+        <v>5</v>
+      </c>
       <c r="Q107" s="19"/>
     </row>
     <row r="108" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="N108" s="46"/>
-      <c r="O108" s="46"/>
+      <c r="A108" s="5" t="str">
+        <f>B108&amp;C108</f>
+        <v>1026003</v>
+      </c>
+      <c r="B108" s="5">
+        <v>102600</v>
+      </c>
+      <c r="C108" s="5">
+        <v>3</v>
+      </c>
+      <c r="D108" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="E108" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F108" s="5">
+        <v>1</v>
+      </c>
+      <c r="G108" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H108" s="5">
+        <v>2026001</v>
+      </c>
+      <c r="I108" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L108" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="M108" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="N108" s="46">
+        <v>6</v>
+      </c>
+      <c r="O108" s="46">
+        <v>5</v>
+      </c>
       <c r="Q108" s="19"/>
     </row>
     <row r="109" s="5" customFormat="1" ht="16.5" spans="1:17">

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="128">
   <si>
     <t>id</t>
   </si>
@@ -1882,7 +1882,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S76"/>
+  <dimension ref="A1:S74"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
@@ -2030,7 +2030,7 @@
     </row>
     <row r="5" s="1" customFormat="1" ht="16.5" spans="1:17">
       <c r="A5" s="24" t="str">
-        <f t="shared" ref="A5:A15" si="0">B5&amp;C5</f>
+        <f t="shared" ref="A5:A21" si="0">B5&amp;C5</f>
         <v>1001001</v>
       </c>
       <c r="B5" s="25">
@@ -2461,7 +2461,7 @@
     </row>
     <row r="15" s="3" customFormat="1" ht="16.5" spans="1:17">
       <c r="A15" s="37" t="str">
-        <f>B15&amp;C15</f>
+        <f t="shared" si="0"/>
         <v>1007001</v>
       </c>
       <c r="B15" s="38">
@@ -2505,7 +2505,7 @@
     </row>
     <row r="16" s="3" customFormat="1" ht="16.5" spans="1:17">
       <c r="A16" s="37" t="str">
-        <f>B16&amp;C16</f>
+        <f t="shared" si="0"/>
         <v>1007002</v>
       </c>
       <c r="B16" s="38">
@@ -2547,7 +2547,7 @@
     </row>
     <row r="17" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A17" s="40" t="str">
-        <f>B17&amp;C17</f>
+        <f t="shared" si="0"/>
         <v>1012001</v>
       </c>
       <c r="B17" s="41">
@@ -2592,7 +2592,7 @@
     </row>
     <row r="18" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A18" s="40" t="str">
-        <f>B18&amp;C18</f>
+        <f t="shared" si="0"/>
         <v>1012002</v>
       </c>
       <c r="B18" s="41">
@@ -2635,7 +2635,7 @@
     </row>
     <row r="19" s="4" customFormat="1" ht="16.5" spans="1:17">
       <c r="A19" s="40" t="str">
-        <f>B19&amp;C19</f>
+        <f t="shared" si="0"/>
         <v>1012003</v>
       </c>
       <c r="B19" s="41">
@@ -2678,112 +2678,112 @@
       </c>
       <c r="Q19" s="43"/>
     </row>
-    <row r="20" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A20" s="40" t="str">
-        <f>B20&amp;C20</f>
-        <v>1012004</v>
-      </c>
-      <c r="B20" s="41">
-        <v>101200</v>
-      </c>
-      <c r="C20" s="41">
+    <row r="20" s="3" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A20" s="34" t="str">
+        <f t="shared" ref="A20:A30" si="1">B20&amp;C20</f>
+        <v>1014001</v>
+      </c>
+      <c r="B20" s="26">
+        <v>101400</v>
+      </c>
+      <c r="C20" s="26">
+        <v>1</v>
+      </c>
+      <c r="D20" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="26">
+        <v>1</v>
+      </c>
+      <c r="G20" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="34">
+        <v>2014001</v>
+      </c>
+      <c r="I20" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="J20" s="34"/>
+      <c r="K20" s="34"/>
+      <c r="L20" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="M20" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="N20" s="17">
         <v>4</v>
       </c>
-      <c r="D20" s="41"/>
-      <c r="E20" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="F20" s="41">
-        <v>1</v>
-      </c>
-      <c r="G20" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="H20" s="40">
-        <v>2012001</v>
-      </c>
-      <c r="I20" s="40" t="s">
-        <v>24</v>
-      </c>
-      <c r="J20" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="K20" s="40" t="s">
-        <v>63</v>
-      </c>
-      <c r="L20" s="42"/>
-      <c r="M20" s="40" t="s">
-        <v>64</v>
-      </c>
-      <c r="N20" s="41">
-        <v>3</v>
-      </c>
-      <c r="O20" s="41">
-        <v>5</v>
-      </c>
-      <c r="Q20" s="43"/>
-    </row>
-    <row r="21" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A21" s="40" t="str">
-        <f>B21&amp;C21</f>
-        <v>1012005</v>
-      </c>
-      <c r="B21" s="41">
-        <v>101200</v>
-      </c>
-      <c r="C21" s="41">
-        <v>5</v>
-      </c>
-      <c r="D21" s="41"/>
-      <c r="E21" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="F21" s="41">
-        <v>1</v>
-      </c>
-      <c r="G21" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="H21" s="40">
-        <v>2012001</v>
-      </c>
-      <c r="I21" s="40" t="s">
-        <v>24</v>
-      </c>
-      <c r="J21" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="K21" s="40" t="s">
-        <v>63</v>
-      </c>
-      <c r="L21" s="42"/>
-      <c r="M21" s="40" t="s">
-        <v>64</v>
-      </c>
-      <c r="N21" s="41">
-        <v>3</v>
-      </c>
-      <c r="O21" s="41">
-        <v>5</v>
-      </c>
-      <c r="Q21" s="43"/>
+      <c r="O20" s="17">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="44"/>
+    </row>
+    <row r="21" s="3" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A21" s="34" t="str">
+        <f t="shared" si="1"/>
+        <v>1014002</v>
+      </c>
+      <c r="B21" s="26">
+        <v>101400</v>
+      </c>
+      <c r="C21" s="26">
+        <v>2</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="E21" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="26">
+        <v>1</v>
+      </c>
+      <c r="G21" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="34">
+        <v>2014001</v>
+      </c>
+      <c r="I21" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="J21" s="34"/>
+      <c r="K21" s="34"/>
+      <c r="L21" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="M21" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="N21" s="17">
+        <v>4</v>
+      </c>
+      <c r="O21" s="17">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="44"/>
     </row>
     <row r="22" s="3" customFormat="1" ht="16.5" spans="1:17">
       <c r="A22" s="34" t="str">
-        <f t="shared" ref="A22:A32" si="1">B22&amp;C22</f>
-        <v>1014001</v>
+        <f t="shared" si="1"/>
+        <v>1014003</v>
       </c>
       <c r="B22" s="26">
         <v>101400</v>
       </c>
       <c r="C22" s="26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22" s="26" t="s">
         <v>65</v>
       </c>
       <c r="E22" s="26" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="F22" s="26">
         <v>1</v>
@@ -2799,11 +2799,11 @@
       </c>
       <c r="J22" s="34"/>
       <c r="K22" s="34"/>
-      <c r="L22" s="35" t="s">
-        <v>66</v>
+      <c r="L22" s="35">
+        <v>10140021</v>
       </c>
       <c r="M22" s="34" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="N22" s="17">
         <v>4</v>
@@ -2813,112 +2813,106 @@
       </c>
       <c r="Q22" s="44"/>
     </row>
-    <row r="23" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A23" s="34" t="str">
+    <row r="23" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A23" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>1014002</v>
-      </c>
-      <c r="B23" s="26">
-        <v>101400</v>
-      </c>
-      <c r="C23" s="26">
-        <v>2</v>
-      </c>
-      <c r="D23" s="26" t="s">
-        <v>65</v>
+        <v>1024001</v>
+      </c>
+      <c r="B23" s="25">
+        <v>102400</v>
+      </c>
+      <c r="C23" s="25">
+        <v>1</v>
+      </c>
+      <c r="D23" s="25" t="s">
+        <v>72</v>
       </c>
       <c r="E23" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="F23" s="26">
-        <v>1</v>
-      </c>
-      <c r="G23" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="H23" s="34">
-        <v>2014001</v>
-      </c>
-      <c r="I23" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="J23" s="34"/>
-      <c r="K23" s="34"/>
-      <c r="L23" s="35" t="s">
-        <v>68</v>
-      </c>
-      <c r="M23" s="34" t="s">
-        <v>69</v>
+      <c r="F23" s="25">
+        <v>1</v>
+      </c>
+      <c r="G23" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="24">
+        <v>2024001</v>
+      </c>
+      <c r="I23" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="M23" s="24" t="s">
+        <v>26</v>
       </c>
       <c r="N23" s="17">
         <v>4</v>
       </c>
       <c r="O23" s="17">
-        <v>3</v>
-      </c>
-      <c r="Q23" s="44"/>
-    </row>
-    <row r="24" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A24" s="34" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A24" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>1014003</v>
-      </c>
-      <c r="B24" s="26">
-        <v>101400</v>
-      </c>
-      <c r="C24" s="26">
-        <v>3</v>
-      </c>
-      <c r="D24" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="F24" s="26">
-        <v>1</v>
-      </c>
-      <c r="G24" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="H24" s="34">
-        <v>2014001</v>
-      </c>
-      <c r="I24" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="J24" s="34"/>
-      <c r="K24" s="34"/>
-      <c r="L24" s="35">
-        <v>10140021</v>
-      </c>
-      <c r="M24" s="34" t="s">
-        <v>71</v>
+        <v>1024002</v>
+      </c>
+      <c r="B24" s="25">
+        <v>102400</v>
+      </c>
+      <c r="C24" s="25">
+        <v>2</v>
+      </c>
+      <c r="D24" s="25"/>
+      <c r="E24" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" s="25">
+        <v>1</v>
+      </c>
+      <c r="G24" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" s="24">
+        <v>2024001</v>
+      </c>
+      <c r="I24" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="J24" s="24"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="M24" s="24" t="s">
+        <v>29</v>
       </c>
       <c r="N24" s="17">
         <v>4</v>
       </c>
       <c r="O24" s="17">
-        <v>3</v>
-      </c>
-      <c r="Q24" s="44"/>
+        <v>5</v>
+      </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="16.5" spans="1:17">
       <c r="A25" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>1024001</v>
+        <v>1024003</v>
       </c>
       <c r="B25" s="25">
         <v>102400</v>
       </c>
       <c r="C25" s="25">
-        <v>1</v>
-      </c>
-      <c r="D25" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="E25" s="26" t="s">
-        <v>22</v>
+        <v>3</v>
+      </c>
+      <c r="D25" s="25"/>
+      <c r="E25" s="30" t="s">
+        <v>30</v>
       </c>
       <c r="F25" s="25">
         <v>1</v>
@@ -2935,10 +2929,10 @@
       <c r="J25" s="24"/>
       <c r="K25" s="24"/>
       <c r="L25" s="27" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M25" s="24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N25" s="17">
         <v>4</v>
@@ -2950,19 +2944,19 @@
     <row r="26" s="1" customFormat="1" ht="16.5" spans="1:17">
       <c r="A26" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>1024002</v>
+        <v>1024004</v>
       </c>
       <c r="B26" s="25">
         <v>102400</v>
       </c>
       <c r="C26" s="25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D26" s="25"/>
-      <c r="E26" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="F26" s="25">
+      <c r="E26" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="F26" s="32">
         <v>1</v>
       </c>
       <c r="G26" s="24" t="s">
@@ -2976,11 +2970,11 @@
       </c>
       <c r="J26" s="24"/>
       <c r="K26" s="24"/>
-      <c r="L26" s="29" t="s">
-        <v>74</v>
+      <c r="L26" s="27">
+        <v>10240041</v>
       </c>
       <c r="M26" s="24" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="N26" s="17">
         <v>4</v>
@@ -2992,19 +2986,19 @@
     <row r="27" s="1" customFormat="1" ht="16.5" spans="1:17">
       <c r="A27" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>1024003</v>
+        <v>1024005</v>
       </c>
       <c r="B27" s="25">
         <v>102400</v>
       </c>
       <c r="C27" s="25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D27" s="25"/>
-      <c r="E27" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="F27" s="25">
+      <c r="E27" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="F27" s="32">
         <v>1</v>
       </c>
       <c r="G27" s="24" t="s">
@@ -3019,10 +3013,10 @@
       <c r="J27" s="24"/>
       <c r="K27" s="24"/>
       <c r="L27" s="27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M27" s="24" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="N27" s="17">
         <v>4</v>
@@ -3034,17 +3028,17 @@
     <row r="28" s="1" customFormat="1" ht="16.5" spans="1:17">
       <c r="A28" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>1024004</v>
+        <v>1024006</v>
       </c>
       <c r="B28" s="25">
         <v>102400</v>
       </c>
       <c r="C28" s="25">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D28" s="25"/>
-      <c r="E28" s="31" t="s">
-        <v>33</v>
+      <c r="E28" s="33" t="s">
+        <v>38</v>
       </c>
       <c r="F28" s="32">
         <v>1</v>
@@ -3061,10 +3055,10 @@
       <c r="J28" s="24"/>
       <c r="K28" s="24"/>
       <c r="L28" s="27">
-        <v>10240041</v>
+        <v>10240061</v>
       </c>
       <c r="M28" s="24" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="N28" s="17">
         <v>4</v>
@@ -3076,19 +3070,19 @@
     <row r="29" s="1" customFormat="1" ht="16.5" spans="1:17">
       <c r="A29" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>1024005</v>
+        <v>1024007</v>
       </c>
       <c r="B29" s="25">
         <v>102400</v>
       </c>
       <c r="C29" s="25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D29" s="25"/>
-      <c r="E29" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="F29" s="32">
+      <c r="E29" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="F29" s="25">
         <v>1</v>
       </c>
       <c r="G29" s="24" t="s">
@@ -3102,11 +3096,11 @@
       </c>
       <c r="J29" s="24"/>
       <c r="K29" s="24"/>
-      <c r="L29" s="27" t="s">
-        <v>76</v>
+      <c r="L29" s="29" t="s">
+        <v>77</v>
       </c>
       <c r="M29" s="24" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="N29" s="17">
         <v>4</v>
@@ -3115,106 +3109,108 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" ht="16.5" spans="1:17">
+    <row r="30" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A30" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>1024006</v>
-      </c>
-      <c r="B30" s="25">
-        <v>102400</v>
-      </c>
-      <c r="C30" s="25">
-        <v>6</v>
-      </c>
-      <c r="D30" s="25"/>
-      <c r="E30" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="F30" s="32">
-        <v>1</v>
-      </c>
-      <c r="G30" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H30" s="24">
-        <v>2024001</v>
-      </c>
-      <c r="I30" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="J30" s="24"/>
-      <c r="K30" s="24"/>
-      <c r="L30" s="27">
-        <v>10240061</v>
-      </c>
-      <c r="M30" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="N30" s="17">
+        <v>1017001</v>
+      </c>
+      <c r="B30" s="5">
+        <v>101700</v>
+      </c>
+      <c r="C30" s="5">
+        <v>1</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F30" s="5">
+        <v>1</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H30" s="5">
+        <v>2017001</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="M30" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="N30" s="45">
         <v>4</v>
       </c>
-      <c r="O30" s="17">
+      <c r="O30" s="45">
         <v>5</v>
       </c>
-    </row>
-    <row r="31" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="Q30" s="18"/>
+    </row>
+    <row r="31" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A31" s="24" t="str">
-        <f t="shared" si="1"/>
-        <v>1024007</v>
-      </c>
-      <c r="B31" s="25">
-        <v>102400</v>
-      </c>
-      <c r="C31" s="25">
-        <v>7</v>
-      </c>
-      <c r="D31" s="25"/>
-      <c r="E31" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="F31" s="25">
-        <v>1</v>
-      </c>
-      <c r="G31" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H31" s="24">
-        <v>2024001</v>
-      </c>
-      <c r="I31" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="J31" s="24"/>
-      <c r="K31" s="24"/>
-      <c r="L31" s="29" t="s">
-        <v>77</v>
-      </c>
-      <c r="M31" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="N31" s="17">
+        <f t="shared" ref="A31:A54" si="2">B31&amp;C31</f>
+        <v>1017002</v>
+      </c>
+      <c r="B31" s="5">
+        <v>101700</v>
+      </c>
+      <c r="C31" s="5">
+        <v>2</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F31" s="5">
+        <v>1</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H31" s="5">
+        <v>2017001</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="M31" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="N31" s="45">
         <v>4</v>
       </c>
-      <c r="O31" s="17">
+      <c r="O31" s="45">
         <v>5</v>
       </c>
+      <c r="Q31" s="18"/>
     </row>
     <row r="32" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A32" s="24" t="str">
-        <f t="shared" si="1"/>
-        <v>1017001</v>
+        <f t="shared" si="2"/>
+        <v>1017003</v>
       </c>
       <c r="B32" s="5">
         <v>101700</v>
       </c>
       <c r="C32" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>78</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="F32" s="5">
         <v>1</v>
@@ -3229,10 +3225,10 @@
         <v>24</v>
       </c>
       <c r="L32" s="5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="M32" s="5" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="N32" s="45">
         <v>4</v>
@@ -3244,20 +3240,20 @@
     </row>
     <row r="33" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A33" s="24" t="str">
-        <f t="shared" ref="A33:A56" si="2">B33&amp;C33</f>
-        <v>1017002</v>
+        <f t="shared" si="2"/>
+        <v>1022001</v>
       </c>
       <c r="B33" s="5">
-        <v>101700</v>
+        <v>102200</v>
       </c>
       <c r="C33" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="F33" s="5">
         <v>1</v>
@@ -3266,19 +3262,19 @@
         <v>23</v>
       </c>
       <c r="H33" s="5">
-        <v>2017001</v>
+        <v>2022001</v>
       </c>
       <c r="I33" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L33" s="5" t="s">
-        <v>80</v>
+      <c r="L33" s="46" t="s">
+        <v>85</v>
       </c>
       <c r="M33" s="5" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="N33" s="45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O33" s="45">
         <v>5</v>
@@ -3288,40 +3284,40 @@
     <row r="34" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A34" s="24" t="str">
         <f t="shared" si="2"/>
-        <v>1017003</v>
+        <v>1022002</v>
       </c>
       <c r="B34" s="5">
-        <v>101700</v>
+        <v>102200</v>
       </c>
       <c r="C34" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F34" s="5">
-        <v>1</v>
-      </c>
-      <c r="G34" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F34" s="17">
+        <v>1</v>
+      </c>
+      <c r="G34" s="47" t="s">
         <v>23</v>
       </c>
       <c r="H34" s="5">
-        <v>2017001</v>
+        <v>2022001</v>
       </c>
       <c r="I34" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L34" s="5" t="s">
-        <v>82</v>
+      <c r="L34" s="46">
+        <v>10220033</v>
       </c>
       <c r="M34" s="5" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="N34" s="45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O34" s="45">
         <v>5</v>
@@ -3331,24 +3327,24 @@
     <row r="35" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A35" s="24" t="str">
         <f t="shared" si="2"/>
-        <v>1022001</v>
+        <v>1022003</v>
       </c>
       <c r="B35" s="5">
         <v>102200</v>
       </c>
       <c r="C35" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>84</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F35" s="5">
-        <v>1</v>
-      </c>
-      <c r="G35" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F35" s="47">
+        <v>1</v>
+      </c>
+      <c r="G35" s="47" t="s">
         <v>23</v>
       </c>
       <c r="H35" s="5">
@@ -3357,11 +3353,11 @@
       <c r="I35" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L35" s="46" t="s">
-        <v>85</v>
+      <c r="L35" s="48" t="s">
+        <v>89</v>
       </c>
       <c r="M35" s="5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="N35" s="45">
         <v>3</v>
@@ -3374,19 +3370,19 @@
     <row r="36" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A36" s="24" t="str">
         <f t="shared" si="2"/>
-        <v>1022002</v>
+        <v>1022004</v>
       </c>
       <c r="B36" s="5">
         <v>102200</v>
       </c>
       <c r="C36" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>84</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F36" s="17">
         <v>1</v>
@@ -3401,10 +3397,7 @@
         <v>24</v>
       </c>
       <c r="L36" s="46">
-        <v>10220033</v>
-      </c>
-      <c r="M36" s="5" t="s">
-        <v>88</v>
+        <v>10220020</v>
       </c>
       <c r="N36" s="45">
         <v>3</v>
@@ -3417,24 +3410,24 @@
     <row r="37" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A37" s="24" t="str">
         <f t="shared" si="2"/>
-        <v>1022003</v>
+        <v>1022005</v>
       </c>
       <c r="B37" s="5">
         <v>102200</v>
       </c>
       <c r="C37" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>84</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F37" s="47">
-        <v>1</v>
-      </c>
-      <c r="G37" s="47" t="s">
+        <v>91</v>
+      </c>
+      <c r="F37" s="5">
+        <v>1</v>
+      </c>
+      <c r="G37" s="5" t="s">
         <v>23</v>
       </c>
       <c r="H37" s="5">
@@ -3443,11 +3436,8 @@
       <c r="I37" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L37" s="48" t="s">
-        <v>89</v>
-      </c>
-      <c r="M37" s="5" t="s">
-        <v>83</v>
+      <c r="L37" s="46">
+        <v>10220019</v>
       </c>
       <c r="N37" s="45">
         <v>3</v>
@@ -3456,38 +3446,42 @@
         <v>5</v>
       </c>
       <c r="Q37" s="18"/>
+      <c r="S37" s="49"/>
     </row>
     <row r="38" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A38" s="24" t="str">
         <f t="shared" si="2"/>
-        <v>1022004</v>
+        <v>1021001</v>
       </c>
       <c r="B38" s="5">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C38" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="F38" s="17">
-        <v>1</v>
-      </c>
-      <c r="G38" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="F38" s="5">
+        <v>1</v>
+      </c>
+      <c r="G38" s="5" t="s">
         <v>23</v>
       </c>
       <c r="H38" s="5">
-        <v>2022001</v>
+        <v>2021001</v>
       </c>
       <c r="I38" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L38" s="46">
-        <v>10220020</v>
+      <c r="L38" s="46" t="s">
+        <v>93</v>
+      </c>
+      <c r="M38" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="N38" s="45">
         <v>3</v>
@@ -3496,23 +3490,24 @@
         <v>5</v>
       </c>
       <c r="Q38" s="18"/>
+      <c r="S38" s="49"/>
     </row>
     <row r="39" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A39" s="24" t="str">
         <f t="shared" si="2"/>
-        <v>1022005</v>
+        <v>1021002</v>
       </c>
       <c r="B39" s="5">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C39" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F39" s="5">
         <v>1</v>
@@ -3521,13 +3516,16 @@
         <v>23</v>
       </c>
       <c r="H39" s="5">
-        <v>2022001</v>
+        <v>2021001</v>
       </c>
       <c r="I39" s="5" t="s">
         <v>24</v>
       </c>
       <c r="L39" s="46">
-        <v>10220019</v>
+        <v>10210031</v>
+      </c>
+      <c r="M39" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="N39" s="45">
         <v>3</v>
@@ -3541,19 +3539,19 @@
     <row r="40" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A40" s="24" t="str">
         <f t="shared" si="2"/>
-        <v>1021001</v>
+        <v>1021003</v>
       </c>
       <c r="B40" s="5">
         <v>102100</v>
       </c>
       <c r="C40" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>92</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="F40" s="5">
         <v>1</v>
@@ -3567,11 +3565,11 @@
       <c r="I40" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L40" s="46" t="s">
-        <v>93</v>
+      <c r="L40" s="46">
+        <v>10210041</v>
       </c>
       <c r="M40" s="5" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="N40" s="45">
         <v>3</v>
@@ -3585,19 +3583,19 @@
     <row r="41" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A41" s="24" t="str">
         <f t="shared" si="2"/>
-        <v>1021002</v>
+        <v>1021004</v>
       </c>
       <c r="B41" s="5">
         <v>102100</v>
       </c>
       <c r="C41" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>92</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F41" s="5">
         <v>1</v>
@@ -3611,11 +3609,11 @@
       <c r="I41" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L41" s="46">
-        <v>10210031</v>
+      <c r="L41" s="46" t="s">
+        <v>96</v>
       </c>
       <c r="M41" s="5" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="N41" s="45">
         <v>3</v>
@@ -3629,19 +3627,19 @@
     <row r="42" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A42" s="24" t="str">
         <f t="shared" si="2"/>
-        <v>1021003</v>
+        <v>1018001</v>
       </c>
       <c r="B42" s="5">
-        <v>102100</v>
+        <v>101800</v>
       </c>
       <c r="C42" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="F42" s="5">
         <v>1</v>
@@ -3650,86 +3648,84 @@
         <v>23</v>
       </c>
       <c r="H42" s="5">
-        <v>2021001</v>
+        <v>2018001</v>
       </c>
       <c r="I42" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L42" s="46">
-        <v>10210041</v>
+      <c r="L42" s="46" t="s">
+        <v>98</v>
       </c>
       <c r="M42" s="5" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="N42" s="45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O42" s="45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q42" s="18"/>
       <c r="S42" s="49"/>
     </row>
     <row r="43" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A43" s="24" t="str">
+      <c r="A43" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>1021004</v>
+        <v>1018002</v>
       </c>
       <c r="B43" s="5">
-        <v>102100</v>
+        <v>101800</v>
       </c>
       <c r="C43" s="5">
+        <v>2</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F43" s="5">
+        <v>1</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H43" s="5">
+        <v>2018002</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L43" s="46">
+        <v>10180031</v>
+      </c>
+      <c r="M43" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="N43" s="45">
         <v>4</v>
       </c>
-      <c r="D43" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F43" s="5">
-        <v>1</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H43" s="5">
-        <v>2021001</v>
-      </c>
-      <c r="I43" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L43" s="46" t="s">
-        <v>96</v>
-      </c>
-      <c r="M43" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="N43" s="45">
-        <v>3</v>
-      </c>
       <c r="O43" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q43" s="18"/>
-      <c r="S43" s="49"/>
-    </row>
-    <row r="44" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A44" s="24" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" ht="16.5" spans="1:19">
+      <c r="A44" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>1018001</v>
+        <v>1018003</v>
       </c>
       <c r="B44" s="5">
         <v>101800</v>
       </c>
       <c r="C44" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="F44" s="5">
         <v>1</v>
@@ -3744,10 +3740,10 @@
         <v>24</v>
       </c>
       <c r="L44" s="46" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M44" s="5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="N44" s="45">
         <v>4</v>
@@ -3755,25 +3751,23 @@
       <c r="O44" s="45">
         <v>6</v>
       </c>
-      <c r="Q44" s="18"/>
-      <c r="S44" s="49"/>
-    </row>
-    <row r="45" s="5" customFormat="1" ht="16.5" spans="1:19">
+    </row>
+    <row r="45" customFormat="1" ht="16.5" spans="1:19">
       <c r="A45" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>1018002</v>
+        <v>1025001</v>
       </c>
       <c r="B45" s="5">
-        <v>101800</v>
+        <v>102500</v>
       </c>
       <c r="C45" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c r="F45" s="5">
         <v>1</v>
@@ -3782,40 +3776,41 @@
         <v>23</v>
       </c>
       <c r="H45" s="5">
-        <v>2018002</v>
+        <v>2025001</v>
       </c>
       <c r="I45" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L45" s="46">
-        <v>10180031</v>
+      <c r="L45" s="46" t="s">
+        <v>101</v>
       </c>
       <c r="M45" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N45" s="45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O45" s="45">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" ht="16.5" spans="1:19">
+        <v>5</v>
+      </c>
+      <c r="Q45" s="8"/>
+    </row>
+    <row r="46" customFormat="1" ht="16.5" spans="1:19">
       <c r="A46" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>1018003</v>
+        <v>1025002</v>
       </c>
       <c r="B46" s="5">
-        <v>101800</v>
+        <v>102500</v>
       </c>
       <c r="C46" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="F46" s="5">
         <v>1</v>
@@ -3824,40 +3819,41 @@
         <v>23</v>
       </c>
       <c r="H46" s="5">
-        <v>2018001</v>
+        <v>2025001</v>
       </c>
       <c r="I46" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L46" s="46" t="s">
-        <v>99</v>
+      <c r="L46" s="46">
+        <v>10250031</v>
       </c>
       <c r="M46" s="5" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="N46" s="45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O46" s="45">
-        <v>6</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="Q46" s="8"/>
     </row>
     <row r="47" customFormat="1" ht="16.5" spans="1:19">
       <c r="A47" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>1025001</v>
+        <v>1025003</v>
       </c>
       <c r="B47" s="5">
         <v>102500</v>
       </c>
       <c r="C47" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>100</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="F47" s="5">
         <v>1</v>
@@ -3872,10 +3868,10 @@
         <v>24</v>
       </c>
       <c r="L47" s="46" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M47" s="5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="N47" s="45">
         <v>3</v>
@@ -3888,19 +3884,19 @@
     <row r="48" customFormat="1" ht="16.5" spans="1:19">
       <c r="A48" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>1025002</v>
+        <v>1023001</v>
       </c>
       <c r="B48" s="5">
-        <v>102500</v>
+        <v>102300</v>
       </c>
       <c r="C48" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="F48" s="5">
         <v>1</v>
@@ -3909,19 +3905,19 @@
         <v>23</v>
       </c>
       <c r="H48" s="5">
-        <v>2025001</v>
+        <v>2023001</v>
       </c>
       <c r="I48" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L48" s="46">
-        <v>10250031</v>
+      <c r="L48" s="46" t="s">
+        <v>105</v>
       </c>
       <c r="M48" s="5" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="N48" s="45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O48" s="45">
         <v>5</v>
@@ -3931,19 +3927,19 @@
     <row r="49" customFormat="1" ht="16.5" spans="1:17">
       <c r="A49" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>1025003</v>
+        <v>1023002</v>
       </c>
       <c r="B49" s="5">
-        <v>102500</v>
+        <v>102300</v>
       </c>
       <c r="C49" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="F49" s="5">
         <v>1</v>
@@ -3952,19 +3948,19 @@
         <v>23</v>
       </c>
       <c r="H49" s="5">
-        <v>2025001</v>
+        <v>2023001</v>
       </c>
       <c r="I49" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L49" s="46" t="s">
-        <v>103</v>
+      <c r="L49" s="46">
+        <v>10230003</v>
       </c>
       <c r="M49" s="5" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="N49" s="45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O49" s="45">
         <v>5</v>
@@ -3974,19 +3970,19 @@
     <row r="50" customFormat="1" ht="16.5" spans="1:17">
       <c r="A50" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>1023001</v>
+        <v>1023003</v>
       </c>
       <c r="B50" s="5">
         <v>102300</v>
       </c>
       <c r="C50" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>104</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="F50" s="5">
         <v>1</v>
@@ -4001,10 +3997,10 @@
         <v>24</v>
       </c>
       <c r="L50" s="46" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M50" s="5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="N50" s="45">
         <v>4</v>
@@ -4017,19 +4013,19 @@
     <row r="51" customFormat="1" ht="16.5" spans="1:17">
       <c r="A51" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>1023002</v>
+        <v>1034001</v>
       </c>
       <c r="B51" s="5">
-        <v>102300</v>
+        <v>103400</v>
       </c>
       <c r="C51" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="F51" s="5">
         <v>1</v>
@@ -4038,41 +4034,41 @@
         <v>23</v>
       </c>
       <c r="H51" s="5">
-        <v>2023001</v>
+        <v>2034001</v>
       </c>
       <c r="I51" s="5" t="s">
         <v>24</v>
       </c>
       <c r="L51" s="46">
-        <v>10230003</v>
+        <v>10340007</v>
       </c>
       <c r="M51" s="5" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="N51" s="45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O51" s="45">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q51" s="8"/>
     </row>
     <row r="52" customFormat="1" ht="16.5" spans="1:17">
       <c r="A52" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>1023003</v>
+        <v>1034002</v>
       </c>
       <c r="B52" s="5">
-        <v>102300</v>
+        <v>103400</v>
       </c>
       <c r="C52" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="F52" s="5">
         <v>1</v>
@@ -4081,43 +4077,40 @@
         <v>23</v>
       </c>
       <c r="H52" s="5">
-        <v>2023001</v>
+        <v>2034001</v>
       </c>
       <c r="I52" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L52" s="46" t="s">
-        <v>106</v>
-      </c>
-      <c r="M52" s="5" t="s">
-        <v>83</v>
-      </c>
+      <c r="L52" s="46"/>
+      <c r="M52" s="5"/>
       <c r="N52" s="45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O52" s="45">
-        <v>5</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="P52" s="50"/>
       <c r="Q52" s="8"/>
     </row>
-    <row r="53" customFormat="1" ht="16.5" spans="1:17">
+    <row r="53" s="6" customFormat="1" ht="16.5" spans="1:17">
       <c r="A53" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>1034001</v>
+        <v>1034003</v>
       </c>
       <c r="B53" s="5">
         <v>103400</v>
       </c>
       <c r="C53" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>107</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F53" s="5">
+        <v>81</v>
+      </c>
+      <c r="F53" s="51">
         <v>1</v>
       </c>
       <c r="G53" s="5" t="s">
@@ -4129,133 +4122,136 @@
       <c r="I53" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L53" s="46">
-        <v>10340007</v>
-      </c>
-      <c r="M53" s="5" t="s">
-        <v>108</v>
-      </c>
+      <c r="L53" s="48"/>
+      <c r="M53" s="51"/>
       <c r="N53" s="45">
         <v>3</v>
       </c>
       <c r="O53" s="45">
         <v>3</v>
       </c>
-      <c r="Q53" s="8"/>
-    </row>
-    <row r="54" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A54" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>1034002</v>
-      </c>
-      <c r="B54" s="5">
-        <v>103400</v>
-      </c>
-      <c r="C54" s="5">
-        <v>2</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="F54" s="5">
-        <v>1</v>
-      </c>
-      <c r="G54" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H54" s="5">
-        <v>2034001</v>
-      </c>
-      <c r="I54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L54" s="46"/>
-      <c r="M54" s="5"/>
-      <c r="N54" s="45">
-        <v>3</v>
-      </c>
-      <c r="O54" s="45">
-        <v>3</v>
-      </c>
-      <c r="P54" s="50"/>
-      <c r="Q54" s="8"/>
-    </row>
-    <row r="55" s="6" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A55" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>1034003</v>
-      </c>
-      <c r="B55" s="5">
-        <v>103400</v>
-      </c>
-      <c r="C55" s="5">
-        <v>3</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F55" s="51">
-        <v>1</v>
-      </c>
-      <c r="G55" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H55" s="5">
-        <v>2034001</v>
-      </c>
-      <c r="I55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L55" s="48"/>
-      <c r="M55" s="51"/>
-      <c r="N55" s="45">
-        <v>3</v>
-      </c>
-      <c r="O55" s="45">
-        <v>3</v>
-      </c>
-      <c r="Q55" s="52"/>
-    </row>
-    <row r="56" s="6" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A56" s="51" t="str">
+      <c r="Q53" s="52"/>
+    </row>
+    <row r="54" s="6" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A54" s="51" t="str">
         <f t="shared" si="2"/>
         <v>1035001</v>
       </c>
-      <c r="B56" s="51">
+      <c r="B54" s="51">
         <v>103500</v>
       </c>
-      <c r="C56" s="51">
-        <v>1</v>
-      </c>
-      <c r="D56" s="51" t="s">
+      <c r="C54" s="51">
+        <v>1</v>
+      </c>
+      <c r="D54" s="51" t="s">
         <v>110</v>
       </c>
-      <c r="E56" s="51" t="s">
+      <c r="E54" s="51" t="s">
         <v>111</v>
       </c>
-      <c r="F56" s="51">
-        <v>1</v>
-      </c>
-      <c r="G56" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="H56" s="51">
+      <c r="F54" s="51">
+        <v>1</v>
+      </c>
+      <c r="G54" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="H54" s="51">
         <v>2035001</v>
       </c>
-      <c r="I56" s="51" t="s">
-        <v>24</v>
-      </c>
-      <c r="L56" s="48" t="s">
+      <c r="I54" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="L54" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="M56" s="51" t="s">
+      <c r="M54" s="51" t="s">
         <v>113</v>
+      </c>
+      <c r="N54" s="45">
+        <v>4</v>
+      </c>
+      <c r="O54" s="45">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="52"/>
+    </row>
+    <row r="55" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A55" s="5" t="str">
+        <f t="shared" ref="A54:A62" si="3">B55&amp;C55</f>
+        <v>1035002</v>
+      </c>
+      <c r="B55" s="5">
+        <v>103500</v>
+      </c>
+      <c r="C55" s="5">
+        <v>2</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F55" s="5">
+        <v>1</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H55" s="5">
+        <v>2035002</v>
+      </c>
+      <c r="I55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L55" s="46" t="s">
+        <v>115</v>
+      </c>
+      <c r="M55" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="N55" s="45">
+        <v>4</v>
+      </c>
+      <c r="O55" s="45">
+        <v>3</v>
+      </c>
+      <c r="Q55" s="8"/>
+    </row>
+    <row r="56" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A56" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1035003</v>
+      </c>
+      <c r="B56" s="5">
+        <v>103500</v>
+      </c>
+      <c r="C56" s="5">
+        <v>3</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F56" s="5">
+        <v>1</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H56" s="5">
+        <v>2035001</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L56" s="46" t="s">
+        <v>117</v>
+      </c>
+      <c r="M56" s="5" t="s">
+        <v>118</v>
       </c>
       <c r="N56" s="45">
         <v>4</v>
@@ -4263,24 +4259,23 @@
       <c r="O56" s="45">
         <v>3</v>
       </c>
-      <c r="Q56" s="52"/>
+      <c r="Q56" s="8"/>
     </row>
     <row r="57" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A57" s="5" t="str">
-        <f t="shared" ref="A56:A64" si="3">B57&amp;C57</f>
-        <v>1035002</v>
+      <c r="A57" s="53">
+        <v>1035011</v>
       </c>
       <c r="B57" s="5">
-        <v>103500</v>
+        <v>103501</v>
       </c>
       <c r="C57" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F57" s="5">
         <v>1</v>
@@ -4289,16 +4284,16 @@
         <v>23</v>
       </c>
       <c r="H57" s="5">
-        <v>2035002</v>
+        <v>2035011</v>
       </c>
       <c r="I57" s="5" t="s">
         <v>24</v>
       </c>
       <c r="L57" s="46" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="M57" s="5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="N57" s="45">
         <v>4</v>
@@ -4311,19 +4306,19 @@
     <row r="58" customFormat="1" ht="16.5" spans="1:17">
       <c r="A58" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>1035003</v>
+        <v>1035012</v>
       </c>
       <c r="B58" s="5">
-        <v>103500</v>
+        <v>103501</v>
       </c>
       <c r="C58" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="F58" s="5">
         <v>1</v>
@@ -4332,16 +4327,16 @@
         <v>23</v>
       </c>
       <c r="H58" s="5">
-        <v>2035001</v>
+        <v>2035012</v>
       </c>
       <c r="I58" s="5" t="s">
         <v>24</v>
       </c>
       <c r="L58" s="46" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="M58" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="N58" s="45">
         <v>4</v>
@@ -4352,20 +4347,21 @@
       <c r="Q58" s="8"/>
     </row>
     <row r="59" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A59" s="53">
-        <v>1035011</v>
+      <c r="A59" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1035013</v>
       </c>
       <c r="B59" s="5">
         <v>103501</v>
       </c>
       <c r="C59" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>119</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="F59" s="5">
         <v>1</v>
@@ -4380,10 +4376,10 @@
         <v>24</v>
       </c>
       <c r="L59" s="46" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="M59" s="5" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="N59" s="45">
         <v>4</v>
@@ -4396,19 +4392,19 @@
     <row r="60" customFormat="1" ht="16.5" spans="1:17">
       <c r="A60" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>1035012</v>
+        <v>1036001</v>
       </c>
       <c r="B60" s="5">
-        <v>103501</v>
+        <v>103600</v>
       </c>
       <c r="C60" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F60" s="5">
         <v>1</v>
@@ -4417,19 +4413,19 @@
         <v>23</v>
       </c>
       <c r="H60" s="5">
-        <v>2035012</v>
+        <v>2036001</v>
       </c>
       <c r="I60" s="5" t="s">
         <v>24</v>
       </c>
       <c r="L60" s="46" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M60" s="5" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="N60" s="45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O60" s="45">
         <v>3</v>
@@ -4439,19 +4435,19 @@
     <row r="61" customFormat="1" ht="16.5" spans="1:17">
       <c r="A61" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>1035013</v>
+        <v>1036002</v>
       </c>
       <c r="B61" s="5">
-        <v>103501</v>
+        <v>103600</v>
       </c>
       <c r="C61" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="F61" s="5">
         <v>1</v>
@@ -4460,19 +4456,19 @@
         <v>23</v>
       </c>
       <c r="H61" s="5">
-        <v>2035011</v>
+        <v>2036002</v>
       </c>
       <c r="I61" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L61" s="46" t="s">
-        <v>122</v>
+      <c r="L61" s="46">
+        <v>10360004</v>
       </c>
       <c r="M61" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="N61" s="45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O61" s="45">
         <v>3</v>
@@ -4482,19 +4478,19 @@
     <row r="62" customFormat="1" ht="16.5" spans="1:17">
       <c r="A62" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>1036001</v>
+        <v>1036003</v>
       </c>
       <c r="B62" s="5">
         <v>103600</v>
       </c>
       <c r="C62" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>123</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="F62" s="5">
         <v>1</v>
@@ -4508,11 +4504,11 @@
       <c r="I62" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L62" s="46" t="s">
-        <v>124</v>
+      <c r="L62" s="46">
+        <v>10360002</v>
       </c>
       <c r="M62" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="N62" s="45">
         <v>3</v>
@@ -4523,89 +4519,35 @@
       <c r="Q62" s="8"/>
     </row>
     <row r="63" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A63" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>1036002</v>
-      </c>
-      <c r="B63" s="5">
-        <v>103600</v>
-      </c>
-      <c r="C63" s="5">
-        <v>2</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="E63" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="F63" s="5">
-        <v>1</v>
-      </c>
-      <c r="G63" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H63" s="5">
-        <v>2036002</v>
-      </c>
-      <c r="I63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L63" s="46">
-        <v>10360004</v>
-      </c>
-      <c r="M63" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="N63" s="45">
-        <v>3</v>
-      </c>
-      <c r="O63" s="45">
-        <v>3</v>
-      </c>
+      <c r="A63" s="5"/>
+      <c r="B63" s="5"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="5"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="5"/>
+      <c r="I63" s="5"/>
+      <c r="L63" s="46"/>
+      <c r="M63" s="5"/>
+      <c r="N63" s="45"/>
+      <c r="O63" s="45"/>
       <c r="Q63" s="8"/>
     </row>
     <row r="64" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A64" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>1036003</v>
-      </c>
-      <c r="B64" s="5">
-        <v>103600</v>
-      </c>
-      <c r="C64" s="5">
-        <v>3</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="E64" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F64" s="5">
-        <v>1</v>
-      </c>
-      <c r="G64" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H64" s="5">
-        <v>2036001</v>
-      </c>
-      <c r="I64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L64" s="46">
-        <v>10360002</v>
-      </c>
-      <c r="M64" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="N64" s="45">
-        <v>3</v>
-      </c>
-      <c r="O64" s="45">
-        <v>3</v>
-      </c>
+      <c r="A64" s="5"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="5"/>
+      <c r="G64" s="5"/>
+      <c r="H64" s="5"/>
+      <c r="I64" s="5"/>
+      <c r="L64" s="46"/>
+      <c r="M64" s="5"/>
+      <c r="N64" s="45"/>
+      <c r="O64" s="45"/>
       <c r="Q64" s="8"/>
     </row>
     <row r="65" customFormat="1" ht="16.5" spans="1:17">
@@ -4767,38 +4709,6 @@
       <c r="N74" s="45"/>
       <c r="O74" s="45"/>
       <c r="Q74" s="8"/>
-    </row>
-    <row r="75" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A75" s="5"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
-      <c r="D75" s="5"/>
-      <c r="E75" s="5"/>
-      <c r="F75" s="5"/>
-      <c r="G75" s="5"/>
-      <c r="H75" s="5"/>
-      <c r="I75" s="5"/>
-      <c r="L75" s="46"/>
-      <c r="M75" s="5"/>
-      <c r="N75" s="45"/>
-      <c r="O75" s="45"/>
-      <c r="Q75" s="8"/>
-    </row>
-    <row r="76" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A76" s="5"/>
-      <c r="B76" s="5"/>
-      <c r="C76" s="5"/>
-      <c r="D76" s="5"/>
-      <c r="E76" s="5"/>
-      <c r="F76" s="5"/>
-      <c r="G76" s="5"/>
-      <c r="H76" s="5"/>
-      <c r="I76" s="5"/>
-      <c r="L76" s="46"/>
-      <c r="M76" s="5"/>
-      <c r="N76" s="45"/>
-      <c r="O76" s="45"/>
-      <c r="Q76" s="8"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:K2">

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="231">
   <si>
     <t>id</t>
   </si>
@@ -509,6 +509,9 @@
     <t>福鼠模式-触发</t>
   </si>
   <si>
+    <t>第二轴改出三个9符号</t>
+  </si>
+  <si>
     <t>必出现3个Jackpot符号</t>
   </si>
   <si>
@@ -765,6 +768,57 @@
   </si>
   <si>
     <t>10260003|10260008</t>
+  </si>
+  <si>
+    <t>澳门壕梦</t>
+  </si>
+  <si>
+    <t>10500001|10500004|10500005|10500006|10500007</t>
+  </si>
+  <si>
+    <t>概率改出wild+概率改出scatter符号+概率改出占据2、3、4格子的普通符号</t>
+  </si>
+  <si>
+    <t>改出4个或以上个数SCATTER</t>
+  </si>
+  <si>
+    <t>10500003|10500008</t>
+  </si>
+  <si>
+    <t>改出3个scatter符号+改出奖池符号</t>
+  </si>
+  <si>
+    <t>糖果派对</t>
+  </si>
+  <si>
+    <t>常规模式（第三层）</t>
+  </si>
+  <si>
+    <t>概率改出过关图标3</t>
+  </si>
+  <si>
+    <t>第二层模式</t>
+  </si>
+  <si>
+    <t>10510001|10510006</t>
+  </si>
+  <si>
+    <t>一定改出透明图标+概率改出过关图标1</t>
+  </si>
+  <si>
+    <t>第一层模式</t>
+  </si>
+  <si>
+    <t>10510002|10510007</t>
+  </si>
+  <si>
+    <t>一定改出透明图标+概率改出过关图标2</t>
+  </si>
+  <si>
+    <t>概率改出免费游戏图标</t>
+  </si>
+  <si>
+    <t>改出1-4个彩池图标</t>
   </si>
 </sst>
 </file>
@@ -1495,7 +1549,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1622,9 +1676,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2158,7 +2209,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S112"/>
+  <dimension ref="A1:S116"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
@@ -4742,7 +4793,7 @@
         <v>10360004</v>
       </c>
       <c r="M61" s="5" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="N61" s="46">
         <v>3</v>
@@ -4785,7 +4836,7 @@
         <v>10360002</v>
       </c>
       <c r="M62" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N62" s="46">
         <v>3</v>
@@ -4807,7 +4858,7 @@
         <v>1</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E63" s="5" t="s">
         <v>111</v>
@@ -4825,10 +4876,10 @@
         <v>24</v>
       </c>
       <c r="L63" s="47" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M63" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N63" s="46">
         <v>5</v>
@@ -4850,10 +4901,10 @@
         <v>2</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F64" s="5">
         <v>1</v>
@@ -4893,7 +4944,7 @@
         <v>3</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E65" s="5" t="s">
         <v>81</v>
@@ -4911,7 +4962,7 @@
         <v>24</v>
       </c>
       <c r="L65" s="47" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M65" s="5" t="s">
         <v>83</v>
@@ -4936,7 +4987,7 @@
         <v>1</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E66" s="5" t="s">
         <v>22</v>
@@ -4979,10 +5030,10 @@
         <v>2</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F67" s="5">
         <v>1</v>
@@ -5019,7 +5070,7 @@
         <v>3</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E68" s="5" t="s">
         <v>81</v>
@@ -5060,7 +5111,7 @@
         <v>1</v>
       </c>
       <c r="D69" s="53" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E69" s="53" t="s">
         <v>22</v>
@@ -5078,10 +5129,10 @@
         <v>24</v>
       </c>
       <c r="L69" s="54" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M69" s="53" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N69" s="55">
         <v>5</v>
@@ -5103,10 +5154,10 @@
         <v>2</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F70" s="5">
         <v>1</v>
@@ -5121,10 +5172,10 @@
         <v>24</v>
       </c>
       <c r="L70" s="47" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M70" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N70" s="46">
         <v>5</v>
@@ -5146,7 +5197,7 @@
         <v>3</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E71" s="5" t="s">
         <v>81</v>
@@ -5164,10 +5215,10 @@
         <v>24</v>
       </c>
       <c r="L71" s="47" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M71" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N71" s="46">
         <v>5</v>
@@ -5189,10 +5240,10 @@
         <v>4</v>
       </c>
       <c r="D72" s="56" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E72" s="56" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F72" s="56">
         <v>1</v>
@@ -5210,7 +5261,7 @@
         <v>10200016</v>
       </c>
       <c r="M72" s="56" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N72" s="58">
         <v>5</v>
@@ -5232,10 +5283,10 @@
         <v>5</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F73" s="5">
         <v>1</v>
@@ -5253,7 +5304,7 @@
         <v>10200021</v>
       </c>
       <c r="M73" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N73" s="46">
         <v>5</v>
@@ -5275,7 +5326,7 @@
         <v>1</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E74" s="5" t="s">
         <v>111</v>
@@ -5293,11 +5344,11 @@
         <v>24</v>
       </c>
       <c r="J74" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L74" s="47"/>
       <c r="M74" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N74" s="46">
         <v>3</v>
@@ -5319,10 +5370,10 @@
         <v>2</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F75" s="5">
         <v>1</v>
@@ -5340,7 +5391,7 @@
         <v>10380002</v>
       </c>
       <c r="M75" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N75" s="46">
         <v>3</v>
@@ -5362,10 +5413,10 @@
         <v>4</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F76" s="5">
         <v>1</v>
@@ -5380,10 +5431,10 @@
         <v>24</v>
       </c>
       <c r="L76" s="47" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M76" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N76" s="46">
         <v>3</v>
@@ -5405,7 +5456,7 @@
         <v>3</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E77" s="5" t="s">
         <v>81</v>
@@ -5423,10 +5474,10 @@
         <v>24</v>
       </c>
       <c r="L77" s="47" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M77" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N77" s="46">
         <v>3</v>
@@ -5448,7 +5499,7 @@
         <v>1</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E78" s="5" t="s">
         <v>111</v>
@@ -5466,10 +5517,10 @@
         <v>24</v>
       </c>
       <c r="L78" s="47" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M78" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N78" s="46">
         <v>3</v>
@@ -5491,10 +5542,10 @@
         <v>2</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F79" s="5">
         <v>1</v>
@@ -5512,7 +5563,7 @@
         <v>10270003</v>
       </c>
       <c r="M79" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N79" s="46">
         <v>3</v>
@@ -5534,7 +5585,7 @@
         <v>3</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E80" s="5" t="s">
         <v>81</v>
@@ -5552,10 +5603,10 @@
         <v>24</v>
       </c>
       <c r="L80" s="47" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M80" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N80" s="46">
         <v>3</v>
@@ -5577,7 +5628,7 @@
         <v>1</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E81" s="5" t="s">
         <v>111</v>
@@ -5595,10 +5646,10 @@
         <v>24</v>
       </c>
       <c r="L81" s="47" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M81" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N81" s="46">
         <v>4</v>
@@ -5620,10 +5671,10 @@
         <v>2</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F82" s="5">
         <v>1</v>
@@ -5638,10 +5689,10 @@
         <v>24</v>
       </c>
       <c r="L82" s="47" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M82" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N82" s="46">
         <v>4</v>
@@ -5663,7 +5714,7 @@
         <v>3</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E83" s="5" t="s">
         <v>81</v>
@@ -5684,7 +5735,7 @@
         <v>10370003</v>
       </c>
       <c r="M83" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N83" s="46">
         <v>4</v>
@@ -5696,7 +5747,7 @@
     </row>
     <row r="84" customFormat="1" ht="16.5" spans="1:17">
       <c r="A84" s="5" t="str">
-        <f t="shared" ref="A84:A105" si="4">B84&amp;C84</f>
+        <f t="shared" ref="A84:A108" si="4">B84&amp;C84</f>
         <v>1031001</v>
       </c>
       <c r="B84" s="5">
@@ -5706,7 +5757,7 @@
         <v>1</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>111</v>
@@ -5724,10 +5775,10 @@
         <v>24</v>
       </c>
       <c r="L84" s="47" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M84" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N84" s="46">
         <v>3</v>
@@ -5749,10 +5800,10 @@
         <v>2</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F85" s="5">
         <v>1</v>
@@ -5770,7 +5821,7 @@
         <v>10310008</v>
       </c>
       <c r="M85" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N85" s="46">
         <v>3</v>
@@ -5792,7 +5843,7 @@
         <v>3</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E86" s="5" t="s">
         <v>94</v>
@@ -5810,10 +5861,10 @@
         <v>24</v>
       </c>
       <c r="L86" s="47" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M86" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N86" s="46">
         <v>3</v>
@@ -5835,7 +5886,7 @@
         <v>4</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E87" s="5" t="s">
         <v>81</v>
@@ -5853,10 +5904,10 @@
         <v>24</v>
       </c>
       <c r="L87" s="47" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M87" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N87" s="46">
         <v>3</v>
@@ -5878,10 +5929,10 @@
         <v>5</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F88" s="5">
         <v>1</v>
@@ -5899,7 +5950,7 @@
         <v>10310003</v>
       </c>
       <c r="M88" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N88" s="46">
         <v>3</v>
@@ -5921,10 +5972,10 @@
         <v>6</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F89" s="5">
         <v>1</v>
@@ -5939,10 +5990,10 @@
         <v>24</v>
       </c>
       <c r="L89" s="47" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M89" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N89" s="46">
         <v>3</v>
@@ -5964,7 +6015,7 @@
         <v>1</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E90" s="5" t="s">
         <v>111</v>
@@ -5982,10 +6033,10 @@
         <v>24</v>
       </c>
       <c r="L90" s="47" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M90" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N90" s="46">
         <v>3</v>
@@ -6007,10 +6058,10 @@
         <v>2</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F91" s="5">
         <v>1</v>
@@ -6025,10 +6076,10 @@
         <v>24</v>
       </c>
       <c r="L91" s="47" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M91" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N91" s="46">
         <v>3</v>
@@ -6050,7 +6101,7 @@
         <v>3</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E92" s="5" t="s">
         <v>81</v>
@@ -6068,10 +6119,10 @@
         <v>24</v>
       </c>
       <c r="L92" s="47" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M92" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N92" s="46">
         <v>3</v>
@@ -6093,7 +6144,7 @@
         <v>1</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E93" s="5" t="s">
         <v>111</v>
@@ -6111,10 +6162,10 @@
         <v>24</v>
       </c>
       <c r="L93" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M93" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N93" s="46">
         <v>3</v>
@@ -6136,10 +6187,10 @@
         <v>2</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F94" s="5">
         <v>1</v>
@@ -6157,7 +6208,7 @@
         <v>10390003</v>
       </c>
       <c r="M94" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N94" s="46">
         <v>3</v>
@@ -6179,7 +6230,7 @@
         <v>3</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E95" s="5" t="s">
         <v>81</v>
@@ -6197,7 +6248,7 @@
         <v>24</v>
       </c>
       <c r="L95" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M95" s="5" t="s">
         <v>83</v>
@@ -6222,7 +6273,7 @@
         <v>1</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E96" s="5" t="s">
         <v>111</v>
@@ -6240,10 +6291,10 @@
         <v>24</v>
       </c>
       <c r="L96" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M96" s="5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N96" s="46">
         <v>6</v>
@@ -6265,10 +6316,10 @@
         <v>2</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F97" s="5">
         <v>1</v>
@@ -6286,7 +6337,7 @@
         <v>10160002</v>
       </c>
       <c r="M97" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N97" s="46">
         <v>6</v>
@@ -6308,7 +6359,7 @@
         <v>3</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E98" s="5" t="s">
         <v>81</v>
@@ -6327,10 +6378,10 @@
       </c>
       <c r="J98" s="5"/>
       <c r="L98" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M98" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N98" s="46">
         <v>6</v>
@@ -6352,7 +6403,7 @@
         <v>1</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E99" s="5" t="s">
         <v>111</v>
@@ -6370,10 +6421,10 @@
         <v>24</v>
       </c>
       <c r="L99" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M99" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N99" s="46">
         <v>3</v>
@@ -6395,10 +6446,10 @@
         <v>2</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F100" s="5">
         <v>1</v>
@@ -6413,7 +6464,7 @@
         <v>24</v>
       </c>
       <c r="J100" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M100" s="5" t="s">
         <v>108</v>
@@ -6438,10 +6489,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F101" s="5">
         <v>1</v>
@@ -6481,7 +6532,7 @@
         <v>4</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E102" s="5" t="s">
         <v>81</v>
@@ -6499,10 +6550,10 @@
         <v>24</v>
       </c>
       <c r="L102" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M102" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N102" s="46">
         <v>3</v>
@@ -6524,10 +6575,10 @@
         <v>5</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F103" s="5">
         <v>1</v>
@@ -6545,7 +6596,7 @@
         <v>10150005</v>
       </c>
       <c r="M103" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N103" s="46">
         <v>3</v>
@@ -6567,10 +6618,10 @@
         <v>6</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F104" s="5">
         <v>1</v>
@@ -6588,7 +6639,7 @@
         <v>10150006</v>
       </c>
       <c r="M104" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N104" s="46">
         <v>3</v>
@@ -6610,10 +6661,10 @@
         <v>7</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F105" s="5">
         <v>1</v>
@@ -6631,7 +6682,7 @@
         <v>10150007</v>
       </c>
       <c r="M105" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N105" s="46">
         <v>3</v>
@@ -6643,7 +6694,7 @@
     </row>
     <row r="106" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A106" s="5" t="str">
-        <f>B106&amp;C106</f>
+        <f t="shared" si="4"/>
         <v>1026001</v>
       </c>
       <c r="B106" s="5">
@@ -6653,7 +6704,7 @@
         <v>1</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E106" s="5" t="s">
         <v>111</v>
@@ -6671,10 +6722,10 @@
         <v>24</v>
       </c>
       <c r="L106" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M106" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N106" s="46">
         <v>6</v>
@@ -6686,7 +6737,7 @@
     </row>
     <row r="107" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A107" s="5" t="str">
-        <f>B107&amp;C107</f>
+        <f t="shared" si="4"/>
         <v>1026002</v>
       </c>
       <c r="B107" s="5">
@@ -6696,10 +6747,10 @@
         <v>2</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F107" s="5">
         <v>1</v>
@@ -6713,11 +6764,11 @@
       <c r="I107" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L107" s="60">
+      <c r="L107" s="47">
         <v>10260002</v>
       </c>
       <c r="M107" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N107" s="46">
         <v>6</v>
@@ -6729,7 +6780,7 @@
     </row>
     <row r="108" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A108" s="5" t="str">
-        <f>B108&amp;C108</f>
+        <f t="shared" si="4"/>
         <v>1026003</v>
       </c>
       <c r="B108" s="5">
@@ -6739,7 +6790,7 @@
         <v>3</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E108" s="5" t="s">
         <v>81</v>
@@ -6757,10 +6808,10 @@
         <v>24</v>
       </c>
       <c r="L108" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M108" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N108" s="46">
         <v>6</v>
@@ -6771,24 +6822,341 @@
       <c r="Q108" s="19"/>
     </row>
     <row r="109" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="N109" s="46"/>
-      <c r="O109" s="46"/>
+      <c r="A109" s="47">
+        <v>1050001</v>
+      </c>
+      <c r="B109" s="5">
+        <v>105000</v>
+      </c>
+      <c r="C109" s="5">
+        <v>1</v>
+      </c>
+      <c r="D109" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="E109" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F109" s="5">
+        <v>1</v>
+      </c>
+      <c r="G109" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H109" s="5">
+        <v>2050001</v>
+      </c>
+      <c r="I109" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L109" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="M109" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="N109" s="46">
+        <v>5</v>
+      </c>
+      <c r="O109" s="46">
+        <v>6</v>
+      </c>
       <c r="Q109" s="19"/>
     </row>
     <row r="110" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="N110" s="46"/>
-      <c r="O110" s="46"/>
+      <c r="A110" s="47">
+        <v>1050002</v>
+      </c>
+      <c r="B110" s="5">
+        <v>105000</v>
+      </c>
+      <c r="C110" s="5">
+        <v>2</v>
+      </c>
+      <c r="D110" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="E110" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F110" s="5">
+        <v>1</v>
+      </c>
+      <c r="G110" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H110" s="5">
+        <v>2050001</v>
+      </c>
+      <c r="I110" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L110" s="47">
+        <v>10500002</v>
+      </c>
+      <c r="M110" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="N110" s="46">
+        <v>5</v>
+      </c>
+      <c r="O110" s="46">
+        <v>6</v>
+      </c>
+      <c r="P110" s="46"/>
       <c r="Q110" s="19"/>
     </row>
     <row r="111" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="N111" s="46"/>
-      <c r="O111" s="46"/>
+      <c r="A111" s="47">
+        <v>1050003</v>
+      </c>
+      <c r="B111" s="5">
+        <v>105000</v>
+      </c>
+      <c r="C111" s="5">
+        <v>3</v>
+      </c>
+      <c r="D111" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="E111" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F111" s="5">
+        <v>1</v>
+      </c>
+      <c r="G111" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H111" s="5">
+        <v>2050001</v>
+      </c>
+      <c r="I111" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L111" s="47" t="s">
+        <v>218</v>
+      </c>
+      <c r="M111" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="N111" s="46">
+        <v>5</v>
+      </c>
+      <c r="O111" s="46">
+        <v>6</v>
+      </c>
       <c r="Q111" s="19"/>
     </row>
     <row r="112" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="N112" s="46"/>
-      <c r="O112" s="46"/>
+      <c r="A112" s="47">
+        <v>1051001</v>
+      </c>
+      <c r="B112" s="5">
+        <v>105100</v>
+      </c>
+      <c r="C112" s="5">
+        <v>1</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="E112" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="F112" s="5">
+        <v>1</v>
+      </c>
+      <c r="G112" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H112" s="5">
+        <v>2051001</v>
+      </c>
+      <c r="I112" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L112" s="47">
+        <v>10510008</v>
+      </c>
+      <c r="M112" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="N112" s="46">
+        <v>6</v>
+      </c>
+      <c r="O112" s="46">
+        <v>6</v>
+      </c>
       <c r="Q112" s="19"/>
+    </row>
+    <row r="113" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A113" s="47">
+        <v>1051002</v>
+      </c>
+      <c r="B113" s="5">
+        <v>105100</v>
+      </c>
+      <c r="C113" s="5">
+        <v>2</v>
+      </c>
+      <c r="D113" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="E113" t="s">
+        <v>223</v>
+      </c>
+      <c r="F113" s="5">
+        <v>1</v>
+      </c>
+      <c r="G113" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H113" s="5">
+        <v>2051001</v>
+      </c>
+      <c r="I113" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L113" s="47" t="s">
+        <v>224</v>
+      </c>
+      <c r="M113" t="s">
+        <v>225</v>
+      </c>
+      <c r="N113" s="46">
+        <v>6</v>
+      </c>
+      <c r="O113" s="46">
+        <v>6</v>
+      </c>
+      <c r="Q113" s="9"/>
+    </row>
+    <row r="114" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A114" s="47">
+        <v>1051003</v>
+      </c>
+      <c r="B114" s="5">
+        <v>105100</v>
+      </c>
+      <c r="C114" s="5">
+        <v>3</v>
+      </c>
+      <c r="D114" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="E114" t="s">
+        <v>226</v>
+      </c>
+      <c r="F114" s="5">
+        <v>1</v>
+      </c>
+      <c r="G114" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H114" s="5">
+        <v>2051001</v>
+      </c>
+      <c r="I114" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L114" s="47" t="s">
+        <v>227</v>
+      </c>
+      <c r="M114" t="s">
+        <v>228</v>
+      </c>
+      <c r="N114" s="46">
+        <v>6</v>
+      </c>
+      <c r="O114" s="46">
+        <v>6</v>
+      </c>
+      <c r="Q114" s="9"/>
+    </row>
+    <row r="115" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A115" s="47">
+        <v>1051004</v>
+      </c>
+      <c r="B115" s="5">
+        <v>105100</v>
+      </c>
+      <c r="C115" s="5">
+        <v>4</v>
+      </c>
+      <c r="D115" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="E115" t="s">
+        <v>132</v>
+      </c>
+      <c r="F115" s="5">
+        <v>1</v>
+      </c>
+      <c r="G115" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H115" s="5">
+        <v>2051001</v>
+      </c>
+      <c r="I115" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L115" s="47">
+        <v>10510005</v>
+      </c>
+      <c r="M115" t="s">
+        <v>229</v>
+      </c>
+      <c r="N115" s="46">
+        <v>6</v>
+      </c>
+      <c r="O115" s="46">
+        <v>6</v>
+      </c>
+      <c r="Q115" s="9"/>
+    </row>
+    <row r="116" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A116" s="47">
+        <v>1051005</v>
+      </c>
+      <c r="B116" s="5">
+        <v>105100</v>
+      </c>
+      <c r="C116" s="5">
+        <v>5</v>
+      </c>
+      <c r="D116" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="E116" t="s">
+        <v>81</v>
+      </c>
+      <c r="F116" s="5">
+        <v>1</v>
+      </c>
+      <c r="G116" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H116" s="5">
+        <v>2051001</v>
+      </c>
+      <c r="I116" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L116" s="47">
+        <v>10510009</v>
+      </c>
+      <c r="M116" t="s">
+        <v>230</v>
+      </c>
+      <c r="N116" s="46">
+        <v>6</v>
+      </c>
+      <c r="O116" s="46">
+        <v>6</v>
+      </c>
+      <c r="Q116" s="9"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:K2">

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -1002,12 +1002,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -5092,10 +5092,10 @@
       <c r="L68" s="47"/>
       <c r="M68" s="5"/>
       <c r="N68" s="46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O68" s="46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q68" s="52"/>
     </row>

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -1002,12 +1002,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1549,13 +1549,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1660,6 +1661,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2222,14 +2228,14 @@
     <col min="11" max="11" width="16.75" customWidth="1"/>
     <col min="12" max="12" width="53.25" customWidth="1"/>
     <col min="13" max="13" width="21.6083333333333" customWidth="1"/>
-    <col min="14" max="15" width="9" style="8"/>
+    <col min="14" max="15" width="9" style="9"/>
     <col min="16" max="16" width="15" customWidth="1"/>
-    <col min="17" max="17" width="23.75" style="9" customWidth="1"/>
+    <col min="17" max="17" width="23.75" style="10" customWidth="1"/>
     <col min="18" max="18" width="60.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:17">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
@@ -2240,34 +2246,34 @@
       </c>
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="12" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="5"/>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="12" t="s">
         <v>4</v>
       </c>
       <c r="I1" s="5"/>
-      <c r="J1" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="12"/>
-      <c r="L1" s="13" t="s">
+      <c r="J1" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="13"/>
+      <c r="L1" s="14" t="s">
         <v>6</v>
       </c>
       <c r="M1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="N1" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="O1" s="15" t="s">
         <v>9</v>
       </c>
       <c r="Q1"/>
     </row>
     <row r="2" ht="16.5" spans="1:17">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -2278,62 +2284,62 @@
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="12" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="5"/>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="12" t="s">
         <v>10</v>
       </c>
       <c r="I2" s="5"/>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="16"/>
-      <c r="L2" s="17" t="s">
+      <c r="K2" s="17"/>
+      <c r="L2" s="18" t="s">
         <v>12</v>
       </c>
       <c r="M2" s="5"/>
-      <c r="N2" s="18" t="s">
+      <c r="N2" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="18" t="s">
+      <c r="O2" s="19" t="s">
         <v>10</v>
       </c>
       <c r="Q2"/>
     </row>
     <row r="3" ht="16.5" spans="1:17">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="20" t="s">
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="19"/>
-      <c r="H3" s="21" t="s">
+      <c r="G3" s="20"/>
+      <c r="H3" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="19"/>
-      <c r="J3" s="22" t="s">
+      <c r="I3" s="20"/>
+      <c r="J3" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="22"/>
-      <c r="L3" s="23" t="s">
+      <c r="K3" s="23"/>
+      <c r="L3" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="M3" s="19"/>
-      <c r="N3" s="18" t="s">
+      <c r="M3" s="20"/>
+      <c r="N3" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="18" t="s">
+      <c r="O3" s="19" t="s">
         <v>20</v>
       </c>
       <c r="Q3"/>
@@ -2343,1101 +2349,1101 @@
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="11"/>
+      <c r="F4" s="12"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="11"/>
+      <c r="H4" s="12"/>
       <c r="I4" s="5"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="13"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="14"/>
       <c r="M4" s="5"/>
-      <c r="N4" s="18"/>
-      <c r="O4" s="18"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
       <c r="Q4"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A5" s="25" t="str">
-        <f t="shared" ref="A5:A15" si="0">B5&amp;C5</f>
+      <c r="A5" s="26" t="str">
+        <f t="shared" ref="A5:A21" si="0">B5&amp;C5</f>
         <v>1001001</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="27">
         <v>100100</v>
       </c>
-      <c r="C5" s="26">
-        <v>1</v>
-      </c>
-      <c r="D5" s="26" t="s">
+      <c r="C5" s="27">
+        <v>1</v>
+      </c>
+      <c r="D5" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="26">
-        <v>1</v>
-      </c>
-      <c r="G5" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="25">
+      <c r="F5" s="27">
+        <v>1</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="26">
         <v>2001001</v>
       </c>
-      <c r="I5" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="28" t="s">
+      <c r="I5" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="26"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="M5" s="25" t="s">
+      <c r="M5" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="N5" s="18">
+      <c r="N5" s="19">
         <v>4</v>
       </c>
-      <c r="O5" s="18">
+      <c r="O5" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A6" s="25" t="str">
+      <c r="A6" s="26" t="str">
         <f t="shared" si="0"/>
         <v>1001002</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="27">
         <v>100100</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="27">
         <v>2</v>
       </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="29" t="s">
+      <c r="D6" s="27"/>
+      <c r="E6" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="26">
-        <v>1</v>
-      </c>
-      <c r="G6" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="25">
+      <c r="F6" s="27">
+        <v>1</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="26">
         <v>2001001</v>
       </c>
-      <c r="I6" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="30" t="s">
+      <c r="I6" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="M6" s="25" t="s">
+      <c r="M6" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="N6" s="18">
+      <c r="N6" s="19">
         <v>4</v>
       </c>
-      <c r="O6" s="18">
+      <c r="O6" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A7" s="25" t="str">
+      <c r="A7" s="26" t="str">
         <f t="shared" si="0"/>
         <v>1001003</v>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="27">
         <v>100100</v>
       </c>
-      <c r="C7" s="26">
-        <v>3</v>
-      </c>
-      <c r="D7" s="26"/>
-      <c r="E7" s="31" t="s">
+      <c r="C7" s="27">
+        <v>3</v>
+      </c>
+      <c r="D7" s="27"/>
+      <c r="E7" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="26">
-        <v>1</v>
-      </c>
-      <c r="G7" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="25">
+      <c r="F7" s="27">
+        <v>1</v>
+      </c>
+      <c r="G7" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="26">
         <v>2001001</v>
       </c>
-      <c r="I7" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="L7" s="28" t="s">
+      <c r="I7" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="M7" s="25" t="s">
+      <c r="M7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="N7" s="18">
+      <c r="N7" s="19">
         <v>4</v>
       </c>
-      <c r="O7" s="18">
+      <c r="O7" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A8" s="25" t="str">
+      <c r="A8" s="26" t="str">
         <f t="shared" si="0"/>
         <v>1001004</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="27">
         <v>100100</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="27">
         <v>4</v>
       </c>
-      <c r="D8" s="26"/>
-      <c r="E8" s="32" t="s">
+      <c r="D8" s="27"/>
+      <c r="E8" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="33">
-        <v>1</v>
-      </c>
-      <c r="G8" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="25">
+      <c r="F8" s="34">
+        <v>1</v>
+      </c>
+      <c r="G8" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="26">
         <v>2001001</v>
       </c>
-      <c r="I8" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="L8" s="28">
+      <c r="I8" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="29">
         <v>10010041</v>
       </c>
-      <c r="M8" s="25" t="s">
+      <c r="M8" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="N8" s="18">
+      <c r="N8" s="19">
         <v>4</v>
       </c>
-      <c r="O8" s="18">
+      <c r="O8" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A9" s="25" t="str">
+      <c r="A9" s="26" t="str">
         <f t="shared" si="0"/>
         <v>1001005</v>
       </c>
-      <c r="B9" s="26">
+      <c r="B9" s="27">
         <v>100100</v>
       </c>
-      <c r="C9" s="26">
-        <v>5</v>
-      </c>
-      <c r="D9" s="26"/>
-      <c r="E9" s="34" t="s">
+      <c r="C9" s="27">
+        <v>5</v>
+      </c>
+      <c r="D9" s="27"/>
+      <c r="E9" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="33">
-        <v>1</v>
-      </c>
-      <c r="G9" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="25">
+      <c r="F9" s="34">
+        <v>1</v>
+      </c>
+      <c r="G9" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="26">
         <v>2001001</v>
       </c>
-      <c r="I9" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="28" t="s">
+      <c r="I9" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="M9" s="25" t="s">
+      <c r="M9" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="N9" s="18">
+      <c r="N9" s="19">
         <v>4</v>
       </c>
-      <c r="O9" s="18">
+      <c r="O9" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A10" s="25" t="str">
+      <c r="A10" s="26" t="str">
         <f t="shared" si="0"/>
         <v>1001006</v>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="27">
         <v>100100</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="27">
         <v>6</v>
       </c>
-      <c r="D10" s="26"/>
-      <c r="E10" s="34" t="s">
+      <c r="D10" s="27"/>
+      <c r="E10" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="33">
-        <v>1</v>
-      </c>
-      <c r="G10" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="25">
+      <c r="F10" s="34">
+        <v>1</v>
+      </c>
+      <c r="G10" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="26">
         <v>2001001</v>
       </c>
-      <c r="I10" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="L10" s="28">
+      <c r="I10" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="29">
         <v>10010061</v>
       </c>
-      <c r="M10" s="25" t="s">
+      <c r="M10" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="N10" s="18">
+      <c r="N10" s="19">
         <v>4</v>
       </c>
-      <c r="O10" s="18">
+      <c r="O10" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A11" s="25" t="str">
+      <c r="A11" s="26" t="str">
         <f t="shared" si="0"/>
         <v>1001007</v>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="27">
         <v>100100</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="27">
         <v>7</v>
       </c>
-      <c r="D11" s="26"/>
-      <c r="E11" s="29" t="s">
+      <c r="D11" s="27"/>
+      <c r="E11" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="26">
-        <v>1</v>
-      </c>
-      <c r="G11" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" s="25">
+      <c r="F11" s="27">
+        <v>1</v>
+      </c>
+      <c r="G11" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="26">
         <v>2001001</v>
       </c>
-      <c r="I11" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="30" t="s">
+      <c r="I11" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="M11" s="25" t="s">
+      <c r="M11" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="N11" s="18">
+      <c r="N11" s="19">
         <v>4</v>
       </c>
-      <c r="O11" s="18">
+      <c r="O11" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A12" s="35" t="str">
+      <c r="A12" s="36" t="str">
         <f t="shared" si="0"/>
         <v>1003001</v>
       </c>
-      <c r="B12" s="27">
+      <c r="B12" s="28">
         <v>100300</v>
       </c>
-      <c r="C12" s="27">
-        <v>1</v>
-      </c>
-      <c r="D12" s="27" t="s">
+      <c r="C12" s="28">
+        <v>1</v>
+      </c>
+      <c r="D12" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="27" t="s">
+      <c r="E12" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="27">
-        <v>1</v>
-      </c>
-      <c r="G12" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="H12" s="35">
+      <c r="F12" s="28">
+        <v>1</v>
+      </c>
+      <c r="G12" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="36">
         <v>2003001</v>
       </c>
-      <c r="I12" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" s="35"/>
-      <c r="K12" s="35"/>
-      <c r="L12" s="36">
+      <c r="I12" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" s="36"/>
+      <c r="K12" s="36"/>
+      <c r="L12" s="37">
         <v>10030022</v>
       </c>
-      <c r="M12" s="35" t="s">
+      <c r="M12" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="N12" s="27">
-        <v>3</v>
-      </c>
-      <c r="O12" s="27">
-        <v>3</v>
-      </c>
-      <c r="Q12" s="37"/>
+      <c r="N12" s="28">
+        <v>3</v>
+      </c>
+      <c r="O12" s="28">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="38"/>
     </row>
     <row r="13" s="2" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A13" s="35" t="str">
-        <f t="shared" ref="A13:A30" si="1">B13&amp;C13</f>
+      <c r="A13" s="36" t="str">
+        <f t="shared" si="0"/>
         <v>1003002</v>
       </c>
-      <c r="B13" s="27">
+      <c r="B13" s="28">
         <v>100300</v>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="28">
         <v>2</v>
       </c>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27" t="s">
+      <c r="D13" s="28"/>
+      <c r="E13" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="27">
-        <v>1</v>
-      </c>
-      <c r="G13" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="H13" s="35">
+      <c r="F13" s="28">
+        <v>1</v>
+      </c>
+      <c r="G13" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="36">
         <v>2003001</v>
       </c>
-      <c r="I13" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="J13" s="35"/>
-      <c r="K13" s="35"/>
-      <c r="L13" s="36" t="s">
+      <c r="I13" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" s="36"/>
+      <c r="K13" s="36"/>
+      <c r="L13" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="M13" s="35" t="s">
+      <c r="M13" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="N13" s="27">
-        <v>3</v>
-      </c>
-      <c r="O13" s="27">
-        <v>3</v>
-      </c>
-      <c r="Q13" s="37"/>
+      <c r="N13" s="28">
+        <v>3</v>
+      </c>
+      <c r="O13" s="28">
+        <v>3</v>
+      </c>
+      <c r="Q13" s="38"/>
     </row>
     <row r="14" s="2" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A14" s="35" t="str">
-        <f t="shared" si="1"/>
+      <c r="A14" s="36" t="str">
+        <f t="shared" si="0"/>
         <v>1003003</v>
       </c>
-      <c r="B14" s="27">
+      <c r="B14" s="28">
         <v>100300</v>
       </c>
-      <c r="C14" s="27">
-        <v>3</v>
-      </c>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27" t="s">
+      <c r="C14" s="28">
+        <v>3</v>
+      </c>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="27">
-        <v>1</v>
-      </c>
-      <c r="G14" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="H14" s="35">
+      <c r="F14" s="28">
+        <v>1</v>
+      </c>
+      <c r="G14" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="36">
         <v>2003002</v>
       </c>
-      <c r="I14" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="J14" s="35" t="s">
+      <c r="I14" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="K14" s="35" t="s">
+      <c r="K14" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="L14" s="36" t="s">
+      <c r="L14" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="M14" s="35" t="s">
+      <c r="M14" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="N14" s="27">
-        <v>3</v>
-      </c>
-      <c r="O14" s="27">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="37"/>
+      <c r="N14" s="28">
+        <v>3</v>
+      </c>
+      <c r="O14" s="28">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="38"/>
     </row>
     <row r="15" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A15" s="38" t="str">
-        <f t="shared" si="1"/>
+      <c r="A15" s="39" t="str">
+        <f t="shared" si="0"/>
         <v>1007001</v>
       </c>
-      <c r="B15" s="39">
+      <c r="B15" s="40">
         <v>100700</v>
       </c>
-      <c r="C15" s="39">
-        <v>1</v>
-      </c>
-      <c r="D15" s="39" t="s">
+      <c r="C15" s="40">
+        <v>1</v>
+      </c>
+      <c r="D15" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="39" t="s">
+      <c r="E15" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="39">
-        <v>1</v>
-      </c>
-      <c r="G15" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="H15" s="38">
+      <c r="F15" s="40">
+        <v>1</v>
+      </c>
+      <c r="G15" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="39">
         <v>2007001</v>
       </c>
-      <c r="I15" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="J15" s="38"/>
-      <c r="K15" s="38"/>
-      <c r="L15" s="40" t="s">
+      <c r="I15" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" s="39"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="M15" s="38" t="s">
+      <c r="M15" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="N15" s="18">
+      <c r="N15" s="19">
         <v>4</v>
       </c>
-      <c r="O15" s="18">
+      <c r="O15" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="16" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A16" s="38" t="str">
-        <f t="shared" si="1"/>
+      <c r="A16" s="39" t="str">
+        <f t="shared" si="0"/>
         <v>1007002</v>
       </c>
-      <c r="B16" s="39">
+      <c r="B16" s="40">
         <v>100700</v>
       </c>
-      <c r="C16" s="39">
+      <c r="C16" s="40">
         <v>2</v>
       </c>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39" t="s">
+      <c r="D16" s="40"/>
+      <c r="E16" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="39">
-        <v>1</v>
-      </c>
-      <c r="G16" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="H16" s="38">
+      <c r="F16" s="40">
+        <v>1</v>
+      </c>
+      <c r="G16" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="39">
         <v>2007001</v>
       </c>
-      <c r="I16" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="J16" s="38"/>
-      <c r="K16" s="38"/>
-      <c r="L16" s="40" t="s">
+      <c r="I16" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="J16" s="39"/>
+      <c r="K16" s="39"/>
+      <c r="L16" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="M16" s="38" t="s">
+      <c r="M16" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="N16" s="18">
+      <c r="N16" s="19">
         <v>4</v>
       </c>
-      <c r="O16" s="18">
+      <c r="O16" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="17" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A17" s="41" t="str">
-        <f t="shared" si="1"/>
+      <c r="A17" s="42" t="str">
+        <f t="shared" si="0"/>
         <v>1012001</v>
       </c>
-      <c r="B17" s="42">
+      <c r="B17" s="43">
         <v>101200</v>
       </c>
-      <c r="C17" s="42">
-        <v>1</v>
-      </c>
-      <c r="D17" s="42" t="s">
+      <c r="C17" s="43">
+        <v>1</v>
+      </c>
+      <c r="D17" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="E17" s="42" t="s">
+      <c r="E17" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="42">
-        <v>1</v>
-      </c>
-      <c r="G17" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="H17" s="41">
+      <c r="F17" s="43">
+        <v>1</v>
+      </c>
+      <c r="G17" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="42">
         <v>2012001</v>
       </c>
-      <c r="I17" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="J17" s="41"/>
-      <c r="K17" s="41"/>
-      <c r="L17" s="43">
+      <c r="I17" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="J17" s="42"/>
+      <c r="K17" s="42"/>
+      <c r="L17" s="44">
         <v>10120011</v>
       </c>
-      <c r="M17" s="41" t="s">
+      <c r="M17" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="N17" s="42">
-        <v>3</v>
-      </c>
-      <c r="O17" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q17" s="44"/>
+      <c r="N17" s="43">
+        <v>3</v>
+      </c>
+      <c r="O17" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="45"/>
     </row>
     <row r="18" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A18" s="41" t="str">
-        <f t="shared" si="1"/>
+      <c r="A18" s="42" t="str">
+        <f t="shared" si="0"/>
         <v>1012002</v>
       </c>
-      <c r="B18" s="42">
+      <c r="B18" s="43">
         <v>101200</v>
       </c>
-      <c r="C18" s="42">
+      <c r="C18" s="43">
         <v>2</v>
       </c>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42" t="s">
+      <c r="D18" s="43"/>
+      <c r="E18" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="42">
-        <v>1</v>
-      </c>
-      <c r="G18" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="H18" s="41">
+      <c r="F18" s="43">
+        <v>1</v>
+      </c>
+      <c r="G18" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="42">
         <v>2012001</v>
       </c>
-      <c r="I18" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="J18" s="41"/>
-      <c r="K18" s="41"/>
-      <c r="L18" s="43">
+      <c r="I18" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="J18" s="42"/>
+      <c r="K18" s="42"/>
+      <c r="L18" s="44">
         <v>10120021</v>
       </c>
-      <c r="M18" s="41" t="s">
+      <c r="M18" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="N18" s="42">
-        <v>3</v>
-      </c>
-      <c r="O18" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q18" s="44"/>
+      <c r="N18" s="43">
+        <v>3</v>
+      </c>
+      <c r="O18" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="45"/>
     </row>
     <row r="19" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A19" s="41" t="str">
-        <f t="shared" si="1"/>
+      <c r="A19" s="42" t="str">
+        <f t="shared" si="0"/>
         <v>1012003</v>
       </c>
-      <c r="B19" s="42">
+      <c r="B19" s="43">
         <v>101200</v>
       </c>
-      <c r="C19" s="42">
-        <v>3</v>
-      </c>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42" t="s">
+      <c r="C19" s="43">
+        <v>3</v>
+      </c>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="F19" s="42">
-        <v>1</v>
-      </c>
-      <c r="G19" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="H19" s="41">
+      <c r="F19" s="43">
+        <v>1</v>
+      </c>
+      <c r="G19" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="42">
         <v>2012001</v>
       </c>
-      <c r="I19" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="J19" s="41" t="s">
+      <c r="I19" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="J19" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="K19" s="41" t="s">
+      <c r="K19" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="L19" s="43"/>
-      <c r="M19" s="41" t="s">
+      <c r="L19" s="44"/>
+      <c r="M19" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="N19" s="42">
-        <v>3</v>
-      </c>
-      <c r="O19" s="42">
-        <v>5</v>
-      </c>
-      <c r="Q19" s="44"/>
+      <c r="N19" s="43">
+        <v>3</v>
+      </c>
+      <c r="O19" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q19" s="45"/>
     </row>
     <row r="20" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A20" s="35" t="str">
-        <f t="shared" si="1"/>
+      <c r="A20" s="36" t="str">
+        <f t="shared" ref="A20:A30" si="1">B20&amp;C20</f>
         <v>1014001</v>
       </c>
-      <c r="B20" s="27">
+      <c r="B20" s="28">
         <v>101400</v>
       </c>
-      <c r="C20" s="27">
-        <v>1</v>
-      </c>
-      <c r="D20" s="27" t="s">
+      <c r="C20" s="28">
+        <v>1</v>
+      </c>
+      <c r="D20" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="E20" s="27" t="s">
+      <c r="E20" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="F20" s="27">
-        <v>1</v>
-      </c>
-      <c r="G20" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="H20" s="35">
+      <c r="F20" s="28">
+        <v>1</v>
+      </c>
+      <c r="G20" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="36">
         <v>2014001</v>
       </c>
-      <c r="I20" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="J20" s="35"/>
-      <c r="K20" s="35"/>
-      <c r="L20" s="36" t="s">
+      <c r="I20" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="J20" s="36"/>
+      <c r="K20" s="36"/>
+      <c r="L20" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="M20" s="35" t="s">
+      <c r="M20" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="N20" s="18">
+      <c r="N20" s="19">
         <v>4</v>
       </c>
-      <c r="O20" s="18">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="45"/>
+      <c r="O20" s="19">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="46"/>
     </row>
     <row r="21" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A21" s="35" t="str">
+      <c r="A21" s="36" t="str">
         <f t="shared" si="1"/>
         <v>1014002</v>
       </c>
-      <c r="B21" s="27">
+      <c r="B21" s="28">
         <v>101400</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="28">
         <v>2</v>
       </c>
-      <c r="D21" s="27" t="s">
+      <c r="D21" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="E21" s="27" t="s">
+      <c r="E21" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="27">
-        <v>1</v>
-      </c>
-      <c r="G21" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="H21" s="35">
+      <c r="F21" s="28">
+        <v>1</v>
+      </c>
+      <c r="G21" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="36">
         <v>2014001</v>
       </c>
-      <c r="I21" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="J21" s="35"/>
-      <c r="K21" s="35"/>
-      <c r="L21" s="36" t="s">
+      <c r="I21" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="J21" s="36"/>
+      <c r="K21" s="36"/>
+      <c r="L21" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="M21" s="35" t="s">
+      <c r="M21" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="N21" s="18">
+      <c r="N21" s="19">
         <v>4</v>
       </c>
-      <c r="O21" s="18">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="45"/>
+      <c r="O21" s="19">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="46"/>
     </row>
     <row r="22" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A22" s="35" t="str">
+      <c r="A22" s="36" t="str">
         <f t="shared" si="1"/>
         <v>1014003</v>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="28">
         <v>101400</v>
       </c>
-      <c r="C22" s="27">
-        <v>3</v>
-      </c>
-      <c r="D22" s="27" t="s">
+      <c r="C22" s="28">
+        <v>3</v>
+      </c>
+      <c r="D22" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="E22" s="27" t="s">
+      <c r="E22" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="F22" s="27">
-        <v>1</v>
-      </c>
-      <c r="G22" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="H22" s="35">
+      <c r="F22" s="28">
+        <v>1</v>
+      </c>
+      <c r="G22" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="36">
         <v>2014001</v>
       </c>
-      <c r="I22" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="J22" s="35"/>
-      <c r="K22" s="35"/>
-      <c r="L22" s="36">
+      <c r="I22" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="J22" s="36"/>
+      <c r="K22" s="36"/>
+      <c r="L22" s="37">
         <v>10140021</v>
       </c>
-      <c r="M22" s="35" t="s">
+      <c r="M22" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="N22" s="18">
+      <c r="N22" s="19">
         <v>4</v>
       </c>
-      <c r="O22" s="18">
-        <v>3</v>
-      </c>
-      <c r="Q22" s="45"/>
+      <c r="O22" s="19">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="46"/>
     </row>
     <row r="23" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A23" s="25" t="str">
+      <c r="A23" s="26" t="str">
         <f t="shared" si="1"/>
         <v>1024001</v>
       </c>
-      <c r="B23" s="26">
+      <c r="B23" s="27">
         <v>102400</v>
       </c>
-      <c r="C23" s="26">
-        <v>1</v>
-      </c>
-      <c r="D23" s="26" t="s">
+      <c r="C23" s="27">
+        <v>1</v>
+      </c>
+      <c r="D23" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="E23" s="27" t="s">
+      <c r="E23" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="F23" s="26">
-        <v>1</v>
-      </c>
-      <c r="G23" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H23" s="25">
+      <c r="F23" s="27">
+        <v>1</v>
+      </c>
+      <c r="G23" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="26">
         <v>2024001</v>
       </c>
-      <c r="I23" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="J23" s="25"/>
-      <c r="K23" s="25"/>
-      <c r="L23" s="28" t="s">
+      <c r="I23" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="M23" s="25" t="s">
+      <c r="M23" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="N23" s="18">
+      <c r="N23" s="19">
         <v>4</v>
       </c>
-      <c r="O23" s="18">
+      <c r="O23" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A24" s="25" t="str">
+      <c r="A24" s="26" t="str">
         <f t="shared" si="1"/>
         <v>1024002</v>
       </c>
-      <c r="B24" s="26">
+      <c r="B24" s="27">
         <v>102400</v>
       </c>
-      <c r="C24" s="26">
+      <c r="C24" s="27">
         <v>2</v>
       </c>
-      <c r="D24" s="26"/>
-      <c r="E24" s="29" t="s">
+      <c r="D24" s="27"/>
+      <c r="E24" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="26">
-        <v>1</v>
-      </c>
-      <c r="G24" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H24" s="25">
+      <c r="F24" s="27">
+        <v>1</v>
+      </c>
+      <c r="G24" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" s="26">
         <v>2024001</v>
       </c>
-      <c r="I24" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="J24" s="25"/>
-      <c r="K24" s="25"/>
-      <c r="L24" s="30" t="s">
+      <c r="I24" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J24" s="26"/>
+      <c r="K24" s="26"/>
+      <c r="L24" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="M24" s="25" t="s">
+      <c r="M24" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="N24" s="18">
+      <c r="N24" s="19">
         <v>4</v>
       </c>
-      <c r="O24" s="18">
+      <c r="O24" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A25" s="25" t="str">
+      <c r="A25" s="26" t="str">
         <f t="shared" si="1"/>
         <v>1024003</v>
       </c>
-      <c r="B25" s="26">
+      <c r="B25" s="27">
         <v>102400</v>
       </c>
-      <c r="C25" s="26">
-        <v>3</v>
-      </c>
-      <c r="D25" s="26"/>
-      <c r="E25" s="31" t="s">
+      <c r="C25" s="27">
+        <v>3</v>
+      </c>
+      <c r="D25" s="27"/>
+      <c r="E25" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F25" s="26">
-        <v>1</v>
-      </c>
-      <c r="G25" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H25" s="25">
+      <c r="F25" s="27">
+        <v>1</v>
+      </c>
+      <c r="G25" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="26">
         <v>2024001</v>
       </c>
-      <c r="I25" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="J25" s="25"/>
-      <c r="K25" s="25"/>
-      <c r="L25" s="28" t="s">
+      <c r="I25" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J25" s="26"/>
+      <c r="K25" s="26"/>
+      <c r="L25" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="M25" s="25" t="s">
+      <c r="M25" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="N25" s="18">
+      <c r="N25" s="19">
         <v>4</v>
       </c>
-      <c r="O25" s="18">
+      <c r="O25" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A26" s="25" t="str">
+      <c r="A26" s="26" t="str">
         <f t="shared" si="1"/>
         <v>1024004</v>
       </c>
-      <c r="B26" s="26">
+      <c r="B26" s="27">
         <v>102400</v>
       </c>
-      <c r="C26" s="26">
+      <c r="C26" s="27">
         <v>4</v>
       </c>
-      <c r="D26" s="26"/>
-      <c r="E26" s="32" t="s">
+      <c r="D26" s="27"/>
+      <c r="E26" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="F26" s="33">
-        <v>1</v>
-      </c>
-      <c r="G26" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H26" s="25">
+      <c r="F26" s="34">
+        <v>1</v>
+      </c>
+      <c r="G26" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="26">
         <v>2024001</v>
       </c>
-      <c r="I26" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="J26" s="25"/>
-      <c r="K26" s="25"/>
-      <c r="L26" s="28">
+      <c r="I26" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J26" s="26"/>
+      <c r="K26" s="26"/>
+      <c r="L26" s="29">
         <v>10240041</v>
       </c>
-      <c r="M26" s="25" t="s">
+      <c r="M26" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="N26" s="18">
+      <c r="N26" s="19">
         <v>4</v>
       </c>
-      <c r="O26" s="18">
+      <c r="O26" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A27" s="25" t="str">
+      <c r="A27" s="26" t="str">
         <f t="shared" si="1"/>
         <v>1024005</v>
       </c>
-      <c r="B27" s="26">
+      <c r="B27" s="27">
         <v>102400</v>
       </c>
-      <c r="C27" s="26">
-        <v>5</v>
-      </c>
-      <c r="D27" s="26"/>
-      <c r="E27" s="34" t="s">
+      <c r="C27" s="27">
+        <v>5</v>
+      </c>
+      <c r="D27" s="27"/>
+      <c r="E27" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="F27" s="33">
-        <v>1</v>
-      </c>
-      <c r="G27" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H27" s="25">
+      <c r="F27" s="34">
+        <v>1</v>
+      </c>
+      <c r="G27" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H27" s="26">
         <v>2024001</v>
       </c>
-      <c r="I27" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="J27" s="25"/>
-      <c r="K27" s="25"/>
-      <c r="L27" s="28" t="s">
+      <c r="I27" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J27" s="26"/>
+      <c r="K27" s="26"/>
+      <c r="L27" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="M27" s="25" t="s">
+      <c r="M27" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="N27" s="18">
+      <c r="N27" s="19">
         <v>4</v>
       </c>
-      <c r="O27" s="18">
+      <c r="O27" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A28" s="25" t="str">
+      <c r="A28" s="26" t="str">
         <f t="shared" si="1"/>
         <v>1024006</v>
       </c>
-      <c r="B28" s="26">
+      <c r="B28" s="27">
         <v>102400</v>
       </c>
-      <c r="C28" s="26">
+      <c r="C28" s="27">
         <v>6</v>
       </c>
-      <c r="D28" s="26"/>
-      <c r="E28" s="34" t="s">
+      <c r="D28" s="27"/>
+      <c r="E28" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="F28" s="33">
-        <v>1</v>
-      </c>
-      <c r="G28" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H28" s="25">
+      <c r="F28" s="34">
+        <v>1</v>
+      </c>
+      <c r="G28" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28" s="26">
         <v>2024001</v>
       </c>
-      <c r="I28" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="J28" s="25"/>
-      <c r="K28" s="25"/>
-      <c r="L28" s="28">
+      <c r="I28" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J28" s="26"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="29">
         <v>10240061</v>
       </c>
-      <c r="M28" s="25" t="s">
+      <c r="M28" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="N28" s="18">
+      <c r="N28" s="19">
         <v>4</v>
       </c>
-      <c r="O28" s="18">
+      <c r="O28" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A29" s="25" t="str">
+      <c r="A29" s="26" t="str">
         <f t="shared" si="1"/>
         <v>1024007</v>
       </c>
-      <c r="B29" s="26">
+      <c r="B29" s="27">
         <v>102400</v>
       </c>
-      <c r="C29" s="26">
+      <c r="C29" s="27">
         <v>7</v>
       </c>
-      <c r="D29" s="26"/>
-      <c r="E29" s="29" t="s">
+      <c r="D29" s="27"/>
+      <c r="E29" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="F29" s="26">
-        <v>1</v>
-      </c>
-      <c r="G29" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H29" s="25">
+      <c r="F29" s="27">
+        <v>1</v>
+      </c>
+      <c r="G29" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H29" s="26">
         <v>2024001</v>
       </c>
-      <c r="I29" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="J29" s="25"/>
-      <c r="K29" s="25"/>
-      <c r="L29" s="30" t="s">
+      <c r="I29" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J29" s="26"/>
+      <c r="K29" s="26"/>
+      <c r="L29" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="M29" s="25" t="s">
+      <c r="M29" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="N29" s="18">
+      <c r="N29" s="19">
         <v>4</v>
       </c>
-      <c r="O29" s="18">
+      <c r="O29" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="30" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A30" s="25" t="str">
+      <c r="A30" s="26" t="str">
         <f t="shared" si="1"/>
         <v>1017001</v>
       </c>
@@ -3471,17 +3477,17 @@
       <c r="M30" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="N30" s="46">
+      <c r="N30" s="47">
         <v>4</v>
       </c>
-      <c r="O30" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q30" s="19"/>
+      <c r="O30" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q30" s="20"/>
     </row>
     <row r="31" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A31" s="25" t="str">
-        <f t="shared" ref="A31:A53" si="2">B31&amp;C31</f>
+      <c r="A31" s="26" t="str">
+        <f t="shared" ref="A31:A54" si="2">B31&amp;C31</f>
         <v>1017002</v>
       </c>
       <c r="B31" s="5">
@@ -3514,16 +3520,16 @@
       <c r="M31" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="N31" s="46">
+      <c r="N31" s="47">
         <v>4</v>
       </c>
-      <c r="O31" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q31" s="19"/>
+      <c r="O31" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q31" s="20"/>
     </row>
     <row r="32" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A32" s="25" t="str">
+      <c r="A32" s="26" t="str">
         <f t="shared" si="2"/>
         <v>1017003</v>
       </c>
@@ -3557,16 +3563,16 @@
       <c r="M32" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N32" s="46">
+      <c r="N32" s="47">
         <v>4</v>
       </c>
-      <c r="O32" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q32" s="19"/>
+      <c r="O32" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="20"/>
     </row>
     <row r="33" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A33" s="25" t="str">
+      <c r="A33" s="26" t="str">
         <f t="shared" si="2"/>
         <v>1022001</v>
       </c>
@@ -3594,22 +3600,22 @@
       <c r="I33" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L33" s="47" t="s">
+      <c r="L33" s="48" t="s">
         <v>85</v>
       </c>
       <c r="M33" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N33" s="46">
-        <v>3</v>
-      </c>
-      <c r="O33" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q33" s="19"/>
+      <c r="N33" s="47">
+        <v>3</v>
+      </c>
+      <c r="O33" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q33" s="20"/>
     </row>
     <row r="34" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A34" s="25" t="str">
+      <c r="A34" s="26" t="str">
         <f t="shared" si="2"/>
         <v>1022002</v>
       </c>
@@ -3625,10 +3631,10 @@
       <c r="E34" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="F34" s="18">
-        <v>1</v>
-      </c>
-      <c r="G34" s="48" t="s">
+      <c r="F34" s="19">
+        <v>1</v>
+      </c>
+      <c r="G34" s="49" t="s">
         <v>23</v>
       </c>
       <c r="H34" s="5">
@@ -3637,22 +3643,22 @@
       <c r="I34" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L34" s="47">
+      <c r="L34" s="48">
         <v>10220033</v>
       </c>
       <c r="M34" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N34" s="46">
-        <v>3</v>
-      </c>
-      <c r="O34" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q34" s="19"/>
+      <c r="N34" s="47">
+        <v>3</v>
+      </c>
+      <c r="O34" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q34" s="20"/>
     </row>
     <row r="35" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A35" s="25" t="str">
+      <c r="A35" s="26" t="str">
         <f t="shared" si="2"/>
         <v>1022003</v>
       </c>
@@ -3668,10 +3674,10 @@
       <c r="E35" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F35" s="48">
-        <v>1</v>
-      </c>
-      <c r="G35" s="48" t="s">
+      <c r="F35" s="49">
+        <v>1</v>
+      </c>
+      <c r="G35" s="49" t="s">
         <v>23</v>
       </c>
       <c r="H35" s="5">
@@ -3680,22 +3686,22 @@
       <c r="I35" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L35" s="49" t="s">
+      <c r="L35" s="50" t="s">
         <v>89</v>
       </c>
       <c r="M35" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N35" s="46">
-        <v>3</v>
-      </c>
-      <c r="O35" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q35" s="19"/>
+      <c r="N35" s="47">
+        <v>3</v>
+      </c>
+      <c r="O35" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q35" s="20"/>
     </row>
     <row r="36" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A36" s="25" t="str">
+      <c r="A36" s="26" t="str">
         <f t="shared" si="2"/>
         <v>1022004</v>
       </c>
@@ -3711,10 +3717,10 @@
       <c r="E36" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F36" s="18">
-        <v>1</v>
-      </c>
-      <c r="G36" s="48" t="s">
+      <c r="F36" s="19">
+        <v>1</v>
+      </c>
+      <c r="G36" s="49" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="5">
@@ -3723,19 +3729,19 @@
       <c r="I36" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L36" s="47">
+      <c r="L36" s="48">
         <v>10220020</v>
       </c>
-      <c r="N36" s="46">
-        <v>3</v>
-      </c>
-      <c r="O36" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q36" s="19"/>
+      <c r="N36" s="47">
+        <v>3</v>
+      </c>
+      <c r="O36" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q36" s="20"/>
     </row>
     <row r="37" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A37" s="25" t="str">
+      <c r="A37" s="26" t="str">
         <f t="shared" si="2"/>
         <v>1022005</v>
       </c>
@@ -3763,20 +3769,20 @@
       <c r="I37" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L37" s="47">
+      <c r="L37" s="48">
         <v>10220019</v>
       </c>
-      <c r="N37" s="46">
-        <v>3</v>
-      </c>
-      <c r="O37" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q37" s="19"/>
-      <c r="S37" s="50"/>
+      <c r="N37" s="47">
+        <v>3</v>
+      </c>
+      <c r="O37" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q37" s="20"/>
+      <c r="S37" s="51"/>
     </row>
     <row r="38" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A38" s="25" t="str">
+      <c r="A38" s="26" t="str">
         <f t="shared" si="2"/>
         <v>1021001</v>
       </c>
@@ -3804,23 +3810,23 @@
       <c r="I38" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L38" s="47" t="s">
+      <c r="L38" s="48" t="s">
         <v>93</v>
       </c>
       <c r="M38" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N38" s="46">
-        <v>3</v>
-      </c>
-      <c r="O38" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q38" s="19"/>
-      <c r="S38" s="50"/>
+      <c r="N38" s="47">
+        <v>3</v>
+      </c>
+      <c r="O38" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q38" s="20"/>
+      <c r="S38" s="51"/>
     </row>
     <row r="39" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A39" s="25" t="str">
+      <c r="A39" s="26" t="str">
         <f t="shared" si="2"/>
         <v>1021002</v>
       </c>
@@ -3848,23 +3854,23 @@
       <c r="I39" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L39" s="47">
+      <c r="L39" s="48">
         <v>10210031</v>
       </c>
       <c r="M39" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N39" s="46">
-        <v>3</v>
-      </c>
-      <c r="O39" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q39" s="19"/>
-      <c r="S39" s="50"/>
+      <c r="N39" s="47">
+        <v>3</v>
+      </c>
+      <c r="O39" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q39" s="20"/>
+      <c r="S39" s="51"/>
     </row>
     <row r="40" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A40" s="25" t="str">
+      <c r="A40" s="26" t="str">
         <f t="shared" si="2"/>
         <v>1021003</v>
       </c>
@@ -3892,23 +3898,23 @@
       <c r="I40" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L40" s="47">
+      <c r="L40" s="48">
         <v>10210041</v>
       </c>
       <c r="M40" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="N40" s="46">
-        <v>3</v>
-      </c>
-      <c r="O40" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q40" s="19"/>
-      <c r="S40" s="50"/>
+      <c r="N40" s="47">
+        <v>3</v>
+      </c>
+      <c r="O40" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q40" s="20"/>
+      <c r="S40" s="51"/>
     </row>
     <row r="41" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A41" s="25" t="str">
+      <c r="A41" s="26" t="str">
         <f t="shared" si="2"/>
         <v>1021004</v>
       </c>
@@ -3936,23 +3942,23 @@
       <c r="I41" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L41" s="47" t="s">
+      <c r="L41" s="48" t="s">
         <v>96</v>
       </c>
       <c r="M41" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N41" s="46">
-        <v>3</v>
-      </c>
-      <c r="O41" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q41" s="19"/>
-      <c r="S41" s="50"/>
+      <c r="N41" s="47">
+        <v>3</v>
+      </c>
+      <c r="O41" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q41" s="20"/>
+      <c r="S41" s="51"/>
     </row>
     <row r="42" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A42" s="25" t="str">
+      <c r="A42" s="26" t="str">
         <f t="shared" si="2"/>
         <v>1018001</v>
       </c>
@@ -3980,20 +3986,20 @@
       <c r="I42" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L42" s="47" t="s">
+      <c r="L42" s="48" t="s">
         <v>98</v>
       </c>
       <c r="M42" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N42" s="46">
+      <c r="N42" s="47">
         <v>4</v>
       </c>
-      <c r="O42" s="46">
+      <c r="O42" s="47">
         <v>6</v>
       </c>
-      <c r="Q42" s="19"/>
-      <c r="S42" s="50"/>
+      <c r="Q42" s="20"/>
+      <c r="S42" s="51"/>
     </row>
     <row r="43" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A43" s="5" t="str">
@@ -4024,16 +4030,16 @@
       <c r="I43" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L43" s="47">
+      <c r="L43" s="48">
         <v>10180031</v>
       </c>
       <c r="M43" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N43" s="46">
+      <c r="N43" s="47">
         <v>4</v>
       </c>
-      <c r="O43" s="46">
+      <c r="O43" s="47">
         <v>6</v>
       </c>
     </row>
@@ -4066,16 +4072,16 @@
       <c r="I44" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L44" s="47" t="s">
+      <c r="L44" s="48" t="s">
         <v>99</v>
       </c>
       <c r="M44" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N44" s="46">
+      <c r="N44" s="47">
         <v>4</v>
       </c>
-      <c r="O44" s="46">
+      <c r="O44" s="47">
         <v>6</v>
       </c>
     </row>
@@ -4108,19 +4114,19 @@
       <c r="I45" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L45" s="47" t="s">
+      <c r="L45" s="48" t="s">
         <v>101</v>
       </c>
       <c r="M45" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N45" s="46">
-        <v>3</v>
-      </c>
-      <c r="O45" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q45" s="9"/>
+      <c r="N45" s="47">
+        <v>3</v>
+      </c>
+      <c r="O45" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q45" s="10"/>
     </row>
     <row r="46" customFormat="1" ht="16.5" spans="1:19">
       <c r="A46" s="5" t="str">
@@ -4151,19 +4157,19 @@
       <c r="I46" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L46" s="47">
+      <c r="L46" s="48">
         <v>10250031</v>
       </c>
       <c r="M46" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="N46" s="46">
-        <v>3</v>
-      </c>
-      <c r="O46" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q46" s="9"/>
+      <c r="N46" s="47">
+        <v>3</v>
+      </c>
+      <c r="O46" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q46" s="10"/>
     </row>
     <row r="47" customFormat="1" ht="16.5" spans="1:19">
       <c r="A47" s="5" t="str">
@@ -4194,19 +4200,19 @@
       <c r="I47" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L47" s="47" t="s">
+      <c r="L47" s="48" t="s">
         <v>103</v>
       </c>
       <c r="M47" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N47" s="46">
-        <v>3</v>
-      </c>
-      <c r="O47" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q47" s="9"/>
+      <c r="N47" s="47">
+        <v>3</v>
+      </c>
+      <c r="O47" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q47" s="10"/>
     </row>
     <row r="48" customFormat="1" ht="16.5" spans="1:19">
       <c r="A48" s="5" t="str">
@@ -4237,19 +4243,19 @@
       <c r="I48" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L48" s="47" t="s">
+      <c r="L48" s="48" t="s">
         <v>105</v>
       </c>
       <c r="M48" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N48" s="46">
+      <c r="N48" s="47">
         <v>4</v>
       </c>
-      <c r="O48" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q48" s="9"/>
+      <c r="O48" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q48" s="10"/>
     </row>
     <row r="49" customFormat="1" ht="16.5" spans="1:17">
       <c r="A49" s="5" t="str">
@@ -4280,19 +4286,19 @@
       <c r="I49" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L49" s="47">
+      <c r="L49" s="48">
         <v>10230003</v>
       </c>
       <c r="M49" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="N49" s="46">
+      <c r="N49" s="47">
         <v>4</v>
       </c>
-      <c r="O49" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q49" s="9"/>
+      <c r="O49" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q49" s="10"/>
     </row>
     <row r="50" customFormat="1" ht="16.5" spans="1:17">
       <c r="A50" s="5" t="str">
@@ -4323,19 +4329,19 @@
       <c r="I50" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L50" s="47" t="s">
+      <c r="L50" s="48" t="s">
         <v>106</v>
       </c>
       <c r="M50" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N50" s="46">
+      <c r="N50" s="47">
         <v>4</v>
       </c>
-      <c r="O50" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q50" s="9"/>
+      <c r="O50" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q50" s="10"/>
     </row>
     <row r="51" customFormat="1" ht="16.5" spans="1:17">
       <c r="A51" s="5" t="str">
@@ -4366,19 +4372,19 @@
       <c r="I51" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L51" s="47">
+      <c r="L51" s="48">
         <v>10340007</v>
       </c>
       <c r="M51" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="N51" s="46">
-        <v>3</v>
-      </c>
-      <c r="O51" s="46">
-        <v>3</v>
-      </c>
-      <c r="Q51" s="9"/>
+      <c r="N51" s="47">
+        <v>3</v>
+      </c>
+      <c r="O51" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q51" s="10"/>
     </row>
     <row r="52" customFormat="1" ht="16.5" spans="1:17">
       <c r="A52" s="5" t="str">
@@ -4409,18 +4415,18 @@
       <c r="I52" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L52" s="47"/>
+      <c r="L52" s="48"/>
       <c r="M52" s="5"/>
-      <c r="N52" s="46">
-        <v>3</v>
-      </c>
-      <c r="O52" s="46">
-        <v>3</v>
-      </c>
-      <c r="P52" s="51"/>
-      <c r="Q52" s="9"/>
-    </row>
-    <row r="53" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N52" s="47">
+        <v>3</v>
+      </c>
+      <c r="O52" s="47">
+        <v>3</v>
+      </c>
+      <c r="P52" s="52"/>
+      <c r="Q52" s="10"/>
+    </row>
+    <row r="53" s="6" customFormat="1" ht="16.5" spans="1:17">
       <c r="A53" s="5" t="str">
         <f t="shared" si="2"/>
         <v>1034003</v>
@@ -4437,7 +4443,7 @@
       <c r="E53" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F53" s="5">
+      <c r="F53" s="53">
         <v>1</v>
       </c>
       <c r="G53" s="5" t="s">
@@ -4449,62 +4455,62 @@
       <c r="I53" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L53" s="47"/>
-      <c r="M53" s="5"/>
-      <c r="N53" s="46">
-        <v>3</v>
-      </c>
-      <c r="O53" s="46">
-        <v>3</v>
-      </c>
-      <c r="Q53" s="9"/>
-    </row>
-    <row r="54" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A54" s="5" t="str">
-        <f t="shared" ref="A54:A83" si="3">B54&amp;C54</f>
+      <c r="L53" s="50"/>
+      <c r="M53" s="53"/>
+      <c r="N53" s="47">
+        <v>3</v>
+      </c>
+      <c r="O53" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q53" s="54"/>
+    </row>
+    <row r="54" s="6" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A54" s="53" t="str">
+        <f t="shared" si="2"/>
         <v>1035001</v>
       </c>
-      <c r="B54" s="5">
+      <c r="B54" s="53">
         <v>103500</v>
       </c>
-      <c r="C54" s="5">
-        <v>1</v>
-      </c>
-      <c r="D54" s="5" t="s">
+      <c r="C54" s="53">
+        <v>1</v>
+      </c>
+      <c r="D54" s="53" t="s">
         <v>110</v>
       </c>
-      <c r="E54" s="5" t="s">
+      <c r="E54" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="F54" s="5">
-        <v>1</v>
-      </c>
-      <c r="G54" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H54" s="5">
+      <c r="F54" s="53">
+        <v>1</v>
+      </c>
+      <c r="G54" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="H54" s="53">
         <v>2035001</v>
       </c>
-      <c r="I54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L54" s="47" t="s">
+      <c r="I54" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="L54" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="M54" s="5" t="s">
+      <c r="M54" s="53" t="s">
         <v>113</v>
       </c>
-      <c r="N54" s="46">
+      <c r="N54" s="47">
         <v>4</v>
       </c>
-      <c r="O54" s="46">
-        <v>3</v>
-      </c>
-      <c r="Q54" s="9"/>
+      <c r="O54" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="54"/>
     </row>
     <row r="55" customFormat="1" ht="16.5" spans="1:17">
       <c r="A55" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="A54:A108" si="3">B55&amp;C55</f>
         <v>1035002</v>
       </c>
       <c r="B55" s="5">
@@ -4531,19 +4537,19 @@
       <c r="I55" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L55" s="47" t="s">
+      <c r="L55" s="48" t="s">
         <v>115</v>
       </c>
       <c r="M55" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="N55" s="46">
+      <c r="N55" s="47">
         <v>4</v>
       </c>
-      <c r="O55" s="46">
-        <v>3</v>
-      </c>
-      <c r="Q55" s="9"/>
+      <c r="O55" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q55" s="10"/>
     </row>
     <row r="56" customFormat="1" ht="16.5" spans="1:17">
       <c r="A56" s="5" t="str">
@@ -4574,23 +4580,22 @@
       <c r="I56" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L56" s="47" t="s">
+      <c r="L56" s="48" t="s">
         <v>117</v>
       </c>
       <c r="M56" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="N56" s="46">
+      <c r="N56" s="47">
         <v>4</v>
       </c>
-      <c r="O56" s="46">
-        <v>3</v>
-      </c>
-      <c r="Q56" s="9"/>
+      <c r="O56" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q56" s="10"/>
     </row>
     <row r="57" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A57" s="5" t="str">
-        <f t="shared" si="3"/>
+      <c r="A57" s="55">
         <v>1035011</v>
       </c>
       <c r="B57" s="5">
@@ -4617,19 +4622,19 @@
       <c r="I57" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L57" s="47" t="s">
+      <c r="L57" s="48" t="s">
         <v>120</v>
       </c>
       <c r="M57" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="N57" s="46">
+      <c r="N57" s="47">
         <v>4</v>
       </c>
-      <c r="O57" s="46">
-        <v>3</v>
-      </c>
-      <c r="Q57" s="9"/>
+      <c r="O57" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="10"/>
     </row>
     <row r="58" customFormat="1" ht="16.5" spans="1:17">
       <c r="A58" s="5" t="str">
@@ -4660,19 +4665,19 @@
       <c r="I58" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L58" s="47" t="s">
+      <c r="L58" s="48" t="s">
         <v>121</v>
       </c>
       <c r="M58" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="N58" s="46">
+      <c r="N58" s="47">
         <v>4</v>
       </c>
-      <c r="O58" s="46">
-        <v>3</v>
-      </c>
-      <c r="Q58" s="9"/>
+      <c r="O58" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="10"/>
     </row>
     <row r="59" customFormat="1" ht="16.5" spans="1:17">
       <c r="A59" s="5" t="str">
@@ -4703,19 +4708,19 @@
       <c r="I59" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L59" s="47" t="s">
+      <c r="L59" s="48" t="s">
         <v>122</v>
       </c>
       <c r="M59" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="N59" s="46">
+      <c r="N59" s="47">
         <v>4</v>
       </c>
-      <c r="O59" s="46">
-        <v>3</v>
-      </c>
-      <c r="Q59" s="9"/>
+      <c r="O59" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="10"/>
     </row>
     <row r="60" customFormat="1" ht="16.5" spans="1:17">
       <c r="A60" s="5" t="str">
@@ -4746,23 +4751,23 @@
       <c r="I60" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L60" s="47" t="s">
+      <c r="L60" s="48" t="s">
         <v>124</v>
       </c>
       <c r="M60" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="N60" s="46">
-        <v>3</v>
-      </c>
-      <c r="O60" s="46">
-        <v>3</v>
-      </c>
-      <c r="Q60" s="9"/>
+      <c r="N60" s="47">
+        <v>3</v>
+      </c>
+      <c r="O60" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="10"/>
     </row>
     <row r="61" customFormat="1" ht="16.5" spans="1:17">
       <c r="A61" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f>B61&amp;C61</f>
         <v>1036002</v>
       </c>
       <c r="B61" s="5">
@@ -4789,19 +4794,19 @@
       <c r="I61" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L61" s="47">
+      <c r="L61" s="48">
         <v>10360004</v>
       </c>
       <c r="M61" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="N61" s="46">
-        <v>3</v>
-      </c>
-      <c r="O61" s="46">
-        <v>3</v>
-      </c>
-      <c r="Q61" s="9"/>
+      <c r="N61" s="47">
+        <v>3</v>
+      </c>
+      <c r="O61" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q61" s="10"/>
     </row>
     <row r="62" customFormat="1" ht="16.5" spans="1:17">
       <c r="A62" s="5" t="str">
@@ -4832,19 +4837,19 @@
       <c r="I62" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L62" s="47">
+      <c r="L62" s="48">
         <v>10360002</v>
       </c>
       <c r="M62" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="N62" s="46">
-        <v>3</v>
-      </c>
-      <c r="O62" s="46">
-        <v>3</v>
-      </c>
-      <c r="Q62" s="9"/>
+      <c r="N62" s="47">
+        <v>3</v>
+      </c>
+      <c r="O62" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="10"/>
     </row>
     <row r="63" customFormat="1" ht="16.5" spans="1:17">
       <c r="A63" s="5" t="str">
@@ -4875,19 +4880,19 @@
       <c r="I63" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L63" s="47" t="s">
+      <c r="L63" s="48" t="s">
         <v>130</v>
       </c>
       <c r="M63" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="N63" s="46">
-        <v>5</v>
-      </c>
-      <c r="O63" s="46">
+      <c r="N63" s="47">
+        <v>5</v>
+      </c>
+      <c r="O63" s="47">
         <v>6</v>
       </c>
-      <c r="Q63" s="9"/>
+      <c r="Q63" s="10"/>
     </row>
     <row r="64" customFormat="1" ht="16.5" spans="1:17">
       <c r="A64" s="5" t="str">
@@ -4918,19 +4923,19 @@
       <c r="I64" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L64" s="47">
+      <c r="L64" s="48">
         <v>10280002</v>
       </c>
       <c r="M64" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="N64" s="46">
-        <v>5</v>
-      </c>
-      <c r="O64" s="46">
+      <c r="N64" s="47">
+        <v>5</v>
+      </c>
+      <c r="O64" s="47">
         <v>6</v>
       </c>
-      <c r="Q64" s="9"/>
+      <c r="Q64" s="10"/>
     </row>
     <row r="65" customFormat="1" ht="16.5" spans="1:17">
       <c r="A65" s="5" t="str">
@@ -4961,19 +4966,19 @@
       <c r="I65" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L65" s="47" t="s">
+      <c r="L65" s="48" t="s">
         <v>133</v>
       </c>
       <c r="M65" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N65" s="46">
-        <v>5</v>
-      </c>
-      <c r="O65" s="46">
+      <c r="N65" s="47">
+        <v>5</v>
+      </c>
+      <c r="O65" s="47">
         <v>6</v>
       </c>
-      <c r="Q65" s="9"/>
+      <c r="Q65" s="10"/>
     </row>
     <row r="66" customFormat="1" ht="16.5" spans="1:17">
       <c r="A66" s="5" t="str">
@@ -5004,19 +5009,19 @@
       <c r="I66" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L66" s="47">
+      <c r="L66" s="48">
         <v>10340007</v>
       </c>
       <c r="M66" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="N66" s="46">
-        <v>3</v>
-      </c>
-      <c r="O66" s="46">
-        <v>3</v>
-      </c>
-      <c r="Q66" s="9"/>
+      <c r="N66" s="47">
+        <v>3</v>
+      </c>
+      <c r="O66" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="10"/>
     </row>
     <row r="67" customFormat="1" ht="16.5" spans="1:17">
       <c r="A67" s="5" t="str">
@@ -5047,18 +5052,18 @@
       <c r="I67" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L67" s="47"/>
+      <c r="L67" s="48"/>
       <c r="M67" s="5"/>
-      <c r="N67" s="46">
-        <v>3</v>
-      </c>
-      <c r="O67" s="46">
-        <v>3</v>
-      </c>
-      <c r="P67" s="51"/>
-      <c r="Q67" s="9"/>
-    </row>
-    <row r="68" s="6" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N67" s="47">
+        <v>3</v>
+      </c>
+      <c r="O67" s="47">
+        <v>3</v>
+      </c>
+      <c r="P67" s="52"/>
+      <c r="Q67" s="10"/>
+    </row>
+    <row r="68" s="7" customFormat="1" ht="16.5" spans="1:17">
       <c r="A68" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1034013</v>
@@ -5089,58 +5094,58 @@
       </c>
       <c r="J68"/>
       <c r="K68"/>
-      <c r="L68" s="47"/>
+      <c r="L68" s="48"/>
       <c r="M68" s="5"/>
-      <c r="N68" s="46">
-        <v>3</v>
-      </c>
-      <c r="O68" s="46">
-        <v>3</v>
-      </c>
-      <c r="Q68" s="52"/>
-    </row>
-    <row r="69" s="6" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A69" s="53" t="str">
+      <c r="N68" s="47">
+        <v>3</v>
+      </c>
+      <c r="O68" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q68" s="56"/>
+    </row>
+    <row r="69" s="7" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A69" s="57" t="str">
         <f t="shared" si="3"/>
         <v>1020001</v>
       </c>
-      <c r="B69" s="53">
+      <c r="B69" s="57">
         <v>102000</v>
       </c>
-      <c r="C69" s="53">
-        <v>1</v>
-      </c>
-      <c r="D69" s="53" t="s">
+      <c r="C69" s="57">
+        <v>1</v>
+      </c>
+      <c r="D69" s="57" t="s">
         <v>136</v>
       </c>
-      <c r="E69" s="53" t="s">
+      <c r="E69" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="F69" s="53">
-        <v>1</v>
-      </c>
-      <c r="G69" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="H69" s="53">
+      <c r="F69" s="57">
+        <v>1</v>
+      </c>
+      <c r="G69" s="57" t="s">
+        <v>23</v>
+      </c>
+      <c r="H69" s="57">
         <v>2020001</v>
       </c>
-      <c r="I69" s="53" t="s">
-        <v>24</v>
-      </c>
-      <c r="L69" s="54" t="s">
+      <c r="I69" s="57" t="s">
+        <v>24</v>
+      </c>
+      <c r="L69" s="58" t="s">
         <v>137</v>
       </c>
-      <c r="M69" s="53" t="s">
+      <c r="M69" s="57" t="s">
         <v>138</v>
       </c>
-      <c r="N69" s="55">
-        <v>5</v>
-      </c>
-      <c r="O69" s="55">
-        <v>5</v>
-      </c>
-      <c r="Q69" s="52"/>
+      <c r="N69" s="59">
+        <v>5</v>
+      </c>
+      <c r="O69" s="59">
+        <v>5</v>
+      </c>
+      <c r="Q69" s="56"/>
     </row>
     <row r="70" customFormat="1" ht="16.5" spans="1:17">
       <c r="A70" s="5" t="str">
@@ -5171,19 +5176,19 @@
       <c r="I70" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L70" s="47" t="s">
+      <c r="L70" s="48" t="s">
         <v>139</v>
       </c>
       <c r="M70" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="N70" s="46">
-        <v>5</v>
-      </c>
-      <c r="O70" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q70" s="9"/>
+      <c r="N70" s="47">
+        <v>5</v>
+      </c>
+      <c r="O70" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q70" s="10"/>
     </row>
     <row r="71" customFormat="1" ht="16.5" spans="1:17">
       <c r="A71" s="5" t="str">
@@ -5214,62 +5219,62 @@
       <c r="I71" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L71" s="47" t="s">
+      <c r="L71" s="48" t="s">
         <v>141</v>
       </c>
       <c r="M71" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="N71" s="46">
-        <v>5</v>
-      </c>
-      <c r="O71" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q71" s="9"/>
-    </row>
-    <row r="72" s="7" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A72" s="56" t="str">
+      <c r="N71" s="47">
+        <v>5</v>
+      </c>
+      <c r="O71" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q71" s="10"/>
+    </row>
+    <row r="72" s="8" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A72" s="60" t="str">
         <f t="shared" si="3"/>
         <v>1020004</v>
       </c>
-      <c r="B72" s="56">
+      <c r="B72" s="60">
         <v>102000</v>
       </c>
-      <c r="C72" s="56">
+      <c r="C72" s="60">
         <v>4</v>
       </c>
-      <c r="D72" s="56" t="s">
+      <c r="D72" s="60" t="s">
         <v>136</v>
       </c>
-      <c r="E72" s="56" t="s">
+      <c r="E72" s="60" t="s">
         <v>143</v>
       </c>
-      <c r="F72" s="56">
-        <v>1</v>
-      </c>
-      <c r="G72" s="56" t="s">
-        <v>23</v>
-      </c>
-      <c r="H72" s="56">
+      <c r="F72" s="60">
+        <v>1</v>
+      </c>
+      <c r="G72" s="60" t="s">
+        <v>23</v>
+      </c>
+      <c r="H72" s="60">
         <v>2020002</v>
       </c>
-      <c r="I72" s="56" t="s">
-        <v>24</v>
-      </c>
-      <c r="L72" s="57">
+      <c r="I72" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="L72" s="61">
         <v>10200016</v>
       </c>
-      <c r="M72" s="56" t="s">
+      <c r="M72" s="60" t="s">
         <v>144</v>
       </c>
-      <c r="N72" s="58">
-        <v>5</v>
-      </c>
-      <c r="O72" s="58">
-        <v>5</v>
-      </c>
-      <c r="Q72" s="59"/>
+      <c r="N72" s="62">
+        <v>5</v>
+      </c>
+      <c r="O72" s="62">
+        <v>5</v>
+      </c>
+      <c r="Q72" s="63"/>
     </row>
     <row r="73" customFormat="1" ht="16.5" spans="1:17">
       <c r="A73" s="5" t="str">
@@ -5300,19 +5305,19 @@
       <c r="I73" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L73" s="47">
+      <c r="L73" s="48">
         <v>10200021</v>
       </c>
       <c r="M73" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="N73" s="46">
-        <v>5</v>
-      </c>
-      <c r="O73" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q73" s="9"/>
+      <c r="N73" s="47">
+        <v>5</v>
+      </c>
+      <c r="O73" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q73" s="10"/>
     </row>
     <row r="74" customFormat="1" ht="16.5" spans="1:17">
       <c r="A74" s="5" t="str">
@@ -5346,17 +5351,17 @@
       <c r="J74" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="L74" s="47"/>
+      <c r="L74" s="48"/>
       <c r="M74" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="N74" s="46">
-        <v>3</v>
-      </c>
-      <c r="O74" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q74" s="9"/>
+      <c r="N74" s="47">
+        <v>3</v>
+      </c>
+      <c r="O74" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q74" s="10"/>
     </row>
     <row r="75" customFormat="1" ht="16.5" spans="1:17">
       <c r="A75" s="5" t="str">
@@ -5387,19 +5392,19 @@
       <c r="I75" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L75" s="47">
+      <c r="L75" s="48">
         <v>10380002</v>
       </c>
       <c r="M75" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="N75" s="46">
-        <v>3</v>
-      </c>
-      <c r="O75" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q75" s="9"/>
+      <c r="N75" s="47">
+        <v>3</v>
+      </c>
+      <c r="O75" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q75" s="10"/>
     </row>
     <row r="76" customFormat="1" ht="16.5" spans="1:17">
       <c r="A76" s="5" t="str">
@@ -5430,19 +5435,19 @@
       <c r="I76" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L76" s="47" t="s">
+      <c r="L76" s="48" t="s">
         <v>152</v>
       </c>
       <c r="M76" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="N76" s="46">
-        <v>3</v>
-      </c>
-      <c r="O76" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q76" s="9"/>
+      <c r="N76" s="47">
+        <v>3</v>
+      </c>
+      <c r="O76" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q76" s="10"/>
     </row>
     <row r="77" customFormat="1" ht="16.5" spans="1:17">
       <c r="A77" s="5" t="str">
@@ -5473,19 +5478,19 @@
       <c r="I77" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L77" s="47" t="s">
+      <c r="L77" s="48" t="s">
         <v>154</v>
       </c>
       <c r="M77" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="N77" s="46">
-        <v>3</v>
-      </c>
-      <c r="O77" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q77" s="9"/>
+      <c r="N77" s="47">
+        <v>3</v>
+      </c>
+      <c r="O77" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q77" s="10"/>
     </row>
     <row r="78" customFormat="1" ht="16.5" spans="1:17">
       <c r="A78" s="5" t="str">
@@ -5516,19 +5521,19 @@
       <c r="I78" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L78" s="47" t="s">
+      <c r="L78" s="48" t="s">
         <v>157</v>
       </c>
       <c r="M78" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="N78" s="46">
-        <v>3</v>
-      </c>
-      <c r="O78" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q78" s="9"/>
+      <c r="N78" s="47">
+        <v>3</v>
+      </c>
+      <c r="O78" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q78" s="10"/>
     </row>
     <row r="79" customFormat="1" ht="16.5" spans="1:17">
       <c r="A79" s="5" t="str">
@@ -5559,19 +5564,19 @@
       <c r="I79" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L79" s="47">
+      <c r="L79" s="48">
         <v>10270003</v>
       </c>
       <c r="M79" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="N79" s="46">
-        <v>3</v>
-      </c>
-      <c r="O79" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q79" s="9"/>
+      <c r="N79" s="47">
+        <v>3</v>
+      </c>
+      <c r="O79" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q79" s="10"/>
     </row>
     <row r="80" customFormat="1" ht="16.5" spans="1:17">
       <c r="A80" s="5" t="str">
@@ -5602,19 +5607,19 @@
       <c r="I80" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L80" s="47" t="s">
+      <c r="L80" s="48" t="s">
         <v>160</v>
       </c>
       <c r="M80" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="N80" s="46">
-        <v>3</v>
-      </c>
-      <c r="O80" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q80" s="9"/>
+      <c r="N80" s="47">
+        <v>3</v>
+      </c>
+      <c r="O80" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q80" s="10"/>
     </row>
     <row r="81" customFormat="1" ht="16.5" spans="1:17">
       <c r="A81" s="5" t="str">
@@ -5645,19 +5650,19 @@
       <c r="I81" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L81" s="47" t="s">
+      <c r="L81" s="48" t="s">
         <v>163</v>
       </c>
       <c r="M81" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="N81" s="46">
+      <c r="N81" s="47">
         <v>4</v>
       </c>
-      <c r="O81" s="46">
-        <v>3</v>
-      </c>
-      <c r="Q81" s="9"/>
+      <c r="O81" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="10"/>
     </row>
     <row r="82" customFormat="1" ht="16.5" spans="1:17">
       <c r="A82" s="5" t="str">
@@ -5688,19 +5693,19 @@
       <c r="I82" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L82" s="47" t="s">
+      <c r="L82" s="48" t="s">
         <v>166</v>
       </c>
       <c r="M82" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="N82" s="46">
+      <c r="N82" s="47">
         <v>4</v>
       </c>
-      <c r="O82" s="46">
-        <v>3</v>
-      </c>
-      <c r="Q82" s="9"/>
+      <c r="O82" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q82" s="10"/>
     </row>
     <row r="83" customFormat="1" ht="16.5" spans="1:17">
       <c r="A83" s="5" t="str">
@@ -5731,23 +5736,23 @@
       <c r="I83" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L83" s="47">
+      <c r="L83" s="48">
         <v>10370003</v>
       </c>
       <c r="M83" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="N83" s="46">
+      <c r="N83" s="47">
         <v>4</v>
       </c>
-      <c r="O83" s="46">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="9"/>
+      <c r="O83" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="10"/>
     </row>
     <row r="84" customFormat="1" ht="16.5" spans="1:17">
       <c r="A84" s="5" t="str">
-        <f t="shared" ref="A84:A108" si="4">B84&amp;C84</f>
+        <f t="shared" si="3"/>
         <v>1031001</v>
       </c>
       <c r="B84" s="5">
@@ -5774,23 +5779,23 @@
       <c r="I84" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L84" s="47" t="s">
+      <c r="L84" s="48" t="s">
         <v>169</v>
       </c>
       <c r="M84" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="N84" s="46">
-        <v>3</v>
-      </c>
-      <c r="O84" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q84" s="9"/>
+      <c r="N84" s="47">
+        <v>3</v>
+      </c>
+      <c r="O84" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q84" s="10"/>
     </row>
     <row r="85" customFormat="1" ht="16.5" spans="1:17">
       <c r="A85" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1031002</v>
       </c>
       <c r="B85" s="5">
@@ -5817,23 +5822,23 @@
       <c r="I85" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L85" s="47">
+      <c r="L85" s="48">
         <v>10310008</v>
       </c>
       <c r="M85" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="N85" s="46">
-        <v>3</v>
-      </c>
-      <c r="O85" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q85" s="9"/>
+      <c r="N85" s="47">
+        <v>3</v>
+      </c>
+      <c r="O85" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q85" s="10"/>
     </row>
     <row r="86" customFormat="1" ht="16.5" spans="1:17">
       <c r="A86" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1031003</v>
       </c>
       <c r="B86" s="5">
@@ -5860,23 +5865,23 @@
       <c r="I86" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L86" s="47" t="s">
+      <c r="L86" s="48" t="s">
         <v>172</v>
       </c>
       <c r="M86" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="N86" s="46">
-        <v>3</v>
-      </c>
-      <c r="O86" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q86" s="9"/>
+      <c r="N86" s="47">
+        <v>3</v>
+      </c>
+      <c r="O86" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q86" s="10"/>
     </row>
     <row r="87" customFormat="1" ht="16.5" spans="1:17">
       <c r="A87" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1031004</v>
       </c>
       <c r="B87" s="5">
@@ -5903,23 +5908,23 @@
       <c r="I87" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L87" s="47" t="s">
+      <c r="L87" s="48" t="s">
         <v>174</v>
       </c>
       <c r="M87" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="N87" s="46">
-        <v>3</v>
-      </c>
-      <c r="O87" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q87" s="9"/>
+      <c r="N87" s="47">
+        <v>3</v>
+      </c>
+      <c r="O87" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q87" s="10"/>
     </row>
     <row r="88" customFormat="1" ht="16.5" spans="1:17">
       <c r="A88" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1031005</v>
       </c>
       <c r="B88" s="5">
@@ -5946,23 +5951,23 @@
       <c r="I88" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L88" s="47">
+      <c r="L88" s="48">
         <v>10310003</v>
       </c>
       <c r="M88" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="N88" s="46">
-        <v>3</v>
-      </c>
-      <c r="O88" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q88" s="9"/>
+      <c r="N88" s="47">
+        <v>3</v>
+      </c>
+      <c r="O88" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q88" s="10"/>
     </row>
     <row r="89" customFormat="1" ht="16.5" spans="1:17">
       <c r="A89" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1031006</v>
       </c>
       <c r="B89" s="5">
@@ -5989,23 +5994,23 @@
       <c r="I89" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L89" s="47" t="s">
+      <c r="L89" s="48" t="s">
         <v>179</v>
       </c>
       <c r="M89" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="N89" s="46">
-        <v>3</v>
-      </c>
-      <c r="O89" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q89" s="9"/>
+      <c r="N89" s="47">
+        <v>3</v>
+      </c>
+      <c r="O89" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q89" s="10"/>
     </row>
     <row r="90" customFormat="1" ht="16.5" spans="1:17">
       <c r="A90" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1040001</v>
       </c>
       <c r="B90" s="5">
@@ -6032,23 +6037,23 @@
       <c r="I90" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L90" s="47" t="s">
+      <c r="L90" s="48" t="s">
         <v>182</v>
       </c>
       <c r="M90" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="N90" s="46">
-        <v>3</v>
-      </c>
-      <c r="O90" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q90" s="9"/>
+      <c r="N90" s="47">
+        <v>3</v>
+      </c>
+      <c r="O90" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q90" s="10"/>
     </row>
     <row r="91" customFormat="1" ht="16.5" spans="1:17">
       <c r="A91" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1040002</v>
       </c>
       <c r="B91" s="5">
@@ -6075,23 +6080,23 @@
       <c r="I91" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L91" s="47" t="s">
+      <c r="L91" s="48" t="s">
         <v>184</v>
       </c>
       <c r="M91" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="N91" s="46">
-        <v>3</v>
-      </c>
-      <c r="O91" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q91" s="9"/>
+      <c r="N91" s="47">
+        <v>3</v>
+      </c>
+      <c r="O91" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q91" s="10"/>
     </row>
     <row r="92" customFormat="1" ht="16.5" spans="1:17">
       <c r="A92" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1040003</v>
       </c>
       <c r="B92" s="5">
@@ -6118,23 +6123,23 @@
       <c r="I92" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L92" s="47" t="s">
+      <c r="L92" s="48" t="s">
         <v>186</v>
       </c>
       <c r="M92" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="N92" s="46">
-        <v>3</v>
-      </c>
-      <c r="O92" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q92" s="9"/>
+      <c r="N92" s="47">
+        <v>3</v>
+      </c>
+      <c r="O92" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q92" s="10"/>
     </row>
     <row r="93" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A93" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1039001</v>
       </c>
       <c r="B93" s="5">
@@ -6167,17 +6172,17 @@
       <c r="M93" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="N93" s="46">
-        <v>3</v>
-      </c>
-      <c r="O93" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q93" s="19"/>
+      <c r="N93" s="47">
+        <v>3</v>
+      </c>
+      <c r="O93" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q93" s="20"/>
     </row>
     <row r="94" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A94" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1039002</v>
       </c>
       <c r="B94" s="5">
@@ -6204,23 +6209,23 @@
       <c r="I94" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L94" s="47">
+      <c r="L94" s="48">
         <v>10390003</v>
       </c>
       <c r="M94" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="N94" s="46">
-        <v>3</v>
-      </c>
-      <c r="O94" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q94" s="19"/>
+      <c r="N94" s="47">
+        <v>3</v>
+      </c>
+      <c r="O94" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q94" s="20"/>
     </row>
     <row r="95" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A95" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1039003</v>
       </c>
       <c r="B95" s="5">
@@ -6253,17 +6258,17 @@
       <c r="M95" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N95" s="46">
-        <v>3</v>
-      </c>
-      <c r="O95" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q95" s="19"/>
+      <c r="N95" s="47">
+        <v>3</v>
+      </c>
+      <c r="O95" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q95" s="20"/>
     </row>
     <row r="96" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A96" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1016001</v>
       </c>
       <c r="B96" s="5">
@@ -6296,17 +6301,17 @@
       <c r="M96" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="N96" s="46">
+      <c r="N96" s="47">
         <v>6</v>
       </c>
-      <c r="O96" s="46">
+      <c r="O96" s="47">
         <v>6</v>
       </c>
-      <c r="Q96" s="19"/>
+      <c r="Q96" s="20"/>
     </row>
     <row r="97" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A97" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1016002</v>
       </c>
       <c r="B97" s="5">
@@ -6333,23 +6338,23 @@
       <c r="I97" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L97" s="47">
+      <c r="L97" s="48">
         <v>10160002</v>
       </c>
       <c r="M97" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="N97" s="46">
+      <c r="N97" s="47">
         <v>6</v>
       </c>
-      <c r="O97" s="46">
+      <c r="O97" s="47">
         <v>6</v>
       </c>
-      <c r="Q97" s="19"/>
+      <c r="Q97" s="20"/>
     </row>
     <row r="98" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A98" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1016003</v>
       </c>
       <c r="B98" s="5">
@@ -6376,24 +6381,23 @@
       <c r="I98" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="J98" s="5"/>
       <c r="L98" s="5" t="s">
         <v>195</v>
       </c>
       <c r="M98" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="N98" s="46">
+      <c r="N98" s="47">
         <v>6</v>
       </c>
-      <c r="O98" s="46">
+      <c r="O98" s="47">
         <v>6</v>
       </c>
-      <c r="Q98" s="19"/>
+      <c r="Q98" s="20"/>
     </row>
     <row r="99" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A99" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1015001</v>
       </c>
       <c r="B99" s="5">
@@ -6426,17 +6430,17 @@
       <c r="M99" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="N99" s="46">
-        <v>3</v>
-      </c>
-      <c r="O99" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q99" s="19"/>
+      <c r="N99" s="47">
+        <v>3</v>
+      </c>
+      <c r="O99" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q99" s="20"/>
     </row>
     <row r="100" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A100" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1015002</v>
       </c>
       <c r="B100" s="5">
@@ -6469,17 +6473,17 @@
       <c r="M100" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="N100" s="46">
-        <v>3</v>
-      </c>
-      <c r="O100" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q100" s="19"/>
+      <c r="N100" s="47">
+        <v>3</v>
+      </c>
+      <c r="O100" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q100" s="20"/>
     </row>
     <row r="101" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A101" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1015003</v>
       </c>
       <c r="B101" s="5">
@@ -6506,23 +6510,23 @@
       <c r="I101" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L101" s="47">
+      <c r="L101" s="48">
         <v>10150002</v>
       </c>
       <c r="M101" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N101" s="46">
-        <v>3</v>
-      </c>
-      <c r="O101" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q101" s="19"/>
+      <c r="N101" s="47">
+        <v>3</v>
+      </c>
+      <c r="O101" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q101" s="20"/>
     </row>
     <row r="102" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A102" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1015004</v>
       </c>
       <c r="B102" s="5">
@@ -6555,17 +6559,17 @@
       <c r="M102" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="N102" s="46">
-        <v>3</v>
-      </c>
-      <c r="O102" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q102" s="19"/>
+      <c r="N102" s="47">
+        <v>3</v>
+      </c>
+      <c r="O102" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q102" s="20"/>
     </row>
     <row r="103" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A103" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1015005</v>
       </c>
       <c r="B103" s="5">
@@ -6592,23 +6596,23 @@
       <c r="I103" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L103" s="47">
+      <c r="L103" s="48">
         <v>10150005</v>
       </c>
       <c r="M103" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="N103" s="46">
-        <v>3</v>
-      </c>
-      <c r="O103" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q103" s="19"/>
+      <c r="N103" s="47">
+        <v>3</v>
+      </c>
+      <c r="O103" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q103" s="20"/>
     </row>
     <row r="104" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A104" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1015006</v>
       </c>
       <c r="B104" s="5">
@@ -6635,23 +6639,23 @@
       <c r="I104" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L104" s="47">
+      <c r="L104" s="48">
         <v>10150006</v>
       </c>
       <c r="M104" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="N104" s="46">
-        <v>3</v>
-      </c>
-      <c r="O104" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q104" s="19"/>
+      <c r="N104" s="47">
+        <v>3</v>
+      </c>
+      <c r="O104" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q104" s="20"/>
     </row>
     <row r="105" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A105" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1015007</v>
       </c>
       <c r="B105" s="5">
@@ -6678,23 +6682,23 @@
       <c r="I105" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L105" s="47">
+      <c r="L105" s="48">
         <v>10150007</v>
       </c>
       <c r="M105" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="N105" s="46">
-        <v>3</v>
-      </c>
-      <c r="O105" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q105" s="19"/>
+      <c r="N105" s="47">
+        <v>3</v>
+      </c>
+      <c r="O105" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q105" s="20"/>
     </row>
     <row r="106" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A106" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1026001</v>
       </c>
       <c r="B106" s="5">
@@ -6727,17 +6731,17 @@
       <c r="M106" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="N106" s="46">
+      <c r="N106" s="47">
         <v>6</v>
       </c>
-      <c r="O106" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q106" s="19"/>
+      <c r="O106" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q106" s="20"/>
     </row>
     <row r="107" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A107" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1026002</v>
       </c>
       <c r="B107" s="5">
@@ -6764,23 +6768,23 @@
       <c r="I107" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L107" s="47">
+      <c r="L107" s="48">
         <v>10260002</v>
       </c>
       <c r="M107" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="N107" s="46">
+      <c r="N107" s="47">
         <v>6</v>
       </c>
-      <c r="O107" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q107" s="19"/>
+      <c r="O107" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q107" s="20"/>
     </row>
     <row r="108" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A108" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1026003</v>
       </c>
       <c r="B108" s="5">
@@ -6813,16 +6817,16 @@
       <c r="M108" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="N108" s="46">
+      <c r="N108" s="47">
         <v>6</v>
       </c>
-      <c r="O108" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q108" s="19"/>
+      <c r="O108" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q108" s="20"/>
     </row>
     <row r="109" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A109" s="47">
+      <c r="A109" s="48">
         <v>1050001</v>
       </c>
       <c r="B109" s="5">
@@ -6855,16 +6859,16 @@
       <c r="M109" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="N109" s="46">
-        <v>5</v>
-      </c>
-      <c r="O109" s="46">
+      <c r="N109" s="47">
+        <v>5</v>
+      </c>
+      <c r="O109" s="47">
         <v>6</v>
       </c>
-      <c r="Q109" s="19"/>
+      <c r="Q109" s="20"/>
     </row>
     <row r="110" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A110" s="47">
+      <c r="A110" s="48">
         <v>1050002</v>
       </c>
       <c r="B110" s="5">
@@ -6891,23 +6895,23 @@
       <c r="I110" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L110" s="47">
+      <c r="L110" s="48">
         <v>10500002</v>
       </c>
       <c r="M110" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="N110" s="46">
-        <v>5</v>
-      </c>
-      <c r="O110" s="46">
+      <c r="N110" s="47">
+        <v>5</v>
+      </c>
+      <c r="O110" s="47">
         <v>6</v>
       </c>
-      <c r="P110" s="46"/>
-      <c r="Q110" s="19"/>
+      <c r="P110" s="47"/>
+      <c r="Q110" s="20"/>
     </row>
     <row r="111" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A111" s="47">
+      <c r="A111" s="48">
         <v>1050003</v>
       </c>
       <c r="B111" s="5">
@@ -6934,22 +6938,22 @@
       <c r="I111" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L111" s="47" t="s">
+      <c r="L111" s="48" t="s">
         <v>218</v>
       </c>
       <c r="M111" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="N111" s="46">
-        <v>5</v>
-      </c>
-      <c r="O111" s="46">
+      <c r="N111" s="47">
+        <v>5</v>
+      </c>
+      <c r="O111" s="47">
         <v>6</v>
       </c>
-      <c r="Q111" s="19"/>
+      <c r="Q111" s="20"/>
     </row>
     <row r="112" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A112" s="47">
+      <c r="A112" s="48">
         <v>1051001</v>
       </c>
       <c r="B112" s="5">
@@ -6976,22 +6980,22 @@
       <c r="I112" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L112" s="47">
+      <c r="L112" s="48">
         <v>10510008</v>
       </c>
       <c r="M112" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="N112" s="46">
+      <c r="N112" s="47">
         <v>6</v>
       </c>
-      <c r="O112" s="46">
+      <c r="O112" s="47">
         <v>6</v>
       </c>
-      <c r="Q112" s="19"/>
+      <c r="Q112" s="20"/>
     </row>
     <row r="113" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A113" s="47">
+      <c r="A113" s="48">
         <v>1051002</v>
       </c>
       <c r="B113" s="5">
@@ -7018,22 +7022,22 @@
       <c r="I113" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L113" s="47" t="s">
+      <c r="L113" s="48" t="s">
         <v>224</v>
       </c>
       <c r="M113" t="s">
         <v>225</v>
       </c>
-      <c r="N113" s="46">
+      <c r="N113" s="47">
         <v>6</v>
       </c>
-      <c r="O113" s="46">
+      <c r="O113" s="47">
         <v>6</v>
       </c>
-      <c r="Q113" s="9"/>
+      <c r="Q113" s="10"/>
     </row>
     <row r="114" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A114" s="47">
+      <c r="A114" s="48">
         <v>1051003</v>
       </c>
       <c r="B114" s="5">
@@ -7060,22 +7064,22 @@
       <c r="I114" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L114" s="47" t="s">
+      <c r="L114" s="48" t="s">
         <v>227</v>
       </c>
       <c r="M114" t="s">
         <v>228</v>
       </c>
-      <c r="N114" s="46">
+      <c r="N114" s="47">
         <v>6</v>
       </c>
-      <c r="O114" s="46">
+      <c r="O114" s="47">
         <v>6</v>
       </c>
-      <c r="Q114" s="9"/>
+      <c r="Q114" s="10"/>
     </row>
     <row r="115" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A115" s="47">
+      <c r="A115" s="48">
         <v>1051004</v>
       </c>
       <c r="B115" s="5">
@@ -7102,22 +7106,22 @@
       <c r="I115" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L115" s="47">
+      <c r="L115" s="48">
         <v>10510005</v>
       </c>
       <c r="M115" t="s">
         <v>229</v>
       </c>
-      <c r="N115" s="46">
+      <c r="N115" s="47">
         <v>6</v>
       </c>
-      <c r="O115" s="46">
+      <c r="O115" s="47">
         <v>6</v>
       </c>
-      <c r="Q115" s="9"/>
+      <c r="Q115" s="10"/>
     </row>
     <row r="116" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A116" s="47">
+      <c r="A116" s="48">
         <v>1051005</v>
       </c>
       <c r="B116" s="5">
@@ -7144,19 +7148,19 @@
       <c r="I116" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L116" s="47">
+      <c r="L116" s="48">
         <v>10510009</v>
       </c>
       <c r="M116" t="s">
         <v>230</v>
       </c>
-      <c r="N116" s="46">
+      <c r="N116" s="47">
         <v>6</v>
       </c>
-      <c r="O116" s="46">
+      <c r="O116" s="47">
         <v>6</v>
       </c>
-      <c r="Q116" s="9"/>
+      <c r="Q116" s="10"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:K2">

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -551,7 +551,7 @@
     <t>第1轴改出1个scatter+第3轴改出1个scatter+第1轴改出5个scatter</t>
   </si>
   <si>
-    <t>10200006|10200007|10200011</t>
+    <t>10200006|10200007|10200015</t>
   </si>
   <si>
     <t>第1轴改出1个scatter+第3轴改出1个scatter+第5轴改出奖池符号</t>
@@ -4767,7 +4767,7 @@
     </row>
     <row r="61" customFormat="1" ht="16.5" spans="1:17">
       <c r="A61" s="5" t="str">
-        <f>B61&amp;C61</f>
+        <f t="shared" si="3"/>
         <v>1036002</v>
       </c>
       <c r="B61" s="5">

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -551,7 +551,7 @@
     <t>第1轴改出1个scatter+第3轴改出1个scatter+第1轴改出5个scatter</t>
   </si>
   <si>
-    <t>10200006|10200007|10200015</t>
+    <t>10200006|10200007|10200011</t>
   </si>
   <si>
     <t>第1轴改出1个scatter+第3轴改出1个scatter+第5轴改出奖池符号</t>
@@ -4767,7 +4767,7 @@
     </row>
     <row r="61" customFormat="1" ht="16.5" spans="1:17">
       <c r="A61" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f>B61&amp;C61</f>
         <v>1036002</v>
       </c>
       <c r="B61" s="5">

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -4767,7 +4767,7 @@
     </row>
     <row r="61" customFormat="1" ht="16.5" spans="1:17">
       <c r="A61" s="5" t="str">
-        <f>B61&amp;C61</f>
+        <f t="shared" si="3"/>
         <v>1036002</v>
       </c>
       <c r="B61" s="5">
@@ -5010,7 +5010,7 @@
         <v>24</v>
       </c>
       <c r="L66" s="48">
-        <v>10340007</v>
+        <v>10340101</v>
       </c>
       <c r="M66" s="5" t="s">
         <v>108</v>

--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\java\gamedoc\游戏配置表\slot\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CB7C16C-D71C-4DA3-867F-A088BB44DBCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialMode" sheetId="1" r:id="rId1"/>
@@ -22,18 +28,21 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
     <author/>
   </authors>
   <commentList>
-    <comment ref="J1" authorId="0">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -55,7 +64,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="1">
+    <comment ref="N1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -77,7 +86,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="1">
+    <comment ref="O1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -99,7 +108,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J2" authorId="0">
+    <comment ref="J2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -126,7 +135,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="267">
   <si>
     <t>id</t>
   </si>
@@ -551,7 +560,7 @@
     <t>第1轴改出1个scatter+第3轴改出1个scatter+第1轴改出5个scatter</t>
   </si>
   <si>
-    <t>10200006|10200007|10200011</t>
+    <t>10200006|10200007|10200015</t>
   </si>
   <si>
     <t>第1轴改出1个scatter+第3轴改出1个scatter+第5轴改出奖池符号</t>
@@ -761,31 +770,46 @@
     <t>寻宝黄金城</t>
   </si>
   <si>
-    <t>10260001|10260004|10260005|10260006|10260007</t>
-  </si>
-  <si>
-    <t>概率改出百搭wild符号+概率改出scatter符号+概率改出占据2、3、4个格子符号</t>
-  </si>
-  <si>
-    <t>10260003|10260008</t>
+    <t>10260001|10260004|10260005|10260006|10260007|10260010</t>
+  </si>
+  <si>
+    <t>概率改出百搭wild符号+概率改出scatter符号+概率改出占据2、3、4个格子符号+异形位置不中奖</t>
+  </si>
+  <si>
+    <t>10260002|10260010</t>
+  </si>
+  <si>
+    <t>10260003|10260008|10260010</t>
   </si>
   <si>
     <t>澳门壕梦</t>
   </si>
   <si>
-    <t>10500001|10500004|10500005|10500006|10500007</t>
-  </si>
-  <si>
-    <t>概率改出wild+概率改出scatter符号+概率改出占据2、3、4格子的普通符号</t>
-  </si>
-  <si>
-    <t>改出4个或以上个数SCATTER</t>
-  </si>
-  <si>
-    <t>10500003|10500008</t>
-  </si>
-  <si>
-    <t>改出3个scatter符号+改出奖池符号</t>
+    <t>10500001|10500004|10500005|10500006|10500007|10500010</t>
+  </si>
+  <si>
+    <t>概率改出wild+概率改出scatter符号+概率改出占据2、3、4格子的普通符号+异形位置改为不中奖图案</t>
+  </si>
+  <si>
+    <t>10500002|10500010</t>
+  </si>
+  <si>
+    <t>改出4个或以上个数SCATTER+异形位置改为不中奖图案</t>
+  </si>
+  <si>
+    <t>10500003|10500008|10500010</t>
+  </si>
+  <si>
+    <t>改出3个scatter符号+改出奖池符号+异形位置改为不中奖图案</t>
+  </si>
+  <si>
+    <t>免费模式</t>
+  </si>
+  <si>
+    <t>10500009|10500010</t>
+  </si>
+  <si>
+    <t>概率改出SCATTER符号+异形位置改为不中奖图案</t>
   </si>
   <si>
     <t>糖果派对</t>
@@ -819,20 +843,110 @@
   </si>
   <si>
     <t>改出1-4个彩池图标</t>
+  </si>
+  <si>
+    <t>黄金帝国</t>
+  </si>
+  <si>
+    <t>10540003|10540004|10540005|10540006|10540007|10540010</t>
+  </si>
+  <si>
+    <t>概率改出3个SCATTER+概率改出占据1个格子的金框符号+概率改出占据2、3、4个格子符号+异形位置改为不中奖图案</t>
+  </si>
+  <si>
+    <t>10540001|10540010</t>
+  </si>
+  <si>
+    <t>改出4个以上SCATTER+异形位置改为不中奖图案</t>
+  </si>
+  <si>
+    <t>10540002|10540008|10540010</t>
+  </si>
+  <si>
+    <t>改出3个SCATTER+奖池符号+异形位置改为不中奖图案</t>
+  </si>
+  <si>
+    <t>10540009|10540010</t>
+  </si>
+  <si>
+    <t>招财猫</t>
+  </si>
+  <si>
+    <t>10260001|10260004|10260005|10260006|10260007|10080010</t>
+  </si>
+  <si>
+    <t>概率改出百搭wild符号+概率改出scatter符号+概率改出占据2、3、4个格子符号+异形位置改为不中奖图案</t>
+  </si>
+  <si>
+    <t>10500003|10500008|10080010</t>
+  </si>
+  <si>
+    <t>1053001</t>
+  </si>
+  <si>
+    <t>麻将胡了2</t>
+  </si>
+  <si>
+    <t>10530001|10530005|10530006|10530007|10530008|10530009|10530010|10530011|10530012|10530013|10530014|10530015|10530016</t>
+  </si>
+  <si>
+    <t>概率改出wild百搭符号+概率改出scatter+概率出金色图标+异形位置改为不中奖图案</t>
+  </si>
+  <si>
+    <t>1053002</t>
+  </si>
+  <si>
+    <t>10530003|10530016</t>
+  </si>
+  <si>
+    <t>概率改出3个scatter+异形位置改为不中奖图案</t>
+  </si>
+  <si>
+    <t>赏金大对决</t>
+  </si>
+  <si>
+    <t>10570001|10570002|10570006|10570015</t>
+  </si>
+  <si>
+    <t>概率改出百搭wild符号+概率改出scatter符号+概率改出金框符号+异形位置改为不中奖图案</t>
+  </si>
+  <si>
+    <t>10570003|10570015</t>
+  </si>
+  <si>
+    <t>改出3个以上SCATTER+异形位置改为不中奖图案</t>
+  </si>
+  <si>
+    <t>10570005|10570004|10570015</t>
+  </si>
+  <si>
+    <t>改出2个SCATTER+奖池符号+异形位置改为不中奖图案</t>
+  </si>
+  <si>
+    <t>极速糖果1000</t>
+  </si>
+  <si>
+    <t>概率改出scatter</t>
+  </si>
+  <si>
+    <t>概率改出3个SCATTER</t>
+  </si>
+  <si>
+    <t>奖池符号</t>
+  </si>
+  <si>
+    <t>10260002|10080010</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="1">
+    <numFmt numFmtId="178" formatCode="0_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -847,6 +961,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -854,151 +974,8 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1012,8 +989,21 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="45">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1022,31 +1012,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.8"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.8"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.6"/>
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.6"/>
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.8"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1070,216 +1066,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.8"/>
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1302,254 +1106,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1559,45 +1121,47 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -1608,13 +1172,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1623,7 +1187,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1631,11 +1195,11 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1660,7 +1224,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1682,98 +1245,184 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 80" xfId="49"/>
+    <cellStyle name="常规 80" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
   <dxfs count="18">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.799340800195319"/>
+          <bgColor theme="8" tint="0.7993408001953185"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -1784,7 +1433,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1812,154 +1461,40 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="7"/>
-      <tableStyleElement type="headerRow" dxfId="6"/>
-      <tableStyleElement type="totalRow" dxfId="5"/>
-      <tableStyleElement type="firstColumn" dxfId="4"/>
-      <tableStyleElement type="lastColumn" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" dxfId="17"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstColumn" dxfId="14"/>
+      <tableStyleElement type="lastColumn" dxfId="13"/>
+      <tableStyleElement type="firstRowStripe" dxfId="12"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="11"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="17"/>
-      <tableStyleElement type="totalRow" dxfId="16"/>
-      <tableStyleElement type="firstRowStripe" dxfId="15"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
-      <tableStyleElement type="pageFieldValues" dxfId="8"/>
+      <tableStyleElement type="headerRow" dxfId="10"/>
+      <tableStyleElement type="totalRow" dxfId="9"/>
+      <tableStyleElement type="firstRowStripe" dxfId="8"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="7"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="6"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="4"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="3"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="2"/>
+      <tableStyleElement type="pageFieldValues" dxfId="1"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2209,14 +1744,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:S116"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:S132"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
     <col min="5" max="5" width="36.375" customWidth="1"/>
@@ -2227,15 +1762,15 @@
     <col min="10" max="10" width="30.125" customWidth="1"/>
     <col min="11" max="11" width="16.75" customWidth="1"/>
     <col min="12" max="12" width="53.25" customWidth="1"/>
-    <col min="13" max="13" width="21.6083333333333" customWidth="1"/>
-    <col min="14" max="15" width="9" style="9"/>
+    <col min="13" max="13" width="21.625" customWidth="1"/>
+    <col min="14" max="15" width="9" style="11"/>
     <col min="16" max="16" width="15" customWidth="1"/>
-    <col min="17" max="17" width="23.75" style="10" customWidth="1"/>
+    <col min="17" max="17" width="23.75" style="12" customWidth="1"/>
     <col min="18" max="18" width="60.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:17">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
@@ -2246,34 +1781,34 @@
       </c>
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="14" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="5"/>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="14" t="s">
         <v>4</v>
       </c>
       <c r="I1" s="5"/>
-      <c r="J1" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="13"/>
-      <c r="L1" s="14" t="s">
+      <c r="J1" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="15"/>
+      <c r="L1" s="16" t="s">
         <v>6</v>
       </c>
       <c r="M1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="15" t="s">
+      <c r="N1" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="15" t="s">
+      <c r="O1" s="17" t="s">
         <v>9</v>
       </c>
       <c r="Q1"/>
     </row>
-    <row r="2" ht="16.5" spans="1:17">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="13" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -2284,1166 +1819,1166 @@
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="14" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="5"/>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="14" t="s">
         <v>10</v>
       </c>
       <c r="I2" s="5"/>
-      <c r="J2" s="16" t="s">
+      <c r="J2" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="17"/>
-      <c r="L2" s="18" t="s">
+      <c r="K2" s="19"/>
+      <c r="L2" s="20" t="s">
         <v>12</v>
       </c>
       <c r="M2" s="5"/>
-      <c r="N2" s="19" t="s">
+      <c r="N2" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="19" t="s">
+      <c r="O2" s="21" t="s">
         <v>10</v>
       </c>
       <c r="Q2"/>
     </row>
-    <row r="3" ht="16.5" spans="1:17">
-      <c r="A3" s="11" t="s">
+    <row r="3" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="21" t="s">
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="20"/>
-      <c r="H3" s="22" t="s">
+      <c r="G3" s="22"/>
+      <c r="H3" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="20"/>
-      <c r="J3" s="23" t="s">
+      <c r="I3" s="22"/>
+      <c r="J3" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="23"/>
-      <c r="L3" s="24" t="s">
+      <c r="K3" s="25"/>
+      <c r="L3" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="M3" s="20"/>
-      <c r="N3" s="19" t="s">
+      <c r="M3" s="22"/>
+      <c r="N3" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="19" t="s">
+      <c r="O3" s="21" t="s">
         <v>20</v>
       </c>
       <c r="Q3"/>
     </row>
-    <row r="4" ht="16.5" spans="1:17">
+    <row r="4" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="12"/>
+      <c r="F4" s="14"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="12"/>
+      <c r="H4" s="14"/>
       <c r="I4" s="5"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="14"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="16"/>
       <c r="M4" s="5"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
+      <c r="N4" s="21"/>
+      <c r="O4" s="21"/>
       <c r="Q4"/>
     </row>
-    <row r="5" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A5" s="26" t="str">
-        <f t="shared" ref="A5:A21" si="0">B5&amp;C5</f>
+    <row r="5" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="28" t="str">
+        <f t="shared" ref="A5:A19" si="0">B5&amp;C5</f>
         <v>1001001</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="29">
         <v>100100</v>
       </c>
-      <c r="C5" s="27">
-        <v>1</v>
-      </c>
-      <c r="D5" s="27" t="s">
+      <c r="C5" s="29">
+        <v>1</v>
+      </c>
+      <c r="D5" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="E5" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="27">
-        <v>1</v>
-      </c>
-      <c r="G5" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="26">
+      <c r="F5" s="29">
+        <v>1</v>
+      </c>
+      <c r="G5" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="28">
         <v>2001001</v>
       </c>
-      <c r="I5" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="29" t="s">
+      <c r="I5" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="M5" s="26" t="s">
+      <c r="M5" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="N5" s="19">
+      <c r="N5" s="21">
         <v>4</v>
       </c>
-      <c r="O5" s="19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A6" s="26" t="str">
+      <c r="O5" s="21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="28" t="str">
         <f t="shared" si="0"/>
         <v>1001002</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="29">
         <v>100100</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="29">
         <v>2</v>
       </c>
-      <c r="D6" s="27"/>
-      <c r="E6" s="30" t="s">
+      <c r="D6" s="29"/>
+      <c r="E6" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="27">
-        <v>1</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="26">
+      <c r="F6" s="29">
+        <v>1</v>
+      </c>
+      <c r="G6" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="28">
         <v>2001001</v>
       </c>
-      <c r="I6" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="31" t="s">
+      <c r="I6" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="28"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="M6" s="26" t="s">
+      <c r="M6" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="N6" s="19">
+      <c r="N6" s="21">
         <v>4</v>
       </c>
-      <c r="O6" s="19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A7" s="26" t="str">
+      <c r="O6" s="21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="28" t="str">
         <f t="shared" si="0"/>
         <v>1001003</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="29">
         <v>100100</v>
       </c>
-      <c r="C7" s="27">
-        <v>3</v>
-      </c>
-      <c r="D7" s="27"/>
-      <c r="E7" s="32" t="s">
+      <c r="C7" s="29">
+        <v>3</v>
+      </c>
+      <c r="D7" s="29"/>
+      <c r="E7" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="27">
-        <v>1</v>
-      </c>
-      <c r="G7" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="26">
+      <c r="F7" s="29">
+        <v>1</v>
+      </c>
+      <c r="G7" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="28">
         <v>2001001</v>
       </c>
-      <c r="I7" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="29" t="s">
+      <c r="I7" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="28"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="M7" s="26" t="s">
+      <c r="M7" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="N7" s="19">
+      <c r="N7" s="21">
         <v>4</v>
       </c>
-      <c r="O7" s="19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A8" s="26" t="str">
+      <c r="O7" s="21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="28" t="str">
         <f t="shared" si="0"/>
         <v>1001004</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="29">
         <v>100100</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="29">
         <v>4</v>
       </c>
-      <c r="D8" s="27"/>
-      <c r="E8" s="33" t="s">
+      <c r="D8" s="29"/>
+      <c r="E8" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="34">
-        <v>1</v>
-      </c>
-      <c r="G8" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="26">
+      <c r="F8" s="36">
+        <v>1</v>
+      </c>
+      <c r="G8" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="28">
         <v>2001001</v>
       </c>
-      <c r="I8" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" s="26"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="29">
+      <c r="I8" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="28"/>
+      <c r="K8" s="28"/>
+      <c r="L8" s="31">
         <v>10010041</v>
       </c>
-      <c r="M8" s="26" t="s">
+      <c r="M8" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="N8" s="19">
+      <c r="N8" s="21">
         <v>4</v>
       </c>
-      <c r="O8" s="19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A9" s="26" t="str">
+      <c r="O8" s="21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="28" t="str">
         <f t="shared" si="0"/>
         <v>1001005</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="29">
         <v>100100</v>
       </c>
-      <c r="C9" s="27">
-        <v>5</v>
-      </c>
-      <c r="D9" s="27"/>
-      <c r="E9" s="35" t="s">
+      <c r="C9" s="29">
+        <v>5</v>
+      </c>
+      <c r="D9" s="29"/>
+      <c r="E9" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="34">
-        <v>1</v>
-      </c>
-      <c r="G9" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="26">
+      <c r="F9" s="36">
+        <v>1</v>
+      </c>
+      <c r="G9" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="28">
         <v>2001001</v>
       </c>
-      <c r="I9" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" s="26"/>
-      <c r="K9" s="26"/>
-      <c r="L9" s="29" t="s">
+      <c r="I9" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="M9" s="26" t="s">
+      <c r="M9" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="N9" s="19">
+      <c r="N9" s="21">
         <v>4</v>
       </c>
-      <c r="O9" s="19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A10" s="26" t="str">
+      <c r="O9" s="21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="28" t="str">
         <f t="shared" si="0"/>
         <v>1001006</v>
       </c>
-      <c r="B10" s="27">
+      <c r="B10" s="29">
         <v>100100</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="29">
         <v>6</v>
       </c>
-      <c r="D10" s="27"/>
-      <c r="E10" s="35" t="s">
+      <c r="D10" s="29"/>
+      <c r="E10" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="34">
-        <v>1</v>
-      </c>
-      <c r="G10" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="26">
+      <c r="F10" s="36">
+        <v>1</v>
+      </c>
+      <c r="G10" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="28">
         <v>2001001</v>
       </c>
-      <c r="I10" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="J10" s="26"/>
-      <c r="K10" s="26"/>
-      <c r="L10" s="29">
+      <c r="I10" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" s="28"/>
+      <c r="K10" s="28"/>
+      <c r="L10" s="31">
         <v>10010061</v>
       </c>
-      <c r="M10" s="26" t="s">
+      <c r="M10" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="N10" s="19">
+      <c r="N10" s="21">
         <v>4</v>
       </c>
-      <c r="O10" s="19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A11" s="26" t="str">
+      <c r="O10" s="21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="28" t="str">
         <f t="shared" si="0"/>
         <v>1001007</v>
       </c>
-      <c r="B11" s="27">
+      <c r="B11" s="29">
         <v>100100</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="29">
         <v>7</v>
       </c>
-      <c r="D11" s="27"/>
-      <c r="E11" s="30" t="s">
+      <c r="D11" s="29"/>
+      <c r="E11" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="27">
-        <v>1</v>
-      </c>
-      <c r="G11" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" s="26">
+      <c r="F11" s="29">
+        <v>1</v>
+      </c>
+      <c r="G11" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="28">
         <v>2001001</v>
       </c>
-      <c r="I11" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="J11" s="26"/>
-      <c r="K11" s="26"/>
-      <c r="L11" s="31" t="s">
+      <c r="I11" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="J11" s="28"/>
+      <c r="K11" s="28"/>
+      <c r="L11" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="M11" s="26" t="s">
+      <c r="M11" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="N11" s="19">
+      <c r="N11" s="21">
         <v>4</v>
       </c>
-      <c r="O11" s="19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A12" s="36" t="str">
+      <c r="O11" s="21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="38" t="str">
         <f t="shared" si="0"/>
         <v>1003001</v>
       </c>
-      <c r="B12" s="28">
+      <c r="B12" s="30">
         <v>100300</v>
       </c>
-      <c r="C12" s="28">
-        <v>1</v>
-      </c>
-      <c r="D12" s="28" t="s">
+      <c r="C12" s="30">
+        <v>1</v>
+      </c>
+      <c r="D12" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="28" t="s">
+      <c r="E12" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="28">
-        <v>1</v>
-      </c>
-      <c r="G12" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="H12" s="36">
+      <c r="F12" s="30">
+        <v>1</v>
+      </c>
+      <c r="G12" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="38">
         <v>2003001</v>
       </c>
-      <c r="I12" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" s="36"/>
-      <c r="K12" s="36"/>
-      <c r="L12" s="37">
+      <c r="I12" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="L12" s="39">
         <v>10030022</v>
       </c>
-      <c r="M12" s="36" t="s">
+      <c r="M12" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="N12" s="28">
-        <v>3</v>
-      </c>
-      <c r="O12" s="28">
-        <v>3</v>
-      </c>
-      <c r="Q12" s="38"/>
-    </row>
-    <row r="13" s="2" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A13" s="36" t="str">
+      <c r="N12" s="30">
+        <v>3</v>
+      </c>
+      <c r="O12" s="30">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="40"/>
+    </row>
+    <row r="13" spans="1:17" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="38" t="str">
         <f t="shared" si="0"/>
         <v>1003002</v>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="30">
         <v>100300</v>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="30">
         <v>2</v>
       </c>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28" t="s">
+      <c r="D13" s="30"/>
+      <c r="E13" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="28">
-        <v>1</v>
-      </c>
-      <c r="G13" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="H13" s="36">
+      <c r="F13" s="30">
+        <v>1</v>
+      </c>
+      <c r="G13" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="38">
         <v>2003001</v>
       </c>
-      <c r="I13" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="J13" s="36"/>
-      <c r="K13" s="36"/>
-      <c r="L13" s="37" t="s">
+      <c r="I13" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="L13" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="M13" s="36" t="s">
+      <c r="M13" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="N13" s="28">
-        <v>3</v>
-      </c>
-      <c r="O13" s="28">
-        <v>3</v>
-      </c>
-      <c r="Q13" s="38"/>
-    </row>
-    <row r="14" s="2" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A14" s="36" t="str">
+      <c r="N13" s="30">
+        <v>3</v>
+      </c>
+      <c r="O13" s="30">
+        <v>3</v>
+      </c>
+      <c r="Q13" s="40"/>
+    </row>
+    <row r="14" spans="1:17" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="38" t="str">
         <f t="shared" si="0"/>
         <v>1003003</v>
       </c>
-      <c r="B14" s="28">
+      <c r="B14" s="30">
         <v>100300</v>
       </c>
-      <c r="C14" s="28">
-        <v>3</v>
-      </c>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28" t="s">
+      <c r="C14" s="30">
+        <v>3</v>
+      </c>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="28">
-        <v>1</v>
-      </c>
-      <c r="G14" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="H14" s="36">
+      <c r="F14" s="30">
+        <v>1</v>
+      </c>
+      <c r="G14" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="38">
         <v>2003002</v>
       </c>
-      <c r="I14" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="J14" s="36" t="s">
+      <c r="I14" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="K14" s="36" t="s">
+      <c r="K14" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="L14" s="37" t="s">
+      <c r="L14" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="M14" s="36" t="s">
+      <c r="M14" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="N14" s="28">
-        <v>3</v>
-      </c>
-      <c r="O14" s="28">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="38"/>
-    </row>
-    <row r="15" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A15" s="39" t="str">
+      <c r="N14" s="30">
+        <v>3</v>
+      </c>
+      <c r="O14" s="30">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="40"/>
+    </row>
+    <row r="15" spans="1:17" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="41" t="str">
         <f t="shared" si="0"/>
         <v>1007001</v>
       </c>
-      <c r="B15" s="40">
+      <c r="B15" s="42">
         <v>100700</v>
       </c>
-      <c r="C15" s="40">
-        <v>1</v>
-      </c>
-      <c r="D15" s="40" t="s">
+      <c r="C15" s="42">
+        <v>1</v>
+      </c>
+      <c r="D15" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="40" t="s">
+      <c r="E15" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="40">
-        <v>1</v>
-      </c>
-      <c r="G15" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="H15" s="39">
+      <c r="F15" s="42">
+        <v>1</v>
+      </c>
+      <c r="G15" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="41">
         <v>2007001</v>
       </c>
-      <c r="I15" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="J15" s="39"/>
-      <c r="K15" s="39"/>
-      <c r="L15" s="41" t="s">
+      <c r="I15" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" s="41"/>
+      <c r="K15" s="41"/>
+      <c r="L15" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="M15" s="39" t="s">
+      <c r="M15" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="N15" s="19">
+      <c r="N15" s="21">
         <v>4</v>
       </c>
-      <c r="O15" s="19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A16" s="39" t="str">
+      <c r="O15" s="21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="41" t="str">
         <f t="shared" si="0"/>
         <v>1007002</v>
       </c>
-      <c r="B16" s="40">
+      <c r="B16" s="42">
         <v>100700</v>
       </c>
-      <c r="C16" s="40">
+      <c r="C16" s="42">
         <v>2</v>
       </c>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40" t="s">
+      <c r="D16" s="42"/>
+      <c r="E16" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="40">
-        <v>1</v>
-      </c>
-      <c r="G16" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="H16" s="39">
+      <c r="F16" s="42">
+        <v>1</v>
+      </c>
+      <c r="G16" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="41">
         <v>2007001</v>
       </c>
-      <c r="I16" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="J16" s="39"/>
-      <c r="K16" s="39"/>
-      <c r="L16" s="41" t="s">
+      <c r="I16" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="J16" s="41"/>
+      <c r="K16" s="41"/>
+      <c r="L16" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="M16" s="39" t="s">
+      <c r="M16" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="N16" s="19">
+      <c r="N16" s="21">
         <v>4</v>
       </c>
-      <c r="O16" s="19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A17" s="42" t="str">
+      <c r="O16" s="21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="44" t="str">
         <f t="shared" si="0"/>
         <v>1012001</v>
       </c>
-      <c r="B17" s="43">
+      <c r="B17" s="45">
         <v>101200</v>
       </c>
-      <c r="C17" s="43">
-        <v>1</v>
-      </c>
-      <c r="D17" s="43" t="s">
+      <c r="C17" s="45">
+        <v>1</v>
+      </c>
+      <c r="D17" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="E17" s="43" t="s">
+      <c r="E17" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="43">
-        <v>1</v>
-      </c>
-      <c r="G17" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="H17" s="42">
+      <c r="F17" s="45">
+        <v>1</v>
+      </c>
+      <c r="G17" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="44">
         <v>2012001</v>
       </c>
-      <c r="I17" s="42" t="s">
-        <v>24</v>
-      </c>
-      <c r="J17" s="42"/>
-      <c r="K17" s="42"/>
-      <c r="L17" s="44">
+      <c r="I17" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="J17" s="44"/>
+      <c r="K17" s="44"/>
+      <c r="L17" s="46">
         <v>10120011</v>
       </c>
-      <c r="M17" s="42" t="s">
+      <c r="M17" s="44" t="s">
         <v>58</v>
       </c>
-      <c r="N17" s="43">
-        <v>3</v>
-      </c>
-      <c r="O17" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q17" s="45"/>
-    </row>
-    <row r="18" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A18" s="42" t="str">
+      <c r="N17" s="45">
+        <v>3</v>
+      </c>
+      <c r="O17" s="45">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="47"/>
+    </row>
+    <row r="18" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="44" t="str">
         <f t="shared" si="0"/>
         <v>1012002</v>
       </c>
-      <c r="B18" s="43">
+      <c r="B18" s="45">
         <v>101200</v>
       </c>
-      <c r="C18" s="43">
+      <c r="C18" s="45">
         <v>2</v>
       </c>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43" t="s">
+      <c r="D18" s="45"/>
+      <c r="E18" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="43">
-        <v>1</v>
-      </c>
-      <c r="G18" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="H18" s="42">
+      <c r="F18" s="45">
+        <v>1</v>
+      </c>
+      <c r="G18" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="44">
         <v>2012001</v>
       </c>
-      <c r="I18" s="42" t="s">
-        <v>24</v>
-      </c>
-      <c r="J18" s="42"/>
-      <c r="K18" s="42"/>
-      <c r="L18" s="44">
+      <c r="I18" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="J18" s="44"/>
+      <c r="K18" s="44"/>
+      <c r="L18" s="46">
         <v>10120021</v>
       </c>
-      <c r="M18" s="42" t="s">
+      <c r="M18" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="N18" s="43">
-        <v>3</v>
-      </c>
-      <c r="O18" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q18" s="45"/>
-    </row>
-    <row r="19" s="4" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A19" s="42" t="str">
+      <c r="N18" s="45">
+        <v>3</v>
+      </c>
+      <c r="O18" s="45">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="47"/>
+    </row>
+    <row r="19" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="44" t="str">
         <f t="shared" si="0"/>
         <v>1012003</v>
       </c>
-      <c r="B19" s="43">
+      <c r="B19" s="45">
         <v>101200</v>
       </c>
-      <c r="C19" s="43">
-        <v>3</v>
-      </c>
-      <c r="D19" s="43"/>
-      <c r="E19" s="43" t="s">
+      <c r="C19" s="45">
+        <v>3</v>
+      </c>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="F19" s="43">
-        <v>1</v>
-      </c>
-      <c r="G19" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="H19" s="42">
+      <c r="F19" s="45">
+        <v>1</v>
+      </c>
+      <c r="G19" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="44">
         <v>2012001</v>
       </c>
-      <c r="I19" s="42" t="s">
-        <v>24</v>
-      </c>
-      <c r="J19" s="42" t="s">
+      <c r="I19" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="J19" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="K19" s="42" t="s">
+      <c r="K19" s="44" t="s">
         <v>63</v>
       </c>
-      <c r="L19" s="44"/>
-      <c r="M19" s="42" t="s">
+      <c r="L19" s="46"/>
+      <c r="M19" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="N19" s="43">
-        <v>3</v>
-      </c>
-      <c r="O19" s="43">
-        <v>5</v>
-      </c>
-      <c r="Q19" s="45"/>
-    </row>
-    <row r="20" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A20" s="36" t="str">
+      <c r="N19" s="45">
+        <v>3</v>
+      </c>
+      <c r="O19" s="45">
+        <v>5</v>
+      </c>
+      <c r="Q19" s="47"/>
+    </row>
+    <row r="20" spans="1:17" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="38" t="str">
         <f t="shared" ref="A20:A30" si="1">B20&amp;C20</f>
         <v>1014001</v>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="30">
         <v>101400</v>
       </c>
-      <c r="C20" s="28">
-        <v>1</v>
-      </c>
-      <c r="D20" s="28" t="s">
+      <c r="C20" s="30">
+        <v>1</v>
+      </c>
+      <c r="D20" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="E20" s="28" t="s">
+      <c r="E20" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="F20" s="28">
-        <v>1</v>
-      </c>
-      <c r="G20" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="H20" s="36">
+      <c r="F20" s="30">
+        <v>1</v>
+      </c>
+      <c r="G20" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="38">
         <v>2014001</v>
       </c>
-      <c r="I20" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="J20" s="36"/>
-      <c r="K20" s="36"/>
-      <c r="L20" s="37" t="s">
+      <c r="I20" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="J20" s="38"/>
+      <c r="K20" s="38"/>
+      <c r="L20" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="M20" s="36" t="s">
+      <c r="M20" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="N20" s="19">
+      <c r="N20" s="21">
         <v>4</v>
       </c>
-      <c r="O20" s="19">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="46"/>
-    </row>
-    <row r="21" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A21" s="36" t="str">
+      <c r="O20" s="21">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="48"/>
+    </row>
+    <row r="21" spans="1:17" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="38" t="str">
         <f t="shared" si="1"/>
         <v>1014002</v>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="30">
         <v>101400</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="30">
         <v>2</v>
       </c>
-      <c r="D21" s="28" t="s">
+      <c r="D21" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="E21" s="28" t="s">
+      <c r="E21" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="28">
-        <v>1</v>
-      </c>
-      <c r="G21" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="H21" s="36">
+      <c r="F21" s="30">
+        <v>1</v>
+      </c>
+      <c r="G21" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="38">
         <v>2014001</v>
       </c>
-      <c r="I21" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="J21" s="36"/>
-      <c r="K21" s="36"/>
-      <c r="L21" s="37" t="s">
+      <c r="I21" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="J21" s="38"/>
+      <c r="K21" s="38"/>
+      <c r="L21" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="M21" s="36" t="s">
+      <c r="M21" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="N21" s="19">
+      <c r="N21" s="21">
         <v>4</v>
       </c>
-      <c r="O21" s="19">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="46"/>
-    </row>
-    <row r="22" s="3" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A22" s="36" t="str">
+      <c r="O21" s="21">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="48"/>
+    </row>
+    <row r="22" spans="1:17" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="38" t="str">
         <f t="shared" si="1"/>
         <v>1014003</v>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="30">
         <v>101400</v>
       </c>
-      <c r="C22" s="28">
-        <v>3</v>
-      </c>
-      <c r="D22" s="28" t="s">
+      <c r="C22" s="30">
+        <v>3</v>
+      </c>
+      <c r="D22" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="E22" s="28" t="s">
+      <c r="E22" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="F22" s="28">
-        <v>1</v>
-      </c>
-      <c r="G22" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="H22" s="36">
+      <c r="F22" s="30">
+        <v>1</v>
+      </c>
+      <c r="G22" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="38">
         <v>2014001</v>
       </c>
-      <c r="I22" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="J22" s="36"/>
-      <c r="K22" s="36"/>
-      <c r="L22" s="37">
+      <c r="I22" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="J22" s="38"/>
+      <c r="K22" s="38"/>
+      <c r="L22" s="39">
         <v>10140021</v>
       </c>
-      <c r="M22" s="36" t="s">
+      <c r="M22" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="N22" s="19">
+      <c r="N22" s="21">
         <v>4</v>
       </c>
-      <c r="O22" s="19">
-        <v>3</v>
-      </c>
-      <c r="Q22" s="46"/>
-    </row>
-    <row r="23" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A23" s="26" t="str">
+      <c r="O22" s="21">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="48"/>
+    </row>
+    <row r="23" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="28" t="str">
         <f t="shared" si="1"/>
         <v>1024001</v>
       </c>
-      <c r="B23" s="27">
+      <c r="B23" s="29">
         <v>102400</v>
       </c>
-      <c r="C23" s="27">
-        <v>1</v>
-      </c>
-      <c r="D23" s="27" t="s">
+      <c r="C23" s="29">
+        <v>1</v>
+      </c>
+      <c r="D23" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="E23" s="28" t="s">
+      <c r="E23" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="F23" s="27">
-        <v>1</v>
-      </c>
-      <c r="G23" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="H23" s="26">
+      <c r="F23" s="29">
+        <v>1</v>
+      </c>
+      <c r="G23" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="28">
         <v>2024001</v>
       </c>
-      <c r="I23" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="J23" s="26"/>
-      <c r="K23" s="26"/>
-      <c r="L23" s="29" t="s">
+      <c r="I23" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="J23" s="28"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="M23" s="26" t="s">
+      <c r="M23" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="N23" s="19">
+      <c r="N23" s="21">
         <v>4</v>
       </c>
-      <c r="O23" s="19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A24" s="26" t="str">
+      <c r="O23" s="21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="28" t="str">
         <f t="shared" si="1"/>
         <v>1024002</v>
       </c>
-      <c r="B24" s="27">
+      <c r="B24" s="29">
         <v>102400</v>
       </c>
-      <c r="C24" s="27">
+      <c r="C24" s="29">
         <v>2</v>
       </c>
-      <c r="D24" s="27"/>
-      <c r="E24" s="30" t="s">
+      <c r="D24" s="29"/>
+      <c r="E24" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="27">
-        <v>1</v>
-      </c>
-      <c r="G24" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="H24" s="26">
+      <c r="F24" s="29">
+        <v>1</v>
+      </c>
+      <c r="G24" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" s="28">
         <v>2024001</v>
       </c>
-      <c r="I24" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="J24" s="26"/>
-      <c r="K24" s="26"/>
-      <c r="L24" s="31" t="s">
+      <c r="I24" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="J24" s="28"/>
+      <c r="K24" s="28"/>
+      <c r="L24" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="M24" s="26" t="s">
+      <c r="M24" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="N24" s="19">
+      <c r="N24" s="21">
         <v>4</v>
       </c>
-      <c r="O24" s="19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A25" s="26" t="str">
+      <c r="O24" s="21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="28" t="str">
         <f t="shared" si="1"/>
         <v>1024003</v>
       </c>
-      <c r="B25" s="27">
+      <c r="B25" s="29">
         <v>102400</v>
       </c>
-      <c r="C25" s="27">
-        <v>3</v>
-      </c>
-      <c r="D25" s="27"/>
-      <c r="E25" s="32" t="s">
+      <c r="C25" s="29">
+        <v>3</v>
+      </c>
+      <c r="D25" s="29"/>
+      <c r="E25" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="F25" s="27">
-        <v>1</v>
-      </c>
-      <c r="G25" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="H25" s="26">
+      <c r="F25" s="29">
+        <v>1</v>
+      </c>
+      <c r="G25" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="28">
         <v>2024001</v>
       </c>
-      <c r="I25" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="J25" s="26"/>
-      <c r="K25" s="26"/>
-      <c r="L25" s="29" t="s">
+      <c r="I25" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="J25" s="28"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="M25" s="26" t="s">
+      <c r="M25" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="N25" s="19">
+      <c r="N25" s="21">
         <v>4</v>
       </c>
-      <c r="O25" s="19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A26" s="26" t="str">
+      <c r="O25" s="21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="28" t="str">
         <f t="shared" si="1"/>
         <v>1024004</v>
       </c>
-      <c r="B26" s="27">
+      <c r="B26" s="29">
         <v>102400</v>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="29">
         <v>4</v>
       </c>
-      <c r="D26" s="27"/>
-      <c r="E26" s="33" t="s">
+      <c r="D26" s="29"/>
+      <c r="E26" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="F26" s="34">
-        <v>1</v>
-      </c>
-      <c r="G26" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="H26" s="26">
+      <c r="F26" s="36">
+        <v>1</v>
+      </c>
+      <c r="G26" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="28">
         <v>2024001</v>
       </c>
-      <c r="I26" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="J26" s="26"/>
-      <c r="K26" s="26"/>
-      <c r="L26" s="29">
+      <c r="I26" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="J26" s="28"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="31">
         <v>10240041</v>
       </c>
-      <c r="M26" s="26" t="s">
+      <c r="M26" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="N26" s="19">
+      <c r="N26" s="21">
         <v>4</v>
       </c>
-      <c r="O26" s="19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A27" s="26" t="str">
+      <c r="O26" s="21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="28" t="str">
         <f t="shared" si="1"/>
         <v>1024005</v>
       </c>
-      <c r="B27" s="27">
+      <c r="B27" s="29">
         <v>102400</v>
       </c>
-      <c r="C27" s="27">
-        <v>5</v>
-      </c>
-      <c r="D27" s="27"/>
-      <c r="E27" s="35" t="s">
+      <c r="C27" s="29">
+        <v>5</v>
+      </c>
+      <c r="D27" s="29"/>
+      <c r="E27" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="F27" s="34">
-        <v>1</v>
-      </c>
-      <c r="G27" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="H27" s="26">
+      <c r="F27" s="36">
+        <v>1</v>
+      </c>
+      <c r="G27" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="H27" s="28">
         <v>2024001</v>
       </c>
-      <c r="I27" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="J27" s="26"/>
-      <c r="K27" s="26"/>
-      <c r="L27" s="29" t="s">
+      <c r="I27" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="J27" s="28"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="M27" s="26" t="s">
+      <c r="M27" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="N27" s="19">
+      <c r="N27" s="21">
         <v>4</v>
       </c>
-      <c r="O27" s="19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A28" s="26" t="str">
+      <c r="O27" s="21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="28" t="str">
         <f t="shared" si="1"/>
         <v>1024006</v>
       </c>
-      <c r="B28" s="27">
+      <c r="B28" s="29">
         <v>102400</v>
       </c>
-      <c r="C28" s="27">
+      <c r="C28" s="29">
         <v>6</v>
       </c>
-      <c r="D28" s="27"/>
-      <c r="E28" s="35" t="s">
+      <c r="D28" s="29"/>
+      <c r="E28" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="F28" s="34">
-        <v>1</v>
-      </c>
-      <c r="G28" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="H28" s="26">
+      <c r="F28" s="36">
+        <v>1</v>
+      </c>
+      <c r="G28" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28" s="28">
         <v>2024001</v>
       </c>
-      <c r="I28" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="J28" s="26"/>
-      <c r="K28" s="26"/>
-      <c r="L28" s="29">
+      <c r="I28" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="J28" s="28"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="31">
         <v>10240061</v>
       </c>
-      <c r="M28" s="26" t="s">
+      <c r="M28" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="N28" s="19">
+      <c r="N28" s="21">
         <v>4</v>
       </c>
-      <c r="O28" s="19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A29" s="26" t="str">
+      <c r="O28" s="21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="28" t="str">
         <f t="shared" si="1"/>
         <v>1024007</v>
       </c>
-      <c r="B29" s="27">
+      <c r="B29" s="29">
         <v>102400</v>
       </c>
-      <c r="C29" s="27">
+      <c r="C29" s="29">
         <v>7</v>
       </c>
-      <c r="D29" s="27"/>
-      <c r="E29" s="30" t="s">
+      <c r="D29" s="29"/>
+      <c r="E29" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="F29" s="27">
-        <v>1</v>
-      </c>
-      <c r="G29" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="H29" s="26">
+      <c r="F29" s="29">
+        <v>1</v>
+      </c>
+      <c r="G29" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="H29" s="28">
         <v>2024001</v>
       </c>
-      <c r="I29" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="J29" s="26"/>
-      <c r="K29" s="26"/>
-      <c r="L29" s="31" t="s">
+      <c r="I29" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="J29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="M29" s="26" t="s">
+      <c r="M29" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="N29" s="19">
+      <c r="N29" s="21">
         <v>4</v>
       </c>
-      <c r="O29" s="19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A30" s="26" t="str">
+      <c r="O29" s="21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="28" t="str">
         <f t="shared" si="1"/>
         <v>1017001</v>
       </c>
@@ -3477,16 +3012,16 @@
       <c r="M30" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="N30" s="47">
+      <c r="N30" s="49">
         <v>4</v>
       </c>
-      <c r="O30" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q30" s="20"/>
-    </row>
-    <row r="31" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A31" s="26" t="str">
+      <c r="O30" s="49">
+        <v>5</v>
+      </c>
+      <c r="Q30" s="22"/>
+    </row>
+    <row r="31" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="28" t="str">
         <f t="shared" ref="A31:A54" si="2">B31&amp;C31</f>
         <v>1017002</v>
       </c>
@@ -3520,16 +3055,16 @@
       <c r="M31" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="N31" s="47">
+      <c r="N31" s="49">
         <v>4</v>
       </c>
-      <c r="O31" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q31" s="20"/>
-    </row>
-    <row r="32" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A32" s="26" t="str">
+      <c r="O31" s="49">
+        <v>5</v>
+      </c>
+      <c r="Q31" s="22"/>
+    </row>
+    <row r="32" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A32" s="28" t="str">
         <f t="shared" si="2"/>
         <v>1017003</v>
       </c>
@@ -3563,16 +3098,16 @@
       <c r="M32" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N32" s="47">
+      <c r="N32" s="49">
         <v>4</v>
       </c>
-      <c r="O32" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q32" s="20"/>
-    </row>
-    <row r="33" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A33" s="26" t="str">
+      <c r="O32" s="49">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="22"/>
+    </row>
+    <row r="33" spans="1:19" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="28" t="str">
         <f t="shared" si="2"/>
         <v>1022001</v>
       </c>
@@ -3600,22 +3135,22 @@
       <c r="I33" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L33" s="48" t="s">
+      <c r="L33" s="50" t="s">
         <v>85</v>
       </c>
       <c r="M33" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N33" s="47">
-        <v>3</v>
-      </c>
-      <c r="O33" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q33" s="20"/>
-    </row>
-    <row r="34" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A34" s="26" t="str">
+      <c r="N33" s="49">
+        <v>3</v>
+      </c>
+      <c r="O33" s="49">
+        <v>5</v>
+      </c>
+      <c r="Q33" s="22"/>
+    </row>
+    <row r="34" spans="1:19" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="28" t="str">
         <f t="shared" si="2"/>
         <v>1022002</v>
       </c>
@@ -3631,10 +3166,10 @@
       <c r="E34" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="F34" s="19">
-        <v>1</v>
-      </c>
-      <c r="G34" s="49" t="s">
+      <c r="F34" s="21">
+        <v>1</v>
+      </c>
+      <c r="G34" s="51" t="s">
         <v>23</v>
       </c>
       <c r="H34" s="5">
@@ -3643,22 +3178,22 @@
       <c r="I34" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L34" s="48">
+      <c r="L34" s="50">
         <v>10220033</v>
       </c>
       <c r="M34" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N34" s="47">
-        <v>3</v>
-      </c>
-      <c r="O34" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q34" s="20"/>
-    </row>
-    <row r="35" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A35" s="26" t="str">
+      <c r="N34" s="49">
+        <v>3</v>
+      </c>
+      <c r="O34" s="49">
+        <v>5</v>
+      </c>
+      <c r="Q34" s="22"/>
+    </row>
+    <row r="35" spans="1:19" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="28" t="str">
         <f t="shared" si="2"/>
         <v>1022003</v>
       </c>
@@ -3674,10 +3209,10 @@
       <c r="E35" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F35" s="49">
-        <v>1</v>
-      </c>
-      <c r="G35" s="49" t="s">
+      <c r="F35" s="51">
+        <v>1</v>
+      </c>
+      <c r="G35" s="51" t="s">
         <v>23</v>
       </c>
       <c r="H35" s="5">
@@ -3686,22 +3221,22 @@
       <c r="I35" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L35" s="50" t="s">
+      <c r="L35" s="52" t="s">
         <v>89</v>
       </c>
       <c r="M35" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N35" s="47">
-        <v>3</v>
-      </c>
-      <c r="O35" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q35" s="20"/>
-    </row>
-    <row r="36" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A36" s="26" t="str">
+      <c r="N35" s="49">
+        <v>3</v>
+      </c>
+      <c r="O35" s="49">
+        <v>5</v>
+      </c>
+      <c r="Q35" s="22"/>
+    </row>
+    <row r="36" spans="1:19" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="28" t="str">
         <f t="shared" si="2"/>
         <v>1022004</v>
       </c>
@@ -3717,10 +3252,10 @@
       <c r="E36" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F36" s="19">
-        <v>1</v>
-      </c>
-      <c r="G36" s="49" t="s">
+      <c r="F36" s="21">
+        <v>1</v>
+      </c>
+      <c r="G36" s="51" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="5">
@@ -3729,19 +3264,19 @@
       <c r="I36" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L36" s="48">
+      <c r="L36" s="50">
         <v>10220020</v>
       </c>
-      <c r="N36" s="47">
-        <v>3</v>
-      </c>
-      <c r="O36" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q36" s="20"/>
-    </row>
-    <row r="37" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A37" s="26" t="str">
+      <c r="N36" s="49">
+        <v>3</v>
+      </c>
+      <c r="O36" s="49">
+        <v>5</v>
+      </c>
+      <c r="Q36" s="22"/>
+    </row>
+    <row r="37" spans="1:19" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A37" s="28" t="str">
         <f t="shared" si="2"/>
         <v>1022005</v>
       </c>
@@ -3769,20 +3304,20 @@
       <c r="I37" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L37" s="48">
+      <c r="L37" s="50">
         <v>10220019</v>
       </c>
-      <c r="N37" s="47">
-        <v>3</v>
-      </c>
-      <c r="O37" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q37" s="20"/>
-      <c r="S37" s="51"/>
-    </row>
-    <row r="38" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A38" s="26" t="str">
+      <c r="N37" s="49">
+        <v>3</v>
+      </c>
+      <c r="O37" s="49">
+        <v>5</v>
+      </c>
+      <c r="Q37" s="22"/>
+      <c r="S37" s="53"/>
+    </row>
+    <row r="38" spans="1:19" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A38" s="28" t="str">
         <f t="shared" si="2"/>
         <v>1021001</v>
       </c>
@@ -3810,23 +3345,23 @@
       <c r="I38" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L38" s="48" t="s">
+      <c r="L38" s="50" t="s">
         <v>93</v>
       </c>
       <c r="M38" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N38" s="47">
-        <v>3</v>
-      </c>
-      <c r="O38" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q38" s="20"/>
-      <c r="S38" s="51"/>
-    </row>
-    <row r="39" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A39" s="26" t="str">
+      <c r="N38" s="49">
+        <v>3</v>
+      </c>
+      <c r="O38" s="49">
+        <v>5</v>
+      </c>
+      <c r="Q38" s="22"/>
+      <c r="S38" s="53"/>
+    </row>
+    <row r="39" spans="1:19" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A39" s="28" t="str">
         <f t="shared" si="2"/>
         <v>1021002</v>
       </c>
@@ -3854,23 +3389,23 @@
       <c r="I39" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L39" s="48">
+      <c r="L39" s="50">
         <v>10210031</v>
       </c>
       <c r="M39" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N39" s="47">
-        <v>3</v>
-      </c>
-      <c r="O39" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q39" s="20"/>
-      <c r="S39" s="51"/>
-    </row>
-    <row r="40" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A40" s="26" t="str">
+      <c r="N39" s="49">
+        <v>3</v>
+      </c>
+      <c r="O39" s="49">
+        <v>5</v>
+      </c>
+      <c r="Q39" s="22"/>
+      <c r="S39" s="53"/>
+    </row>
+    <row r="40" spans="1:19" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A40" s="28" t="str">
         <f t="shared" si="2"/>
         <v>1021003</v>
       </c>
@@ -3898,23 +3433,23 @@
       <c r="I40" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L40" s="48">
+      <c r="L40" s="50">
         <v>10210041</v>
       </c>
       <c r="M40" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="N40" s="47">
-        <v>3</v>
-      </c>
-      <c r="O40" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q40" s="20"/>
-      <c r="S40" s="51"/>
-    </row>
-    <row r="41" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A41" s="26" t="str">
+      <c r="N40" s="49">
+        <v>3</v>
+      </c>
+      <c r="O40" s="49">
+        <v>5</v>
+      </c>
+      <c r="Q40" s="22"/>
+      <c r="S40" s="53"/>
+    </row>
+    <row r="41" spans="1:19" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A41" s="28" t="str">
         <f t="shared" si="2"/>
         <v>1021004</v>
       </c>
@@ -3942,23 +3477,23 @@
       <c r="I41" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L41" s="48" t="s">
+      <c r="L41" s="50" t="s">
         <v>96</v>
       </c>
       <c r="M41" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N41" s="47">
-        <v>3</v>
-      </c>
-      <c r="O41" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q41" s="20"/>
-      <c r="S41" s="51"/>
-    </row>
-    <row r="42" s="5" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A42" s="26" t="str">
+      <c r="N41" s="49">
+        <v>3</v>
+      </c>
+      <c r="O41" s="49">
+        <v>5</v>
+      </c>
+      <c r="Q41" s="22"/>
+      <c r="S41" s="53"/>
+    </row>
+    <row r="42" spans="1:19" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A42" s="28" t="str">
         <f t="shared" si="2"/>
         <v>1018001</v>
       </c>
@@ -3986,22 +3521,22 @@
       <c r="I42" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L42" s="48" t="s">
+      <c r="L42" s="50" t="s">
         <v>98</v>
       </c>
       <c r="M42" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N42" s="47">
+      <c r="N42" s="49">
         <v>4</v>
       </c>
-      <c r="O42" s="47">
+      <c r="O42" s="49">
         <v>6</v>
       </c>
-      <c r="Q42" s="20"/>
-      <c r="S42" s="51"/>
-    </row>
-    <row r="43" s="5" customFormat="1" ht="16.5" spans="1:19">
+      <c r="Q42" s="22"/>
+      <c r="S42" s="53"/>
+    </row>
+    <row r="43" spans="1:19" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="str">
         <f t="shared" si="2"/>
         <v>1018002</v>
@@ -4030,20 +3565,20 @@
       <c r="I43" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L43" s="48">
+      <c r="L43" s="50">
         <v>10180031</v>
       </c>
       <c r="M43" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N43" s="47">
+      <c r="N43" s="49">
         <v>4</v>
       </c>
-      <c r="O43" s="47">
+      <c r="O43" s="49">
         <v>6</v>
       </c>
     </row>
-    <row r="44" ht="16.5" spans="1:19">
+    <row r="44" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="str">
         <f t="shared" si="2"/>
         <v>1018003</v>
@@ -4072,20 +3607,20 @@
       <c r="I44" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L44" s="48" t="s">
+      <c r="L44" s="50" t="s">
         <v>99</v>
       </c>
       <c r="M44" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N44" s="47">
+      <c r="N44" s="49">
         <v>4</v>
       </c>
-      <c r="O44" s="47">
+      <c r="O44" s="49">
         <v>6</v>
       </c>
     </row>
-    <row r="45" customFormat="1" ht="16.5" spans="1:19">
+    <row r="45" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="str">
         <f t="shared" si="2"/>
         <v>1025001</v>
@@ -4114,21 +3649,20 @@
       <c r="I45" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L45" s="48" t="s">
+      <c r="L45" s="50" t="s">
         <v>101</v>
       </c>
       <c r="M45" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N45" s="47">
-        <v>3</v>
-      </c>
-      <c r="O45" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q45" s="10"/>
-    </row>
-    <row r="46" customFormat="1" ht="16.5" spans="1:19">
+      <c r="N45" s="49">
+        <v>3</v>
+      </c>
+      <c r="O45" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="str">
         <f t="shared" si="2"/>
         <v>1025002</v>
@@ -4157,21 +3691,20 @@
       <c r="I46" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L46" s="48">
+      <c r="L46" s="50">
         <v>10250031</v>
       </c>
       <c r="M46" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="N46" s="47">
-        <v>3</v>
-      </c>
-      <c r="O46" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q46" s="10"/>
-    </row>
-    <row r="47" customFormat="1" ht="16.5" spans="1:19">
+      <c r="N46" s="49">
+        <v>3</v>
+      </c>
+      <c r="O46" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A47" s="5" t="str">
         <f t="shared" si="2"/>
         <v>1025003</v>
@@ -4200,21 +3733,20 @@
       <c r="I47" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L47" s="48" t="s">
+      <c r="L47" s="50" t="s">
         <v>103</v>
       </c>
       <c r="M47" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N47" s="47">
-        <v>3</v>
-      </c>
-      <c r="O47" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q47" s="10"/>
-    </row>
-    <row r="48" customFormat="1" ht="16.5" spans="1:19">
+      <c r="N47" s="49">
+        <v>3</v>
+      </c>
+      <c r="O47" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A48" s="5" t="str">
         <f t="shared" si="2"/>
         <v>1023001</v>
@@ -4243,21 +3775,20 @@
       <c r="I48" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L48" s="48" t="s">
+      <c r="L48" s="50" t="s">
         <v>105</v>
       </c>
       <c r="M48" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N48" s="47">
+      <c r="N48" s="49">
         <v>4</v>
       </c>
-      <c r="O48" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q48" s="10"/>
-    </row>
-    <row r="49" customFormat="1" ht="16.5" spans="1:17">
+      <c r="O48" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="str">
         <f t="shared" si="2"/>
         <v>1023002</v>
@@ -4286,21 +3817,20 @@
       <c r="I49" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L49" s="48">
+      <c r="L49" s="50">
         <v>10230003</v>
       </c>
       <c r="M49" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="N49" s="47">
+      <c r="N49" s="49">
         <v>4</v>
       </c>
-      <c r="O49" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q49" s="10"/>
-    </row>
-    <row r="50" customFormat="1" ht="16.5" spans="1:17">
+      <c r="O49" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A50" s="5" t="str">
         <f t="shared" si="2"/>
         <v>1023003</v>
@@ -4329,21 +3859,20 @@
       <c r="I50" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L50" s="48" t="s">
+      <c r="L50" s="50" t="s">
         <v>106</v>
       </c>
       <c r="M50" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N50" s="47">
+      <c r="N50" s="49">
         <v>4</v>
       </c>
-      <c r="O50" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q50" s="10"/>
-    </row>
-    <row r="51" customFormat="1" ht="16.5" spans="1:17">
+      <c r="O50" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A51" s="5" t="str">
         <f t="shared" si="2"/>
         <v>1034001</v>
@@ -4372,21 +3901,20 @@
       <c r="I51" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L51" s="48">
+      <c r="L51" s="50">
         <v>10340007</v>
       </c>
       <c r="M51" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="N51" s="47">
-        <v>3</v>
-      </c>
-      <c r="O51" s="47">
-        <v>3</v>
-      </c>
-      <c r="Q51" s="10"/>
-    </row>
-    <row r="52" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N51" s="49">
+        <v>3</v>
+      </c>
+      <c r="O51" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="str">
         <f t="shared" si="2"/>
         <v>1034002</v>
@@ -4415,18 +3943,17 @@
       <c r="I52" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L52" s="48"/>
+      <c r="L52" s="50"/>
       <c r="M52" s="5"/>
-      <c r="N52" s="47">
-        <v>3</v>
-      </c>
-      <c r="O52" s="47">
-        <v>3</v>
-      </c>
-      <c r="P52" s="52"/>
-      <c r="Q52" s="10"/>
-    </row>
-    <row r="53" s="6" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N52" s="49">
+        <v>3</v>
+      </c>
+      <c r="O52" s="49">
+        <v>3</v>
+      </c>
+      <c r="P52" s="10"/>
+    </row>
+    <row r="53" spans="1:17" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A53" s="5" t="str">
         <f t="shared" si="2"/>
         <v>1034003</v>
@@ -4443,7 +3970,7 @@
       <c r="E53" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F53" s="53">
+      <c r="F53" s="54">
         <v>1</v>
       </c>
       <c r="G53" s="5" t="s">
@@ -4455,62 +3982,62 @@
       <c r="I53" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L53" s="50"/>
-      <c r="M53" s="53"/>
-      <c r="N53" s="47">
-        <v>3</v>
-      </c>
-      <c r="O53" s="47">
-        <v>3</v>
-      </c>
-      <c r="Q53" s="54"/>
-    </row>
-    <row r="54" s="6" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A54" s="53" t="str">
+      <c r="L53" s="52"/>
+      <c r="M53" s="54"/>
+      <c r="N53" s="49">
+        <v>3</v>
+      </c>
+      <c r="O53" s="49">
+        <v>3</v>
+      </c>
+      <c r="Q53" s="55"/>
+    </row>
+    <row r="54" spans="1:17" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A54" s="54" t="str">
         <f t="shared" si="2"/>
         <v>1035001</v>
       </c>
-      <c r="B54" s="53">
+      <c r="B54" s="54">
         <v>103500</v>
       </c>
-      <c r="C54" s="53">
-        <v>1</v>
-      </c>
-      <c r="D54" s="53" t="s">
+      <c r="C54" s="54">
+        <v>1</v>
+      </c>
+      <c r="D54" s="54" t="s">
         <v>110</v>
       </c>
-      <c r="E54" s="53" t="s">
+      <c r="E54" s="54" t="s">
         <v>111</v>
       </c>
-      <c r="F54" s="53">
-        <v>1</v>
-      </c>
-      <c r="G54" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="H54" s="53">
+      <c r="F54" s="54">
+        <v>1</v>
+      </c>
+      <c r="G54" s="54" t="s">
+        <v>23</v>
+      </c>
+      <c r="H54" s="54">
         <v>2035001</v>
       </c>
-      <c r="I54" s="53" t="s">
-        <v>24</v>
-      </c>
-      <c r="L54" s="50" t="s">
+      <c r="I54" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="L54" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="M54" s="53" t="s">
+      <c r="M54" s="54" t="s">
         <v>113</v>
       </c>
-      <c r="N54" s="47">
+      <c r="N54" s="49">
         <v>4</v>
       </c>
-      <c r="O54" s="47">
-        <v>3</v>
-      </c>
-      <c r="Q54" s="54"/>
-    </row>
-    <row r="55" customFormat="1" ht="16.5" spans="1:17">
+      <c r="O54" s="49">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="55"/>
+    </row>
+    <row r="55" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A55" s="5" t="str">
-        <f t="shared" ref="A54:A108" si="3">B55&amp;C55</f>
+        <f t="shared" ref="A55:A108" si="3">B55&amp;C55</f>
         <v>1035002</v>
       </c>
       <c r="B55" s="5">
@@ -4537,21 +4064,20 @@
       <c r="I55" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L55" s="48" t="s">
+      <c r="L55" s="50" t="s">
         <v>115</v>
       </c>
       <c r="M55" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="N55" s="47">
+      <c r="N55" s="49">
         <v>4</v>
       </c>
-      <c r="O55" s="47">
-        <v>3</v>
-      </c>
-      <c r="Q55" s="10"/>
-    </row>
-    <row r="56" customFormat="1" ht="16.5" spans="1:17">
+      <c r="O55" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A56" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1035003</v>
@@ -4580,22 +4106,21 @@
       <c r="I56" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L56" s="48" t="s">
+      <c r="L56" s="50" t="s">
         <v>117</v>
       </c>
       <c r="M56" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="N56" s="47">
+      <c r="N56" s="49">
         <v>4</v>
       </c>
-      <c r="O56" s="47">
-        <v>3</v>
-      </c>
-      <c r="Q56" s="10"/>
-    </row>
-    <row r="57" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A57" s="55">
+      <c r="O56" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A57" s="56">
         <v>1035011</v>
       </c>
       <c r="B57" s="5">
@@ -4622,21 +4147,20 @@
       <c r="I57" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L57" s="48" t="s">
+      <c r="L57" s="50" t="s">
         <v>120</v>
       </c>
       <c r="M57" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="N57" s="47">
+      <c r="N57" s="49">
         <v>4</v>
       </c>
-      <c r="O57" s="47">
-        <v>3</v>
-      </c>
-      <c r="Q57" s="10"/>
-    </row>
-    <row r="58" customFormat="1" ht="16.5" spans="1:17">
+      <c r="O57" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A58" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1035012</v>
@@ -4665,21 +4189,20 @@
       <c r="I58" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L58" s="48" t="s">
+      <c r="L58" s="50" t="s">
         <v>121</v>
       </c>
       <c r="M58" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="N58" s="47">
+      <c r="N58" s="49">
         <v>4</v>
       </c>
-      <c r="O58" s="47">
-        <v>3</v>
-      </c>
-      <c r="Q58" s="10"/>
-    </row>
-    <row r="59" customFormat="1" ht="16.5" spans="1:17">
+      <c r="O58" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A59" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1035013</v>
@@ -4708,21 +4231,20 @@
       <c r="I59" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L59" s="48" t="s">
+      <c r="L59" s="50" t="s">
         <v>122</v>
       </c>
       <c r="M59" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="N59" s="47">
+      <c r="N59" s="49">
         <v>4</v>
       </c>
-      <c r="O59" s="47">
-        <v>3</v>
-      </c>
-      <c r="Q59" s="10"/>
-    </row>
-    <row r="60" customFormat="1" ht="16.5" spans="1:17">
+      <c r="O59" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A60" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1036001</v>
@@ -4751,23 +4273,22 @@
       <c r="I60" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L60" s="48" t="s">
+      <c r="L60" s="50" t="s">
         <v>124</v>
       </c>
       <c r="M60" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="N60" s="47">
-        <v>3</v>
-      </c>
-      <c r="O60" s="47">
-        <v>3</v>
-      </c>
-      <c r="Q60" s="10"/>
-    </row>
-    <row r="61" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N60" s="49">
+        <v>3</v>
+      </c>
+      <c r="O60" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A61" s="5" t="str">
-        <f>B61&amp;C61</f>
+        <f t="shared" si="3"/>
         <v>1036002</v>
       </c>
       <c r="B61" s="5">
@@ -4794,21 +4315,20 @@
       <c r="I61" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L61" s="48">
+      <c r="L61" s="50">
         <v>10360004</v>
       </c>
       <c r="M61" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="N61" s="47">
-        <v>3</v>
-      </c>
-      <c r="O61" s="47">
-        <v>3</v>
-      </c>
-      <c r="Q61" s="10"/>
-    </row>
-    <row r="62" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N61" s="49">
+        <v>3</v>
+      </c>
+      <c r="O61" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A62" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1036003</v>
@@ -4837,21 +4357,20 @@
       <c r="I62" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L62" s="48">
+      <c r="L62" s="50">
         <v>10360002</v>
       </c>
       <c r="M62" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="N62" s="47">
-        <v>3</v>
-      </c>
-      <c r="O62" s="47">
-        <v>3</v>
-      </c>
-      <c r="Q62" s="10"/>
-    </row>
-    <row r="63" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N62" s="49">
+        <v>3</v>
+      </c>
+      <c r="O62" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A63" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1028001</v>
@@ -4880,21 +4399,20 @@
       <c r="I63" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L63" s="48" t="s">
+      <c r="L63" s="50" t="s">
         <v>130</v>
       </c>
       <c r="M63" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="N63" s="47">
-        <v>5</v>
-      </c>
-      <c r="O63" s="47">
+      <c r="N63" s="49">
+        <v>5</v>
+      </c>
+      <c r="O63" s="49">
         <v>6</v>
       </c>
-      <c r="Q63" s="10"/>
-    </row>
-    <row r="64" customFormat="1" ht="16.5" spans="1:17">
+    </row>
+    <row r="64" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A64" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1028002</v>
@@ -4923,21 +4441,20 @@
       <c r="I64" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L64" s="48">
+      <c r="L64" s="50">
         <v>10280002</v>
       </c>
       <c r="M64" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="N64" s="47">
-        <v>5</v>
-      </c>
-      <c r="O64" s="47">
+      <c r="N64" s="49">
+        <v>5</v>
+      </c>
+      <c r="O64" s="49">
         <v>6</v>
       </c>
-      <c r="Q64" s="10"/>
-    </row>
-    <row r="65" customFormat="1" ht="16.5" spans="1:17">
+    </row>
+    <row r="65" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A65" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1028003</v>
@@ -4966,21 +4483,20 @@
       <c r="I65" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L65" s="48" t="s">
+      <c r="L65" s="50" t="s">
         <v>133</v>
       </c>
       <c r="M65" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N65" s="47">
-        <v>5</v>
-      </c>
-      <c r="O65" s="47">
+      <c r="N65" s="49">
+        <v>5</v>
+      </c>
+      <c r="O65" s="49">
         <v>6</v>
       </c>
-      <c r="Q65" s="10"/>
-    </row>
-    <row r="66" customFormat="1" ht="16.5" spans="1:17">
+    </row>
+    <row r="66" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A66" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1034011</v>
@@ -5009,21 +4525,20 @@
       <c r="I66" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L66" s="48">
-        <v>10340007</v>
+      <c r="L66" s="50">
+        <v>10340101</v>
       </c>
       <c r="M66" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="N66" s="47">
-        <v>3</v>
-      </c>
-      <c r="O66" s="47">
-        <v>3</v>
-      </c>
-      <c r="Q66" s="10"/>
-    </row>
-    <row r="67" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N66" s="49">
+        <v>3</v>
+      </c>
+      <c r="O66" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A67" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1034012</v>
@@ -5052,18 +4567,17 @@
       <c r="I67" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L67" s="48"/>
+      <c r="L67" s="50"/>
       <c r="M67" s="5"/>
-      <c r="N67" s="47">
-        <v>3</v>
-      </c>
-      <c r="O67" s="47">
-        <v>3</v>
-      </c>
-      <c r="P67" s="52"/>
-      <c r="Q67" s="10"/>
-    </row>
-    <row r="68" s="7" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N67" s="49">
+        <v>3</v>
+      </c>
+      <c r="O67" s="49">
+        <v>3</v>
+      </c>
+      <c r="P67" s="10"/>
+    </row>
+    <row r="68" spans="1:17" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A68" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1034013</v>
@@ -5094,60 +4608,60 @@
       </c>
       <c r="J68"/>
       <c r="K68"/>
-      <c r="L68" s="48"/>
+      <c r="L68" s="50"/>
       <c r="M68" s="5"/>
-      <c r="N68" s="47">
-        <v>3</v>
-      </c>
-      <c r="O68" s="47">
-        <v>3</v>
-      </c>
-      <c r="Q68" s="56"/>
-    </row>
-    <row r="69" s="7" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A69" s="57" t="str">
+      <c r="N68" s="49">
+        <v>3</v>
+      </c>
+      <c r="O68" s="49">
+        <v>3</v>
+      </c>
+      <c r="Q68" s="57"/>
+    </row>
+    <row r="69" spans="1:17" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A69" s="58" t="str">
         <f t="shared" si="3"/>
         <v>1020001</v>
       </c>
-      <c r="B69" s="57">
+      <c r="B69" s="58">
         <v>102000</v>
       </c>
-      <c r="C69" s="57">
-        <v>1</v>
-      </c>
-      <c r="D69" s="57" t="s">
+      <c r="C69" s="58">
+        <v>1</v>
+      </c>
+      <c r="D69" s="58" t="s">
         <v>136</v>
       </c>
-      <c r="E69" s="57" t="s">
+      <c r="E69" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="F69" s="57">
-        <v>1</v>
-      </c>
-      <c r="G69" s="57" t="s">
-        <v>23</v>
-      </c>
-      <c r="H69" s="57">
+      <c r="F69" s="58">
+        <v>1</v>
+      </c>
+      <c r="G69" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="H69" s="58">
         <v>2020001</v>
       </c>
-      <c r="I69" s="57" t="s">
-        <v>24</v>
-      </c>
-      <c r="L69" s="58" t="s">
+      <c r="I69" s="58" t="s">
+        <v>24</v>
+      </c>
+      <c r="L69" s="59" t="s">
         <v>137</v>
       </c>
-      <c r="M69" s="57" t="s">
+      <c r="M69" s="58" t="s">
         <v>138</v>
       </c>
-      <c r="N69" s="59">
-        <v>5</v>
-      </c>
-      <c r="O69" s="59">
-        <v>5</v>
-      </c>
-      <c r="Q69" s="56"/>
-    </row>
-    <row r="70" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N69" s="60">
+        <v>5</v>
+      </c>
+      <c r="O69" s="60">
+        <v>5</v>
+      </c>
+      <c r="Q69" s="57"/>
+    </row>
+    <row r="70" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A70" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1020002</v>
@@ -5176,21 +4690,20 @@
       <c r="I70" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L70" s="48" t="s">
+      <c r="L70" s="50" t="s">
         <v>139</v>
       </c>
       <c r="M70" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="N70" s="47">
-        <v>5</v>
-      </c>
-      <c r="O70" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q70" s="10"/>
-    </row>
-    <row r="71" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N70" s="49">
+        <v>5</v>
+      </c>
+      <c r="O70" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A71" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1020003</v>
@@ -5219,64 +4732,63 @@
       <c r="I71" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L71" s="48" t="s">
+      <c r="L71" s="50" t="s">
         <v>141</v>
       </c>
       <c r="M71" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="N71" s="47">
-        <v>5</v>
-      </c>
-      <c r="O71" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q71" s="10"/>
-    </row>
-    <row r="72" s="8" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A72" s="60" t="str">
+      <c r="N71" s="49">
+        <v>5</v>
+      </c>
+      <c r="O71" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A72" s="61" t="str">
         <f t="shared" si="3"/>
         <v>1020004</v>
       </c>
-      <c r="B72" s="60">
+      <c r="B72" s="61">
         <v>102000</v>
       </c>
-      <c r="C72" s="60">
+      <c r="C72" s="61">
         <v>4</v>
       </c>
-      <c r="D72" s="60" t="s">
+      <c r="D72" s="61" t="s">
         <v>136</v>
       </c>
-      <c r="E72" s="60" t="s">
+      <c r="E72" s="61" t="s">
         <v>143</v>
       </c>
-      <c r="F72" s="60">
-        <v>1</v>
-      </c>
-      <c r="G72" s="60" t="s">
-        <v>23</v>
-      </c>
-      <c r="H72" s="60">
+      <c r="F72" s="61">
+        <v>1</v>
+      </c>
+      <c r="G72" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="H72" s="61">
         <v>2020002</v>
       </c>
-      <c r="I72" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="L72" s="61">
+      <c r="I72" s="61" t="s">
+        <v>24</v>
+      </c>
+      <c r="L72" s="62">
         <v>10200016</v>
       </c>
-      <c r="M72" s="60" t="s">
+      <c r="M72" s="61" t="s">
         <v>144</v>
       </c>
-      <c r="N72" s="62">
-        <v>5</v>
-      </c>
-      <c r="O72" s="62">
-        <v>5</v>
-      </c>
-      <c r="Q72" s="63"/>
-    </row>
-    <row r="73" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N72" s="63">
+        <v>5</v>
+      </c>
+      <c r="O72" s="63">
+        <v>5</v>
+      </c>
+      <c r="Q72" s="64"/>
+    </row>
+    <row r="73" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A73" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1020005</v>
@@ -5305,21 +4817,20 @@
       <c r="I73" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L73" s="48">
+      <c r="L73" s="50">
         <v>10200021</v>
       </c>
       <c r="M73" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="N73" s="47">
-        <v>5</v>
-      </c>
-      <c r="O73" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q73" s="10"/>
-    </row>
-    <row r="74" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N73" s="49">
+        <v>5</v>
+      </c>
+      <c r="O73" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A74" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1038001</v>
@@ -5351,19 +4862,18 @@
       <c r="J74" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="L74" s="48"/>
+      <c r="L74" s="50"/>
       <c r="M74" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="N74" s="47">
-        <v>3</v>
-      </c>
-      <c r="O74" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q74" s="10"/>
-    </row>
-    <row r="75" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N74" s="49">
+        <v>3</v>
+      </c>
+      <c r="O74" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A75" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1038002</v>
@@ -5392,21 +4902,20 @@
       <c r="I75" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L75" s="48">
+      <c r="L75" s="50">
         <v>10380002</v>
       </c>
       <c r="M75" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="N75" s="47">
-        <v>3</v>
-      </c>
-      <c r="O75" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q75" s="10"/>
-    </row>
-    <row r="76" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N75" s="49">
+        <v>3</v>
+      </c>
+      <c r="O75" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A76" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1038004</v>
@@ -5435,21 +4944,20 @@
       <c r="I76" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L76" s="48" t="s">
+      <c r="L76" s="50" t="s">
         <v>152</v>
       </c>
       <c r="M76" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="N76" s="47">
-        <v>3</v>
-      </c>
-      <c r="O76" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q76" s="10"/>
-    </row>
-    <row r="77" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N76" s="49">
+        <v>3</v>
+      </c>
+      <c r="O76" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A77" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1038003</v>
@@ -5478,21 +4986,20 @@
       <c r="I77" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L77" s="48" t="s">
+      <c r="L77" s="50" t="s">
         <v>154</v>
       </c>
       <c r="M77" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="N77" s="47">
-        <v>3</v>
-      </c>
-      <c r="O77" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q77" s="10"/>
-    </row>
-    <row r="78" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N77" s="49">
+        <v>3</v>
+      </c>
+      <c r="O77" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A78" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1027001</v>
@@ -5521,21 +5028,20 @@
       <c r="I78" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L78" s="48" t="s">
+      <c r="L78" s="50" t="s">
         <v>157</v>
       </c>
       <c r="M78" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="N78" s="47">
-        <v>3</v>
-      </c>
-      <c r="O78" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q78" s="10"/>
-    </row>
-    <row r="79" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N78" s="49">
+        <v>3</v>
+      </c>
+      <c r="O78" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A79" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1027002</v>
@@ -5564,21 +5070,20 @@
       <c r="I79" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L79" s="48">
+      <c r="L79" s="50">
         <v>10270003</v>
       </c>
       <c r="M79" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="N79" s="47">
-        <v>3</v>
-      </c>
-      <c r="O79" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q79" s="10"/>
-    </row>
-    <row r="80" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N79" s="49">
+        <v>3</v>
+      </c>
+      <c r="O79" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A80" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1027003</v>
@@ -5607,21 +5112,20 @@
       <c r="I80" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L80" s="48" t="s">
+      <c r="L80" s="50" t="s">
         <v>160</v>
       </c>
       <c r="M80" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="N80" s="47">
-        <v>3</v>
-      </c>
-      <c r="O80" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q80" s="10"/>
-    </row>
-    <row r="81" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N80" s="49">
+        <v>3</v>
+      </c>
+      <c r="O80" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A81" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1037001</v>
@@ -5650,21 +5154,20 @@
       <c r="I81" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L81" s="48" t="s">
+      <c r="L81" s="50" t="s">
         <v>163</v>
       </c>
       <c r="M81" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="N81" s="47">
+      <c r="N81" s="49">
         <v>4</v>
       </c>
-      <c r="O81" s="47">
-        <v>3</v>
-      </c>
-      <c r="Q81" s="10"/>
-    </row>
-    <row r="82" customFormat="1" ht="16.5" spans="1:17">
+      <c r="O81" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A82" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1037002</v>
@@ -5693,21 +5196,20 @@
       <c r="I82" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L82" s="48" t="s">
+      <c r="L82" s="50" t="s">
         <v>166</v>
       </c>
       <c r="M82" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="N82" s="47">
+      <c r="N82" s="49">
         <v>4</v>
       </c>
-      <c r="O82" s="47">
-        <v>3</v>
-      </c>
-      <c r="Q82" s="10"/>
-    </row>
-    <row r="83" customFormat="1" ht="16.5" spans="1:17">
+      <c r="O82" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A83" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1037003</v>
@@ -5736,21 +5238,20 @@
       <c r="I83" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L83" s="48">
+      <c r="L83" s="50">
         <v>10370003</v>
       </c>
       <c r="M83" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="N83" s="47">
+      <c r="N83" s="49">
         <v>4</v>
       </c>
-      <c r="O83" s="47">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="10"/>
-    </row>
-    <row r="84" customFormat="1" ht="16.5" spans="1:17">
+      <c r="O83" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A84" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1031001</v>
@@ -5779,21 +5280,20 @@
       <c r="I84" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L84" s="48" t="s">
+      <c r="L84" s="50" t="s">
         <v>169</v>
       </c>
       <c r="M84" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="N84" s="47">
-        <v>3</v>
-      </c>
-      <c r="O84" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q84" s="10"/>
-    </row>
-    <row r="85" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N84" s="49">
+        <v>3</v>
+      </c>
+      <c r="O84" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A85" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1031002</v>
@@ -5822,21 +5322,20 @@
       <c r="I85" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L85" s="48">
+      <c r="L85" s="50">
         <v>10310008</v>
       </c>
       <c r="M85" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="N85" s="47">
-        <v>3</v>
-      </c>
-      <c r="O85" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q85" s="10"/>
-    </row>
-    <row r="86" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N85" s="49">
+        <v>3</v>
+      </c>
+      <c r="O85" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A86" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1031003</v>
@@ -5865,21 +5364,20 @@
       <c r="I86" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L86" s="48" t="s">
+      <c r="L86" s="50" t="s">
         <v>172</v>
       </c>
       <c r="M86" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="N86" s="47">
-        <v>3</v>
-      </c>
-      <c r="O86" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q86" s="10"/>
-    </row>
-    <row r="87" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N86" s="49">
+        <v>3</v>
+      </c>
+      <c r="O86" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A87" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1031004</v>
@@ -5908,21 +5406,20 @@
       <c r="I87" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L87" s="48" t="s">
+      <c r="L87" s="50" t="s">
         <v>174</v>
       </c>
       <c r="M87" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="N87" s="47">
-        <v>3</v>
-      </c>
-      <c r="O87" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q87" s="10"/>
-    </row>
-    <row r="88" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N87" s="49">
+        <v>3</v>
+      </c>
+      <c r="O87" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A88" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1031005</v>
@@ -5951,21 +5448,20 @@
       <c r="I88" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L88" s="48">
+      <c r="L88" s="50">
         <v>10310003</v>
       </c>
       <c r="M88" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="N88" s="47">
-        <v>3</v>
-      </c>
-      <c r="O88" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q88" s="10"/>
-    </row>
-    <row r="89" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N88" s="49">
+        <v>3</v>
+      </c>
+      <c r="O88" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A89" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1031006</v>
@@ -5994,21 +5490,20 @@
       <c r="I89" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L89" s="48" t="s">
+      <c r="L89" s="50" t="s">
         <v>179</v>
       </c>
       <c r="M89" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="N89" s="47">
-        <v>3</v>
-      </c>
-      <c r="O89" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q89" s="10"/>
-    </row>
-    <row r="90" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N89" s="49">
+        <v>3</v>
+      </c>
+      <c r="O89" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A90" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1040001</v>
@@ -6037,21 +5532,20 @@
       <c r="I90" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L90" s="48" t="s">
+      <c r="L90" s="50" t="s">
         <v>182</v>
       </c>
       <c r="M90" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="N90" s="47">
-        <v>3</v>
-      </c>
-      <c r="O90" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q90" s="10"/>
-    </row>
-    <row r="91" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N90" s="49">
+        <v>3</v>
+      </c>
+      <c r="O90" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A91" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1040002</v>
@@ -6080,21 +5574,20 @@
       <c r="I91" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L91" s="48" t="s">
+      <c r="L91" s="50" t="s">
         <v>184</v>
       </c>
       <c r="M91" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="N91" s="47">
-        <v>3</v>
-      </c>
-      <c r="O91" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q91" s="10"/>
-    </row>
-    <row r="92" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N91" s="49">
+        <v>3</v>
+      </c>
+      <c r="O91" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A92" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1040003</v>
@@ -6123,21 +5616,20 @@
       <c r="I92" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L92" s="48" t="s">
+      <c r="L92" s="50" t="s">
         <v>186</v>
       </c>
       <c r="M92" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="N92" s="47">
-        <v>3</v>
-      </c>
-      <c r="O92" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q92" s="10"/>
-    </row>
-    <row r="93" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N92" s="49">
+        <v>3</v>
+      </c>
+      <c r="O92" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A93" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1039001</v>
@@ -6172,15 +5664,15 @@
       <c r="M93" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="N93" s="47">
-        <v>3</v>
-      </c>
-      <c r="O93" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q93" s="20"/>
-    </row>
-    <row r="94" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N93" s="49">
+        <v>3</v>
+      </c>
+      <c r="O93" s="49">
+        <v>5</v>
+      </c>
+      <c r="Q93" s="22"/>
+    </row>
+    <row r="94" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A94" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1039002</v>
@@ -6209,21 +5701,21 @@
       <c r="I94" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L94" s="48">
+      <c r="L94" s="50">
         <v>10390003</v>
       </c>
       <c r="M94" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="N94" s="47">
-        <v>3</v>
-      </c>
-      <c r="O94" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q94" s="20"/>
-    </row>
-    <row r="95" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N94" s="49">
+        <v>3</v>
+      </c>
+      <c r="O94" s="49">
+        <v>5</v>
+      </c>
+      <c r="Q94" s="22"/>
+    </row>
+    <row r="95" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A95" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1039003</v>
@@ -6258,15 +5750,15 @@
       <c r="M95" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N95" s="47">
-        <v>3</v>
-      </c>
-      <c r="O95" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q95" s="20"/>
-    </row>
-    <row r="96" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N95" s="49">
+        <v>3</v>
+      </c>
+      <c r="O95" s="49">
+        <v>5</v>
+      </c>
+      <c r="Q95" s="22"/>
+    </row>
+    <row r="96" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A96" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1016001</v>
@@ -6301,15 +5793,15 @@
       <c r="M96" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="N96" s="47">
+      <c r="N96" s="49">
         <v>6</v>
       </c>
-      <c r="O96" s="47">
+      <c r="O96" s="49">
         <v>6</v>
       </c>
-      <c r="Q96" s="20"/>
-    </row>
-    <row r="97" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="Q96" s="22"/>
+    </row>
+    <row r="97" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A97" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1016002</v>
@@ -6338,21 +5830,21 @@
       <c r="I97" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L97" s="48">
+      <c r="L97" s="50">
         <v>10160002</v>
       </c>
       <c r="M97" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="N97" s="47">
+      <c r="N97" s="49">
         <v>6</v>
       </c>
-      <c r="O97" s="47">
+      <c r="O97" s="49">
         <v>6</v>
       </c>
-      <c r="Q97" s="20"/>
-    </row>
-    <row r="98" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="Q97" s="22"/>
+    </row>
+    <row r="98" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A98" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1016003</v>
@@ -6387,15 +5879,15 @@
       <c r="M98" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="N98" s="47">
+      <c r="N98" s="49">
         <v>6</v>
       </c>
-      <c r="O98" s="47">
+      <c r="O98" s="49">
         <v>6</v>
       </c>
-      <c r="Q98" s="20"/>
-    </row>
-    <row r="99" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="Q98" s="22"/>
+    </row>
+    <row r="99" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A99" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1015001</v>
@@ -6430,15 +5922,15 @@
       <c r="M99" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="N99" s="47">
-        <v>3</v>
-      </c>
-      <c r="O99" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q99" s="20"/>
-    </row>
-    <row r="100" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N99" s="49">
+        <v>3</v>
+      </c>
+      <c r="O99" s="49">
+        <v>5</v>
+      </c>
+      <c r="Q99" s="22"/>
+    </row>
+    <row r="100" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A100" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1015002</v>
@@ -6473,15 +5965,15 @@
       <c r="M100" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="N100" s="47">
-        <v>3</v>
-      </c>
-      <c r="O100" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q100" s="20"/>
-    </row>
-    <row r="101" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N100" s="49">
+        <v>3</v>
+      </c>
+      <c r="O100" s="49">
+        <v>5</v>
+      </c>
+      <c r="Q100" s="22"/>
+    </row>
+    <row r="101" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A101" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1015003</v>
@@ -6510,21 +6002,21 @@
       <c r="I101" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L101" s="48">
+      <c r="L101" s="50">
         <v>10150002</v>
       </c>
       <c r="M101" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N101" s="47">
-        <v>3</v>
-      </c>
-      <c r="O101" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q101" s="20"/>
-    </row>
-    <row r="102" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N101" s="49">
+        <v>3</v>
+      </c>
+      <c r="O101" s="49">
+        <v>5</v>
+      </c>
+      <c r="Q101" s="22"/>
+    </row>
+    <row r="102" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A102" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1015004</v>
@@ -6559,15 +6051,15 @@
       <c r="M102" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="N102" s="47">
-        <v>3</v>
-      </c>
-      <c r="O102" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q102" s="20"/>
-    </row>
-    <row r="103" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N102" s="49">
+        <v>3</v>
+      </c>
+      <c r="O102" s="49">
+        <v>5</v>
+      </c>
+      <c r="Q102" s="22"/>
+    </row>
+    <row r="103" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A103" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1015005</v>
@@ -6596,21 +6088,21 @@
       <c r="I103" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L103" s="48">
+      <c r="L103" s="50">
         <v>10150005</v>
       </c>
       <c r="M103" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="N103" s="47">
-        <v>3</v>
-      </c>
-      <c r="O103" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q103" s="20"/>
-    </row>
-    <row r="104" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N103" s="49">
+        <v>3</v>
+      </c>
+      <c r="O103" s="49">
+        <v>5</v>
+      </c>
+      <c r="Q103" s="22"/>
+    </row>
+    <row r="104" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A104" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1015006</v>
@@ -6639,21 +6131,21 @@
       <c r="I104" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L104" s="48">
+      <c r="L104" s="50">
         <v>10150006</v>
       </c>
       <c r="M104" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="N104" s="47">
-        <v>3</v>
-      </c>
-      <c r="O104" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q104" s="20"/>
-    </row>
-    <row r="105" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N104" s="49">
+        <v>3</v>
+      </c>
+      <c r="O104" s="49">
+        <v>5</v>
+      </c>
+      <c r="Q104" s="22"/>
+    </row>
+    <row r="105" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A105" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1015007</v>
@@ -6682,21 +6174,21 @@
       <c r="I105" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L105" s="48">
+      <c r="L105" s="50">
         <v>10150007</v>
       </c>
       <c r="M105" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="N105" s="47">
-        <v>3</v>
-      </c>
-      <c r="O105" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q105" s="20"/>
-    </row>
-    <row r="106" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="N105" s="49">
+        <v>3</v>
+      </c>
+      <c r="O105" s="49">
+        <v>5</v>
+      </c>
+      <c r="Q105" s="22"/>
+    </row>
+    <row r="106" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A106" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1026001</v>
@@ -6731,15 +6223,15 @@
       <c r="M106" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="N106" s="47">
+      <c r="N106" s="49">
         <v>6</v>
       </c>
-      <c r="O106" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q106" s="20"/>
-    </row>
-    <row r="107" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="O106" s="49">
+        <v>6</v>
+      </c>
+      <c r="Q106" s="22"/>
+    </row>
+    <row r="107" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A107" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1026002</v>
@@ -6768,21 +6260,21 @@
       <c r="I107" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L107" s="48">
-        <v>10260002</v>
+      <c r="L107" s="50" t="s">
+        <v>213</v>
       </c>
       <c r="M107" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="N107" s="47">
+      <c r="N107" s="49">
         <v>6</v>
       </c>
-      <c r="O107" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q107" s="20"/>
-    </row>
-    <row r="108" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="O107" s="49">
+        <v>6</v>
+      </c>
+      <c r="Q107" s="22"/>
+    </row>
+    <row r="108" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A108" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1026003</v>
@@ -6812,21 +6304,21 @@
         <v>24</v>
       </c>
       <c r="L108" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M108" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="N108" s="47">
+      <c r="N108" s="49">
         <v>6</v>
       </c>
-      <c r="O108" s="47">
-        <v>5</v>
-      </c>
-      <c r="Q108" s="20"/>
-    </row>
-    <row r="109" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A109" s="48">
+      <c r="O108" s="49">
+        <v>6</v>
+      </c>
+      <c r="Q108" s="22"/>
+    </row>
+    <row r="109" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A109" s="50">
         <v>1050001</v>
       </c>
       <c r="B109" s="5">
@@ -6836,7 +6328,7 @@
         <v>1</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E109" s="5" t="s">
         <v>111</v>
@@ -6854,21 +6346,21 @@
         <v>24</v>
       </c>
       <c r="L109" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M109" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="N109" s="47">
-        <v>5</v>
-      </c>
-      <c r="O109" s="47">
+        <v>217</v>
+      </c>
+      <c r="N109" s="49">
         <v>6</v>
       </c>
-      <c r="Q109" s="20"/>
-    </row>
-    <row r="110" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A110" s="48">
+      <c r="O109" s="49">
+        <v>6</v>
+      </c>
+      <c r="Q109" s="22"/>
+    </row>
+    <row r="110" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A110" s="50">
         <v>1050002</v>
       </c>
       <c r="B110" s="5">
@@ -6878,7 +6370,7 @@
         <v>2</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E110" s="5" t="s">
         <v>132</v>
@@ -6895,23 +6387,23 @@
       <c r="I110" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L110" s="48">
-        <v>10500002</v>
+      <c r="L110" s="50" t="s">
+        <v>218</v>
       </c>
       <c r="M110" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="N110" s="47">
-        <v>5</v>
-      </c>
-      <c r="O110" s="47">
+        <v>219</v>
+      </c>
+      <c r="N110" s="49">
         <v>6</v>
       </c>
-      <c r="P110" s="47"/>
-      <c r="Q110" s="20"/>
-    </row>
-    <row r="111" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A111" s="48">
+      <c r="O110" s="49">
+        <v>6</v>
+      </c>
+      <c r="P110" s="49"/>
+      <c r="Q110" s="22"/>
+    </row>
+    <row r="111" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A111" s="50">
         <v>1050003</v>
       </c>
       <c r="B111" s="5">
@@ -6921,7 +6413,7 @@
         <v>3</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E111" s="5" t="s">
         <v>81</v>
@@ -6938,77 +6430,77 @@
       <c r="I111" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L111" s="48" t="s">
-        <v>218</v>
+      <c r="L111" s="50" t="s">
+        <v>220</v>
       </c>
       <c r="M111" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="N111" s="47">
-        <v>5</v>
-      </c>
-      <c r="O111" s="47">
+        <v>221</v>
+      </c>
+      <c r="N111" s="49">
         <v>6</v>
       </c>
-      <c r="Q111" s="20"/>
-    </row>
-    <row r="112" s="5" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A112" s="48">
+      <c r="O111" s="49">
+        <v>6</v>
+      </c>
+      <c r="Q111" s="22"/>
+    </row>
+    <row r="112" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A112" s="50">
+        <v>1050004</v>
+      </c>
+      <c r="B112" s="5">
+        <v>105000</v>
+      </c>
+      <c r="C112" s="5">
+        <v>4</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="E112" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="F112" s="5">
+        <v>1</v>
+      </c>
+      <c r="G112" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H112" s="5">
+        <v>2050001</v>
+      </c>
+      <c r="I112" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L112" s="50" t="s">
+        <v>223</v>
+      </c>
+      <c r="M112" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="N112" s="49">
+        <v>6</v>
+      </c>
+      <c r="O112" s="49">
+        <v>6</v>
+      </c>
+      <c r="Q112" s="22"/>
+    </row>
+    <row r="113" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A113" s="50">
         <v>1051001</v>
-      </c>
-      <c r="B112" s="5">
-        <v>105100</v>
-      </c>
-      <c r="C112" s="5">
-        <v>1</v>
-      </c>
-      <c r="D112" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="E112" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="F112" s="5">
-        <v>1</v>
-      </c>
-      <c r="G112" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H112" s="5">
-        <v>2051001</v>
-      </c>
-      <c r="I112" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L112" s="48">
-        <v>10510008</v>
-      </c>
-      <c r="M112" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="N112" s="47">
-        <v>6</v>
-      </c>
-      <c r="O112" s="47">
-        <v>6</v>
-      </c>
-      <c r="Q112" s="20"/>
-    </row>
-    <row r="113" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A113" s="48">
-        <v>1051002</v>
       </c>
       <c r="B113" s="5">
         <v>105100</v>
       </c>
       <c r="C113" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="E113" t="s">
-        <v>223</v>
+        <v>225</v>
+      </c>
+      <c r="E113" s="5" t="s">
+        <v>226</v>
       </c>
       <c r="F113" s="5">
         <v>1</v>
@@ -7022,35 +6514,35 @@
       <c r="I113" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L113" s="48" t="s">
-        <v>224</v>
-      </c>
-      <c r="M113" t="s">
-        <v>225</v>
-      </c>
-      <c r="N113" s="47">
+      <c r="L113" s="50">
+        <v>10510008</v>
+      </c>
+      <c r="M113" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="N113" s="49">
         <v>6</v>
       </c>
-      <c r="O113" s="47">
+      <c r="O113" s="49">
         <v>6</v>
       </c>
-      <c r="Q113" s="10"/>
-    </row>
-    <row r="114" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A114" s="48">
-        <v>1051003</v>
+      <c r="Q113" s="22"/>
+    </row>
+    <row r="114" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A114" s="50">
+        <v>1051002</v>
       </c>
       <c r="B114" s="5">
         <v>105100</v>
       </c>
       <c r="C114" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E114" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F114" s="5">
         <v>1</v>
@@ -7064,35 +6556,34 @@
       <c r="I114" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L114" s="48" t="s">
-        <v>227</v>
+      <c r="L114" s="50" t="s">
+        <v>229</v>
       </c>
       <c r="M114" t="s">
-        <v>228</v>
-      </c>
-      <c r="N114" s="47">
+        <v>230</v>
+      </c>
+      <c r="N114" s="49">
         <v>6</v>
       </c>
-      <c r="O114" s="47">
+      <c r="O114" s="49">
         <v>6</v>
       </c>
-      <c r="Q114" s="10"/>
-    </row>
-    <row r="115" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A115" s="48">
-        <v>1051004</v>
+    </row>
+    <row r="115" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A115" s="50">
+        <v>1051003</v>
       </c>
       <c r="B115" s="5">
         <v>105100</v>
       </c>
       <c r="C115" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E115" t="s">
-        <v>132</v>
+        <v>231</v>
       </c>
       <c r="F115" s="5">
         <v>1</v>
@@ -7106,35 +6597,34 @@
       <c r="I115" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L115" s="48">
-        <v>10510005</v>
+      <c r="L115" s="50" t="s">
+        <v>232</v>
       </c>
       <c r="M115" t="s">
-        <v>229</v>
-      </c>
-      <c r="N115" s="47">
+        <v>233</v>
+      </c>
+      <c r="N115" s="49">
         <v>6</v>
       </c>
-      <c r="O115" s="47">
+      <c r="O115" s="49">
         <v>6</v>
       </c>
-      <c r="Q115" s="10"/>
-    </row>
-    <row r="116" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A116" s="48">
-        <v>1051005</v>
+    </row>
+    <row r="116" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A116" s="50">
+        <v>1051004</v>
       </c>
       <c r="B116" s="5">
         <v>105100</v>
       </c>
       <c r="C116" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E116" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="F116" s="5">
         <v>1</v>
@@ -7148,33 +6638,701 @@
       <c r="I116" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L116" s="48">
+      <c r="L116" s="50">
+        <v>10510005</v>
+      </c>
+      <c r="M116" t="s">
+        <v>234</v>
+      </c>
+      <c r="N116" s="49">
+        <v>6</v>
+      </c>
+      <c r="O116" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A117" s="50">
+        <v>1051005</v>
+      </c>
+      <c r="B117" s="5">
+        <v>105100</v>
+      </c>
+      <c r="C117" s="5">
+        <v>5</v>
+      </c>
+      <c r="D117" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="E117" t="s">
+        <v>81</v>
+      </c>
+      <c r="F117" s="5">
+        <v>1</v>
+      </c>
+      <c r="G117" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H117" s="5">
+        <v>2051001</v>
+      </c>
+      <c r="I117" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L117" s="50">
         <v>10510009</v>
       </c>
-      <c r="M116" t="s">
-        <v>230</v>
-      </c>
-      <c r="N116" s="47">
+      <c r="M117" t="s">
+        <v>235</v>
+      </c>
+      <c r="N117" s="49">
         <v>6</v>
       </c>
-      <c r="O116" s="47">
+      <c r="O117" s="49">
         <v>6</v>
       </c>
-      <c r="Q116" s="10"/>
+    </row>
+    <row r="118" spans="1:17" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A118" s="43">
+        <v>1054001</v>
+      </c>
+      <c r="B118" s="41">
+        <v>105400</v>
+      </c>
+      <c r="C118" s="41">
+        <v>1</v>
+      </c>
+      <c r="D118" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="E118" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="F118" s="41">
+        <v>1</v>
+      </c>
+      <c r="G118" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="H118" s="41">
+        <v>2054001</v>
+      </c>
+      <c r="I118" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="L118" s="43" t="s">
+        <v>237</v>
+      </c>
+      <c r="M118" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="N118" s="65">
+        <v>6</v>
+      </c>
+      <c r="O118" s="65">
+        <v>6</v>
+      </c>
+      <c r="Q118" s="66"/>
+    </row>
+    <row r="119" spans="1:17" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A119" s="43">
+        <v>1054002</v>
+      </c>
+      <c r="B119" s="41">
+        <v>105400</v>
+      </c>
+      <c r="C119" s="41">
+        <v>2</v>
+      </c>
+      <c r="D119" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="E119" s="41" t="s">
+        <v>132</v>
+      </c>
+      <c r="F119" s="41">
+        <v>1</v>
+      </c>
+      <c r="G119" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="H119" s="41">
+        <v>2054001</v>
+      </c>
+      <c r="I119" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="L119" s="43" t="s">
+        <v>239</v>
+      </c>
+      <c r="M119" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="N119" s="65">
+        <v>6</v>
+      </c>
+      <c r="O119" s="65">
+        <v>6</v>
+      </c>
+      <c r="Q119" s="66"/>
+    </row>
+    <row r="120" spans="1:17" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A120" s="43">
+        <v>1054003</v>
+      </c>
+      <c r="B120" s="41">
+        <v>105400</v>
+      </c>
+      <c r="C120" s="41">
+        <v>3</v>
+      </c>
+      <c r="D120" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="E120" s="41" t="s">
+        <v>81</v>
+      </c>
+      <c r="F120" s="41">
+        <v>1</v>
+      </c>
+      <c r="G120" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="H120" s="41">
+        <v>2054001</v>
+      </c>
+      <c r="I120" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="L120" s="43" t="s">
+        <v>241</v>
+      </c>
+      <c r="M120" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="N120" s="65">
+        <v>6</v>
+      </c>
+      <c r="O120" s="65">
+        <v>6</v>
+      </c>
+      <c r="Q120" s="66"/>
+    </row>
+    <row r="121" spans="1:17" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A121" s="43">
+        <v>1054004</v>
+      </c>
+      <c r="B121" s="41">
+        <v>105400</v>
+      </c>
+      <c r="C121" s="41">
+        <v>4</v>
+      </c>
+      <c r="D121" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="E121" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="F121" s="41">
+        <v>1</v>
+      </c>
+      <c r="G121" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="H121" s="41">
+        <v>2054001</v>
+      </c>
+      <c r="I121" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="L121" s="43" t="s">
+        <v>243</v>
+      </c>
+      <c r="M121" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="N121" s="65">
+        <v>6</v>
+      </c>
+      <c r="O121" s="65">
+        <v>6</v>
+      </c>
+      <c r="Q121" s="66"/>
+    </row>
+    <row r="122" spans="1:17" s="10" customFormat="1" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A122" s="67">
+        <v>1008001</v>
+      </c>
+      <c r="B122" s="10">
+        <v>100800</v>
+      </c>
+      <c r="C122" s="10">
+        <v>1</v>
+      </c>
+      <c r="D122" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="E122" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F122" s="10">
+        <v>1</v>
+      </c>
+      <c r="G122" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H122" s="68">
+        <v>2008001</v>
+      </c>
+      <c r="I122" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L122" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="M122" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="N122" s="49">
+        <v>6</v>
+      </c>
+      <c r="O122" s="49">
+        <v>6</v>
+      </c>
+      <c r="Q122" s="69"/>
+    </row>
+    <row r="123" spans="1:17" s="10" customFormat="1" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A123" s="67">
+        <v>1008002</v>
+      </c>
+      <c r="B123" s="10">
+        <v>100800</v>
+      </c>
+      <c r="C123" s="10">
+        <v>2</v>
+      </c>
+      <c r="D123" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="E123" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F123" s="10">
+        <v>1</v>
+      </c>
+      <c r="G123" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H123" s="68">
+        <v>2008001</v>
+      </c>
+      <c r="I123" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L123" s="71" t="s">
+        <v>266</v>
+      </c>
+      <c r="M123" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="N123" s="49">
+        <v>6</v>
+      </c>
+      <c r="O123" s="49">
+        <v>6</v>
+      </c>
+      <c r="Q123" s="69"/>
+    </row>
+    <row r="124" spans="1:17" s="10" customFormat="1" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A124" s="67">
+        <v>1008003</v>
+      </c>
+      <c r="B124" s="10">
+        <v>100800</v>
+      </c>
+      <c r="C124" s="10">
+        <v>3</v>
+      </c>
+      <c r="D124" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="E124" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F124" s="10">
+        <v>1</v>
+      </c>
+      <c r="G124" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H124" s="68">
+        <v>2008001</v>
+      </c>
+      <c r="I124" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L124" s="50" t="s">
+        <v>247</v>
+      </c>
+      <c r="M124" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="N124" s="49">
+        <v>6</v>
+      </c>
+      <c r="O124" s="49">
+        <v>6</v>
+      </c>
+      <c r="Q124" s="69"/>
+    </row>
+    <row r="125" spans="1:17" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A125" s="52" t="s">
+        <v>248</v>
+      </c>
+      <c r="B125" s="21">
+        <v>105300</v>
+      </c>
+      <c r="C125" s="21">
+        <v>1</v>
+      </c>
+      <c r="D125" s="70" t="s">
+        <v>249</v>
+      </c>
+      <c r="E125" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="F125" s="21">
+        <v>1</v>
+      </c>
+      <c r="G125" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="H125" s="51">
+        <v>2053001</v>
+      </c>
+      <c r="I125" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="J125" s="51"/>
+      <c r="K125" s="51"/>
+      <c r="L125" s="52" t="s">
+        <v>250</v>
+      </c>
+      <c r="M125" s="51" t="s">
+        <v>251</v>
+      </c>
+      <c r="N125" s="21">
+        <v>5</v>
+      </c>
+      <c r="O125" s="21">
+        <v>5</v>
+      </c>
+      <c r="Q125" s="48"/>
+    </row>
+    <row r="126" spans="1:17" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A126" s="52" t="s">
+        <v>252</v>
+      </c>
+      <c r="B126" s="21">
+        <v>105300</v>
+      </c>
+      <c r="C126" s="21">
+        <v>2</v>
+      </c>
+      <c r="D126" s="70" t="s">
+        <v>249</v>
+      </c>
+      <c r="E126" s="70" t="s">
+        <v>55</v>
+      </c>
+      <c r="F126" s="21">
+        <v>1</v>
+      </c>
+      <c r="G126" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="H126" s="51">
+        <v>2053001</v>
+      </c>
+      <c r="I126" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="J126" s="51"/>
+      <c r="K126" s="51"/>
+      <c r="L126" s="52" t="s">
+        <v>253</v>
+      </c>
+      <c r="M126" s="51" t="s">
+        <v>254</v>
+      </c>
+      <c r="N126" s="21">
+        <v>5</v>
+      </c>
+      <c r="O126" s="21">
+        <v>5</v>
+      </c>
+      <c r="Q126" s="48"/>
+    </row>
+    <row r="127" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A127" s="50">
+        <v>1057001</v>
+      </c>
+      <c r="B127" s="5">
+        <v>105700</v>
+      </c>
+      <c r="C127" s="5">
+        <v>1</v>
+      </c>
+      <c r="D127" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="E127" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="F127" s="21">
+        <v>1</v>
+      </c>
+      <c r="G127" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="H127" s="51">
+        <v>2057001</v>
+      </c>
+      <c r="I127" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="L127" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="M127" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="N127" s="49">
+        <v>6</v>
+      </c>
+      <c r="O127" s="49">
+        <v>5</v>
+      </c>
+      <c r="Q127" s="22"/>
+    </row>
+    <row r="128" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A128" s="50">
+        <v>1057002</v>
+      </c>
+      <c r="B128" s="5">
+        <v>105700</v>
+      </c>
+      <c r="C128" s="5">
+        <v>2</v>
+      </c>
+      <c r="D128" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="E128" s="70" t="s">
+        <v>55</v>
+      </c>
+      <c r="F128" s="21">
+        <v>1</v>
+      </c>
+      <c r="G128" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="H128" s="51">
+        <v>2057001</v>
+      </c>
+      <c r="I128" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="L128" s="50" t="s">
+        <v>258</v>
+      </c>
+      <c r="M128" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="N128" s="49">
+        <v>6</v>
+      </c>
+      <c r="O128" s="49">
+        <v>5</v>
+      </c>
+      <c r="Q128" s="22"/>
+    </row>
+    <row r="129" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A129" s="50">
+        <v>1057003</v>
+      </c>
+      <c r="B129" s="5">
+        <v>105700</v>
+      </c>
+      <c r="C129" s="5">
+        <v>3</v>
+      </c>
+      <c r="D129" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="E129" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F129" s="21">
+        <v>1</v>
+      </c>
+      <c r="G129" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="H129" s="51">
+        <v>2057001</v>
+      </c>
+      <c r="I129" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="L129" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="M129" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="N129" s="49">
+        <v>6</v>
+      </c>
+      <c r="O129" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A130" s="50">
+        <v>1058001</v>
+      </c>
+      <c r="B130" s="5">
+        <v>105800</v>
+      </c>
+      <c r="C130" s="5">
+        <v>1</v>
+      </c>
+      <c r="D130" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E130" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="F130" s="21">
+        <v>1</v>
+      </c>
+      <c r="G130" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="H130" s="5">
+        <v>2058001</v>
+      </c>
+      <c r="I130" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="L130" s="50">
+        <v>10580001</v>
+      </c>
+      <c r="M130" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="N130" s="49">
+        <v>7</v>
+      </c>
+      <c r="O130" s="49">
+        <v>7</v>
+      </c>
+      <c r="Q130" s="22"/>
+    </row>
+    <row r="131" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A131" s="50">
+        <v>1058002</v>
+      </c>
+      <c r="B131" s="5">
+        <v>105800</v>
+      </c>
+      <c r="C131" s="5">
+        <v>2</v>
+      </c>
+      <c r="D131" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E131" s="70" t="s">
+        <v>55</v>
+      </c>
+      <c r="F131" s="21">
+        <v>1</v>
+      </c>
+      <c r="G131" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="H131" s="5">
+        <v>2058001</v>
+      </c>
+      <c r="I131" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="L131" s="50">
+        <v>10580002</v>
+      </c>
+      <c r="M131" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="N131" s="49">
+        <v>7</v>
+      </c>
+      <c r="O131" s="49">
+        <v>7</v>
+      </c>
+      <c r="Q131" s="22"/>
+    </row>
+    <row r="132" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A132" s="50">
+        <v>1058003</v>
+      </c>
+      <c r="B132" s="5">
+        <v>105800</v>
+      </c>
+      <c r="C132" s="5">
+        <v>3</v>
+      </c>
+      <c r="D132" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E132" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F132" s="21">
+        <v>1</v>
+      </c>
+      <c r="G132" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="H132" s="5">
+        <v>2058001</v>
+      </c>
+      <c r="I132" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="L132" s="50">
+        <v>10580003</v>
+      </c>
+      <c r="M132" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="N132" s="49">
+        <v>7</v>
+      </c>
+      <c r="O132" s="49">
+        <v>7</v>
+      </c>
+      <c r="Q132" s="22"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:K2">
+  <phoneticPr fontId="7" type="noConversion"/>
+  <conditionalFormatting sqref="J2:L2">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD(MID($A2,1,4),2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2">
-    <cfRule type="expression" dxfId="0" priority="2">
-      <formula>MOD(MID($A2,1,4),2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\java\gamedoc\游戏配置表\slot\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CB7C16C-D71C-4DA3-867F-A088BB44DBCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialMode" sheetId="1" r:id="rId1"/>
@@ -28,21 +22,18 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
     <author/>
   </authors>
   <commentList>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -64,7 +55,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="N1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -86,7 +77,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="O1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -108,7 +99,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="J2" authorId="0">
       <text>
         <r>
           <rPr>
@@ -135,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="265">
   <si>
     <t>id</t>
   </si>
@@ -878,12 +869,12 @@
     <t>概率改出百搭wild符号+概率改出scatter符号+概率改出占据2、3、4个格子符号+异形位置改为不中奖图案</t>
   </si>
   <si>
+    <t>10260002|10080010</t>
+  </si>
+  <si>
     <t>10500003|10500008|10080010</t>
   </si>
   <si>
-    <t>1053001</t>
-  </si>
-  <si>
     <t>麻将胡了2</t>
   </si>
   <si>
@@ -893,9 +884,6 @@
     <t>概率改出wild百搭符号+概率改出scatter+概率出金色图标+异形位置改为不中奖图案</t>
   </si>
   <si>
-    <t>1053002</t>
-  </si>
-  <si>
     <t>10530003|10530016</t>
   </si>
   <si>
@@ -933,20 +921,20 @@
   </si>
   <si>
     <t>奖池符号</t>
-  </si>
-  <si>
-    <t>10260002|10080010</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="0_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -961,12 +949,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -974,8 +956,151 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -989,21 +1114,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="14">
+  <fills count="45">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1012,37 +1124,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor theme="8" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
+        <fgColor theme="6" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1066,24 +1172,216 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
+        <fgColor theme="8" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
+        <fgColor theme="8" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1106,12 +1404,254 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1121,47 +1661,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -1172,22 +1710,22 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1195,11 +1733,11 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1224,6 +1762,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1245,184 +1784,98 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 80" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 80" xfId="49"/>
   </cellStyles>
   <dxfs count="18">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.7993408001953185"/>
+          <bgColor theme="8" tint="0.799340800195319"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
       <border>
@@ -1433,7 +1886,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1461,40 +1914,154 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
+          <color theme="4" tint="0.399975585192419"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="17"/>
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstColumn" dxfId="14"/>
-      <tableStyleElement type="lastColumn" dxfId="13"/>
-      <tableStyleElement type="firstRowStripe" dxfId="12"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="11"/>
+      <tableStyleElement type="wholeTable" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="totalRow" dxfId="5"/>
+      <tableStyleElement type="firstColumn" dxfId="4"/>
+      <tableStyleElement type="lastColumn" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="10"/>
-      <tableStyleElement type="totalRow" dxfId="9"/>
-      <tableStyleElement type="firstRowStripe" dxfId="8"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="7"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="6"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="4"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="3"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="2"/>
-      <tableStyleElement type="pageFieldValues" dxfId="1"/>
+      <tableStyleElement type="headerRow" dxfId="17"/>
+      <tableStyleElement type="totalRow" dxfId="16"/>
+      <tableStyleElement type="firstRowStripe" dxfId="15"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
+      <tableStyleElement type="pageFieldValues" dxfId="8"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1744,14 +2311,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:S132"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
     <col min="5" max="5" width="36.375" customWidth="1"/>
@@ -1762,15 +2329,15 @@
     <col min="10" max="10" width="30.125" customWidth="1"/>
     <col min="11" max="11" width="16.75" customWidth="1"/>
     <col min="12" max="12" width="53.25" customWidth="1"/>
-    <col min="13" max="13" width="21.625" customWidth="1"/>
-    <col min="14" max="15" width="9" style="11"/>
+    <col min="13" max="13" width="21.6083333333333" customWidth="1"/>
+    <col min="14" max="15" width="9" style="9"/>
     <col min="16" max="16" width="15" customWidth="1"/>
-    <col min="17" max="17" width="23.75" style="12" customWidth="1"/>
+    <col min="17" max="17" width="23.75" style="10" customWidth="1"/>
     <col min="18" max="18" width="60.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
+    <row r="1" ht="16.5" spans="1:17">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
@@ -1781,34 +2348,34 @@
       </c>
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="12" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="5"/>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="12" t="s">
         <v>4</v>
       </c>
       <c r="I1" s="5"/>
-      <c r="J1" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="15"/>
-      <c r="L1" s="16" t="s">
+      <c r="J1" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="13"/>
+      <c r="L1" s="14" t="s">
         <v>6</v>
       </c>
       <c r="M1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="17" t="s">
+      <c r="N1" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="17" t="s">
+      <c r="O1" s="15" t="s">
         <v>9</v>
       </c>
       <c r="Q1"/>
     </row>
-    <row r="2" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="13" t="s">
+    <row r="2" ht="16.5" spans="1:17">
+      <c r="A2" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -1819,1166 +2386,1166 @@
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="12" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="5"/>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="12" t="s">
         <v>10</v>
       </c>
       <c r="I2" s="5"/>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="19"/>
-      <c r="L2" s="20" t="s">
+      <c r="K2" s="17"/>
+      <c r="L2" s="18" t="s">
         <v>12</v>
       </c>
       <c r="M2" s="5"/>
-      <c r="N2" s="21" t="s">
+      <c r="N2" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="21" t="s">
+      <c r="O2" s="19" t="s">
         <v>10</v>
       </c>
       <c r="Q2"/>
     </row>
-    <row r="3" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="13" t="s">
+    <row r="3" ht="16.5" spans="1:17">
+      <c r="A3" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="23" t="s">
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="22"/>
-      <c r="H3" s="24" t="s">
+      <c r="G3" s="20"/>
+      <c r="H3" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="22"/>
-      <c r="J3" s="25" t="s">
+      <c r="I3" s="20"/>
+      <c r="J3" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="25"/>
-      <c r="L3" s="26" t="s">
+      <c r="K3" s="23"/>
+      <c r="L3" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="M3" s="22"/>
-      <c r="N3" s="21" t="s">
+      <c r="M3" s="20"/>
+      <c r="N3" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="21" t="s">
+      <c r="O3" s="19" t="s">
         <v>20</v>
       </c>
       <c r="Q3"/>
     </row>
-    <row r="4" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="4" ht="16.5" spans="1:17">
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="14"/>
+      <c r="F4" s="12"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="14"/>
+      <c r="H4" s="12"/>
       <c r="I4" s="5"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="16"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="14"/>
       <c r="M4" s="5"/>
-      <c r="N4" s="21"/>
-      <c r="O4" s="21"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
       <c r="Q4"/>
     </row>
-    <row r="5" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="28" t="str">
-        <f t="shared" ref="A5:A19" si="0">B5&amp;C5</f>
+    <row r="5" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A5" s="26" t="str">
+        <f t="shared" ref="A5:A21" si="0">B5&amp;C5</f>
         <v>1001001</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="27">
         <v>100100</v>
       </c>
-      <c r="C5" s="29">
-        <v>1</v>
-      </c>
-      <c r="D5" s="29" t="s">
+      <c r="C5" s="27">
+        <v>1</v>
+      </c>
+      <c r="D5" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="E5" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="29">
-        <v>1</v>
-      </c>
-      <c r="G5" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="28">
+      <c r="F5" s="27">
+        <v>1</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="26">
         <v>2001001</v>
       </c>
-      <c r="I5" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="28"/>
-      <c r="K5" s="28"/>
-      <c r="L5" s="31" t="s">
+      <c r="I5" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="26"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="M5" s="28" t="s">
+      <c r="M5" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="N5" s="21">
+      <c r="N5" s="19">
         <v>4</v>
       </c>
-      <c r="O5" s="21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="28" t="str">
+      <c r="O5" s="19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A6" s="26" t="str">
         <f t="shared" si="0"/>
         <v>1001002</v>
       </c>
-      <c r="B6" s="29">
+      <c r="B6" s="27">
         <v>100100</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="27">
         <v>2</v>
       </c>
-      <c r="D6" s="29"/>
-      <c r="E6" s="32" t="s">
+      <c r="D6" s="27"/>
+      <c r="E6" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="29">
-        <v>1</v>
-      </c>
-      <c r="G6" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="28">
+      <c r="F6" s="27">
+        <v>1</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="26">
         <v>2001001</v>
       </c>
-      <c r="I6" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="28"/>
-      <c r="K6" s="28"/>
-      <c r="L6" s="33" t="s">
+      <c r="I6" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="M6" s="28" t="s">
+      <c r="M6" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="N6" s="21">
+      <c r="N6" s="19">
         <v>4</v>
       </c>
-      <c r="O6" s="21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="28" t="str">
+      <c r="O6" s="19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A7" s="26" t="str">
         <f t="shared" si="0"/>
         <v>1001003</v>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="27">
         <v>100100</v>
       </c>
-      <c r="C7" s="29">
-        <v>3</v>
-      </c>
-      <c r="D7" s="29"/>
-      <c r="E7" s="34" t="s">
+      <c r="C7" s="27">
+        <v>3</v>
+      </c>
+      <c r="D7" s="27"/>
+      <c r="E7" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="29">
-        <v>1</v>
-      </c>
-      <c r="G7" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="28">
+      <c r="F7" s="27">
+        <v>1</v>
+      </c>
+      <c r="G7" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="26">
         <v>2001001</v>
       </c>
-      <c r="I7" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="31" t="s">
+      <c r="I7" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="M7" s="28" t="s">
+      <c r="M7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="N7" s="21">
+      <c r="N7" s="19">
         <v>4</v>
       </c>
-      <c r="O7" s="21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="28" t="str">
+      <c r="O7" s="19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A8" s="26" t="str">
         <f t="shared" si="0"/>
         <v>1001004</v>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="27">
         <v>100100</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="27">
         <v>4</v>
       </c>
-      <c r="D8" s="29"/>
-      <c r="E8" s="35" t="s">
+      <c r="D8" s="27"/>
+      <c r="E8" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="36">
-        <v>1</v>
-      </c>
-      <c r="G8" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="28">
+      <c r="F8" s="34">
+        <v>1</v>
+      </c>
+      <c r="G8" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="26">
         <v>2001001</v>
       </c>
-      <c r="I8" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" s="28"/>
-      <c r="K8" s="28"/>
-      <c r="L8" s="31">
+      <c r="I8" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="29">
         <v>10010041</v>
       </c>
-      <c r="M8" s="28" t="s">
+      <c r="M8" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="N8" s="21">
+      <c r="N8" s="19">
         <v>4</v>
       </c>
-      <c r="O8" s="21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="28" t="str">
+      <c r="O8" s="19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A9" s="26" t="str">
         <f t="shared" si="0"/>
         <v>1001005</v>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="27">
         <v>100100</v>
       </c>
-      <c r="C9" s="29">
-        <v>5</v>
-      </c>
-      <c r="D9" s="29"/>
-      <c r="E9" s="37" t="s">
+      <c r="C9" s="27">
+        <v>5</v>
+      </c>
+      <c r="D9" s="27"/>
+      <c r="E9" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="36">
-        <v>1</v>
-      </c>
-      <c r="G9" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="28">
+      <c r="F9" s="34">
+        <v>1</v>
+      </c>
+      <c r="G9" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="26">
         <v>2001001</v>
       </c>
-      <c r="I9" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" s="28"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="31" t="s">
+      <c r="I9" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="M9" s="28" t="s">
+      <c r="M9" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="N9" s="21">
+      <c r="N9" s="19">
         <v>4</v>
       </c>
-      <c r="O9" s="21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="28" t="str">
+      <c r="O9" s="19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A10" s="26" t="str">
         <f t="shared" si="0"/>
         <v>1001006</v>
       </c>
-      <c r="B10" s="29">
+      <c r="B10" s="27">
         <v>100100</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="27">
         <v>6</v>
       </c>
-      <c r="D10" s="29"/>
-      <c r="E10" s="37" t="s">
+      <c r="D10" s="27"/>
+      <c r="E10" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="36">
-        <v>1</v>
-      </c>
-      <c r="G10" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="28">
+      <c r="F10" s="34">
+        <v>1</v>
+      </c>
+      <c r="G10" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="26">
         <v>2001001</v>
       </c>
-      <c r="I10" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="J10" s="28"/>
-      <c r="K10" s="28"/>
-      <c r="L10" s="31">
+      <c r="I10" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="29">
         <v>10010061</v>
       </c>
-      <c r="M10" s="28" t="s">
+      <c r="M10" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="N10" s="21">
+      <c r="N10" s="19">
         <v>4</v>
       </c>
-      <c r="O10" s="21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="28" t="str">
+      <c r="O10" s="19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A11" s="26" t="str">
         <f t="shared" si="0"/>
         <v>1001007</v>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="27">
         <v>100100</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="27">
         <v>7</v>
       </c>
-      <c r="D11" s="29"/>
-      <c r="E11" s="32" t="s">
+      <c r="D11" s="27"/>
+      <c r="E11" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="29">
-        <v>1</v>
-      </c>
-      <c r="G11" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" s="28">
+      <c r="F11" s="27">
+        <v>1</v>
+      </c>
+      <c r="G11" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="26">
         <v>2001001</v>
       </c>
-      <c r="I11" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="J11" s="28"/>
-      <c r="K11" s="28"/>
-      <c r="L11" s="33" t="s">
+      <c r="I11" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="M11" s="28" t="s">
+      <c r="M11" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="N11" s="21">
+      <c r="N11" s="19">
         <v>4</v>
       </c>
-      <c r="O11" s="21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="38" t="str">
+      <c r="O11" s="19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A12" s="36" t="str">
         <f t="shared" si="0"/>
         <v>1003001</v>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="28">
         <v>100300</v>
       </c>
-      <c r="C12" s="30">
-        <v>1</v>
-      </c>
-      <c r="D12" s="30" t="s">
+      <c r="C12" s="28">
+        <v>1</v>
+      </c>
+      <c r="D12" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="30" t="s">
+      <c r="E12" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="30">
-        <v>1</v>
-      </c>
-      <c r="G12" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="H12" s="38">
+      <c r="F12" s="28">
+        <v>1</v>
+      </c>
+      <c r="G12" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="36">
         <v>2003001</v>
       </c>
-      <c r="I12" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="39">
+      <c r="I12" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" s="36"/>
+      <c r="K12" s="36"/>
+      <c r="L12" s="37">
         <v>10030022</v>
       </c>
-      <c r="M12" s="38" t="s">
+      <c r="M12" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="N12" s="30">
-        <v>3</v>
-      </c>
-      <c r="O12" s="30">
-        <v>3</v>
-      </c>
-      <c r="Q12" s="40"/>
-    </row>
-    <row r="13" spans="1:17" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="38" t="str">
+      <c r="N12" s="28">
+        <v>3</v>
+      </c>
+      <c r="O12" s="28">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="38"/>
+    </row>
+    <row r="13" s="2" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A13" s="36" t="str">
         <f t="shared" si="0"/>
         <v>1003002</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="28">
         <v>100300</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="28">
         <v>2</v>
       </c>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30" t="s">
+      <c r="D13" s="28"/>
+      <c r="E13" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="30">
-        <v>1</v>
-      </c>
-      <c r="G13" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="H13" s="38">
+      <c r="F13" s="28">
+        <v>1</v>
+      </c>
+      <c r="G13" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="36">
         <v>2003001</v>
       </c>
-      <c r="I13" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-      <c r="L13" s="39" t="s">
+      <c r="I13" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" s="36"/>
+      <c r="K13" s="36"/>
+      <c r="L13" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="M13" s="38" t="s">
+      <c r="M13" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="N13" s="30">
-        <v>3</v>
-      </c>
-      <c r="O13" s="30">
-        <v>3</v>
-      </c>
-      <c r="Q13" s="40"/>
-    </row>
-    <row r="14" spans="1:17" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="38" t="str">
+      <c r="N13" s="28">
+        <v>3</v>
+      </c>
+      <c r="O13" s="28">
+        <v>3</v>
+      </c>
+      <c r="Q13" s="38"/>
+    </row>
+    <row r="14" s="2" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A14" s="36" t="str">
         <f t="shared" si="0"/>
         <v>1003003</v>
       </c>
-      <c r="B14" s="30">
+      <c r="B14" s="28">
         <v>100300</v>
       </c>
-      <c r="C14" s="30">
-        <v>3</v>
-      </c>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30" t="s">
+      <c r="C14" s="28">
+        <v>3</v>
+      </c>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="30">
-        <v>1</v>
-      </c>
-      <c r="G14" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="H14" s="38">
+      <c r="F14" s="28">
+        <v>1</v>
+      </c>
+      <c r="G14" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="36">
         <v>2003002</v>
       </c>
-      <c r="I14" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="J14" s="38" t="s">
+      <c r="I14" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="K14" s="38" t="s">
+      <c r="K14" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="L14" s="39" t="s">
+      <c r="L14" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="M14" s="38" t="s">
+      <c r="M14" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="N14" s="30">
-        <v>3</v>
-      </c>
-      <c r="O14" s="30">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="40"/>
-    </row>
-    <row r="15" spans="1:17" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="41" t="str">
+      <c r="N14" s="28">
+        <v>3</v>
+      </c>
+      <c r="O14" s="28">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="38"/>
+    </row>
+    <row r="15" s="3" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A15" s="39" t="str">
         <f t="shared" si="0"/>
         <v>1007001</v>
       </c>
-      <c r="B15" s="42">
+      <c r="B15" s="40">
         <v>100700</v>
       </c>
-      <c r="C15" s="42">
-        <v>1</v>
-      </c>
-      <c r="D15" s="42" t="s">
+      <c r="C15" s="40">
+        <v>1</v>
+      </c>
+      <c r="D15" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="42" t="s">
+      <c r="E15" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="42">
-        <v>1</v>
-      </c>
-      <c r="G15" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="H15" s="41">
+      <c r="F15" s="40">
+        <v>1</v>
+      </c>
+      <c r="G15" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="39">
         <v>2007001</v>
       </c>
-      <c r="I15" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="J15" s="41"/>
-      <c r="K15" s="41"/>
-      <c r="L15" s="43" t="s">
+      <c r="I15" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" s="39"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="M15" s="41" t="s">
+      <c r="M15" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="N15" s="21">
+      <c r="N15" s="19">
         <v>4</v>
       </c>
-      <c r="O15" s="21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="41" t="str">
+      <c r="O15" s="19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" s="3" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A16" s="39" t="str">
         <f t="shared" si="0"/>
         <v>1007002</v>
       </c>
-      <c r="B16" s="42">
+      <c r="B16" s="40">
         <v>100700</v>
       </c>
-      <c r="C16" s="42">
+      <c r="C16" s="40">
         <v>2</v>
       </c>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42" t="s">
+      <c r="D16" s="40"/>
+      <c r="E16" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="42">
-        <v>1</v>
-      </c>
-      <c r="G16" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="H16" s="41">
+      <c r="F16" s="40">
+        <v>1</v>
+      </c>
+      <c r="G16" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="39">
         <v>2007001</v>
       </c>
-      <c r="I16" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="J16" s="41"/>
-      <c r="K16" s="41"/>
-      <c r="L16" s="43" t="s">
+      <c r="I16" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="J16" s="39"/>
+      <c r="K16" s="39"/>
+      <c r="L16" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="M16" s="41" t="s">
+      <c r="M16" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="N16" s="21">
+      <c r="N16" s="19">
         <v>4</v>
       </c>
-      <c r="O16" s="21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="44" t="str">
+      <c r="O16" s="19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" s="4" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A17" s="42" t="str">
         <f t="shared" si="0"/>
         <v>1012001</v>
       </c>
-      <c r="B17" s="45">
+      <c r="B17" s="43">
         <v>101200</v>
       </c>
-      <c r="C17" s="45">
-        <v>1</v>
-      </c>
-      <c r="D17" s="45" t="s">
+      <c r="C17" s="43">
+        <v>1</v>
+      </c>
+      <c r="D17" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="E17" s="45" t="s">
+      <c r="E17" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="45">
-        <v>1</v>
-      </c>
-      <c r="G17" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="H17" s="44">
+      <c r="F17" s="43">
+        <v>1</v>
+      </c>
+      <c r="G17" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="42">
         <v>2012001</v>
       </c>
-      <c r="I17" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="J17" s="44"/>
-      <c r="K17" s="44"/>
-      <c r="L17" s="46">
+      <c r="I17" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="J17" s="42"/>
+      <c r="K17" s="42"/>
+      <c r="L17" s="44">
         <v>10120011</v>
       </c>
-      <c r="M17" s="44" t="s">
+      <c r="M17" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="N17" s="45">
-        <v>3</v>
-      </c>
-      <c r="O17" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q17" s="47"/>
-    </row>
-    <row r="18" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="44" t="str">
+      <c r="N17" s="43">
+        <v>3</v>
+      </c>
+      <c r="O17" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="45"/>
+    </row>
+    <row r="18" s="4" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A18" s="42" t="str">
         <f t="shared" si="0"/>
         <v>1012002</v>
       </c>
-      <c r="B18" s="45">
+      <c r="B18" s="43">
         <v>101200</v>
       </c>
-      <c r="C18" s="45">
+      <c r="C18" s="43">
         <v>2</v>
       </c>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45" t="s">
+      <c r="D18" s="43"/>
+      <c r="E18" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="45">
-        <v>1</v>
-      </c>
-      <c r="G18" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="H18" s="44">
+      <c r="F18" s="43">
+        <v>1</v>
+      </c>
+      <c r="G18" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="42">
         <v>2012001</v>
       </c>
-      <c r="I18" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="J18" s="44"/>
-      <c r="K18" s="44"/>
-      <c r="L18" s="46">
+      <c r="I18" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="J18" s="42"/>
+      <c r="K18" s="42"/>
+      <c r="L18" s="44">
         <v>10120021</v>
       </c>
-      <c r="M18" s="44" t="s">
+      <c r="M18" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="N18" s="45">
-        <v>3</v>
-      </c>
-      <c r="O18" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q18" s="47"/>
-    </row>
-    <row r="19" spans="1:17" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="44" t="str">
+      <c r="N18" s="43">
+        <v>3</v>
+      </c>
+      <c r="O18" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="45"/>
+    </row>
+    <row r="19" s="4" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A19" s="42" t="str">
         <f t="shared" si="0"/>
         <v>1012003</v>
       </c>
-      <c r="B19" s="45">
+      <c r="B19" s="43">
         <v>101200</v>
       </c>
-      <c r="C19" s="45">
-        <v>3</v>
-      </c>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45" t="s">
+      <c r="C19" s="43">
+        <v>3</v>
+      </c>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="F19" s="45">
-        <v>1</v>
-      </c>
-      <c r="G19" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="H19" s="44">
+      <c r="F19" s="43">
+        <v>1</v>
+      </c>
+      <c r="G19" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="42">
         <v>2012001</v>
       </c>
-      <c r="I19" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="J19" s="44" t="s">
+      <c r="I19" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="J19" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="K19" s="44" t="s">
+      <c r="K19" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="L19" s="46"/>
-      <c r="M19" s="44" t="s">
+      <c r="L19" s="44"/>
+      <c r="M19" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="N19" s="45">
-        <v>3</v>
-      </c>
-      <c r="O19" s="45">
-        <v>5</v>
-      </c>
-      <c r="Q19" s="47"/>
-    </row>
-    <row r="20" spans="1:17" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="38" t="str">
+      <c r="N19" s="43">
+        <v>3</v>
+      </c>
+      <c r="O19" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q19" s="45"/>
+    </row>
+    <row r="20" s="3" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A20" s="36" t="str">
         <f t="shared" ref="A20:A30" si="1">B20&amp;C20</f>
         <v>1014001</v>
       </c>
-      <c r="B20" s="30">
+      <c r="B20" s="28">
         <v>101400</v>
       </c>
-      <c r="C20" s="30">
-        <v>1</v>
-      </c>
-      <c r="D20" s="30" t="s">
+      <c r="C20" s="28">
+        <v>1</v>
+      </c>
+      <c r="D20" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="E20" s="30" t="s">
+      <c r="E20" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="F20" s="30">
-        <v>1</v>
-      </c>
-      <c r="G20" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="H20" s="38">
+      <c r="F20" s="28">
+        <v>1</v>
+      </c>
+      <c r="G20" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="36">
         <v>2014001</v>
       </c>
-      <c r="I20" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="J20" s="38"/>
-      <c r="K20" s="38"/>
-      <c r="L20" s="39" t="s">
+      <c r="I20" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="J20" s="36"/>
+      <c r="K20" s="36"/>
+      <c r="L20" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="M20" s="38" t="s">
+      <c r="M20" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="N20" s="21">
+      <c r="N20" s="19">
         <v>4</v>
       </c>
-      <c r="O20" s="21">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="48"/>
-    </row>
-    <row r="21" spans="1:17" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="38" t="str">
+      <c r="O20" s="19">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="46"/>
+    </row>
+    <row r="21" s="3" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A21" s="36" t="str">
         <f t="shared" si="1"/>
         <v>1014002</v>
       </c>
-      <c r="B21" s="30">
+      <c r="B21" s="28">
         <v>101400</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="28">
         <v>2</v>
       </c>
-      <c r="D21" s="30" t="s">
+      <c r="D21" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="E21" s="30" t="s">
+      <c r="E21" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="30">
-        <v>1</v>
-      </c>
-      <c r="G21" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="H21" s="38">
+      <c r="F21" s="28">
+        <v>1</v>
+      </c>
+      <c r="G21" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="36">
         <v>2014001</v>
       </c>
-      <c r="I21" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="J21" s="38"/>
-      <c r="K21" s="38"/>
-      <c r="L21" s="39" t="s">
+      <c r="I21" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="J21" s="36"/>
+      <c r="K21" s="36"/>
+      <c r="L21" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="M21" s="38" t="s">
+      <c r="M21" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="N21" s="21">
+      <c r="N21" s="19">
         <v>4</v>
       </c>
-      <c r="O21" s="21">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="48"/>
-    </row>
-    <row r="22" spans="1:17" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="38" t="str">
+      <c r="O21" s="19">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="46"/>
+    </row>
+    <row r="22" s="3" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A22" s="36" t="str">
         <f t="shared" si="1"/>
         <v>1014003</v>
       </c>
-      <c r="B22" s="30">
+      <c r="B22" s="28">
         <v>101400</v>
       </c>
-      <c r="C22" s="30">
-        <v>3</v>
-      </c>
-      <c r="D22" s="30" t="s">
+      <c r="C22" s="28">
+        <v>3</v>
+      </c>
+      <c r="D22" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="E22" s="30" t="s">
+      <c r="E22" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="F22" s="30">
-        <v>1</v>
-      </c>
-      <c r="G22" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="H22" s="38">
+      <c r="F22" s="28">
+        <v>1</v>
+      </c>
+      <c r="G22" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="36">
         <v>2014001</v>
       </c>
-      <c r="I22" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="J22" s="38"/>
-      <c r="K22" s="38"/>
-      <c r="L22" s="39">
+      <c r="I22" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="J22" s="36"/>
+      <c r="K22" s="36"/>
+      <c r="L22" s="37">
         <v>10140021</v>
       </c>
-      <c r="M22" s="38" t="s">
+      <c r="M22" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="N22" s="21">
+      <c r="N22" s="19">
         <v>4</v>
       </c>
-      <c r="O22" s="21">
-        <v>3</v>
-      </c>
-      <c r="Q22" s="48"/>
-    </row>
-    <row r="23" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="28" t="str">
+      <c r="O22" s="19">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="46"/>
+    </row>
+    <row r="23" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A23" s="26" t="str">
         <f t="shared" si="1"/>
         <v>1024001</v>
       </c>
-      <c r="B23" s="29">
+      <c r="B23" s="27">
         <v>102400</v>
       </c>
-      <c r="C23" s="29">
-        <v>1</v>
-      </c>
-      <c r="D23" s="29" t="s">
+      <c r="C23" s="27">
+        <v>1</v>
+      </c>
+      <c r="D23" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="E23" s="30" t="s">
+      <c r="E23" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="F23" s="29">
-        <v>1</v>
-      </c>
-      <c r="G23" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="H23" s="28">
+      <c r="F23" s="27">
+        <v>1</v>
+      </c>
+      <c r="G23" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="26">
         <v>2024001</v>
       </c>
-      <c r="I23" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="J23" s="28"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="31" t="s">
+      <c r="I23" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="M23" s="28" t="s">
+      <c r="M23" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="N23" s="21">
+      <c r="N23" s="19">
         <v>4</v>
       </c>
-      <c r="O23" s="21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="28" t="str">
+      <c r="O23" s="19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A24" s="26" t="str">
         <f t="shared" si="1"/>
         <v>1024002</v>
       </c>
-      <c r="B24" s="29">
+      <c r="B24" s="27">
         <v>102400</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C24" s="27">
         <v>2</v>
       </c>
-      <c r="D24" s="29"/>
-      <c r="E24" s="32" t="s">
+      <c r="D24" s="27"/>
+      <c r="E24" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="29">
-        <v>1</v>
-      </c>
-      <c r="G24" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="H24" s="28">
+      <c r="F24" s="27">
+        <v>1</v>
+      </c>
+      <c r="G24" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" s="26">
         <v>2024001</v>
       </c>
-      <c r="I24" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="J24" s="28"/>
-      <c r="K24" s="28"/>
-      <c r="L24" s="33" t="s">
+      <c r="I24" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J24" s="26"/>
+      <c r="K24" s="26"/>
+      <c r="L24" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="M24" s="28" t="s">
+      <c r="M24" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="N24" s="21">
+      <c r="N24" s="19">
         <v>4</v>
       </c>
-      <c r="O24" s="21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="28" t="str">
+      <c r="O24" s="19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A25" s="26" t="str">
         <f t="shared" si="1"/>
         <v>1024003</v>
       </c>
-      <c r="B25" s="29">
+      <c r="B25" s="27">
         <v>102400</v>
       </c>
-      <c r="C25" s="29">
-        <v>3</v>
-      </c>
-      <c r="D25" s="29"/>
-      <c r="E25" s="34" t="s">
+      <c r="C25" s="27">
+        <v>3</v>
+      </c>
+      <c r="D25" s="27"/>
+      <c r="E25" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F25" s="29">
-        <v>1</v>
-      </c>
-      <c r="G25" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="H25" s="28">
+      <c r="F25" s="27">
+        <v>1</v>
+      </c>
+      <c r="G25" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="26">
         <v>2024001</v>
       </c>
-      <c r="I25" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="J25" s="28"/>
-      <c r="K25" s="28"/>
-      <c r="L25" s="31" t="s">
+      <c r="I25" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J25" s="26"/>
+      <c r="K25" s="26"/>
+      <c r="L25" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="M25" s="28" t="s">
+      <c r="M25" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="N25" s="21">
+      <c r="N25" s="19">
         <v>4</v>
       </c>
-      <c r="O25" s="21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="28" t="str">
+      <c r="O25" s="19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A26" s="26" t="str">
         <f t="shared" si="1"/>
         <v>1024004</v>
       </c>
-      <c r="B26" s="29">
+      <c r="B26" s="27">
         <v>102400</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C26" s="27">
         <v>4</v>
       </c>
-      <c r="D26" s="29"/>
-      <c r="E26" s="35" t="s">
+      <c r="D26" s="27"/>
+      <c r="E26" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="F26" s="36">
-        <v>1</v>
-      </c>
-      <c r="G26" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="H26" s="28">
+      <c r="F26" s="34">
+        <v>1</v>
+      </c>
+      <c r="G26" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="26">
         <v>2024001</v>
       </c>
-      <c r="I26" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="J26" s="28"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="31">
+      <c r="I26" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J26" s="26"/>
+      <c r="K26" s="26"/>
+      <c r="L26" s="29">
         <v>10240041</v>
       </c>
-      <c r="M26" s="28" t="s">
+      <c r="M26" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="N26" s="21">
+      <c r="N26" s="19">
         <v>4</v>
       </c>
-      <c r="O26" s="21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="28" t="str">
+      <c r="O26" s="19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A27" s="26" t="str">
         <f t="shared" si="1"/>
         <v>1024005</v>
       </c>
-      <c r="B27" s="29">
+      <c r="B27" s="27">
         <v>102400</v>
       </c>
-      <c r="C27" s="29">
-        <v>5</v>
-      </c>
-      <c r="D27" s="29"/>
-      <c r="E27" s="37" t="s">
+      <c r="C27" s="27">
+        <v>5</v>
+      </c>
+      <c r="D27" s="27"/>
+      <c r="E27" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="F27" s="36">
-        <v>1</v>
-      </c>
-      <c r="G27" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="H27" s="28">
+      <c r="F27" s="34">
+        <v>1</v>
+      </c>
+      <c r="G27" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H27" s="26">
         <v>2024001</v>
       </c>
-      <c r="I27" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="J27" s="28"/>
-      <c r="K27" s="28"/>
-      <c r="L27" s="31" t="s">
+      <c r="I27" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J27" s="26"/>
+      <c r="K27" s="26"/>
+      <c r="L27" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="M27" s="28" t="s">
+      <c r="M27" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="N27" s="21">
+      <c r="N27" s="19">
         <v>4</v>
       </c>
-      <c r="O27" s="21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="28" t="str">
+      <c r="O27" s="19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A28" s="26" t="str">
         <f t="shared" si="1"/>
         <v>1024006</v>
       </c>
-      <c r="B28" s="29">
+      <c r="B28" s="27">
         <v>102400</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C28" s="27">
         <v>6</v>
       </c>
-      <c r="D28" s="29"/>
-      <c r="E28" s="37" t="s">
+      <c r="D28" s="27"/>
+      <c r="E28" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="F28" s="36">
-        <v>1</v>
-      </c>
-      <c r="G28" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="H28" s="28">
+      <c r="F28" s="34">
+        <v>1</v>
+      </c>
+      <c r="G28" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28" s="26">
         <v>2024001</v>
       </c>
-      <c r="I28" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="J28" s="28"/>
-      <c r="K28" s="28"/>
-      <c r="L28" s="31">
+      <c r="I28" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J28" s="26"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="29">
         <v>10240061</v>
       </c>
-      <c r="M28" s="28" t="s">
+      <c r="M28" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="N28" s="21">
+      <c r="N28" s="19">
         <v>4</v>
       </c>
-      <c r="O28" s="21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="28" t="str">
+      <c r="O28" s="19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A29" s="26" t="str">
         <f t="shared" si="1"/>
         <v>1024007</v>
       </c>
-      <c r="B29" s="29">
+      <c r="B29" s="27">
         <v>102400</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C29" s="27">
         <v>7</v>
       </c>
-      <c r="D29" s="29"/>
-      <c r="E29" s="32" t="s">
+      <c r="D29" s="27"/>
+      <c r="E29" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="F29" s="29">
-        <v>1</v>
-      </c>
-      <c r="G29" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="H29" s="28">
+      <c r="F29" s="27">
+        <v>1</v>
+      </c>
+      <c r="G29" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H29" s="26">
         <v>2024001</v>
       </c>
-      <c r="I29" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="J29" s="28"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="33" t="s">
+      <c r="I29" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J29" s="26"/>
+      <c r="K29" s="26"/>
+      <c r="L29" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="M29" s="28" t="s">
+      <c r="M29" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="N29" s="21">
+      <c r="N29" s="19">
         <v>4</v>
       </c>
-      <c r="O29" s="21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A30" s="28" t="str">
+      <c r="O29" s="19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A30" s="26" t="str">
         <f t="shared" si="1"/>
         <v>1017001</v>
       </c>
@@ -3012,16 +3579,16 @@
       <c r="M30" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="N30" s="49">
+      <c r="N30" s="47">
         <v>4</v>
       </c>
-      <c r="O30" s="49">
-        <v>5</v>
-      </c>
-      <c r="Q30" s="22"/>
-    </row>
-    <row r="31" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A31" s="28" t="str">
+      <c r="O30" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q30" s="20"/>
+    </row>
+    <row r="31" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A31" s="26" t="str">
         <f t="shared" ref="A31:A54" si="2">B31&amp;C31</f>
         <v>1017002</v>
       </c>
@@ -3055,16 +3622,16 @@
       <c r="M31" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="N31" s="49">
+      <c r="N31" s="47">
         <v>4</v>
       </c>
-      <c r="O31" s="49">
-        <v>5</v>
-      </c>
-      <c r="Q31" s="22"/>
-    </row>
-    <row r="32" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A32" s="28" t="str">
+      <c r="O31" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q31" s="20"/>
+    </row>
+    <row r="32" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A32" s="26" t="str">
         <f t="shared" si="2"/>
         <v>1017003</v>
       </c>
@@ -3098,16 +3665,16 @@
       <c r="M32" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N32" s="49">
+      <c r="N32" s="47">
         <v>4</v>
       </c>
-      <c r="O32" s="49">
-        <v>5</v>
-      </c>
-      <c r="Q32" s="22"/>
-    </row>
-    <row r="33" spans="1:19" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="28" t="str">
+      <c r="O32" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="20"/>
+    </row>
+    <row r="33" s="5" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A33" s="26" t="str">
         <f t="shared" si="2"/>
         <v>1022001</v>
       </c>
@@ -3135,22 +3702,22 @@
       <c r="I33" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L33" s="50" t="s">
+      <c r="L33" s="48" t="s">
         <v>85</v>
       </c>
       <c r="M33" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N33" s="49">
-        <v>3</v>
-      </c>
-      <c r="O33" s="49">
-        <v>5</v>
-      </c>
-      <c r="Q33" s="22"/>
-    </row>
-    <row r="34" spans="1:19" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A34" s="28" t="str">
+      <c r="N33" s="47">
+        <v>3</v>
+      </c>
+      <c r="O33" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q33" s="20"/>
+    </row>
+    <row r="34" s="5" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A34" s="26" t="str">
         <f t="shared" si="2"/>
         <v>1022002</v>
       </c>
@@ -3166,10 +3733,10 @@
       <c r="E34" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="F34" s="21">
-        <v>1</v>
-      </c>
-      <c r="G34" s="51" t="s">
+      <c r="F34" s="19">
+        <v>1</v>
+      </c>
+      <c r="G34" s="49" t="s">
         <v>23</v>
       </c>
       <c r="H34" s="5">
@@ -3178,22 +3745,22 @@
       <c r="I34" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L34" s="50">
+      <c r="L34" s="48">
         <v>10220033</v>
       </c>
       <c r="M34" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N34" s="49">
-        <v>3</v>
-      </c>
-      <c r="O34" s="49">
-        <v>5</v>
-      </c>
-      <c r="Q34" s="22"/>
-    </row>
-    <row r="35" spans="1:19" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A35" s="28" t="str">
+      <c r="N34" s="47">
+        <v>3</v>
+      </c>
+      <c r="O34" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q34" s="20"/>
+    </row>
+    <row r="35" s="5" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A35" s="26" t="str">
         <f t="shared" si="2"/>
         <v>1022003</v>
       </c>
@@ -3209,10 +3776,10 @@
       <c r="E35" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F35" s="51">
-        <v>1</v>
-      </c>
-      <c r="G35" s="51" t="s">
+      <c r="F35" s="49">
+        <v>1</v>
+      </c>
+      <c r="G35" s="49" t="s">
         <v>23</v>
       </c>
       <c r="H35" s="5">
@@ -3221,22 +3788,22 @@
       <c r="I35" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L35" s="52" t="s">
+      <c r="L35" s="50" t="s">
         <v>89</v>
       </c>
       <c r="M35" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N35" s="49">
-        <v>3</v>
-      </c>
-      <c r="O35" s="49">
-        <v>5</v>
-      </c>
-      <c r="Q35" s="22"/>
-    </row>
-    <row r="36" spans="1:19" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A36" s="28" t="str">
+      <c r="N35" s="47">
+        <v>3</v>
+      </c>
+      <c r="O35" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q35" s="20"/>
+    </row>
+    <row r="36" s="5" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A36" s="26" t="str">
         <f t="shared" si="2"/>
         <v>1022004</v>
       </c>
@@ -3252,10 +3819,10 @@
       <c r="E36" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F36" s="21">
-        <v>1</v>
-      </c>
-      <c r="G36" s="51" t="s">
+      <c r="F36" s="19">
+        <v>1</v>
+      </c>
+      <c r="G36" s="49" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="5">
@@ -3264,19 +3831,19 @@
       <c r="I36" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L36" s="50">
+      <c r="L36" s="48">
         <v>10220020</v>
       </c>
-      <c r="N36" s="49">
-        <v>3</v>
-      </c>
-      <c r="O36" s="49">
-        <v>5</v>
-      </c>
-      <c r="Q36" s="22"/>
-    </row>
-    <row r="37" spans="1:19" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A37" s="28" t="str">
+      <c r="N36" s="47">
+        <v>3</v>
+      </c>
+      <c r="O36" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q36" s="20"/>
+    </row>
+    <row r="37" s="5" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A37" s="26" t="str">
         <f t="shared" si="2"/>
         <v>1022005</v>
       </c>
@@ -3304,20 +3871,20 @@
       <c r="I37" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L37" s="50">
+      <c r="L37" s="48">
         <v>10220019</v>
       </c>
-      <c r="N37" s="49">
-        <v>3</v>
-      </c>
-      <c r="O37" s="49">
-        <v>5</v>
-      </c>
-      <c r="Q37" s="22"/>
-      <c r="S37" s="53"/>
-    </row>
-    <row r="38" spans="1:19" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A38" s="28" t="str">
+      <c r="N37" s="47">
+        <v>3</v>
+      </c>
+      <c r="O37" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q37" s="20"/>
+      <c r="S37" s="51"/>
+    </row>
+    <row r="38" s="5" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A38" s="26" t="str">
         <f t="shared" si="2"/>
         <v>1021001</v>
       </c>
@@ -3345,23 +3912,23 @@
       <c r="I38" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L38" s="50" t="s">
+      <c r="L38" s="48" t="s">
         <v>93</v>
       </c>
       <c r="M38" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N38" s="49">
-        <v>3</v>
-      </c>
-      <c r="O38" s="49">
-        <v>5</v>
-      </c>
-      <c r="Q38" s="22"/>
-      <c r="S38" s="53"/>
-    </row>
-    <row r="39" spans="1:19" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A39" s="28" t="str">
+      <c r="N38" s="47">
+        <v>3</v>
+      </c>
+      <c r="O38" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q38" s="20"/>
+      <c r="S38" s="51"/>
+    </row>
+    <row r="39" s="5" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A39" s="26" t="str">
         <f t="shared" si="2"/>
         <v>1021002</v>
       </c>
@@ -3389,23 +3956,23 @@
       <c r="I39" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L39" s="50">
+      <c r="L39" s="48">
         <v>10210031</v>
       </c>
       <c r="M39" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N39" s="49">
-        <v>3</v>
-      </c>
-      <c r="O39" s="49">
-        <v>5</v>
-      </c>
-      <c r="Q39" s="22"/>
-      <c r="S39" s="53"/>
-    </row>
-    <row r="40" spans="1:19" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A40" s="28" t="str">
+      <c r="N39" s="47">
+        <v>3</v>
+      </c>
+      <c r="O39" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q39" s="20"/>
+      <c r="S39" s="51"/>
+    </row>
+    <row r="40" s="5" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A40" s="26" t="str">
         <f t="shared" si="2"/>
         <v>1021003</v>
       </c>
@@ -3433,23 +4000,23 @@
       <c r="I40" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L40" s="50">
+      <c r="L40" s="48">
         <v>10210041</v>
       </c>
       <c r="M40" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="N40" s="49">
-        <v>3</v>
-      </c>
-      <c r="O40" s="49">
-        <v>5</v>
-      </c>
-      <c r="Q40" s="22"/>
-      <c r="S40" s="53"/>
-    </row>
-    <row r="41" spans="1:19" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A41" s="28" t="str">
+      <c r="N40" s="47">
+        <v>3</v>
+      </c>
+      <c r="O40" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q40" s="20"/>
+      <c r="S40" s="51"/>
+    </row>
+    <row r="41" s="5" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A41" s="26" t="str">
         <f t="shared" si="2"/>
         <v>1021004</v>
       </c>
@@ -3477,23 +4044,23 @@
       <c r="I41" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L41" s="50" t="s">
+      <c r="L41" s="48" t="s">
         <v>96</v>
       </c>
       <c r="M41" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N41" s="49">
-        <v>3</v>
-      </c>
-      <c r="O41" s="49">
-        <v>5</v>
-      </c>
-      <c r="Q41" s="22"/>
-      <c r="S41" s="53"/>
-    </row>
-    <row r="42" spans="1:19" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A42" s="28" t="str">
+      <c r="N41" s="47">
+        <v>3</v>
+      </c>
+      <c r="O41" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q41" s="20"/>
+      <c r="S41" s="51"/>
+    </row>
+    <row r="42" s="5" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A42" s="26" t="str">
         <f t="shared" si="2"/>
         <v>1018001</v>
       </c>
@@ -3521,22 +4088,22 @@
       <c r="I42" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L42" s="50" t="s">
+      <c r="L42" s="48" t="s">
         <v>98</v>
       </c>
       <c r="M42" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N42" s="49">
+      <c r="N42" s="47">
         <v>4</v>
       </c>
-      <c r="O42" s="49">
+      <c r="O42" s="47">
         <v>6</v>
       </c>
-      <c r="Q42" s="22"/>
-      <c r="S42" s="53"/>
-    </row>
-    <row r="43" spans="1:19" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="Q42" s="20"/>
+      <c r="S42" s="51"/>
+    </row>
+    <row r="43" s="5" customFormat="1" ht="16.5" spans="1:19">
       <c r="A43" s="5" t="str">
         <f t="shared" si="2"/>
         <v>1018002</v>
@@ -3565,20 +4132,20 @@
       <c r="I43" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L43" s="50">
+      <c r="L43" s="48">
         <v>10180031</v>
       </c>
       <c r="M43" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N43" s="49">
+      <c r="N43" s="47">
         <v>4</v>
       </c>
-      <c r="O43" s="49">
+      <c r="O43" s="47">
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="44" ht="16.5" spans="1:19">
       <c r="A44" s="5" t="str">
         <f t="shared" si="2"/>
         <v>1018003</v>
@@ -3607,20 +4174,20 @@
       <c r="I44" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L44" s="50" t="s">
+      <c r="L44" s="48" t="s">
         <v>99</v>
       </c>
       <c r="M44" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N44" s="49">
+      <c r="N44" s="47">
         <v>4</v>
       </c>
-      <c r="O44" s="49">
+      <c r="O44" s="47">
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="45" customFormat="1" ht="16.5" spans="1:19">
       <c r="A45" s="5" t="str">
         <f t="shared" si="2"/>
         <v>1025001</v>
@@ -3649,20 +4216,21 @@
       <c r="I45" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L45" s="50" t="s">
+      <c r="L45" s="48" t="s">
         <v>101</v>
       </c>
       <c r="M45" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N45" s="49">
-        <v>3</v>
-      </c>
-      <c r="O45" s="49">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N45" s="47">
+        <v>3</v>
+      </c>
+      <c r="O45" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q45" s="10"/>
+    </row>
+    <row r="46" customFormat="1" ht="16.5" spans="1:19">
       <c r="A46" s="5" t="str">
         <f t="shared" si="2"/>
         <v>1025002</v>
@@ -3691,20 +4259,21 @@
       <c r="I46" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L46" s="50">
+      <c r="L46" s="48">
         <v>10250031</v>
       </c>
       <c r="M46" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="N46" s="49">
-        <v>3</v>
-      </c>
-      <c r="O46" s="49">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N46" s="47">
+        <v>3</v>
+      </c>
+      <c r="O46" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q46" s="10"/>
+    </row>
+    <row r="47" customFormat="1" ht="16.5" spans="1:19">
       <c r="A47" s="5" t="str">
         <f t="shared" si="2"/>
         <v>1025003</v>
@@ -3733,20 +4302,21 @@
       <c r="I47" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L47" s="50" t="s">
+      <c r="L47" s="48" t="s">
         <v>103</v>
       </c>
       <c r="M47" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N47" s="49">
-        <v>3</v>
-      </c>
-      <c r="O47" s="49">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N47" s="47">
+        <v>3</v>
+      </c>
+      <c r="O47" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q47" s="10"/>
+    </row>
+    <row r="48" customFormat="1" ht="16.5" spans="1:19">
       <c r="A48" s="5" t="str">
         <f t="shared" si="2"/>
         <v>1023001</v>
@@ -3775,20 +4345,21 @@
       <c r="I48" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L48" s="50" t="s">
+      <c r="L48" s="48" t="s">
         <v>105</v>
       </c>
       <c r="M48" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N48" s="49">
+      <c r="N48" s="47">
         <v>4</v>
       </c>
-      <c r="O48" s="49">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="O48" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q48" s="10"/>
+    </row>
+    <row r="49" customFormat="1" ht="16.5" spans="1:17">
       <c r="A49" s="5" t="str">
         <f t="shared" si="2"/>
         <v>1023002</v>
@@ -3817,20 +4388,21 @@
       <c r="I49" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L49" s="50">
+      <c r="L49" s="48">
         <v>10230003</v>
       </c>
       <c r="M49" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="N49" s="49">
+      <c r="N49" s="47">
         <v>4</v>
       </c>
-      <c r="O49" s="49">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="O49" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q49" s="10"/>
+    </row>
+    <row r="50" customFormat="1" ht="16.5" spans="1:17">
       <c r="A50" s="5" t="str">
         <f t="shared" si="2"/>
         <v>1023003</v>
@@ -3859,20 +4431,21 @@
       <c r="I50" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L50" s="50" t="s">
+      <c r="L50" s="48" t="s">
         <v>106</v>
       </c>
       <c r="M50" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N50" s="49">
+      <c r="N50" s="47">
         <v>4</v>
       </c>
-      <c r="O50" s="49">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="O50" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q50" s="10"/>
+    </row>
+    <row r="51" customFormat="1" ht="16.5" spans="1:17">
       <c r="A51" s="5" t="str">
         <f t="shared" si="2"/>
         <v>1034001</v>
@@ -3901,20 +4474,21 @@
       <c r="I51" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L51" s="50">
+      <c r="L51" s="48">
         <v>10340007</v>
       </c>
       <c r="M51" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="N51" s="49">
-        <v>3</v>
-      </c>
-      <c r="O51" s="49">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="N51" s="47">
+        <v>3</v>
+      </c>
+      <c r="O51" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q51" s="10"/>
+    </row>
+    <row r="52" customFormat="1" ht="16.5" spans="1:17">
       <c r="A52" s="5" t="str">
         <f t="shared" si="2"/>
         <v>1034002</v>
@@ -3943,17 +4517,18 @@
       <c r="I52" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L52" s="50"/>
+      <c r="L52" s="48"/>
       <c r="M52" s="5"/>
-      <c r="N52" s="49">
-        <v>3</v>
-      </c>
-      <c r="O52" s="49">
-        <v>3</v>
-      </c>
-      <c r="P52" s="10"/>
-    </row>
-    <row r="53" spans="1:17" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N52" s="47">
+        <v>3</v>
+      </c>
+      <c r="O52" s="47">
+        <v>3</v>
+      </c>
+      <c r="P52" s="52"/>
+      <c r="Q52" s="10"/>
+    </row>
+    <row r="53" s="6" customFormat="1" ht="16.5" spans="1:17">
       <c r="A53" s="5" t="str">
         <f t="shared" si="2"/>
         <v>1034003</v>
@@ -3970,7 +4545,7 @@
       <c r="E53" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F53" s="54">
+      <c r="F53" s="53">
         <v>1</v>
       </c>
       <c r="G53" s="5" t="s">
@@ -3982,62 +4557,62 @@
       <c r="I53" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L53" s="52"/>
-      <c r="M53" s="54"/>
-      <c r="N53" s="49">
-        <v>3</v>
-      </c>
-      <c r="O53" s="49">
-        <v>3</v>
-      </c>
-      <c r="Q53" s="55"/>
-    </row>
-    <row r="54" spans="1:17" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A54" s="54" t="str">
+      <c r="L53" s="50"/>
+      <c r="M53" s="53"/>
+      <c r="N53" s="47">
+        <v>3</v>
+      </c>
+      <c r="O53" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q53" s="54"/>
+    </row>
+    <row r="54" s="6" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A54" s="53" t="str">
         <f t="shared" si="2"/>
         <v>1035001</v>
       </c>
-      <c r="B54" s="54">
+      <c r="B54" s="53">
         <v>103500</v>
       </c>
-      <c r="C54" s="54">
-        <v>1</v>
-      </c>
-      <c r="D54" s="54" t="s">
+      <c r="C54" s="53">
+        <v>1</v>
+      </c>
+      <c r="D54" s="53" t="s">
         <v>110</v>
       </c>
-      <c r="E54" s="54" t="s">
+      <c r="E54" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="F54" s="54">
-        <v>1</v>
-      </c>
-      <c r="G54" s="54" t="s">
-        <v>23</v>
-      </c>
-      <c r="H54" s="54">
+      <c r="F54" s="53">
+        <v>1</v>
+      </c>
+      <c r="G54" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="H54" s="53">
         <v>2035001</v>
       </c>
-      <c r="I54" s="54" t="s">
-        <v>24</v>
-      </c>
-      <c r="L54" s="52" t="s">
+      <c r="I54" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="L54" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="M54" s="54" t="s">
+      <c r="M54" s="53" t="s">
         <v>113</v>
       </c>
-      <c r="N54" s="49">
+      <c r="N54" s="47">
         <v>4</v>
       </c>
-      <c r="O54" s="49">
-        <v>3</v>
-      </c>
-      <c r="Q54" s="55"/>
-    </row>
-    <row r="55" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="O54" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="54"/>
+    </row>
+    <row r="55" customFormat="1" ht="16.5" spans="1:17">
       <c r="A55" s="5" t="str">
-        <f t="shared" ref="A55:A108" si="3">B55&amp;C55</f>
+        <f t="shared" ref="A54:A108" si="3">B55&amp;C55</f>
         <v>1035002</v>
       </c>
       <c r="B55" s="5">
@@ -4064,20 +4639,21 @@
       <c r="I55" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L55" s="50" t="s">
+      <c r="L55" s="48" t="s">
         <v>115</v>
       </c>
       <c r="M55" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="N55" s="49">
+      <c r="N55" s="47">
         <v>4</v>
       </c>
-      <c r="O55" s="49">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="O55" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q55" s="10"/>
+    </row>
+    <row r="56" customFormat="1" ht="16.5" spans="1:17">
       <c r="A56" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1035003</v>
@@ -4106,21 +4682,22 @@
       <c r="I56" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L56" s="50" t="s">
+      <c r="L56" s="48" t="s">
         <v>117</v>
       </c>
       <c r="M56" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="N56" s="49">
+      <c r="N56" s="47">
         <v>4</v>
       </c>
-      <c r="O56" s="49">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A57" s="56">
+      <c r="O56" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q56" s="10"/>
+    </row>
+    <row r="57" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A57" s="55">
         <v>1035011</v>
       </c>
       <c r="B57" s="5">
@@ -4147,20 +4724,21 @@
       <c r="I57" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L57" s="50" t="s">
+      <c r="L57" s="48" t="s">
         <v>120</v>
       </c>
       <c r="M57" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="N57" s="49">
+      <c r="N57" s="47">
         <v>4</v>
       </c>
-      <c r="O57" s="49">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="O57" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="10"/>
+    </row>
+    <row r="58" customFormat="1" ht="16.5" spans="1:17">
       <c r="A58" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1035012</v>
@@ -4189,20 +4767,21 @@
       <c r="I58" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L58" s="50" t="s">
+      <c r="L58" s="48" t="s">
         <v>121</v>
       </c>
       <c r="M58" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="N58" s="49">
+      <c r="N58" s="47">
         <v>4</v>
       </c>
-      <c r="O58" s="49">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="O58" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="10"/>
+    </row>
+    <row r="59" customFormat="1" ht="16.5" spans="1:17">
       <c r="A59" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1035013</v>
@@ -4231,20 +4810,21 @@
       <c r="I59" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L59" s="50" t="s">
+      <c r="L59" s="48" t="s">
         <v>122</v>
       </c>
       <c r="M59" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="N59" s="49">
+      <c r="N59" s="47">
         <v>4</v>
       </c>
-      <c r="O59" s="49">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="O59" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="10"/>
+    </row>
+    <row r="60" customFormat="1" ht="16.5" spans="1:17">
       <c r="A60" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1036001</v>
@@ -4273,20 +4853,21 @@
       <c r="I60" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L60" s="50" t="s">
+      <c r="L60" s="48" t="s">
         <v>124</v>
       </c>
       <c r="M60" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="N60" s="49">
-        <v>3</v>
-      </c>
-      <c r="O60" s="49">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N60" s="47">
+        <v>3</v>
+      </c>
+      <c r="O60" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="10"/>
+    </row>
+    <row r="61" customFormat="1" ht="16.5" spans="1:17">
       <c r="A61" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1036002</v>
@@ -4315,20 +4896,21 @@
       <c r="I61" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L61" s="50">
+      <c r="L61" s="48">
         <v>10360004</v>
       </c>
       <c r="M61" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="N61" s="49">
-        <v>3</v>
-      </c>
-      <c r="O61" s="49">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N61" s="47">
+        <v>3</v>
+      </c>
+      <c r="O61" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q61" s="10"/>
+    </row>
+    <row r="62" customFormat="1" ht="16.5" spans="1:17">
       <c r="A62" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1036003</v>
@@ -4357,20 +4939,21 @@
       <c r="I62" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L62" s="50">
+      <c r="L62" s="48">
         <v>10360002</v>
       </c>
       <c r="M62" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="N62" s="49">
-        <v>3</v>
-      </c>
-      <c r="O62" s="49">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N62" s="47">
+        <v>3</v>
+      </c>
+      <c r="O62" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="10"/>
+    </row>
+    <row r="63" customFormat="1" ht="16.5" spans="1:17">
       <c r="A63" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1028001</v>
@@ -4399,20 +4982,21 @@
       <c r="I63" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L63" s="50" t="s">
+      <c r="L63" s="48" t="s">
         <v>130</v>
       </c>
       <c r="M63" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="N63" s="49">
-        <v>5</v>
-      </c>
-      <c r="O63" s="49">
+      <c r="N63" s="47">
+        <v>5</v>
+      </c>
+      <c r="O63" s="47">
         <v>6</v>
       </c>
-    </row>
-    <row r="64" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="Q63" s="10"/>
+    </row>
+    <row r="64" customFormat="1" ht="16.5" spans="1:17">
       <c r="A64" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1028002</v>
@@ -4441,20 +5025,21 @@
       <c r="I64" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L64" s="50">
+      <c r="L64" s="48">
         <v>10280002</v>
       </c>
       <c r="M64" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="N64" s="49">
-        <v>5</v>
-      </c>
-      <c r="O64" s="49">
+      <c r="N64" s="47">
+        <v>5</v>
+      </c>
+      <c r="O64" s="47">
         <v>6</v>
       </c>
-    </row>
-    <row r="65" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="Q64" s="10"/>
+    </row>
+    <row r="65" customFormat="1" ht="16.5" spans="1:17">
       <c r="A65" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1028003</v>
@@ -4483,20 +5068,21 @@
       <c r="I65" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L65" s="50" t="s">
+      <c r="L65" s="48" t="s">
         <v>133</v>
       </c>
       <c r="M65" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N65" s="49">
-        <v>5</v>
-      </c>
-      <c r="O65" s="49">
+      <c r="N65" s="47">
+        <v>5</v>
+      </c>
+      <c r="O65" s="47">
         <v>6</v>
       </c>
-    </row>
-    <row r="66" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="Q65" s="10"/>
+    </row>
+    <row r="66" customFormat="1" ht="16.5" spans="1:17">
       <c r="A66" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1034011</v>
@@ -4525,20 +5111,21 @@
       <c r="I66" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L66" s="50">
+      <c r="L66" s="48">
         <v>10340101</v>
       </c>
       <c r="M66" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="N66" s="49">
-        <v>3</v>
-      </c>
-      <c r="O66" s="49">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="N66" s="47">
+        <v>3</v>
+      </c>
+      <c r="O66" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="10"/>
+    </row>
+    <row r="67" customFormat="1" ht="16.5" spans="1:17">
       <c r="A67" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1034012</v>
@@ -4567,17 +5154,18 @@
       <c r="I67" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L67" s="50"/>
+      <c r="L67" s="48"/>
       <c r="M67" s="5"/>
-      <c r="N67" s="49">
-        <v>3</v>
-      </c>
-      <c r="O67" s="49">
-        <v>3</v>
-      </c>
-      <c r="P67" s="10"/>
-    </row>
-    <row r="68" spans="1:17" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N67" s="47">
+        <v>3</v>
+      </c>
+      <c r="O67" s="47">
+        <v>3</v>
+      </c>
+      <c r="P67" s="52"/>
+      <c r="Q67" s="10"/>
+    </row>
+    <row r="68" s="7" customFormat="1" ht="16.5" spans="1:17">
       <c r="A68" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1034013</v>
@@ -4608,60 +5196,60 @@
       </c>
       <c r="J68"/>
       <c r="K68"/>
-      <c r="L68" s="50"/>
+      <c r="L68" s="48"/>
       <c r="M68" s="5"/>
-      <c r="N68" s="49">
-        <v>3</v>
-      </c>
-      <c r="O68" s="49">
-        <v>3</v>
-      </c>
-      <c r="Q68" s="57"/>
-    </row>
-    <row r="69" spans="1:17" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A69" s="58" t="str">
+      <c r="N68" s="47">
+        <v>3</v>
+      </c>
+      <c r="O68" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q68" s="56"/>
+    </row>
+    <row r="69" s="7" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A69" s="57" t="str">
         <f t="shared" si="3"/>
         <v>1020001</v>
       </c>
-      <c r="B69" s="58">
+      <c r="B69" s="57">
         <v>102000</v>
       </c>
-      <c r="C69" s="58">
-        <v>1</v>
-      </c>
-      <c r="D69" s="58" t="s">
+      <c r="C69" s="57">
+        <v>1</v>
+      </c>
+      <c r="D69" s="57" t="s">
         <v>136</v>
       </c>
-      <c r="E69" s="58" t="s">
+      <c r="E69" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="F69" s="58">
-        <v>1</v>
-      </c>
-      <c r="G69" s="58" t="s">
-        <v>23</v>
-      </c>
-      <c r="H69" s="58">
+      <c r="F69" s="57">
+        <v>1</v>
+      </c>
+      <c r="G69" s="57" t="s">
+        <v>23</v>
+      </c>
+      <c r="H69" s="57">
         <v>2020001</v>
       </c>
-      <c r="I69" s="58" t="s">
-        <v>24</v>
-      </c>
-      <c r="L69" s="59" t="s">
+      <c r="I69" s="57" t="s">
+        <v>24</v>
+      </c>
+      <c r="L69" s="58" t="s">
         <v>137</v>
       </c>
-      <c r="M69" s="58" t="s">
+      <c r="M69" s="57" t="s">
         <v>138</v>
       </c>
-      <c r="N69" s="60">
-        <v>5</v>
-      </c>
-      <c r="O69" s="60">
-        <v>5</v>
-      </c>
-      <c r="Q69" s="57"/>
-    </row>
-    <row r="70" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N69" s="59">
+        <v>5</v>
+      </c>
+      <c r="O69" s="59">
+        <v>5</v>
+      </c>
+      <c r="Q69" s="56"/>
+    </row>
+    <row r="70" customFormat="1" ht="16.5" spans="1:17">
       <c r="A70" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1020002</v>
@@ -4690,20 +5278,21 @@
       <c r="I70" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L70" s="50" t="s">
+      <c r="L70" s="48" t="s">
         <v>139</v>
       </c>
       <c r="M70" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="N70" s="49">
-        <v>5</v>
-      </c>
-      <c r="O70" s="49">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="71" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N70" s="47">
+        <v>5</v>
+      </c>
+      <c r="O70" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q70" s="10"/>
+    </row>
+    <row r="71" customFormat="1" ht="16.5" spans="1:17">
       <c r="A71" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1020003</v>
@@ -4732,63 +5321,64 @@
       <c r="I71" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L71" s="50" t="s">
+      <c r="L71" s="48" t="s">
         <v>141</v>
       </c>
       <c r="M71" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="N71" s="49">
-        <v>5</v>
-      </c>
-      <c r="O71" s="49">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A72" s="61" t="str">
+      <c r="N71" s="47">
+        <v>5</v>
+      </c>
+      <c r="O71" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q71" s="10"/>
+    </row>
+    <row r="72" s="8" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A72" s="60" t="str">
         <f t="shared" si="3"/>
         <v>1020004</v>
       </c>
-      <c r="B72" s="61">
+      <c r="B72" s="60">
         <v>102000</v>
       </c>
-      <c r="C72" s="61">
+      <c r="C72" s="60">
         <v>4</v>
       </c>
-      <c r="D72" s="61" t="s">
+      <c r="D72" s="60" t="s">
         <v>136</v>
       </c>
-      <c r="E72" s="61" t="s">
+      <c r="E72" s="60" t="s">
         <v>143</v>
       </c>
-      <c r="F72" s="61">
-        <v>1</v>
-      </c>
-      <c r="G72" s="61" t="s">
-        <v>23</v>
-      </c>
-      <c r="H72" s="61">
+      <c r="F72" s="60">
+        <v>1</v>
+      </c>
+      <c r="G72" s="60" t="s">
+        <v>23</v>
+      </c>
+      <c r="H72" s="60">
         <v>2020002</v>
       </c>
-      <c r="I72" s="61" t="s">
-        <v>24</v>
-      </c>
-      <c r="L72" s="62">
+      <c r="I72" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="L72" s="61">
         <v>10200016</v>
       </c>
-      <c r="M72" s="61" t="s">
+      <c r="M72" s="60" t="s">
         <v>144</v>
       </c>
-      <c r="N72" s="63">
-        <v>5</v>
-      </c>
-      <c r="O72" s="63">
-        <v>5</v>
-      </c>
-      <c r="Q72" s="64"/>
-    </row>
-    <row r="73" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N72" s="62">
+        <v>5</v>
+      </c>
+      <c r="O72" s="62">
+        <v>5</v>
+      </c>
+      <c r="Q72" s="63"/>
+    </row>
+    <row r="73" customFormat="1" ht="16.5" spans="1:17">
       <c r="A73" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1020005</v>
@@ -4817,20 +5407,21 @@
       <c r="I73" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L73" s="50">
+      <c r="L73" s="48">
         <v>10200021</v>
       </c>
       <c r="M73" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="N73" s="49">
-        <v>5</v>
-      </c>
-      <c r="O73" s="49">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="74" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N73" s="47">
+        <v>5</v>
+      </c>
+      <c r="O73" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q73" s="10"/>
+    </row>
+    <row r="74" customFormat="1" ht="16.5" spans="1:17">
       <c r="A74" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1038001</v>
@@ -4862,18 +5453,19 @@
       <c r="J74" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="L74" s="50"/>
+      <c r="L74" s="48"/>
       <c r="M74" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="N74" s="49">
-        <v>3</v>
-      </c>
-      <c r="O74" s="49">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="75" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N74" s="47">
+        <v>3</v>
+      </c>
+      <c r="O74" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q74" s="10"/>
+    </row>
+    <row r="75" customFormat="1" ht="16.5" spans="1:17">
       <c r="A75" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1038002</v>
@@ -4902,20 +5494,21 @@
       <c r="I75" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L75" s="50">
+      <c r="L75" s="48">
         <v>10380002</v>
       </c>
       <c r="M75" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="N75" s="49">
-        <v>3</v>
-      </c>
-      <c r="O75" s="49">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="76" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N75" s="47">
+        <v>3</v>
+      </c>
+      <c r="O75" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q75" s="10"/>
+    </row>
+    <row r="76" customFormat="1" ht="16.5" spans="1:17">
       <c r="A76" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1038004</v>
@@ -4944,20 +5537,21 @@
       <c r="I76" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L76" s="50" t="s">
+      <c r="L76" s="48" t="s">
         <v>152</v>
       </c>
       <c r="M76" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="N76" s="49">
-        <v>3</v>
-      </c>
-      <c r="O76" s="49">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N76" s="47">
+        <v>3</v>
+      </c>
+      <c r="O76" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q76" s="10"/>
+    </row>
+    <row r="77" customFormat="1" ht="16.5" spans="1:17">
       <c r="A77" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1038003</v>
@@ -4986,20 +5580,21 @@
       <c r="I77" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L77" s="50" t="s">
+      <c r="L77" s="48" t="s">
         <v>154</v>
       </c>
       <c r="M77" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="N77" s="49">
-        <v>3</v>
-      </c>
-      <c r="O77" s="49">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="78" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N77" s="47">
+        <v>3</v>
+      </c>
+      <c r="O77" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q77" s="10"/>
+    </row>
+    <row r="78" customFormat="1" ht="16.5" spans="1:17">
       <c r="A78" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1027001</v>
@@ -5028,20 +5623,21 @@
       <c r="I78" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L78" s="50" t="s">
+      <c r="L78" s="48" t="s">
         <v>157</v>
       </c>
       <c r="M78" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="N78" s="49">
-        <v>3</v>
-      </c>
-      <c r="O78" s="49">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="79" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N78" s="47">
+        <v>3</v>
+      </c>
+      <c r="O78" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q78" s="10"/>
+    </row>
+    <row r="79" customFormat="1" ht="16.5" spans="1:17">
       <c r="A79" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1027002</v>
@@ -5070,20 +5666,21 @@
       <c r="I79" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L79" s="50">
+      <c r="L79" s="48">
         <v>10270003</v>
       </c>
       <c r="M79" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="N79" s="49">
-        <v>3</v>
-      </c>
-      <c r="O79" s="49">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="80" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N79" s="47">
+        <v>3</v>
+      </c>
+      <c r="O79" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q79" s="10"/>
+    </row>
+    <row r="80" customFormat="1" ht="16.5" spans="1:17">
       <c r="A80" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1027003</v>
@@ -5112,20 +5709,21 @@
       <c r="I80" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L80" s="50" t="s">
+      <c r="L80" s="48" t="s">
         <v>160</v>
       </c>
       <c r="M80" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="N80" s="49">
-        <v>3</v>
-      </c>
-      <c r="O80" s="49">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N80" s="47">
+        <v>3</v>
+      </c>
+      <c r="O80" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q80" s="10"/>
+    </row>
+    <row r="81" customFormat="1" ht="16.5" spans="1:17">
       <c r="A81" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1037001</v>
@@ -5154,20 +5752,21 @@
       <c r="I81" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L81" s="50" t="s">
+      <c r="L81" s="48" t="s">
         <v>163</v>
       </c>
       <c r="M81" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="N81" s="49">
+      <c r="N81" s="47">
         <v>4</v>
       </c>
-      <c r="O81" s="49">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="O81" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="10"/>
+    </row>
+    <row r="82" customFormat="1" ht="16.5" spans="1:17">
       <c r="A82" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1037002</v>
@@ -5196,20 +5795,21 @@
       <c r="I82" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L82" s="50" t="s">
+      <c r="L82" s="48" t="s">
         <v>166</v>
       </c>
       <c r="M82" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="N82" s="49">
+      <c r="N82" s="47">
         <v>4</v>
       </c>
-      <c r="O82" s="49">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="83" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="O82" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q82" s="10"/>
+    </row>
+    <row r="83" customFormat="1" ht="16.5" spans="1:17">
       <c r="A83" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1037003</v>
@@ -5238,20 +5838,21 @@
       <c r="I83" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L83" s="50">
+      <c r="L83" s="48">
         <v>10370003</v>
       </c>
       <c r="M83" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="N83" s="49">
+      <c r="N83" s="47">
         <v>4</v>
       </c>
-      <c r="O83" s="49">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="O83" s="47">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="10"/>
+    </row>
+    <row r="84" customFormat="1" ht="16.5" spans="1:17">
       <c r="A84" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1031001</v>
@@ -5280,20 +5881,21 @@
       <c r="I84" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L84" s="50" t="s">
+      <c r="L84" s="48" t="s">
         <v>169</v>
       </c>
       <c r="M84" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="N84" s="49">
-        <v>3</v>
-      </c>
-      <c r="O84" s="49">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="85" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N84" s="47">
+        <v>3</v>
+      </c>
+      <c r="O84" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q84" s="10"/>
+    </row>
+    <row r="85" customFormat="1" ht="16.5" spans="1:17">
       <c r="A85" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1031002</v>
@@ -5322,20 +5924,21 @@
       <c r="I85" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L85" s="50">
+      <c r="L85" s="48">
         <v>10310008</v>
       </c>
       <c r="M85" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="N85" s="49">
-        <v>3</v>
-      </c>
-      <c r="O85" s="49">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="86" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N85" s="47">
+        <v>3</v>
+      </c>
+      <c r="O85" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q85" s="10"/>
+    </row>
+    <row r="86" customFormat="1" ht="16.5" spans="1:17">
       <c r="A86" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1031003</v>
@@ -5364,20 +5967,21 @@
       <c r="I86" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L86" s="50" t="s">
+      <c r="L86" s="48" t="s">
         <v>172</v>
       </c>
       <c r="M86" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="N86" s="49">
-        <v>3</v>
-      </c>
-      <c r="O86" s="49">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="87" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N86" s="47">
+        <v>3</v>
+      </c>
+      <c r="O86" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q86" s="10"/>
+    </row>
+    <row r="87" customFormat="1" ht="16.5" spans="1:17">
       <c r="A87" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1031004</v>
@@ -5406,20 +6010,21 @@
       <c r="I87" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L87" s="50" t="s">
+      <c r="L87" s="48" t="s">
         <v>174</v>
       </c>
       <c r="M87" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="N87" s="49">
-        <v>3</v>
-      </c>
-      <c r="O87" s="49">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="88" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N87" s="47">
+        <v>3</v>
+      </c>
+      <c r="O87" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q87" s="10"/>
+    </row>
+    <row r="88" customFormat="1" ht="16.5" spans="1:17">
       <c r="A88" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1031005</v>
@@ -5448,20 +6053,21 @@
       <c r="I88" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L88" s="50">
+      <c r="L88" s="48">
         <v>10310003</v>
       </c>
       <c r="M88" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="N88" s="49">
-        <v>3</v>
-      </c>
-      <c r="O88" s="49">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="89" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N88" s="47">
+        <v>3</v>
+      </c>
+      <c r="O88" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q88" s="10"/>
+    </row>
+    <row r="89" customFormat="1" ht="16.5" spans="1:17">
       <c r="A89" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1031006</v>
@@ -5490,20 +6096,21 @@
       <c r="I89" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L89" s="50" t="s">
+      <c r="L89" s="48" t="s">
         <v>179</v>
       </c>
       <c r="M89" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="N89" s="49">
-        <v>3</v>
-      </c>
-      <c r="O89" s="49">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="90" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N89" s="47">
+        <v>3</v>
+      </c>
+      <c r="O89" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q89" s="10"/>
+    </row>
+    <row r="90" customFormat="1" ht="16.5" spans="1:17">
       <c r="A90" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1040001</v>
@@ -5532,20 +6139,21 @@
       <c r="I90" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L90" s="50" t="s">
+      <c r="L90" s="48" t="s">
         <v>182</v>
       </c>
       <c r="M90" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="N90" s="49">
-        <v>3</v>
-      </c>
-      <c r="O90" s="49">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="91" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N90" s="47">
+        <v>3</v>
+      </c>
+      <c r="O90" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q90" s="10"/>
+    </row>
+    <row r="91" customFormat="1" ht="16.5" spans="1:17">
       <c r="A91" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1040002</v>
@@ -5574,20 +6182,21 @@
       <c r="I91" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L91" s="50" t="s">
+      <c r="L91" s="48" t="s">
         <v>184</v>
       </c>
       <c r="M91" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="N91" s="49">
-        <v>3</v>
-      </c>
-      <c r="O91" s="49">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="92" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N91" s="47">
+        <v>3</v>
+      </c>
+      <c r="O91" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q91" s="10"/>
+    </row>
+    <row r="92" customFormat="1" ht="16.5" spans="1:17">
       <c r="A92" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1040003</v>
@@ -5616,20 +6225,21 @@
       <c r="I92" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L92" s="50" t="s">
+      <c r="L92" s="48" t="s">
         <v>186</v>
       </c>
       <c r="M92" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="N92" s="49">
-        <v>3</v>
-      </c>
-      <c r="O92" s="49">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="93" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N92" s="47">
+        <v>3</v>
+      </c>
+      <c r="O92" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q92" s="10"/>
+    </row>
+    <row r="93" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A93" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1039001</v>
@@ -5664,15 +6274,15 @@
       <c r="M93" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="N93" s="49">
-        <v>3</v>
-      </c>
-      <c r="O93" s="49">
-        <v>5</v>
-      </c>
-      <c r="Q93" s="22"/>
-    </row>
-    <row r="94" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N93" s="47">
+        <v>3</v>
+      </c>
+      <c r="O93" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q93" s="20"/>
+    </row>
+    <row r="94" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A94" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1039002</v>
@@ -5701,21 +6311,21 @@
       <c r="I94" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L94" s="50">
+      <c r="L94" s="48">
         <v>10390003</v>
       </c>
       <c r="M94" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="N94" s="49">
-        <v>3</v>
-      </c>
-      <c r="O94" s="49">
-        <v>5</v>
-      </c>
-      <c r="Q94" s="22"/>
-    </row>
-    <row r="95" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N94" s="47">
+        <v>3</v>
+      </c>
+      <c r="O94" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q94" s="20"/>
+    </row>
+    <row r="95" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A95" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1039003</v>
@@ -5750,15 +6360,15 @@
       <c r="M95" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N95" s="49">
-        <v>3</v>
-      </c>
-      <c r="O95" s="49">
-        <v>5</v>
-      </c>
-      <c r="Q95" s="22"/>
-    </row>
-    <row r="96" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N95" s="47">
+        <v>3</v>
+      </c>
+      <c r="O95" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q95" s="20"/>
+    </row>
+    <row r="96" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A96" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1016001</v>
@@ -5793,15 +6403,15 @@
       <c r="M96" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="N96" s="49">
+      <c r="N96" s="47">
         <v>6</v>
       </c>
-      <c r="O96" s="49">
+      <c r="O96" s="47">
         <v>6</v>
       </c>
-      <c r="Q96" s="22"/>
-    </row>
-    <row r="97" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="Q96" s="20"/>
+    </row>
+    <row r="97" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A97" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1016002</v>
@@ -5830,21 +6440,21 @@
       <c r="I97" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L97" s="50">
+      <c r="L97" s="48">
         <v>10160002</v>
       </c>
       <c r="M97" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="N97" s="49">
+      <c r="N97" s="47">
         <v>6</v>
       </c>
-      <c r="O97" s="49">
+      <c r="O97" s="47">
         <v>6</v>
       </c>
-      <c r="Q97" s="22"/>
-    </row>
-    <row r="98" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="Q97" s="20"/>
+    </row>
+    <row r="98" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A98" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1016003</v>
@@ -5879,15 +6489,15 @@
       <c r="M98" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="N98" s="49">
+      <c r="N98" s="47">
         <v>6</v>
       </c>
-      <c r="O98" s="49">
+      <c r="O98" s="47">
         <v>6</v>
       </c>
-      <c r="Q98" s="22"/>
-    </row>
-    <row r="99" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="Q98" s="20"/>
+    </row>
+    <row r="99" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A99" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1015001</v>
@@ -5922,15 +6532,15 @@
       <c r="M99" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="N99" s="49">
-        <v>3</v>
-      </c>
-      <c r="O99" s="49">
-        <v>5</v>
-      </c>
-      <c r="Q99" s="22"/>
-    </row>
-    <row r="100" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N99" s="47">
+        <v>3</v>
+      </c>
+      <c r="O99" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q99" s="20"/>
+    </row>
+    <row r="100" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A100" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1015002</v>
@@ -5965,15 +6575,15 @@
       <c r="M100" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="N100" s="49">
-        <v>3</v>
-      </c>
-      <c r="O100" s="49">
-        <v>5</v>
-      </c>
-      <c r="Q100" s="22"/>
-    </row>
-    <row r="101" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N100" s="47">
+        <v>3</v>
+      </c>
+      <c r="O100" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q100" s="20"/>
+    </row>
+    <row r="101" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A101" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1015003</v>
@@ -6002,21 +6612,21 @@
       <c r="I101" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L101" s="50">
+      <c r="L101" s="48">
         <v>10150002</v>
       </c>
       <c r="M101" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N101" s="49">
-        <v>3</v>
-      </c>
-      <c r="O101" s="49">
-        <v>5</v>
-      </c>
-      <c r="Q101" s="22"/>
-    </row>
-    <row r="102" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N101" s="47">
+        <v>3</v>
+      </c>
+      <c r="O101" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q101" s="20"/>
+    </row>
+    <row r="102" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A102" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1015004</v>
@@ -6051,15 +6661,15 @@
       <c r="M102" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="N102" s="49">
-        <v>3</v>
-      </c>
-      <c r="O102" s="49">
-        <v>5</v>
-      </c>
-      <c r="Q102" s="22"/>
-    </row>
-    <row r="103" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N102" s="47">
+        <v>3</v>
+      </c>
+      <c r="O102" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q102" s="20"/>
+    </row>
+    <row r="103" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A103" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1015005</v>
@@ -6088,21 +6698,21 @@
       <c r="I103" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L103" s="50">
+      <c r="L103" s="48">
         <v>10150005</v>
       </c>
       <c r="M103" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="N103" s="49">
-        <v>3</v>
-      </c>
-      <c r="O103" s="49">
-        <v>5</v>
-      </c>
-      <c r="Q103" s="22"/>
-    </row>
-    <row r="104" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N103" s="47">
+        <v>3</v>
+      </c>
+      <c r="O103" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q103" s="20"/>
+    </row>
+    <row r="104" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A104" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1015006</v>
@@ -6131,21 +6741,21 @@
       <c r="I104" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L104" s="50">
+      <c r="L104" s="48">
         <v>10150006</v>
       </c>
       <c r="M104" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="N104" s="49">
-        <v>3</v>
-      </c>
-      <c r="O104" s="49">
-        <v>5</v>
-      </c>
-      <c r="Q104" s="22"/>
-    </row>
-    <row r="105" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N104" s="47">
+        <v>3</v>
+      </c>
+      <c r="O104" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q104" s="20"/>
+    </row>
+    <row r="105" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A105" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1015007</v>
@@ -6174,21 +6784,21 @@
       <c r="I105" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L105" s="50">
+      <c r="L105" s="48">
         <v>10150007</v>
       </c>
       <c r="M105" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="N105" s="49">
-        <v>3</v>
-      </c>
-      <c r="O105" s="49">
-        <v>5</v>
-      </c>
-      <c r="Q105" s="22"/>
-    </row>
-    <row r="106" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="N105" s="47">
+        <v>3</v>
+      </c>
+      <c r="O105" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q105" s="20"/>
+    </row>
+    <row r="106" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A106" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1026001</v>
@@ -6217,21 +6827,21 @@
       <c r="I106" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L106" s="5" t="s">
+      <c r="L106" s="48" t="s">
         <v>211</v>
       </c>
       <c r="M106" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="N106" s="49">
+      <c r="N106" s="47">
         <v>6</v>
       </c>
-      <c r="O106" s="49">
+      <c r="O106" s="47">
         <v>6</v>
       </c>
-      <c r="Q106" s="22"/>
-    </row>
-    <row r="107" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="Q106" s="20"/>
+    </row>
+    <row r="107" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A107" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1026002</v>
@@ -6260,21 +6870,21 @@
       <c r="I107" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L107" s="50" t="s">
+      <c r="L107" s="48" t="s">
         <v>213</v>
       </c>
       <c r="M107" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="N107" s="49">
+      <c r="N107" s="47">
         <v>6</v>
       </c>
-      <c r="O107" s="49">
+      <c r="O107" s="47">
         <v>6</v>
       </c>
-      <c r="Q107" s="22"/>
-    </row>
-    <row r="108" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="Q107" s="20"/>
+    </row>
+    <row r="108" s="5" customFormat="1" ht="16.5" spans="1:17">
       <c r="A108" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1026003</v>
@@ -6303,22 +6913,22 @@
       <c r="I108" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L108" s="5" t="s">
+      <c r="L108" s="48" t="s">
         <v>214</v>
       </c>
       <c r="M108" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="N108" s="49">
+      <c r="N108" s="47">
         <v>6</v>
       </c>
-      <c r="O108" s="49">
+      <c r="O108" s="47">
         <v>6</v>
       </c>
-      <c r="Q108" s="22"/>
-    </row>
-    <row r="109" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A109" s="50">
+      <c r="Q108" s="20"/>
+    </row>
+    <row r="109" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A109" s="5">
         <v>1050001</v>
       </c>
       <c r="B109" s="5">
@@ -6345,22 +6955,22 @@
       <c r="I109" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L109" s="5" t="s">
+      <c r="L109" s="48" t="s">
         <v>216</v>
       </c>
       <c r="M109" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="N109" s="49">
+      <c r="N109" s="47">
         <v>6</v>
       </c>
-      <c r="O109" s="49">
+      <c r="O109" s="47">
         <v>6</v>
       </c>
-      <c r="Q109" s="22"/>
-    </row>
-    <row r="110" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A110" s="50">
+      <c r="Q109" s="20"/>
+    </row>
+    <row r="110" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A110" s="5">
         <v>1050002</v>
       </c>
       <c r="B110" s="5">
@@ -6387,23 +6997,23 @@
       <c r="I110" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L110" s="50" t="s">
+      <c r="L110" s="48" t="s">
         <v>218</v>
       </c>
       <c r="M110" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="N110" s="49">
+      <c r="N110" s="47">
         <v>6</v>
       </c>
-      <c r="O110" s="49">
+      <c r="O110" s="47">
         <v>6</v>
       </c>
-      <c r="P110" s="49"/>
-      <c r="Q110" s="22"/>
-    </row>
-    <row r="111" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A111" s="50">
+      <c r="P110" s="5"/>
+      <c r="Q110" s="20"/>
+    </row>
+    <row r="111" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A111" s="5">
         <v>1050003</v>
       </c>
       <c r="B111" s="5">
@@ -6430,22 +7040,22 @@
       <c r="I111" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L111" s="50" t="s">
+      <c r="L111" s="48" t="s">
         <v>220</v>
       </c>
       <c r="M111" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="N111" s="49">
+      <c r="N111" s="47">
         <v>6</v>
       </c>
-      <c r="O111" s="49">
+      <c r="O111" s="47">
         <v>6</v>
       </c>
-      <c r="Q111" s="22"/>
-    </row>
-    <row r="112" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A112" s="50">
+      <c r="Q111" s="20"/>
+    </row>
+    <row r="112" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A112" s="5">
         <v>1050004</v>
       </c>
       <c r="B112" s="5">
@@ -6472,22 +7082,22 @@
       <c r="I112" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L112" s="50" t="s">
+      <c r="L112" s="48" t="s">
         <v>223</v>
       </c>
       <c r="M112" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="N112" s="49">
+      <c r="N112" s="47">
         <v>6</v>
       </c>
-      <c r="O112" s="49">
+      <c r="O112" s="47">
         <v>6</v>
       </c>
-      <c r="Q112" s="22"/>
-    </row>
-    <row r="113" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A113" s="50">
+      <c r="Q112" s="20"/>
+    </row>
+    <row r="113" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A113" s="5">
         <v>1051001</v>
       </c>
       <c r="B113" s="5">
@@ -6514,22 +7124,22 @@
       <c r="I113" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L113" s="50">
+      <c r="L113" s="48">
         <v>10510008</v>
       </c>
       <c r="M113" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="N113" s="49">
+      <c r="N113" s="47">
         <v>6</v>
       </c>
-      <c r="O113" s="49">
+      <c r="O113" s="47">
         <v>6</v>
       </c>
-      <c r="Q113" s="22"/>
-    </row>
-    <row r="114" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A114" s="50">
+      <c r="Q113" s="20"/>
+    </row>
+    <row r="114" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A114" s="5">
         <v>1051002</v>
       </c>
       <c r="B114" s="5">
@@ -6541,7 +7151,7 @@
       <c r="D114" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="E114" t="s">
+      <c r="E114" s="5" t="s">
         <v>228</v>
       </c>
       <c r="F114" s="5">
@@ -6556,21 +7166,22 @@
       <c r="I114" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L114" s="50" t="s">
+      <c r="L114" s="48" t="s">
         <v>229</v>
       </c>
-      <c r="M114" t="s">
+      <c r="M114" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="N114" s="49">
+      <c r="N114" s="47">
         <v>6</v>
       </c>
-      <c r="O114" s="49">
+      <c r="O114" s="47">
         <v>6</v>
       </c>
-    </row>
-    <row r="115" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A115" s="50">
+      <c r="Q114" s="20"/>
+    </row>
+    <row r="115" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A115" s="5">
         <v>1051003</v>
       </c>
       <c r="B115" s="5">
@@ -6582,7 +7193,7 @@
       <c r="D115" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="E115" t="s">
+      <c r="E115" s="5" t="s">
         <v>231</v>
       </c>
       <c r="F115" s="5">
@@ -6597,21 +7208,22 @@
       <c r="I115" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L115" s="50" t="s">
+      <c r="L115" s="48" t="s">
         <v>232</v>
       </c>
-      <c r="M115" t="s">
+      <c r="M115" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="N115" s="49">
+      <c r="N115" s="47">
         <v>6</v>
       </c>
-      <c r="O115" s="49">
+      <c r="O115" s="47">
         <v>6</v>
       </c>
-    </row>
-    <row r="116" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A116" s="50">
+      <c r="Q115" s="20"/>
+    </row>
+    <row r="116" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A116" s="5">
         <v>1051004</v>
       </c>
       <c r="B116" s="5">
@@ -6623,7 +7235,7 @@
       <c r="D116" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="E116" t="s">
+      <c r="E116" s="5" t="s">
         <v>132</v>
       </c>
       <c r="F116" s="5">
@@ -6638,21 +7250,22 @@
       <c r="I116" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L116" s="50">
+      <c r="L116" s="48">
         <v>10510005</v>
       </c>
-      <c r="M116" t="s">
+      <c r="M116" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="N116" s="49">
+      <c r="N116" s="47">
         <v>6</v>
       </c>
-      <c r="O116" s="49">
+      <c r="O116" s="47">
         <v>6</v>
       </c>
-    </row>
-    <row r="117" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A117" s="50">
+      <c r="Q116" s="20"/>
+    </row>
+    <row r="117" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A117" s="5">
         <v>1051005</v>
       </c>
       <c r="B117" s="5">
@@ -6664,7 +7277,7 @@
       <c r="D117" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="E117" t="s">
+      <c r="E117" s="5" t="s">
         <v>81</v>
       </c>
       <c r="F117" s="5">
@@ -6679,403 +7292,404 @@
       <c r="I117" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L117" s="50">
+      <c r="L117" s="48">
         <v>10510009</v>
       </c>
-      <c r="M117" t="s">
+      <c r="M117" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="N117" s="49">
+      <c r="N117" s="47">
         <v>6</v>
       </c>
-      <c r="O117" s="49">
+      <c r="O117" s="47">
         <v>6</v>
       </c>
-    </row>
-    <row r="118" spans="1:17" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A118" s="43">
+      <c r="Q117" s="20"/>
+    </row>
+    <row r="118" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A118" s="5">
         <v>1054001</v>
       </c>
-      <c r="B118" s="41">
+      <c r="B118" s="5">
         <v>105400</v>
       </c>
-      <c r="C118" s="41">
-        <v>1</v>
-      </c>
-      <c r="D118" s="9" t="s">
+      <c r="C118" s="5">
+        <v>1</v>
+      </c>
+      <c r="D118" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="E118" s="41" t="s">
+      <c r="E118" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="F118" s="41">
-        <v>1</v>
-      </c>
-      <c r="G118" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="H118" s="41">
+      <c r="F118" s="5">
+        <v>1</v>
+      </c>
+      <c r="G118" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H118" s="5">
         <v>2054001</v>
       </c>
-      <c r="I118" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="L118" s="43" t="s">
+      <c r="I118" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L118" s="48" t="s">
         <v>237</v>
       </c>
-      <c r="M118" s="9" t="s">
+      <c r="M118" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="N118" s="65">
+      <c r="N118" s="47">
         <v>6</v>
       </c>
-      <c r="O118" s="65">
+      <c r="O118" s="47">
         <v>6</v>
       </c>
-      <c r="Q118" s="66"/>
-    </row>
-    <row r="119" spans="1:17" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A119" s="43">
+      <c r="Q118" s="20"/>
+    </row>
+    <row r="119" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A119" s="5">
         <v>1054002</v>
       </c>
-      <c r="B119" s="41">
+      <c r="B119" s="5">
         <v>105400</v>
       </c>
-      <c r="C119" s="41">
+      <c r="C119" s="5">
         <v>2</v>
       </c>
-      <c r="D119" s="9" t="s">
+      <c r="D119" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="E119" s="41" t="s">
+      <c r="E119" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F119" s="41">
-        <v>1</v>
-      </c>
-      <c r="G119" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="H119" s="41">
+      <c r="F119" s="5">
+        <v>1</v>
+      </c>
+      <c r="G119" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H119" s="5">
         <v>2054001</v>
       </c>
-      <c r="I119" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="L119" s="43" t="s">
+      <c r="I119" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L119" s="48" t="s">
         <v>239</v>
       </c>
-      <c r="M119" s="9" t="s">
+      <c r="M119" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="N119" s="65">
+      <c r="N119" s="47">
         <v>6</v>
       </c>
-      <c r="O119" s="65">
+      <c r="O119" s="47">
         <v>6</v>
       </c>
-      <c r="Q119" s="66"/>
-    </row>
-    <row r="120" spans="1:17" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A120" s="43">
+      <c r="Q119" s="20"/>
+    </row>
+    <row r="120" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A120" s="5">
         <v>1054003</v>
       </c>
-      <c r="B120" s="41">
+      <c r="B120" s="5">
         <v>105400</v>
       </c>
-      <c r="C120" s="41">
-        <v>3</v>
-      </c>
-      <c r="D120" s="9" t="s">
+      <c r="C120" s="5">
+        <v>3</v>
+      </c>
+      <c r="D120" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="E120" s="41" t="s">
+      <c r="E120" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F120" s="41">
-        <v>1</v>
-      </c>
-      <c r="G120" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="H120" s="41">
+      <c r="F120" s="5">
+        <v>1</v>
+      </c>
+      <c r="G120" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H120" s="5">
         <v>2054001</v>
       </c>
-      <c r="I120" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="L120" s="43" t="s">
+      <c r="I120" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L120" s="48" t="s">
         <v>241</v>
       </c>
-      <c r="M120" s="9" t="s">
+      <c r="M120" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="N120" s="65">
+      <c r="N120" s="47">
         <v>6</v>
       </c>
-      <c r="O120" s="65">
+      <c r="O120" s="47">
         <v>6</v>
       </c>
-      <c r="Q120" s="66"/>
-    </row>
-    <row r="121" spans="1:17" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A121" s="43">
+      <c r="Q120" s="20"/>
+    </row>
+    <row r="121" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A121" s="5">
         <v>1054004</v>
       </c>
-      <c r="B121" s="41">
+      <c r="B121" s="5">
         <v>105400</v>
       </c>
-      <c r="C121" s="41">
+      <c r="C121" s="5">
         <v>4</v>
       </c>
-      <c r="D121" s="9" t="s">
+      <c r="D121" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="E121" s="9" t="s">
+      <c r="E121" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="F121" s="41">
-        <v>1</v>
-      </c>
-      <c r="G121" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="H121" s="41">
+      <c r="F121" s="5">
+        <v>1</v>
+      </c>
+      <c r="G121" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H121" s="5">
         <v>2054001</v>
       </c>
-      <c r="I121" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="L121" s="43" t="s">
+      <c r="I121" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L121" s="48" t="s">
         <v>243</v>
       </c>
-      <c r="M121" s="9" t="s">
+      <c r="M121" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="N121" s="65">
+      <c r="N121" s="47">
         <v>6</v>
       </c>
-      <c r="O121" s="65">
+      <c r="O121" s="47">
         <v>6</v>
       </c>
-      <c r="Q121" s="66"/>
-    </row>
-    <row r="122" spans="1:17" s="10" customFormat="1" ht="17.25" x14ac:dyDescent="0.35">
-      <c r="A122" s="67">
+      <c r="Q121" s="20"/>
+    </row>
+    <row r="122" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A122" s="5">
         <v>1008001</v>
       </c>
-      <c r="B122" s="10">
+      <c r="B122" s="5">
         <v>100800</v>
       </c>
-      <c r="C122" s="10">
-        <v>1</v>
-      </c>
-      <c r="D122" s="10" t="s">
+      <c r="C122" s="5">
+        <v>1</v>
+      </c>
+      <c r="D122" s="5" t="s">
         <v>244</v>
       </c>
       <c r="E122" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="F122" s="10">
+      <c r="F122" s="5">
         <v>1</v>
       </c>
       <c r="G122" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H122" s="68">
+      <c r="H122" s="5">
         <v>2008001</v>
       </c>
       <c r="I122" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L122" s="5" t="s">
+      <c r="L122" s="48" t="s">
         <v>245</v>
       </c>
       <c r="M122" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="N122" s="49">
+      <c r="N122" s="47">
         <v>6</v>
       </c>
-      <c r="O122" s="49">
+      <c r="O122" s="47">
         <v>6</v>
       </c>
-      <c r="Q122" s="69"/>
-    </row>
-    <row r="123" spans="1:17" s="10" customFormat="1" ht="17.25" x14ac:dyDescent="0.35">
-      <c r="A123" s="67">
+      <c r="Q122" s="20"/>
+    </row>
+    <row r="123" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A123" s="5">
         <v>1008002</v>
       </c>
-      <c r="B123" s="10">
+      <c r="B123" s="5">
         <v>100800</v>
       </c>
-      <c r="C123" s="10">
+      <c r="C123" s="5">
         <v>2</v>
       </c>
-      <c r="D123" s="10" t="s">
+      <c r="D123" s="5" t="s">
         <v>244</v>
       </c>
       <c r="E123" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F123" s="10">
+      <c r="F123" s="5">
         <v>1</v>
       </c>
       <c r="G123" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H123" s="68">
+      <c r="H123" s="5">
         <v>2008001</v>
       </c>
       <c r="I123" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L123" s="71" t="s">
-        <v>266</v>
+      <c r="L123" s="48" t="s">
+        <v>247</v>
       </c>
       <c r="M123" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="N123" s="49">
+      <c r="N123" s="47">
         <v>6</v>
       </c>
-      <c r="O123" s="49">
+      <c r="O123" s="47">
         <v>6</v>
       </c>
-      <c r="Q123" s="69"/>
-    </row>
-    <row r="124" spans="1:17" s="10" customFormat="1" ht="17.25" x14ac:dyDescent="0.35">
-      <c r="A124" s="67">
+      <c r="Q123" s="20"/>
+    </row>
+    <row r="124" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A124" s="5">
         <v>1008003</v>
       </c>
-      <c r="B124" s="10">
+      <c r="B124" s="5">
         <v>100800</v>
       </c>
-      <c r="C124" s="10">
-        <v>3</v>
-      </c>
-      <c r="D124" s="10" t="s">
+      <c r="C124" s="5">
+        <v>3</v>
+      </c>
+      <c r="D124" s="5" t="s">
         <v>244</v>
       </c>
       <c r="E124" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F124" s="10">
+      <c r="F124" s="5">
         <v>1</v>
       </c>
       <c r="G124" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H124" s="68">
+      <c r="H124" s="5">
         <v>2008001</v>
       </c>
       <c r="I124" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L124" s="50" t="s">
-        <v>247</v>
+      <c r="L124" s="48" t="s">
+        <v>248</v>
       </c>
       <c r="M124" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="N124" s="49">
+      <c r="N124" s="47">
         <v>6</v>
       </c>
-      <c r="O124" s="49">
+      <c r="O124" s="47">
         <v>6</v>
       </c>
-      <c r="Q124" s="69"/>
-    </row>
-    <row r="125" spans="1:17" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A125" s="52" t="s">
-        <v>248</v>
-      </c>
-      <c r="B125" s="21">
+      <c r="Q124" s="20"/>
+    </row>
+    <row r="125" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A125" s="5">
+        <v>1053001</v>
+      </c>
+      <c r="B125" s="5">
         <v>105300</v>
       </c>
-      <c r="C125" s="21">
-        <v>1</v>
-      </c>
-      <c r="D125" s="70" t="s">
+      <c r="C125" s="5">
+        <v>1</v>
+      </c>
+      <c r="D125" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="E125" s="70" t="s">
+      <c r="E125" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F125" s="21">
-        <v>1</v>
-      </c>
-      <c r="G125" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="H125" s="51">
+      <c r="F125" s="5">
+        <v>1</v>
+      </c>
+      <c r="G125" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H125" s="5">
         <v>2053001</v>
       </c>
-      <c r="I125" s="51" t="s">
-        <v>24</v>
-      </c>
-      <c r="J125" s="51"/>
-      <c r="K125" s="51"/>
-      <c r="L125" s="52" t="s">
+      <c r="I125" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J125" s="5"/>
+      <c r="K125" s="5"/>
+      <c r="L125" s="48" t="s">
         <v>250</v>
       </c>
-      <c r="M125" s="51" t="s">
+      <c r="M125" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="N125" s="21">
-        <v>5</v>
-      </c>
-      <c r="O125" s="21">
-        <v>5</v>
-      </c>
-      <c r="Q125" s="48"/>
-    </row>
-    <row r="126" spans="1:17" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A126" s="52" t="s">
+      <c r="N125" s="47">
+        <v>5</v>
+      </c>
+      <c r="O125" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q125" s="20"/>
+    </row>
+    <row r="126" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A126" s="5">
+        <v>1053002</v>
+      </c>
+      <c r="B126" s="5">
+        <v>105300</v>
+      </c>
+      <c r="C126" s="5">
+        <v>2</v>
+      </c>
+      <c r="D126" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="E126" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F126" s="5">
+        <v>1</v>
+      </c>
+      <c r="G126" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H126" s="5">
+        <v>2053001</v>
+      </c>
+      <c r="I126" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J126" s="5"/>
+      <c r="K126" s="5"/>
+      <c r="L126" s="48" t="s">
         <v>252</v>
       </c>
-      <c r="B126" s="21">
-        <v>105300</v>
-      </c>
-      <c r="C126" s="21">
-        <v>2</v>
-      </c>
-      <c r="D126" s="70" t="s">
-        <v>249</v>
-      </c>
-      <c r="E126" s="70" t="s">
-        <v>55</v>
-      </c>
-      <c r="F126" s="21">
-        <v>1</v>
-      </c>
-      <c r="G126" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="H126" s="51">
-        <v>2053001</v>
-      </c>
-      <c r="I126" s="51" t="s">
-        <v>24</v>
-      </c>
-      <c r="J126" s="51"/>
-      <c r="K126" s="51"/>
-      <c r="L126" s="52" t="s">
+      <c r="M126" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="M126" s="51" t="s">
-        <v>254</v>
-      </c>
-      <c r="N126" s="21">
-        <v>5</v>
-      </c>
-      <c r="O126" s="21">
-        <v>5</v>
-      </c>
-      <c r="Q126" s="48"/>
-    </row>
-    <row r="127" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A127" s="50">
+      <c r="N126" s="47">
+        <v>5</v>
+      </c>
+      <c r="O126" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q126" s="20"/>
+    </row>
+    <row r="127" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A127" s="5">
         <v>1057001</v>
       </c>
       <c r="B127" s="5">
@@ -7085,39 +7699,39 @@
         <v>1</v>
       </c>
       <c r="D127" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="E127" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F127" s="5">
+        <v>1</v>
+      </c>
+      <c r="G127" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H127" s="5">
+        <v>2057001</v>
+      </c>
+      <c r="I127" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L127" s="48" t="s">
         <v>255</v>
       </c>
-      <c r="E127" s="70" t="s">
-        <v>22</v>
-      </c>
-      <c r="F127" s="21">
-        <v>1</v>
-      </c>
-      <c r="G127" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="H127" s="51">
-        <v>2057001</v>
-      </c>
-      <c r="I127" s="51" t="s">
-        <v>24</v>
-      </c>
-      <c r="L127" s="5" t="s">
+      <c r="M127" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="M127" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="N127" s="49">
+      <c r="N127" s="47">
         <v>6</v>
       </c>
-      <c r="O127" s="49">
-        <v>5</v>
-      </c>
-      <c r="Q127" s="22"/>
-    </row>
-    <row r="128" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A128" s="50">
+      <c r="O127" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q127" s="20"/>
+    </row>
+    <row r="128" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A128" s="5">
         <v>1057002</v>
       </c>
       <c r="B128" s="5">
@@ -7127,39 +7741,39 @@
         <v>2</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="E128" s="70" t="s">
+        <v>254</v>
+      </c>
+      <c r="E128" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="F128" s="21">
-        <v>1</v>
-      </c>
-      <c r="G128" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="H128" s="51">
+      <c r="F128" s="5">
+        <v>1</v>
+      </c>
+      <c r="G128" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H128" s="5">
         <v>2057001</v>
       </c>
-      <c r="I128" s="51" t="s">
-        <v>24</v>
-      </c>
-      <c r="L128" s="50" t="s">
+      <c r="I128" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L128" s="48" t="s">
+        <v>257</v>
+      </c>
+      <c r="M128" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="M128" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="N128" s="49">
+      <c r="N128" s="47">
         <v>6</v>
       </c>
-      <c r="O128" s="49">
-        <v>5</v>
-      </c>
-      <c r="Q128" s="22"/>
-    </row>
-    <row r="129" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A129" s="50">
+      <c r="O128" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q128" s="20"/>
+    </row>
+    <row r="129" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A129" s="5">
         <v>1057003</v>
       </c>
       <c r="B129" s="5">
@@ -7169,38 +7783,39 @@
         <v>3</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E129" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F129" s="21">
-        <v>1</v>
-      </c>
-      <c r="G129" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="H129" s="51">
+      <c r="F129" s="5">
+        <v>1</v>
+      </c>
+      <c r="G129" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H129" s="5">
         <v>2057001</v>
       </c>
-      <c r="I129" s="51" t="s">
-        <v>24</v>
-      </c>
-      <c r="L129" s="5" t="s">
+      <c r="I129" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L129" s="48" t="s">
+        <v>259</v>
+      </c>
+      <c r="M129" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="M129" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="N129" s="49">
+      <c r="N129" s="47">
         <v>6</v>
       </c>
-      <c r="O129" s="49">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="130" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A130" s="50">
+      <c r="O129" s="47">
+        <v>5</v>
+      </c>
+      <c r="Q129" s="20"/>
+    </row>
+    <row r="130" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A130" s="5">
         <v>1058001</v>
       </c>
       <c r="B130" s="5">
@@ -7210,39 +7825,39 @@
         <v>1</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="E130" s="70" t="s">
+        <v>261</v>
+      </c>
+      <c r="E130" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F130" s="21">
-        <v>1</v>
-      </c>
-      <c r="G130" s="51" t="s">
+      <c r="F130" s="5">
+        <v>1</v>
+      </c>
+      <c r="G130" s="5" t="s">
         <v>23</v>
       </c>
       <c r="H130" s="5">
         <v>2058001</v>
       </c>
-      <c r="I130" s="51" t="s">
-        <v>24</v>
-      </c>
-      <c r="L130" s="50">
+      <c r="I130" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L130" s="48">
         <v>10580001</v>
       </c>
       <c r="M130" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="N130" s="49">
+        <v>262</v>
+      </c>
+      <c r="N130" s="47">
         <v>7</v>
       </c>
-      <c r="O130" s="49">
+      <c r="O130" s="47">
         <v>7</v>
       </c>
-      <c r="Q130" s="22"/>
-    </row>
-    <row r="131" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A131" s="50">
+      <c r="Q130" s="20"/>
+    </row>
+    <row r="131" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A131" s="5">
         <v>1058002</v>
       </c>
       <c r="B131" s="5">
@@ -7252,39 +7867,39 @@
         <v>2</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="E131" s="70" t="s">
+        <v>261</v>
+      </c>
+      <c r="E131" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="F131" s="21">
-        <v>1</v>
-      </c>
-      <c r="G131" s="51" t="s">
+      <c r="F131" s="5">
+        <v>1</v>
+      </c>
+      <c r="G131" s="5" t="s">
         <v>23</v>
       </c>
       <c r="H131" s="5">
         <v>2058001</v>
       </c>
-      <c r="I131" s="51" t="s">
-        <v>24</v>
-      </c>
-      <c r="L131" s="50">
+      <c r="I131" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L131" s="48">
         <v>10580002</v>
       </c>
       <c r="M131" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="N131" s="49">
+        <v>263</v>
+      </c>
+      <c r="N131" s="47">
         <v>7</v>
       </c>
-      <c r="O131" s="49">
+      <c r="O131" s="47">
         <v>7</v>
       </c>
-      <c r="Q131" s="22"/>
-    </row>
-    <row r="132" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A132" s="50">
+      <c r="Q131" s="20"/>
+    </row>
+    <row r="132" s="5" customFormat="1" ht="16.5" spans="1:17">
+      <c r="A132" s="5">
         <v>1058003</v>
       </c>
       <c r="B132" s="5">
@@ -7294,45 +7909,50 @@
         <v>3</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E132" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F132" s="21">
-        <v>1</v>
-      </c>
-      <c r="G132" s="51" t="s">
+      <c r="F132" s="5">
+        <v>1</v>
+      </c>
+      <c r="G132" s="5" t="s">
         <v>23</v>
       </c>
       <c r="H132" s="5">
         <v>2058001</v>
       </c>
-      <c r="I132" s="51" t="s">
-        <v>24</v>
-      </c>
-      <c r="L132" s="50">
+      <c r="I132" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L132" s="48">
         <v>10580003</v>
       </c>
       <c r="M132" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="N132" s="49">
+        <v>264</v>
+      </c>
+      <c r="N132" s="47">
         <v>7</v>
       </c>
-      <c r="O132" s="49">
+      <c r="O132" s="47">
         <v>7</v>
       </c>
-      <c r="Q132" s="22"/>
+      <c r="Q132" s="20"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
-  <conditionalFormatting sqref="J2:L2">
+  <conditionalFormatting sqref="J2:K2">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD(MID($A2,1,4),2)=1</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="L2">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>MOD(MID($A2,1,4),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/SpecialMode.xlsx
+++ b/slots/resources/sample/SpecialMode.xlsx
@@ -572,7 +572,7 @@
     <t>恶魔之子</t>
   </si>
   <si>
-    <t>10380001_1|10380004_1|10380005_1</t>
+    <t>10380001_10|10380004_1|10380005_1</t>
   </si>
   <si>
     <t>概率改出wild+概率改出奖金符号+改出奖池符号</t>
